--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="167">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,267 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Peruvian Primera Division</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie A</t>
+  </si>
+  <si>
+    <t>Chilean Primera Division</t>
+  </si>
+  <si>
+    <t>Mexican Liga MX</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Latvian Virsliga</t>
+  </si>
+  <si>
+    <t>Slovakian 2 Liga</t>
+  </si>
+  <si>
+    <t>Romanian Liga I</t>
+  </si>
+  <si>
+    <t>Bulgarian A League</t>
+  </si>
+  <si>
+    <t>Czech 1 Liga</t>
+  </si>
+  <si>
+    <t>Swedish Superettan</t>
+  </si>
+  <si>
+    <t>Swedish Allsvenskan</t>
+  </si>
+  <si>
+    <t>Polish I Liga</t>
+  </si>
+  <si>
+    <t>Norwegian 1st Division</t>
+  </si>
+  <si>
+    <t>Norwegian Eliteserien</t>
+  </si>
+  <si>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
+    <t>Polish Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Hungarian NB I</t>
+  </si>
+  <si>
+    <t>Icelandic Urvalsdeild</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:15:00</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>01:06:00</t>
+  </si>
+  <si>
+    <t>01:15:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>17:05:00</t>
+  </si>
+  <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>18:15:00</t>
+  </si>
+  <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>19:15:00</t>
+  </si>
+  <si>
+    <t>Deportivo Garcilaso</t>
+  </si>
+  <si>
+    <t>Barcelona (Ecu)</t>
+  </si>
+  <si>
+    <t>Deportes Concepcion</t>
+  </si>
+  <si>
+    <t>Pachuca</t>
+  </si>
+  <si>
+    <t>Once Caldas</t>
+  </si>
+  <si>
+    <t>FK Tukums 2000</t>
+  </si>
+  <si>
+    <t>Samorin</t>
+  </si>
+  <si>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>Dunav Ruse</t>
+  </si>
+  <si>
+    <t>SK Artis Brno</t>
+  </si>
+  <si>
+    <t>SC Grobina</t>
+  </si>
+  <si>
+    <t>Orebro</t>
+  </si>
+  <si>
+    <t>Hacken</t>
+  </si>
+  <si>
+    <t>Miedz Legnica</t>
+  </si>
+  <si>
+    <t>Stabaek</t>
+  </si>
+  <si>
+    <t>Rosenborg</t>
+  </si>
+  <si>
+    <t>Randers</t>
+  </si>
+  <si>
+    <t>Zaglebie Lubin</t>
+  </si>
+  <si>
+    <t>Osters</t>
+  </si>
+  <si>
+    <t>MTK Budapest</t>
+  </si>
+  <si>
+    <t>Breidablik</t>
+  </si>
+  <si>
+    <t>CSKA Sofia</t>
+  </si>
+  <si>
+    <t>Botosani</t>
+  </si>
+  <si>
+    <t>Mushuc Runa</t>
+  </si>
+  <si>
+    <t>KA Akureyri</t>
+  </si>
+  <si>
+    <t>FC Cajamarca</t>
+  </si>
+  <si>
+    <t>LDU</t>
+  </si>
+  <si>
+    <t>OHiggins</t>
+  </si>
+  <si>
+    <t>Queretaro</t>
+  </si>
+  <si>
+    <t>Cucuta Deportivo</t>
+  </si>
+  <si>
+    <t>Rigas Futbola Skola</t>
+  </si>
+  <si>
+    <t>Malzenice</t>
+  </si>
+  <si>
+    <t>FC Voluntari</t>
+  </si>
+  <si>
+    <t>Ludogorets</t>
+  </si>
+  <si>
+    <t>Mlada Boleslav</t>
+  </si>
+  <si>
+    <t>Ogre United</t>
+  </si>
+  <si>
+    <t>Oddevold</t>
+  </si>
+  <si>
+    <t>AIK</t>
+  </si>
+  <si>
+    <t>Podbeskidzie B-B</t>
+  </si>
+  <si>
+    <t>Hodd</t>
+  </si>
+  <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
+    <t>Piast Gliwice</t>
+  </si>
+  <si>
+    <t>Varbergs BoIS</t>
+  </si>
+  <si>
+    <t>Zalaegerszeg</t>
+  </si>
+  <si>
+    <t>IBV</t>
+  </si>
+  <si>
+    <t>Botev Plovdiv</t>
+  </si>
+  <si>
+    <t>Rapid Bucharest</t>
+  </si>
+  <si>
+    <t>Libertad FC</t>
+  </si>
+  <si>
+    <t>Thor</t>
+  </si>
+  <si>
+    <t>2026-07-25 00:47:14</t>
   </si>
 </sst>
 </file>
@@ -585,7 +846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +1089,6056 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2">
+        <v>1.04</v>
+      </c>
+      <c r="G2">
+        <v>1.78</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>1000</v>
+      </c>
+      <c r="J2">
+        <v>3.5</v>
+      </c>
+      <c r="K2">
+        <v>1000</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.01</v>
+      </c>
+      <c r="N2">
+        <v>1.72</v>
+      </c>
+      <c r="O2">
+        <v>1.33</v>
+      </c>
+      <c r="P2">
+        <v>1.72</v>
+      </c>
+      <c r="Q2">
+        <v>1.85</v>
+      </c>
+      <c r="R2">
+        <v>1.28</v>
+      </c>
+      <c r="S2">
+        <v>3.25</v>
+      </c>
+      <c r="T2">
+        <v>1.01</v>
+      </c>
+      <c r="U2">
+        <v>1.01</v>
+      </c>
+      <c r="V2">
+        <v>1.01</v>
+      </c>
+      <c r="W2">
+        <v>2.38</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>10</v>
+      </c>
+      <c r="AQ2">
+        <v>15</v>
+      </c>
+      <c r="AR2">
+        <v>34</v>
+      </c>
+      <c r="AS2">
+        <v>40</v>
+      </c>
+      <c r="AT2">
+        <v>5.8</v>
+      </c>
+      <c r="AU2">
+        <v>7.4</v>
+      </c>
+      <c r="AV2">
+        <v>18.5</v>
+      </c>
+      <c r="AW2">
+        <v>40</v>
+      </c>
+      <c r="AX2">
+        <v>6.8</v>
+      </c>
+      <c r="AY2">
+        <v>8.4</v>
+      </c>
+      <c r="AZ2">
+        <v>18.5</v>
+      </c>
+      <c r="BA2">
+        <v>40</v>
+      </c>
+      <c r="BB2">
+        <v>11</v>
+      </c>
+      <c r="BC2">
+        <v>14.5</v>
+      </c>
+      <c r="BD2">
+        <v>28</v>
+      </c>
+      <c r="BE2">
+        <v>40</v>
+      </c>
+      <c r="BF2">
+        <v>1.01</v>
+      </c>
+      <c r="BG2">
+        <v>1.01</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F3">
+        <v>2.2</v>
+      </c>
+      <c r="G3">
+        <v>2.44</v>
+      </c>
+      <c r="H3">
+        <v>3.55</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>3.1</v>
+      </c>
+      <c r="K3">
+        <v>3.45</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>1.67</v>
+      </c>
+      <c r="O3">
+        <v>1.41</v>
+      </c>
+      <c r="P3">
+        <v>1.67</v>
+      </c>
+      <c r="Q3">
+        <v>2.24</v>
+      </c>
+      <c r="R3">
+        <v>1.21</v>
+      </c>
+      <c r="S3">
+        <v>3.6</v>
+      </c>
+      <c r="T3">
+        <v>1.01</v>
+      </c>
+      <c r="U3">
+        <v>1.01</v>
+      </c>
+      <c r="V3">
+        <v>1.33</v>
+      </c>
+      <c r="W3">
+        <v>1.69</v>
+      </c>
+      <c r="X3">
+        <v>15.5</v>
+      </c>
+      <c r="Y3">
+        <v>17</v>
+      </c>
+      <c r="Z3">
+        <v>38</v>
+      </c>
+      <c r="AA3">
+        <v>100</v>
+      </c>
+      <c r="AB3">
+        <v>11.5</v>
+      </c>
+      <c r="AC3">
+        <v>10.5</v>
+      </c>
+      <c r="AD3">
+        <v>23</v>
+      </c>
+      <c r="AE3">
+        <v>75</v>
+      </c>
+      <c r="AF3">
+        <v>20</v>
+      </c>
+      <c r="AG3">
+        <v>17</v>
+      </c>
+      <c r="AH3">
+        <v>30</v>
+      </c>
+      <c r="AI3">
+        <v>100</v>
+      </c>
+      <c r="AJ3">
+        <v>46</v>
+      </c>
+      <c r="AK3">
+        <v>40</v>
+      </c>
+      <c r="AL3">
+        <v>70</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>2.2</v>
+      </c>
+      <c r="AQ3">
+        <v>2.22</v>
+      </c>
+      <c r="AR3">
+        <v>2.4</v>
+      </c>
+      <c r="AS3">
+        <v>2.5</v>
+      </c>
+      <c r="AT3">
+        <v>2.1</v>
+      </c>
+      <c r="AU3">
+        <v>2.06</v>
+      </c>
+      <c r="AV3">
+        <v>2.3</v>
+      </c>
+      <c r="AW3">
+        <v>2.48</v>
+      </c>
+      <c r="AX3">
+        <v>9.4</v>
+      </c>
+      <c r="AY3">
+        <v>2.22</v>
+      </c>
+      <c r="AZ3">
+        <v>2.36</v>
+      </c>
+      <c r="BA3">
+        <v>2.5</v>
+      </c>
+      <c r="BB3">
+        <v>2.42</v>
+      </c>
+      <c r="BC3">
+        <v>19</v>
+      </c>
+      <c r="BD3">
+        <v>2.48</v>
+      </c>
+      <c r="BE3">
+        <v>2.56</v>
+      </c>
+      <c r="BF3">
+        <v>2.56</v>
+      </c>
+      <c r="BG3">
+        <v>2.56</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.01</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F4">
+        <v>2.4</v>
+      </c>
+      <c r="G4">
+        <v>2.64</v>
+      </c>
+      <c r="H4">
+        <v>2.96</v>
+      </c>
+      <c r="I4">
+        <v>3.2</v>
+      </c>
+      <c r="J4">
+        <v>3.45</v>
+      </c>
+      <c r="K4">
+        <v>3.85</v>
+      </c>
+      <c r="L4">
+        <v>1.41</v>
+      </c>
+      <c r="M4">
+        <v>1.07</v>
+      </c>
+      <c r="N4">
+        <v>3.55</v>
+      </c>
+      <c r="O4">
+        <v>1.32</v>
+      </c>
+      <c r="P4">
+        <v>1.96</v>
+      </c>
+      <c r="Q4">
+        <v>1.94</v>
+      </c>
+      <c r="R4">
+        <v>1.34</v>
+      </c>
+      <c r="S4">
+        <v>3.4</v>
+      </c>
+      <c r="T4">
+        <v>1.75</v>
+      </c>
+      <c r="U4">
+        <v>2.12</v>
+      </c>
+      <c r="V4">
+        <v>1.45</v>
+      </c>
+      <c r="W4">
+        <v>1.61</v>
+      </c>
+      <c r="X4">
+        <v>16.5</v>
+      </c>
+      <c r="Y4">
+        <v>12.5</v>
+      </c>
+      <c r="Z4">
+        <v>22</v>
+      </c>
+      <c r="AA4">
+        <v>55</v>
+      </c>
+      <c r="AB4">
+        <v>11</v>
+      </c>
+      <c r="AC4">
+        <v>8.4</v>
+      </c>
+      <c r="AD4">
+        <v>14</v>
+      </c>
+      <c r="AE4">
+        <v>36</v>
+      </c>
+      <c r="AF4">
+        <v>17</v>
+      </c>
+      <c r="AG4">
+        <v>13</v>
+      </c>
+      <c r="AH4">
+        <v>18</v>
+      </c>
+      <c r="AI4">
+        <v>46</v>
+      </c>
+      <c r="AJ4">
+        <v>38</v>
+      </c>
+      <c r="AK4">
+        <v>29</v>
+      </c>
+      <c r="AL4">
+        <v>40</v>
+      </c>
+      <c r="AM4">
+        <v>110</v>
+      </c>
+      <c r="AN4">
+        <v>24</v>
+      </c>
+      <c r="AO4">
+        <v>38</v>
+      </c>
+      <c r="AP4">
+        <v>12</v>
+      </c>
+      <c r="AQ4">
+        <v>10</v>
+      </c>
+      <c r="AR4">
+        <v>18</v>
+      </c>
+      <c r="AS4">
+        <v>42</v>
+      </c>
+      <c r="AT4">
+        <v>9</v>
+      </c>
+      <c r="AU4">
+        <v>7</v>
+      </c>
+      <c r="AV4">
+        <v>11.5</v>
+      </c>
+      <c r="AW4">
+        <v>7.2</v>
+      </c>
+      <c r="AX4">
+        <v>14</v>
+      </c>
+      <c r="AY4">
+        <v>10</v>
+      </c>
+      <c r="AZ4">
+        <v>15</v>
+      </c>
+      <c r="BA4">
+        <v>38</v>
+      </c>
+      <c r="BB4">
+        <v>27</v>
+      </c>
+      <c r="BC4">
+        <v>6.8</v>
+      </c>
+      <c r="BD4">
+        <v>7.2</v>
+      </c>
+      <c r="BE4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF4">
+        <v>20</v>
+      </c>
+      <c r="BG4">
+        <v>7.2</v>
+      </c>
+      <c r="BH4">
+        <v>3.4</v>
+      </c>
+      <c r="BI4">
+        <v>2.76</v>
+      </c>
+      <c r="BJ4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK4">
+        <v>5.3</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>10.5</v>
+      </c>
+      <c r="BN4">
+        <v>5.7</v>
+      </c>
+      <c r="BO4">
+        <v>4.4</v>
+      </c>
+      <c r="BP4">
+        <v>20</v>
+      </c>
+      <c r="BQ4">
+        <v>7.4</v>
+      </c>
+      <c r="BR4">
+        <v>34</v>
+      </c>
+      <c r="BS4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT4">
+        <v>6.4</v>
+      </c>
+      <c r="BU4">
+        <v>4.8</v>
+      </c>
+      <c r="BV4">
+        <v>25</v>
+      </c>
+      <c r="BW4">
+        <v>8</v>
+      </c>
+      <c r="BX4">
+        <v>38</v>
+      </c>
+      <c r="BY4">
+        <v>9</v>
+      </c>
+      <c r="BZ4">
+        <v>29</v>
+      </c>
+      <c r="CA4">
+        <v>8.4</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F5">
+        <v>1.58</v>
+      </c>
+      <c r="G5">
+        <v>1.64</v>
+      </c>
+      <c r="H5">
+        <v>6.4</v>
+      </c>
+      <c r="I5">
+        <v>6.8</v>
+      </c>
+      <c r="J5">
+        <v>4.3</v>
+      </c>
+      <c r="K5">
+        <v>4.7</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.05</v>
+      </c>
+      <c r="N5">
+        <v>4.4</v>
+      </c>
+      <c r="O5">
+        <v>1.24</v>
+      </c>
+      <c r="P5">
+        <v>2.2</v>
+      </c>
+      <c r="Q5">
+        <v>1.71</v>
+      </c>
+      <c r="R5">
+        <v>1.47</v>
+      </c>
+      <c r="S5">
+        <v>2.76</v>
+      </c>
+      <c r="T5">
+        <v>1.8</v>
+      </c>
+      <c r="U5">
+        <v>2.06</v>
+      </c>
+      <c r="V5">
+        <v>1.17</v>
+      </c>
+      <c r="W5">
+        <v>2.56</v>
+      </c>
+      <c r="X5">
+        <v>21</v>
+      </c>
+      <c r="Y5">
+        <v>25</v>
+      </c>
+      <c r="Z5">
+        <v>55</v>
+      </c>
+      <c r="AA5">
+        <v>180</v>
+      </c>
+      <c r="AB5">
+        <v>10.5</v>
+      </c>
+      <c r="AC5">
+        <v>11</v>
+      </c>
+      <c r="AD5">
+        <v>25</v>
+      </c>
+      <c r="AE5">
+        <v>85</v>
+      </c>
+      <c r="AF5">
+        <v>11</v>
+      </c>
+      <c r="AG5">
+        <v>11</v>
+      </c>
+      <c r="AH5">
+        <v>22</v>
+      </c>
+      <c r="AI5">
+        <v>75</v>
+      </c>
+      <c r="AJ5">
+        <v>16.5</v>
+      </c>
+      <c r="AK5">
+        <v>17</v>
+      </c>
+      <c r="AL5">
+        <v>34</v>
+      </c>
+      <c r="AM5">
+        <v>120</v>
+      </c>
+      <c r="AN5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO5">
+        <v>90</v>
+      </c>
+      <c r="AP5">
+        <v>15.5</v>
+      </c>
+      <c r="AQ5">
+        <v>17.5</v>
+      </c>
+      <c r="AR5">
+        <v>7.2</v>
+      </c>
+      <c r="AS5">
+        <v>7.8</v>
+      </c>
+      <c r="AT5">
+        <v>8.4</v>
+      </c>
+      <c r="AU5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV5">
+        <v>18</v>
+      </c>
+      <c r="AW5">
+        <v>7.4</v>
+      </c>
+      <c r="AX5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY5">
+        <v>8.6</v>
+      </c>
+      <c r="AZ5">
+        <v>15.5</v>
+      </c>
+      <c r="BA5">
+        <v>7.8</v>
+      </c>
+      <c r="BB5">
+        <v>12</v>
+      </c>
+      <c r="BC5">
+        <v>12.5</v>
+      </c>
+      <c r="BD5">
+        <v>6.6</v>
+      </c>
+      <c r="BE5">
+        <v>7.6</v>
+      </c>
+      <c r="BF5">
+        <v>6.6</v>
+      </c>
+      <c r="BG5">
+        <v>7.6</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>1.01</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>1.01</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>1.01</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.01</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.01</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.01</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F6">
+        <v>1.46</v>
+      </c>
+      <c r="G6">
+        <v>1.54</v>
+      </c>
+      <c r="H6">
+        <v>7.6</v>
+      </c>
+      <c r="I6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J6">
+        <v>4.3</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.06</v>
+      </c>
+      <c r="N6">
+        <v>3.9</v>
+      </c>
+      <c r="O6">
+        <v>1.28</v>
+      </c>
+      <c r="P6">
+        <v>1.99</v>
+      </c>
+      <c r="Q6">
+        <v>1.83</v>
+      </c>
+      <c r="R6">
+        <v>1.39</v>
+      </c>
+      <c r="S6">
+        <v>3.1</v>
+      </c>
+      <c r="T6">
+        <v>2.02</v>
+      </c>
+      <c r="U6">
+        <v>1.81</v>
+      </c>
+      <c r="V6">
+        <v>1.12</v>
+      </c>
+      <c r="W6">
+        <v>2.84</v>
+      </c>
+      <c r="X6">
+        <v>19.5</v>
+      </c>
+      <c r="Y6">
+        <v>32</v>
+      </c>
+      <c r="Z6">
+        <v>90</v>
+      </c>
+      <c r="AA6">
+        <v>340</v>
+      </c>
+      <c r="AB6">
+        <v>8.4</v>
+      </c>
+      <c r="AC6">
+        <v>11</v>
+      </c>
+      <c r="AD6">
+        <v>34</v>
+      </c>
+      <c r="AE6">
+        <v>160</v>
+      </c>
+      <c r="AF6">
+        <v>10</v>
+      </c>
+      <c r="AG6">
+        <v>12.5</v>
+      </c>
+      <c r="AH6">
+        <v>32</v>
+      </c>
+      <c r="AI6">
+        <v>140</v>
+      </c>
+      <c r="AJ6">
+        <v>14</v>
+      </c>
+      <c r="AK6">
+        <v>19.5</v>
+      </c>
+      <c r="AL6">
+        <v>42</v>
+      </c>
+      <c r="AM6">
+        <v>180</v>
+      </c>
+      <c r="AN6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO6">
+        <v>220</v>
+      </c>
+      <c r="AP6">
+        <v>13.5</v>
+      </c>
+      <c r="AQ6">
+        <v>18</v>
+      </c>
+      <c r="AR6">
+        <v>5.9</v>
+      </c>
+      <c r="AS6">
+        <v>6.2</v>
+      </c>
+      <c r="AT6">
+        <v>7</v>
+      </c>
+      <c r="AU6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV6">
+        <v>5.3</v>
+      </c>
+      <c r="AW6">
+        <v>6</v>
+      </c>
+      <c r="AX6">
+        <v>6.4</v>
+      </c>
+      <c r="AY6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ6">
+        <v>18.5</v>
+      </c>
+      <c r="BA6">
+        <v>6</v>
+      </c>
+      <c r="BB6">
+        <v>9.6</v>
+      </c>
+      <c r="BC6">
+        <v>13.5</v>
+      </c>
+      <c r="BD6">
+        <v>28</v>
+      </c>
+      <c r="BE6">
+        <v>6</v>
+      </c>
+      <c r="BF6">
+        <v>5.9</v>
+      </c>
+      <c r="BG6">
+        <v>6.2</v>
+      </c>
+      <c r="BH6">
+        <v>3.75</v>
+      </c>
+      <c r="BI6">
+        <v>2.9</v>
+      </c>
+      <c r="BJ6">
+        <v>12</v>
+      </c>
+      <c r="BK6">
+        <v>5.6</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN6">
+        <v>4.1</v>
+      </c>
+      <c r="BO6">
+        <v>3.05</v>
+      </c>
+      <c r="BP6">
+        <v>9.6</v>
+      </c>
+      <c r="BQ6">
+        <v>5</v>
+      </c>
+      <c r="BR6">
+        <v>27</v>
+      </c>
+      <c r="BS6">
+        <v>7.4</v>
+      </c>
+      <c r="BT6">
+        <v>12</v>
+      </c>
+      <c r="BU6">
+        <v>5.6</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ6">
+        <v>18</v>
+      </c>
+      <c r="CA6">
+        <v>6.6</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F7">
+        <v>1.04</v>
+      </c>
+      <c r="G7">
+        <v>1000</v>
+      </c>
+      <c r="H7">
+        <v>1.04</v>
+      </c>
+      <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="J7">
+        <v>1.01</v>
+      </c>
+      <c r="K7">
+        <v>410</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.24</v>
+      </c>
+      <c r="Q7">
+        <v>1.01</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" t="s">
+        <v>147</v>
+      </c>
+      <c r="F8">
+        <v>2.02</v>
+      </c>
+      <c r="G8">
+        <v>2.38</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
+        <v>4.2</v>
+      </c>
+      <c r="J8">
+        <v>3.35</v>
+      </c>
+      <c r="K8">
+        <v>5.8</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
+        <v>3.45</v>
+      </c>
+      <c r="O8">
+        <v>1.25</v>
+      </c>
+      <c r="P8">
+        <v>2</v>
+      </c>
+      <c r="Q8">
+        <v>1.74</v>
+      </c>
+      <c r="R8">
+        <v>1.37</v>
+      </c>
+      <c r="S8">
+        <v>2.82</v>
+      </c>
+      <c r="T8">
+        <v>1.01</v>
+      </c>
+      <c r="U8">
+        <v>1.01</v>
+      </c>
+      <c r="V8">
+        <v>1.31</v>
+      </c>
+      <c r="W8">
+        <v>1.73</v>
+      </c>
+      <c r="X8">
+        <v>1000</v>
+      </c>
+      <c r="Y8">
+        <v>1000</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>1000</v>
+      </c>
+      <c r="AC8">
+        <v>1000</v>
+      </c>
+      <c r="AD8">
+        <v>1000</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>1000</v>
+      </c>
+      <c r="AG8">
+        <v>1000</v>
+      </c>
+      <c r="AH8">
+        <v>1000</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>1000</v>
+      </c>
+      <c r="AL8">
+        <v>1000</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8">
+        <v>1.03</v>
+      </c>
+      <c r="AR8">
+        <v>1.03</v>
+      </c>
+      <c r="AS8">
+        <v>1.03</v>
+      </c>
+      <c r="AT8">
+        <v>1.03</v>
+      </c>
+      <c r="AU8">
+        <v>1.03</v>
+      </c>
+      <c r="AV8">
+        <v>1.03</v>
+      </c>
+      <c r="AW8">
+        <v>1.03</v>
+      </c>
+      <c r="AX8">
+        <v>1.03</v>
+      </c>
+      <c r="AY8">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8">
+        <v>1.03</v>
+      </c>
+      <c r="BA8">
+        <v>1.03</v>
+      </c>
+      <c r="BB8">
+        <v>1.03</v>
+      </c>
+      <c r="BC8">
+        <v>1.03</v>
+      </c>
+      <c r="BD8">
+        <v>1.03</v>
+      </c>
+      <c r="BE8">
+        <v>1.03</v>
+      </c>
+      <c r="BF8">
+        <v>1.01</v>
+      </c>
+      <c r="BG8">
+        <v>1.01</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>1.01</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
+        <v>1.01</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>1.01</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>1.01</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
+        <v>1.01</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
+        <v>1.01</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F9">
+        <v>1.89</v>
+      </c>
+      <c r="G9">
+        <v>1.94</v>
+      </c>
+      <c r="H9">
+        <v>4.5</v>
+      </c>
+      <c r="I9">
+        <v>4.9</v>
+      </c>
+      <c r="J9">
+        <v>3.65</v>
+      </c>
+      <c r="K9">
+        <v>3.8</v>
+      </c>
+      <c r="L9">
+        <v>1.34</v>
+      </c>
+      <c r="M9">
+        <v>1.07</v>
+      </c>
+      <c r="N9">
+        <v>3.55</v>
+      </c>
+      <c r="O9">
+        <v>1.33</v>
+      </c>
+      <c r="P9">
+        <v>1.89</v>
+      </c>
+      <c r="Q9">
+        <v>1.98</v>
+      </c>
+      <c r="R9">
+        <v>1.34</v>
+      </c>
+      <c r="S9">
+        <v>3.5</v>
+      </c>
+      <c r="T9">
+        <v>1.82</v>
+      </c>
+      <c r="U9">
+        <v>2.04</v>
+      </c>
+      <c r="V9">
+        <v>1.25</v>
+      </c>
+      <c r="W9">
+        <v>2.06</v>
+      </c>
+      <c r="X9">
+        <v>16.5</v>
+      </c>
+      <c r="Y9">
+        <v>15.5</v>
+      </c>
+      <c r="Z9">
+        <v>36</v>
+      </c>
+      <c r="AA9">
+        <v>120</v>
+      </c>
+      <c r="AB9">
+        <v>10</v>
+      </c>
+      <c r="AC9">
+        <v>9.6</v>
+      </c>
+      <c r="AD9">
+        <v>18.5</v>
+      </c>
+      <c r="AE9">
+        <v>65</v>
+      </c>
+      <c r="AF9">
+        <v>15</v>
+      </c>
+      <c r="AG9">
+        <v>12.5</v>
+      </c>
+      <c r="AH9">
+        <v>22</v>
+      </c>
+      <c r="AI9">
+        <v>65</v>
+      </c>
+      <c r="AJ9">
+        <v>27</v>
+      </c>
+      <c r="AK9">
+        <v>23</v>
+      </c>
+      <c r="AL9">
+        <v>44</v>
+      </c>
+      <c r="AM9">
+        <v>120</v>
+      </c>
+      <c r="AN9">
+        <v>17</v>
+      </c>
+      <c r="AO9">
+        <v>70</v>
+      </c>
+      <c r="AP9">
+        <v>12</v>
+      </c>
+      <c r="AQ9">
+        <v>13</v>
+      </c>
+      <c r="AR9">
+        <v>4.9</v>
+      </c>
+      <c r="AS9">
+        <v>5.5</v>
+      </c>
+      <c r="AT9">
+        <v>8</v>
+      </c>
+      <c r="AU9">
+        <v>7</v>
+      </c>
+      <c r="AV9">
+        <v>15</v>
+      </c>
+      <c r="AW9">
+        <v>5.3</v>
+      </c>
+      <c r="AX9">
+        <v>10.5</v>
+      </c>
+      <c r="AY9">
+        <v>9.4</v>
+      </c>
+      <c r="AZ9">
+        <v>16</v>
+      </c>
+      <c r="BA9">
+        <v>5.3</v>
+      </c>
+      <c r="BB9">
+        <v>19.5</v>
+      </c>
+      <c r="BC9">
+        <v>19</v>
+      </c>
+      <c r="BD9">
+        <v>5.1</v>
+      </c>
+      <c r="BE9">
+        <v>5.5</v>
+      </c>
+      <c r="BF9">
+        <v>12</v>
+      </c>
+      <c r="BG9">
+        <v>5.3</v>
+      </c>
+      <c r="BH9">
+        <v>3.45</v>
+      </c>
+      <c r="BI9">
+        <v>2.76</v>
+      </c>
+      <c r="BJ9">
+        <v>10.5</v>
+      </c>
+      <c r="BK9">
+        <v>6</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>12.5</v>
+      </c>
+      <c r="BN9">
+        <v>4.5</v>
+      </c>
+      <c r="BO9">
+        <v>3.45</v>
+      </c>
+      <c r="BP9">
+        <v>13</v>
+      </c>
+      <c r="BQ9">
+        <v>6.6</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>9.4</v>
+      </c>
+      <c r="BT9">
+        <v>8.4</v>
+      </c>
+      <c r="BU9">
+        <v>6</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>10.5</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>11</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" t="s">
+        <v>149</v>
+      </c>
+      <c r="F10">
+        <v>9.4</v>
+      </c>
+      <c r="G10">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>1.35</v>
+      </c>
+      <c r="I10">
+        <v>1.42</v>
+      </c>
+      <c r="J10">
+        <v>5.1</v>
+      </c>
+      <c r="K10">
+        <v>5.9</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>2.2</v>
+      </c>
+      <c r="Q10">
+        <v>1.59</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E11" t="s">
+        <v>150</v>
+      </c>
+      <c r="F11">
+        <v>3.95</v>
+      </c>
+      <c r="G11">
+        <v>4.8</v>
+      </c>
+      <c r="H11">
+        <v>1.89</v>
+      </c>
+      <c r="I11">
+        <v>2.06</v>
+      </c>
+      <c r="J11">
+        <v>3.55</v>
+      </c>
+      <c r="K11">
+        <v>4.1</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.06</v>
+      </c>
+      <c r="N11">
+        <v>3.85</v>
+      </c>
+      <c r="O11">
+        <v>1.28</v>
+      </c>
+      <c r="P11">
+        <v>1.98</v>
+      </c>
+      <c r="Q11">
+        <v>1.83</v>
+      </c>
+      <c r="R11">
+        <v>1.38</v>
+      </c>
+      <c r="S11">
+        <v>3.1</v>
+      </c>
+      <c r="T11">
+        <v>1.74</v>
+      </c>
+      <c r="U11">
+        <v>2.1</v>
+      </c>
+      <c r="V11">
+        <v>1.94</v>
+      </c>
+      <c r="W11">
+        <v>1.27</v>
+      </c>
+      <c r="X11">
+        <v>19.5</v>
+      </c>
+      <c r="Y11">
+        <v>12</v>
+      </c>
+      <c r="Z11">
+        <v>15.5</v>
+      </c>
+      <c r="AA11">
+        <v>28</v>
+      </c>
+      <c r="AB11">
+        <v>20</v>
+      </c>
+      <c r="AC11">
+        <v>10.5</v>
+      </c>
+      <c r="AD11">
+        <v>13</v>
+      </c>
+      <c r="AE11">
+        <v>25</v>
+      </c>
+      <c r="AF11">
+        <v>40</v>
+      </c>
+      <c r="AG11">
+        <v>21</v>
+      </c>
+      <c r="AH11">
+        <v>22</v>
+      </c>
+      <c r="AI11">
+        <v>42</v>
+      </c>
+      <c r="AJ11">
+        <v>110</v>
+      </c>
+      <c r="AK11">
+        <v>65</v>
+      </c>
+      <c r="AL11">
+        <v>70</v>
+      </c>
+      <c r="AM11">
+        <v>110</v>
+      </c>
+      <c r="AN11">
+        <v>65</v>
+      </c>
+      <c r="AO11">
+        <v>16</v>
+      </c>
+      <c r="AP11">
+        <v>13</v>
+      </c>
+      <c r="AQ11">
+        <v>8.4</v>
+      </c>
+      <c r="AR11">
+        <v>10.5</v>
+      </c>
+      <c r="AS11">
+        <v>19</v>
+      </c>
+      <c r="AT11">
+        <v>13.5</v>
+      </c>
+      <c r="AU11">
+        <v>7.4</v>
+      </c>
+      <c r="AV11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW11">
+        <v>17</v>
+      </c>
+      <c r="AX11">
+        <v>3.8</v>
+      </c>
+      <c r="AY11">
+        <v>12.5</v>
+      </c>
+      <c r="AZ11">
+        <v>15</v>
+      </c>
+      <c r="BA11">
+        <v>24</v>
+      </c>
+      <c r="BB11">
+        <v>4</v>
+      </c>
+      <c r="BC11">
+        <v>3.95</v>
+      </c>
+      <c r="BD11">
+        <v>40</v>
+      </c>
+      <c r="BE11">
+        <v>4</v>
+      </c>
+      <c r="BF11">
+        <v>38</v>
+      </c>
+      <c r="BG11">
+        <v>9.6</v>
+      </c>
+      <c r="BH11">
+        <v>3.7</v>
+      </c>
+      <c r="BI11">
+        <v>2.86</v>
+      </c>
+      <c r="BJ11">
+        <v>10</v>
+      </c>
+      <c r="BK11">
+        <v>5.2</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>10</v>
+      </c>
+      <c r="BN11">
+        <v>8</v>
+      </c>
+      <c r="BO11">
+        <v>5.7</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>8.4</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>8.6</v>
+      </c>
+      <c r="BT11">
+        <v>4.9</v>
+      </c>
+      <c r="BU11">
+        <v>3.65</v>
+      </c>
+      <c r="BV11">
+        <v>14</v>
+      </c>
+      <c r="BW11">
+        <v>6</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>7.8</v>
+      </c>
+      <c r="BZ11">
+        <v>23</v>
+      </c>
+      <c r="CA11">
+        <v>7.4</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E12" t="s">
+        <v>151</v>
+      </c>
+      <c r="F12">
+        <v>1.04</v>
+      </c>
+      <c r="G12">
+        <v>1000</v>
+      </c>
+      <c r="H12">
+        <v>1.04</v>
+      </c>
+      <c r="I12">
+        <v>1000</v>
+      </c>
+      <c r="J12">
+        <v>1.01</v>
+      </c>
+      <c r="K12">
+        <v>440</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1.24</v>
+      </c>
+      <c r="Q12">
+        <v>1.01</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" t="s">
+        <v>152</v>
+      </c>
+      <c r="F13">
+        <v>2.68</v>
+      </c>
+      <c r="G13">
+        <v>3.2</v>
+      </c>
+      <c r="H13">
+        <v>2.52</v>
+      </c>
+      <c r="I13">
+        <v>2.88</v>
+      </c>
+      <c r="J13">
+        <v>3.4</v>
+      </c>
+      <c r="K13">
+        <v>4.3</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>2.7</v>
+      </c>
+      <c r="O13">
+        <v>1.23</v>
+      </c>
+      <c r="P13">
+        <v>2.1</v>
+      </c>
+      <c r="Q13">
+        <v>1.7</v>
+      </c>
+      <c r="R13">
+        <v>1.43</v>
+      </c>
+      <c r="S13">
+        <v>2.7</v>
+      </c>
+      <c r="T13">
+        <v>1.01</v>
+      </c>
+      <c r="U13">
+        <v>1.01</v>
+      </c>
+      <c r="V13">
+        <v>1.53</v>
+      </c>
+      <c r="W13">
+        <v>1.46</v>
+      </c>
+      <c r="X13">
+        <v>1000</v>
+      </c>
+      <c r="Y13">
+        <v>1000</v>
+      </c>
+      <c r="Z13">
+        <v>1000</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>1000</v>
+      </c>
+      <c r="AC13">
+        <v>1000</v>
+      </c>
+      <c r="AD13">
+        <v>1000</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>1000</v>
+      </c>
+      <c r="AG13">
+        <v>1000</v>
+      </c>
+      <c r="AH13">
+        <v>1000</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>1000</v>
+      </c>
+      <c r="AK13">
+        <v>1000</v>
+      </c>
+      <c r="AL13">
+        <v>1000</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>1000</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13">
+        <v>1.01</v>
+      </c>
+      <c r="AR13">
+        <v>1.01</v>
+      </c>
+      <c r="AS13">
+        <v>1.01</v>
+      </c>
+      <c r="AT13">
+        <v>1.01</v>
+      </c>
+      <c r="AU13">
+        <v>1.01</v>
+      </c>
+      <c r="AV13">
+        <v>1.01</v>
+      </c>
+      <c r="AW13">
+        <v>1.01</v>
+      </c>
+      <c r="AX13">
+        <v>1.01</v>
+      </c>
+      <c r="AY13">
+        <v>1.01</v>
+      </c>
+      <c r="AZ13">
+        <v>1.01</v>
+      </c>
+      <c r="BA13">
+        <v>1.01</v>
+      </c>
+      <c r="BB13">
+        <v>1.01</v>
+      </c>
+      <c r="BC13">
+        <v>1.01</v>
+      </c>
+      <c r="BD13">
+        <v>1.01</v>
+      </c>
+      <c r="BE13">
+        <v>1.01</v>
+      </c>
+      <c r="BF13">
+        <v>1.01</v>
+      </c>
+      <c r="BG13">
+        <v>1.01</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>1.01</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.01</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>1.01</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.01</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.01</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.01</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.01</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.01</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" t="s">
+        <v>153</v>
+      </c>
+      <c r="F14">
+        <v>1.92</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>3.75</v>
+      </c>
+      <c r="I14">
+        <v>4.2</v>
+      </c>
+      <c r="J14">
+        <v>4.1</v>
+      </c>
+      <c r="K14">
+        <v>4.5</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>2.6</v>
+      </c>
+      <c r="Q14">
+        <v>1.54</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" t="s">
+        <v>129</v>
+      </c>
+      <c r="E15" t="s">
+        <v>154</v>
+      </c>
+      <c r="F15">
+        <v>1.99</v>
+      </c>
+      <c r="G15">
+        <v>2.2</v>
+      </c>
+      <c r="H15">
+        <v>3.45</v>
+      </c>
+      <c r="I15">
+        <v>4.3</v>
+      </c>
+      <c r="J15">
+        <v>3.8</v>
+      </c>
+      <c r="K15">
+        <v>4.3</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>2.32</v>
+      </c>
+      <c r="O15">
+        <v>1.22</v>
+      </c>
+      <c r="P15">
+        <v>1.98</v>
+      </c>
+      <c r="Q15">
+        <v>1.6</v>
+      </c>
+      <c r="R15">
+        <v>1.38</v>
+      </c>
+      <c r="S15">
+        <v>2.52</v>
+      </c>
+      <c r="T15">
+        <v>1.62</v>
+      </c>
+      <c r="U15">
+        <v>2.28</v>
+      </c>
+      <c r="V15">
+        <v>1.32</v>
+      </c>
+      <c r="W15">
+        <v>1.83</v>
+      </c>
+      <c r="X15">
+        <v>24</v>
+      </c>
+      <c r="Y15">
+        <v>21</v>
+      </c>
+      <c r="Z15">
+        <v>36</v>
+      </c>
+      <c r="AA15">
+        <v>85</v>
+      </c>
+      <c r="AB15">
+        <v>14</v>
+      </c>
+      <c r="AC15">
+        <v>11</v>
+      </c>
+      <c r="AD15">
+        <v>19</v>
+      </c>
+      <c r="AE15">
+        <v>50</v>
+      </c>
+      <c r="AF15">
+        <v>17.5</v>
+      </c>
+      <c r="AG15">
+        <v>13</v>
+      </c>
+      <c r="AH15">
+        <v>20</v>
+      </c>
+      <c r="AI15">
+        <v>55</v>
+      </c>
+      <c r="AJ15">
+        <v>30</v>
+      </c>
+      <c r="AK15">
+        <v>25</v>
+      </c>
+      <c r="AL15">
+        <v>38</v>
+      </c>
+      <c r="AM15">
+        <v>90</v>
+      </c>
+      <c r="AN15">
+        <v>14.5</v>
+      </c>
+      <c r="AO15">
+        <v>42</v>
+      </c>
+      <c r="AP15">
+        <v>14</v>
+      </c>
+      <c r="AQ15">
+        <v>12.5</v>
+      </c>
+      <c r="AR15">
+        <v>21</v>
+      </c>
+      <c r="AS15">
+        <v>4.1</v>
+      </c>
+      <c r="AT15">
+        <v>8.6</v>
+      </c>
+      <c r="AU15">
+        <v>6.8</v>
+      </c>
+      <c r="AV15">
+        <v>11.5</v>
+      </c>
+      <c r="AW15">
+        <v>3.95</v>
+      </c>
+      <c r="AX15">
+        <v>10.5</v>
+      </c>
+      <c r="AY15">
+        <v>8</v>
+      </c>
+      <c r="AZ15">
+        <v>12</v>
+      </c>
+      <c r="BA15">
+        <v>4</v>
+      </c>
+      <c r="BB15">
+        <v>18</v>
+      </c>
+      <c r="BC15">
+        <v>14.5</v>
+      </c>
+      <c r="BD15">
+        <v>3.85</v>
+      </c>
+      <c r="BE15">
+        <v>4.1</v>
+      </c>
+      <c r="BF15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG15">
+        <v>3.9</v>
+      </c>
+      <c r="BH15">
+        <v>4.1</v>
+      </c>
+      <c r="BI15">
+        <v>3.1</v>
+      </c>
+      <c r="BJ15">
+        <v>9.4</v>
+      </c>
+      <c r="BK15">
+        <v>4.8</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>9</v>
+      </c>
+      <c r="BN15">
+        <v>5.3</v>
+      </c>
+      <c r="BO15">
+        <v>3.9</v>
+      </c>
+      <c r="BP15">
+        <v>14.5</v>
+      </c>
+      <c r="BQ15">
+        <v>5.9</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>7.2</v>
+      </c>
+      <c r="BT15">
+        <v>7.6</v>
+      </c>
+      <c r="BU15">
+        <v>5.4</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>7.4</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>7.8</v>
+      </c>
+      <c r="BZ15">
+        <v>20</v>
+      </c>
+      <c r="CA15">
+        <v>6.6</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" t="s">
+        <v>130</v>
+      </c>
+      <c r="E16" t="s">
+        <v>155</v>
+      </c>
+      <c r="F16">
+        <v>1.04</v>
+      </c>
+      <c r="G16">
+        <v>1.5</v>
+      </c>
+      <c r="H16">
+        <v>3.05</v>
+      </c>
+      <c r="I16">
+        <v>1000</v>
+      </c>
+      <c r="J16">
+        <v>5.3</v>
+      </c>
+      <c r="K16">
+        <v>450</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>3.25</v>
+      </c>
+      <c r="Q16">
+        <v>1.31</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E17" t="s">
+        <v>156</v>
+      </c>
+      <c r="F17">
+        <v>1.7</v>
+      </c>
+      <c r="G17">
+        <v>1.82</v>
+      </c>
+      <c r="H17">
+        <v>4.9</v>
+      </c>
+      <c r="I17">
+        <v>6</v>
+      </c>
+      <c r="J17">
+        <v>3.95</v>
+      </c>
+      <c r="K17">
+        <v>4.3</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.05</v>
+      </c>
+      <c r="N17">
+        <v>4.1</v>
+      </c>
+      <c r="O17">
+        <v>1.26</v>
+      </c>
+      <c r="P17">
+        <v>2.1</v>
+      </c>
+      <c r="Q17">
+        <v>1.78</v>
+      </c>
+      <c r="R17">
+        <v>1.42</v>
+      </c>
+      <c r="S17">
+        <v>2.98</v>
+      </c>
+      <c r="T17">
+        <v>1.78</v>
+      </c>
+      <c r="U17">
+        <v>2.08</v>
+      </c>
+      <c r="V17">
+        <v>1.21</v>
+      </c>
+      <c r="W17">
+        <v>2.2</v>
+      </c>
+      <c r="X17">
+        <v>20</v>
+      </c>
+      <c r="Y17">
+        <v>23</v>
+      </c>
+      <c r="Z17">
+        <v>48</v>
+      </c>
+      <c r="AA17">
+        <v>140</v>
+      </c>
+      <c r="AB17">
+        <v>11</v>
+      </c>
+      <c r="AC17">
+        <v>11</v>
+      </c>
+      <c r="AD17">
+        <v>24</v>
+      </c>
+      <c r="AE17">
+        <v>80</v>
+      </c>
+      <c r="AF17">
+        <v>13</v>
+      </c>
+      <c r="AG17">
+        <v>12</v>
+      </c>
+      <c r="AH17">
+        <v>22</v>
+      </c>
+      <c r="AI17">
+        <v>75</v>
+      </c>
+      <c r="AJ17">
+        <v>21</v>
+      </c>
+      <c r="AK17">
+        <v>21</v>
+      </c>
+      <c r="AL17">
+        <v>38</v>
+      </c>
+      <c r="AM17">
+        <v>110</v>
+      </c>
+      <c r="AN17">
+        <v>11.5</v>
+      </c>
+      <c r="AO17">
+        <v>80</v>
+      </c>
+      <c r="AP17">
+        <v>15</v>
+      </c>
+      <c r="AQ17">
+        <v>15</v>
+      </c>
+      <c r="AR17">
+        <v>4.6</v>
+      </c>
+      <c r="AS17">
+        <v>4.9</v>
+      </c>
+      <c r="AT17">
+        <v>8.4</v>
+      </c>
+      <c r="AU17">
+        <v>7.2</v>
+      </c>
+      <c r="AV17">
+        <v>15.5</v>
+      </c>
+      <c r="AW17">
+        <v>4.8</v>
+      </c>
+      <c r="AX17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY17">
+        <v>7.8</v>
+      </c>
+      <c r="AZ17">
+        <v>14.5</v>
+      </c>
+      <c r="BA17">
+        <v>4.8</v>
+      </c>
+      <c r="BB17">
+        <v>15.5</v>
+      </c>
+      <c r="BC17">
+        <v>13.5</v>
+      </c>
+      <c r="BD17">
+        <v>4.5</v>
+      </c>
+      <c r="BE17">
+        <v>4.9</v>
+      </c>
+      <c r="BF17">
+        <v>7.6</v>
+      </c>
+      <c r="BG17">
+        <v>4.8</v>
+      </c>
+      <c r="BH17">
+        <v>3.8</v>
+      </c>
+      <c r="BI17">
+        <v>3.05</v>
+      </c>
+      <c r="BJ17">
+        <v>10</v>
+      </c>
+      <c r="BK17">
+        <v>5.9</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>13</v>
+      </c>
+      <c r="BN17">
+        <v>4.5</v>
+      </c>
+      <c r="BO17">
+        <v>3.6</v>
+      </c>
+      <c r="BP17">
+        <v>11.5</v>
+      </c>
+      <c r="BQ17">
+        <v>6.4</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT17">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU17">
+        <v>5.4</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>10.5</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>11</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" t="s">
+        <v>132</v>
+      </c>
+      <c r="E18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F18">
+        <v>1.79</v>
+      </c>
+      <c r="G18">
+        <v>1.86</v>
+      </c>
+      <c r="H18">
+        <v>4.6</v>
+      </c>
+      <c r="I18">
+        <v>4.8</v>
+      </c>
+      <c r="J18">
+        <v>4</v>
+      </c>
+      <c r="K18">
+        <v>4.4</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.05</v>
+      </c>
+      <c r="N18">
+        <v>4.7</v>
+      </c>
+      <c r="O18">
+        <v>1.23</v>
+      </c>
+      <c r="P18">
+        <v>2.28</v>
+      </c>
+      <c r="Q18">
+        <v>1.59</v>
+      </c>
+      <c r="R18">
+        <v>1.52</v>
+      </c>
+      <c r="S18">
+        <v>2.66</v>
+      </c>
+      <c r="T18">
+        <v>1.7</v>
+      </c>
+      <c r="U18">
+        <v>2.26</v>
+      </c>
+      <c r="V18">
+        <v>1.26</v>
+      </c>
+      <c r="W18">
+        <v>2.16</v>
+      </c>
+      <c r="X18">
+        <v>21</v>
+      </c>
+      <c r="Y18">
+        <v>23</v>
+      </c>
+      <c r="Z18">
+        <v>44</v>
+      </c>
+      <c r="AA18">
+        <v>120</v>
+      </c>
+      <c r="AB18">
+        <v>11.5</v>
+      </c>
+      <c r="AC18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD18">
+        <v>22</v>
+      </c>
+      <c r="AE18">
+        <v>65</v>
+      </c>
+      <c r="AF18">
+        <v>12.5</v>
+      </c>
+      <c r="AG18">
+        <v>12</v>
+      </c>
+      <c r="AH18">
+        <v>21</v>
+      </c>
+      <c r="AI18">
+        <v>65</v>
+      </c>
+      <c r="AJ18">
+        <v>23</v>
+      </c>
+      <c r="AK18">
+        <v>17.5</v>
+      </c>
+      <c r="AL18">
+        <v>34</v>
+      </c>
+      <c r="AM18">
+        <v>90</v>
+      </c>
+      <c r="AN18">
+        <v>9</v>
+      </c>
+      <c r="AO18">
+        <v>55</v>
+      </c>
+      <c r="AP18">
+        <v>17</v>
+      </c>
+      <c r="AQ18">
+        <v>17.5</v>
+      </c>
+      <c r="AR18">
+        <v>6.6</v>
+      </c>
+      <c r="AS18">
+        <v>7.4</v>
+      </c>
+      <c r="AT18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU18">
+        <v>8.4</v>
+      </c>
+      <c r="AV18">
+        <v>16.5</v>
+      </c>
+      <c r="AW18">
+        <v>6.8</v>
+      </c>
+      <c r="AX18">
+        <v>9.6</v>
+      </c>
+      <c r="AY18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ18">
+        <v>15.5</v>
+      </c>
+      <c r="BA18">
+        <v>6.8</v>
+      </c>
+      <c r="BB18">
+        <v>15</v>
+      </c>
+      <c r="BC18">
+        <v>13.5</v>
+      </c>
+      <c r="BD18">
+        <v>6.4</v>
+      </c>
+      <c r="BE18">
+        <v>7.2</v>
+      </c>
+      <c r="BF18">
+        <v>7.8</v>
+      </c>
+      <c r="BG18">
+        <v>6.8</v>
+      </c>
+      <c r="BH18">
+        <v>3.85</v>
+      </c>
+      <c r="BI18">
+        <v>3.15</v>
+      </c>
+      <c r="BJ18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK18">
+        <v>6</v>
+      </c>
+      <c r="BL18">
+        <v>100</v>
+      </c>
+      <c r="BM18">
+        <v>13.5</v>
+      </c>
+      <c r="BN18">
+        <v>4.6</v>
+      </c>
+      <c r="BO18">
+        <v>3.7</v>
+      </c>
+      <c r="BP18">
+        <v>12.5</v>
+      </c>
+      <c r="BQ18">
+        <v>7</v>
+      </c>
+      <c r="BR18">
+        <v>24</v>
+      </c>
+      <c r="BS18">
+        <v>9.6</v>
+      </c>
+      <c r="BT18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU18">
+        <v>5.4</v>
+      </c>
+      <c r="BV18">
+        <v>38</v>
+      </c>
+      <c r="BW18">
+        <v>11</v>
+      </c>
+      <c r="BX18">
+        <v>42</v>
+      </c>
+      <c r="BY18">
+        <v>11.5</v>
+      </c>
+      <c r="BZ18">
+        <v>18</v>
+      </c>
+      <c r="CA18">
+        <v>8.4</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" t="s">
+        <v>133</v>
+      </c>
+      <c r="E19" t="s">
+        <v>158</v>
+      </c>
+      <c r="F19">
+        <v>1.39</v>
+      </c>
+      <c r="G19">
+        <v>3.35</v>
+      </c>
+      <c r="H19">
+        <v>2.52</v>
+      </c>
+      <c r="I19">
+        <v>2.78</v>
+      </c>
+      <c r="J19">
+        <v>1.58</v>
+      </c>
+      <c r="K19">
+        <v>470</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>1.25</v>
+      </c>
+      <c r="Q19">
+        <v>2.24</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" t="s">
+        <v>159</v>
+      </c>
+      <c r="F20">
+        <v>2.86</v>
+      </c>
+      <c r="G20">
+        <v>3.1</v>
+      </c>
+      <c r="H20">
+        <v>2.32</v>
+      </c>
+      <c r="I20">
+        <v>2.5</v>
+      </c>
+      <c r="J20">
+        <v>3.85</v>
+      </c>
+      <c r="K20">
+        <v>4.4</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
+        <v>1.01</v>
+      </c>
+      <c r="N20">
+        <v>5.3</v>
+      </c>
+      <c r="O20">
+        <v>1.19</v>
+      </c>
+      <c r="P20">
+        <v>2.48</v>
+      </c>
+      <c r="Q20">
+        <v>1.47</v>
+      </c>
+      <c r="R20">
+        <v>1.6</v>
+      </c>
+      <c r="S20">
+        <v>2.4</v>
+      </c>
+      <c r="T20">
+        <v>1.53</v>
+      </c>
+      <c r="U20">
+        <v>2.6</v>
+      </c>
+      <c r="V20">
+        <v>1.67</v>
+      </c>
+      <c r="W20">
+        <v>1.47</v>
+      </c>
+      <c r="X20">
+        <v>30</v>
+      </c>
+      <c r="Y20">
+        <v>19.5</v>
+      </c>
+      <c r="Z20">
+        <v>29</v>
+      </c>
+      <c r="AA20">
+        <v>40</v>
+      </c>
+      <c r="AB20">
+        <v>21</v>
+      </c>
+      <c r="AC20">
+        <v>12.5</v>
+      </c>
+      <c r="AD20">
+        <v>12.5</v>
+      </c>
+      <c r="AE20">
+        <v>30</v>
+      </c>
+      <c r="AF20">
+        <v>32</v>
+      </c>
+      <c r="AG20">
+        <v>16.5</v>
+      </c>
+      <c r="AH20">
+        <v>18</v>
+      </c>
+      <c r="AI20">
+        <v>42</v>
+      </c>
+      <c r="AJ20">
+        <v>55</v>
+      </c>
+      <c r="AK20">
+        <v>40</v>
+      </c>
+      <c r="AL20">
+        <v>40</v>
+      </c>
+      <c r="AM20">
+        <v>70</v>
+      </c>
+      <c r="AN20">
+        <v>22</v>
+      </c>
+      <c r="AO20">
+        <v>15.5</v>
+      </c>
+      <c r="AP20">
+        <v>4.5</v>
+      </c>
+      <c r="AQ20">
+        <v>11</v>
+      </c>
+      <c r="AR20">
+        <v>16.5</v>
+      </c>
+      <c r="AS20">
+        <v>4.6</v>
+      </c>
+      <c r="AT20">
+        <v>15</v>
+      </c>
+      <c r="AU20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV20">
+        <v>10.5</v>
+      </c>
+      <c r="AW20">
+        <v>17.5</v>
+      </c>
+      <c r="AX20">
+        <v>20</v>
+      </c>
+      <c r="AY20">
+        <v>11.5</v>
+      </c>
+      <c r="AZ20">
+        <v>10.5</v>
+      </c>
+      <c r="BA20">
+        <v>20</v>
+      </c>
+      <c r="BB20">
+        <v>4.8</v>
+      </c>
+      <c r="BC20">
+        <v>20</v>
+      </c>
+      <c r="BD20">
+        <v>22</v>
+      </c>
+      <c r="BE20">
+        <v>4.8</v>
+      </c>
+      <c r="BF20">
+        <v>12.5</v>
+      </c>
+      <c r="BG20">
+        <v>11</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>1.01</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>1.01</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.01</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>1.01</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>1.01</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.01</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>1.01</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.01</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.01</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
+        <v>1.01</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" t="s">
+        <v>135</v>
+      </c>
+      <c r="E21" t="s">
+        <v>160</v>
+      </c>
+      <c r="F21">
+        <v>2.14</v>
+      </c>
+      <c r="G21">
+        <v>2.9</v>
+      </c>
+      <c r="H21">
+        <v>2.7</v>
+      </c>
+      <c r="I21">
+        <v>3.95</v>
+      </c>
+      <c r="J21">
+        <v>3.25</v>
+      </c>
+      <c r="K21">
+        <v>6.2</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>1.91</v>
+      </c>
+      <c r="Q21">
+        <v>1.64</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>0</v>
+      </c>
+      <c r="BK21">
+        <v>0</v>
+      </c>
+      <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
+        <v>0</v>
+      </c>
+      <c r="BN21">
+        <v>0</v>
+      </c>
+      <c r="BO21">
+        <v>0</v>
+      </c>
+      <c r="BP21">
+        <v>0</v>
+      </c>
+      <c r="BQ21">
+        <v>0</v>
+      </c>
+      <c r="BR21">
+        <v>0</v>
+      </c>
+      <c r="BS21">
+        <v>0</v>
+      </c>
+      <c r="BT21">
+        <v>0</v>
+      </c>
+      <c r="BU21">
+        <v>0</v>
+      </c>
+      <c r="BV21">
+        <v>0</v>
+      </c>
+      <c r="BW21">
+        <v>0</v>
+      </c>
+      <c r="BX21">
+        <v>0</v>
+      </c>
+      <c r="BY21">
+        <v>0</v>
+      </c>
+      <c r="BZ21">
+        <v>0</v>
+      </c>
+      <c r="CA21">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" t="s">
+        <v>111</v>
+      </c>
+      <c r="D22" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" t="s">
+        <v>161</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>1.24</v>
+      </c>
+      <c r="Q22">
+        <v>1.01</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
+      <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
+        <v>0</v>
+      </c>
+      <c r="BU22">
+        <v>0</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22">
+        <v>0</v>
+      </c>
+      <c r="BZ22">
+        <v>0</v>
+      </c>
+      <c r="CA22">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" t="s">
+        <v>137</v>
+      </c>
+      <c r="E23" t="s">
+        <v>162</v>
+      </c>
+      <c r="F23">
+        <v>1.57</v>
+      </c>
+      <c r="G23">
+        <v>1.79</v>
+      </c>
+      <c r="H23">
+        <v>4.6</v>
+      </c>
+      <c r="I23">
+        <v>14</v>
+      </c>
+      <c r="J23">
+        <v>3.45</v>
+      </c>
+      <c r="K23">
+        <v>4.4</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>1.8</v>
+      </c>
+      <c r="Q23">
+        <v>1.73</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
+        <v>0</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23">
+        <v>0</v>
+      </c>
+      <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
+        <v>0</v>
+      </c>
+      <c r="BU23">
+        <v>0</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>0</v>
+      </c>
+      <c r="BX23">
+        <v>0</v>
+      </c>
+      <c r="BY23">
+        <v>0</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" t="s">
+        <v>138</v>
+      </c>
+      <c r="E24" t="s">
+        <v>163</v>
+      </c>
+      <c r="F24">
+        <v>3.05</v>
+      </c>
+      <c r="G24">
+        <v>3.65</v>
+      </c>
+      <c r="H24">
+        <v>2.42</v>
+      </c>
+      <c r="I24">
+        <v>2.64</v>
+      </c>
+      <c r="J24">
+        <v>3.2</v>
+      </c>
+      <c r="K24">
+        <v>3.55</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>1.66</v>
+      </c>
+      <c r="Q24">
+        <v>2.06</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>0</v>
+      </c>
+      <c r="AV24">
+        <v>0</v>
+      </c>
+      <c r="AW24">
+        <v>0</v>
+      </c>
+      <c r="AX24">
+        <v>0</v>
+      </c>
+      <c r="AY24">
+        <v>0</v>
+      </c>
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
+        <v>0</v>
+      </c>
+      <c r="BB24">
+        <v>0</v>
+      </c>
+      <c r="BC24">
+        <v>0</v>
+      </c>
+      <c r="BD24">
+        <v>0</v>
+      </c>
+      <c r="BE24">
+        <v>0</v>
+      </c>
+      <c r="BF24">
+        <v>0</v>
+      </c>
+      <c r="BG24">
+        <v>0</v>
+      </c>
+      <c r="BH24">
+        <v>0</v>
+      </c>
+      <c r="BI24">
+        <v>0</v>
+      </c>
+      <c r="BJ24">
+        <v>0</v>
+      </c>
+      <c r="BK24">
+        <v>0</v>
+      </c>
+      <c r="BL24">
+        <v>0</v>
+      </c>
+      <c r="BM24">
+        <v>0</v>
+      </c>
+      <c r="BN24">
+        <v>0</v>
+      </c>
+      <c r="BO24">
+        <v>0</v>
+      </c>
+      <c r="BP24">
+        <v>0</v>
+      </c>
+      <c r="BQ24">
+        <v>0</v>
+      </c>
+      <c r="BR24">
+        <v>0</v>
+      </c>
+      <c r="BS24">
+        <v>0</v>
+      </c>
+      <c r="BT24">
+        <v>0</v>
+      </c>
+      <c r="BU24">
+        <v>0</v>
+      </c>
+      <c r="BV24">
+        <v>0</v>
+      </c>
+      <c r="BW24">
+        <v>0</v>
+      </c>
+      <c r="BX24">
+        <v>0</v>
+      </c>
+      <c r="BY24">
+        <v>0</v>
+      </c>
+      <c r="BZ24">
+        <v>0</v>
+      </c>
+      <c r="CA24">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" t="s">
+        <v>164</v>
+      </c>
+      <c r="F25">
+        <v>1.53</v>
+      </c>
+      <c r="G25">
+        <v>1.89</v>
+      </c>
+      <c r="H25">
+        <v>2.16</v>
+      </c>
+      <c r="I25">
+        <v>12</v>
+      </c>
+      <c r="J25">
+        <v>3.85</v>
+      </c>
+      <c r="K25">
+        <v>480</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>1.76</v>
+      </c>
+      <c r="Q25">
+        <v>1.78</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>0</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
+      <c r="AV25">
+        <v>0</v>
+      </c>
+      <c r="AW25">
+        <v>0</v>
+      </c>
+      <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <v>0</v>
+      </c>
+      <c r="BB25">
+        <v>0</v>
+      </c>
+      <c r="BC25">
+        <v>0</v>
+      </c>
+      <c r="BD25">
+        <v>0</v>
+      </c>
+      <c r="BE25">
+        <v>0</v>
+      </c>
+      <c r="BF25">
+        <v>0</v>
+      </c>
+      <c r="BG25">
+        <v>0</v>
+      </c>
+      <c r="BH25">
+        <v>0</v>
+      </c>
+      <c r="BI25">
+        <v>0</v>
+      </c>
+      <c r="BJ25">
+        <v>0</v>
+      </c>
+      <c r="BK25">
+        <v>0</v>
+      </c>
+      <c r="BL25">
+        <v>0</v>
+      </c>
+      <c r="BM25">
+        <v>0</v>
+      </c>
+      <c r="BN25">
+        <v>0</v>
+      </c>
+      <c r="BO25">
+        <v>0</v>
+      </c>
+      <c r="BP25">
+        <v>0</v>
+      </c>
+      <c r="BQ25">
+        <v>0</v>
+      </c>
+      <c r="BR25">
+        <v>0</v>
+      </c>
+      <c r="BS25">
+        <v>0</v>
+      </c>
+      <c r="BT25">
+        <v>0</v>
+      </c>
+      <c r="BU25">
+        <v>0</v>
+      </c>
+      <c r="BV25">
+        <v>0</v>
+      </c>
+      <c r="BW25">
+        <v>0</v>
+      </c>
+      <c r="BX25">
+        <v>0</v>
+      </c>
+      <c r="BY25">
+        <v>0</v>
+      </c>
+      <c r="BZ25">
+        <v>0</v>
+      </c>
+      <c r="CA25">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" t="s">
+        <v>140</v>
+      </c>
+      <c r="E26" t="s">
+        <v>165</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>1.24</v>
+      </c>
+      <c r="Q26">
+        <v>1.02</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AO26">
+        <v>0</v>
+      </c>
+      <c r="AP26">
+        <v>0</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26">
+        <v>0</v>
+      </c>
+      <c r="AV26">
+        <v>0</v>
+      </c>
+      <c r="AW26">
+        <v>0</v>
+      </c>
+      <c r="AX26">
+        <v>0</v>
+      </c>
+      <c r="AY26">
+        <v>0</v>
+      </c>
+      <c r="AZ26">
+        <v>0</v>
+      </c>
+      <c r="BA26">
+        <v>0</v>
+      </c>
+      <c r="BB26">
+        <v>0</v>
+      </c>
+      <c r="BC26">
+        <v>0</v>
+      </c>
+      <c r="BD26">
+        <v>0</v>
+      </c>
+      <c r="BE26">
+        <v>0</v>
+      </c>
+      <c r="BF26">
+        <v>0</v>
+      </c>
+      <c r="BG26">
+        <v>0</v>
+      </c>
+      <c r="BH26">
+        <v>0</v>
+      </c>
+      <c r="BI26">
+        <v>0</v>
+      </c>
+      <c r="BJ26">
+        <v>0</v>
+      </c>
+      <c r="BK26">
+        <v>0</v>
+      </c>
+      <c r="BL26">
+        <v>0</v>
+      </c>
+      <c r="BM26">
+        <v>0</v>
+      </c>
+      <c r="BN26">
+        <v>0</v>
+      </c>
+      <c r="BO26">
+        <v>0</v>
+      </c>
+      <c r="BP26">
+        <v>0</v>
+      </c>
+      <c r="BQ26">
+        <v>0</v>
+      </c>
+      <c r="BR26">
+        <v>0</v>
+      </c>
+      <c r="BS26">
+        <v>0</v>
+      </c>
+      <c r="BT26">
+        <v>0</v>
+      </c>
+      <c r="BU26">
+        <v>0</v>
+      </c>
+      <c r="BV26">
+        <v>0</v>
+      </c>
+      <c r="BW26">
+        <v>0</v>
+      </c>
+      <c r="BX26">
+        <v>0</v>
+      </c>
+      <c r="BY26">
+        <v>0</v>
+      </c>
+      <c r="BZ26">
+        <v>0</v>
+      </c>
+      <c r="CA26">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -514,7 +514,7 @@
     <t>Thor</t>
   </si>
   <si>
-    <t>2026-07-25 00:47:14</t>
+    <t>2026-07-25 03:06:10</t>
   </si>
 </sst>
 </file>
@@ -1108,22 +1108,22 @@
         <v>141</v>
       </c>
       <c r="F2">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="G2">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J2">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1132,40 +1132,40 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.72</v>
+        <v>3.4</v>
       </c>
       <c r="O2">
         <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q2">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R2">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S2">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V2">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W2">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z2">
         <v>1000</v>
@@ -1174,10 +1174,10 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD2">
         <v>1000</v>
@@ -1186,25 +1186,25 @@
         <v>1000</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI2">
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM2">
         <v>1000</v>
@@ -1216,58 +1216,58 @@
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>10</v>
+        <v>1.9</v>
       </c>
       <c r="AQ2">
-        <v>15</v>
+        <v>1.97</v>
       </c>
       <c r="AR2">
-        <v>34</v>
+        <v>2.1</v>
       </c>
       <c r="AS2">
-        <v>40</v>
+        <v>2.1</v>
       </c>
       <c r="AT2">
-        <v>5.8</v>
+        <v>1.73</v>
       </c>
       <c r="AU2">
-        <v>7.4</v>
+        <v>1.83</v>
       </c>
       <c r="AV2">
-        <v>18.5</v>
+        <v>2.1</v>
       </c>
       <c r="AW2">
-        <v>40</v>
+        <v>2.1</v>
       </c>
       <c r="AX2">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="AY2">
-        <v>8.4</v>
+        <v>1.84</v>
       </c>
       <c r="AZ2">
-        <v>18.5</v>
+        <v>1.99</v>
       </c>
       <c r="BA2">
-        <v>40</v>
+        <v>2.1</v>
       </c>
       <c r="BB2">
-        <v>11</v>
+        <v>1.91</v>
       </c>
       <c r="BC2">
-        <v>14.5</v>
+        <v>1.94</v>
       </c>
       <c r="BD2">
-        <v>28</v>
+        <v>2.02</v>
       </c>
       <c r="BE2">
-        <v>40</v>
+        <v>2.1</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1374,13 +1374,13 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="O3">
         <v>1.41</v>
       </c>
       <c r="P3">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="Q3">
         <v>2.24</v>
@@ -1592,25 +1592,25 @@
         <v>143</v>
       </c>
       <c r="F4">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G4">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H4">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>3.2</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L4">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M4">
         <v>1.07</v>
@@ -1619,22 +1619,22 @@
         <v>3.55</v>
       </c>
       <c r="O4">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P4">
         <v>1.96</v>
       </c>
       <c r="Q4">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R4">
         <v>1.34</v>
       </c>
       <c r="S4">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T4">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U4">
         <v>2.12</v>
@@ -1643,10 +1643,10 @@
         <v>1.45</v>
       </c>
       <c r="W4">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y4">
         <v>12.5</v>
@@ -1661,7 +1661,7 @@
         <v>11</v>
       </c>
       <c r="AC4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4">
         <v>14</v>
@@ -1679,7 +1679,7 @@
         <v>18</v>
       </c>
       <c r="AI4">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AJ4">
         <v>38</v>
@@ -1697,7 +1697,7 @@
         <v>24</v>
       </c>
       <c r="AO4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP4">
         <v>12</v>
@@ -1721,7 +1721,7 @@
         <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX4">
         <v>14</v>
@@ -1739,58 +1739,58 @@
         <v>27</v>
       </c>
       <c r="BC4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD4">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE4">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4">
         <v>20</v>
       </c>
       <c r="BG4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI4">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="BJ4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK4">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN4">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BO4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ4">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU4">
         <v>4.8</v>
@@ -1799,19 +1799,19 @@
         <v>25</v>
       </c>
       <c r="BW4">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BX4">
         <v>38</v>
       </c>
       <c r="BY4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BZ4">
         <v>29</v>
       </c>
       <c r="CA4">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="s">
         <v>166</v>
@@ -1837,16 +1837,16 @@
         <v>1.58</v>
       </c>
       <c r="G5">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
         <v>6.8</v>
       </c>
       <c r="J5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K5">
         <v>4.7</v>
@@ -1885,7 +1885,7 @@
         <v>1.17</v>
       </c>
       <c r="W5">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="X5">
         <v>21</v>
@@ -2076,7 +2076,7 @@
         <v>145</v>
       </c>
       <c r="F6">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G6">
         <v>1.54</v>
@@ -2085,13 +2085,13 @@
         <v>7.6</v>
       </c>
       <c r="I6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2106,22 +2106,22 @@
         <v>1.28</v>
       </c>
       <c r="P6">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q6">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R6">
         <v>1.39</v>
       </c>
       <c r="S6">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T6">
         <v>2.02</v>
       </c>
       <c r="U6">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V6">
         <v>1.12</v>
@@ -2154,7 +2154,7 @@
         <v>160</v>
       </c>
       <c r="AF6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG6">
         <v>12.5</v>
@@ -2166,10 +2166,10 @@
         <v>140</v>
       </c>
       <c r="AJ6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK6">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AL6">
         <v>42</v>
@@ -2178,7 +2178,7 @@
         <v>180</v>
       </c>
       <c r="AN6">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AO6">
         <v>220</v>
@@ -2190,10 +2190,10 @@
         <v>18</v>
       </c>
       <c r="AR6">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS6">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT6">
         <v>7</v>
@@ -2202,10 +2202,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV6">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AW6">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX6">
         <v>6.4</v>
@@ -2217,7 +2217,7 @@
         <v>18.5</v>
       </c>
       <c r="BA6">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB6">
         <v>9.6</v>
@@ -2226,34 +2226,34 @@
         <v>13.5</v>
       </c>
       <c r="BD6">
-        <v>28</v>
+        <v>5.9</v>
       </c>
       <c r="BE6">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF6">
         <v>5.9</v>
       </c>
       <c r="BG6">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH6">
         <v>3.75</v>
       </c>
       <c r="BI6">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BJ6">
         <v>12</v>
       </c>
       <c r="BK6">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN6">
         <v>4.1</v>
@@ -2262,7 +2262,7 @@
         <v>3.05</v>
       </c>
       <c r="BP6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ6">
         <v>5</v>
@@ -2277,25 +2277,25 @@
         <v>12</v>
       </c>
       <c r="BU6">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ6">
         <v>18</v>
       </c>
       <c r="CA6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB6" t="s">
         <v>166</v>
@@ -2820,7 +2820,7 @@
         <v>3.8</v>
       </c>
       <c r="L9">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
         <v>1.07</v>
@@ -2832,10 +2832,10 @@
         <v>1.33</v>
       </c>
       <c r="P9">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q9">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R9">
         <v>1.34</v>
@@ -2844,7 +2844,7 @@
         <v>3.5</v>
       </c>
       <c r="T9">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U9">
         <v>2.04</v>
@@ -2880,7 +2880,7 @@
         <v>65</v>
       </c>
       <c r="AF9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG9">
         <v>12.5</v>
@@ -2907,7 +2907,7 @@
         <v>17</v>
       </c>
       <c r="AO9">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AP9">
         <v>12</v>
@@ -2946,7 +2946,7 @@
         <v>5.3</v>
       </c>
       <c r="BB9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC9">
         <v>19</v>
@@ -2961,7 +2961,7 @@
         <v>12</v>
       </c>
       <c r="BG9">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH9">
         <v>3.45</v>
@@ -2997,13 +2997,13 @@
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT9">
         <v>8.4</v>
       </c>
       <c r="BU9">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BV9">
         <v>1000</v>
@@ -3077,7 +3077,7 @@
         <v>2.2</v>
       </c>
       <c r="Q10">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3286,13 +3286,13 @@
         <v>150</v>
       </c>
       <c r="F11">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="G11">
         <v>4.8</v>
       </c>
       <c r="H11">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="I11">
         <v>2.06</v>
@@ -3346,10 +3346,10 @@
         <v>12</v>
       </c>
       <c r="Z11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA11">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AB11">
         <v>20</v>
@@ -3358,7 +3358,7 @@
         <v>10.5</v>
       </c>
       <c r="AD11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE11">
         <v>25</v>
@@ -3391,7 +3391,7 @@
         <v>65</v>
       </c>
       <c r="AO11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP11">
         <v>13</v>
@@ -3418,7 +3418,7 @@
         <v>17</v>
       </c>
       <c r="AX11">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AY11">
         <v>12.5</v>
@@ -3430,16 +3430,16 @@
         <v>24</v>
       </c>
       <c r="BB11">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BC11">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BD11">
         <v>40</v>
       </c>
       <c r="BE11">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BF11">
         <v>38</v>
@@ -3448,7 +3448,7 @@
         <v>9.6</v>
       </c>
       <c r="BH11">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI11">
         <v>2.86</v>
@@ -3457,31 +3457,31 @@
         <v>10</v>
       </c>
       <c r="BK11">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN11">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO11">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT11">
         <v>4.9</v>
@@ -3493,19 +3493,19 @@
         <v>14</v>
       </c>
       <c r="BW11">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ11">
         <v>23</v>
       </c>
       <c r="CA11">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB11" t="s">
         <v>166</v>
@@ -4012,13 +4012,13 @@
         <v>153</v>
       </c>
       <c r="F14">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="H14">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I14">
         <v>4.2</v>
@@ -4254,19 +4254,19 @@
         <v>154</v>
       </c>
       <c r="F15">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G15">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H15">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I15">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J15">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K15">
         <v>4.3</v>
@@ -4278,16 +4278,16 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.32</v>
+        <v>4</v>
       </c>
       <c r="O15">
         <v>1.22</v>
       </c>
       <c r="P15">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="Q15">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R15">
         <v>1.38</v>
@@ -4296,19 +4296,19 @@
         <v>2.52</v>
       </c>
       <c r="T15">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="U15">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V15">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W15">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y15">
         <v>21</v>
@@ -4332,10 +4332,10 @@
         <v>50</v>
       </c>
       <c r="AF15">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG15">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH15">
         <v>20</v>
@@ -4344,7 +4344,7 @@
         <v>55</v>
       </c>
       <c r="AJ15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK15">
         <v>25</v>
@@ -4356,7 +4356,7 @@
         <v>90</v>
       </c>
       <c r="AN15">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO15">
         <v>42</v>
@@ -4365,13 +4365,13 @@
         <v>14</v>
       </c>
       <c r="AQ15">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AT15">
         <v>8.6</v>
@@ -4380,10 +4380,10 @@
         <v>6.8</v>
       </c>
       <c r="AV15">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW15">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AX15">
         <v>10.5</v>
@@ -4395,31 +4395,31 @@
         <v>12</v>
       </c>
       <c r="BA15">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BB15">
         <v>18</v>
       </c>
       <c r="BC15">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD15">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BE15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BF15">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG15">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BH15">
         <v>4.1</v>
       </c>
       <c r="BI15">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ15">
         <v>9.4</v>
@@ -4440,7 +4440,7 @@
         <v>3.9</v>
       </c>
       <c r="BP15">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ15">
         <v>5.9</v>
@@ -4452,7 +4452,7 @@
         <v>7.2</v>
       </c>
       <c r="BT15">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU15">
         <v>5.4</v>
@@ -4470,7 +4470,7 @@
         <v>7.8</v>
       </c>
       <c r="BZ15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA15">
         <v>6.6</v>
@@ -4496,7 +4496,7 @@
         <v>155</v>
       </c>
       <c r="F16">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="G16">
         <v>1.5</v>
@@ -4505,7 +4505,7 @@
         <v>3.05</v>
       </c>
       <c r="I16">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="J16">
         <v>5.3</v>
@@ -4738,7 +4738,7 @@
         <v>156</v>
       </c>
       <c r="F17">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G17">
         <v>1.82</v>
@@ -4747,13 +4747,13 @@
         <v>4.9</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J17">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K17">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4762,7 +4762,7 @@
         <v>1.05</v>
       </c>
       <c r="N17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O17">
         <v>1.26</v>
@@ -4774,7 +4774,7 @@
         <v>1.78</v>
       </c>
       <c r="R17">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S17">
         <v>2.98</v>
@@ -4783,10 +4783,10 @@
         <v>1.78</v>
       </c>
       <c r="U17">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V17">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W17">
         <v>2.2</v>
@@ -4813,7 +4813,7 @@
         <v>24</v>
       </c>
       <c r="AE17">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF17">
         <v>13</v>
@@ -4852,10 +4852,10 @@
         <v>15</v>
       </c>
       <c r="AR17">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS17">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT17">
         <v>8.4</v>
@@ -4900,22 +4900,22 @@
         <v>4.8</v>
       </c>
       <c r="BH17">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI17">
         <v>3.05</v>
       </c>
       <c r="BJ17">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK17">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="BN17">
         <v>4.5</v>
@@ -4927,37 +4927,37 @@
         <v>11.5</v>
       </c>
       <c r="BQ17">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT17">
+        <v>8.6</v>
+      </c>
+      <c r="BU17">
+        <v>5.6</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>12</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>12</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BU17">
-        <v>5.4</v>
-      </c>
-      <c r="BV17">
-        <v>1000</v>
-      </c>
-      <c r="BW17">
-        <v>10.5</v>
-      </c>
-      <c r="BX17">
-        <v>1000</v>
-      </c>
-      <c r="BY17">
-        <v>11</v>
-      </c>
-      <c r="BZ17">
-        <v>1000</v>
-      </c>
-      <c r="CA17">
-        <v>8.199999999999999</v>
       </c>
       <c r="CB17" t="s">
         <v>166</v>
@@ -4980,7 +4980,7 @@
         <v>157</v>
       </c>
       <c r="F18">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G18">
         <v>1.86</v>
@@ -4995,7 +4995,7 @@
         <v>4</v>
       </c>
       <c r="K18">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5007,22 +5007,22 @@
         <v>4.7</v>
       </c>
       <c r="O18">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P18">
         <v>2.28</v>
       </c>
       <c r="Q18">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="R18">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S18">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T18">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U18">
         <v>2.26</v>
@@ -5046,7 +5046,7 @@
         <v>120</v>
       </c>
       <c r="AB18">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC18">
         <v>9.800000000000001</v>
@@ -5082,19 +5082,19 @@
         <v>90</v>
       </c>
       <c r="AN18">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO18">
         <v>55</v>
       </c>
       <c r="AP18">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ18">
         <v>17.5</v>
       </c>
       <c r="AR18">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS18">
         <v>7.4</v>
@@ -5109,7 +5109,7 @@
         <v>16.5</v>
       </c>
       <c r="AW18">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX18">
         <v>9.6</v>
@@ -5121,7 +5121,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB18">
         <v>15</v>
@@ -5139,43 +5139,43 @@
         <v>7.8</v>
       </c>
       <c r="BG18">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH18">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BI18">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BJ18">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BK18">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM18">
         <v>13.5</v>
       </c>
       <c r="BN18">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO18">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BP18">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ18">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR18">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS18">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT18">
         <v>8.199999999999999</v>
@@ -5184,19 +5184,19 @@
         <v>5.4</v>
       </c>
       <c r="BV18">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW18">
         <v>11</v>
       </c>
       <c r="BX18">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY18">
         <v>11.5</v>
       </c>
       <c r="BZ18">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="CA18">
         <v>8.4</v>
@@ -5228,13 +5228,13 @@
         <v>3.35</v>
       </c>
       <c r="H19">
-        <v>2.52</v>
+        <v>1.39</v>
       </c>
       <c r="I19">
         <v>2.78</v>
       </c>
       <c r="J19">
-        <v>1.58</v>
+        <v>1.02</v>
       </c>
       <c r="K19">
         <v>470</v>
@@ -5464,22 +5464,22 @@
         <v>159</v>
       </c>
       <c r="F20">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="G20">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H20">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="I20">
         <v>2.5</v>
       </c>
       <c r="J20">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5488,40 +5488,40 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O20">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P20">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q20">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="R20">
         <v>1.6</v>
       </c>
       <c r="S20">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="T20">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U20">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V20">
         <v>1.67</v>
       </c>
       <c r="W20">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X20">
         <v>30</v>
       </c>
       <c r="Y20">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z20">
         <v>29</v>
@@ -5530,7 +5530,7 @@
         <v>40</v>
       </c>
       <c r="AB20">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC20">
         <v>12.5</v>
@@ -5575,34 +5575,34 @@
         <v>4.5</v>
       </c>
       <c r="AQ20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR20">
         <v>16.5</v>
       </c>
       <c r="AS20">
-        <v>4.6</v>
+        <v>23</v>
       </c>
       <c r="AT20">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="AU20">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AV20">
         <v>10.5</v>
       </c>
       <c r="AW20">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX20">
         <v>20</v>
       </c>
       <c r="AY20">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ20">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BA20">
         <v>20</v>
@@ -5620,10 +5620,10 @@
         <v>4.8</v>
       </c>
       <c r="BF20">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5712,7 +5712,7 @@
         <v>2.9</v>
       </c>
       <c r="H21">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="I21">
         <v>3.95</v>
@@ -5721,7 +5721,7 @@
         <v>3.25</v>
       </c>
       <c r="K21">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5981,7 +5981,7 @@
         <v>1.24</v>
       </c>
       <c r="Q22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6190,7 +6190,7 @@
         <v>162</v>
       </c>
       <c r="F23">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G23">
         <v>1.79</v>
@@ -6199,7 +6199,7 @@
         <v>4.6</v>
       </c>
       <c r="I23">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="J23">
         <v>3.45</v>
@@ -6432,22 +6432,22 @@
         <v>163</v>
       </c>
       <c r="F24">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G24">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="H24">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="I24">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="J24">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K24">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L24">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="170">
   <si>
     <t>League</t>
   </si>
@@ -313,6 +313,9 @@
     <t>Icelandic Urvalsdeild</t>
   </si>
   <si>
+    <t>Bolivian Liga de Futbol Profesional</t>
+  </si>
+  <si>
     <t>2026-07-27</t>
   </si>
   <si>
@@ -436,6 +439,9 @@
     <t>Mushuc Runa</t>
   </si>
   <si>
+    <t>CD Gualberto Villarroel</t>
+  </si>
+  <si>
     <t>KA Akureyri</t>
   </si>
   <si>
@@ -511,10 +517,13 @@
     <t>Libertad FC</t>
   </si>
   <si>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
     <t>Thor</t>
   </si>
   <si>
-    <t>2026-07-25 03:06:10</t>
+    <t>2026-07-25 05:25:25</t>
   </si>
 </sst>
 </file>
@@ -846,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB26"/>
+  <dimension ref="A1:CB27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1096,52 +1105,52 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F2">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G2">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K2">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="L2">
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P2">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="Q2">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="R2">
         <v>1.32</v>
@@ -1150,124 +1159,124 @@
         <v>3.6</v>
       </c>
       <c r="T2">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="V2">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W2">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="X2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Y2">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AB2">
+        <v>7.4</v>
+      </c>
+      <c r="AC2">
         <v>10</v>
       </c>
-      <c r="AC2">
-        <v>14.5</v>
-      </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG2">
+        <v>10.5</v>
+      </c>
+      <c r="AH2">
+        <v>27</v>
+      </c>
+      <c r="AI2">
+        <v>140</v>
+      </c>
+      <c r="AJ2">
+        <v>15</v>
+      </c>
+      <c r="AK2">
+        <v>18.5</v>
+      </c>
+      <c r="AL2">
+        <v>44</v>
+      </c>
+      <c r="AM2">
+        <v>210</v>
+      </c>
+      <c r="AN2">
         <v>12.5</v>
       </c>
-      <c r="AG2">
-        <v>15</v>
-      </c>
-      <c r="AH2">
-        <v>38</v>
-      </c>
-      <c r="AI2">
-        <v>1000</v>
-      </c>
-      <c r="AJ2">
-        <v>21</v>
-      </c>
-      <c r="AK2">
-        <v>26</v>
-      </c>
-      <c r="AL2">
-        <v>65</v>
-      </c>
-      <c r="AM2">
-        <v>1000</v>
-      </c>
-      <c r="AN2">
-        <v>1000</v>
-      </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AP2">
-        <v>1.9</v>
+        <v>12</v>
       </c>
       <c r="AQ2">
-        <v>1.97</v>
+        <v>17.5</v>
       </c>
       <c r="AR2">
-        <v>2.1</v>
+        <v>7.8</v>
       </c>
       <c r="AS2">
-        <v>2.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2">
-        <v>1.73</v>
+        <v>6.4</v>
       </c>
       <c r="AU2">
-        <v>1.83</v>
+        <v>8.4</v>
       </c>
       <c r="AV2">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="AW2">
-        <v>2.1</v>
+        <v>8.4</v>
       </c>
       <c r="AX2">
-        <v>1.8</v>
+        <v>7.8</v>
       </c>
       <c r="AY2">
-        <v>1.84</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
-        <v>1.99</v>
+        <v>6.8</v>
       </c>
       <c r="BA2">
-        <v>2.1</v>
+        <v>8.4</v>
       </c>
       <c r="BB2">
-        <v>1.91</v>
+        <v>13</v>
       </c>
       <c r="BC2">
-        <v>1.94</v>
+        <v>6</v>
       </c>
       <c r="BD2">
-        <v>2.02</v>
+        <v>7.4</v>
       </c>
       <c r="BE2">
-        <v>2.1</v>
+        <v>8.6</v>
       </c>
       <c r="BF2">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="BG2">
-        <v>2.1</v>
+        <v>8.6</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1330,7 +1339,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1338,16 +1347,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F3">
         <v>2.2</v>
@@ -1380,7 +1389,7 @@
         <v>1.41</v>
       </c>
       <c r="P3">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="Q3">
         <v>2.24</v>
@@ -1572,7 +1581,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1580,19 +1589,19 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F4">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G4">
         <v>2.6</v>
@@ -1604,7 +1613,7 @@
         <v>3.2</v>
       </c>
       <c r="J4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K4">
         <v>3.7</v>
@@ -1616,7 +1625,7 @@
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O4">
         <v>1.33</v>
@@ -1634,7 +1643,7 @@
         <v>3.55</v>
       </c>
       <c r="T4">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="U4">
         <v>2.12</v>
@@ -1643,7 +1652,7 @@
         <v>1.45</v>
       </c>
       <c r="W4">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X4">
         <v>16</v>
@@ -1709,7 +1718,7 @@
         <v>18</v>
       </c>
       <c r="AS4">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AT4">
         <v>9</v>
@@ -1754,7 +1763,7 @@
         <v>7.4</v>
       </c>
       <c r="BH4">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
         <v>3</v>
@@ -1763,16 +1772,16 @@
         <v>9.6</v>
       </c>
       <c r="BK4">
-        <v>5.9</v>
+        <v>1.54</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>13.5</v>
+        <v>1.81</v>
       </c>
       <c r="BN4">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
         <v>4.3</v>
@@ -1781,13 +1790,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ4">
-        <v>8.6</v>
+        <v>1.68</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>10.5</v>
+        <v>1.74</v>
       </c>
       <c r="BT4">
         <v>6.2</v>
@@ -1799,22 +1808,22 @@
         <v>25</v>
       </c>
       <c r="BW4">
-        <v>9.4</v>
+        <v>1.71</v>
       </c>
       <c r="BX4">
         <v>38</v>
       </c>
       <c r="BY4">
-        <v>11</v>
+        <v>1.75</v>
       </c>
       <c r="BZ4">
         <v>29</v>
       </c>
       <c r="CA4">
-        <v>10</v>
+        <v>1.73</v>
       </c>
       <c r="CB4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1822,16 +1831,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F5">
         <v>1.58</v>
@@ -1840,7 +1849,7 @@
         <v>1.67</v>
       </c>
       <c r="H5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>6.8</v>
@@ -1873,7 +1882,7 @@
         <v>1.47</v>
       </c>
       <c r="S5">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="T5">
         <v>1.8</v>
@@ -2056,7 +2065,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2064,19 +2073,19 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F6">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G6">
         <v>1.54</v>
@@ -2085,13 +2094,13 @@
         <v>7.6</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>4.4</v>
       </c>
       <c r="K6">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2109,13 +2118,13 @@
         <v>2</v>
       </c>
       <c r="Q6">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="R6">
         <v>1.39</v>
       </c>
       <c r="S6">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="T6">
         <v>2.02</v>
@@ -2124,7 +2133,7 @@
         <v>1.83</v>
       </c>
       <c r="V6">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W6">
         <v>2.84</v>
@@ -2154,7 +2163,7 @@
         <v>160</v>
       </c>
       <c r="AF6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG6">
         <v>12.5</v>
@@ -2190,10 +2199,10 @@
         <v>18</v>
       </c>
       <c r="AR6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS6">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT6">
         <v>7</v>
@@ -2202,10 +2211,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV6">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AW6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX6">
         <v>6.4</v>
@@ -2217,7 +2226,7 @@
         <v>18.5</v>
       </c>
       <c r="BA6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB6">
         <v>9.6</v>
@@ -2226,16 +2235,16 @@
         <v>13.5</v>
       </c>
       <c r="BD6">
-        <v>5.9</v>
+        <v>28</v>
       </c>
       <c r="BE6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF6">
         <v>5.9</v>
       </c>
       <c r="BG6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH6">
         <v>3.75</v>
@@ -2298,7 +2307,7 @@
         <v>6.4</v>
       </c>
       <c r="CB6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2306,16 +2315,16 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F7">
         <v>1.04</v>
@@ -2540,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2548,16 +2557,16 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F8">
         <v>2.02</v>
@@ -2596,7 +2605,7 @@
         <v>1.74</v>
       </c>
       <c r="R8">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S8">
         <v>2.82</v>
@@ -2782,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2790,16 +2799,16 @@
         <v>87</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F9">
         <v>1.89</v>
@@ -2820,7 +2829,7 @@
         <v>3.8</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M9">
         <v>1.07</v>
@@ -3024,7 +3033,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="CB9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3032,34 +3041,34 @@
         <v>88</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E10" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F10">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H10">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="I10">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="J10">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="K10">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3077,7 +3086,7 @@
         <v>2.2</v>
       </c>
       <c r="Q10">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3266,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3274,25 +3283,25 @@
         <v>89</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F11">
         <v>4.1</v>
       </c>
       <c r="G11">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="H11">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I11">
         <v>2.06</v>
@@ -3430,16 +3439,16 @@
         <v>24</v>
       </c>
       <c r="BB11">
+        <v>4.5</v>
+      </c>
+      <c r="BC11">
         <v>4.4</v>
-      </c>
-      <c r="BC11">
-        <v>4.3</v>
       </c>
       <c r="BD11">
         <v>40</v>
       </c>
       <c r="BE11">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF11">
         <v>38</v>
@@ -3508,7 +3517,7 @@
         <v>7</v>
       </c>
       <c r="CB11" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3516,16 +3525,16 @@
         <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F12">
         <v>1.04</v>
@@ -3750,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3758,16 +3767,16 @@
         <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F13">
         <v>2.68</v>
@@ -3776,16 +3785,16 @@
         <v>3.2</v>
       </c>
       <c r="H13">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="I13">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="J13">
         <v>3.4</v>
       </c>
       <c r="K13">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3812,16 +3821,16 @@
         <v>2.7</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U13">
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W13">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3992,7 +4001,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4000,22 +4009,22 @@
         <v>91</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E14" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F14">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="G14">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H14">
         <v>3.85</v>
@@ -4024,7 +4033,7 @@
         <v>4.2</v>
       </c>
       <c r="J14">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K14">
         <v>4.5</v>
@@ -4234,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4242,31 +4251,31 @@
         <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F15">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G15">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H15">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I15">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J15">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K15">
         <v>4.3</v>
@@ -4278,13 +4287,13 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>4</v>
+        <v>2.32</v>
       </c>
       <c r="O15">
         <v>1.22</v>
       </c>
       <c r="P15">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="Q15">
         <v>1.61</v>
@@ -4296,16 +4305,16 @@
         <v>2.52</v>
       </c>
       <c r="T15">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U15">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V15">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W15">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X15">
         <v>23</v>
@@ -4332,10 +4341,10 @@
         <v>50</v>
       </c>
       <c r="AF15">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG15">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH15">
         <v>20</v>
@@ -4380,10 +4389,10 @@
         <v>6.8</v>
       </c>
       <c r="AV15">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AW15">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AX15">
         <v>10.5</v>
@@ -4395,16 +4404,16 @@
         <v>12</v>
       </c>
       <c r="BA15">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BB15">
         <v>18</v>
       </c>
       <c r="BC15">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD15">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BE15">
         <v>4</v>
@@ -4413,10 +4422,10 @@
         <v>9</v>
       </c>
       <c r="BG15">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BH15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI15">
         <v>3.05</v>
@@ -4425,13 +4434,13 @@
         <v>9.4</v>
       </c>
       <c r="BK15">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BN15">
         <v>5.3</v>
@@ -4440,19 +4449,19 @@
         <v>3.9</v>
       </c>
       <c r="BP15">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ15">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU15">
         <v>5.4</v>
@@ -4461,22 +4470,22 @@
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA15">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB15" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4484,16 +4493,16 @@
         <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E16" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F16">
         <v>1.42</v>
@@ -4718,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4726,28 +4735,28 @@
         <v>94</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E17" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F17">
         <v>1.72</v>
       </c>
       <c r="G17">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H17">
         <v>4.9</v>
       </c>
       <c r="I17">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J17">
         <v>3.9</v>
@@ -4765,7 +4774,7 @@
         <v>4.2</v>
       </c>
       <c r="O17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P17">
         <v>2.1</v>
@@ -4915,7 +4924,7 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="BN17">
         <v>4.5</v>
@@ -4960,7 +4969,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="CB17" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4968,19 +4977,19 @@
         <v>95</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E18" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F18">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="G18">
         <v>1.86</v>
@@ -4989,13 +4998,13 @@
         <v>4.6</v>
       </c>
       <c r="I18">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J18">
         <v>4</v>
       </c>
       <c r="K18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5019,7 +5028,7 @@
         <v>1.51</v>
       </c>
       <c r="S18">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="T18">
         <v>1.71</v>
@@ -5202,7 +5211,7 @@
         <v>8.4</v>
       </c>
       <c r="CB18" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5210,31 +5219,31 @@
         <v>96</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E19" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F19">
         <v>1.39</v>
       </c>
       <c r="G19">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="H19">
-        <v>1.39</v>
+        <v>2.28</v>
       </c>
       <c r="I19">
         <v>2.78</v>
       </c>
       <c r="J19">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="K19">
         <v>470</v>
@@ -5444,7 +5453,7 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5452,16 +5461,16 @@
         <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E20" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F20">
         <v>2.8</v>
@@ -5503,7 +5512,7 @@
         <v>1.6</v>
       </c>
       <c r="S20">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="T20">
         <v>1.54</v>
@@ -5563,31 +5572,31 @@
         <v>40</v>
       </c>
       <c r="AM20">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN20">
         <v>22</v>
       </c>
       <c r="AO20">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AP20">
-        <v>4.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ20">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR20">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS20">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT20">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="AU20">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AV20">
         <v>10.5</v>
@@ -5608,7 +5617,7 @@
         <v>20</v>
       </c>
       <c r="BB20">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BC20">
         <v>20</v>
@@ -5620,7 +5629,7 @@
         <v>4.8</v>
       </c>
       <c r="BF20">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BG20">
         <v>11.5</v>
@@ -5686,7 +5695,7 @@
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5694,16 +5703,16 @@
         <v>97</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F21">
         <v>2.14</v>
@@ -5721,7 +5730,7 @@
         <v>3.25</v>
       </c>
       <c r="K21">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5928,7 +5937,7 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5936,16 +5945,16 @@
         <v>98</v>
       </c>
       <c r="B22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E22" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -6170,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6178,34 +6187,34 @@
         <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D23" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E23" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F23">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="G23">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="H23">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I23">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="J23">
         <v>3.45</v>
       </c>
       <c r="K23">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6412,7 +6421,7 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6420,28 +6429,28 @@
         <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E24" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F24">
         <v>3.15</v>
       </c>
       <c r="G24">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="H24">
         <v>2.38</v>
       </c>
       <c r="I24">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="J24">
         <v>3.25</v>
@@ -6654,7 +6663,7 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6662,16 +6671,16 @@
         <v>81</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E25" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F25">
         <v>1.53</v>
@@ -6896,42 +6905,42 @@
         <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
         <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E26" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -6946,199 +6955,441 @@
         <v>0</v>
       </c>
       <c r="P26">
+        <v>1.1</v>
+      </c>
+      <c r="Q26">
+        <v>1.01</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AO26">
+        <v>0</v>
+      </c>
+      <c r="AP26">
+        <v>0</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26">
+        <v>0</v>
+      </c>
+      <c r="AV26">
+        <v>0</v>
+      </c>
+      <c r="AW26">
+        <v>0</v>
+      </c>
+      <c r="AX26">
+        <v>0</v>
+      </c>
+      <c r="AY26">
+        <v>0</v>
+      </c>
+      <c r="AZ26">
+        <v>0</v>
+      </c>
+      <c r="BA26">
+        <v>0</v>
+      </c>
+      <c r="BB26">
+        <v>0</v>
+      </c>
+      <c r="BC26">
+        <v>0</v>
+      </c>
+      <c r="BD26">
+        <v>0</v>
+      </c>
+      <c r="BE26">
+        <v>0</v>
+      </c>
+      <c r="BF26">
+        <v>0</v>
+      </c>
+      <c r="BG26">
+        <v>0</v>
+      </c>
+      <c r="BH26">
+        <v>0</v>
+      </c>
+      <c r="BI26">
+        <v>0</v>
+      </c>
+      <c r="BJ26">
+        <v>0</v>
+      </c>
+      <c r="BK26">
+        <v>0</v>
+      </c>
+      <c r="BL26">
+        <v>0</v>
+      </c>
+      <c r="BM26">
+        <v>0</v>
+      </c>
+      <c r="BN26">
+        <v>0</v>
+      </c>
+      <c r="BO26">
+        <v>0</v>
+      </c>
+      <c r="BP26">
+        <v>0</v>
+      </c>
+      <c r="BQ26">
+        <v>0</v>
+      </c>
+      <c r="BR26">
+        <v>0</v>
+      </c>
+      <c r="BS26">
+        <v>0</v>
+      </c>
+      <c r="BT26">
+        <v>0</v>
+      </c>
+      <c r="BU26">
+        <v>0</v>
+      </c>
+      <c r="BV26">
+        <v>0</v>
+      </c>
+      <c r="BW26">
+        <v>0</v>
+      </c>
+      <c r="BX26">
+        <v>0</v>
+      </c>
+      <c r="BY26">
+        <v>0</v>
+      </c>
+      <c r="BZ26">
+        <v>0</v>
+      </c>
+      <c r="CA26">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>98</v>
+      </c>
+      <c r="B27" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" t="s">
+        <v>142</v>
+      </c>
+      <c r="E27" t="s">
+        <v>168</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
         <v>1.24</v>
       </c>
-      <c r="Q26">
+      <c r="Q27">
         <v>1.02</v>
       </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>0</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-      <c r="AB26">
-        <v>0</v>
-      </c>
-      <c r="AC26">
-        <v>0</v>
-      </c>
-      <c r="AD26">
-        <v>0</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>0</v>
-      </c>
-      <c r="AG26">
-        <v>0</v>
-      </c>
-      <c r="AH26">
-        <v>0</v>
-      </c>
-      <c r="AI26">
-        <v>0</v>
-      </c>
-      <c r="AJ26">
-        <v>0</v>
-      </c>
-      <c r="AK26">
-        <v>0</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>0</v>
-      </c>
-      <c r="AN26">
-        <v>0</v>
-      </c>
-      <c r="AO26">
-        <v>0</v>
-      </c>
-      <c r="AP26">
-        <v>0</v>
-      </c>
-      <c r="AQ26">
-        <v>0</v>
-      </c>
-      <c r="AR26">
-        <v>0</v>
-      </c>
-      <c r="AS26">
-        <v>0</v>
-      </c>
-      <c r="AT26">
-        <v>0</v>
-      </c>
-      <c r="AU26">
-        <v>0</v>
-      </c>
-      <c r="AV26">
-        <v>0</v>
-      </c>
-      <c r="AW26">
-        <v>0</v>
-      </c>
-      <c r="AX26">
-        <v>0</v>
-      </c>
-      <c r="AY26">
-        <v>0</v>
-      </c>
-      <c r="AZ26">
-        <v>0</v>
-      </c>
-      <c r="BA26">
-        <v>0</v>
-      </c>
-      <c r="BB26">
-        <v>0</v>
-      </c>
-      <c r="BC26">
-        <v>0</v>
-      </c>
-      <c r="BD26">
-        <v>0</v>
-      </c>
-      <c r="BE26">
-        <v>0</v>
-      </c>
-      <c r="BF26">
-        <v>0</v>
-      </c>
-      <c r="BG26">
-        <v>0</v>
-      </c>
-      <c r="BH26">
-        <v>0</v>
-      </c>
-      <c r="BI26">
-        <v>0</v>
-      </c>
-      <c r="BJ26">
-        <v>0</v>
-      </c>
-      <c r="BK26">
-        <v>0</v>
-      </c>
-      <c r="BL26">
-        <v>0</v>
-      </c>
-      <c r="BM26">
-        <v>0</v>
-      </c>
-      <c r="BN26">
-        <v>0</v>
-      </c>
-      <c r="BO26">
-        <v>0</v>
-      </c>
-      <c r="BP26">
-        <v>0</v>
-      </c>
-      <c r="BQ26">
-        <v>0</v>
-      </c>
-      <c r="BR26">
-        <v>0</v>
-      </c>
-      <c r="BS26">
-        <v>0</v>
-      </c>
-      <c r="BT26">
-        <v>0</v>
-      </c>
-      <c r="BU26">
-        <v>0</v>
-      </c>
-      <c r="BV26">
-        <v>0</v>
-      </c>
-      <c r="BW26">
-        <v>0</v>
-      </c>
-      <c r="BX26">
-        <v>0</v>
-      </c>
-      <c r="BY26">
-        <v>0</v>
-      </c>
-      <c r="BZ26">
-        <v>0</v>
-      </c>
-      <c r="CA26">
-        <v>0</v>
-      </c>
-      <c r="CB26" t="s">
-        <v>166</v>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27">
+        <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>0</v>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+      <c r="AN27">
+        <v>0</v>
+      </c>
+      <c r="AO27">
+        <v>0</v>
+      </c>
+      <c r="AP27">
+        <v>0</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27">
+        <v>0</v>
+      </c>
+      <c r="AV27">
+        <v>0</v>
+      </c>
+      <c r="AW27">
+        <v>0</v>
+      </c>
+      <c r="AX27">
+        <v>0</v>
+      </c>
+      <c r="AY27">
+        <v>0</v>
+      </c>
+      <c r="AZ27">
+        <v>0</v>
+      </c>
+      <c r="BA27">
+        <v>0</v>
+      </c>
+      <c r="BB27">
+        <v>0</v>
+      </c>
+      <c r="BC27">
+        <v>0</v>
+      </c>
+      <c r="BD27">
+        <v>0</v>
+      </c>
+      <c r="BE27">
+        <v>0</v>
+      </c>
+      <c r="BF27">
+        <v>0</v>
+      </c>
+      <c r="BG27">
+        <v>0</v>
+      </c>
+      <c r="BH27">
+        <v>0</v>
+      </c>
+      <c r="BI27">
+        <v>0</v>
+      </c>
+      <c r="BJ27">
+        <v>0</v>
+      </c>
+      <c r="BK27">
+        <v>0</v>
+      </c>
+      <c r="BL27">
+        <v>0</v>
+      </c>
+      <c r="BM27">
+        <v>0</v>
+      </c>
+      <c r="BN27">
+        <v>0</v>
+      </c>
+      <c r="BO27">
+        <v>0</v>
+      </c>
+      <c r="BP27">
+        <v>0</v>
+      </c>
+      <c r="BQ27">
+        <v>0</v>
+      </c>
+      <c r="BR27">
+        <v>0</v>
+      </c>
+      <c r="BS27">
+        <v>0</v>
+      </c>
+      <c r="BT27">
+        <v>0</v>
+      </c>
+      <c r="BU27">
+        <v>0</v>
+      </c>
+      <c r="BV27">
+        <v>0</v>
+      </c>
+      <c r="BW27">
+        <v>0</v>
+      </c>
+      <c r="BX27">
+        <v>0</v>
+      </c>
+      <c r="BY27">
+        <v>0</v>
+      </c>
+      <c r="BZ27">
+        <v>0</v>
+      </c>
+      <c r="CA27">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -523,7 +523,7 @@
     <t>Thor</t>
   </si>
   <si>
-    <t>2026-07-25 05:25:25</t>
+    <t>2026-07-25 07:44:46</t>
   </si>
 </sst>
 </file>
@@ -1219,7 +1219,7 @@
         <v>210</v>
       </c>
       <c r="AN2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO2">
         <v>210</v>
@@ -1231,10 +1231,10 @@
         <v>17.5</v>
       </c>
       <c r="AR2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT2">
         <v>6.4</v>
@@ -1243,10 +1243,10 @@
         <v>8.4</v>
       </c>
       <c r="AV2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AW2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX2">
         <v>7.8</v>
@@ -1258,25 +1258,25 @@
         <v>6.8</v>
       </c>
       <c r="BA2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2">
         <v>13</v>
       </c>
       <c r="BC2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD2">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="BE2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF2">
         <v>7.6</v>
       </c>
       <c r="BG2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1389,10 +1389,10 @@
         <v>1.41</v>
       </c>
       <c r="P3">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="Q3">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R3">
         <v>1.21</v>
@@ -1404,7 +1404,7 @@
         <v>1.01</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="V3">
         <v>1.33</v>
@@ -1464,58 +1464,58 @@
         <v>1000</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP3">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AQ3">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="AR3">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AS3">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AT3">
+        <v>2.14</v>
+      </c>
+      <c r="AU3">
         <v>2.1</v>
       </c>
-      <c r="AU3">
-        <v>2.06</v>
-      </c>
       <c r="AV3">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AW3">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="AX3">
         <v>9.4</v>
       </c>
       <c r="AY3">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="AZ3">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BA3">
+        <v>2.56</v>
+      </c>
+      <c r="BB3">
         <v>2.5</v>
-      </c>
-      <c r="BB3">
-        <v>2.42</v>
       </c>
       <c r="BC3">
         <v>19</v>
       </c>
       <c r="BD3">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="BE3">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="BF3">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="BG3">
         <v>2.56</v>
@@ -1625,7 +1625,7 @@
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O4">
         <v>1.33</v>
@@ -1637,13 +1637,13 @@
         <v>1.98</v>
       </c>
       <c r="R4">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S4">
         <v>3.55</v>
       </c>
       <c r="T4">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="U4">
         <v>2.12</v>
@@ -1652,7 +1652,7 @@
         <v>1.45</v>
       </c>
       <c r="W4">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X4">
         <v>16</v>
@@ -1718,7 +1718,7 @@
         <v>18</v>
       </c>
       <c r="AS4">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="AT4">
         <v>9</v>
@@ -1763,7 +1763,7 @@
         <v>7.4</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI4">
         <v>3</v>
@@ -1772,16 +1772,16 @@
         <v>9.6</v>
       </c>
       <c r="BK4">
-        <v>1.54</v>
+        <v>5.9</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.81</v>
+        <v>13.5</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO4">
         <v>4.3</v>
@@ -1790,13 +1790,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ4">
-        <v>1.68</v>
+        <v>8.6</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>1.74</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
         <v>6.2</v>
@@ -1808,19 +1808,19 @@
         <v>25</v>
       </c>
       <c r="BW4">
-        <v>1.71</v>
+        <v>9.4</v>
       </c>
       <c r="BX4">
         <v>38</v>
       </c>
       <c r="BY4">
-        <v>1.75</v>
+        <v>11</v>
       </c>
       <c r="BZ4">
         <v>29</v>
       </c>
       <c r="CA4">
-        <v>1.73</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="s">
         <v>169</v>
@@ -1846,7 +1846,7 @@
         <v>1.58</v>
       </c>
       <c r="G5">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H5">
         <v>6</v>
@@ -1957,7 +1957,7 @@
         <v>17.5</v>
       </c>
       <c r="AR5">
-        <v>7.2</v>
+        <v>38</v>
       </c>
       <c r="AS5">
         <v>7.8</v>
@@ -2094,37 +2094,37 @@
         <v>7.6</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>4.4</v>
       </c>
       <c r="K6">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="L6">
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
-        <v>3.9</v>
+        <v>2.12</v>
       </c>
       <c r="O6">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P6">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q6">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="R6">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S6">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="T6">
         <v>2.02</v>
@@ -2247,64 +2247,64 @@
         <v>6.8</v>
       </c>
       <c r="BH6">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
         <v>169</v>
@@ -2360,7 +2360,7 @@
         <v>1.24</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2584,7 +2584,7 @@
         <v>3.35</v>
       </c>
       <c r="K8">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2617,7 +2617,7 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W8">
         <v>1.73</v>
@@ -2829,7 +2829,7 @@
         <v>3.8</v>
       </c>
       <c r="L9">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="M9">
         <v>1.07</v>
@@ -3083,10 +3083,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q10">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3782,10 +3782,10 @@
         <v>2.68</v>
       </c>
       <c r="G13">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H13">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="I13">
         <v>2.82</v>
@@ -3803,16 +3803,16 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="O13">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P13">
         <v>2.1</v>
       </c>
       <c r="Q13">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R13">
         <v>1.43</v>
@@ -3821,7 +3821,7 @@
         <v>2.7</v>
       </c>
       <c r="T13">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="U13">
         <v>1.01</v>
@@ -3830,7 +3830,7 @@
         <v>1.54</v>
       </c>
       <c r="W13">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4021,7 +4021,7 @@
         <v>155</v>
       </c>
       <c r="F14">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="G14">
         <v>1.95</v>
@@ -4030,13 +4030,13 @@
         <v>3.85</v>
       </c>
       <c r="I14">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K14">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4051,7 +4051,7 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="Q14">
         <v>1.54</v>
@@ -4263,7 +4263,7 @@
         <v>156</v>
       </c>
       <c r="F15">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G15">
         <v>2.22</v>
@@ -4305,13 +4305,13 @@
         <v>2.52</v>
       </c>
       <c r="T15">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U15">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V15">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W15">
         <v>1.82</v>
@@ -4505,7 +4505,7 @@
         <v>157</v>
       </c>
       <c r="F16">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="G16">
         <v>1.5</v>
@@ -4514,7 +4514,7 @@
         <v>3.05</v>
       </c>
       <c r="I16">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="J16">
         <v>5.3</v>
@@ -4750,13 +4750,13 @@
         <v>1.72</v>
       </c>
       <c r="G17">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H17">
         <v>4.9</v>
       </c>
       <c r="I17">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J17">
         <v>3.9</v>
@@ -4798,7 +4798,7 @@
         <v>1.22</v>
       </c>
       <c r="W17">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X17">
         <v>20</v>
@@ -4828,7 +4828,7 @@
         <v>13</v>
       </c>
       <c r="AG17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH17">
         <v>22</v>
@@ -4861,10 +4861,10 @@
         <v>15</v>
       </c>
       <c r="AR17">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS17">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT17">
         <v>8.4</v>
@@ -4876,7 +4876,7 @@
         <v>15.5</v>
       </c>
       <c r="AW17">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX17">
         <v>9.800000000000001</v>
@@ -4888,7 +4888,7 @@
         <v>14.5</v>
       </c>
       <c r="BA17">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB17">
         <v>15.5</v>
@@ -4897,16 +4897,16 @@
         <v>13.5</v>
       </c>
       <c r="BD17">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE17">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF17">
         <v>7.6</v>
       </c>
       <c r="BG17">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH17">
         <v>3.75</v>
@@ -4989,7 +4989,7 @@
         <v>159</v>
       </c>
       <c r="F18">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G18">
         <v>1.86</v>
@@ -4998,13 +4998,13 @@
         <v>4.6</v>
       </c>
       <c r="I18">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J18">
         <v>4</v>
       </c>
       <c r="K18">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5070,7 +5070,7 @@
         <v>12.5</v>
       </c>
       <c r="AG18">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH18">
         <v>21</v>
@@ -5091,7 +5091,7 @@
         <v>90</v>
       </c>
       <c r="AN18">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO18">
         <v>55</v>
@@ -5103,10 +5103,10 @@
         <v>17.5</v>
       </c>
       <c r="AR18">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS18">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT18">
         <v>9.800000000000001</v>
@@ -5118,7 +5118,7 @@
         <v>16.5</v>
       </c>
       <c r="AW18">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX18">
         <v>9.6</v>
@@ -5130,7 +5130,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB18">
         <v>15</v>
@@ -5139,16 +5139,16 @@
         <v>13.5</v>
       </c>
       <c r="BD18">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BE18">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF18">
         <v>7.8</v>
       </c>
       <c r="BG18">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BH18">
         <v>4</v>
@@ -5234,16 +5234,16 @@
         <v>1.39</v>
       </c>
       <c r="G19">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="H19">
-        <v>2.28</v>
+        <v>1.39</v>
       </c>
       <c r="I19">
         <v>2.78</v>
       </c>
       <c r="J19">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="K19">
         <v>470</v>
@@ -5473,7 +5473,7 @@
         <v>161</v>
       </c>
       <c r="F20">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G20">
         <v>3.05</v>
@@ -5506,13 +5506,13 @@
         <v>2.5</v>
       </c>
       <c r="Q20">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="R20">
         <v>1.6</v>
       </c>
       <c r="S20">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="T20">
         <v>1.54</v>
@@ -5572,7 +5572,7 @@
         <v>40</v>
       </c>
       <c r="AM20">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN20">
         <v>22</v>
@@ -5587,13 +5587,13 @@
         <v>13.5</v>
       </c>
       <c r="AR20">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS20">
         <v>25</v>
       </c>
       <c r="AT20">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AU20">
         <v>8.6</v>
@@ -5605,7 +5605,7 @@
         <v>16.5</v>
       </c>
       <c r="AX20">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AY20">
         <v>12</v>
@@ -5617,7 +5617,7 @@
         <v>20</v>
       </c>
       <c r="BB20">
-        <v>4.7</v>
+        <v>30</v>
       </c>
       <c r="BC20">
         <v>20</v>
@@ -5629,10 +5629,10 @@
         <v>4.8</v>
       </c>
       <c r="BF20">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BG20">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5715,7 +5715,7 @@
         <v>162</v>
       </c>
       <c r="F21">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="G21">
         <v>2.9</v>
@@ -5730,7 +5730,7 @@
         <v>3.25</v>
       </c>
       <c r="K21">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -6199,22 +6199,22 @@
         <v>164</v>
       </c>
       <c r="F23">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="G23">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="I23">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J23">
         <v>3.45</v>
       </c>
       <c r="K23">
-        <v>4.3</v>
+        <v>330</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6716,7 +6716,7 @@
         <v>1.76</v>
       </c>
       <c r="Q25">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -6955,7 +6955,7 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q26">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -523,7 +523,7 @@
     <t>Thor</t>
   </si>
   <si>
-    <t>2026-07-25 07:44:46</t>
+    <t>2026-07-25 10:03:49</t>
   </si>
 </sst>
 </file>
@@ -1129,7 +1129,7 @@
         <v>7.8</v>
       </c>
       <c r="J2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>4.4</v>
@@ -1359,10 +1359,10 @@
         <v>144</v>
       </c>
       <c r="F3">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G3">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H3">
         <v>3.55</v>
@@ -1371,7 +1371,7 @@
         <v>4</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K3">
         <v>3.45</v>
@@ -1389,10 +1389,10 @@
         <v>1.41</v>
       </c>
       <c r="P3">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="Q3">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R3">
         <v>1.21</v>
@@ -1410,7 +1410,7 @@
         <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X3">
         <v>15.5</v>
@@ -1616,16 +1616,16 @@
         <v>3.45</v>
       </c>
       <c r="K4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L4">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O4">
         <v>1.33</v>
@@ -1843,10 +1843,10 @@
         <v>146</v>
       </c>
       <c r="F5">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G5">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H5">
         <v>6</v>
@@ -1867,7 +1867,7 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O5">
         <v>1.24</v>
@@ -1879,7 +1879,7 @@
         <v>1.71</v>
       </c>
       <c r="R5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S5">
         <v>2.8</v>
@@ -2085,19 +2085,19 @@
         <v>147</v>
       </c>
       <c r="F6">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="G6">
         <v>1.54</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>9</v>
       </c>
       <c r="J6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K6">
         <v>4.9</v>
@@ -2109,37 +2109,37 @@
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>2.12</v>
+        <v>3.2</v>
       </c>
       <c r="O6">
         <v>1.27</v>
       </c>
       <c r="P6">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q6">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S6">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="T6">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="U6">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="V6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W6">
         <v>2.84</v>
       </c>
       <c r="X6">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Y6">
         <v>32</v>
@@ -2199,10 +2199,10 @@
         <v>18</v>
       </c>
       <c r="AR6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT6">
         <v>7</v>
@@ -2211,10 +2211,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AW6">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX6">
         <v>6.4</v>
@@ -2226,7 +2226,7 @@
         <v>18.5</v>
       </c>
       <c r="BA6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB6">
         <v>9.6</v>
@@ -2238,13 +2238,13 @@
         <v>28</v>
       </c>
       <c r="BE6">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF6">
         <v>5.9</v>
       </c>
       <c r="BG6">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2826,7 +2826,7 @@
         <v>3.65</v>
       </c>
       <c r="K9">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L9">
         <v>1.34</v>
@@ -2934,7 +2934,7 @@
         <v>8</v>
       </c>
       <c r="AU9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV9">
         <v>15</v>
@@ -3083,10 +3083,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q10">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3307,7 +3307,7 @@
         <v>2.06</v>
       </c>
       <c r="J11">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K11">
         <v>4.1</v>
@@ -3316,7 +3316,7 @@
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N11">
         <v>3.85</v>
@@ -3325,16 +3325,16 @@
         <v>1.28</v>
       </c>
       <c r="P11">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="Q11">
         <v>1.83</v>
       </c>
       <c r="R11">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="S11">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="T11">
         <v>1.74</v>
@@ -3806,7 +3806,7 @@
         <v>2.76</v>
       </c>
       <c r="O13">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P13">
         <v>2.1</v>
@@ -4030,7 +4030,7 @@
         <v>3.85</v>
       </c>
       <c r="I14">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J14">
         <v>4.3</v>
@@ -4263,7 +4263,7 @@
         <v>156</v>
       </c>
       <c r="F15">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="G15">
         <v>2.22</v>
@@ -4305,16 +4305,16 @@
         <v>2.52</v>
       </c>
       <c r="T15">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U15">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V15">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W15">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="X15">
         <v>23</v>
@@ -4750,16 +4750,16 @@
         <v>1.72</v>
       </c>
       <c r="G17">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="H17">
         <v>4.9</v>
       </c>
       <c r="I17">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J17">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K17">
         <v>4.4</v>
@@ -4789,16 +4789,16 @@
         <v>2.98</v>
       </c>
       <c r="T17">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U17">
         <v>2.12</v>
       </c>
       <c r="V17">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W17">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X17">
         <v>20</v>
@@ -4870,7 +4870,7 @@
         <v>8.4</v>
       </c>
       <c r="AU17">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV17">
         <v>15.5</v>
@@ -4924,7 +4924,7 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BN17">
         <v>4.5</v>
@@ -4936,16 +4936,16 @@
         <v>11.5</v>
       </c>
       <c r="BQ17">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT17">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU17">
         <v>5.6</v>
@@ -4954,19 +4954,19 @@
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB17" t="s">
         <v>169</v>
@@ -4989,16 +4989,16 @@
         <v>159</v>
       </c>
       <c r="F18">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="G18">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H18">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I18">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -5028,7 +5028,7 @@
         <v>1.51</v>
       </c>
       <c r="S18">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T18">
         <v>1.71</v>
@@ -5037,7 +5037,7 @@
         <v>2.26</v>
       </c>
       <c r="V18">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W18">
         <v>2.16</v>
@@ -5070,7 +5070,7 @@
         <v>12.5</v>
       </c>
       <c r="AG18">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH18">
         <v>21</v>
@@ -5091,7 +5091,7 @@
         <v>90</v>
       </c>
       <c r="AN18">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO18">
         <v>55</v>
@@ -5103,10 +5103,10 @@
         <v>17.5</v>
       </c>
       <c r="AR18">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS18">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT18">
         <v>9.800000000000001</v>
@@ -5139,10 +5139,10 @@
         <v>13.5</v>
       </c>
       <c r="BD18">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE18">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF18">
         <v>7.8</v>
@@ -5234,7 +5234,7 @@
         <v>1.39</v>
       </c>
       <c r="G19">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H19">
         <v>1.39</v>
@@ -6444,7 +6444,7 @@
         <v>3.15</v>
       </c>
       <c r="G24">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="H24">
         <v>2.38</v>
@@ -6471,10 +6471,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="Q24">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="R24">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -523,7 +523,7 @@
     <t>Thor</t>
   </si>
   <si>
-    <t>2026-07-25 10:03:49</t>
+    <t>2026-07-25 12:21:53</t>
   </si>
 </sst>
 </file>
@@ -1362,7 +1362,7 @@
         <v>2.22</v>
       </c>
       <c r="G3">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H3">
         <v>3.55</v>
@@ -1374,151 +1374,151 @@
         <v>3.15</v>
       </c>
       <c r="K3">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="O3">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P3">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q3">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="R3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U3">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="V3">
         <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X3">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="Y3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Z3">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AA3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AB3">
+        <v>8.4</v>
+      </c>
+      <c r="AC3">
+        <v>7.6</v>
+      </c>
+      <c r="AD3">
+        <v>16</v>
+      </c>
+      <c r="AE3">
+        <v>55</v>
+      </c>
+      <c r="AF3">
+        <v>14</v>
+      </c>
+      <c r="AG3">
         <v>11.5</v>
       </c>
-      <c r="AC3">
-        <v>10.5</v>
-      </c>
-      <c r="AD3">
-        <v>23</v>
-      </c>
-      <c r="AE3">
-        <v>75</v>
-      </c>
-      <c r="AF3">
-        <v>20</v>
-      </c>
-      <c r="AG3">
-        <v>17</v>
-      </c>
       <c r="AH3">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AI3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AJ3">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AK3">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AL3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO3">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP3">
-        <v>2.26</v>
+        <v>5.4</v>
       </c>
       <c r="AQ3">
-        <v>2.28</v>
+        <v>10</v>
       </c>
       <c r="AR3">
-        <v>2.46</v>
+        <v>7.6</v>
       </c>
       <c r="AS3">
-        <v>2.56</v>
+        <v>9.6</v>
       </c>
       <c r="AT3">
-        <v>2.14</v>
+        <v>7.2</v>
       </c>
       <c r="AU3">
-        <v>2.1</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>2.36</v>
+        <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>2.54</v>
+        <v>9</v>
       </c>
       <c r="AX3">
+        <v>12</v>
+      </c>
+      <c r="AY3">
+        <v>10</v>
+      </c>
+      <c r="AZ3">
+        <v>17.5</v>
+      </c>
+      <c r="BA3">
         <v>9.4</v>
       </c>
-      <c r="AY3">
-        <v>2.28</v>
-      </c>
-      <c r="AZ3">
-        <v>2.42</v>
-      </c>
-      <c r="BA3">
-        <v>2.56</v>
-      </c>
       <c r="BB3">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="BC3">
-        <v>19</v>
+        <v>7.8</v>
       </c>
       <c r="BD3">
-        <v>2.54</v>
+        <v>9</v>
       </c>
       <c r="BE3">
-        <v>2.64</v>
+        <v>10</v>
       </c>
       <c r="BF3">
-        <v>2.64</v>
+        <v>18.5</v>
       </c>
       <c r="BG3">
-        <v>2.56</v>
+        <v>9.6</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1604,7 +1604,7 @@
         <v>2.46</v>
       </c>
       <c r="G4">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -1619,7 +1619,7 @@
         <v>3.75</v>
       </c>
       <c r="L4">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="M4">
         <v>1.07</v>
@@ -1652,7 +1652,7 @@
         <v>1.45</v>
       </c>
       <c r="W4">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X4">
         <v>16</v>
@@ -1843,7 +1843,7 @@
         <v>146</v>
       </c>
       <c r="F5">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G5">
         <v>1.64</v>
@@ -1858,7 +1858,7 @@
         <v>4.2</v>
       </c>
       <c r="K5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1870,34 +1870,34 @@
         <v>4.6</v>
       </c>
       <c r="O5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P5">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q5">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R5">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S5">
         <v>2.8</v>
       </c>
       <c r="T5">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U5">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V5">
         <v>1.17</v>
       </c>
       <c r="W5">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="X5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Y5">
         <v>25</v>
@@ -1912,7 +1912,7 @@
         <v>10.5</v>
       </c>
       <c r="AC5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD5">
         <v>25</v>
@@ -1924,7 +1924,7 @@
         <v>11</v>
       </c>
       <c r="AG5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
         <v>22</v>
@@ -1933,7 +1933,7 @@
         <v>75</v>
       </c>
       <c r="AJ5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK5">
         <v>17</v>
@@ -1945,13 +1945,13 @@
         <v>120</v>
       </c>
       <c r="AN5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO5">
         <v>90</v>
       </c>
       <c r="AP5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ5">
         <v>17.5</v>
@@ -1960,10 +1960,10 @@
         <v>38</v>
       </c>
       <c r="AS5">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU5">
         <v>8.800000000000001</v>
@@ -1972,37 +1972,37 @@
         <v>18</v>
       </c>
       <c r="AW5">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY5">
+        <v>9</v>
+      </c>
+      <c r="AZ5">
+        <v>17</v>
+      </c>
+      <c r="BA5">
+        <v>10</v>
+      </c>
+      <c r="BB5">
+        <v>13</v>
+      </c>
+      <c r="BC5">
+        <v>14</v>
+      </c>
+      <c r="BD5">
         <v>8.199999999999999</v>
       </c>
-      <c r="AY5">
-        <v>8.6</v>
-      </c>
-      <c r="AZ5">
-        <v>15.5</v>
-      </c>
-      <c r="BA5">
-        <v>7.8</v>
-      </c>
-      <c r="BB5">
-        <v>12</v>
-      </c>
-      <c r="BC5">
-        <v>12.5</v>
-      </c>
-      <c r="BD5">
-        <v>6.6</v>
-      </c>
       <c r="BE5">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BF5">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG5">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2088,7 +2088,7 @@
         <v>1.47</v>
       </c>
       <c r="G6">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H6">
         <v>7.8</v>
@@ -2106,37 +2106,37 @@
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N6">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="O6">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P6">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q6">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="R6">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S6">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="T6">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="U6">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="V6">
         <v>1.12</v>
       </c>
       <c r="W6">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="X6">
         <v>17</v>
@@ -2345,202 +2345,202 @@
         <v>410</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="P7">
         <v>1.24</v>
       </c>
       <c r="Q7">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2814,22 +2814,22 @@
         <v>1.89</v>
       </c>
       <c r="G9">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="H9">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K9">
         <v>3.85</v>
       </c>
       <c r="L9">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M9">
         <v>1.07</v>
@@ -2856,13 +2856,13 @@
         <v>1.84</v>
       </c>
       <c r="U9">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V9">
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="X9">
         <v>16.5</v>
@@ -2901,7 +2901,7 @@
         <v>65</v>
       </c>
       <c r="AJ9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK9">
         <v>23</v>
@@ -2925,7 +2925,7 @@
         <v>13</v>
       </c>
       <c r="AR9">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS9">
         <v>5.5</v>
@@ -2976,7 +2976,7 @@
         <v>3.45</v>
       </c>
       <c r="BI9">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ9">
         <v>10.5</v>
@@ -2988,7 +2988,7 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN9">
         <v>4.5</v>
@@ -3000,19 +3000,19 @@
         <v>13</v>
       </c>
       <c r="BQ9">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT9">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BV9">
         <v>1000</v>
@@ -3024,13 +3024,13 @@
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB9" t="s">
         <v>169</v>
@@ -3086,7 +3086,7 @@
         <v>2.2</v>
       </c>
       <c r="Q10">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3295,19 +3295,19 @@
         <v>152</v>
       </c>
       <c r="F11">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G11">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="H11">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="I11">
         <v>2.06</v>
       </c>
       <c r="J11">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="K11">
         <v>4.1</v>
@@ -3316,7 +3316,7 @@
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N11">
         <v>3.85</v>
@@ -3325,28 +3325,28 @@
         <v>1.28</v>
       </c>
       <c r="P11">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="Q11">
         <v>1.83</v>
       </c>
       <c r="R11">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S11">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="T11">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U11">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V11">
         <v>1.94</v>
       </c>
       <c r="W11">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X11">
         <v>19.5</v>
@@ -3457,64 +3457,64 @@
         <v>9.6</v>
       </c>
       <c r="BH11">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
         <v>169</v>
@@ -3830,7 +3830,7 @@
         <v>1.54</v>
       </c>
       <c r="W13">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4030,7 +4030,7 @@
         <v>3.85</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J14">
         <v>4.3</v>
@@ -4054,7 +4054,7 @@
         <v>2.72</v>
       </c>
       <c r="Q14">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4263,22 +4263,22 @@
         <v>156</v>
       </c>
       <c r="F15">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="G15">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="H15">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="I15">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J15">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K15">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4305,16 +4305,16 @@
         <v>2.52</v>
       </c>
       <c r="T15">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W15">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="X15">
         <v>23</v>
@@ -4377,7 +4377,7 @@
         <v>12</v>
       </c>
       <c r="AR15">
-        <v>20</v>
+        <v>3.8</v>
       </c>
       <c r="AS15">
         <v>4</v>
@@ -4425,64 +4425,64 @@
         <v>3.85</v>
       </c>
       <c r="BH15">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
         <v>169</v>
@@ -4924,7 +4924,7 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>2.36</v>
+        <v>6.2</v>
       </c>
       <c r="BN17">
         <v>4.5</v>
@@ -4989,10 +4989,10 @@
         <v>159</v>
       </c>
       <c r="F18">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G18">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="H18">
         <v>4.5</v>
@@ -5013,7 +5013,7 @@
         <v>1.05</v>
       </c>
       <c r="N18">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O18">
         <v>1.24</v>
@@ -5028,7 +5028,7 @@
         <v>1.51</v>
       </c>
       <c r="S18">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T18">
         <v>1.71</v>
@@ -5037,10 +5037,10 @@
         <v>2.26</v>
       </c>
       <c r="V18">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W18">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X18">
         <v>21</v>
@@ -5052,34 +5052,34 @@
         <v>44</v>
       </c>
       <c r="AA18">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB18">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AC18">
         <v>9.800000000000001</v>
       </c>
       <c r="AD18">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE18">
         <v>65</v>
       </c>
       <c r="AF18">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG18">
         <v>10</v>
       </c>
       <c r="AH18">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI18">
         <v>65</v>
       </c>
       <c r="AJ18">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK18">
         <v>17.5</v>
@@ -5103,10 +5103,10 @@
         <v>17.5</v>
       </c>
       <c r="AR18">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS18">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AT18">
         <v>9.800000000000001</v>
@@ -5118,7 +5118,7 @@
         <v>16.5</v>
       </c>
       <c r="AW18">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX18">
         <v>9.6</v>
@@ -5130,7 +5130,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB18">
         <v>15</v>
@@ -5139,76 +5139,76 @@
         <v>13.5</v>
       </c>
       <c r="BD18">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE18">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF18">
         <v>7.8</v>
       </c>
       <c r="BG18">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH18">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM18">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="s">
         <v>169</v>
@@ -5231,22 +5231,22 @@
         <v>160</v>
       </c>
       <c r="F19">
-        <v>1.39</v>
+        <v>3.05</v>
       </c>
       <c r="G19">
         <v>3.15</v>
       </c>
       <c r="H19">
-        <v>1.39</v>
+        <v>2.5</v>
       </c>
       <c r="I19">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="J19">
-        <v>1.58</v>
+        <v>3.2</v>
       </c>
       <c r="K19">
-        <v>470</v>
+        <v>3.7</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5479,7 +5479,7 @@
         <v>3.05</v>
       </c>
       <c r="H20">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I20">
         <v>2.5</v>
@@ -5497,28 +5497,28 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O20">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P20">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q20">
         <v>1.48</v>
       </c>
       <c r="R20">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S20">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T20">
         <v>1.54</v>
       </c>
       <c r="U20">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V20">
         <v>1.67</v>
@@ -5584,25 +5584,25 @@
         <v>17.5</v>
       </c>
       <c r="AQ20">
+        <v>11</v>
+      </c>
+      <c r="AR20">
         <v>13.5</v>
       </c>
-      <c r="AR20">
-        <v>16.5</v>
-      </c>
       <c r="AS20">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AT20">
         <v>15</v>
       </c>
       <c r="AU20">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV20">
         <v>10.5</v>
       </c>
       <c r="AW20">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX20">
         <v>17</v>
@@ -5617,7 +5617,7 @@
         <v>20</v>
       </c>
       <c r="BB20">
-        <v>30</v>
+        <v>4.7</v>
       </c>
       <c r="BC20">
         <v>20</v>
@@ -5629,10 +5629,10 @@
         <v>4.8</v>
       </c>
       <c r="BF20">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BG20">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -6199,22 +6199,22 @@
         <v>164</v>
       </c>
       <c r="F23">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G23">
         <v>2</v>
       </c>
       <c r="H23">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="I23">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J23">
         <v>3.45</v>
       </c>
       <c r="K23">
-        <v>330</v>
+        <v>4.3</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6232,7 +6232,7 @@
         <v>1.8</v>
       </c>
       <c r="Q23">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6447,7 +6447,7 @@
         <v>3.5</v>
       </c>
       <c r="H24">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I24">
         <v>2.68</v>
@@ -6474,7 +6474,7 @@
         <v>1.79</v>
       </c>
       <c r="Q24">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6686,19 +6686,19 @@
         <v>1.53</v>
       </c>
       <c r="G25">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="H25">
-        <v>2.16</v>
+        <v>4.9</v>
       </c>
       <c r="I25">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="J25">
         <v>3.85</v>
       </c>
       <c r="K25">
-        <v>480</v>
+        <v>6</v>
       </c>
       <c r="L25">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -523,7 +523,7 @@
     <t>Thor</t>
   </si>
   <si>
-    <t>2026-07-25 12:21:53</t>
+    <t>2026-07-25 14:39:06</t>
   </si>
 </sst>
 </file>
@@ -1132,10 +1132,10 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M2">
         <v>1.07</v>
@@ -1144,7 +1144,7 @@
         <v>3.45</v>
       </c>
       <c r="O2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P2">
         <v>1.85</v>
@@ -1201,7 +1201,7 @@
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI2">
         <v>140</v>
@@ -1231,10 +1231,10 @@
         <v>17.5</v>
       </c>
       <c r="AR2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT2">
         <v>6.4</v>
@@ -1279,64 +1279,64 @@
         <v>9</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
         <v>169</v>
@@ -1371,19 +1371,19 @@
         <v>4</v>
       </c>
       <c r="J3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M3">
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O3">
         <v>1.44</v>
@@ -1395,16 +1395,16 @@
         <v>2.32</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S3">
         <v>4.3</v>
       </c>
       <c r="T3">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="U3">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V3">
         <v>1.33</v>
@@ -1461,22 +1461,22 @@
         <v>170</v>
       </c>
       <c r="AN3">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AO3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AP3">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3">
         <v>10</v>
       </c>
       <c r="AR3">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS3">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT3">
         <v>7.2</v>
@@ -1488,7 +1488,7 @@
         <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX3">
         <v>12</v>
@@ -1500,85 +1500,85 @@
         <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BB3">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC3">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BD3">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE3">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF3">
         <v>18.5</v>
       </c>
       <c r="BG3">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>169</v>
@@ -1610,7 +1610,7 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J4">
         <v>3.45</v>
@@ -1619,7 +1619,7 @@
         <v>3.75</v>
       </c>
       <c r="L4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M4">
         <v>1.07</v>
@@ -1640,16 +1640,16 @@
         <v>1.36</v>
       </c>
       <c r="S4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T4">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U4">
         <v>2.12</v>
       </c>
       <c r="V4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W4">
         <v>1.63</v>
@@ -1667,7 +1667,7 @@
         <v>55</v>
       </c>
       <c r="AB4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC4">
         <v>8.199999999999999</v>
@@ -1679,7 +1679,7 @@
         <v>36</v>
       </c>
       <c r="AF4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG4">
         <v>13</v>
@@ -1718,7 +1718,7 @@
         <v>18</v>
       </c>
       <c r="AS4">
-        <v>42</v>
+        <v>8.6</v>
       </c>
       <c r="AT4">
         <v>9</v>
@@ -1730,7 +1730,7 @@
         <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="AX4">
         <v>14</v>
@@ -1742,85 +1742,85 @@
         <v>15</v>
       </c>
       <c r="BA4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC4">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BD4">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BE4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF4">
         <v>20</v>
       </c>
       <c r="BG4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH4">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>169</v>
@@ -1861,13 +1861,13 @@
         <v>4.6</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O5">
         <v>1.25</v>
@@ -1879,10 +1879,10 @@
         <v>1.73</v>
       </c>
       <c r="R5">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S5">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T5">
         <v>1.82</v>
@@ -1936,7 +1936,7 @@
         <v>16</v>
       </c>
       <c r="AK5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL5">
         <v>34</v>
@@ -1960,7 +1960,7 @@
         <v>38</v>
       </c>
       <c r="AS5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT5">
         <v>8.6</v>
@@ -1996,73 +1996,73 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BE5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF5">
         <v>7</v>
       </c>
       <c r="BG5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
         <v>169</v>
@@ -2106,7 +2106,7 @@
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N6">
         <v>3.9</v>
@@ -2118,7 +2118,7 @@
         <v>1.97</v>
       </c>
       <c r="Q6">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R6">
         <v>1.38</v>
@@ -2202,7 +2202,7 @@
         <v>6.8</v>
       </c>
       <c r="AS6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT6">
         <v>7</v>
@@ -2214,7 +2214,7 @@
         <v>6</v>
       </c>
       <c r="AW6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX6">
         <v>6.4</v>
@@ -2235,7 +2235,7 @@
         <v>13.5</v>
       </c>
       <c r="BD6">
-        <v>28</v>
+        <v>6.2</v>
       </c>
       <c r="BE6">
         <v>7.2</v>
@@ -2250,61 +2250,61 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
         <v>169</v>
@@ -2327,7 +2327,7 @@
         <v>148</v>
       </c>
       <c r="F7">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="G7">
         <v>1000</v>
@@ -2336,13 +2336,13 @@
         <v>1.04</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K7">
-        <v>410</v>
+        <v>500</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2351,16 +2351,16 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O7">
         <v>1.1</v>
       </c>
       <c r="P7">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="R7">
         <v>1.18</v>
@@ -2369,10 +2369,10 @@
         <v>1.1</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
         <v>1.01</v>
@@ -2435,52 +2435,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2492,55 +2492,55 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2587,7 +2587,7 @@
         <v>5.7</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M8">
         <v>1.01</v>
@@ -2611,10 +2611,10 @@
         <v>2.82</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
         <v>1.32</v>
@@ -2734,55 +2734,55 @@
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2811,25 +2811,25 @@
         <v>150</v>
       </c>
       <c r="F9">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G9">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H9">
         <v>4.4</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J9">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K9">
         <v>3.85</v>
       </c>
       <c r="L9">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="M9">
         <v>1.07</v>
@@ -2838,31 +2838,31 @@
         <v>3.55</v>
       </c>
       <c r="O9">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P9">
         <v>1.88</v>
       </c>
       <c r="Q9">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R9">
         <v>1.34</v>
       </c>
       <c r="S9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T9">
         <v>1.84</v>
       </c>
       <c r="U9">
+        <v>2.04</v>
+      </c>
+      <c r="V9">
+        <v>1.26</v>
+      </c>
+      <c r="W9">
         <v>2.02</v>
-      </c>
-      <c r="V9">
-        <v>1.25</v>
-      </c>
-      <c r="W9">
-        <v>2</v>
       </c>
       <c r="X9">
         <v>16.5</v>
@@ -2880,7 +2880,7 @@
         <v>10</v>
       </c>
       <c r="AC9">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD9">
         <v>18.5</v>
@@ -2913,10 +2913,10 @@
         <v>120</v>
       </c>
       <c r="AN9">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO9">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP9">
         <v>12</v>
@@ -2925,10 +2925,10 @@
         <v>13</v>
       </c>
       <c r="AR9">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AS9">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT9">
         <v>8</v>
@@ -2940,7 +2940,7 @@
         <v>15</v>
       </c>
       <c r="AW9">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AX9">
         <v>10.5</v>
@@ -2952,7 +2952,7 @@
         <v>16</v>
       </c>
       <c r="BA9">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB9">
         <v>19</v>
@@ -2961,16 +2961,16 @@
         <v>19</v>
       </c>
       <c r="BD9">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE9">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF9">
         <v>12</v>
       </c>
       <c r="BG9">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH9">
         <v>3.45</v>
@@ -3012,7 +3012,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU9">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BV9">
         <v>1000</v>
@@ -3053,7 +3053,7 @@
         <v>151</v>
       </c>
       <c r="F10">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G10">
         <v>12</v>
@@ -3062,7 +3062,7 @@
         <v>1.38</v>
       </c>
       <c r="I10">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="J10">
         <v>4.9</v>
@@ -3071,208 +3071,208 @@
         <v>5.7</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P10">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q10">
         <v>1.7</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
         <v>169</v>
@@ -3298,16 +3298,16 @@
         <v>4</v>
       </c>
       <c r="G11">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H11">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="I11">
         <v>2.06</v>
       </c>
       <c r="J11">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="K11">
         <v>4.1</v>
@@ -3337,22 +3337,22 @@
         <v>3.05</v>
       </c>
       <c r="T11">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U11">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V11">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W11">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X11">
         <v>19.5</v>
       </c>
       <c r="Y11">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z11">
         <v>15</v>
@@ -3370,7 +3370,7 @@
         <v>12.5</v>
       </c>
       <c r="AE11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF11">
         <v>40</v>
@@ -3379,7 +3379,7 @@
         <v>21</v>
       </c>
       <c r="AH11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI11">
         <v>42</v>
@@ -3427,7 +3427,7 @@
         <v>17</v>
       </c>
       <c r="AX11">
-        <v>4.1</v>
+        <v>23</v>
       </c>
       <c r="AY11">
         <v>12.5</v>
@@ -3439,16 +3439,16 @@
         <v>24</v>
       </c>
       <c r="BB11">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BC11">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BD11">
         <v>40</v>
       </c>
       <c r="BE11">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF11">
         <v>38</v>
@@ -3460,61 +3460,61 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
         <v>169</v>
@@ -3540,223 +3540,223 @@
         <v>1.04</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H12">
         <v>1.04</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J12">
         <v>1.01</v>
       </c>
       <c r="K12">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
         <v>169</v>
@@ -3779,166 +3779,166 @@
         <v>154</v>
       </c>
       <c r="F13">
+        <v>2.8</v>
+      </c>
+      <c r="G13">
+        <v>3.15</v>
+      </c>
+      <c r="H13">
+        <v>2.46</v>
+      </c>
+      <c r="I13">
         <v>2.68</v>
       </c>
-      <c r="G13">
-        <v>3.25</v>
-      </c>
-      <c r="H13">
-        <v>2.42</v>
-      </c>
-      <c r="I13">
-        <v>2.82</v>
-      </c>
       <c r="J13">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K13">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N13">
-        <v>2.76</v>
+        <v>4.3</v>
       </c>
       <c r="O13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P13">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q13">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="R13">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S13">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="T13">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V13">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="W13">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4021,226 +4021,226 @@
         <v>155</v>
       </c>
       <c r="F14">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="G14">
         <v>1.95</v>
       </c>
       <c r="H14">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I14">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J14">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K14">
         <v>4.4</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P14">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="Q14">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="s">
         <v>169</v>
@@ -4281,7 +4281,7 @@
         <v>5.9</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M15">
         <v>1.01</v>
@@ -4377,7 +4377,7 @@
         <v>12</v>
       </c>
       <c r="AR15">
-        <v>3.8</v>
+        <v>20</v>
       </c>
       <c r="AS15">
         <v>4</v>
@@ -4505,226 +4505,226 @@
         <v>157</v>
       </c>
       <c r="F16">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="G16">
         <v>1.5</v>
       </c>
       <c r="H16">
-        <v>3.05</v>
+        <v>6.4</v>
       </c>
       <c r="I16">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="J16">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K16">
-        <v>450</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="P16">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q16">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="s">
         <v>169</v>
@@ -4756,10 +4756,10 @@
         <v>4.9</v>
       </c>
       <c r="I17">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K17">
         <v>4.4</v>
@@ -4816,7 +4816,7 @@
         <v>11</v>
       </c>
       <c r="AC17">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD17">
         <v>24</v>
@@ -4849,7 +4849,7 @@
         <v>110</v>
       </c>
       <c r="AN17">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO17">
         <v>80</v>
@@ -4861,10 +4861,10 @@
         <v>15</v>
       </c>
       <c r="AR17">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AS17">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AT17">
         <v>8.4</v>
@@ -4876,7 +4876,7 @@
         <v>15.5</v>
       </c>
       <c r="AW17">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AX17">
         <v>9.800000000000001</v>
@@ -4888,7 +4888,7 @@
         <v>14.5</v>
       </c>
       <c r="BA17">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BB17">
         <v>15.5</v>
@@ -4897,22 +4897,22 @@
         <v>13.5</v>
       </c>
       <c r="BD17">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE17">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BF17">
         <v>7.6</v>
       </c>
       <c r="BG17">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BH17">
         <v>3.75</v>
       </c>
       <c r="BI17">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ17">
         <v>9.800000000000001</v>
@@ -5007,7 +5007,7 @@
         <v>4.3</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M18">
         <v>1.05</v>
@@ -5028,16 +5028,16 @@
         <v>1.51</v>
       </c>
       <c r="S18">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="T18">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U18">
         <v>2.26</v>
       </c>
       <c r="V18">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W18">
         <v>2.14</v>
@@ -5055,7 +5055,7 @@
         <v>110</v>
       </c>
       <c r="AB18">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
         <v>9.800000000000001</v>
@@ -5064,10 +5064,10 @@
         <v>19</v>
       </c>
       <c r="AE18">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF18">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -5076,10 +5076,10 @@
         <v>18</v>
       </c>
       <c r="AI18">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ18">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK18">
         <v>17.5</v>
@@ -5103,22 +5103,22 @@
         <v>17.5</v>
       </c>
       <c r="AR18">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
       <c r="AS18">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="AT18">
         <v>9.800000000000001</v>
       </c>
       <c r="AU18">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV18">
         <v>16.5</v>
       </c>
       <c r="AW18">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="AX18">
         <v>9.6</v>
@@ -5130,7 +5130,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="BB18">
         <v>15</v>
@@ -5139,16 +5139,16 @@
         <v>13.5</v>
       </c>
       <c r="BD18">
-        <v>6.8</v>
+        <v>3.55</v>
       </c>
       <c r="BE18">
-        <v>7.8</v>
+        <v>3.75</v>
       </c>
       <c r="BF18">
         <v>7.8</v>
       </c>
       <c r="BG18">
-        <v>7.4</v>
+        <v>3.65</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5231,220 +5231,220 @@
         <v>160</v>
       </c>
       <c r="F19">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="G19">
         <v>3.15</v>
       </c>
       <c r="H19">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="I19">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="J19">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K19">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P19">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="Q19">
         <v>2.24</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BH19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19">
         <v>0</v>
@@ -5476,25 +5476,25 @@
         <v>2.82</v>
       </c>
       <c r="G20">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H20">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="I20">
         <v>2.5</v>
       </c>
       <c r="J20">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N20">
         <v>5.5</v>
@@ -5506,25 +5506,25 @@
         <v>2.52</v>
       </c>
       <c r="Q20">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="R20">
         <v>1.61</v>
       </c>
       <c r="S20">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="T20">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U20">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V20">
         <v>1.67</v>
       </c>
       <c r="W20">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X20">
         <v>30</v>
@@ -5581,10 +5581,10 @@
         <v>16</v>
       </c>
       <c r="AP20">
-        <v>17.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ20">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AR20">
         <v>13.5</v>
@@ -5596,7 +5596,7 @@
         <v>15</v>
       </c>
       <c r="AU20">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AV20">
         <v>10.5</v>
@@ -5629,70 +5629,70 @@
         <v>4.8</v>
       </c>
       <c r="BF20">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BG20">
         <v>9.4</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI20">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK20">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB20" t="s">
         <v>169</v>
@@ -5715,22 +5715,22 @@
         <v>162</v>
       </c>
       <c r="F21">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G21">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="H21">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="I21">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="J21">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K21">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5745,10 +5745,10 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="Q21">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -6199,22 +6199,22 @@
         <v>164</v>
       </c>
       <c r="F23">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="H23">
+        <v>4.8</v>
+      </c>
+      <c r="I23">
+        <v>6.2</v>
+      </c>
+      <c r="J23">
         <v>3.7</v>
       </c>
-      <c r="I23">
-        <v>8.4</v>
-      </c>
-      <c r="J23">
-        <v>3.45</v>
-      </c>
       <c r="K23">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6229,10 +6229,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="Q23">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6686,10 +6686,10 @@
         <v>1.53</v>
       </c>
       <c r="G25">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="H25">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I25">
         <v>9.6</v>
@@ -6716,7 +6716,7 @@
         <v>1.76</v>
       </c>
       <c r="Q25">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>1.01</v>
       </c>
       <c r="K26">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -6958,7 +6958,7 @@
         <v>1.24</v>
       </c>
       <c r="Q26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R26">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -523,7 +523,7 @@
     <t>Thor</t>
   </si>
   <si>
-    <t>2026-07-25 14:39:06</t>
+    <t>2026-07-25 16:56:02</t>
   </si>
 </sst>
 </file>
@@ -1117,7 +1117,7 @@
         <v>143</v>
       </c>
       <c r="F2">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G2">
         <v>1.63</v>
@@ -1126,16 +1126,16 @@
         <v>6.6</v>
       </c>
       <c r="I2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J2">
         <v>4</v>
       </c>
       <c r="K2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L2">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="M2">
         <v>1.07</v>
@@ -1144,7 +1144,7 @@
         <v>3.45</v>
       </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P2">
         <v>1.85</v>
@@ -1159,13 +1159,13 @@
         <v>3.6</v>
       </c>
       <c r="T2">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U2">
         <v>1.8</v>
       </c>
       <c r="V2">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W2">
         <v>2.58</v>
@@ -1174,7 +1174,7 @@
         <v>17</v>
       </c>
       <c r="Y2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Z2">
         <v>60</v>
@@ -1183,10 +1183,10 @@
         <v>270</v>
       </c>
       <c r="AB2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2">
         <v>28</v>
@@ -1195,7 +1195,7 @@
         <v>140</v>
       </c>
       <c r="AF2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
@@ -1219,7 +1219,7 @@
         <v>210</v>
       </c>
       <c r="AN2">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AO2">
         <v>210</v>
@@ -1234,7 +1234,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT2">
         <v>6.4</v>
@@ -1243,10 +1243,10 @@
         <v>8.4</v>
       </c>
       <c r="AV2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AW2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX2">
         <v>7.8</v>
@@ -1255,10 +1255,10 @@
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB2">
         <v>13</v>
@@ -1270,31 +1270,31 @@
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2">
         <v>7.6</v>
       </c>
       <c r="BG2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH2">
         <v>3.4</v>
       </c>
       <c r="BI2">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BJ2">
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BN2">
         <v>3.95</v>
@@ -1306,37 +1306,37 @@
         <v>10.5</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2">
         <v>11</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BZ2">
         <v>22</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="CB2" t="s">
         <v>169</v>
@@ -1401,10 +1401,10 @@
         <v>4.3</v>
       </c>
       <c r="T3">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="U3">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V3">
         <v>1.33</v>
@@ -1679,7 +1679,7 @@
         <v>36</v>
       </c>
       <c r="AF4">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG4">
         <v>13</v>
@@ -1718,7 +1718,7 @@
         <v>18</v>
       </c>
       <c r="AS4">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AT4">
         <v>9</v>
@@ -1748,19 +1748,19 @@
         <v>28</v>
       </c>
       <c r="BC4">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BD4">
         <v>34</v>
       </c>
       <c r="BE4">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4">
         <v>20</v>
       </c>
       <c r="BG4">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1846,7 +1846,7 @@
         <v>1.6</v>
       </c>
       <c r="G5">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H5">
         <v>6</v>
@@ -1861,7 +1861,7 @@
         <v>4.6</v>
       </c>
       <c r="L5">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M5">
         <v>1.05</v>
@@ -1876,13 +1876,13 @@
         <v>2.24</v>
       </c>
       <c r="Q5">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R5">
         <v>1.5</v>
       </c>
       <c r="S5">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="T5">
         <v>1.82</v>
@@ -1894,7 +1894,7 @@
         <v>1.17</v>
       </c>
       <c r="W5">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="X5">
         <v>19</v>
@@ -2014,13 +2014,13 @@
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN5">
         <v>4.5</v>
@@ -2032,37 +2032,37 @@
         <v>10.5</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BR5">
         <v>24</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT5">
         <v>10</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX5">
         <v>55</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ5">
         <v>17</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB5" t="s">
         <v>169</v>
@@ -2100,13 +2100,13 @@
         <v>4.3</v>
       </c>
       <c r="K6">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L6">
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N6">
         <v>3.9</v>
@@ -2115,10 +2115,10 @@
         <v>1.28</v>
       </c>
       <c r="P6">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q6">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R6">
         <v>1.38</v>
@@ -2202,7 +2202,7 @@
         <v>6.8</v>
       </c>
       <c r="AS6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT6">
         <v>7</v>
@@ -2214,7 +2214,7 @@
         <v>6</v>
       </c>
       <c r="AW6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX6">
         <v>6.4</v>
@@ -2235,7 +2235,7 @@
         <v>13.5</v>
       </c>
       <c r="BD6">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="BE6">
         <v>7.2</v>
@@ -2339,10 +2339,10 @@
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K7">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2814,16 +2814,16 @@
         <v>1.9</v>
       </c>
       <c r="G9">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="H9">
         <v>4.4</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J9">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K9">
         <v>3.85</v>
@@ -2835,13 +2835,13 @@
         <v>1.07</v>
       </c>
       <c r="N9">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O9">
         <v>1.34</v>
       </c>
       <c r="P9">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -2862,7 +2862,7 @@
         <v>1.26</v>
       </c>
       <c r="W9">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X9">
         <v>16.5</v>
@@ -3012,7 +3012,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU9">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BV9">
         <v>1000</v>
@@ -3053,25 +3053,25 @@
         <v>151</v>
       </c>
       <c r="F10">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="G10">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="H10">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="I10">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="J10">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="K10">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L10">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M10">
         <v>1.05</v>
@@ -3083,31 +3083,31 @@
         <v>1.24</v>
       </c>
       <c r="P10">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q10">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R10">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S10">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="T10">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="U10">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="V10">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="W10">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -3119,10 +3119,10 @@
         <v>14</v>
       </c>
       <c r="AB10">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AC10">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD10">
         <v>11</v>
@@ -3131,40 +3131,40 @@
         <v>18.5</v>
       </c>
       <c r="AF10">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AG10">
         <v>38</v>
       </c>
       <c r="AH10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI10">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ10">
-        <v>430</v>
+        <v>340</v>
       </c>
       <c r="AK10">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AL10">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AM10">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AN10">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="AO10">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AP10">
         <v>14.5</v>
       </c>
       <c r="AQ10">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AR10">
         <v>7.2</v>
@@ -3173,7 +3173,7 @@
         <v>8.6</v>
       </c>
       <c r="AT10">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AU10">
         <v>10</v>
@@ -3185,94 +3185,94 @@
         <v>11</v>
       </c>
       <c r="AX10">
+        <v>5</v>
+      </c>
+      <c r="AY10">
+        <v>4.7</v>
+      </c>
+      <c r="AZ10">
+        <v>21</v>
+      </c>
+      <c r="BA10">
         <v>4.8</v>
       </c>
-      <c r="AY10">
-        <v>4.5</v>
-      </c>
-      <c r="AZ10">
-        <v>4.4</v>
-      </c>
-      <c r="BA10">
-        <v>4.5</v>
-      </c>
       <c r="BB10">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BC10">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BD10">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE10">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF10">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BG10">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BH10">
         <v>4.1</v>
       </c>
       <c r="BI10">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ10">
+        <v>12</v>
+      </c>
+      <c r="BK10">
+        <v>5.4</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>9.4</v>
+      </c>
+      <c r="BN10">
         <v>12.5</v>
       </c>
-      <c r="BK10">
-        <v>1.04</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>1.04</v>
-      </c>
-      <c r="BN10">
-        <v>13.5</v>
-      </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT10">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BU10">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BV10">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BX10">
         <v>25</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ10">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB10" t="s">
         <v>169</v>
@@ -3313,7 +3313,7 @@
         <v>4.1</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M11">
         <v>1.06</v>
@@ -3457,64 +3457,64 @@
         <v>9.6</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="CB11" t="s">
         <v>169</v>
@@ -3549,10 +3549,10 @@
         <v>990</v>
       </c>
       <c r="J12">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="K12">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3576,7 +3576,7 @@
         <v>1.18</v>
       </c>
       <c r="S12">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T12">
         <v>1.11</v>
@@ -3585,10 +3585,10 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3785,7 +3785,7 @@
         <v>3.15</v>
       </c>
       <c r="H13">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="I13">
         <v>2.68</v>
@@ -3812,22 +3812,22 @@
         <v>2.14</v>
       </c>
       <c r="Q13">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R13">
         <v>1.45</v>
       </c>
       <c r="S13">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="T13">
         <v>1.62</v>
       </c>
       <c r="U13">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="V13">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W13">
         <v>1.47</v>
@@ -3944,61 +3944,61 @@
         <v>1000</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
         <v>1000</v>
       </c>
       <c r="BO13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="s">
         <v>169</v>
@@ -4021,19 +4021,19 @@
         <v>155</v>
       </c>
       <c r="F14">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G14">
         <v>1.95</v>
       </c>
       <c r="H14">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K14">
         <v>4.4</v>
@@ -4048,19 +4048,19 @@
         <v>5.8</v>
       </c>
       <c r="O14">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P14">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q14">
         <v>1.54</v>
       </c>
       <c r="R14">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="S14">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T14">
         <v>1.56</v>
@@ -4147,7 +4147,7 @@
         <v>9</v>
       </c>
       <c r="AV14">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW14">
         <v>6.8</v>
@@ -4168,10 +4168,10 @@
         <v>19</v>
       </c>
       <c r="BC14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BD14">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="BE14">
         <v>7.2</v>
@@ -4186,61 +4186,61 @@
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="s">
         <v>169</v>
@@ -4263,58 +4263,58 @@
         <v>156</v>
       </c>
       <c r="F15">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="G15">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="H15">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="I15">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J15">
         <v>3.5</v>
       </c>
       <c r="K15">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="L15">
         <v>1.28</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N15">
-        <v>2.32</v>
+        <v>4.4</v>
       </c>
       <c r="O15">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P15">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="Q15">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="R15">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="S15">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="T15">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V15">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W15">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="X15">
         <v>23</v>
@@ -4425,64 +4425,64 @@
         <v>3.85</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB15" t="s">
         <v>169</v>
@@ -4523,16 +4523,16 @@
         <v>7</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M16">
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P16">
         <v>3.3</v>
@@ -4541,16 +4541,16 @@
         <v>1.32</v>
       </c>
       <c r="R16">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="S16">
-        <v>1.32</v>
+        <v>1.89</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="V16">
         <v>1.13</v>
@@ -4559,58 +4559,58 @@
         <v>3</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP16">
         <v>1.03</v>
@@ -4625,106 +4625,106 @@
         <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AW16">
         <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA16">
         <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BE16">
         <v>1.03</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="CB16" t="s">
         <v>169</v>
@@ -4753,10 +4753,10 @@
         <v>1.8</v>
       </c>
       <c r="H17">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J17">
         <v>3.95</v>
@@ -4765,7 +4765,7 @@
         <v>4.4</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M17">
         <v>1.05</v>
@@ -4989,22 +4989,22 @@
         <v>159</v>
       </c>
       <c r="F18">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G18">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H18">
         <v>4.5</v>
       </c>
       <c r="I18">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J18">
         <v>4</v>
       </c>
       <c r="K18">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L18">
         <v>1.3</v>
@@ -5022,13 +5022,13 @@
         <v>2.28</v>
       </c>
       <c r="Q18">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R18">
         <v>1.51</v>
       </c>
       <c r="S18">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="T18">
         <v>1.7</v>
@@ -5037,7 +5037,7 @@
         <v>2.26</v>
       </c>
       <c r="V18">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W18">
         <v>2.14</v>
@@ -5055,7 +5055,7 @@
         <v>110</v>
       </c>
       <c r="AB18">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC18">
         <v>9.800000000000001</v>
@@ -5067,7 +5067,7 @@
         <v>55</v>
       </c>
       <c r="AF18">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -5103,10 +5103,10 @@
         <v>17.5</v>
       </c>
       <c r="AR18">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="AS18">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT18">
         <v>9.800000000000001</v>
@@ -5118,7 +5118,7 @@
         <v>16.5</v>
       </c>
       <c r="AW18">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="AX18">
         <v>9.6</v>
@@ -5130,7 +5130,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="BB18">
         <v>15</v>
@@ -5139,76 +5139,76 @@
         <v>13.5</v>
       </c>
       <c r="BD18">
-        <v>3.55</v>
+        <v>7.2</v>
       </c>
       <c r="BE18">
-        <v>3.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF18">
         <v>7.8</v>
       </c>
       <c r="BG18">
-        <v>3.65</v>
+        <v>7.6</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI18">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK18">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL18">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO18">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB18" t="s">
         <v>169</v>
@@ -5231,16 +5231,16 @@
         <v>160</v>
       </c>
       <c r="F19">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="G19">
         <v>3.15</v>
       </c>
       <c r="H19">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="I19">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="J19">
         <v>3.05</v>
@@ -5249,16 +5249,16 @@
         <v>3.4</v>
       </c>
       <c r="L19">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N19">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="O19">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P19">
         <v>1.69</v>
@@ -5267,184 +5267,184 @@
         <v>2.24</v>
       </c>
       <c r="R19">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S19">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T19">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U19">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="V19">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W19">
         <v>1.46</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z19">
+        <v>21</v>
+      </c>
+      <c r="AA19">
+        <v>55</v>
+      </c>
+      <c r="AB19">
         <v>11.5</v>
       </c>
-      <c r="Z19">
-        <v>1000</v>
-      </c>
-      <c r="AA19">
-        <v>1000</v>
-      </c>
-      <c r="AB19">
-        <v>1000</v>
-      </c>
       <c r="AC19">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE19">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP19">
-        <v>1.28</v>
+        <v>9.4</v>
       </c>
       <c r="AQ19">
-        <v>1.15</v>
+        <v>8.4</v>
       </c>
       <c r="AR19">
-        <v>1.28</v>
+        <v>15</v>
       </c>
       <c r="AS19">
-        <v>1.28</v>
+        <v>36</v>
       </c>
       <c r="AT19">
-        <v>1.28</v>
+        <v>9</v>
       </c>
       <c r="AU19">
-        <v>1.12</v>
+        <v>6.4</v>
       </c>
       <c r="AV19">
-        <v>1.28</v>
+        <v>11</v>
       </c>
       <c r="AW19">
-        <v>1.25</v>
+        <v>5.3</v>
       </c>
       <c r="AX19">
-        <v>1.28</v>
+        <v>17.5</v>
       </c>
       <c r="AY19">
-        <v>1.28</v>
+        <v>11.5</v>
       </c>
       <c r="AZ19">
-        <v>1.28</v>
+        <v>16.5</v>
       </c>
       <c r="BA19">
-        <v>1.28</v>
+        <v>5.7</v>
       </c>
       <c r="BB19">
-        <v>1.28</v>
+        <v>5.7</v>
       </c>
       <c r="BC19">
-        <v>1.28</v>
+        <v>5.5</v>
       </c>
       <c r="BD19">
-        <v>1.28</v>
+        <v>5.7</v>
       </c>
       <c r="BE19">
-        <v>1.28</v>
+        <v>6</v>
       </c>
       <c r="BF19">
-        <v>1.28</v>
+        <v>32</v>
       </c>
       <c r="BG19">
-        <v>1.28</v>
+        <v>5.3</v>
       </c>
       <c r="BH19">
         <v>1000</v>
       </c>
       <c r="BI19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
       </c>
       <c r="BK19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
         <v>0</v>
@@ -5476,22 +5476,22 @@
         <v>2.82</v>
       </c>
       <c r="G20">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H20">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I20">
         <v>2.5</v>
       </c>
       <c r="J20">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L20">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="M20">
         <v>1.03</v>
@@ -5506,25 +5506,25 @@
         <v>2.52</v>
       </c>
       <c r="Q20">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="R20">
         <v>1.61</v>
       </c>
       <c r="S20">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="T20">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U20">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V20">
         <v>1.67</v>
       </c>
       <c r="W20">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X20">
         <v>30</v>
@@ -5566,7 +5566,7 @@
         <v>55</v>
       </c>
       <c r="AK20">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL20">
         <v>40</v>
@@ -5581,7 +5581,7 @@
         <v>16</v>
       </c>
       <c r="AP20">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="AQ20">
         <v>13.5</v>
@@ -5590,22 +5590,22 @@
         <v>13.5</v>
       </c>
       <c r="AS20">
-        <v>23</v>
+        <v>4.4</v>
       </c>
       <c r="AT20">
         <v>15</v>
       </c>
       <c r="AU20">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV20">
         <v>10.5</v>
       </c>
       <c r="AW20">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX20">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AY20">
         <v>12</v>
@@ -5614,10 +5614,10 @@
         <v>13</v>
       </c>
       <c r="BA20">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BB20">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BC20">
         <v>20</v>
@@ -5626,31 +5626,31 @@
         <v>22</v>
       </c>
       <c r="BE20">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BF20">
         <v>12.5</v>
       </c>
       <c r="BG20">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BH20">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI20">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BJ20">
         <v>8.6</v>
       </c>
       <c r="BK20">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN20">
         <v>6.6</v>
@@ -5662,13 +5662,13 @@
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BT20">
         <v>5.9</v>
@@ -5680,19 +5680,19 @@
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ20">
         <v>16</v>
       </c>
       <c r="CA20">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB20" t="s">
         <v>169</v>
@@ -5718,31 +5718,31 @@
         <v>2.3</v>
       </c>
       <c r="G21">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H21">
         <v>2.96</v>
       </c>
       <c r="I21">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="J21">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K21">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P21">
         <v>2.08</v>
@@ -5751,184 +5751,184 @@
         <v>1.76</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
         <v>0</v>
@@ -5975,208 +5975,208 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="P22">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q22">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
         <v>169</v>
@@ -6208,7 +6208,7 @@
         <v>4.8</v>
       </c>
       <c r="I23">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J23">
         <v>3.7</v>
@@ -6217,16 +6217,16 @@
         <v>4.2</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P23">
         <v>1.94</v>
@@ -6235,190 +6235,190 @@
         <v>1.89</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ23">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA23">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD23">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BG23">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BH23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="s">
         <v>169</v>
@@ -6450,7 +6450,7 @@
         <v>2.36</v>
       </c>
       <c r="I24">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="J24">
         <v>3.25</v>
@@ -6459,16 +6459,16 @@
         <v>3.6</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P24">
         <v>1.79</v>
@@ -6477,190 +6477,190 @@
         <v>2.1</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AO24">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU24">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV24">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW24">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX24">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AY24">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ24">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA24">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB24">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD24">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BF24">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BG24">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH24">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BI24">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BJ24">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK24">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN24">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BO24">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BP24">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BQ24">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BR24">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BS24">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BT24">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BU24">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BV24">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BW24">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BX24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BZ24">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="CA24">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="CB24" t="s">
         <v>169</v>
@@ -6683,226 +6683,226 @@
         <v>166</v>
       </c>
       <c r="F25">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="G25">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="H25">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="I25">
         <v>9.6</v>
       </c>
       <c r="J25">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K25">
         <v>6</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P25">
         <v>1.76</v>
       </c>
       <c r="Q25">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL25">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AU25">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AV25">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW25">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AX25">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY25">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AZ25">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BA25">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BB25">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BC25">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD25">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BE25">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BF25">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BG25">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BH25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BK25">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BL25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN25">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BO25">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BP25">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BQ25">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BR25">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BS25">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BT25">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BU25">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BV25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW25">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX25">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ25">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CA25">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="CB25" t="s">
         <v>169</v>
@@ -6925,220 +6925,220 @@
         <v>167</v>
       </c>
       <c r="F26">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="G26">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H26">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="I26">
         <v>1000</v>
       </c>
       <c r="J26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K26">
-        <v>440</v>
+        <v>950</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P26">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q26">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
         <v>0</v>
@@ -7185,208 +7185,208 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P27">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="Q27">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="s">
         <v>169</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -523,7 +523,7 @@
     <t>Thor</t>
   </si>
   <si>
-    <t>2026-07-25 16:56:02</t>
+    <t>2026-07-25 19:11:31</t>
   </si>
 </sst>
 </file>
@@ -1135,7 +1135,7 @@
         <v>4.5</v>
       </c>
       <c r="L2">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="M2">
         <v>1.07</v>
@@ -1359,10 +1359,10 @@
         <v>144</v>
       </c>
       <c r="F3">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G3">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H3">
         <v>3.55</v>
@@ -1688,7 +1688,7 @@
         <v>18</v>
       </c>
       <c r="AI4">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AJ4">
         <v>38</v>
@@ -1742,7 +1742,7 @@
         <v>15</v>
       </c>
       <c r="BA4">
-        <v>40</v>
+        <v>7.8</v>
       </c>
       <c r="BB4">
         <v>28</v>
@@ -1861,7 +1861,7 @@
         <v>4.6</v>
       </c>
       <c r="L5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M5">
         <v>1.05</v>
@@ -1882,7 +1882,7 @@
         <v>1.5</v>
       </c>
       <c r="S5">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="T5">
         <v>1.82</v>
@@ -1954,7 +1954,7 @@
         <v>16</v>
       </c>
       <c r="AQ5">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR5">
         <v>38</v>
@@ -1969,10 +1969,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW5">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AX5">
         <v>9.199999999999999</v>
@@ -1993,10 +1993,10 @@
         <v>14</v>
       </c>
       <c r="BD5">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BE5">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF5">
         <v>7</v>
@@ -2005,64 +2005,64 @@
         <v>9</v>
       </c>
       <c r="BH5">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>3.2</v>
+        <v>2.04</v>
       </c>
       <c r="BJ5">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK5">
-        <v>5.2</v>
+        <v>1.77</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.4</v>
+        <v>2.04</v>
       </c>
       <c r="BN5">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO5">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="BP5">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ5">
-        <v>5.2</v>
+        <v>1.77</v>
       </c>
       <c r="BR5">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BS5">
-        <v>7.2</v>
+        <v>1.92</v>
       </c>
       <c r="BT5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>1.76</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>8.4</v>
+        <v>1.98</v>
       </c>
       <c r="BX5">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8.6</v>
+        <v>1.98</v>
       </c>
       <c r="BZ5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="CA5">
-        <v>6.4</v>
+        <v>1.87</v>
       </c>
       <c r="CB5" t="s">
         <v>169</v>
@@ -2085,7 +2085,7 @@
         <v>147</v>
       </c>
       <c r="F6">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="G6">
         <v>1.53</v>
@@ -2094,16 +2094,16 @@
         <v>7.8</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M6">
         <v>1.06</v>
@@ -2127,10 +2127,10 @@
         <v>3.15</v>
       </c>
       <c r="T6">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U6">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V6">
         <v>1.12</v>
@@ -2145,7 +2145,7 @@
         <v>32</v>
       </c>
       <c r="Z6">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA6">
         <v>340</v>
@@ -2163,7 +2163,7 @@
         <v>160</v>
       </c>
       <c r="AF6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG6">
         <v>12.5</v>
@@ -2199,10 +2199,10 @@
         <v>18</v>
       </c>
       <c r="AR6">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS6">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT6">
         <v>7</v>
@@ -2211,10 +2211,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV6">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AW6">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX6">
         <v>6.4</v>
@@ -2226,7 +2226,7 @@
         <v>18.5</v>
       </c>
       <c r="BA6">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB6">
         <v>9.6</v>
@@ -2238,73 +2238,73 @@
         <v>32</v>
       </c>
       <c r="BE6">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF6">
         <v>5.9</v>
       </c>
       <c r="BG6">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="CB6" t="s">
         <v>169</v>
@@ -2339,7 +2339,7 @@
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2587,7 +2587,7 @@
         <v>5.7</v>
       </c>
       <c r="L8">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M8">
         <v>1.01</v>
@@ -2811,25 +2811,25 @@
         <v>150</v>
       </c>
       <c r="F9">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G9">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="H9">
         <v>4.4</v>
       </c>
       <c r="I9">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J9">
+        <v>3.6</v>
+      </c>
+      <c r="K9">
         <v>3.8</v>
       </c>
-      <c r="K9">
-        <v>3.85</v>
-      </c>
       <c r="L9">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M9">
         <v>1.07</v>
@@ -2844,7 +2844,7 @@
         <v>1.89</v>
       </c>
       <c r="Q9">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R9">
         <v>1.34</v>
@@ -2862,25 +2862,25 @@
         <v>1.26</v>
       </c>
       <c r="W9">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y9">
         <v>15.5</v>
       </c>
       <c r="Z9">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AA9">
         <v>120</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9">
         <v>18.5</v>
@@ -2889,31 +2889,31 @@
         <v>65</v>
       </c>
       <c r="AF9">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI9">
         <v>65</v>
       </c>
       <c r="AJ9">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL9">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM9">
         <v>120</v>
       </c>
       <c r="AN9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO9">
         <v>75</v>
@@ -2922,25 +2922,25 @@
         <v>12</v>
       </c>
       <c r="AQ9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR9">
-        <v>5.2</v>
+        <v>29</v>
       </c>
       <c r="AS9">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AT9">
         <v>8</v>
       </c>
       <c r="AU9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW9">
-        <v>5.6</v>
+        <v>50</v>
       </c>
       <c r="AX9">
         <v>10.5</v>
@@ -2949,10 +2949,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA9">
-        <v>5.6</v>
+        <v>50</v>
       </c>
       <c r="BB9">
         <v>19</v>
@@ -2961,16 +2961,16 @@
         <v>19</v>
       </c>
       <c r="BD9">
-        <v>5.3</v>
+        <v>32</v>
       </c>
       <c r="BE9">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF9">
         <v>12</v>
       </c>
       <c r="BG9">
-        <v>5.7</v>
+        <v>50</v>
       </c>
       <c r="BH9">
         <v>3.45</v>
@@ -3068,7 +3068,7 @@
         <v>4.7</v>
       </c>
       <c r="K10">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L10">
         <v>1.28</v>
@@ -3089,16 +3089,16 @@
         <v>1.71</v>
       </c>
       <c r="R10">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S10">
         <v>2.88</v>
       </c>
       <c r="T10">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U10">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V10">
         <v>3</v>
@@ -3218,7 +3218,7 @@
         <v>4.1</v>
       </c>
       <c r="BI10">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BJ10">
         <v>12</v>
@@ -3313,7 +3313,7 @@
         <v>4.1</v>
       </c>
       <c r="L11">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="M11">
         <v>1.06</v>
@@ -3549,7 +3549,7 @@
         <v>990</v>
       </c>
       <c r="J12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="K12">
         <v>950</v>
@@ -3830,7 +3830,7 @@
         <v>1.6</v>
       </c>
       <c r="W13">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X13">
         <v>19</v>
@@ -4057,7 +4057,7 @@
         <v>1.54</v>
       </c>
       <c r="R14">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S14">
         <v>2.28</v>
@@ -4066,7 +4066,7 @@
         <v>1.56</v>
       </c>
       <c r="U14">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="V14">
         <v>1.33</v>
@@ -4171,7 +4171,7 @@
         <v>13</v>
       </c>
       <c r="BD14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BE14">
         <v>7.2</v>
@@ -4186,7 +4186,7 @@
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="BJ14">
         <v>12.5</v>
@@ -4198,7 +4198,7 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="BN14">
         <v>7.4</v>
@@ -4210,13 +4210,13 @@
         <v>18</v>
       </c>
       <c r="BQ14">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="BR14">
         <v>30</v>
       </c>
       <c r="BS14">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="BT14">
         <v>11</v>
@@ -4228,19 +4228,19 @@
         <v>40</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="BX14">
         <v>46</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="BZ14">
         <v>20</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="CB14" t="s">
         <v>169</v>
@@ -4293,10 +4293,10 @@
         <v>1.24</v>
       </c>
       <c r="P15">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q15">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R15">
         <v>1.45</v>
@@ -4538,7 +4538,7 @@
         <v>3.3</v>
       </c>
       <c r="Q16">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="R16">
         <v>1.94</v>
@@ -4637,7 +4637,7 @@
         <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AY16">
         <v>8.800000000000001</v>
@@ -4670,7 +4670,7 @@
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BJ16">
         <v>13</v>
@@ -4700,13 +4700,13 @@
         <v>23</v>
       </c>
       <c r="BS16">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="BT16">
         <v>15.5</v>
       </c>
       <c r="BU16">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="BV16">
         <v>1000</v>
@@ -4715,7 +4715,7 @@
         <v>2.2</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY16">
         <v>2.18</v>
@@ -4724,7 +4724,7 @@
         <v>12</v>
       </c>
       <c r="CA16">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CB16" t="s">
         <v>169</v>
@@ -4912,7 +4912,7 @@
         <v>3.75</v>
       </c>
       <c r="BI17">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ17">
         <v>9.800000000000001</v>
@@ -4989,7 +4989,7 @@
         <v>159</v>
       </c>
       <c r="F18">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G18">
         <v>1.86</v>
@@ -4998,7 +4998,7 @@
         <v>4.5</v>
       </c>
       <c r="I18">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -5037,7 +5037,7 @@
         <v>2.26</v>
       </c>
       <c r="V18">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W18">
         <v>2.14</v>
@@ -5067,7 +5067,7 @@
         <v>55</v>
       </c>
       <c r="AF18">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -5103,10 +5103,10 @@
         <v>17.5</v>
       </c>
       <c r="AR18">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS18">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT18">
         <v>9.800000000000001</v>
@@ -5118,7 +5118,7 @@
         <v>16.5</v>
       </c>
       <c r="AW18">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX18">
         <v>9.6</v>
@@ -5130,7 +5130,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB18">
         <v>15</v>
@@ -5139,16 +5139,16 @@
         <v>13.5</v>
       </c>
       <c r="BD18">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE18">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF18">
         <v>7.8</v>
       </c>
       <c r="BG18">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH18">
         <v>4</v>
@@ -5160,7 +5160,7 @@
         <v>9.4</v>
       </c>
       <c r="BK18">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL18">
         <v>95</v>
@@ -5172,13 +5172,13 @@
         <v>4.7</v>
       </c>
       <c r="BO18">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BP18">
         <v>12</v>
       </c>
       <c r="BQ18">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="BR18">
         <v>23</v>
@@ -5190,7 +5190,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU18">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BV18">
         <v>36</v>
@@ -5240,7 +5240,7 @@
         <v>2.7</v>
       </c>
       <c r="I19">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J19">
         <v>3.05</v>
@@ -5264,7 +5264,7 @@
         <v>1.69</v>
       </c>
       <c r="Q19">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R19">
         <v>1.25</v>
@@ -5360,7 +5360,7 @@
         <v>11</v>
       </c>
       <c r="AW19">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX19">
         <v>17.5</v>
@@ -5378,73 +5378,73 @@
         <v>5.7</v>
       </c>
       <c r="BC19">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD19">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE19">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF19">
         <v>32</v>
       </c>
       <c r="BG19">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH19">
         <v>1000</v>
       </c>
       <c r="BI19">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK19">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO19">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ19">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU19">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW19">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="BZ19">
         <v>0</v>
@@ -5512,7 +5512,7 @@
         <v>1.61</v>
       </c>
       <c r="S20">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T20">
         <v>1.54</v>
@@ -5581,7 +5581,7 @@
         <v>16</v>
       </c>
       <c r="AP20">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AQ20">
         <v>13.5</v>
@@ -5590,7 +5590,7 @@
         <v>13.5</v>
       </c>
       <c r="AS20">
-        <v>4.4</v>
+        <v>23</v>
       </c>
       <c r="AT20">
         <v>15</v>
@@ -5715,7 +5715,7 @@
         <v>162</v>
       </c>
       <c r="F21">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G21">
         <v>2.64</v>
@@ -5739,7 +5739,7 @@
         <v>1.04</v>
       </c>
       <c r="N21">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="O21">
         <v>1.23</v>
@@ -5748,19 +5748,19 @@
         <v>2.08</v>
       </c>
       <c r="Q21">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R21">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S21">
         <v>2.56</v>
       </c>
       <c r="T21">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U21">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V21">
         <v>1.42</v>
@@ -5880,55 +5880,55 @@
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN21">
         <v>1000</v>
       </c>
       <c r="BO21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP21">
         <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT21">
         <v>1000</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21">
         <v>0</v>
@@ -5999,10 +5999,10 @@
         <v>1.09</v>
       </c>
       <c r="T22">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V22">
         <v>1.01</v>
@@ -6122,61 +6122,61 @@
         <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="s">
         <v>169</v>
@@ -6238,13 +6238,13 @@
         <v>1.35</v>
       </c>
       <c r="S23">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T23">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U23">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V23">
         <v>1.21</v>
@@ -6364,61 +6364,61 @@
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO23">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU23">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="s">
         <v>169</v>
@@ -6444,10 +6444,10 @@
         <v>3.15</v>
       </c>
       <c r="G24">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H24">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I24">
         <v>2.58</v>
@@ -6492,7 +6492,7 @@
         <v>1.63</v>
       </c>
       <c r="W24">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X24">
         <v>13</v>
@@ -6552,7 +6552,7 @@
         <v>9.6</v>
       </c>
       <c r="AQ24">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR24">
         <v>12</v>
@@ -6612,31 +6612,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK24">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BN24">
         <v>6.4</v>
       </c>
       <c r="BO24">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BP24">
         <v>27</v>
       </c>
       <c r="BQ24">
-        <v>20</v>
+        <v>1.04</v>
       </c>
       <c r="BR24">
         <v>42</v>
       </c>
       <c r="BS24">
-        <v>30</v>
+        <v>1.04</v>
       </c>
       <c r="BT24">
         <v>5.3</v>
@@ -6648,19 +6648,19 @@
         <v>19</v>
       </c>
       <c r="BW24">
-        <v>14.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>25</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24">
         <v>32</v>
       </c>
       <c r="CA24">
-        <v>23</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="s">
         <v>169</v>
@@ -6683,16 +6683,16 @@
         <v>166</v>
       </c>
       <c r="F25">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="G25">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="H25">
         <v>1.04</v>
       </c>
       <c r="I25">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="J25">
         <v>3.8</v>
@@ -6707,7 +6707,7 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>1.76</v>
+        <v>2.78</v>
       </c>
       <c r="O25">
         <v>1.29</v>
@@ -6722,19 +6722,19 @@
         <v>1.18</v>
       </c>
       <c r="S25">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V25">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W25">
-        <v>2.12</v>
+        <v>1.54</v>
       </c>
       <c r="X25">
         <v>22</v>
@@ -6848,19 +6848,19 @@
         <v>1000</v>
       </c>
       <c r="BI25">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BJ25">
         <v>15.5</v>
       </c>
       <c r="BK25">
-        <v>6.6</v>
+        <v>1.64</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>21</v>
+        <v>1.84</v>
       </c>
       <c r="BN25">
         <v>5.8</v>
@@ -6872,37 +6872,37 @@
         <v>16</v>
       </c>
       <c r="BQ25">
-        <v>7</v>
+        <v>1.65</v>
       </c>
       <c r="BR25">
         <v>40</v>
       </c>
       <c r="BS25">
-        <v>16.5</v>
+        <v>1.76</v>
       </c>
       <c r="BT25">
         <v>13.5</v>
       </c>
       <c r="BU25">
-        <v>5.9</v>
+        <v>1.62</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>21</v>
+        <v>1.8</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>21</v>
+        <v>1.8</v>
       </c>
       <c r="BZ25">
         <v>30</v>
       </c>
       <c r="CA25">
-        <v>12.5</v>
+        <v>1.73</v>
       </c>
       <c r="CB25" t="s">
         <v>169</v>
@@ -6925,19 +6925,19 @@
         <v>167</v>
       </c>
       <c r="F26">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="G26">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="H26">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="I26">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J26">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="K26">
         <v>950</v>
@@ -6949,13 +6949,13 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="O26">
         <v>1.15</v>
       </c>
       <c r="P26">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q26">
         <v>1.15</v>
@@ -6964,121 +6964,121 @@
         <v>1.26</v>
       </c>
       <c r="S26">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T26">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U26">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V26">
         <v>1.01</v>
       </c>
       <c r="W26">
+        <v>2</v>
+      </c>
+      <c r="X26">
+        <v>1000</v>
+      </c>
+      <c r="Y26">
+        <v>1000</v>
+      </c>
+      <c r="Z26">
+        <v>1000</v>
+      </c>
+      <c r="AA26">
+        <v>1000</v>
+      </c>
+      <c r="AB26">
+        <v>1000</v>
+      </c>
+      <c r="AC26">
+        <v>1000</v>
+      </c>
+      <c r="AD26">
+        <v>1000</v>
+      </c>
+      <c r="AE26">
+        <v>1000</v>
+      </c>
+      <c r="AF26">
+        <v>1000</v>
+      </c>
+      <c r="AG26">
+        <v>1000</v>
+      </c>
+      <c r="AH26">
+        <v>1000</v>
+      </c>
+      <c r="AI26">
+        <v>1000</v>
+      </c>
+      <c r="AJ26">
+        <v>1000</v>
+      </c>
+      <c r="AK26">
+        <v>1000</v>
+      </c>
+      <c r="AL26">
+        <v>1000</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
+        <v>1000</v>
+      </c>
+      <c r="AO26">
+        <v>1000</v>
+      </c>
+      <c r="AP26">
         <v>1.01</v>
       </c>
-      <c r="X26">
-        <v>1000</v>
-      </c>
-      <c r="Y26">
-        <v>1000</v>
-      </c>
-      <c r="Z26">
-        <v>1000</v>
-      </c>
-      <c r="AA26">
-        <v>1000</v>
-      </c>
-      <c r="AB26">
-        <v>1000</v>
-      </c>
-      <c r="AC26">
-        <v>1000</v>
-      </c>
-      <c r="AD26">
-        <v>1000</v>
-      </c>
-      <c r="AE26">
-        <v>1000</v>
-      </c>
-      <c r="AF26">
-        <v>1000</v>
-      </c>
-      <c r="AG26">
-        <v>1000</v>
-      </c>
-      <c r="AH26">
-        <v>1000</v>
-      </c>
-      <c r="AI26">
-        <v>1000</v>
-      </c>
-      <c r="AJ26">
-        <v>1000</v>
-      </c>
-      <c r="AK26">
-        <v>1000</v>
-      </c>
-      <c r="AL26">
-        <v>1000</v>
-      </c>
-      <c r="AM26">
-        <v>1000</v>
-      </c>
-      <c r="AN26">
-        <v>1000</v>
-      </c>
-      <c r="AO26">
-        <v>1000</v>
-      </c>
-      <c r="AP26">
-        <v>1.03</v>
-      </c>
       <c r="AQ26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF26">
         <v>1.01</v>
@@ -7090,55 +7090,55 @@
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
       </c>
       <c r="BK26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN26">
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT26">
         <v>1000</v>
       </c>
       <c r="BU26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26">
         <v>0</v>
@@ -7188,31 +7188,31 @@
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N27">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O27">
         <v>1.11</v>
       </c>
       <c r="P27">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q27">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="R27">
         <v>1.25</v>
       </c>
       <c r="S27">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T27">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U27">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V27">
         <v>1.01</v>
@@ -7275,52 +7275,52 @@
         <v>1000</v>
       </c>
       <c r="AP27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF27">
         <v>1.01</v>
@@ -7332,61 +7332,61 @@
         <v>1000</v>
       </c>
       <c r="BI27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ27">
         <v>1000</v>
       </c>
       <c r="BK27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN27">
         <v>1000</v>
       </c>
       <c r="BO27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP27">
         <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT27">
         <v>1000</v>
       </c>
       <c r="BU27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV27">
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB27" t="s">
         <v>169</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -523,7 +523,7 @@
     <t>Thor</t>
   </si>
   <si>
-    <t>2026-07-25 19:11:31</t>
+    <t>2026-07-25 21:25:55</t>
   </si>
 </sst>
 </file>
@@ -1135,7 +1135,7 @@
         <v>4.5</v>
       </c>
       <c r="L2">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="M2">
         <v>1.07</v>
@@ -1183,13 +1183,13 @@
         <v>270</v>
       </c>
       <c r="AB2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC2">
         <v>9.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AE2">
         <v>140</v>
@@ -1201,7 +1201,7 @@
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI2">
         <v>140</v>
@@ -1231,10 +1231,10 @@
         <v>17.5</v>
       </c>
       <c r="AR2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT2">
         <v>6.4</v>
@@ -1243,10 +1243,10 @@
         <v>8.4</v>
       </c>
       <c r="AV2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AW2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX2">
         <v>7.8</v>
@@ -1255,28 +1255,28 @@
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB2">
         <v>13</v>
       </c>
       <c r="BC2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD2">
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF2">
         <v>7.6</v>
       </c>
       <c r="BG2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH2">
         <v>3.4</v>
@@ -1383,16 +1383,16 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O3">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P3">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Q3">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R3">
         <v>1.24</v>
@@ -1401,7 +1401,7 @@
         <v>4.3</v>
       </c>
       <c r="T3">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U3">
         <v>1.9</v>
@@ -1416,7 +1416,7 @@
         <v>11</v>
       </c>
       <c r="Y3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z3">
         <v>26</v>
@@ -1425,10 +1425,10 @@
         <v>80</v>
       </c>
       <c r="AB3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD3">
         <v>16</v>
@@ -1449,10 +1449,10 @@
         <v>70</v>
       </c>
       <c r="AJ3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL3">
         <v>50</v>
@@ -1467,16 +1467,16 @@
         <v>70</v>
       </c>
       <c r="AP3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ3">
         <v>10</v>
       </c>
       <c r="AR3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT3">
         <v>7.2</v>
@@ -1488,7 +1488,7 @@
         <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX3">
         <v>12</v>
@@ -1500,25 +1500,25 @@
         <v>17.5</v>
       </c>
       <c r="BA3">
+        <v>11</v>
+      </c>
+      <c r="BB3">
+        <v>27</v>
+      </c>
+      <c r="BC3">
+        <v>24</v>
+      </c>
+      <c r="BD3">
         <v>10.5</v>
       </c>
-      <c r="BB3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC3">
-        <v>8.6</v>
-      </c>
-      <c r="BD3">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BE3">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF3">
-        <v>18.5</v>
+        <v>9</v>
       </c>
       <c r="BG3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1616,7 +1616,7 @@
         <v>3.45</v>
       </c>
       <c r="K4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L4">
         <v>1.36</v>
@@ -1628,22 +1628,22 @@
         <v>3.5</v>
       </c>
       <c r="O4">
+        <v>1.34</v>
+      </c>
+      <c r="P4">
+        <v>1.87</v>
+      </c>
+      <c r="Q4">
+        <v>2</v>
+      </c>
+      <c r="R4">
         <v>1.33</v>
       </c>
-      <c r="P4">
-        <v>1.96</v>
-      </c>
-      <c r="Q4">
-        <v>1.98</v>
-      </c>
-      <c r="R4">
-        <v>1.36</v>
-      </c>
       <c r="S4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T4">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U4">
         <v>2.12</v>
@@ -1658,7 +1658,7 @@
         <v>16</v>
       </c>
       <c r="Y4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z4">
         <v>22</v>
@@ -1670,13 +1670,13 @@
         <v>10.5</v>
       </c>
       <c r="AC4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD4">
         <v>14</v>
       </c>
       <c r="AE4">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AF4">
         <v>18.5</v>
@@ -1694,10 +1694,10 @@
         <v>38</v>
       </c>
       <c r="AK4">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AL4">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AM4">
         <v>110</v>
@@ -1718,7 +1718,7 @@
         <v>18</v>
       </c>
       <c r="AS4">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AT4">
         <v>9</v>
@@ -1742,7 +1742,7 @@
         <v>15</v>
       </c>
       <c r="BA4">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB4">
         <v>28</v>
@@ -1754,13 +1754,13 @@
         <v>34</v>
       </c>
       <c r="BE4">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4">
         <v>20</v>
       </c>
       <c r="BG4">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1846,7 +1846,7 @@
         <v>1.6</v>
       </c>
       <c r="G5">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H5">
         <v>6</v>
@@ -1861,7 +1861,7 @@
         <v>4.6</v>
       </c>
       <c r="L5">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M5">
         <v>1.05</v>
@@ -1894,7 +1894,7 @@
         <v>1.17</v>
       </c>
       <c r="W5">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="X5">
         <v>19</v>
@@ -2026,7 +2026,7 @@
         <v>5.6</v>
       </c>
       <c r="BO5">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BP5">
         <v>13.5</v>
@@ -2250,7 +2250,7 @@
         <v>3.75</v>
       </c>
       <c r="BI6">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BJ6">
         <v>12</v>
@@ -2327,7 +2327,7 @@
         <v>148</v>
       </c>
       <c r="F7">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G7">
         <v>1000</v>
@@ -2435,52 +2435,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2569,34 +2569,34 @@
         <v>149</v>
       </c>
       <c r="F8">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G8">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="I8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J8">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K8">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N8">
         <v>3.45</v>
       </c>
       <c r="O8">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="P8">
         <v>2</v>
@@ -2605,10 +2605,10 @@
         <v>1.74</v>
       </c>
       <c r="R8">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S8">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2623,112 +2623,112 @@
         <v>1.73</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW8">
         <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA8">
         <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2817,19 +2817,19 @@
         <v>1.97</v>
       </c>
       <c r="H9">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J9">
         <v>3.6</v>
       </c>
       <c r="K9">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L9">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="M9">
         <v>1.07</v>
@@ -2859,7 +2859,7 @@
         <v>2.04</v>
       </c>
       <c r="V9">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
         <v>2.02</v>
@@ -2952,7 +2952,7 @@
         <v>16.5</v>
       </c>
       <c r="BA9">
-        <v>50</v>
+        <v>6.6</v>
       </c>
       <c r="BB9">
         <v>19</v>
@@ -3065,10 +3065,10 @@
         <v>1.5</v>
       </c>
       <c r="J10">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K10">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="L10">
         <v>1.28</v>
@@ -3077,28 +3077,28 @@
         <v>1.05</v>
       </c>
       <c r="N10">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P10">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="Q10">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="R10">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S10">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T10">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="U10">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="V10">
         <v>3</v>
@@ -3107,7 +3107,7 @@
         <v>1.11</v>
       </c>
       <c r="X10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -3158,7 +3158,7 @@
         <v>210</v>
       </c>
       <c r="AO10">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AP10">
         <v>14.5</v>
@@ -3170,46 +3170,46 @@
         <v>7.2</v>
       </c>
       <c r="AS10">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT10">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AU10">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AV10">
         <v>7.6</v>
       </c>
       <c r="AW10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX10">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AY10">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AZ10">
         <v>21</v>
       </c>
       <c r="BA10">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BB10">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BC10">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BD10">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BE10">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF10">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BG10">
         <v>5.2</v>
@@ -3218,7 +3218,7 @@
         <v>4.1</v>
       </c>
       <c r="BI10">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BJ10">
         <v>12</v>
@@ -3230,7 +3230,7 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN10">
         <v>12.5</v>
@@ -3242,13 +3242,13 @@
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT10">
         <v>4.1</v>
@@ -3266,10 +3266,10 @@
         <v>25</v>
       </c>
       <c r="BY10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ10">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CA10">
         <v>6</v>
@@ -3549,7 +3549,7 @@
         <v>990</v>
       </c>
       <c r="J12">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K12">
         <v>950</v>
@@ -3576,7 +3576,7 @@
         <v>1.18</v>
       </c>
       <c r="S12">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T12">
         <v>1.11</v>
@@ -3645,52 +3645,52 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
         <v>1.01</v>
@@ -3797,7 +3797,7 @@
         <v>3.95</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M13">
         <v>1.05</v>
@@ -3818,7 +3818,7 @@
         <v>1.45</v>
       </c>
       <c r="S13">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T13">
         <v>1.62</v>
@@ -3830,7 +3830,7 @@
         <v>1.6</v>
       </c>
       <c r="W13">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X13">
         <v>19</v>
@@ -3941,64 +3941,64 @@
         <v>14</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="CB13" t="s">
         <v>169</v>
@@ -4021,13 +4021,13 @@
         <v>155</v>
       </c>
       <c r="F14">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="G14">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H14">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I14">
         <v>4</v>
@@ -4057,7 +4057,7 @@
         <v>1.54</v>
       </c>
       <c r="R14">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S14">
         <v>2.28</v>
@@ -4072,7 +4072,7 @@
         <v>1.33</v>
       </c>
       <c r="W14">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X14">
         <v>27</v>
@@ -4135,7 +4135,7 @@
         <v>18.5</v>
       </c>
       <c r="AR14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS14">
         <v>7.4</v>
@@ -4150,7 +4150,7 @@
         <v>12.5</v>
       </c>
       <c r="AW14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX14">
         <v>13</v>
@@ -4162,7 +4162,7 @@
         <v>12.5</v>
       </c>
       <c r="BA14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB14">
         <v>19</v>
@@ -4278,7 +4278,7 @@
         <v>3.5</v>
       </c>
       <c r="K15">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L15">
         <v>1.28</v>
@@ -4296,13 +4296,13 @@
         <v>2.14</v>
       </c>
       <c r="Q15">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R15">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S15">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T15">
         <v>1.65</v>
@@ -4356,7 +4356,7 @@
         <v>32</v>
       </c>
       <c r="AK15">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL15">
         <v>38</v>
@@ -4380,7 +4380,7 @@
         <v>20</v>
       </c>
       <c r="AS15">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT15">
         <v>8.6</v>
@@ -4392,19 +4392,19 @@
         <v>11.5</v>
       </c>
       <c r="AW15">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX15">
         <v>10.5</v>
       </c>
       <c r="AY15">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
         <v>12</v>
       </c>
       <c r="BA15">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB15">
         <v>18</v>
@@ -4413,16 +4413,16 @@
         <v>14.5</v>
       </c>
       <c r="BD15">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BE15">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF15">
         <v>9</v>
       </c>
       <c r="BG15">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BH15">
         <v>4</v>
@@ -4529,10 +4529,10 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="O16">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="P16">
         <v>3.3</v>
@@ -4544,13 +4544,13 @@
         <v>1.94</v>
       </c>
       <c r="S16">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="T16">
         <v>1.58</v>
       </c>
       <c r="U16">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V16">
         <v>1.13</v>
@@ -4562,7 +4562,7 @@
         <v>50</v>
       </c>
       <c r="Y16">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Z16">
         <v>80</v>
@@ -4586,13 +4586,13 @@
         <v>15.5</v>
       </c>
       <c r="AG16">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH16">
         <v>23</v>
       </c>
       <c r="AI16">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ16">
         <v>17.5</v>
@@ -4613,16 +4613,16 @@
         <v>60</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT16">
         <v>12.5</v>
@@ -4634,7 +4634,7 @@
         <v>21</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX16">
         <v>10</v>
@@ -4643,10 +4643,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ16">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB16">
         <v>11.5</v>
@@ -4658,31 +4658,31 @@
         <v>18</v>
       </c>
       <c r="BE16">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF16">
         <v>3.35</v>
       </c>
       <c r="BG16">
-        <v>38</v>
+        <v>4.9</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BJ16">
         <v>13</v>
       </c>
       <c r="BK16">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BN16">
         <v>6.2</v>
@@ -4706,22 +4706,22 @@
         <v>15.5</v>
       </c>
       <c r="BU16">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BX16">
         <v>50</v>
       </c>
       <c r="BY16">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BZ16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA16">
         <v>1.92</v>
@@ -4912,7 +4912,7 @@
         <v>3.75</v>
       </c>
       <c r="BI17">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BJ17">
         <v>9.800000000000001</v>
@@ -5007,7 +5007,7 @@
         <v>4.1</v>
       </c>
       <c r="L18">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="M18">
         <v>1.05</v>
@@ -5067,7 +5067,7 @@
         <v>55</v>
       </c>
       <c r="AF18">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -5103,10 +5103,10 @@
         <v>17.5</v>
       </c>
       <c r="AR18">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AS18">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT18">
         <v>9.800000000000001</v>
@@ -5118,7 +5118,7 @@
         <v>16.5</v>
       </c>
       <c r="AW18">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX18">
         <v>9.6</v>
@@ -5130,7 +5130,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB18">
         <v>15</v>
@@ -5139,55 +5139,55 @@
         <v>13.5</v>
       </c>
       <c r="BD18">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE18">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF18">
         <v>7.8</v>
       </c>
       <c r="BG18">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH18">
         <v>4</v>
       </c>
       <c r="BI18">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BJ18">
         <v>9.4</v>
       </c>
       <c r="BK18">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BL18">
         <v>95</v>
       </c>
       <c r="BM18">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN18">
         <v>4.7</v>
       </c>
       <c r="BO18">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP18">
         <v>12</v>
       </c>
       <c r="BQ18">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="BR18">
         <v>23</v>
       </c>
       <c r="BS18">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT18">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU18">
         <v>5.4</v>
@@ -5196,7 +5196,7 @@
         <v>36</v>
       </c>
       <c r="BW18">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX18">
         <v>40</v>
@@ -5208,7 +5208,7 @@
         <v>17.5</v>
       </c>
       <c r="CA18">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB18" t="s">
         <v>169</v>
@@ -5724,10 +5724,10 @@
         <v>2.96</v>
       </c>
       <c r="I21">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="J21">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K21">
         <v>3.95</v>
@@ -5739,16 +5739,16 @@
         <v>1.04</v>
       </c>
       <c r="N21">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O21">
         <v>1.23</v>
       </c>
       <c r="P21">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q21">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R21">
         <v>1.34</v>
@@ -5763,7 +5763,7 @@
         <v>1.11</v>
       </c>
       <c r="V21">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W21">
         <v>1.61</v>
@@ -5823,52 +5823,52 @@
         <v>1000</v>
       </c>
       <c r="AP21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF21">
         <v>1.01</v>
@@ -5996,7 +5996,7 @@
         <v>1.25</v>
       </c>
       <c r="S22">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="T22">
         <v>1.11</v>
@@ -6065,52 +6065,52 @@
         <v>1000</v>
       </c>
       <c r="AP22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF22">
         <v>1.01</v>
@@ -6199,7 +6199,7 @@
         <v>164</v>
       </c>
       <c r="F23">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G23">
         <v>1.88</v>
@@ -6211,40 +6211,40 @@
         <v>5.8</v>
       </c>
       <c r="J23">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K23">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L23">
         <v>1.3</v>
       </c>
       <c r="M23">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N23">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O23">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P23">
+        <v>1.88</v>
+      </c>
+      <c r="Q23">
+        <v>1.93</v>
+      </c>
+      <c r="R23">
+        <v>1.34</v>
+      </c>
+      <c r="S23">
+        <v>3.45</v>
+      </c>
+      <c r="T23">
+        <v>1.86</v>
+      </c>
+      <c r="U23">
         <v>1.94</v>
-      </c>
-      <c r="Q23">
-        <v>1.89</v>
-      </c>
-      <c r="R23">
-        <v>1.35</v>
-      </c>
-      <c r="S23">
-        <v>3.25</v>
-      </c>
-      <c r="T23">
-        <v>1.82</v>
-      </c>
-      <c r="U23">
-        <v>2</v>
       </c>
       <c r="V23">
         <v>1.21</v>
@@ -6256,10 +6256,10 @@
         <v>16</v>
       </c>
       <c r="Y23">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z23">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AA23">
         <v>150</v>
@@ -6274,7 +6274,7 @@
         <v>21</v>
       </c>
       <c r="AE23">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF23">
         <v>12</v>
@@ -6286,7 +6286,7 @@
         <v>21</v>
       </c>
       <c r="AI23">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ23">
         <v>21</v>
@@ -6307,7 +6307,7 @@
         <v>85</v>
       </c>
       <c r="AP23">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ23">
         <v>14.5</v>
@@ -6316,10 +6316,10 @@
         <v>32</v>
       </c>
       <c r="AS23">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT23">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU23">
         <v>7.6</v>
@@ -6328,7 +6328,7 @@
         <v>16.5</v>
       </c>
       <c r="AW23">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX23">
         <v>9.4</v>
@@ -6340,7 +6340,7 @@
         <v>16.5</v>
       </c>
       <c r="BA23">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB23">
         <v>16</v>
@@ -6349,52 +6349,52 @@
         <v>16</v>
       </c>
       <c r="BD23">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE23">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF23">
         <v>8.6</v>
       </c>
       <c r="BG23">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="BJ23">
         <v>14.5</v>
       </c>
       <c r="BK23">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="BN23">
         <v>6</v>
       </c>
       <c r="BO23">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BP23">
         <v>18</v>
       </c>
       <c r="BQ23">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="BR23">
         <v>40</v>
       </c>
       <c r="BS23">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="BT23">
         <v>12.5</v>
@@ -6406,19 +6406,19 @@
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="BZ23">
         <v>32</v>
       </c>
       <c r="CA23">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="CB23" t="s">
         <v>169</v>
@@ -6447,7 +6447,7 @@
         <v>3.45</v>
       </c>
       <c r="H24">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="I24">
         <v>2.58</v>
@@ -6459,7 +6459,7 @@
         <v>3.6</v>
       </c>
       <c r="L24">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="M24">
         <v>1.08</v>
@@ -6606,19 +6606,19 @@
         <v>3.25</v>
       </c>
       <c r="BI24">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ24">
         <v>9.800000000000001</v>
       </c>
       <c r="BK24">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="BN24">
         <v>6.4</v>
@@ -6630,37 +6630,37 @@
         <v>27</v>
       </c>
       <c r="BQ24">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR24">
         <v>42</v>
       </c>
       <c r="BS24">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BT24">
         <v>5.3</v>
       </c>
       <c r="BU24">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BV24">
         <v>19</v>
       </c>
       <c r="BW24">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ24">
         <v>32</v>
       </c>
       <c r="CA24">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="CB24" t="s">
         <v>169</v>
@@ -6686,10 +6686,10 @@
         <v>1.54</v>
       </c>
       <c r="G25">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H25">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="I25">
         <v>8.6</v>
@@ -6698,7 +6698,7 @@
         <v>3.8</v>
       </c>
       <c r="K25">
-        <v>6</v>
+        <v>950</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6707,7 +6707,7 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="O25">
         <v>1.29</v>
@@ -6719,10 +6719,10 @@
         <v>1.87</v>
       </c>
       <c r="R25">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S25">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="T25">
         <v>1.11</v>
@@ -6734,13 +6734,13 @@
         <v>1.13</v>
       </c>
       <c r="W25">
-        <v>1.54</v>
+        <v>2.26</v>
       </c>
       <c r="X25">
         <v>22</v>
       </c>
       <c r="Y25">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="Z25">
         <v>75</v>
@@ -6755,7 +6755,7 @@
         <v>13.5</v>
       </c>
       <c r="AD25">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="AE25">
         <v>1000</v>
@@ -6767,7 +6767,7 @@
         <v>14.5</v>
       </c>
       <c r="AH25">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI25">
         <v>1000</v>
@@ -6785,64 +6785,64 @@
         <v>1000</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO25">
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AQ25">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="AR25">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="AS25">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="AT25">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AU25">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="AV25">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="AW25">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="AX25">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AY25">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AZ25">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="BA25">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="BB25">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="BC25">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="BD25">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="BE25">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="BF25">
-        <v>2.22</v>
+        <v>6.6</v>
       </c>
       <c r="BG25">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -6928,7 +6928,7 @@
         <v>1.04</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H26">
         <v>1.04</v>
@@ -6937,7 +6937,7 @@
         <v>990</v>
       </c>
       <c r="J26">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="K26">
         <v>950</v>
@@ -6949,13 +6949,13 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O26">
         <v>1.15</v>
       </c>
       <c r="P26">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Q26">
         <v>1.15</v>
@@ -7200,13 +7200,13 @@
         <v>1.74</v>
       </c>
       <c r="Q27">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="R27">
         <v>1.25</v>
       </c>
       <c r="S27">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="T27">
         <v>1.11</v>
@@ -7275,52 +7275,52 @@
         <v>1000</v>
       </c>
       <c r="AP27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF27">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -523,7 +523,7 @@
     <t>Thor</t>
   </si>
   <si>
-    <t>2026-07-25 21:25:55</t>
+    <t>2026-07-25 23:39:35</t>
   </si>
 </sst>
 </file>
@@ -1135,7 +1135,7 @@
         <v>4.5</v>
       </c>
       <c r="L2">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="M2">
         <v>1.07</v>
@@ -1210,7 +1210,7 @@
         <v>15</v>
       </c>
       <c r="AK2">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AL2">
         <v>44</v>
@@ -1359,28 +1359,28 @@
         <v>144</v>
       </c>
       <c r="F3">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G3">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H3">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J3">
         <v>3.1</v>
       </c>
       <c r="K3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
         <v>1.45</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
         <v>2.9</v>
@@ -1392,13 +1392,13 @@
         <v>1.64</v>
       </c>
       <c r="Q3">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R3">
         <v>1.24</v>
       </c>
       <c r="S3">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T3">
         <v>1.98</v>
@@ -1410,7 +1410,7 @@
         <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X3">
         <v>11</v>
@@ -1422,7 +1422,7 @@
         <v>26</v>
       </c>
       <c r="AA3">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AB3">
         <v>8.199999999999999</v>
@@ -1431,10 +1431,10 @@
         <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AE3">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AF3">
         <v>14</v>
@@ -1446,25 +1446,25 @@
         <v>21</v>
       </c>
       <c r="AI3">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AJ3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK3">
         <v>30</v>
       </c>
       <c r="AL3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM3">
         <v>170</v>
       </c>
       <c r="AN3">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AO3">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AP3">
         <v>9</v>
@@ -1473,10 +1473,10 @@
         <v>10</v>
       </c>
       <c r="AR3">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AS3">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AT3">
         <v>7.2</v>
@@ -1488,7 +1488,7 @@
         <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>10.5</v>
+        <v>46</v>
       </c>
       <c r="AX3">
         <v>12</v>
@@ -1500,7 +1500,7 @@
         <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BB3">
         <v>27</v>
@@ -1509,16 +1509,16 @@
         <v>24</v>
       </c>
       <c r="BD3">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="BE3">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF3">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BG3">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1604,16 +1604,16 @@
         <v>2.46</v>
       </c>
       <c r="G4">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I4">
         <v>3.15</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K4">
         <v>3.7</v>
@@ -1628,13 +1628,13 @@
         <v>3.5</v>
       </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P4">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R4">
         <v>1.33</v>
@@ -1643,7 +1643,7 @@
         <v>3.6</v>
       </c>
       <c r="T4">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U4">
         <v>2.12</v>
@@ -1652,16 +1652,16 @@
         <v>1.46</v>
       </c>
       <c r="W4">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y4">
         <v>12</v>
       </c>
       <c r="Z4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA4">
         <v>55</v>
@@ -1676,31 +1676,31 @@
         <v>14</v>
       </c>
       <c r="AE4">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH4">
         <v>18</v>
       </c>
       <c r="AI4">
-        <v>48</v>
+        <v>210</v>
       </c>
       <c r="AJ4">
         <v>38</v>
       </c>
       <c r="AK4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL4">
         <v>48</v>
       </c>
       <c r="AM4">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
         <v>24</v>
@@ -1709,25 +1709,25 @@
         <v>36</v>
       </c>
       <c r="AP4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR4">
         <v>18</v>
       </c>
       <c r="AS4">
-        <v>7.6</v>
+        <v>27</v>
       </c>
       <c r="AT4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW4">
         <v>30</v>
@@ -1736,31 +1736,31 @@
         <v>14</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA4">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="BB4">
         <v>28</v>
       </c>
       <c r="BC4">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="BD4">
         <v>34</v>
       </c>
       <c r="BE4">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BF4">
         <v>20</v>
       </c>
       <c r="BG4">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1846,10 +1846,10 @@
         <v>1.6</v>
       </c>
       <c r="G5">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
         <v>6.8</v>
@@ -1861,7 +1861,7 @@
         <v>4.6</v>
       </c>
       <c r="L5">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="M5">
         <v>1.05</v>
@@ -1945,7 +1945,7 @@
         <v>120</v>
       </c>
       <c r="AN5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO5">
         <v>90</v>
@@ -1960,10 +1960,10 @@
         <v>38</v>
       </c>
       <c r="AS5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5">
         <v>8.800000000000001</v>
@@ -1972,7 +1972,7 @@
         <v>20</v>
       </c>
       <c r="AW5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX5">
         <v>9.199999999999999</v>
@@ -1984,7 +1984,7 @@
         <v>17</v>
       </c>
       <c r="BA5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB5">
         <v>13</v>
@@ -1993,76 +1993,76 @@
         <v>14</v>
       </c>
       <c r="BD5">
-        <v>24</v>
+        <v>8.4</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BF5">
         <v>7</v>
       </c>
       <c r="BG5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI5">
-        <v>2.04</v>
+        <v>3.2</v>
       </c>
       <c r="BJ5">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>1.77</v>
+        <v>5.2</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>2.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN5">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO5">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BP5">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BQ5">
-        <v>1.77</v>
+        <v>5.2</v>
       </c>
       <c r="BR5">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BS5">
-        <v>1.92</v>
+        <v>7.2</v>
       </c>
       <c r="BT5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BU5">
-        <v>1.76</v>
+        <v>5</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.98</v>
+        <v>8.4</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY5">
-        <v>1.98</v>
+        <v>8.6</v>
       </c>
       <c r="BZ5">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="CA5">
-        <v>1.87</v>
+        <v>6.4</v>
       </c>
       <c r="CB5" t="s">
         <v>169</v>
@@ -2085,7 +2085,7 @@
         <v>147</v>
       </c>
       <c r="F6">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G6">
         <v>1.53</v>
@@ -2094,46 +2094,46 @@
         <v>7.8</v>
       </c>
       <c r="I6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="J6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M6">
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O6">
         <v>1.28</v>
       </c>
       <c r="P6">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q6">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S6">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T6">
         <v>2.04</v>
       </c>
       <c r="U6">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V6">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W6">
         <v>2.88</v>
@@ -2247,22 +2247,22 @@
         <v>8</v>
       </c>
       <c r="BH6">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI6">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ6">
         <v>12</v>
       </c>
       <c r="BK6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN6">
         <v>4</v>
@@ -2271,10 +2271,10 @@
         <v>3.05</v>
       </c>
       <c r="BP6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BQ6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BR6">
         <v>27</v>
@@ -2283,7 +2283,7 @@
         <v>7.8</v>
       </c>
       <c r="BT6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BU6">
         <v>5.8</v>
@@ -2292,19 +2292,19 @@
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CA6">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB6" t="s">
         <v>169</v>
@@ -2327,7 +2327,7 @@
         <v>148</v>
       </c>
       <c r="F7">
-        <v>1.67</v>
+        <v>1.04</v>
       </c>
       <c r="G7">
         <v>1000</v>
@@ -2339,7 +2339,7 @@
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2575,40 +2575,40 @@
         <v>2.36</v>
       </c>
       <c r="H8">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J8">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K8">
         <v>4</v>
       </c>
       <c r="L8">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M8">
         <v>1.05</v>
       </c>
       <c r="N8">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="O8">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P8">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q8">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="R8">
         <v>1.38</v>
       </c>
       <c r="S8">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2686,7 +2686,7 @@
         <v>19</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT8">
         <v>8.199999999999999</v>
@@ -2698,7 +2698,7 @@
         <v>11</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AX8">
         <v>11</v>
@@ -2710,7 +2710,7 @@
         <v>12</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB8">
         <v>20</v>
@@ -2719,70 +2719,70 @@
         <v>16</v>
       </c>
       <c r="BD8">
-        <v>1.05</v>
+        <v>3.9</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF8">
         <v>10.5</v>
       </c>
       <c r="BG8">
-        <v>1.05</v>
+        <v>3.9</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2817,7 +2817,7 @@
         <v>1.97</v>
       </c>
       <c r="H9">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I9">
         <v>4.9</v>
@@ -3059,19 +3059,19 @@
         <v>10.5</v>
       </c>
       <c r="H10">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="I10">
         <v>1.5</v>
       </c>
       <c r="J10">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K10">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L10">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M10">
         <v>1.05</v>
@@ -3080,19 +3080,19 @@
         <v>4.2</v>
       </c>
       <c r="O10">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P10">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q10">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R10">
         <v>1.42</v>
       </c>
       <c r="S10">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="T10">
         <v>2</v>
@@ -3104,16 +3104,16 @@
         <v>3</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y10">
         <v>9</v>
       </c>
       <c r="Z10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA10">
         <v>14</v>
@@ -3122,13 +3122,13 @@
         <v>34</v>
       </c>
       <c r="AC10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD10">
         <v>11</v>
       </c>
       <c r="AE10">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AF10">
         <v>85</v>
@@ -3158,13 +3158,13 @@
         <v>210</v>
       </c>
       <c r="AO10">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AP10">
         <v>14.5</v>
       </c>
       <c r="AQ10">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR10">
         <v>7.2</v>
@@ -3173,7 +3173,7 @@
         <v>10.5</v>
       </c>
       <c r="AT10">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AU10">
         <v>9.4</v>
@@ -3185,73 +3185,73 @@
         <v>11.5</v>
       </c>
       <c r="AX10">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY10">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AZ10">
         <v>21</v>
       </c>
       <c r="BA10">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB10">
+        <v>5.9</v>
+      </c>
+      <c r="BC10">
         <v>5.8</v>
       </c>
-      <c r="BC10">
+      <c r="BD10">
         <v>5.7</v>
       </c>
-      <c r="BD10">
-        <v>5.6</v>
-      </c>
       <c r="BE10">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF10">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG10">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH10">
         <v>4.1</v>
       </c>
       <c r="BI10">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BJ10">
         <v>12</v>
       </c>
       <c r="BK10">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN10">
         <v>12.5</v>
       </c>
       <c r="BO10">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT10">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BU10">
         <v>3.05</v>
@@ -3260,19 +3260,19 @@
         <v>9</v>
       </c>
       <c r="BW10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BX10">
         <v>25</v>
       </c>
       <c r="BY10">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ10">
         <v>15.5</v>
       </c>
       <c r="CA10">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB10" t="s">
         <v>169</v>
@@ -3301,7 +3301,7 @@
         <v>4.8</v>
       </c>
       <c r="H11">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I11">
         <v>2.06</v>
@@ -3370,7 +3370,7 @@
         <v>12.5</v>
       </c>
       <c r="AE11">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AF11">
         <v>40</v>
@@ -3439,16 +3439,16 @@
         <v>24</v>
       </c>
       <c r="BB11">
+        <v>5</v>
+      </c>
+      <c r="BC11">
         <v>4.8</v>
-      </c>
-      <c r="BC11">
-        <v>4.7</v>
       </c>
       <c r="BD11">
         <v>40</v>
       </c>
       <c r="BE11">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF11">
         <v>38</v>
@@ -3478,7 +3478,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO11">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BP11">
         <v>1000</v>
@@ -3502,7 +3502,7 @@
         <v>14</v>
       </c>
       <c r="BW11">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX11">
         <v>28</v>
@@ -3549,7 +3549,7 @@
         <v>990</v>
       </c>
       <c r="J12">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="K12">
         <v>950</v>
@@ -3779,7 +3779,7 @@
         <v>154</v>
       </c>
       <c r="F13">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="G13">
         <v>3.15</v>
@@ -3797,7 +3797,7 @@
         <v>3.95</v>
       </c>
       <c r="L13">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M13">
         <v>1.05</v>
@@ -4057,10 +4057,10 @@
         <v>1.54</v>
       </c>
       <c r="R14">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S14">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="T14">
         <v>1.56</v>
@@ -4084,7 +4084,7 @@
         <v>42</v>
       </c>
       <c r="AA14">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AB14">
         <v>14.5</v>
@@ -4129,13 +4129,13 @@
         <v>29</v>
       </c>
       <c r="AP14">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ14">
         <v>18.5</v>
       </c>
       <c r="AR14">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS14">
         <v>7.4</v>
@@ -4150,7 +4150,7 @@
         <v>12.5</v>
       </c>
       <c r="AW14">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX14">
         <v>13</v>
@@ -4162,7 +4162,7 @@
         <v>12.5</v>
       </c>
       <c r="BA14">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB14">
         <v>19</v>
@@ -4204,13 +4204,13 @@
         <v>7.4</v>
       </c>
       <c r="BO14">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP14">
         <v>18</v>
       </c>
       <c r="BQ14">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BR14">
         <v>30</v>
@@ -4225,7 +4225,7 @@
         <v>4.9</v>
       </c>
       <c r="BV14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW14">
         <v>1.91</v>
@@ -4234,13 +4234,13 @@
         <v>46</v>
       </c>
       <c r="BY14">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BZ14">
         <v>20</v>
       </c>
       <c r="CA14">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CB14" t="s">
         <v>169</v>
@@ -4263,7 +4263,7 @@
         <v>156</v>
       </c>
       <c r="F15">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="G15">
         <v>2.22</v>
@@ -4278,7 +4278,7 @@
         <v>3.5</v>
       </c>
       <c r="K15">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L15">
         <v>1.28</v>
@@ -4293,22 +4293,22 @@
         <v>1.24</v>
       </c>
       <c r="P15">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q15">
         <v>1.71</v>
       </c>
       <c r="R15">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S15">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T15">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U15">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V15">
         <v>1.31</v>
@@ -4356,7 +4356,7 @@
         <v>32</v>
       </c>
       <c r="AK15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL15">
         <v>38</v>
@@ -4380,7 +4380,7 @@
         <v>20</v>
       </c>
       <c r="AS15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AT15">
         <v>8.6</v>
@@ -4392,19 +4392,19 @@
         <v>11.5</v>
       </c>
       <c r="AW15">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AX15">
         <v>10.5</v>
       </c>
       <c r="AY15">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AZ15">
         <v>12</v>
       </c>
       <c r="BA15">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BB15">
         <v>18</v>
@@ -4413,16 +4413,16 @@
         <v>14.5</v>
       </c>
       <c r="BD15">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BE15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BF15">
         <v>9</v>
       </c>
       <c r="BG15">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BH15">
         <v>4</v>
@@ -4544,13 +4544,13 @@
         <v>1.94</v>
       </c>
       <c r="S16">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="T16">
         <v>1.58</v>
       </c>
       <c r="U16">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V16">
         <v>1.13</v>
@@ -4670,22 +4670,22 @@
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="BJ16">
         <v>13</v>
       </c>
       <c r="BK16">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BN16">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO16">
         <v>3.3</v>
@@ -4700,31 +4700,31 @@
         <v>23</v>
       </c>
       <c r="BS16">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BT16">
         <v>15.5</v>
       </c>
       <c r="BU16">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BX16">
         <v>50</v>
       </c>
       <c r="BY16">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BZ16">
         <v>11.5</v>
       </c>
       <c r="CA16">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CB16" t="s">
         <v>169</v>
@@ -4747,7 +4747,7 @@
         <v>158</v>
       </c>
       <c r="F17">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="G17">
         <v>1.8</v>
@@ -4765,7 +4765,7 @@
         <v>4.4</v>
       </c>
       <c r="L17">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M17">
         <v>1.05</v>
@@ -4912,7 +4912,7 @@
         <v>3.75</v>
       </c>
       <c r="BI17">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BJ17">
         <v>9.800000000000001</v>
@@ -5004,7 +5004,7 @@
         <v>4</v>
       </c>
       <c r="K18">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L18">
         <v>1.34</v>
@@ -5022,7 +5022,7 @@
         <v>2.28</v>
       </c>
       <c r="Q18">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R18">
         <v>1.51</v>
@@ -5037,10 +5037,10 @@
         <v>2.26</v>
       </c>
       <c r="V18">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W18">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X18">
         <v>21</v>
@@ -5160,7 +5160,7 @@
         <v>9.4</v>
       </c>
       <c r="BK18">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL18">
         <v>95</v>
@@ -5279,7 +5279,7 @@
         <v>1.96</v>
       </c>
       <c r="V19">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W19">
         <v>1.46</v>
@@ -5491,7 +5491,7 @@
         <v>4.3</v>
       </c>
       <c r="L20">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="M20">
         <v>1.03</v>
@@ -5509,7 +5509,7 @@
         <v>1.57</v>
       </c>
       <c r="R20">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S20">
         <v>2.44</v>
@@ -5581,7 +5581,7 @@
         <v>16</v>
       </c>
       <c r="AP20">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ20">
         <v>13.5</v>
@@ -5590,7 +5590,7 @@
         <v>13.5</v>
       </c>
       <c r="AS20">
-        <v>23</v>
+        <v>4.4</v>
       </c>
       <c r="AT20">
         <v>15</v>
@@ -5614,7 +5614,7 @@
         <v>13</v>
       </c>
       <c r="BA20">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BB20">
         <v>4.5</v>
@@ -5718,16 +5718,16 @@
         <v>2.32</v>
       </c>
       <c r="G21">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H21">
         <v>2.96</v>
       </c>
       <c r="I21">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="J21">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K21">
         <v>3.95</v>
@@ -5748,7 +5748,7 @@
         <v>2.1</v>
       </c>
       <c r="Q21">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R21">
         <v>1.34</v>
@@ -5763,10 +5763,10 @@
         <v>1.11</v>
       </c>
       <c r="V21">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -6223,19 +6223,19 @@
         <v>1.07</v>
       </c>
       <c r="N23">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O23">
         <v>1.32</v>
       </c>
       <c r="P23">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q23">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="R23">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S23">
         <v>3.45</v>
@@ -6304,7 +6304,7 @@
         <v>12.5</v>
       </c>
       <c r="AO23">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AP23">
         <v>12.5</v>
@@ -6316,7 +6316,7 @@
         <v>32</v>
       </c>
       <c r="AS23">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT23">
         <v>7.4</v>
@@ -6325,10 +6325,10 @@
         <v>7.6</v>
       </c>
       <c r="AV23">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW23">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX23">
         <v>9.4</v>
@@ -6340,10 +6340,10 @@
         <v>16.5</v>
       </c>
       <c r="BA23">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB23">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC23">
         <v>16</v>
@@ -6352,7 +6352,7 @@
         <v>7</v>
       </c>
       <c r="BE23">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF23">
         <v>8.6</v>
@@ -6447,7 +6447,7 @@
         <v>3.45</v>
       </c>
       <c r="H24">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I24">
         <v>2.58</v>
@@ -6459,7 +6459,7 @@
         <v>3.6</v>
       </c>
       <c r="L24">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M24">
         <v>1.08</v>
@@ -6477,7 +6477,7 @@
         <v>2.1</v>
       </c>
       <c r="R24">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S24">
         <v>3.8</v>
@@ -6683,226 +6683,226 @@
         <v>166</v>
       </c>
       <c r="F25">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="G25">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="H25">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="I25">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="J25">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K25">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L25">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N25">
-        <v>2.76</v>
+        <v>3.65</v>
       </c>
       <c r="O25">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P25">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="Q25">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R25">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="S25">
-        <v>2.32</v>
+        <v>3.35</v>
       </c>
       <c r="T25">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="U25">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V25">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="W25">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="X25">
+        <v>18.5</v>
+      </c>
+      <c r="Y25">
+        <v>24</v>
+      </c>
+      <c r="Z25">
+        <v>65</v>
+      </c>
+      <c r="AA25">
+        <v>210</v>
+      </c>
+      <c r="AB25">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC25">
+        <v>11.5</v>
+      </c>
+      <c r="AD25">
+        <v>29</v>
+      </c>
+      <c r="AE25">
+        <v>110</v>
+      </c>
+      <c r="AF25">
+        <v>12</v>
+      </c>
+      <c r="AG25">
+        <v>12</v>
+      </c>
+      <c r="AH25">
+        <v>27</v>
+      </c>
+      <c r="AI25">
+        <v>110</v>
+      </c>
+      <c r="AJ25">
+        <v>20</v>
+      </c>
+      <c r="AK25">
         <v>22</v>
       </c>
-      <c r="Y25">
-        <v>950</v>
-      </c>
-      <c r="Z25">
-        <v>75</v>
-      </c>
-      <c r="AA25">
-        <v>1000</v>
-      </c>
-      <c r="AB25">
+      <c r="AL25">
+        <v>46</v>
+      </c>
+      <c r="AM25">
+        <v>160</v>
+      </c>
+      <c r="AN25">
+        <v>12.5</v>
+      </c>
+      <c r="AO25">
+        <v>150</v>
+      </c>
+      <c r="AP25">
+        <v>11</v>
+      </c>
+      <c r="AQ25">
+        <v>14</v>
+      </c>
+      <c r="AR25">
+        <v>4</v>
+      </c>
+      <c r="AS25">
+        <v>4.2</v>
+      </c>
+      <c r="AT25">
+        <v>7.2</v>
+      </c>
+      <c r="AU25">
+        <v>8</v>
+      </c>
+      <c r="AV25">
+        <v>17</v>
+      </c>
+      <c r="AW25">
+        <v>4.2</v>
+      </c>
+      <c r="AX25">
+        <v>7.2</v>
+      </c>
+      <c r="AY25">
+        <v>7.4</v>
+      </c>
+      <c r="AZ25">
+        <v>16</v>
+      </c>
+      <c r="BA25">
+        <v>4.2</v>
+      </c>
+      <c r="BB25">
+        <v>12</v>
+      </c>
+      <c r="BC25">
+        <v>13</v>
+      </c>
+      <c r="BD25">
+        <v>3.95</v>
+      </c>
+      <c r="BE25">
+        <v>4.2</v>
+      </c>
+      <c r="BF25">
+        <v>7.8</v>
+      </c>
+      <c r="BG25">
+        <v>4.2</v>
+      </c>
+      <c r="BH25">
+        <v>3.55</v>
+      </c>
+      <c r="BI25">
+        <v>2.78</v>
+      </c>
+      <c r="BJ25">
+        <v>11</v>
+      </c>
+      <c r="BK25">
+        <v>6</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>12</v>
+      </c>
+      <c r="BN25">
+        <v>4.2</v>
+      </c>
+      <c r="BO25">
+        <v>3.25</v>
+      </c>
+      <c r="BP25">
         <v>11.5</v>
       </c>
-      <c r="AC25">
-        <v>13.5</v>
-      </c>
-      <c r="AD25">
-        <v>950</v>
-      </c>
-      <c r="AE25">
-        <v>1000</v>
-      </c>
-      <c r="AF25">
-        <v>14.5</v>
-      </c>
-      <c r="AG25">
-        <v>14.5</v>
-      </c>
-      <c r="AH25">
-        <v>950</v>
-      </c>
-      <c r="AI25">
-        <v>1000</v>
-      </c>
-      <c r="AJ25">
-        <v>24</v>
-      </c>
-      <c r="AK25">
-        <v>26</v>
-      </c>
-      <c r="AL25">
-        <v>55</v>
-      </c>
-      <c r="AM25">
-        <v>1000</v>
-      </c>
-      <c r="AN25">
-        <v>15</v>
-      </c>
-      <c r="AO25">
-        <v>1000</v>
-      </c>
-      <c r="AP25">
-        <v>2.32</v>
-      </c>
-      <c r="AQ25">
-        <v>2.4</v>
-      </c>
-      <c r="AR25">
-        <v>2.52</v>
-      </c>
-      <c r="AS25">
-        <v>2.6</v>
-      </c>
-      <c r="AT25">
-        <v>2.12</v>
-      </c>
-      <c r="AU25">
-        <v>2.18</v>
-      </c>
-      <c r="AV25">
-        <v>2.42</v>
-      </c>
-      <c r="AW25">
-        <v>2.6</v>
-      </c>
-      <c r="AX25">
-        <v>2.2</v>
-      </c>
-      <c r="AY25">
-        <v>2.2</v>
-      </c>
-      <c r="AZ25">
-        <v>2.4</v>
-      </c>
-      <c r="BA25">
-        <v>2.6</v>
-      </c>
-      <c r="BB25">
-        <v>2.34</v>
-      </c>
-      <c r="BC25">
-        <v>2.36</v>
-      </c>
-      <c r="BD25">
-        <v>2.48</v>
-      </c>
-      <c r="BE25">
-        <v>2.6</v>
-      </c>
-      <c r="BF25">
-        <v>6.6</v>
-      </c>
-      <c r="BG25">
-        <v>2.6</v>
-      </c>
-      <c r="BH25">
-        <v>1000</v>
-      </c>
-      <c r="BI25">
-        <v>1.84</v>
-      </c>
-      <c r="BJ25">
-        <v>15.5</v>
-      </c>
-      <c r="BK25">
-        <v>1.64</v>
-      </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
-        <v>1.84</v>
-      </c>
-      <c r="BN25">
-        <v>5.8</v>
-      </c>
-      <c r="BO25">
-        <v>2.84</v>
-      </c>
-      <c r="BP25">
-        <v>16</v>
-      </c>
       <c r="BQ25">
-        <v>1.65</v>
+        <v>6</v>
       </c>
       <c r="BR25">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
-        <v>1.76</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT25">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="BU25">
-        <v>1.62</v>
+        <v>5.5</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>1.8</v>
+        <v>10.5</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>1.8</v>
+        <v>10.5</v>
       </c>
       <c r="BZ25">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="CA25">
-        <v>1.73</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB25" t="s">
         <v>169</v>
@@ -6937,7 +6937,7 @@
         <v>990</v>
       </c>
       <c r="J26">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="K26">
         <v>950</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="199">
   <si>
     <t>League</t>
   </si>
@@ -286,27 +286,27 @@
     <t>Czech 1 Liga</t>
   </si>
   <si>
+    <t>Swedish Allsvenskan</t>
+  </si>
+  <si>
+    <t>Polish I Liga</t>
+  </si>
+  <si>
+    <t>Polish Ekstraklasa</t>
+  </si>
+  <si>
     <t>Swedish Superettan</t>
   </si>
   <si>
-    <t>Swedish Allsvenskan</t>
-  </si>
-  <si>
-    <t>Polish I Liga</t>
-  </si>
-  <si>
     <t>Norwegian 1st Division</t>
   </si>
   <si>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
     <t>Norwegian Eliteserien</t>
   </si>
   <si>
-    <t>Danish Superliga</t>
-  </si>
-  <si>
-    <t>Polish Ekstraklasa</t>
-  </si>
-  <si>
     <t>Hungarian NB I</t>
   </si>
   <si>
@@ -316,6 +316,21 @@
     <t>Bolivian Liga de Futbol Profesional</t>
   </si>
   <si>
+    <t>Brazilian Campeonato Women</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
+    <t>Uruguayan Primera Division</t>
+  </si>
+  <si>
+    <t>Brazilian Serie C</t>
+  </si>
+  <si>
+    <t>Chilean Primera B</t>
+  </si>
+  <si>
     <t>2026-07-27</t>
   </si>
   <si>
@@ -367,6 +382,18 @@
     <t>19:15:00</t>
   </si>
   <si>
+    <t>21:30:00</t>
+  </si>
+  <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
     <t>Deportivo Garcilaso</t>
   </si>
   <si>
@@ -400,27 +427,27 @@
     <t>SC Grobina</t>
   </si>
   <si>
+    <t>Hacken</t>
+  </si>
+  <si>
+    <t>Miedz Legnica</t>
+  </si>
+  <si>
+    <t>Zaglebie Lubin</t>
+  </si>
+  <si>
     <t>Orebro</t>
   </si>
   <si>
-    <t>Hacken</t>
-  </si>
-  <si>
-    <t>Miedz Legnica</t>
-  </si>
-  <si>
     <t>Stabaek</t>
   </si>
   <si>
+    <t>Randers</t>
+  </si>
+  <si>
     <t>Rosenborg</t>
   </si>
   <si>
-    <t>Randers</t>
-  </si>
-  <si>
-    <t>Zaglebie Lubin</t>
-  </si>
-  <si>
     <t>Osters</t>
   </si>
   <si>
@@ -436,15 +463,45 @@
     <t>Botosani</t>
   </si>
   <si>
+    <t>CD Gualberto Villarroel</t>
+  </si>
+  <si>
     <t>Mushuc Runa</t>
   </si>
   <si>
-    <t>CD Gualberto Villarroel</t>
-  </si>
-  <si>
     <t>KA Akureyri</t>
   </si>
   <si>
+    <t>Guayaquil City</t>
+  </si>
+  <si>
+    <t>EC Bahia (W)</t>
+  </si>
+  <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>Atletico GO</t>
+  </si>
+  <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
+    <t>Torque</t>
+  </si>
+  <si>
+    <t>Guarani</t>
+  </si>
+  <si>
+    <t>Floresta EC</t>
+  </si>
+  <si>
+    <t>Union Espanola</t>
+  </si>
+  <si>
+    <t>Union La Calera</t>
+  </si>
+  <si>
     <t>FC Cajamarca</t>
   </si>
   <si>
@@ -478,27 +535,27 @@
     <t>Ogre United</t>
   </si>
   <si>
+    <t>AIK</t>
+  </si>
+  <si>
+    <t>Podbeskidzie B-B</t>
+  </si>
+  <si>
+    <t>Piast Gliwice</t>
+  </si>
+  <si>
     <t>Oddevold</t>
   </si>
   <si>
-    <t>AIK</t>
-  </si>
-  <si>
-    <t>Podbeskidzie B-B</t>
-  </si>
-  <si>
     <t>Hodd</t>
   </si>
   <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
     <t>Fredrikstad</t>
   </si>
   <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
-    <t>Piast Gliwice</t>
-  </si>
-  <si>
     <t>Varbergs BoIS</t>
   </si>
   <si>
@@ -514,16 +571,46 @@
     <t>Rapid Bucharest</t>
   </si>
   <si>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
     <t>Libertad FC</t>
   </si>
   <si>
-    <t>Universitario de Vinto</t>
-  </si>
-  <si>
     <t>Thor</t>
   </si>
   <si>
-    <t>2026-07-25 23:39:35</t>
+    <t>Univ Catolica (Ecu)</t>
+  </si>
+  <si>
+    <t>Botafogo RJ (W)</t>
+  </si>
+  <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
+    <t>Operario PR</t>
+  </si>
+  <si>
+    <t>Cuiaba</t>
+  </si>
+  <si>
+    <t>Wanderers (Uru)</t>
+  </si>
+  <si>
+    <t>Inter Limeira</t>
+  </si>
+  <si>
+    <t>Maringa</t>
+  </si>
+  <si>
+    <t>Deportes Recoleta</t>
+  </si>
+  <si>
+    <t>Everton De Vina</t>
+  </si>
+  <si>
+    <t>2026-07-26 01:52:46</t>
   </si>
 </sst>
 </file>
@@ -855,7 +942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB27"/>
+  <dimension ref="A1:CB37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1105,82 +1192,82 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="F2">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="G2">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="I2">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="K2">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L2">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O2">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="P2">
+        <v>1.8</v>
+      </c>
+      <c r="Q2">
+        <v>2.12</v>
+      </c>
+      <c r="R2">
+        <v>1.29</v>
+      </c>
+      <c r="S2">
+        <v>3.95</v>
+      </c>
+      <c r="T2">
+        <v>2.02</v>
+      </c>
+      <c r="U2">
         <v>1.85</v>
       </c>
-      <c r="Q2">
-        <v>2</v>
-      </c>
-      <c r="R2">
-        <v>1.32</v>
-      </c>
-      <c r="S2">
-        <v>3.6</v>
-      </c>
-      <c r="T2">
-        <v>2.06</v>
-      </c>
-      <c r="U2">
-        <v>1.8</v>
-      </c>
       <c r="V2">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W2">
-        <v>2.58</v>
+        <v>2.28</v>
       </c>
       <c r="X2">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y2">
         <v>25</v>
       </c>
       <c r="Z2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA2">
-        <v>270</v>
+        <v>190</v>
       </c>
       <c r="AB2">
         <v>7.4</v>
@@ -1189,13 +1276,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="AE2">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AF2">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
@@ -1204,88 +1291,88 @@
         <v>950</v>
       </c>
       <c r="AI2">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AJ2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AK2">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AL2">
         <v>44</v>
       </c>
       <c r="AM2">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN2">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AO2">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="AP2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ2">
         <v>12</v>
       </c>
-      <c r="AQ2">
-        <v>17.5</v>
-      </c>
       <c r="AR2">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="AS2">
-        <v>9.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT2">
         <v>6.4</v>
       </c>
       <c r="AU2">
+        <v>7.8</v>
+      </c>
+      <c r="AV2">
+        <v>16.5</v>
+      </c>
+      <c r="AW2">
+        <v>5.7</v>
+      </c>
+      <c r="AX2">
         <v>8.4</v>
-      </c>
-      <c r="AV2">
-        <v>7.4</v>
-      </c>
-      <c r="AW2">
-        <v>9.4</v>
-      </c>
-      <c r="AX2">
-        <v>7.8</v>
       </c>
       <c r="AY2">
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BA2">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
       <c r="BB2">
         <v>13</v>
       </c>
       <c r="BC2">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BD2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BE2">
-        <v>9.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF2">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BG2">
-        <v>9.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH2">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="BI2">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
         <v>6.4</v>
@@ -1294,31 +1381,31 @@
         <v>1000</v>
       </c>
       <c r="BM2">
+        <v>13</v>
+      </c>
+      <c r="BN2">
+        <v>4.2</v>
+      </c>
+      <c r="BO2">
+        <v>3.25</v>
+      </c>
+      <c r="BP2">
         <v>12.5</v>
       </c>
-      <c r="BN2">
-        <v>3.95</v>
-      </c>
-      <c r="BO2">
-        <v>3.1</v>
-      </c>
-      <c r="BP2">
-        <v>10.5</v>
-      </c>
       <c r="BQ2">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
+        <v>10</v>
+      </c>
+      <c r="BT2">
         <v>9.199999999999999</v>
       </c>
-      <c r="BT2">
-        <v>11</v>
-      </c>
       <c r="BU2">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BV2">
         <v>1000</v>
@@ -1330,16 +1417,16 @@
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ2">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1347,25 +1434,25 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="F3">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G3">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H3">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I3">
         <v>4.1</v>
@@ -1374,37 +1461,37 @@
         <v>3.1</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L3">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="M3">
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="O3">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="P3">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q3">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R3">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S3">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="T3">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U3">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="V3">
         <v>1.33</v>
@@ -1434,16 +1521,16 @@
         <v>20</v>
       </c>
       <c r="AE3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG3">
         <v>11.5</v>
       </c>
       <c r="AH3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI3">
         <v>90</v>
@@ -1452,7 +1539,7 @@
         <v>32</v>
       </c>
       <c r="AK3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL3">
         <v>55</v>
@@ -1464,22 +1551,22 @@
         <v>34</v>
       </c>
       <c r="AO3">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP3">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AQ3">
         <v>10</v>
       </c>
       <c r="AR3">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="AS3">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AT3">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU3">
         <v>6.6</v>
@@ -1500,88 +1587,88 @@
         <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BB3">
         <v>27</v>
       </c>
       <c r="BC3">
-        <v>24</v>
+        <v>7.2</v>
       </c>
       <c r="BD3">
         <v>42</v>
       </c>
       <c r="BE3">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BF3">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.86</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>15</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1589,73 +1676,73 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="F4">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="G4">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="H4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K4">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L4">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O4">
         <v>1.35</v>
       </c>
       <c r="P4">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q4">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R4">
         <v>1.33</v>
       </c>
       <c r="S4">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T4">
         <v>1.79</v>
       </c>
       <c r="U4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W4">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X4">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
         <v>12</v>
@@ -1670,19 +1757,19 @@
         <v>10.5</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD4">
         <v>14</v>
       </c>
       <c r="AE4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF4">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH4">
         <v>18</v>
@@ -1694,136 +1781,136 @@
         <v>38</v>
       </c>
       <c r="AK4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS4">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AT4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV4">
         <v>12</v>
       </c>
       <c r="AW4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY4">
         <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="BB4">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BC4">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BD4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE4">
         <v>38</v>
       </c>
       <c r="BF4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="CB4" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1831,22 +1918,22 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="F5">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G5">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="H5">
         <v>6.2</v>
@@ -1858,22 +1945,22 @@
         <v>4.2</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L5">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="O5">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P5">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q5">
         <v>1.74</v>
@@ -1882,10 +1969,10 @@
         <v>1.5</v>
       </c>
       <c r="S5">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="T5">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U5">
         <v>2.1</v>
@@ -1897,175 +1984,175 @@
         <v>2.56</v>
       </c>
       <c r="X5">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>10.5</v>
+        <v>950</v>
       </c>
       <c r="AC5">
-        <v>10.5</v>
+        <v>950</v>
       </c>
       <c r="AD5">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
+        <v>18</v>
+      </c>
+      <c r="AG5">
+        <v>950</v>
+      </c>
+      <c r="AH5">
+        <v>1000</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
         <v>11</v>
       </c>
-      <c r="AG5">
-        <v>10.5</v>
-      </c>
-      <c r="AH5">
-        <v>22</v>
-      </c>
-      <c r="AI5">
-        <v>75</v>
-      </c>
-      <c r="AJ5">
-        <v>16</v>
-      </c>
-      <c r="AK5">
-        <v>16.5</v>
-      </c>
-      <c r="AL5">
-        <v>34</v>
-      </c>
-      <c r="AM5">
-        <v>120</v>
-      </c>
-      <c r="AN5">
-        <v>7.8</v>
-      </c>
       <c r="AO5">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>16</v>
+        <v>1.48</v>
       </c>
       <c r="AQ5">
-        <v>19.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR5">
-        <v>38</v>
+        <v>1.48</v>
       </c>
       <c r="AS5">
-        <v>9.800000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="AT5">
-        <v>8.800000000000001</v>
+        <v>1.36</v>
       </c>
       <c r="AU5">
-        <v>8.800000000000001</v>
+        <v>1.36</v>
       </c>
       <c r="AV5">
-        <v>20</v>
+        <v>1.48</v>
       </c>
       <c r="AW5">
-        <v>10</v>
+        <v>1.48</v>
       </c>
       <c r="AX5">
-        <v>9.199999999999999</v>
+        <v>1.37</v>
       </c>
       <c r="AY5">
-        <v>9</v>
+        <v>1.37</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>1.48</v>
       </c>
       <c r="BA5">
-        <v>10.5</v>
+        <v>1.48</v>
       </c>
       <c r="BB5">
-        <v>13</v>
+        <v>1.48</v>
       </c>
       <c r="BC5">
-        <v>14</v>
+        <v>1.48</v>
       </c>
       <c r="BD5">
-        <v>8.4</v>
+        <v>1.48</v>
       </c>
       <c r="BE5">
-        <v>9.4</v>
+        <v>1.48</v>
       </c>
       <c r="BF5">
-        <v>7</v>
+        <v>1.3</v>
       </c>
       <c r="BG5">
-        <v>10</v>
+        <v>1.48</v>
       </c>
       <c r="BH5">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2073,58 +2160,58 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="E6" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="F6">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="G6">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="H6">
         <v>7.8</v>
       </c>
       <c r="I6">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
       <c r="L6">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="M6">
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O6">
         <v>1.28</v>
       </c>
       <c r="P6">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q6">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R6">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S6">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T6">
         <v>2.04</v>
@@ -2133,10 +2220,10 @@
         <v>1.82</v>
       </c>
       <c r="V6">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W6">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="X6">
         <v>17</v>
@@ -2175,7 +2262,7 @@
         <v>140</v>
       </c>
       <c r="AJ6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK6">
         <v>17</v>
@@ -2199,10 +2286,10 @@
         <v>18</v>
       </c>
       <c r="AR6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT6">
         <v>7</v>
@@ -2211,10 +2298,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX6">
         <v>6.4</v>
@@ -2226,7 +2313,7 @@
         <v>18.5</v>
       </c>
       <c r="BA6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB6">
         <v>9.6</v>
@@ -2238,25 +2325,25 @@
         <v>32</v>
       </c>
       <c r="BE6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF6">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BG6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH6">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI6">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ6">
         <v>12</v>
       </c>
       <c r="BK6">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2274,40 +2361,40 @@
         <v>9.4</v>
       </c>
       <c r="BQ6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BR6">
         <v>27</v>
       </c>
       <c r="BS6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT6">
         <v>12.5</v>
       </c>
       <c r="BU6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ6">
         <v>17</v>
       </c>
       <c r="CA6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB6" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2315,16 +2402,16 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="F7">
         <v>1.04</v>
@@ -2336,10 +2423,10 @@
         <v>1.04</v>
       </c>
       <c r="I7">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J7">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2549,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2557,16 +2644,16 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="F8">
         <v>2.08</v>
@@ -2575,10 +2662,10 @@
         <v>2.36</v>
       </c>
       <c r="H8">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J8">
         <v>3.4</v>
@@ -2596,7 +2683,7 @@
         <v>4</v>
       </c>
       <c r="O8">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="P8">
         <v>2.02</v>
@@ -2605,16 +2692,16 @@
         <v>1.77</v>
       </c>
       <c r="R8">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S8">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="V8">
         <v>1.32</v>
@@ -2632,7 +2719,7 @@
         <v>32</v>
       </c>
       <c r="AA8">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB8">
         <v>13.5</v>
@@ -2677,46 +2764,46 @@
         <v>42</v>
       </c>
       <c r="AP8">
-        <v>12.5</v>
+        <v>3.55</v>
       </c>
       <c r="AQ8">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="AR8">
-        <v>19</v>
+        <v>3.75</v>
       </c>
       <c r="AS8">
         <v>4</v>
       </c>
       <c r="AT8">
-        <v>8.199999999999999</v>
+        <v>3.25</v>
       </c>
       <c r="AU8">
-        <v>6.4</v>
+        <v>3.05</v>
       </c>
       <c r="AV8">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="AW8">
+        <v>3.9</v>
+      </c>
+      <c r="AX8">
+        <v>3.45</v>
+      </c>
+      <c r="AY8">
+        <v>3.25</v>
+      </c>
+      <c r="AZ8">
+        <v>3.5</v>
+      </c>
+      <c r="BA8">
         <v>3.95</v>
       </c>
-      <c r="AX8">
-        <v>11</v>
-      </c>
-      <c r="AY8">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ8">
-        <v>12</v>
-      </c>
-      <c r="BA8">
-        <v>4</v>
-      </c>
       <c r="BB8">
-        <v>20</v>
+        <v>3.8</v>
       </c>
       <c r="BC8">
-        <v>16</v>
+        <v>3.7</v>
       </c>
       <c r="BD8">
         <v>3.9</v>
@@ -2725,7 +2812,7 @@
         <v>4.1</v>
       </c>
       <c r="BF8">
-        <v>10.5</v>
+        <v>3.45</v>
       </c>
       <c r="BG8">
         <v>3.9</v>
@@ -2734,7 +2821,7 @@
         <v>3.85</v>
       </c>
       <c r="BI8">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="BJ8">
         <v>9.6</v>
@@ -2791,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2799,16 +2886,16 @@
         <v>87</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="E9" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="F9">
         <v>1.89</v>
@@ -2826,10 +2913,10 @@
         <v>3.6</v>
       </c>
       <c r="K9">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L9">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="M9">
         <v>1.07</v>
@@ -2871,7 +2958,7 @@
         <v>15.5</v>
       </c>
       <c r="Z9">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA9">
         <v>120</v>
@@ -2883,7 +2970,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD9">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE9">
         <v>65</v>
@@ -2928,7 +3015,7 @@
         <v>29</v>
       </c>
       <c r="AS9">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT9">
         <v>8</v>
@@ -2955,7 +3042,7 @@
         <v>6.6</v>
       </c>
       <c r="BB9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC9">
         <v>19</v>
@@ -2964,19 +3051,19 @@
         <v>32</v>
       </c>
       <c r="BE9">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG9">
         <v>50</v>
       </c>
       <c r="BH9">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI9">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BJ9">
         <v>10.5</v>
@@ -2994,13 +3081,13 @@
         <v>4.5</v>
       </c>
       <c r="BO9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ9">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR9">
         <v>1000</v>
@@ -3024,7 +3111,7 @@
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
@@ -3033,7 +3120,7 @@
         <v>9</v>
       </c>
       <c r="CB9" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3041,16 +3128,16 @@
         <v>88</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E10" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="F10">
         <v>8</v>
@@ -3065,19 +3152,19 @@
         <v>1.5</v>
       </c>
       <c r="J10">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K10">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L10">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M10">
         <v>1.05</v>
       </c>
       <c r="N10">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O10">
         <v>1.26</v>
@@ -3089,16 +3176,16 @@
         <v>1.77</v>
       </c>
       <c r="R10">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S10">
         <v>2.96</v>
       </c>
       <c r="T10">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U10">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V10">
         <v>3</v>
@@ -3110,7 +3197,7 @@
         <v>22</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Z10">
         <v>10</v>
@@ -3119,7 +3206,7 @@
         <v>14</v>
       </c>
       <c r="AB10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AC10">
         <v>13</v>
@@ -3134,7 +3221,7 @@
         <v>85</v>
       </c>
       <c r="AG10">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AH10">
         <v>32</v>
@@ -3158,7 +3245,7 @@
         <v>210</v>
       </c>
       <c r="AO10">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AP10">
         <v>14.5</v>
@@ -3173,7 +3260,7 @@
         <v>10.5</v>
       </c>
       <c r="AT10">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AU10">
         <v>9.4</v>
@@ -3185,97 +3272,97 @@
         <v>11.5</v>
       </c>
       <c r="AX10">
+        <v>6.2</v>
+      </c>
+      <c r="AY10">
         <v>5.6</v>
-      </c>
-      <c r="AY10">
-        <v>5.2</v>
       </c>
       <c r="AZ10">
         <v>21</v>
       </c>
       <c r="BA10">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BB10">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BC10">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD10">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE10">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF10">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG10">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BH10">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI10">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BJ10">
         <v>12</v>
       </c>
       <c r="BK10">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN10">
         <v>12.5</v>
       </c>
       <c r="BO10">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>8.6</v>
+      </c>
+      <c r="BT10">
+        <v>4.1</v>
+      </c>
+      <c r="BU10">
+        <v>3.1</v>
+      </c>
+      <c r="BV10">
         <v>9.199999999999999</v>
       </c>
-      <c r="BR10">
-        <v>1000</v>
-      </c>
-      <c r="BS10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT10">
-        <v>4</v>
-      </c>
-      <c r="BU10">
-        <v>3.05</v>
-      </c>
-      <c r="BV10">
-        <v>9</v>
-      </c>
       <c r="BW10">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BX10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ10">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="CA10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB10" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3283,16 +3370,16 @@
         <v>89</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E11" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="F11">
         <v>4</v>
@@ -3313,13 +3400,13 @@
         <v>4.1</v>
       </c>
       <c r="L11">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="M11">
         <v>1.06</v>
       </c>
       <c r="N11">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O11">
         <v>1.28</v>
@@ -3457,7 +3544,7 @@
         <v>9.6</v>
       </c>
       <c r="BH11">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI11">
         <v>2.86</v>
@@ -3466,31 +3553,31 @@
         <v>10</v>
       </c>
       <c r="BK11">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN11">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BO11">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT11">
         <v>4.9</v>
@@ -3508,16 +3595,16 @@
         <v>28</v>
       </c>
       <c r="BY11">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ11">
         <v>23</v>
       </c>
       <c r="CA11">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB11" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3525,16 +3612,16 @@
         <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E12" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="F12">
         <v>1.04</v>
@@ -3549,7 +3636,7 @@
         <v>990</v>
       </c>
       <c r="J12">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="K12">
         <v>950</v>
@@ -3759,7 +3846,7 @@
         <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3767,241 +3854,241 @@
         <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D13" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E13" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="F13">
-        <v>2.76</v>
+        <v>1.91</v>
       </c>
       <c r="G13">
-        <v>3.15</v>
+        <v>1.94</v>
       </c>
       <c r="H13">
-        <v>2.42</v>
+        <v>3.95</v>
       </c>
       <c r="I13">
+        <v>4</v>
+      </c>
+      <c r="J13">
+        <v>4.3</v>
+      </c>
+      <c r="K13">
+        <v>4.4</v>
+      </c>
+      <c r="L13">
+        <v>1.25</v>
+      </c>
+      <c r="M13">
+        <v>1.03</v>
+      </c>
+      <c r="N13">
+        <v>5.8</v>
+      </c>
+      <c r="O13">
+        <v>1.18</v>
+      </c>
+      <c r="P13">
         <v>2.68</v>
       </c>
-      <c r="J13">
-        <v>3.55</v>
-      </c>
-      <c r="K13">
-        <v>3.95</v>
-      </c>
-      <c r="L13">
-        <v>1.35</v>
-      </c>
-      <c r="M13">
-        <v>1.05</v>
-      </c>
-      <c r="N13">
-        <v>4.3</v>
-      </c>
-      <c r="O13">
-        <v>1.25</v>
-      </c>
-      <c r="P13">
-        <v>2.14</v>
-      </c>
       <c r="Q13">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="R13">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="S13">
-        <v>2.82</v>
+        <v>2.34</v>
       </c>
       <c r="T13">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="U13">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="V13">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="W13">
-        <v>1.47</v>
+        <v>2.06</v>
       </c>
       <c r="X13">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="Y13">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="Z13">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="AA13">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AB13">
         <v>14.5</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AD13">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AE13">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AF13">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="AG13">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AH13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI13">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AJ13">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="AK13">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="AL13">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AM13">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AN13">
-        <v>25</v>
+        <v>8.4</v>
       </c>
       <c r="AO13">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="AP13">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="AQ13">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="AR13">
-        <v>15.5</v>
+        <v>26</v>
       </c>
       <c r="AS13">
-        <v>5.8</v>
+        <v>34</v>
       </c>
       <c r="AT13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU13">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV13">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="AW13">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AX13">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="AY13">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AZ13">
         <v>13</v>
       </c>
       <c r="BA13">
-        <v>5.8</v>
+        <v>30</v>
       </c>
       <c r="BB13">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="BC13">
-        <v>5.6</v>
+        <v>15</v>
       </c>
       <c r="BD13">
-        <v>5.8</v>
+        <v>21</v>
       </c>
       <c r="BE13">
-        <v>6.2</v>
+        <v>42</v>
       </c>
       <c r="BF13">
-        <v>16.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG13">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BH13">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="BI13">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BJ13">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK13">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BL13">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM13">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN13">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BO13">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BP13">
+        <v>13</v>
+      </c>
+      <c r="BQ13">
+        <v>7.6</v>
+      </c>
+      <c r="BR13">
         <v>22</v>
       </c>
-      <c r="BQ13">
-        <v>7</v>
-      </c>
-      <c r="BR13">
+      <c r="BS13">
+        <v>6.8</v>
+      </c>
+      <c r="BT13">
+        <v>8</v>
+      </c>
+      <c r="BU13">
+        <v>4.9</v>
+      </c>
+      <c r="BV13">
+        <v>28</v>
+      </c>
+      <c r="BW13">
+        <v>7.4</v>
+      </c>
+      <c r="BX13">
         <v>32</v>
-      </c>
-      <c r="BS13">
-        <v>7.8</v>
-      </c>
-      <c r="BT13">
-        <v>6</v>
-      </c>
-      <c r="BU13">
-        <v>4.5</v>
-      </c>
-      <c r="BV13">
-        <v>19</v>
-      </c>
-      <c r="BW13">
-        <v>6.6</v>
-      </c>
-      <c r="BX13">
-        <v>29</v>
       </c>
       <c r="BY13">
         <v>7.6</v>
       </c>
       <c r="BZ13">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="CA13">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="CB13" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4009,241 +4096,241 @@
         <v>91</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="E14" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="F14">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="G14">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="H14">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="J14">
+        <v>3.5</v>
+      </c>
+      <c r="K14">
         <v>4.3</v>
       </c>
-      <c r="K14">
+      <c r="L14">
+        <v>1.28</v>
+      </c>
+      <c r="M14">
+        <v>1.05</v>
+      </c>
+      <c r="N14">
         <v>4.4</v>
       </c>
-      <c r="L14">
-        <v>1.25</v>
-      </c>
-      <c r="M14">
-        <v>1.03</v>
-      </c>
-      <c r="N14">
-        <v>5.8</v>
-      </c>
       <c r="O14">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="P14">
-        <v>2.68</v>
+        <v>2.14</v>
       </c>
       <c r="Q14">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="R14">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="S14">
-        <v>2.34</v>
+        <v>2.74</v>
       </c>
       <c r="T14">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="U14">
-        <v>2.64</v>
+        <v>2.28</v>
       </c>
       <c r="V14">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W14">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="X14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Y14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z14">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA14">
         <v>75</v>
       </c>
       <c r="AB14">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC14">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF14">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AG14">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AI14">
         <v>48</v>
       </c>
       <c r="AJ14">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AK14">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AL14">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AM14">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AN14">
+        <v>15</v>
+      </c>
+      <c r="AO14">
+        <v>42</v>
+      </c>
+      <c r="AP14">
+        <v>14</v>
+      </c>
+      <c r="AQ14">
+        <v>12</v>
+      </c>
+      <c r="AR14">
+        <v>21</v>
+      </c>
+      <c r="AS14">
+        <v>4.1</v>
+      </c>
+      <c r="AT14">
         <v>8.6</v>
       </c>
-      <c r="AO14">
-        <v>29</v>
-      </c>
-      <c r="AP14">
-        <v>6.6</v>
-      </c>
-      <c r="AQ14">
-        <v>18.5</v>
-      </c>
-      <c r="AR14">
+      <c r="AU14">
+        <v>6.8</v>
+      </c>
+      <c r="AV14">
+        <v>11.5</v>
+      </c>
+      <c r="AW14">
+        <v>4</v>
+      </c>
+      <c r="AX14">
+        <v>10.5</v>
+      </c>
+      <c r="AY14">
+        <v>8</v>
+      </c>
+      <c r="AZ14">
+        <v>12</v>
+      </c>
+      <c r="BA14">
+        <v>4</v>
+      </c>
+      <c r="BB14">
+        <v>18</v>
+      </c>
+      <c r="BC14">
+        <v>14.5</v>
+      </c>
+      <c r="BD14">
+        <v>3.9</v>
+      </c>
+      <c r="BE14">
+        <v>4.1</v>
+      </c>
+      <c r="BF14">
+        <v>9</v>
+      </c>
+      <c r="BG14">
+        <v>3.95</v>
+      </c>
+      <c r="BH14">
+        <v>4</v>
+      </c>
+      <c r="BI14">
+        <v>3.05</v>
+      </c>
+      <c r="BJ14">
+        <v>9.4</v>
+      </c>
+      <c r="BK14">
+        <v>5</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>9.6</v>
+      </c>
+      <c r="BN14">
+        <v>5.3</v>
+      </c>
+      <c r="BO14">
+        <v>3.9</v>
+      </c>
+      <c r="BP14">
+        <v>14.5</v>
+      </c>
+      <c r="BQ14">
+        <v>6</v>
+      </c>
+      <c r="BR14">
+        <v>26</v>
+      </c>
+      <c r="BS14">
         <v>7.4</v>
       </c>
-      <c r="AS14">
-        <v>7.4</v>
-      </c>
-      <c r="AT14">
-        <v>12</v>
-      </c>
-      <c r="AU14">
-        <v>9</v>
-      </c>
-      <c r="AV14">
-        <v>12.5</v>
-      </c>
-      <c r="AW14">
+      <c r="BT14">
         <v>7.6</v>
       </c>
-      <c r="AX14">
-        <v>13</v>
-      </c>
-      <c r="AY14">
-        <v>9.4</v>
-      </c>
-      <c r="AZ14">
-        <v>12.5</v>
-      </c>
-      <c r="BA14">
-        <v>7.6</v>
-      </c>
-      <c r="BB14">
-        <v>19</v>
-      </c>
-      <c r="BC14">
-        <v>13</v>
-      </c>
-      <c r="BD14">
-        <v>21</v>
-      </c>
-      <c r="BE14">
-        <v>7.2</v>
-      </c>
-      <c r="BF14">
-        <v>7.2</v>
-      </c>
-      <c r="BG14">
-        <v>20</v>
-      </c>
-      <c r="BH14">
-        <v>1000</v>
-      </c>
-      <c r="BI14">
-        <v>2</v>
-      </c>
-      <c r="BJ14">
-        <v>12.5</v>
-      </c>
-      <c r="BK14">
+      <c r="BU14">
         <v>5.4</v>
       </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>1.97</v>
-      </c>
-      <c r="BN14">
-        <v>7.4</v>
-      </c>
-      <c r="BO14">
-        <v>3.45</v>
-      </c>
-      <c r="BP14">
-        <v>18</v>
-      </c>
-      <c r="BQ14">
-        <v>1.81</v>
-      </c>
-      <c r="BR14">
-        <v>30</v>
-      </c>
-      <c r="BS14">
-        <v>1.88</v>
-      </c>
-      <c r="BT14">
-        <v>11</v>
-      </c>
-      <c r="BU14">
-        <v>4.9</v>
-      </c>
       <c r="BV14">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.91</v>
+        <v>7.8</v>
       </c>
       <c r="BX14">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.93</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ14">
         <v>20</v>
       </c>
       <c r="CA14">
-        <v>1.83</v>
+        <v>6.8</v>
       </c>
       <c r="CB14" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4251,241 +4338,241 @@
         <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E15" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="F15">
+        <v>2.86</v>
+      </c>
+      <c r="G15">
+        <v>3.15</v>
+      </c>
+      <c r="H15">
+        <v>2.7</v>
+      </c>
+      <c r="I15">
+        <v>2.92</v>
+      </c>
+      <c r="J15">
+        <v>3.1</v>
+      </c>
+      <c r="K15">
+        <v>3.4</v>
+      </c>
+      <c r="L15">
+        <v>1.46</v>
+      </c>
+      <c r="M15">
+        <v>1.1</v>
+      </c>
+      <c r="N15">
+        <v>3</v>
+      </c>
+      <c r="O15">
+        <v>1.42</v>
+      </c>
+      <c r="P15">
+        <v>1.69</v>
+      </c>
+      <c r="Q15">
+        <v>2.26</v>
+      </c>
+      <c r="R15">
+        <v>1.25</v>
+      </c>
+      <c r="S15">
+        <v>4.3</v>
+      </c>
+      <c r="T15">
+        <v>1.89</v>
+      </c>
+      <c r="U15">
         <v>1.97</v>
       </c>
-      <c r="G15">
-        <v>2.22</v>
-      </c>
-      <c r="H15">
-        <v>3.45</v>
-      </c>
-      <c r="I15">
-        <v>4.2</v>
-      </c>
-      <c r="J15">
-        <v>3.5</v>
-      </c>
-      <c r="K15">
-        <v>4.3</v>
-      </c>
-      <c r="L15">
-        <v>1.28</v>
-      </c>
-      <c r="M15">
-        <v>1.05</v>
-      </c>
-      <c r="N15">
-        <v>4.4</v>
-      </c>
-      <c r="O15">
-        <v>1.24</v>
-      </c>
-      <c r="P15">
-        <v>2.16</v>
-      </c>
-      <c r="Q15">
+      <c r="V15">
+        <v>1.52</v>
+      </c>
+      <c r="W15">
+        <v>1.46</v>
+      </c>
+      <c r="X15">
+        <v>12.5</v>
+      </c>
+      <c r="Y15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z15">
+        <v>21</v>
+      </c>
+      <c r="AA15">
+        <v>55</v>
+      </c>
+      <c r="AB15">
+        <v>11.5</v>
+      </c>
+      <c r="AC15">
+        <v>7.4</v>
+      </c>
+      <c r="AD15">
+        <v>15</v>
+      </c>
+      <c r="AE15">
+        <v>36</v>
+      </c>
+      <c r="AF15">
+        <v>23</v>
+      </c>
+      <c r="AG15">
+        <v>15.5</v>
+      </c>
+      <c r="AH15">
+        <v>22</v>
+      </c>
+      <c r="AI15">
+        <v>65</v>
+      </c>
+      <c r="AJ15">
+        <v>65</v>
+      </c>
+      <c r="AK15">
+        <v>46</v>
+      </c>
+      <c r="AL15">
+        <v>65</v>
+      </c>
+      <c r="AM15">
+        <v>150</v>
+      </c>
+      <c r="AN15">
+        <v>50</v>
+      </c>
+      <c r="AO15">
+        <v>36</v>
+      </c>
+      <c r="AP15">
+        <v>9.4</v>
+      </c>
+      <c r="AQ15">
+        <v>8.4</v>
+      </c>
+      <c r="AR15">
+        <v>15</v>
+      </c>
+      <c r="AS15">
+        <v>36</v>
+      </c>
+      <c r="AT15">
+        <v>9</v>
+      </c>
+      <c r="AU15">
+        <v>6.4</v>
+      </c>
+      <c r="AV15">
+        <v>11</v>
+      </c>
+      <c r="AW15">
+        <v>5.4</v>
+      </c>
+      <c r="AX15">
+        <v>17.5</v>
+      </c>
+      <c r="AY15">
+        <v>11.5</v>
+      </c>
+      <c r="AZ15">
+        <v>16.5</v>
+      </c>
+      <c r="BA15">
+        <v>5.7</v>
+      </c>
+      <c r="BB15">
+        <v>5.7</v>
+      </c>
+      <c r="BC15">
+        <v>5.6</v>
+      </c>
+      <c r="BD15">
+        <v>5.8</v>
+      </c>
+      <c r="BE15">
+        <v>6.2</v>
+      </c>
+      <c r="BF15">
+        <v>32</v>
+      </c>
+      <c r="BG15">
+        <v>5.4</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.79</v>
+      </c>
+      <c r="BJ15">
+        <v>14.5</v>
+      </c>
+      <c r="BK15">
+        <v>1.59</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.79</v>
+      </c>
+      <c r="BN15">
+        <v>8</v>
+      </c>
+      <c r="BO15">
+        <v>4.5</v>
+      </c>
+      <c r="BP15">
+        <v>36</v>
+      </c>
+      <c r="BQ15">
         <v>1.71</v>
       </c>
-      <c r="R15">
-        <v>1.45</v>
-      </c>
-      <c r="S15">
-        <v>2.78</v>
-      </c>
-      <c r="T15">
-        <v>1.63</v>
-      </c>
-      <c r="U15">
-        <v>2.26</v>
-      </c>
-      <c r="V15">
-        <v>1.31</v>
-      </c>
-      <c r="W15">
-        <v>1.81</v>
-      </c>
-      <c r="X15">
-        <v>23</v>
-      </c>
-      <c r="Y15">
-        <v>21</v>
-      </c>
-      <c r="Z15">
-        <v>36</v>
-      </c>
-      <c r="AA15">
-        <v>85</v>
-      </c>
-      <c r="AB15">
-        <v>14</v>
-      </c>
-      <c r="AC15">
-        <v>11</v>
-      </c>
-      <c r="AD15">
-        <v>19</v>
-      </c>
-      <c r="AE15">
-        <v>50</v>
-      </c>
-      <c r="AF15">
-        <v>17.5</v>
-      </c>
-      <c r="AG15">
-        <v>13</v>
-      </c>
-      <c r="AH15">
-        <v>20</v>
-      </c>
-      <c r="AI15">
-        <v>55</v>
-      </c>
-      <c r="AJ15">
-        <v>32</v>
-      </c>
-      <c r="AK15">
-        <v>25</v>
-      </c>
-      <c r="AL15">
-        <v>38</v>
-      </c>
-      <c r="AM15">
-        <v>90</v>
-      </c>
-      <c r="AN15">
-        <v>15</v>
-      </c>
-      <c r="AO15">
-        <v>42</v>
-      </c>
-      <c r="AP15">
-        <v>14</v>
-      </c>
-      <c r="AQ15">
-        <v>12</v>
-      </c>
-      <c r="AR15">
-        <v>20</v>
-      </c>
-      <c r="AS15">
-        <v>4</v>
-      </c>
-      <c r="AT15">
-        <v>8.6</v>
-      </c>
-      <c r="AU15">
-        <v>6.8</v>
-      </c>
-      <c r="AV15">
-        <v>11.5</v>
-      </c>
-      <c r="AW15">
-        <v>3.95</v>
-      </c>
-      <c r="AX15">
-        <v>10.5</v>
-      </c>
-      <c r="AY15">
-        <v>8</v>
-      </c>
-      <c r="AZ15">
-        <v>12</v>
-      </c>
-      <c r="BA15">
-        <v>3.95</v>
-      </c>
-      <c r="BB15">
-        <v>18</v>
-      </c>
-      <c r="BC15">
-        <v>14.5</v>
-      </c>
-      <c r="BD15">
-        <v>3.85</v>
-      </c>
-      <c r="BE15">
-        <v>4</v>
-      </c>
-      <c r="BF15">
-        <v>9</v>
-      </c>
-      <c r="BG15">
-        <v>3.85</v>
-      </c>
-      <c r="BH15">
-        <v>4</v>
-      </c>
-      <c r="BI15">
-        <v>3.05</v>
-      </c>
-      <c r="BJ15">
-        <v>9.4</v>
-      </c>
-      <c r="BK15">
-        <v>5</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>9.6</v>
-      </c>
-      <c r="BN15">
-        <v>5.3</v>
-      </c>
-      <c r="BO15">
-        <v>3.9</v>
-      </c>
-      <c r="BP15">
-        <v>14.5</v>
-      </c>
-      <c r="BQ15">
-        <v>6</v>
-      </c>
       <c r="BR15">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>7.4</v>
+        <v>1.74</v>
       </c>
       <c r="BT15">
         <v>7.6</v>
       </c>
       <c r="BU15">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW15">
-        <v>7.8</v>
+        <v>1.69</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>8.199999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="BZ15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="CA15">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4493,241 +4580,241 @@
         <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="E16" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="F16">
-        <v>1.43</v>
+        <v>2.76</v>
       </c>
       <c r="G16">
-        <v>1.5</v>
+        <v>3.15</v>
       </c>
       <c r="H16">
-        <v>6.4</v>
+        <v>2.42</v>
       </c>
       <c r="I16">
-        <v>8.4</v>
+        <v>2.68</v>
       </c>
       <c r="J16">
-        <v>5.4</v>
+        <v>3.55</v>
       </c>
       <c r="K16">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="L16">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N16">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="O16">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="P16">
-        <v>3.3</v>
+        <v>2.14</v>
       </c>
       <c r="Q16">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="R16">
-        <v>1.94</v>
+        <v>1.45</v>
       </c>
       <c r="S16">
-        <v>1.89</v>
+        <v>2.82</v>
       </c>
       <c r="T16">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="U16">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="V16">
-        <v>1.13</v>
+        <v>1.6</v>
       </c>
       <c r="W16">
-        <v>3</v>
+        <v>1.47</v>
       </c>
       <c r="X16">
+        <v>19</v>
+      </c>
+      <c r="Y16">
+        <v>15</v>
+      </c>
+      <c r="Z16">
+        <v>21</v>
+      </c>
+      <c r="AA16">
+        <v>40</v>
+      </c>
+      <c r="AB16">
+        <v>14.5</v>
+      </c>
+      <c r="AC16">
+        <v>9</v>
+      </c>
+      <c r="AD16">
+        <v>14</v>
+      </c>
+      <c r="AE16">
+        <v>28</v>
+      </c>
+      <c r="AF16">
+        <v>24</v>
+      </c>
+      <c r="AG16">
+        <v>15</v>
+      </c>
+      <c r="AH16">
+        <v>16.5</v>
+      </c>
+      <c r="AI16">
+        <v>38</v>
+      </c>
+      <c r="AJ16">
         <v>50</v>
       </c>
-      <c r="Y16">
-        <v>48</v>
-      </c>
-      <c r="Z16">
-        <v>80</v>
-      </c>
-      <c r="AA16">
-        <v>190</v>
-      </c>
-      <c r="AB16">
-        <v>19</v>
-      </c>
-      <c r="AC16">
-        <v>17</v>
-      </c>
-      <c r="AD16">
+      <c r="AK16">
         <v>32</v>
       </c>
-      <c r="AE16">
-        <v>85</v>
-      </c>
-      <c r="AF16">
-        <v>15.5</v>
-      </c>
-      <c r="AG16">
-        <v>13</v>
-      </c>
-      <c r="AH16">
-        <v>23</v>
-      </c>
-      <c r="AI16">
-        <v>70</v>
-      </c>
-      <c r="AJ16">
-        <v>17.5</v>
-      </c>
-      <c r="AK16">
-        <v>16</v>
-      </c>
       <c r="AL16">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AM16">
         <v>75</v>
       </c>
       <c r="AN16">
-        <v>4.7</v>
+        <v>25</v>
       </c>
       <c r="AO16">
-        <v>60</v>
+        <v>19.5</v>
       </c>
       <c r="AP16">
+        <v>15.5</v>
+      </c>
+      <c r="AQ16">
+        <v>11</v>
+      </c>
+      <c r="AR16">
+        <v>15.5</v>
+      </c>
+      <c r="AS16">
+        <v>5.8</v>
+      </c>
+      <c r="AT16">
+        <v>11.5</v>
+      </c>
+      <c r="AU16">
+        <v>7.4</v>
+      </c>
+      <c r="AV16">
+        <v>10</v>
+      </c>
+      <c r="AW16">
+        <v>21</v>
+      </c>
+      <c r="AX16">
+        <v>17.5</v>
+      </c>
+      <c r="AY16">
+        <v>11</v>
+      </c>
+      <c r="AZ16">
+        <v>13</v>
+      </c>
+      <c r="BA16">
+        <v>5.8</v>
+      </c>
+      <c r="BB16">
+        <v>6</v>
+      </c>
+      <c r="BC16">
+        <v>5.6</v>
+      </c>
+      <c r="BD16">
+        <v>5.8</v>
+      </c>
+      <c r="BE16">
+        <v>6.2</v>
+      </c>
+      <c r="BF16">
+        <v>16.5</v>
+      </c>
+      <c r="BG16">
+        <v>14</v>
+      </c>
+      <c r="BH16">
+        <v>4</v>
+      </c>
+      <c r="BI16">
+        <v>3.15</v>
+      </c>
+      <c r="BJ16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK16">
         <v>4.8</v>
       </c>
-      <c r="AQ16">
-        <v>4.8</v>
-      </c>
-      <c r="AR16">
-        <v>5</v>
-      </c>
-      <c r="AS16">
-        <v>5.1</v>
-      </c>
-      <c r="AT16">
-        <v>12.5</v>
-      </c>
-      <c r="AU16">
-        <v>11</v>
-      </c>
-      <c r="AV16">
-        <v>21</v>
-      </c>
-      <c r="AW16">
-        <v>5</v>
-      </c>
-      <c r="AX16">
-        <v>10</v>
-      </c>
-      <c r="AY16">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ16">
-        <v>15</v>
-      </c>
-      <c r="BA16">
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN16">
+        <v>6.6</v>
+      </c>
+      <c r="BO16">
         <v>4.9</v>
       </c>
-      <c r="BB16">
-        <v>11.5</v>
-      </c>
-      <c r="BC16">
-        <v>10.5</v>
-      </c>
-      <c r="BD16">
-        <v>18</v>
-      </c>
-      <c r="BE16">
-        <v>4.9</v>
-      </c>
-      <c r="BF16">
-        <v>3.35</v>
-      </c>
-      <c r="BG16">
-        <v>4.9</v>
-      </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>2.26</v>
-      </c>
-      <c r="BJ16">
-        <v>13</v>
-      </c>
-      <c r="BK16">
-        <v>1.94</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>2.22</v>
-      </c>
-      <c r="BN16">
+      <c r="BP16">
+        <v>22</v>
+      </c>
+      <c r="BQ16">
+        <v>6.8</v>
+      </c>
+      <c r="BR16">
+        <v>32</v>
+      </c>
+      <c r="BS16">
+        <v>7.6</v>
+      </c>
+      <c r="BT16">
+        <v>5.9</v>
+      </c>
+      <c r="BU16">
+        <v>4.5</v>
+      </c>
+      <c r="BV16">
+        <v>18.5</v>
+      </c>
+      <c r="BW16">
         <v>6.4</v>
       </c>
-      <c r="BO16">
-        <v>3.3</v>
-      </c>
-      <c r="BP16">
-        <v>11.5</v>
-      </c>
-      <c r="BQ16">
-        <v>5.4</v>
-      </c>
-      <c r="BR16">
-        <v>23</v>
-      </c>
-      <c r="BS16">
-        <v>2.06</v>
-      </c>
-      <c r="BT16">
-        <v>15.5</v>
-      </c>
-      <c r="BU16">
-        <v>1.99</v>
-      </c>
-      <c r="BV16">
-        <v>1000</v>
-      </c>
-      <c r="BW16">
-        <v>2.2</v>
-      </c>
       <c r="BX16">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="BY16">
-        <v>2.18</v>
+        <v>7.4</v>
       </c>
       <c r="BZ16">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="CA16">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="CB16" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4735,241 +4822,241 @@
         <v>94</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D17" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="E17" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="F17">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="G17">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H17">
+        <v>6.4</v>
+      </c>
+      <c r="I17">
+        <v>8.4</v>
+      </c>
+      <c r="J17">
+        <v>5.4</v>
+      </c>
+      <c r="K17">
+        <v>7</v>
+      </c>
+      <c r="L17">
+        <v>1.18</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>7.8</v>
+      </c>
+      <c r="O17">
+        <v>1.12</v>
+      </c>
+      <c r="P17">
+        <v>3.35</v>
+      </c>
+      <c r="Q17">
+        <v>1.35</v>
+      </c>
+      <c r="R17">
+        <v>1.96</v>
+      </c>
+      <c r="S17">
+        <v>1.86</v>
+      </c>
+      <c r="T17">
+        <v>1.57</v>
+      </c>
+      <c r="U17">
+        <v>2.5</v>
+      </c>
+      <c r="V17">
+        <v>1.13</v>
+      </c>
+      <c r="W17">
+        <v>3</v>
+      </c>
+      <c r="X17">
+        <v>50</v>
+      </c>
+      <c r="Y17">
+        <v>48</v>
+      </c>
+      <c r="Z17">
+        <v>80</v>
+      </c>
+      <c r="AA17">
+        <v>190</v>
+      </c>
+      <c r="AB17">
+        <v>19</v>
+      </c>
+      <c r="AC17">
+        <v>17.5</v>
+      </c>
+      <c r="AD17">
+        <v>32</v>
+      </c>
+      <c r="AE17">
+        <v>85</v>
+      </c>
+      <c r="AF17">
+        <v>16</v>
+      </c>
+      <c r="AG17">
+        <v>13.5</v>
+      </c>
+      <c r="AH17">
+        <v>23</v>
+      </c>
+      <c r="AI17">
+        <v>65</v>
+      </c>
+      <c r="AJ17">
+        <v>17.5</v>
+      </c>
+      <c r="AK17">
+        <v>16</v>
+      </c>
+      <c r="AL17">
+        <v>27</v>
+      </c>
+      <c r="AM17">
+        <v>75</v>
+      </c>
+      <c r="AN17">
+        <v>4.6</v>
+      </c>
+      <c r="AO17">
+        <v>60</v>
+      </c>
+      <c r="AP17">
+        <v>4.8</v>
+      </c>
+      <c r="AQ17">
+        <v>4.8</v>
+      </c>
+      <c r="AR17">
         <v>5</v>
       </c>
-      <c r="I17">
-        <v>5.7</v>
-      </c>
-      <c r="J17">
-        <v>3.95</v>
-      </c>
-      <c r="K17">
-        <v>4.4</v>
-      </c>
-      <c r="L17">
-        <v>1.36</v>
-      </c>
-      <c r="M17">
-        <v>1.05</v>
-      </c>
-      <c r="N17">
-        <v>4.2</v>
-      </c>
-      <c r="O17">
-        <v>1.27</v>
-      </c>
-      <c r="P17">
-        <v>2.1</v>
-      </c>
-      <c r="Q17">
-        <v>1.78</v>
-      </c>
-      <c r="R17">
-        <v>1.43</v>
-      </c>
-      <c r="S17">
-        <v>2.98</v>
-      </c>
-      <c r="T17">
-        <v>1.79</v>
-      </c>
-      <c r="U17">
-        <v>2.12</v>
-      </c>
-      <c r="V17">
-        <v>1.21</v>
-      </c>
-      <c r="W17">
-        <v>2.24</v>
-      </c>
-      <c r="X17">
-        <v>20</v>
-      </c>
-      <c r="Y17">
-        <v>23</v>
-      </c>
-      <c r="Z17">
-        <v>48</v>
-      </c>
-      <c r="AA17">
-        <v>140</v>
-      </c>
-      <c r="AB17">
-        <v>11</v>
-      </c>
-      <c r="AC17">
-        <v>9.6</v>
-      </c>
-      <c r="AD17">
-        <v>24</v>
-      </c>
-      <c r="AE17">
-        <v>70</v>
-      </c>
-      <c r="AF17">
-        <v>13</v>
-      </c>
-      <c r="AG17">
-        <v>11</v>
-      </c>
-      <c r="AH17">
-        <v>22</v>
-      </c>
-      <c r="AI17">
-        <v>75</v>
-      </c>
-      <c r="AJ17">
+      <c r="AS17">
+        <v>5.2</v>
+      </c>
+      <c r="AT17">
+        <v>12.5</v>
+      </c>
+      <c r="AU17">
+        <v>11.5</v>
+      </c>
+      <c r="AV17">
         <v>21</v>
       </c>
-      <c r="AK17">
-        <v>21</v>
-      </c>
-      <c r="AL17">
-        <v>38</v>
-      </c>
-      <c r="AM17">
-        <v>110</v>
-      </c>
-      <c r="AN17">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO17">
-        <v>80</v>
-      </c>
-      <c r="AP17">
-        <v>15</v>
-      </c>
-      <c r="AQ17">
-        <v>15</v>
-      </c>
-      <c r="AR17">
-        <v>5.6</v>
-      </c>
-      <c r="AS17">
-        <v>6</v>
-      </c>
-      <c r="AT17">
-        <v>8.4</v>
-      </c>
-      <c r="AU17">
-        <v>7.4</v>
-      </c>
-      <c r="AV17">
-        <v>15.5</v>
-      </c>
       <c r="AW17">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="AX17">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY17">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ17">
         <v>14.5</v>
       </c>
       <c r="BA17">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="BB17">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC17">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD17">
-        <v>5.4</v>
+        <v>18</v>
       </c>
       <c r="BE17">
+        <v>4.9</v>
+      </c>
+      <c r="BF17">
+        <v>3.3</v>
+      </c>
+      <c r="BG17">
+        <v>4.9</v>
+      </c>
+      <c r="BH17">
+        <v>5.7</v>
+      </c>
+      <c r="BI17">
+        <v>4.5</v>
+      </c>
+      <c r="BJ17">
+        <v>9.6</v>
+      </c>
+      <c r="BK17">
+        <v>5.6</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>11</v>
+      </c>
+      <c r="BN17">
+        <v>4.8</v>
+      </c>
+      <c r="BO17">
+        <v>3.8</v>
+      </c>
+      <c r="BP17">
+        <v>8.6</v>
+      </c>
+      <c r="BQ17">
+        <v>5.2</v>
+      </c>
+      <c r="BR17">
+        <v>970</v>
+      </c>
+      <c r="BS17">
+        <v>7.4</v>
+      </c>
+      <c r="BT17">
+        <v>11.5</v>
+      </c>
+      <c r="BU17">
         <v>6</v>
       </c>
-      <c r="BF17">
-        <v>7.6</v>
-      </c>
-      <c r="BG17">
-        <v>5.9</v>
-      </c>
-      <c r="BH17">
-        <v>3.75</v>
-      </c>
-      <c r="BI17">
-        <v>3.05</v>
-      </c>
-      <c r="BJ17">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK17">
-        <v>6</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>6.2</v>
-      </c>
-      <c r="BN17">
-        <v>4.5</v>
-      </c>
-      <c r="BO17">
-        <v>3.6</v>
-      </c>
-      <c r="BP17">
-        <v>11.5</v>
-      </c>
-      <c r="BQ17">
-        <v>6.6</v>
-      </c>
-      <c r="BR17">
-        <v>1000</v>
-      </c>
-      <c r="BS17">
-        <v>9.6</v>
-      </c>
-      <c r="BT17">
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>10</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>10</v>
+      </c>
+      <c r="BZ17">
         <v>8.800000000000001</v>
       </c>
-      <c r="BU17">
-        <v>5.6</v>
-      </c>
-      <c r="BV17">
-        <v>1000</v>
-      </c>
-      <c r="BW17">
-        <v>11.5</v>
-      </c>
-      <c r="BX17">
-        <v>1000</v>
-      </c>
-      <c r="BY17">
-        <v>11.5</v>
-      </c>
-      <c r="BZ17">
-        <v>1000</v>
-      </c>
       <c r="CA17">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="CB17" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4977,16 +5064,16 @@
         <v>95</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D18" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E18" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="F18">
         <v>1.82</v>
@@ -5007,13 +5094,13 @@
         <v>4.3</v>
       </c>
       <c r="L18">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M18">
         <v>1.05</v>
       </c>
       <c r="N18">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O18">
         <v>1.24</v>
@@ -5028,19 +5115,19 @@
         <v>1.51</v>
       </c>
       <c r="S18">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="T18">
         <v>1.7</v>
       </c>
       <c r="U18">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V18">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W18">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X18">
         <v>21</v>
@@ -5055,7 +5142,7 @@
         <v>110</v>
       </c>
       <c r="AB18">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC18">
         <v>9.800000000000001</v>
@@ -5067,7 +5154,7 @@
         <v>55</v>
       </c>
       <c r="AF18">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -5103,10 +5190,10 @@
         <v>17.5</v>
       </c>
       <c r="AR18">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS18">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AT18">
         <v>9.800000000000001</v>
@@ -5118,7 +5205,7 @@
         <v>16.5</v>
       </c>
       <c r="AW18">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX18">
         <v>9.6</v>
@@ -5130,7 +5217,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB18">
         <v>15</v>
@@ -5139,25 +5226,25 @@
         <v>13.5</v>
       </c>
       <c r="BD18">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE18">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF18">
         <v>7.8</v>
       </c>
       <c r="BG18">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BH18">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BI18">
         <v>3.45</v>
       </c>
       <c r="BJ18">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK18">
         <v>7.8</v>
@@ -5166,7 +5253,7 @@
         <v>95</v>
       </c>
       <c r="BM18">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BN18">
         <v>4.7</v>
@@ -5175,43 +5262,43 @@
         <v>4.1</v>
       </c>
       <c r="BP18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BQ18">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR18">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BS18">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT18">
         <v>8</v>
       </c>
       <c r="BU18">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV18">
         <v>36</v>
       </c>
       <c r="BW18">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX18">
         <v>40</v>
       </c>
       <c r="BY18">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ18">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="CA18">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB18" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5219,279 +5306,279 @@
         <v>96</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E19" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="F19">
-        <v>2.86</v>
+        <v>1.71</v>
       </c>
       <c r="G19">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="H19">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="I19">
-        <v>2.96</v>
+        <v>5.7</v>
       </c>
       <c r="J19">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="K19">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M19">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="N19">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="O19">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="P19">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="Q19">
-        <v>2.26</v>
+        <v>1.78</v>
       </c>
       <c r="R19">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="S19">
-        <v>4.3</v>
+        <v>2.98</v>
       </c>
       <c r="T19">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="U19">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="V19">
-        <v>1.51</v>
+        <v>1.21</v>
       </c>
       <c r="W19">
-        <v>1.46</v>
+        <v>2.24</v>
       </c>
       <c r="X19">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="Y19">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="Z19">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="AA19">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="AB19">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC19">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD19">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AE19">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AF19">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AG19">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AH19">
         <v>22</v>
       </c>
       <c r="AI19">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ19">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="AK19">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="AL19">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AM19">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AN19">
-        <v>50</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO19">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AP19">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="AQ19">
+        <v>15</v>
+      </c>
+      <c r="AR19">
+        <v>5.6</v>
+      </c>
+      <c r="AS19">
+        <v>6</v>
+      </c>
+      <c r="AT19">
         <v>8.4</v>
       </c>
-      <c r="AR19">
-        <v>15</v>
-      </c>
-      <c r="AS19">
-        <v>36</v>
-      </c>
-      <c r="AT19">
-        <v>9</v>
-      </c>
       <c r="AU19">
+        <v>7.4</v>
+      </c>
+      <c r="AV19">
+        <v>15.5</v>
+      </c>
+      <c r="AW19">
+        <v>5.8</v>
+      </c>
+      <c r="AX19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY19">
+        <v>7.8</v>
+      </c>
+      <c r="AZ19">
+        <v>14.5</v>
+      </c>
+      <c r="BA19">
+        <v>5.9</v>
+      </c>
+      <c r="BB19">
+        <v>15.5</v>
+      </c>
+      <c r="BC19">
+        <v>13.5</v>
+      </c>
+      <c r="BD19">
+        <v>5.4</v>
+      </c>
+      <c r="BE19">
+        <v>6</v>
+      </c>
+      <c r="BF19">
+        <v>7.6</v>
+      </c>
+      <c r="BG19">
+        <v>5.9</v>
+      </c>
+      <c r="BH19">
+        <v>3.8</v>
+      </c>
+      <c r="BI19">
+        <v>3.35</v>
+      </c>
+      <c r="BJ19">
+        <v>10</v>
+      </c>
+      <c r="BK19">
+        <v>5.9</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>13</v>
+      </c>
+      <c r="BN19">
+        <v>4.5</v>
+      </c>
+      <c r="BO19">
+        <v>3.6</v>
+      </c>
+      <c r="BP19">
+        <v>11.5</v>
+      </c>
+      <c r="BQ19">
         <v>6.4</v>
       </c>
-      <c r="AV19">
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU19">
+        <v>5.4</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>10.5</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
         <v>11</v>
       </c>
-      <c r="AW19">
-        <v>5.4</v>
-      </c>
-      <c r="AX19">
-        <v>17.5</v>
-      </c>
-      <c r="AY19">
-        <v>11.5</v>
-      </c>
-      <c r="AZ19">
-        <v>16.5</v>
-      </c>
-      <c r="BA19">
-        <v>5.7</v>
-      </c>
-      <c r="BB19">
-        <v>5.7</v>
-      </c>
-      <c r="BC19">
-        <v>5.6</v>
-      </c>
-      <c r="BD19">
-        <v>5.8</v>
-      </c>
-      <c r="BE19">
-        <v>6.2</v>
-      </c>
-      <c r="BF19">
-        <v>32</v>
-      </c>
-      <c r="BG19">
-        <v>5.4</v>
-      </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
-      <c r="BI19">
-        <v>1.79</v>
-      </c>
-      <c r="BJ19">
-        <v>14.5</v>
-      </c>
-      <c r="BK19">
-        <v>1.59</v>
-      </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
-        <v>1.79</v>
-      </c>
-      <c r="BN19">
-        <v>8</v>
-      </c>
-      <c r="BO19">
-        <v>4.5</v>
-      </c>
-      <c r="BP19">
-        <v>36</v>
-      </c>
-      <c r="BQ19">
-        <v>1.71</v>
-      </c>
-      <c r="BR19">
-        <v>1000</v>
-      </c>
-      <c r="BS19">
-        <v>1.74</v>
-      </c>
-      <c r="BT19">
-        <v>7.6</v>
-      </c>
-      <c r="BU19">
-        <v>3.8</v>
-      </c>
-      <c r="BV19">
-        <v>30</v>
-      </c>
-      <c r="BW19">
-        <v>1.69</v>
-      </c>
-      <c r="BX19">
-        <v>1000</v>
-      </c>
-      <c r="BY19">
-        <v>1.74</v>
-      </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB19" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="E20" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="F20">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="G20">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="H20">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="I20">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J20">
         <v>3.9</v>
       </c>
       <c r="K20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L20">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M20">
         <v>1.03</v>
@@ -5500,22 +5587,22 @@
         <v>5.5</v>
       </c>
       <c r="O20">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P20">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q20">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R20">
         <v>1.62</v>
       </c>
       <c r="S20">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="T20">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="U20">
         <v>2.64</v>
@@ -5524,10 +5611,10 @@
         <v>1.67</v>
       </c>
       <c r="W20">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="X20">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y20">
         <v>19</v>
@@ -5536,7 +5623,7 @@
         <v>29</v>
       </c>
       <c r="AA20">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB20">
         <v>22</v>
@@ -5554,7 +5641,7 @@
         <v>32</v>
       </c>
       <c r="AG20">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH20">
         <v>18</v>
@@ -5566,7 +5653,7 @@
         <v>55</v>
       </c>
       <c r="AK20">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL20">
         <v>40</v>
@@ -5581,19 +5668,19 @@
         <v>16</v>
       </c>
       <c r="AP20">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AQ20">
         <v>13.5</v>
       </c>
       <c r="AR20">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS20">
-        <v>4.4</v>
+        <v>24</v>
       </c>
       <c r="AT20">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU20">
         <v>8.800000000000001</v>
@@ -5605,7 +5692,7 @@
         <v>16.5</v>
       </c>
       <c r="AX20">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AY20">
         <v>12</v>
@@ -5632,43 +5719,43 @@
         <v>12.5</v>
       </c>
       <c r="BG20">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH20">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI20">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ20">
         <v>8.6</v>
       </c>
       <c r="BK20">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN20">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO20">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BT20">
         <v>5.9</v>
@@ -5680,22 +5767,22 @@
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ20">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA20">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB20" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5703,34 +5790,34 @@
         <v>97</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E21" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="F21">
         <v>2.32</v>
       </c>
       <c r="G21">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H21">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I21">
+        <v>3.3</v>
+      </c>
+      <c r="J21">
         <v>3.5</v>
       </c>
-      <c r="J21">
-        <v>3.55</v>
-      </c>
       <c r="K21">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5745,7 +5832,7 @@
         <v>1.23</v>
       </c>
       <c r="P21">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q21">
         <v>1.76</v>
@@ -5766,7 +5853,7 @@
         <v>1.4</v>
       </c>
       <c r="W21">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -5937,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5945,16 +6032,16 @@
         <v>98</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E22" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -6179,7 +6266,7 @@
         <v>1.04</v>
       </c>
       <c r="CB22" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6187,16 +6274,16 @@
         <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E23" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="F23">
         <v>1.76</v>
@@ -6211,13 +6298,13 @@
         <v>5.8</v>
       </c>
       <c r="J23">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K23">
         <v>4.1</v>
       </c>
       <c r="L23">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="M23">
         <v>1.07</v>
@@ -6232,7 +6319,7 @@
         <v>1.87</v>
       </c>
       <c r="Q23">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R23">
         <v>1.32</v>
@@ -6241,7 +6328,7 @@
         <v>3.45</v>
       </c>
       <c r="T23">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U23">
         <v>1.94</v>
@@ -6265,7 +6352,7 @@
         <v>150</v>
       </c>
       <c r="AB23">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC23">
         <v>9.199999999999999</v>
@@ -6277,7 +6364,7 @@
         <v>75</v>
       </c>
       <c r="AF23">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG23">
         <v>11</v>
@@ -6304,7 +6391,7 @@
         <v>12.5</v>
       </c>
       <c r="AO23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP23">
         <v>12.5</v>
@@ -6316,7 +6403,7 @@
         <v>32</v>
       </c>
       <c r="AS23">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT23">
         <v>7.4</v>
@@ -6328,7 +6415,7 @@
         <v>17.5</v>
       </c>
       <c r="AW23">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX23">
         <v>9.4</v>
@@ -6340,7 +6427,7 @@
         <v>16.5</v>
       </c>
       <c r="BA23">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB23">
         <v>17</v>
@@ -6349,79 +6436,79 @@
         <v>16</v>
       </c>
       <c r="BD23">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BE23">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF23">
         <v>8.6</v>
       </c>
       <c r="BG23">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI23">
-        <v>1.84</v>
+        <v>2.74</v>
       </c>
       <c r="BJ23">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BK23">
-        <v>1.63</v>
+        <v>5.3</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.84</v>
+        <v>9.6</v>
       </c>
       <c r="BN23">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BO23">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="BP23">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BQ23">
-        <v>1.67</v>
+        <v>5.7</v>
       </c>
       <c r="BR23">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.76</v>
+        <v>7.6</v>
       </c>
       <c r="BT23">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU23">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.79</v>
+        <v>8.4</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ23">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="CA23">
-        <v>1.74</v>
+        <v>7.2</v>
       </c>
       <c r="CB23" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6429,19 +6516,19 @@
         <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D24" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="E24" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="F24">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="G24">
         <v>3.45</v>
@@ -6450,16 +6537,16 @@
         <v>2.4</v>
       </c>
       <c r="I24">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="J24">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K24">
         <v>3.6</v>
       </c>
       <c r="L24">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="M24">
         <v>1.08</v>
@@ -6489,7 +6576,7 @@
         <v>2.04</v>
       </c>
       <c r="V24">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W24">
         <v>1.41</v>
@@ -6606,548 +6693,548 @@
         <v>3.25</v>
       </c>
       <c r="BI24">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ24">
         <v>9.800000000000001</v>
       </c>
       <c r="BK24">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BN24">
         <v>6.4</v>
       </c>
       <c r="BO24">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP24">
         <v>27</v>
       </c>
       <c r="BQ24">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BR24">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT24">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BU24">
         <v>4.2</v>
       </c>
       <c r="BV24">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BW24">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY24">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ24">
         <v>32</v>
       </c>
       <c r="CA24">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB24" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D25" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="E25" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="F25">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="G25">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="H25">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="I25">
-        <v>7.8</v>
+        <v>990</v>
       </c>
       <c r="J25">
-        <v>3.85</v>
+        <v>2.18</v>
       </c>
       <c r="K25">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L25">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N25">
-        <v>3.65</v>
+        <v>1.32</v>
       </c>
       <c r="O25">
+        <v>1.15</v>
+      </c>
+      <c r="P25">
         <v>1.31</v>
       </c>
-      <c r="P25">
-        <v>1.92</v>
-      </c>
       <c r="Q25">
-        <v>1.9</v>
+        <v>1.15</v>
       </c>
       <c r="R25">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="S25">
-        <v>3.35</v>
+        <v>1.16</v>
       </c>
       <c r="T25">
-        <v>1.91</v>
+        <v>1.11</v>
       </c>
       <c r="U25">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="V25">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W25">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="X25">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y25">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z25">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA25">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB25">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC25">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD25">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE25">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF25">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG25">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH25">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI25">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AK25">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL25">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM25">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN25">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO25">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP25">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AR25">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AS25">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU25">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV25">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AW25">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG25">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH25">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BN25">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BP25">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT25">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="CA25">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E26" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="F26">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="G26">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="H26">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="I26">
-        <v>990</v>
+        <v>6.8</v>
       </c>
       <c r="J26">
-        <v>2.14</v>
+        <v>3.85</v>
       </c>
       <c r="K26">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L26">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M26">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N26">
-        <v>1.32</v>
+        <v>3.7</v>
       </c>
       <c r="O26">
+        <v>1.31</v>
+      </c>
+      <c r="P26">
+        <v>1.93</v>
+      </c>
+      <c r="Q26">
+        <v>1.76</v>
+      </c>
+      <c r="R26">
+        <v>1.36</v>
+      </c>
+      <c r="S26">
+        <v>3.3</v>
+      </c>
+      <c r="T26">
+        <v>1.89</v>
+      </c>
+      <c r="U26">
+        <v>1.94</v>
+      </c>
+      <c r="V26">
         <v>1.15</v>
       </c>
-      <c r="P26">
-        <v>1.31</v>
-      </c>
-      <c r="Q26">
-        <v>1.15</v>
-      </c>
-      <c r="R26">
-        <v>1.26</v>
-      </c>
-      <c r="S26">
-        <v>1.16</v>
-      </c>
-      <c r="T26">
-        <v>1.11</v>
-      </c>
-      <c r="U26">
-        <v>1.11</v>
-      </c>
-      <c r="V26">
-        <v>1.01</v>
-      </c>
       <c r="W26">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="X26">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y26">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z26">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB26">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE26">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF26">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG26">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH26">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI26">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ26">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL26">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM26">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN26">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP26">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ26">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR26">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS26">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT26">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU26">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV26">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW26">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX26">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY26">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AZ26">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA26">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB26">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BC26">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD26">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE26">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF26">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG26">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH26">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI26">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BJ26">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK26">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BN26">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO26">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ26">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU26">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ26">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CA26">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="CB26" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7155,16 +7242,16 @@
         <v>98</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="E27" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -7389,7 +7476,2427 @@
         <v>1.04</v>
       </c>
       <c r="CB27" t="s">
-        <v>169</v>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" t="s">
+        <v>152</v>
+      </c>
+      <c r="E28" t="s">
+        <v>188</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28">
+        <v>4.7</v>
+      </c>
+      <c r="H28">
+        <v>2</v>
+      </c>
+      <c r="I28">
+        <v>2.16</v>
+      </c>
+      <c r="J28">
+        <v>3.1</v>
+      </c>
+      <c r="K28">
+        <v>3.65</v>
+      </c>
+      <c r="L28">
+        <v>1.46</v>
+      </c>
+      <c r="M28">
+        <v>1.09</v>
+      </c>
+      <c r="N28">
+        <v>3</v>
+      </c>
+      <c r="O28">
+        <v>1.42</v>
+      </c>
+      <c r="P28">
+        <v>1.71</v>
+      </c>
+      <c r="Q28">
+        <v>2.3</v>
+      </c>
+      <c r="R28">
+        <v>1.27</v>
+      </c>
+      <c r="S28">
+        <v>4.2</v>
+      </c>
+      <c r="T28">
+        <v>1.96</v>
+      </c>
+      <c r="U28">
+        <v>1.86</v>
+      </c>
+      <c r="V28">
+        <v>1.87</v>
+      </c>
+      <c r="W28">
+        <v>1.27</v>
+      </c>
+      <c r="X28">
+        <v>13</v>
+      </c>
+      <c r="Y28">
+        <v>9</v>
+      </c>
+      <c r="Z28">
+        <v>14.5</v>
+      </c>
+      <c r="AA28">
+        <v>30</v>
+      </c>
+      <c r="AB28">
+        <v>15</v>
+      </c>
+      <c r="AC28">
+        <v>9</v>
+      </c>
+      <c r="AD28">
+        <v>13</v>
+      </c>
+      <c r="AE28">
+        <v>28</v>
+      </c>
+      <c r="AF28">
+        <v>34</v>
+      </c>
+      <c r="AG28">
+        <v>23</v>
+      </c>
+      <c r="AH28">
+        <v>24</v>
+      </c>
+      <c r="AI28">
+        <v>50</v>
+      </c>
+      <c r="AJ28">
+        <v>120</v>
+      </c>
+      <c r="AK28">
+        <v>70</v>
+      </c>
+      <c r="AL28">
+        <v>90</v>
+      </c>
+      <c r="AM28">
+        <v>170</v>
+      </c>
+      <c r="AN28">
+        <v>110</v>
+      </c>
+      <c r="AO28">
+        <v>25</v>
+      </c>
+      <c r="AP28">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ28">
+        <v>6.6</v>
+      </c>
+      <c r="AR28">
+        <v>9</v>
+      </c>
+      <c r="AS28">
+        <v>4.3</v>
+      </c>
+      <c r="AT28">
+        <v>10.5</v>
+      </c>
+      <c r="AU28">
+        <v>6.4</v>
+      </c>
+      <c r="AV28">
+        <v>9.6</v>
+      </c>
+      <c r="AW28">
+        <v>19</v>
+      </c>
+      <c r="AX28">
+        <v>4.4</v>
+      </c>
+      <c r="AY28">
+        <v>12.5</v>
+      </c>
+      <c r="AZ28">
+        <v>16</v>
+      </c>
+      <c r="BA28">
+        <v>4.6</v>
+      </c>
+      <c r="BB28">
+        <v>4.9</v>
+      </c>
+      <c r="BC28">
+        <v>4.8</v>
+      </c>
+      <c r="BD28">
+        <v>4.8</v>
+      </c>
+      <c r="BE28">
+        <v>5</v>
+      </c>
+      <c r="BF28">
+        <v>4.8</v>
+      </c>
+      <c r="BG28">
+        <v>17</v>
+      </c>
+      <c r="BH28">
+        <v>3.15</v>
+      </c>
+      <c r="BI28">
+        <v>2.46</v>
+      </c>
+      <c r="BJ28">
+        <v>11</v>
+      </c>
+      <c r="BK28">
+        <v>5.5</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>10</v>
+      </c>
+      <c r="BN28">
+        <v>7.8</v>
+      </c>
+      <c r="BO28">
+        <v>5.6</v>
+      </c>
+      <c r="BP28">
+        <v>1000</v>
+      </c>
+      <c r="BQ28">
+        <v>8.6</v>
+      </c>
+      <c r="BR28">
+        <v>1000</v>
+      </c>
+      <c r="BS28">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT28">
+        <v>4.8</v>
+      </c>
+      <c r="BU28">
+        <v>3.6</v>
+      </c>
+      <c r="BV28">
+        <v>16.5</v>
+      </c>
+      <c r="BW28">
+        <v>6.6</v>
+      </c>
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
+        <v>8.4</v>
+      </c>
+      <c r="BZ28">
+        <v>1000</v>
+      </c>
+      <c r="CA28">
+        <v>8.4</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" t="s">
+        <v>153</v>
+      </c>
+      <c r="E29" t="s">
+        <v>189</v>
+      </c>
+      <c r="F29">
+        <v>1.3</v>
+      </c>
+      <c r="G29">
+        <v>1.37</v>
+      </c>
+      <c r="H29">
+        <v>8</v>
+      </c>
+      <c r="I29">
+        <v>16</v>
+      </c>
+      <c r="J29">
+        <v>4.8</v>
+      </c>
+      <c r="K29">
+        <v>6.4</v>
+      </c>
+      <c r="L29">
+        <v>1.26</v>
+      </c>
+      <c r="M29">
+        <v>1.04</v>
+      </c>
+      <c r="N29">
+        <v>4.3</v>
+      </c>
+      <c r="O29">
+        <v>1.22</v>
+      </c>
+      <c r="P29">
+        <v>2.22</v>
+      </c>
+      <c r="Q29">
+        <v>1.6</v>
+      </c>
+      <c r="R29">
+        <v>1.5</v>
+      </c>
+      <c r="S29">
+        <v>2.42</v>
+      </c>
+      <c r="T29">
+        <v>2.08</v>
+      </c>
+      <c r="U29">
+        <v>1.75</v>
+      </c>
+      <c r="V29">
+        <v>1.06</v>
+      </c>
+      <c r="W29">
+        <v>3.7</v>
+      </c>
+      <c r="X29">
+        <v>27</v>
+      </c>
+      <c r="Y29">
+        <v>46</v>
+      </c>
+      <c r="Z29">
+        <v>140</v>
+      </c>
+      <c r="AA29">
+        <v>610</v>
+      </c>
+      <c r="AB29">
+        <v>10.5</v>
+      </c>
+      <c r="AC29">
+        <v>16.5</v>
+      </c>
+      <c r="AD29">
+        <v>55</v>
+      </c>
+      <c r="AE29">
+        <v>260</v>
+      </c>
+      <c r="AF29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG29">
+        <v>13</v>
+      </c>
+      <c r="AH29">
+        <v>38</v>
+      </c>
+      <c r="AI29">
+        <v>200</v>
+      </c>
+      <c r="AJ29">
+        <v>12.5</v>
+      </c>
+      <c r="AK29">
+        <v>18</v>
+      </c>
+      <c r="AL29">
+        <v>50</v>
+      </c>
+      <c r="AM29">
+        <v>220</v>
+      </c>
+      <c r="AN29">
+        <v>6.2</v>
+      </c>
+      <c r="AO29">
+        <v>360</v>
+      </c>
+      <c r="AP29">
+        <v>3.85</v>
+      </c>
+      <c r="AQ29">
+        <v>4.1</v>
+      </c>
+      <c r="AR29">
+        <v>4.4</v>
+      </c>
+      <c r="AS29">
+        <v>4.5</v>
+      </c>
+      <c r="AT29">
+        <v>3.15</v>
+      </c>
+      <c r="AU29">
+        <v>3.55</v>
+      </c>
+      <c r="AV29">
+        <v>4.1</v>
+      </c>
+      <c r="AW29">
+        <v>4.4</v>
+      </c>
+      <c r="AX29">
+        <v>3.1</v>
+      </c>
+      <c r="AY29">
+        <v>3.35</v>
+      </c>
+      <c r="AZ29">
+        <v>4</v>
+      </c>
+      <c r="BA29">
+        <v>4.4</v>
+      </c>
+      <c r="BB29">
+        <v>3.3</v>
+      </c>
+      <c r="BC29">
+        <v>3.6</v>
+      </c>
+      <c r="BD29">
+        <v>4.1</v>
+      </c>
+      <c r="BE29">
+        <v>4.4</v>
+      </c>
+      <c r="BF29">
+        <v>2.62</v>
+      </c>
+      <c r="BG29">
+        <v>4.4</v>
+      </c>
+      <c r="BH29">
+        <v>4.2</v>
+      </c>
+      <c r="BI29">
+        <v>3.15</v>
+      </c>
+      <c r="BJ29">
+        <v>13</v>
+      </c>
+      <c r="BK29">
+        <v>6.4</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>1.71</v>
+      </c>
+      <c r="BN29">
+        <v>3.8</v>
+      </c>
+      <c r="BO29">
+        <v>2.96</v>
+      </c>
+      <c r="BP29">
+        <v>7.6</v>
+      </c>
+      <c r="BQ29">
+        <v>4.7</v>
+      </c>
+      <c r="BR29">
+        <v>25</v>
+      </c>
+      <c r="BS29">
+        <v>8.4</v>
+      </c>
+      <c r="BT29">
+        <v>15</v>
+      </c>
+      <c r="BU29">
+        <v>6.8</v>
+      </c>
+      <c r="BV29">
+        <v>1000</v>
+      </c>
+      <c r="BW29">
+        <v>1.7</v>
+      </c>
+      <c r="BX29">
+        <v>1000</v>
+      </c>
+      <c r="BY29">
+        <v>1.7</v>
+      </c>
+      <c r="BZ29">
+        <v>12.5</v>
+      </c>
+      <c r="CA29">
+        <v>6.2</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" t="s">
+        <v>124</v>
+      </c>
+      <c r="D30" t="s">
+        <v>154</v>
+      </c>
+      <c r="E30" t="s">
+        <v>190</v>
+      </c>
+      <c r="F30">
+        <v>1.94</v>
+      </c>
+      <c r="G30">
+        <v>2.12</v>
+      </c>
+      <c r="H30">
+        <v>4.1</v>
+      </c>
+      <c r="I30">
+        <v>4.9</v>
+      </c>
+      <c r="J30">
+        <v>3.3</v>
+      </c>
+      <c r="K30">
+        <v>3.85</v>
+      </c>
+      <c r="L30">
+        <v>1.38</v>
+      </c>
+      <c r="M30">
+        <v>1.08</v>
+      </c>
+      <c r="N30">
+        <v>3.2</v>
+      </c>
+      <c r="O30">
+        <v>1.37</v>
+      </c>
+      <c r="P30">
+        <v>1.74</v>
+      </c>
+      <c r="Q30">
+        <v>2.08</v>
+      </c>
+      <c r="R30">
+        <v>1.28</v>
+      </c>
+      <c r="S30">
+        <v>3.75</v>
+      </c>
+      <c r="T30">
+        <v>1.86</v>
+      </c>
+      <c r="U30">
+        <v>1.92</v>
+      </c>
+      <c r="V30">
+        <v>1.26</v>
+      </c>
+      <c r="W30">
+        <v>1.89</v>
+      </c>
+      <c r="X30">
+        <v>15</v>
+      </c>
+      <c r="Y30">
+        <v>15</v>
+      </c>
+      <c r="Z30">
+        <v>40</v>
+      </c>
+      <c r="AA30">
+        <v>130</v>
+      </c>
+      <c r="AB30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC30">
+        <v>9.6</v>
+      </c>
+      <c r="AD30">
+        <v>22</v>
+      </c>
+      <c r="AE30">
+        <v>80</v>
+      </c>
+      <c r="AF30">
+        <v>14.5</v>
+      </c>
+      <c r="AG30">
+        <v>13</v>
+      </c>
+      <c r="AH30">
+        <v>25</v>
+      </c>
+      <c r="AI30">
+        <v>90</v>
+      </c>
+      <c r="AJ30">
+        <v>30</v>
+      </c>
+      <c r="AK30">
+        <v>29</v>
+      </c>
+      <c r="AL30">
+        <v>55</v>
+      </c>
+      <c r="AM30">
+        <v>160</v>
+      </c>
+      <c r="AN30">
+        <v>22</v>
+      </c>
+      <c r="AO30">
+        <v>95</v>
+      </c>
+      <c r="AP30">
+        <v>9</v>
+      </c>
+      <c r="AQ30">
+        <v>10</v>
+      </c>
+      <c r="AR30">
+        <v>4</v>
+      </c>
+      <c r="AS30">
+        <v>4.3</v>
+      </c>
+      <c r="AT30">
+        <v>7</v>
+      </c>
+      <c r="AU30">
+        <v>6</v>
+      </c>
+      <c r="AV30">
+        <v>15</v>
+      </c>
+      <c r="AW30">
+        <v>4.2</v>
+      </c>
+      <c r="AX30">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY30">
+        <v>7.8</v>
+      </c>
+      <c r="AZ30">
+        <v>14.5</v>
+      </c>
+      <c r="BA30">
+        <v>4.2</v>
+      </c>
+      <c r="BB30">
+        <v>20</v>
+      </c>
+      <c r="BC30">
+        <v>17</v>
+      </c>
+      <c r="BD30">
+        <v>4.1</v>
+      </c>
+      <c r="BE30">
+        <v>4.3</v>
+      </c>
+      <c r="BF30">
+        <v>13</v>
+      </c>
+      <c r="BG30">
+        <v>4.2</v>
+      </c>
+      <c r="BH30">
+        <v>3.3</v>
+      </c>
+      <c r="BI30">
+        <v>2.82</v>
+      </c>
+      <c r="BJ30">
+        <v>11</v>
+      </c>
+      <c r="BK30">
+        <v>5.2</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>9.4</v>
+      </c>
+      <c r="BN30">
+        <v>4.8</v>
+      </c>
+      <c r="BO30">
+        <v>3.55</v>
+      </c>
+      <c r="BP30">
+        <v>15.5</v>
+      </c>
+      <c r="BQ30">
+        <v>6</v>
+      </c>
+      <c r="BR30">
+        <v>34</v>
+      </c>
+      <c r="BS30">
+        <v>7.6</v>
+      </c>
+      <c r="BT30">
+        <v>8</v>
+      </c>
+      <c r="BU30">
+        <v>5.7</v>
+      </c>
+      <c r="BV30">
+        <v>42</v>
+      </c>
+      <c r="BW30">
+        <v>8</v>
+      </c>
+      <c r="BX30">
+        <v>55</v>
+      </c>
+      <c r="BY30">
+        <v>8.4</v>
+      </c>
+      <c r="BZ30">
+        <v>32</v>
+      </c>
+      <c r="CA30">
+        <v>7.6</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>101</v>
+      </c>
+      <c r="B31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" t="s">
+        <v>155</v>
+      </c>
+      <c r="E31" t="s">
+        <v>191</v>
+      </c>
+      <c r="F31">
+        <v>1.98</v>
+      </c>
+      <c r="G31">
+        <v>2.18</v>
+      </c>
+      <c r="H31">
+        <v>4</v>
+      </c>
+      <c r="I31">
+        <v>4.9</v>
+      </c>
+      <c r="J31">
+        <v>3.25</v>
+      </c>
+      <c r="K31">
+        <v>3.6</v>
+      </c>
+      <c r="L31">
+        <v>1.01</v>
+      </c>
+      <c r="M31">
+        <v>1.09</v>
+      </c>
+      <c r="N31">
+        <v>3.1</v>
+      </c>
+      <c r="O31">
+        <v>1.4</v>
+      </c>
+      <c r="P31">
+        <v>1.71</v>
+      </c>
+      <c r="Q31">
+        <v>2.12</v>
+      </c>
+      <c r="R31">
+        <v>1.26</v>
+      </c>
+      <c r="S31">
+        <v>4.1</v>
+      </c>
+      <c r="T31">
+        <v>1.91</v>
+      </c>
+      <c r="U31">
+        <v>1.91</v>
+      </c>
+      <c r="V31">
+        <v>1.27</v>
+      </c>
+      <c r="W31">
+        <v>1.84</v>
+      </c>
+      <c r="X31">
+        <v>13</v>
+      </c>
+      <c r="Y31">
+        <v>14</v>
+      </c>
+      <c r="Z31">
+        <v>36</v>
+      </c>
+      <c r="AA31">
+        <v>150</v>
+      </c>
+      <c r="AB31">
+        <v>8.4</v>
+      </c>
+      <c r="AC31">
+        <v>8</v>
+      </c>
+      <c r="AD31">
+        <v>18.5</v>
+      </c>
+      <c r="AE31">
+        <v>65</v>
+      </c>
+      <c r="AF31">
+        <v>13</v>
+      </c>
+      <c r="AG31">
+        <v>11.5</v>
+      </c>
+      <c r="AH31">
+        <v>21</v>
+      </c>
+      <c r="AI31">
+        <v>75</v>
+      </c>
+      <c r="AJ31">
+        <v>28</v>
+      </c>
+      <c r="AK31">
+        <v>27</v>
+      </c>
+      <c r="AL31">
+        <v>50</v>
+      </c>
+      <c r="AM31">
+        <v>150</v>
+      </c>
+      <c r="AN31">
+        <v>22</v>
+      </c>
+      <c r="AO31">
+        <v>110</v>
+      </c>
+      <c r="AP31">
+        <v>9.6</v>
+      </c>
+      <c r="AQ31">
+        <v>10</v>
+      </c>
+      <c r="AR31">
+        <v>6.6</v>
+      </c>
+      <c r="AS31">
+        <v>7.8</v>
+      </c>
+      <c r="AT31">
+        <v>6.8</v>
+      </c>
+      <c r="AU31">
+        <v>6</v>
+      </c>
+      <c r="AV31">
+        <v>13.5</v>
+      </c>
+      <c r="AW31">
+        <v>7.2</v>
+      </c>
+      <c r="AX31">
+        <v>10</v>
+      </c>
+      <c r="AY31">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ31">
+        <v>17</v>
+      </c>
+      <c r="BA31">
+        <v>7.4</v>
+      </c>
+      <c r="BB31">
+        <v>6.2</v>
+      </c>
+      <c r="BC31">
+        <v>21</v>
+      </c>
+      <c r="BD31">
+        <v>7</v>
+      </c>
+      <c r="BE31">
+        <v>7.8</v>
+      </c>
+      <c r="BF31">
+        <v>15.5</v>
+      </c>
+      <c r="BG31">
+        <v>7.6</v>
+      </c>
+      <c r="BH31">
+        <v>1000</v>
+      </c>
+      <c r="BI31">
+        <v>1.04</v>
+      </c>
+      <c r="BJ31">
+        <v>1000</v>
+      </c>
+      <c r="BK31">
+        <v>1.04</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>1.04</v>
+      </c>
+      <c r="BN31">
+        <v>1000</v>
+      </c>
+      <c r="BO31">
+        <v>1.04</v>
+      </c>
+      <c r="BP31">
+        <v>1000</v>
+      </c>
+      <c r="BQ31">
+        <v>1.04</v>
+      </c>
+      <c r="BR31">
+        <v>1000</v>
+      </c>
+      <c r="BS31">
+        <v>1.04</v>
+      </c>
+      <c r="BT31">
+        <v>1000</v>
+      </c>
+      <c r="BU31">
+        <v>1.04</v>
+      </c>
+      <c r="BV31">
+        <v>1000</v>
+      </c>
+      <c r="BW31">
+        <v>1.04</v>
+      </c>
+      <c r="BX31">
+        <v>1000</v>
+      </c>
+      <c r="BY31">
+        <v>1.04</v>
+      </c>
+      <c r="BZ31">
+        <v>1000</v>
+      </c>
+      <c r="CA31">
+        <v>1.04</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>101</v>
+      </c>
+      <c r="B32" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" t="s">
+        <v>156</v>
+      </c>
+      <c r="E32" t="s">
+        <v>192</v>
+      </c>
+      <c r="F32">
+        <v>1.85</v>
+      </c>
+      <c r="G32">
+        <v>2.24</v>
+      </c>
+      <c r="H32">
+        <v>3.85</v>
+      </c>
+      <c r="I32">
+        <v>6</v>
+      </c>
+      <c r="J32">
+        <v>3.25</v>
+      </c>
+      <c r="K32">
+        <v>950</v>
+      </c>
+      <c r="L32">
+        <v>1.01</v>
+      </c>
+      <c r="M32">
+        <v>1.01</v>
+      </c>
+      <c r="N32">
+        <v>2.28</v>
+      </c>
+      <c r="O32">
+        <v>1.48</v>
+      </c>
+      <c r="P32">
+        <v>1.43</v>
+      </c>
+      <c r="Q32">
+        <v>2.06</v>
+      </c>
+      <c r="R32">
+        <v>1.17</v>
+      </c>
+      <c r="S32">
+        <v>4.4</v>
+      </c>
+      <c r="T32">
+        <v>2</v>
+      </c>
+      <c r="U32">
+        <v>1.57</v>
+      </c>
+      <c r="V32">
+        <v>1.2</v>
+      </c>
+      <c r="W32">
+        <v>1.81</v>
+      </c>
+      <c r="X32">
+        <v>1000</v>
+      </c>
+      <c r="Y32">
+        <v>1000</v>
+      </c>
+      <c r="Z32">
+        <v>1000</v>
+      </c>
+      <c r="AA32">
+        <v>1000</v>
+      </c>
+      <c r="AB32">
+        <v>1000</v>
+      </c>
+      <c r="AC32">
+        <v>1000</v>
+      </c>
+      <c r="AD32">
+        <v>1000</v>
+      </c>
+      <c r="AE32">
+        <v>1000</v>
+      </c>
+      <c r="AF32">
+        <v>1000</v>
+      </c>
+      <c r="AG32">
+        <v>1000</v>
+      </c>
+      <c r="AH32">
+        <v>1000</v>
+      </c>
+      <c r="AI32">
+        <v>1000</v>
+      </c>
+      <c r="AJ32">
+        <v>1000</v>
+      </c>
+      <c r="AK32">
+        <v>1000</v>
+      </c>
+      <c r="AL32">
+        <v>1000</v>
+      </c>
+      <c r="AM32">
+        <v>1000</v>
+      </c>
+      <c r="AN32">
+        <v>1000</v>
+      </c>
+      <c r="AO32">
+        <v>1000</v>
+      </c>
+      <c r="AP32">
+        <v>1.01</v>
+      </c>
+      <c r="AQ32">
+        <v>1.01</v>
+      </c>
+      <c r="AR32">
+        <v>1.01</v>
+      </c>
+      <c r="AS32">
+        <v>1.01</v>
+      </c>
+      <c r="AT32">
+        <v>1.01</v>
+      </c>
+      <c r="AU32">
+        <v>1.01</v>
+      </c>
+      <c r="AV32">
+        <v>1.01</v>
+      </c>
+      <c r="AW32">
+        <v>1.01</v>
+      </c>
+      <c r="AX32">
+        <v>1.01</v>
+      </c>
+      <c r="AY32">
+        <v>1.01</v>
+      </c>
+      <c r="AZ32">
+        <v>1.01</v>
+      </c>
+      <c r="BA32">
+        <v>1.01</v>
+      </c>
+      <c r="BB32">
+        <v>1.01</v>
+      </c>
+      <c r="BC32">
+        <v>1.01</v>
+      </c>
+      <c r="BD32">
+        <v>1.01</v>
+      </c>
+      <c r="BE32">
+        <v>1.01</v>
+      </c>
+      <c r="BF32">
+        <v>1.01</v>
+      </c>
+      <c r="BG32">
+        <v>1.01</v>
+      </c>
+      <c r="BH32">
+        <v>1000</v>
+      </c>
+      <c r="BI32">
+        <v>1.04</v>
+      </c>
+      <c r="BJ32">
+        <v>1000</v>
+      </c>
+      <c r="BK32">
+        <v>1.04</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>1.04</v>
+      </c>
+      <c r="BN32">
+        <v>1000</v>
+      </c>
+      <c r="BO32">
+        <v>1.04</v>
+      </c>
+      <c r="BP32">
+        <v>1000</v>
+      </c>
+      <c r="BQ32">
+        <v>1.04</v>
+      </c>
+      <c r="BR32">
+        <v>1000</v>
+      </c>
+      <c r="BS32">
+        <v>1.04</v>
+      </c>
+      <c r="BT32">
+        <v>1000</v>
+      </c>
+      <c r="BU32">
+        <v>1.04</v>
+      </c>
+      <c r="BV32">
+        <v>1000</v>
+      </c>
+      <c r="BW32">
+        <v>1.04</v>
+      </c>
+      <c r="BX32">
+        <v>1000</v>
+      </c>
+      <c r="BY32">
+        <v>1.04</v>
+      </c>
+      <c r="BZ32">
+        <v>1000</v>
+      </c>
+      <c r="CA32">
+        <v>1.04</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" t="s">
+        <v>157</v>
+      </c>
+      <c r="E33" t="s">
+        <v>193</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>1.01</v>
+      </c>
+      <c r="M33">
+        <v>1.04</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>1.14</v>
+      </c>
+      <c r="S33">
+        <v>1.05</v>
+      </c>
+      <c r="T33">
+        <v>1.11</v>
+      </c>
+      <c r="U33">
+        <v>1.11</v>
+      </c>
+      <c r="V33">
+        <v>1.01</v>
+      </c>
+      <c r="W33">
+        <v>1.01</v>
+      </c>
+      <c r="X33">
+        <v>1000</v>
+      </c>
+      <c r="Y33">
+        <v>1000</v>
+      </c>
+      <c r="Z33">
+        <v>1000</v>
+      </c>
+      <c r="AA33">
+        <v>1000</v>
+      </c>
+      <c r="AB33">
+        <v>1000</v>
+      </c>
+      <c r="AC33">
+        <v>1000</v>
+      </c>
+      <c r="AD33">
+        <v>1000</v>
+      </c>
+      <c r="AE33">
+        <v>1000</v>
+      </c>
+      <c r="AF33">
+        <v>1000</v>
+      </c>
+      <c r="AG33">
+        <v>1000</v>
+      </c>
+      <c r="AH33">
+        <v>1000</v>
+      </c>
+      <c r="AI33">
+        <v>1000</v>
+      </c>
+      <c r="AJ33">
+        <v>1000</v>
+      </c>
+      <c r="AK33">
+        <v>1000</v>
+      </c>
+      <c r="AL33">
+        <v>1000</v>
+      </c>
+      <c r="AM33">
+        <v>1000</v>
+      </c>
+      <c r="AN33">
+        <v>1000</v>
+      </c>
+      <c r="AO33">
+        <v>1000</v>
+      </c>
+      <c r="AP33">
+        <v>1.01</v>
+      </c>
+      <c r="AQ33">
+        <v>1.01</v>
+      </c>
+      <c r="AR33">
+        <v>1.01</v>
+      </c>
+      <c r="AS33">
+        <v>1.01</v>
+      </c>
+      <c r="AT33">
+        <v>1.01</v>
+      </c>
+      <c r="AU33">
+        <v>1.01</v>
+      </c>
+      <c r="AV33">
+        <v>1.01</v>
+      </c>
+      <c r="AW33">
+        <v>1.01</v>
+      </c>
+      <c r="AX33">
+        <v>1.01</v>
+      </c>
+      <c r="AY33">
+        <v>1.01</v>
+      </c>
+      <c r="AZ33">
+        <v>1.01</v>
+      </c>
+      <c r="BA33">
+        <v>1.01</v>
+      </c>
+      <c r="BB33">
+        <v>1.01</v>
+      </c>
+      <c r="BC33">
+        <v>1.01</v>
+      </c>
+      <c r="BD33">
+        <v>1.01</v>
+      </c>
+      <c r="BE33">
+        <v>1.01</v>
+      </c>
+      <c r="BF33">
+        <v>1.01</v>
+      </c>
+      <c r="BG33">
+        <v>1.01</v>
+      </c>
+      <c r="BH33">
+        <v>1000</v>
+      </c>
+      <c r="BI33">
+        <v>1.04</v>
+      </c>
+      <c r="BJ33">
+        <v>1000</v>
+      </c>
+      <c r="BK33">
+        <v>1.04</v>
+      </c>
+      <c r="BL33">
+        <v>1000</v>
+      </c>
+      <c r="BM33">
+        <v>1.04</v>
+      </c>
+      <c r="BN33">
+        <v>1000</v>
+      </c>
+      <c r="BO33">
+        <v>1.04</v>
+      </c>
+      <c r="BP33">
+        <v>1000</v>
+      </c>
+      <c r="BQ33">
+        <v>1.04</v>
+      </c>
+      <c r="BR33">
+        <v>1000</v>
+      </c>
+      <c r="BS33">
+        <v>1.04</v>
+      </c>
+      <c r="BT33">
+        <v>1000</v>
+      </c>
+      <c r="BU33">
+        <v>1.04</v>
+      </c>
+      <c r="BV33">
+        <v>1000</v>
+      </c>
+      <c r="BW33">
+        <v>1.04</v>
+      </c>
+      <c r="BX33">
+        <v>1000</v>
+      </c>
+      <c r="BY33">
+        <v>1.04</v>
+      </c>
+      <c r="BZ33">
+        <v>1000</v>
+      </c>
+      <c r="CA33">
+        <v>1.04</v>
+      </c>
+      <c r="CB33" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="34" spans="1:80">
+      <c r="A34" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" t="s">
+        <v>158</v>
+      </c>
+      <c r="E34" t="s">
+        <v>194</v>
+      </c>
+      <c r="F34">
+        <v>1.04</v>
+      </c>
+      <c r="G34">
+        <v>990</v>
+      </c>
+      <c r="H34">
+        <v>1.04</v>
+      </c>
+      <c r="I34">
+        <v>1000</v>
+      </c>
+      <c r="J34">
+        <v>1.08</v>
+      </c>
+      <c r="K34">
+        <v>950</v>
+      </c>
+      <c r="L34">
+        <v>1.01</v>
+      </c>
+      <c r="M34">
+        <v>1.01</v>
+      </c>
+      <c r="N34">
+        <v>1.29</v>
+      </c>
+      <c r="O34">
+        <v>1.31</v>
+      </c>
+      <c r="P34">
+        <v>1.25</v>
+      </c>
+      <c r="Q34">
+        <v>1.31</v>
+      </c>
+      <c r="R34">
+        <v>1.17</v>
+      </c>
+      <c r="S34">
+        <v>1.31</v>
+      </c>
+      <c r="T34">
+        <v>1.11</v>
+      </c>
+      <c r="U34">
+        <v>1.11</v>
+      </c>
+      <c r="V34">
+        <v>1.02</v>
+      </c>
+      <c r="W34">
+        <v>1.02</v>
+      </c>
+      <c r="X34">
+        <v>1000</v>
+      </c>
+      <c r="Y34">
+        <v>1000</v>
+      </c>
+      <c r="Z34">
+        <v>1000</v>
+      </c>
+      <c r="AA34">
+        <v>1000</v>
+      </c>
+      <c r="AB34">
+        <v>1000</v>
+      </c>
+      <c r="AC34">
+        <v>1000</v>
+      </c>
+      <c r="AD34">
+        <v>1000</v>
+      </c>
+      <c r="AE34">
+        <v>1000</v>
+      </c>
+      <c r="AF34">
+        <v>1000</v>
+      </c>
+      <c r="AG34">
+        <v>1000</v>
+      </c>
+      <c r="AH34">
+        <v>1000</v>
+      </c>
+      <c r="AI34">
+        <v>1000</v>
+      </c>
+      <c r="AJ34">
+        <v>1000</v>
+      </c>
+      <c r="AK34">
+        <v>1000</v>
+      </c>
+      <c r="AL34">
+        <v>1000</v>
+      </c>
+      <c r="AM34">
+        <v>1000</v>
+      </c>
+      <c r="AN34">
+        <v>1000</v>
+      </c>
+      <c r="AO34">
+        <v>1000</v>
+      </c>
+      <c r="AP34">
+        <v>1.01</v>
+      </c>
+      <c r="AQ34">
+        <v>1.01</v>
+      </c>
+      <c r="AR34">
+        <v>1.01</v>
+      </c>
+      <c r="AS34">
+        <v>1.01</v>
+      </c>
+      <c r="AT34">
+        <v>1.01</v>
+      </c>
+      <c r="AU34">
+        <v>1.01</v>
+      </c>
+      <c r="AV34">
+        <v>1.01</v>
+      </c>
+      <c r="AW34">
+        <v>1.01</v>
+      </c>
+      <c r="AX34">
+        <v>1.01</v>
+      </c>
+      <c r="AY34">
+        <v>1.01</v>
+      </c>
+      <c r="AZ34">
+        <v>1.01</v>
+      </c>
+      <c r="BA34">
+        <v>1.01</v>
+      </c>
+      <c r="BB34">
+        <v>1.01</v>
+      </c>
+      <c r="BC34">
+        <v>1.01</v>
+      </c>
+      <c r="BD34">
+        <v>1.01</v>
+      </c>
+      <c r="BE34">
+        <v>1.01</v>
+      </c>
+      <c r="BF34">
+        <v>1.01</v>
+      </c>
+      <c r="BG34">
+        <v>1.01</v>
+      </c>
+      <c r="BH34">
+        <v>1000</v>
+      </c>
+      <c r="BI34">
+        <v>1.04</v>
+      </c>
+      <c r="BJ34">
+        <v>1000</v>
+      </c>
+      <c r="BK34">
+        <v>1.04</v>
+      </c>
+      <c r="BL34">
+        <v>1000</v>
+      </c>
+      <c r="BM34">
+        <v>1.04</v>
+      </c>
+      <c r="BN34">
+        <v>1000</v>
+      </c>
+      <c r="BO34">
+        <v>1.04</v>
+      </c>
+      <c r="BP34">
+        <v>1000</v>
+      </c>
+      <c r="BQ34">
+        <v>1.04</v>
+      </c>
+      <c r="BR34">
+        <v>1000</v>
+      </c>
+      <c r="BS34">
+        <v>1.04</v>
+      </c>
+      <c r="BT34">
+        <v>1000</v>
+      </c>
+      <c r="BU34">
+        <v>1.04</v>
+      </c>
+      <c r="BV34">
+        <v>1000</v>
+      </c>
+      <c r="BW34">
+        <v>1.04</v>
+      </c>
+      <c r="BX34">
+        <v>1000</v>
+      </c>
+      <c r="BY34">
+        <v>1.04</v>
+      </c>
+      <c r="BZ34">
+        <v>1000</v>
+      </c>
+      <c r="CA34">
+        <v>1.04</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="35" spans="1:80">
+      <c r="A35" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" t="s">
+        <v>125</v>
+      </c>
+      <c r="D35" t="s">
+        <v>159</v>
+      </c>
+      <c r="E35" t="s">
+        <v>195</v>
+      </c>
+      <c r="F35">
+        <v>3.05</v>
+      </c>
+      <c r="G35">
+        <v>3.65</v>
+      </c>
+      <c r="H35">
+        <v>2.32</v>
+      </c>
+      <c r="I35">
+        <v>2.66</v>
+      </c>
+      <c r="J35">
+        <v>2.94</v>
+      </c>
+      <c r="K35">
+        <v>3.65</v>
+      </c>
+      <c r="L35">
+        <v>1.01</v>
+      </c>
+      <c r="M35">
+        <v>1.01</v>
+      </c>
+      <c r="N35">
+        <v>2.92</v>
+      </c>
+      <c r="O35">
+        <v>1.38</v>
+      </c>
+      <c r="P35">
+        <v>1.69</v>
+      </c>
+      <c r="Q35">
+        <v>2.14</v>
+      </c>
+      <c r="R35">
+        <v>1.2</v>
+      </c>
+      <c r="S35">
+        <v>3.15</v>
+      </c>
+      <c r="T35">
+        <v>1.11</v>
+      </c>
+      <c r="U35">
+        <v>1.11</v>
+      </c>
+      <c r="V35">
+        <v>1.6</v>
+      </c>
+      <c r="W35">
+        <v>1.37</v>
+      </c>
+      <c r="X35">
+        <v>1000</v>
+      </c>
+      <c r="Y35">
+        <v>1000</v>
+      </c>
+      <c r="Z35">
+        <v>1000</v>
+      </c>
+      <c r="AA35">
+        <v>1000</v>
+      </c>
+      <c r="AB35">
+        <v>1000</v>
+      </c>
+      <c r="AC35">
+        <v>1000</v>
+      </c>
+      <c r="AD35">
+        <v>1000</v>
+      </c>
+      <c r="AE35">
+        <v>1000</v>
+      </c>
+      <c r="AF35">
+        <v>1000</v>
+      </c>
+      <c r="AG35">
+        <v>1000</v>
+      </c>
+      <c r="AH35">
+        <v>1000</v>
+      </c>
+      <c r="AI35">
+        <v>1000</v>
+      </c>
+      <c r="AJ35">
+        <v>1000</v>
+      </c>
+      <c r="AK35">
+        <v>1000</v>
+      </c>
+      <c r="AL35">
+        <v>1000</v>
+      </c>
+      <c r="AM35">
+        <v>1000</v>
+      </c>
+      <c r="AN35">
+        <v>1000</v>
+      </c>
+      <c r="AO35">
+        <v>1000</v>
+      </c>
+      <c r="AP35">
+        <v>1.01</v>
+      </c>
+      <c r="AQ35">
+        <v>1.01</v>
+      </c>
+      <c r="AR35">
+        <v>1.01</v>
+      </c>
+      <c r="AS35">
+        <v>1.01</v>
+      </c>
+      <c r="AT35">
+        <v>1.01</v>
+      </c>
+      <c r="AU35">
+        <v>1.01</v>
+      </c>
+      <c r="AV35">
+        <v>1.01</v>
+      </c>
+      <c r="AW35">
+        <v>1.01</v>
+      </c>
+      <c r="AX35">
+        <v>1.01</v>
+      </c>
+      <c r="AY35">
+        <v>1.01</v>
+      </c>
+      <c r="AZ35">
+        <v>1.01</v>
+      </c>
+      <c r="BA35">
+        <v>1.01</v>
+      </c>
+      <c r="BB35">
+        <v>1.01</v>
+      </c>
+      <c r="BC35">
+        <v>1.01</v>
+      </c>
+      <c r="BD35">
+        <v>1.01</v>
+      </c>
+      <c r="BE35">
+        <v>1.01</v>
+      </c>
+      <c r="BF35">
+        <v>1.01</v>
+      </c>
+      <c r="BG35">
+        <v>1.01</v>
+      </c>
+      <c r="BH35">
+        <v>3.7</v>
+      </c>
+      <c r="BI35">
+        <v>2.4</v>
+      </c>
+      <c r="BJ35">
+        <v>1000</v>
+      </c>
+      <c r="BK35">
+        <v>1.38</v>
+      </c>
+      <c r="BL35">
+        <v>1000</v>
+      </c>
+      <c r="BM35">
+        <v>1.38</v>
+      </c>
+      <c r="BN35">
+        <v>1000</v>
+      </c>
+      <c r="BO35">
+        <v>1.38</v>
+      </c>
+      <c r="BP35">
+        <v>1000</v>
+      </c>
+      <c r="BQ35">
+        <v>1.38</v>
+      </c>
+      <c r="BR35">
+        <v>1000</v>
+      </c>
+      <c r="BS35">
+        <v>1.38</v>
+      </c>
+      <c r="BT35">
+        <v>1000</v>
+      </c>
+      <c r="BU35">
+        <v>1.38</v>
+      </c>
+      <c r="BV35">
+        <v>1000</v>
+      </c>
+      <c r="BW35">
+        <v>1.38</v>
+      </c>
+      <c r="BX35">
+        <v>1000</v>
+      </c>
+      <c r="BY35">
+        <v>1.38</v>
+      </c>
+      <c r="BZ35">
+        <v>1000</v>
+      </c>
+      <c r="CA35">
+        <v>1.38</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="36" spans="1:80">
+      <c r="A36" t="s">
+        <v>104</v>
+      </c>
+      <c r="B36" t="s">
+        <v>105</v>
+      </c>
+      <c r="C36" t="s">
+        <v>125</v>
+      </c>
+      <c r="D36" t="s">
+        <v>160</v>
+      </c>
+      <c r="E36" t="s">
+        <v>196</v>
+      </c>
+      <c r="F36">
+        <v>1.84</v>
+      </c>
+      <c r="G36">
+        <v>2.08</v>
+      </c>
+      <c r="H36">
+        <v>4</v>
+      </c>
+      <c r="I36">
+        <v>5.1</v>
+      </c>
+      <c r="J36">
+        <v>3.5</v>
+      </c>
+      <c r="K36">
+        <v>4.1</v>
+      </c>
+      <c r="L36">
+        <v>1.31</v>
+      </c>
+      <c r="M36">
+        <v>1.06</v>
+      </c>
+      <c r="N36">
+        <v>3.75</v>
+      </c>
+      <c r="O36">
+        <v>1.28</v>
+      </c>
+      <c r="P36">
+        <v>1.96</v>
+      </c>
+      <c r="Q36">
+        <v>1.83</v>
+      </c>
+      <c r="R36">
+        <v>1.37</v>
+      </c>
+      <c r="S36">
+        <v>3.1</v>
+      </c>
+      <c r="T36">
+        <v>1.73</v>
+      </c>
+      <c r="U36">
+        <v>2.08</v>
+      </c>
+      <c r="V36">
+        <v>1.25</v>
+      </c>
+      <c r="W36">
+        <v>1.94</v>
+      </c>
+      <c r="X36">
+        <v>19.5</v>
+      </c>
+      <c r="Y36">
+        <v>20</v>
+      </c>
+      <c r="Z36">
+        <v>42</v>
+      </c>
+      <c r="AA36">
+        <v>120</v>
+      </c>
+      <c r="AB36">
+        <v>11.5</v>
+      </c>
+      <c r="AC36">
+        <v>10.5</v>
+      </c>
+      <c r="AD36">
+        <v>22</v>
+      </c>
+      <c r="AE36">
+        <v>65</v>
+      </c>
+      <c r="AF36">
+        <v>15</v>
+      </c>
+      <c r="AG36">
+        <v>12.5</v>
+      </c>
+      <c r="AH36">
+        <v>22</v>
+      </c>
+      <c r="AI36">
+        <v>70</v>
+      </c>
+      <c r="AJ36">
+        <v>27</v>
+      </c>
+      <c r="AK36">
+        <v>25</v>
+      </c>
+      <c r="AL36">
+        <v>42</v>
+      </c>
+      <c r="AM36">
+        <v>120</v>
+      </c>
+      <c r="AN36">
+        <v>15.5</v>
+      </c>
+      <c r="AO36">
+        <v>70</v>
+      </c>
+      <c r="AP36">
+        <v>3.55</v>
+      </c>
+      <c r="AQ36">
+        <v>3.55</v>
+      </c>
+      <c r="AR36">
+        <v>3.95</v>
+      </c>
+      <c r="AS36">
+        <v>4.2</v>
+      </c>
+      <c r="AT36">
+        <v>3.15</v>
+      </c>
+      <c r="AU36">
+        <v>3.05</v>
+      </c>
+      <c r="AV36">
+        <v>3.6</v>
+      </c>
+      <c r="AW36">
+        <v>4</v>
+      </c>
+      <c r="AX36">
+        <v>3.35</v>
+      </c>
+      <c r="AY36">
+        <v>3.2</v>
+      </c>
+      <c r="AZ36">
+        <v>3.6</v>
+      </c>
+      <c r="BA36">
+        <v>4.1</v>
+      </c>
+      <c r="BB36">
+        <v>3.75</v>
+      </c>
+      <c r="BC36">
+        <v>3.7</v>
+      </c>
+      <c r="BD36">
+        <v>3.95</v>
+      </c>
+      <c r="BE36">
+        <v>4.2</v>
+      </c>
+      <c r="BF36">
+        <v>3.4</v>
+      </c>
+      <c r="BG36">
+        <v>4.1</v>
+      </c>
+      <c r="BH36">
+        <v>3.75</v>
+      </c>
+      <c r="BI36">
+        <v>2.84</v>
+      </c>
+      <c r="BJ36">
+        <v>10</v>
+      </c>
+      <c r="BK36">
+        <v>4.9</v>
+      </c>
+      <c r="BL36">
+        <v>1000</v>
+      </c>
+      <c r="BM36">
+        <v>9</v>
+      </c>
+      <c r="BN36">
+        <v>4.9</v>
+      </c>
+      <c r="BO36">
+        <v>3.65</v>
+      </c>
+      <c r="BP36">
+        <v>14</v>
+      </c>
+      <c r="BQ36">
+        <v>5.7</v>
+      </c>
+      <c r="BR36">
+        <v>28</v>
+      </c>
+      <c r="BS36">
+        <v>7.2</v>
+      </c>
+      <c r="BT36">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU36">
+        <v>5.8</v>
+      </c>
+      <c r="BV36">
+        <v>38</v>
+      </c>
+      <c r="BW36">
+        <v>7.6</v>
+      </c>
+      <c r="BX36">
+        <v>46</v>
+      </c>
+      <c r="BY36">
+        <v>8</v>
+      </c>
+      <c r="BZ36">
+        <v>24</v>
+      </c>
+      <c r="CA36">
+        <v>6.8</v>
+      </c>
+      <c r="CB36" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="37" spans="1:80">
+      <c r="A37" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" t="s">
+        <v>125</v>
+      </c>
+      <c r="D37" t="s">
+        <v>161</v>
+      </c>
+      <c r="E37" t="s">
+        <v>197</v>
+      </c>
+      <c r="F37">
+        <v>2.34</v>
+      </c>
+      <c r="G37">
+        <v>2.5</v>
+      </c>
+      <c r="H37">
+        <v>3.3</v>
+      </c>
+      <c r="I37">
+        <v>3.65</v>
+      </c>
+      <c r="J37">
+        <v>3.15</v>
+      </c>
+      <c r="K37">
+        <v>3.45</v>
+      </c>
+      <c r="L37">
+        <v>1.46</v>
+      </c>
+      <c r="M37">
+        <v>1.09</v>
+      </c>
+      <c r="N37">
+        <v>3.2</v>
+      </c>
+      <c r="O37">
+        <v>1.4</v>
+      </c>
+      <c r="P37">
+        <v>1.75</v>
+      </c>
+      <c r="Q37">
+        <v>2.14</v>
+      </c>
+      <c r="R37">
+        <v>1.29</v>
+      </c>
+      <c r="S37">
+        <v>4</v>
+      </c>
+      <c r="T37">
+        <v>1.86</v>
+      </c>
+      <c r="U37">
+        <v>2.14</v>
+      </c>
+      <c r="V37">
+        <v>1.38</v>
+      </c>
+      <c r="W37">
+        <v>1.66</v>
+      </c>
+      <c r="X37">
+        <v>14.5</v>
+      </c>
+      <c r="Y37">
+        <v>13</v>
+      </c>
+      <c r="Z37">
+        <v>24</v>
+      </c>
+      <c r="AA37">
+        <v>80</v>
+      </c>
+      <c r="AB37">
+        <v>11</v>
+      </c>
+      <c r="AC37">
+        <v>7.6</v>
+      </c>
+      <c r="AD37">
+        <v>16</v>
+      </c>
+      <c r="AE37">
+        <v>46</v>
+      </c>
+      <c r="AF37">
+        <v>18</v>
+      </c>
+      <c r="AG37">
+        <v>14</v>
+      </c>
+      <c r="AH37">
+        <v>23</v>
+      </c>
+      <c r="AI37">
+        <v>65</v>
+      </c>
+      <c r="AJ37">
+        <v>42</v>
+      </c>
+      <c r="AK37">
+        <v>36</v>
+      </c>
+      <c r="AL37">
+        <v>55</v>
+      </c>
+      <c r="AM37">
+        <v>140</v>
+      </c>
+      <c r="AN37">
+        <v>30</v>
+      </c>
+      <c r="AO37">
+        <v>60</v>
+      </c>
+      <c r="AP37">
+        <v>10.5</v>
+      </c>
+      <c r="AQ37">
+        <v>3.9</v>
+      </c>
+      <c r="AR37">
+        <v>4.5</v>
+      </c>
+      <c r="AS37">
+        <v>5.1</v>
+      </c>
+      <c r="AT37">
+        <v>8</v>
+      </c>
+      <c r="AU37">
+        <v>6.6</v>
+      </c>
+      <c r="AV37">
+        <v>4.1</v>
+      </c>
+      <c r="AW37">
+        <v>5</v>
+      </c>
+      <c r="AX37">
+        <v>13</v>
+      </c>
+      <c r="AY37">
+        <v>10</v>
+      </c>
+      <c r="AZ37">
+        <v>16</v>
+      </c>
+      <c r="BA37">
+        <v>5.1</v>
+      </c>
+      <c r="BB37">
+        <v>4.9</v>
+      </c>
+      <c r="BC37">
+        <v>4.8</v>
+      </c>
+      <c r="BD37">
+        <v>5.1</v>
+      </c>
+      <c r="BE37">
+        <v>5.4</v>
+      </c>
+      <c r="BF37">
+        <v>4.7</v>
+      </c>
+      <c r="BG37">
+        <v>5.1</v>
+      </c>
+      <c r="BH37">
+        <v>3.15</v>
+      </c>
+      <c r="BI37">
+        <v>2.88</v>
+      </c>
+      <c r="BJ37">
+        <v>10</v>
+      </c>
+      <c r="BK37">
+        <v>6.2</v>
+      </c>
+      <c r="BL37">
+        <v>1000</v>
+      </c>
+      <c r="BM37">
+        <v>3.9</v>
+      </c>
+      <c r="BN37">
+        <v>5.2</v>
+      </c>
+      <c r="BO37">
+        <v>4</v>
+      </c>
+      <c r="BP37">
+        <v>1000</v>
+      </c>
+      <c r="BQ37">
+        <v>9</v>
+      </c>
+      <c r="BR37">
+        <v>1000</v>
+      </c>
+      <c r="BS37">
+        <v>11.5</v>
+      </c>
+      <c r="BT37">
+        <v>6.4</v>
+      </c>
+      <c r="BU37">
+        <v>4.8</v>
+      </c>
+      <c r="BV37">
+        <v>1000</v>
+      </c>
+      <c r="BW37">
+        <v>10.5</v>
+      </c>
+      <c r="BX37">
+        <v>1000</v>
+      </c>
+      <c r="BY37">
+        <v>12</v>
+      </c>
+      <c r="BZ37">
+        <v>1000</v>
+      </c>
+      <c r="CA37">
+        <v>3.55</v>
+      </c>
+      <c r="CB37" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -676,7 +676,7 @@
     <t>Everton De Vina</t>
   </si>
   <si>
-    <t>2026-07-26 10:45:17</t>
+    <t>2026-07-26 12:56:39</t>
   </si>
 </sst>
 </file>
@@ -1273,16 +1273,16 @@
         <v>1.73</v>
       </c>
       <c r="G2">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K2">
         <v>4.2</v>
@@ -1297,13 +1297,13 @@
         <v>3.8</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P2">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q2">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R2">
         <v>1.37</v>
@@ -1312,7 +1312,7 @@
         <v>3.55</v>
       </c>
       <c r="T2">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U2">
         <v>2</v>
@@ -1321,16 +1321,16 @@
         <v>1.21</v>
       </c>
       <c r="W2">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X2">
         <v>16</v>
       </c>
       <c r="Y2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA2">
         <v>160</v>
@@ -1357,7 +1357,7 @@
         <v>26</v>
       </c>
       <c r="AI2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ2">
         <v>20</v>
@@ -1366,13 +1366,13 @@
         <v>23</v>
       </c>
       <c r="AL2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM2">
         <v>150</v>
       </c>
       <c r="AN2">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO2">
         <v>110</v>
@@ -1381,13 +1381,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR2">
         <v>32</v>
       </c>
       <c r="AS2">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT2">
         <v>7.6</v>
@@ -1396,10 +1396,10 @@
         <v>8</v>
       </c>
       <c r="AV2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX2">
         <v>9.199999999999999</v>
@@ -1408,25 +1408,25 @@
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BB2">
+        <v>15</v>
+      </c>
+      <c r="BC2">
         <v>15.5</v>
       </c>
-      <c r="BC2">
-        <v>14.5</v>
-      </c>
       <c r="BD2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BE2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG2">
         <v>55</v>
@@ -1435,7 +1435,7 @@
         <v>3.45</v>
       </c>
       <c r="BI2">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ2">
         <v>10.5</v>
@@ -1447,7 +1447,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN2">
         <v>4.4</v>
@@ -1456,10 +1456,10 @@
         <v>3.35</v>
       </c>
       <c r="BP2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR2">
         <v>1000</v>
@@ -1468,25 +1468,25 @@
         <v>9.4</v>
       </c>
       <c r="BT2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ2">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
         <v>8.800000000000001</v>
@@ -1512,40 +1512,40 @@
         <v>178</v>
       </c>
       <c r="F3">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="G3">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="H3">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="I3">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="J3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M3">
         <v>1.08</v>
       </c>
       <c r="N3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O3">
         <v>1.38</v>
       </c>
       <c r="P3">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q3">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R3">
         <v>1.32</v>
@@ -1554,94 +1554,94 @@
         <v>3.85</v>
       </c>
       <c r="T3">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U3">
         <v>2.02</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W3">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="X3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y3">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z3">
+        <v>25</v>
+      </c>
+      <c r="AA3">
+        <v>70</v>
+      </c>
+      <c r="AB3">
+        <v>9.4</v>
+      </c>
+      <c r="AC3">
+        <v>7.6</v>
+      </c>
+      <c r="AD3">
+        <v>15</v>
+      </c>
+      <c r="AE3">
+        <v>55</v>
+      </c>
+      <c r="AF3">
+        <v>14.5</v>
+      </c>
+      <c r="AG3">
+        <v>12</v>
+      </c>
+      <c r="AH3">
+        <v>18</v>
+      </c>
+      <c r="AI3">
+        <v>60</v>
+      </c>
+      <c r="AJ3">
+        <v>32</v>
+      </c>
+      <c r="AK3">
         <v>27</v>
       </c>
-      <c r="AA3">
-        <v>80</v>
-      </c>
-      <c r="AB3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC3">
-        <v>7.8</v>
-      </c>
-      <c r="AD3">
-        <v>17</v>
-      </c>
-      <c r="AE3">
-        <v>48</v>
-      </c>
-      <c r="AF3">
-        <v>13.5</v>
-      </c>
-      <c r="AG3">
-        <v>11</v>
-      </c>
-      <c r="AH3">
-        <v>18.5</v>
-      </c>
-      <c r="AI3">
-        <v>65</v>
-      </c>
-      <c r="AJ3">
-        <v>29</v>
-      </c>
-      <c r="AK3">
-        <v>25</v>
-      </c>
       <c r="AL3">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM3">
         <v>120</v>
       </c>
       <c r="AN3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AO3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP3">
         <v>11</v>
       </c>
       <c r="AQ3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AS3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT3">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV3">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AW3">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AX3">
         <v>12</v>
@@ -1650,13 +1650,13 @@
         <v>10</v>
       </c>
       <c r="AZ3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA3">
         <v>50</v>
       </c>
       <c r="BB3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC3">
         <v>22</v>
@@ -1665,13 +1665,13 @@
         <v>38</v>
       </c>
       <c r="BE3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BF3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BG3">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BH3">
         <v>3.3</v>
@@ -1689,7 +1689,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BN3">
         <v>5</v>
@@ -1698,10 +1698,10 @@
         <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR3">
         <v>32</v>
@@ -1716,13 +1716,13 @@
         <v>6</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW3">
         <v>11</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY3">
         <v>12.5</v>
@@ -1731,7 +1731,7 @@
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="s">
         <v>220</v>
@@ -1766,13 +1766,13 @@
         <v>3.25</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K4">
         <v>3.55</v>
       </c>
       <c r="L4">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M4">
         <v>1.08</v>
@@ -1802,7 +1802,7 @@
         <v>2.1</v>
       </c>
       <c r="V4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
         <v>1.66</v>
@@ -1817,7 +1817,7 @@
         <v>22</v>
       </c>
       <c r="AA4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB4">
         <v>9.800000000000001</v>
@@ -1898,7 +1898,7 @@
         <v>42</v>
       </c>
       <c r="BB4">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BC4">
         <v>24</v>
@@ -1931,7 +1931,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN4">
         <v>5.4</v>
@@ -1943,10 +1943,10 @@
         <v>19</v>
       </c>
       <c r="BQ4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS4">
         <v>10.5</v>
@@ -1961,19 +1961,19 @@
         <v>26</v>
       </c>
       <c r="BW4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4">
         <v>38</v>
       </c>
       <c r="CA4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
         <v>220</v>
@@ -1996,10 +1996,10 @@
         <v>180</v>
       </c>
       <c r="F5">
+        <v>1.61</v>
+      </c>
+      <c r="G5">
         <v>1.62</v>
-      </c>
-      <c r="G5">
-        <v>1.63</v>
       </c>
       <c r="H5">
         <v>6.4</v>
@@ -2047,7 +2047,7 @@
         <v>1.17</v>
       </c>
       <c r="W5">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X5">
         <v>18.5</v>
@@ -2065,13 +2065,13 @@
         <v>9.6</v>
       </c>
       <c r="AC5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF5">
         <v>9.800000000000001</v>
@@ -2101,7 +2101,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO5">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP5">
         <v>16</v>
@@ -2116,7 +2116,7 @@
         <v>15</v>
       </c>
       <c r="AT5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5">
         <v>9</v>
@@ -2134,10 +2134,10 @@
         <v>9</v>
       </c>
       <c r="AZ5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA5">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BB5">
         <v>13.5</v>
@@ -2238,22 +2238,22 @@
         <v>181</v>
       </c>
       <c r="F6">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="G6">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6">
         <v>4.7</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L6">
         <v>1.37</v>
@@ -2265,40 +2265,40 @@
         <v>4.3</v>
       </c>
       <c r="O6">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P6">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q6">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="R6">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S6">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T6">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U6">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V6">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W6">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="X6">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y6">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Z6">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AA6">
         <v>330</v>
@@ -2322,7 +2322,7 @@
         <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI6">
         <v>140</v>
@@ -2334,7 +2334,7 @@
         <v>17</v>
       </c>
       <c r="AL6">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM6">
         <v>180</v>
@@ -2352,10 +2352,10 @@
         <v>22</v>
       </c>
       <c r="AR6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AS6">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AT6">
         <v>7.4</v>
@@ -2364,7 +2364,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW6">
         <v>36</v>
@@ -2379,7 +2379,7 @@
         <v>21</v>
       </c>
       <c r="BA6">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BB6">
         <v>10.5</v>
@@ -2388,22 +2388,22 @@
         <v>13.5</v>
       </c>
       <c r="BD6">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BE6">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BF6">
         <v>6.4</v>
       </c>
       <c r="BG6">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BH6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI6">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BJ6">
         <v>12</v>
@@ -2421,13 +2421,13 @@
         <v>4.1</v>
       </c>
       <c r="BO6">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BP6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BQ6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR6">
         <v>26</v>
@@ -2442,7 +2442,7 @@
         <v>5.5</v>
       </c>
       <c r="BV6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BW6">
         <v>9.199999999999999</v>
@@ -2451,10 +2451,10 @@
         <v>75</v>
       </c>
       <c r="BY6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="CA6">
         <v>6.4</v>
@@ -2480,226 +2480,226 @@
         <v>182</v>
       </c>
       <c r="F7">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="G7">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="H7">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="I7">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="J7">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="L7">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="M7">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N7">
         <v>2.68</v>
       </c>
       <c r="O7">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="P7">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="Q7">
+        <v>2.26</v>
+      </c>
+      <c r="R7">
+        <v>1.22</v>
+      </c>
+      <c r="S7">
+        <v>3.45</v>
+      </c>
+      <c r="T7">
         <v>2.02</v>
       </c>
-      <c r="R7">
-        <v>1.25</v>
-      </c>
-      <c r="S7">
-        <v>3.7</v>
-      </c>
-      <c r="T7">
-        <v>2.14</v>
-      </c>
       <c r="U7">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="V7">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="W7">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="X7">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y7">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Z7">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AA7">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="AB7">
         <v>8</v>
       </c>
       <c r="AC7">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AE7">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="AF7">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG7">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH7">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AI7">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AJ7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AK7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL7">
         <v>60</v>
       </c>
       <c r="AM7">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AN7">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AO7">
-        <v>270</v>
+        <v>170</v>
       </c>
       <c r="AP7">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AQ7">
+        <v>4.5</v>
+      </c>
+      <c r="AR7">
+        <v>5.7</v>
+      </c>
+      <c r="AS7">
+        <v>6.2</v>
+      </c>
+      <c r="AT7">
+        <v>3.6</v>
+      </c>
+      <c r="AU7">
         <v>3.65</v>
       </c>
-      <c r="AR7">
+      <c r="AV7">
+        <v>5</v>
+      </c>
+      <c r="AW7">
+        <v>6</v>
+      </c>
+      <c r="AX7">
         <v>4.1</v>
       </c>
-      <c r="AS7">
-        <v>4.3</v>
-      </c>
-      <c r="AT7">
-        <v>2.82</v>
-      </c>
-      <c r="AU7">
+      <c r="AY7">
+        <v>4.1</v>
+      </c>
+      <c r="AZ7">
+        <v>5.1</v>
+      </c>
+      <c r="BA7">
+        <v>6.2</v>
+      </c>
+      <c r="BB7">
+        <v>5.1</v>
+      </c>
+      <c r="BC7">
+        <v>5.2</v>
+      </c>
+      <c r="BD7">
+        <v>5.9</v>
+      </c>
+      <c r="BE7">
+        <v>6.2</v>
+      </c>
+      <c r="BF7">
+        <v>4.9</v>
+      </c>
+      <c r="BG7">
+        <v>6.2</v>
+      </c>
+      <c r="BH7">
+        <v>3.05</v>
+      </c>
+      <c r="BI7">
+        <v>2.38</v>
+      </c>
+      <c r="BJ7">
+        <v>12</v>
+      </c>
+      <c r="BK7">
+        <v>5.5</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>2.32</v>
+      </c>
+      <c r="BN7">
+        <v>4.5</v>
+      </c>
+      <c r="BO7">
         <v>3.1</v>
       </c>
-      <c r="AV7">
-        <v>3.85</v>
-      </c>
-      <c r="AW7">
-        <v>4.2</v>
-      </c>
-      <c r="AX7">
-        <v>3.05</v>
-      </c>
-      <c r="AY7">
-        <v>3.2</v>
-      </c>
-      <c r="AZ7">
-        <v>3.85</v>
-      </c>
-      <c r="BA7">
-        <v>4.2</v>
-      </c>
-      <c r="BB7">
-        <v>3.55</v>
-      </c>
-      <c r="BC7">
-        <v>3.7</v>
-      </c>
-      <c r="BD7">
-        <v>4</v>
-      </c>
-      <c r="BE7">
-        <v>4.3</v>
-      </c>
-      <c r="BF7">
-        <v>3.45</v>
-      </c>
-      <c r="BG7">
-        <v>4.3</v>
-      </c>
-      <c r="BH7">
-        <v>3.15</v>
-      </c>
-      <c r="BI7">
-        <v>2.72</v>
-      </c>
-      <c r="BJ7">
-        <v>12.5</v>
-      </c>
-      <c r="BK7">
-        <v>5.8</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>2.42</v>
-      </c>
-      <c r="BN7">
-        <v>4.1</v>
-      </c>
-      <c r="BO7">
-        <v>2.98</v>
-      </c>
       <c r="BP7">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BQ7">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
+        <v>2.2</v>
+      </c>
+      <c r="BT7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU7">
+        <v>4.7</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>2.24</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
         <v>2.28</v>
       </c>
-      <c r="BT7">
-        <v>10.5</v>
-      </c>
-      <c r="BU7">
-        <v>5.4</v>
-      </c>
-      <c r="BV7">
-        <v>1000</v>
-      </c>
-      <c r="BW7">
-        <v>2.38</v>
-      </c>
-      <c r="BX7">
-        <v>1000</v>
-      </c>
-      <c r="BY7">
-        <v>2.38</v>
-      </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="CB7" t="s">
         <v>220</v>
@@ -2722,220 +2722,220 @@
         <v>183</v>
       </c>
       <c r="F8">
-        <v>2.72</v>
+        <v>11</v>
       </c>
       <c r="G8">
+        <v>14</v>
+      </c>
+      <c r="H8">
+        <v>1.25</v>
+      </c>
+      <c r="I8">
+        <v>1.3</v>
+      </c>
+      <c r="J8">
+        <v>6.4</v>
+      </c>
+      <c r="K8">
+        <v>8</v>
+      </c>
+      <c r="L8">
+        <v>1.2</v>
+      </c>
+      <c r="M8">
+        <v>1.02</v>
+      </c>
+      <c r="N8">
+        <v>7.2</v>
+      </c>
+      <c r="O8">
+        <v>1.13</v>
+      </c>
+      <c r="P8">
+        <v>3.15</v>
+      </c>
+      <c r="Q8">
+        <v>1.37</v>
+      </c>
+      <c r="R8">
+        <v>1.85</v>
+      </c>
+      <c r="S8">
+        <v>1.93</v>
+      </c>
+      <c r="T8">
+        <v>1.8</v>
+      </c>
+      <c r="U8">
+        <v>2</v>
+      </c>
+      <c r="V8">
+        <v>4.1</v>
+      </c>
+      <c r="W8">
+        <v>1.08</v>
+      </c>
+      <c r="X8">
+        <v>42</v>
+      </c>
+      <c r="Y8">
         <v>14.5</v>
       </c>
-      <c r="H8">
-        <v>1.17</v>
-      </c>
-      <c r="I8">
-        <v>1.45</v>
-      </c>
-      <c r="J8">
-        <v>1.33</v>
-      </c>
-      <c r="K8">
-        <v>1000</v>
-      </c>
-      <c r="L8">
-        <v>1.22</v>
-      </c>
-      <c r="M8">
-        <v>1.01</v>
-      </c>
-      <c r="N8">
-        <v>6</v>
-      </c>
-      <c r="O8">
-        <v>1.15</v>
-      </c>
-      <c r="P8">
-        <v>2.42</v>
-      </c>
-      <c r="Q8">
-        <v>1.34</v>
-      </c>
-      <c r="R8">
-        <v>1.63</v>
-      </c>
-      <c r="S8">
-        <v>2.02</v>
-      </c>
-      <c r="T8">
-        <v>1.83</v>
-      </c>
-      <c r="U8">
-        <v>1.9</v>
-      </c>
-      <c r="V8">
-        <v>3</v>
-      </c>
-      <c r="W8">
-        <v>1.07</v>
-      </c>
-      <c r="X8">
-        <v>38</v>
-      </c>
-      <c r="Y8">
-        <v>1000</v>
-      </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AC8">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AD8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AH8">
+        <v>29</v>
+      </c>
+      <c r="AI8">
         <v>32</v>
       </c>
-      <c r="AI8">
-        <v>1000</v>
-      </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM8">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN8">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BH8">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BJ8">
         <v>12</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT8">
         <v>4.3</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BV8">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BX8">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -3218,13 +3218,13 @@
         <v>5.2</v>
       </c>
       <c r="J10">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K10">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L10">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="M10">
         <v>1.07</v>
@@ -3272,7 +3272,7 @@
         <v>120</v>
       </c>
       <c r="AB10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC10">
         <v>9.199999999999999</v>
@@ -3293,7 +3293,7 @@
         <v>21</v>
       </c>
       <c r="AI10">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ10">
         <v>24</v>
@@ -3305,7 +3305,7 @@
         <v>40</v>
       </c>
       <c r="AM10">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN10">
         <v>16</v>
@@ -3320,10 +3320,10 @@
         <v>13.5</v>
       </c>
       <c r="AR10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS10">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT10">
         <v>7.8</v>
@@ -3338,7 +3338,7 @@
         <v>50</v>
       </c>
       <c r="AX10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY10">
         <v>9.4</v>
@@ -3359,7 +3359,7 @@
         <v>32</v>
       </c>
       <c r="BE10">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF10">
         <v>12</v>
@@ -3466,7 +3466,7 @@
         <v>4.1</v>
       </c>
       <c r="L11">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="M11">
         <v>1.06</v>
@@ -3690,226 +3690,226 @@
         <v>187</v>
       </c>
       <c r="F12">
-        <v>1.19</v>
+        <v>1.66</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>1.79</v>
       </c>
       <c r="H12">
-        <v>1.19</v>
+        <v>4.4</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>1.22</v>
+        <v>3.5</v>
       </c>
       <c r="K12">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N12">
-        <v>1.25</v>
+        <v>3.85</v>
       </c>
       <c r="O12">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P12">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q12">
-        <v>1.23</v>
+        <v>1.78</v>
       </c>
       <c r="R12">
+        <v>1.41</v>
+      </c>
+      <c r="S12">
+        <v>2.58</v>
+      </c>
+      <c r="T12">
+        <v>1.79</v>
+      </c>
+      <c r="U12">
+        <v>2.04</v>
+      </c>
+      <c r="V12">
         <v>1.18</v>
       </c>
-      <c r="S12">
-        <v>1.23</v>
-      </c>
-      <c r="T12">
-        <v>1.11</v>
-      </c>
-      <c r="U12">
-        <v>1.11</v>
-      </c>
-      <c r="V12">
-        <v>1.12</v>
-      </c>
       <c r="W12">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI12">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK12">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB12" t="s">
         <v>220</v>
@@ -3947,13 +3947,13 @@
         <v>2.52</v>
       </c>
       <c r="K13">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L13">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M13">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N13">
         <v>3.7</v>
@@ -3974,10 +3974,10 @@
         <v>2.92</v>
       </c>
       <c r="T13">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="U13">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="V13">
         <v>1.34</v>
@@ -4040,112 +4040,112 @@
         <v>40</v>
       </c>
       <c r="AP13">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="AQ13">
-        <v>9.6</v>
+        <v>3.4</v>
       </c>
       <c r="AR13">
-        <v>16.5</v>
+        <v>3.75</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT13">
-        <v>8</v>
+        <v>3.25</v>
       </c>
       <c r="AU13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV13">
-        <v>10</v>
+        <v>3.45</v>
       </c>
       <c r="AW13">
-        <v>26</v>
+        <v>3.95</v>
       </c>
       <c r="AX13">
-        <v>11.5</v>
+        <v>3.55</v>
       </c>
       <c r="AY13">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="AZ13">
-        <v>12</v>
+        <v>3.55</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB13">
-        <v>24</v>
+        <v>3.9</v>
       </c>
       <c r="BC13">
+        <v>3.8</v>
+      </c>
+      <c r="BD13">
+        <v>3.95</v>
+      </c>
+      <c r="BE13">
+        <v>4.1</v>
+      </c>
+      <c r="BF13">
+        <v>3.65</v>
+      </c>
+      <c r="BG13">
+        <v>3.9</v>
+      </c>
+      <c r="BH13">
+        <v>3.6</v>
+      </c>
+      <c r="BI13">
+        <v>2.78</v>
+      </c>
+      <c r="BJ13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK13">
+        <v>5</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN13">
+        <v>5.6</v>
+      </c>
+      <c r="BO13">
+        <v>3.65</v>
+      </c>
+      <c r="BP13">
         <v>18.5</v>
       </c>
-      <c r="BD13">
-        <v>27</v>
-      </c>
-      <c r="BE13">
-        <v>1.01</v>
-      </c>
-      <c r="BF13">
-        <v>14</v>
-      </c>
-      <c r="BG13">
-        <v>23</v>
-      </c>
-      <c r="BH13">
-        <v>1000</v>
-      </c>
-      <c r="BI13">
-        <v>1.01</v>
-      </c>
-      <c r="BJ13">
-        <v>1000</v>
-      </c>
-      <c r="BK13">
-        <v>1.01</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>1.01</v>
-      </c>
-      <c r="BN13">
-        <v>1000</v>
-      </c>
-      <c r="BO13">
-        <v>1.01</v>
-      </c>
-      <c r="BP13">
-        <v>1000</v>
-      </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -4174,13 +4174,13 @@
         <v>189</v>
       </c>
       <c r="F14">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="G14">
         <v>11</v>
       </c>
       <c r="H14">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="I14">
         <v>1.4</v>
@@ -4189,7 +4189,7 @@
         <v>5.1</v>
       </c>
       <c r="K14">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L14">
         <v>1.27</v>
@@ -4204,22 +4204,22 @@
         <v>1.26</v>
       </c>
       <c r="P14">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q14">
         <v>1.77</v>
       </c>
       <c r="R14">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S14">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T14">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U14">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V14">
         <v>3.5</v>
@@ -4312,7 +4312,7 @@
         <v>5.9</v>
       </c>
       <c r="AZ14">
-        <v>20</v>
+        <v>5.7</v>
       </c>
       <c r="BA14">
         <v>6</v>
@@ -4676,10 +4676,10 @@
         <v>4.4</v>
       </c>
       <c r="L16">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M16">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N16">
         <v>5.9</v>
@@ -4691,13 +4691,13 @@
         <v>2.66</v>
       </c>
       <c r="Q16">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R16">
         <v>1.67</v>
       </c>
       <c r="S16">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T16">
         <v>1.57</v>
@@ -4766,7 +4766,7 @@
         <v>27</v>
       </c>
       <c r="AP16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ16">
         <v>20</v>
@@ -4808,13 +4808,13 @@
         <v>15.5</v>
       </c>
       <c r="BD16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE16">
         <v>50</v>
       </c>
       <c r="BF16">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG16">
         <v>24</v>
@@ -4900,7 +4900,7 @@
         <v>192</v>
       </c>
       <c r="F17">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G17">
         <v>1.85</v>
@@ -4915,7 +4915,7 @@
         <v>4</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L17">
         <v>1.29</v>
@@ -4924,7 +4924,7 @@
         <v>1.05</v>
       </c>
       <c r="N17">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>1.24</v>
@@ -4978,7 +4978,7 @@
         <v>55</v>
       </c>
       <c r="AF17">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -4990,7 +4990,7 @@
         <v>55</v>
       </c>
       <c r="AJ17">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK17">
         <v>17.5</v>
@@ -5005,19 +5005,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AO17">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP17">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ17">
         <v>17.5</v>
       </c>
       <c r="AR17">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AS17">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT17">
         <v>9.800000000000001</v>
@@ -5029,7 +5029,7 @@
         <v>16.5</v>
       </c>
       <c r="AW17">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX17">
         <v>9.6</v>
@@ -5041,7 +5041,7 @@
         <v>15.5</v>
       </c>
       <c r="BA17">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB17">
         <v>17.5</v>
@@ -5050,7 +5050,7 @@
         <v>13.5</v>
       </c>
       <c r="BD17">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE17">
         <v>10.5</v>
@@ -5059,7 +5059,7 @@
         <v>7.8</v>
       </c>
       <c r="BG17">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH17">
         <v>4</v>
@@ -5181,7 +5181,7 @@
         <v>1.97</v>
       </c>
       <c r="S18">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="T18">
         <v>1.59</v>
@@ -5426,7 +5426,7 @@
         <v>3</v>
       </c>
       <c r="T19">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U19">
         <v>2.12</v>
@@ -5465,7 +5465,7 @@
         <v>13</v>
       </c>
       <c r="AG19">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH19">
         <v>22</v>
@@ -5498,13 +5498,13 @@
         <v>15</v>
       </c>
       <c r="AR19">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AS19">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT19">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU19">
         <v>8.4</v>
@@ -5513,7 +5513,7 @@
         <v>15.5</v>
       </c>
       <c r="AW19">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AX19">
         <v>9.800000000000001</v>
@@ -5525,31 +5525,31 @@
         <v>16.5</v>
       </c>
       <c r="BA19">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BB19">
         <v>15.5</v>
       </c>
       <c r="BC19">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BD19">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE19">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF19">
         <v>8.6</v>
       </c>
       <c r="BG19">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BH19">
         <v>3.75</v>
       </c>
       <c r="BI19">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="BJ19">
         <v>9.800000000000001</v>
@@ -5626,7 +5626,7 @@
         <v>195</v>
       </c>
       <c r="F20">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G20">
         <v>3.05</v>
@@ -5644,19 +5644,19 @@
         <v>3.3</v>
       </c>
       <c r="L20">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M20">
         <v>1.1</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O20">
         <v>1.43</v>
       </c>
       <c r="P20">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q20">
         <v>2.28</v>
@@ -6113,10 +6113,10 @@
         <v>2.76</v>
       </c>
       <c r="G22">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H22">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I22">
         <v>2.68</v>
@@ -6128,7 +6128,7 @@
         <v>3.95</v>
       </c>
       <c r="L22">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="M22">
         <v>1.05</v>
@@ -6161,7 +6161,7 @@
         <v>1.6</v>
       </c>
       <c r="W22">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X22">
         <v>19</v>
@@ -6460,7 +6460,7 @@
         <v>16</v>
       </c>
       <c r="AP23">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ23">
         <v>13.5</v>
@@ -6597,13 +6597,13 @@
         <v>2.3</v>
       </c>
       <c r="G24">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H24">
         <v>2.98</v>
       </c>
       <c r="I24">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J24">
         <v>3.6</v>
@@ -6624,7 +6624,7 @@
         <v>1.26</v>
       </c>
       <c r="P24">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q24">
         <v>1.77</v>
@@ -6636,7 +6636,7 @@
         <v>2.94</v>
       </c>
       <c r="T24">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U24">
         <v>2.3</v>
@@ -6669,7 +6669,7 @@
         <v>16</v>
       </c>
       <c r="AE24">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF24">
         <v>19.5</v>
@@ -6711,7 +6711,7 @@
         <v>17.5</v>
       </c>
       <c r="AS24">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT24">
         <v>9.4</v>
@@ -6738,16 +6738,16 @@
         <v>4.5</v>
       </c>
       <c r="BB24">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC24">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD24">
         <v>4.5</v>
       </c>
       <c r="BE24">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF24">
         <v>12.5</v>
@@ -6836,28 +6836,28 @@
         <v>200</v>
       </c>
       <c r="F25">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G25">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="H25">
         <v>2.12</v>
       </c>
       <c r="I25">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="J25">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="K25">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L25">
         <v>1.53</v>
       </c>
       <c r="M25">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N25">
         <v>2.28</v>
@@ -6866,10 +6866,10 @@
         <v>1.55</v>
       </c>
       <c r="P25">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q25">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R25">
         <v>1.16</v>
@@ -6884,16 +6884,16 @@
         <v>1.69</v>
       </c>
       <c r="V25">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W25">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X25">
         <v>9.199999999999999</v>
       </c>
       <c r="Y25">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z25">
         <v>15.5</v>
@@ -6905,7 +6905,7 @@
         <v>12</v>
       </c>
       <c r="AC25">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD25">
         <v>14.5</v>
@@ -6923,7 +6923,7 @@
         <v>29</v>
       </c>
       <c r="AI25">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ25">
         <v>110</v>
@@ -6944,58 +6944,58 @@
         <v>46</v>
       </c>
       <c r="AP25">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AQ25">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AR25">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AS25">
+        <v>4.9</v>
+      </c>
+      <c r="AT25">
+        <v>3.8</v>
+      </c>
+      <c r="AU25">
+        <v>3.2</v>
+      </c>
+      <c r="AV25">
+        <v>4</v>
+      </c>
+      <c r="AW25">
+        <v>4.9</v>
+      </c>
+      <c r="AX25">
+        <v>4.7</v>
+      </c>
+      <c r="AY25">
+        <v>4.4</v>
+      </c>
+      <c r="AZ25">
         <v>4.6</v>
       </c>
-      <c r="AT25">
-        <v>3.6</v>
-      </c>
-      <c r="AU25">
-        <v>3.15</v>
-      </c>
-      <c r="AV25">
-        <v>3.8</v>
-      </c>
-      <c r="AW25">
-        <v>4.6</v>
-      </c>
-      <c r="AX25">
-        <v>4.4</v>
-      </c>
-      <c r="AY25">
-        <v>4.1</v>
-      </c>
-      <c r="AZ25">
-        <v>4.3</v>
-      </c>
       <c r="BA25">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB25">
+        <v>5.3</v>
+      </c>
+      <c r="BC25">
+        <v>5.2</v>
+      </c>
+      <c r="BD25">
+        <v>5.3</v>
+      </c>
+      <c r="BE25">
+        <v>5.4</v>
+      </c>
+      <c r="BF25">
+        <v>5.3</v>
+      </c>
+      <c r="BG25">
         <v>4.9</v>
-      </c>
-      <c r="BC25">
-        <v>4.8</v>
-      </c>
-      <c r="BD25">
-        <v>4.9</v>
-      </c>
-      <c r="BE25">
-        <v>5</v>
-      </c>
-      <c r="BF25">
-        <v>4.9</v>
-      </c>
-      <c r="BG25">
-        <v>4.6</v>
       </c>
       <c r="BH25">
         <v>2.72</v>
@@ -7078,7 +7078,7 @@
         <v>201</v>
       </c>
       <c r="F26">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="G26">
         <v>3.45</v>
@@ -7090,7 +7090,7 @@
         <v>3.3</v>
       </c>
       <c r="J26">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="K26">
         <v>3.1</v>
@@ -7099,7 +7099,7 @@
         <v>1.6</v>
       </c>
       <c r="M26">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N26">
         <v>2.06</v>
@@ -7111,7 +7111,7 @@
         <v>1.38</v>
       </c>
       <c r="Q26">
-        <v>2.86</v>
+        <v>2.64</v>
       </c>
       <c r="R26">
         <v>1.13</v>
@@ -7168,7 +7168,7 @@
         <v>110</v>
       </c>
       <c r="AJ26">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK26">
         <v>70</v>
@@ -7198,22 +7198,22 @@
         <v>6.4</v>
       </c>
       <c r="AT26">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="AU26">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="AV26">
         <v>4.9</v>
       </c>
       <c r="AW26">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX26">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AY26">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AZ26">
         <v>5.7</v>
@@ -7231,13 +7231,13 @@
         <v>6.6</v>
       </c>
       <c r="BE26">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF26">
         <v>6.6</v>
       </c>
       <c r="BG26">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH26">
         <v>2.5</v>
@@ -7323,10 +7323,10 @@
         <v>1.65</v>
       </c>
       <c r="G27">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H27">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I27">
         <v>8.199999999999999</v>
@@ -7344,7 +7344,7 @@
         <v>1.11</v>
       </c>
       <c r="N27">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="O27">
         <v>1.55</v>
@@ -7359,7 +7359,7 @@
         <v>1.16</v>
       </c>
       <c r="S27">
-        <v>4.6</v>
+        <v>1.05</v>
       </c>
       <c r="T27">
         <v>2.32</v>
@@ -7371,7 +7371,7 @@
         <v>1.13</v>
       </c>
       <c r="W27">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -7428,55 +7428,55 @@
         <v>370</v>
       </c>
       <c r="AP27">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AQ27">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AR27">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS27">
         <v>4.4</v>
       </c>
       <c r="AT27">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AU27">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AV27">
         <v>3.95</v>
       </c>
       <c r="AW27">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX27">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AY27">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AZ27">
         <v>4</v>
       </c>
       <c r="BA27">
+        <v>4.4</v>
+      </c>
+      <c r="BB27">
+        <v>3.85</v>
+      </c>
+      <c r="BC27">
+        <v>4</v>
+      </c>
+      <c r="BD27">
         <v>4.3</v>
-      </c>
-      <c r="BB27">
-        <v>3.8</v>
-      </c>
-      <c r="BC27">
-        <v>3.95</v>
-      </c>
-      <c r="BD27">
-        <v>4.2</v>
       </c>
       <c r="BE27">
         <v>4.4</v>
       </c>
       <c r="BF27">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BG27">
         <v>4.4</v>
@@ -7804,22 +7804,22 @@
         <v>204</v>
       </c>
       <c r="F29">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G29">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="H29">
         <v>6</v>
       </c>
       <c r="I29">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J29">
         <v>4.2</v>
       </c>
       <c r="K29">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L29">
         <v>1.31</v>
@@ -7837,13 +7837,13 @@
         <v>2</v>
       </c>
       <c r="Q29">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R29">
         <v>1.4</v>
       </c>
       <c r="S29">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T29">
         <v>1.9</v>
@@ -7852,10 +7852,10 @@
         <v>1.94</v>
       </c>
       <c r="V29">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W29">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="X29">
         <v>20</v>
@@ -7867,7 +7867,7 @@
         <v>60</v>
       </c>
       <c r="AA29">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB29">
         <v>8.800000000000001</v>
@@ -8049,19 +8049,19 @@
         <v>3.15</v>
       </c>
       <c r="G30">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H30">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I30">
         <v>2.58</v>
       </c>
       <c r="J30">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K30">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L30">
         <v>1.39</v>
@@ -8088,7 +8088,7 @@
         <v>3.8</v>
       </c>
       <c r="T30">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U30">
         <v>2.06</v>
@@ -8097,7 +8097,7 @@
         <v>1.63</v>
       </c>
       <c r="W30">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X30">
         <v>13</v>
@@ -8172,7 +8172,7 @@
         <v>6.8</v>
       </c>
       <c r="AV30">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW30">
         <v>21</v>
@@ -8291,19 +8291,19 @@
         <v>1.71</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="H31">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="I31">
         <v>5</v>
       </c>
       <c r="J31">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K31">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L31">
         <v>1.24</v>
@@ -8330,34 +8330,34 @@
         <v>2.28</v>
       </c>
       <c r="T31">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="U31">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="V31">
         <v>1.25</v>
       </c>
       <c r="W31">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X31">
         <v>28</v>
       </c>
       <c r="Y31">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="Z31">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AA31">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB31">
         <v>14</v>
       </c>
       <c r="AC31">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD31">
         <v>19.5</v>
@@ -8378,7 +8378,7 @@
         <v>65</v>
       </c>
       <c r="AJ31">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AK31">
         <v>18</v>
@@ -8387,67 +8387,67 @@
         <v>28</v>
       </c>
       <c r="AM31">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AN31">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO31">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AP31">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ31">
+        <v>4.8</v>
+      </c>
+      <c r="AR31">
+        <v>5.1</v>
+      </c>
+      <c r="AS31">
+        <v>5.6</v>
+      </c>
+      <c r="AT31">
+        <v>4</v>
+      </c>
+      <c r="AU31">
+        <v>3.8</v>
+      </c>
+      <c r="AV31">
+        <v>4.4</v>
+      </c>
+      <c r="AW31">
+        <v>5.2</v>
+      </c>
+      <c r="AX31">
+        <v>4.1</v>
+      </c>
+      <c r="AY31">
+        <v>3.8</v>
+      </c>
+      <c r="AZ31">
+        <v>4.2</v>
+      </c>
+      <c r="BA31">
+        <v>5</v>
+      </c>
+      <c r="BB31">
+        <v>4.7</v>
+      </c>
+      <c r="BC31">
+        <v>4.3</v>
+      </c>
+      <c r="BD31">
+        <v>4.7</v>
+      </c>
+      <c r="BE31">
         <v>5.3</v>
       </c>
-      <c r="AR31">
-        <v>5.9</v>
-      </c>
-      <c r="AS31">
-        <v>6.4</v>
-      </c>
-      <c r="AT31">
-        <v>4.6</v>
-      </c>
-      <c r="AU31">
-        <v>4.4</v>
-      </c>
-      <c r="AV31">
+      <c r="BF31">
+        <v>3.35</v>
+      </c>
+      <c r="BG31">
         <v>5</v>
-      </c>
-      <c r="AW31">
-        <v>6</v>
-      </c>
-      <c r="AX31">
-        <v>4.7</v>
-      </c>
-      <c r="AY31">
-        <v>4.2</v>
-      </c>
-      <c r="AZ31">
-        <v>4.9</v>
-      </c>
-      <c r="BA31">
-        <v>6</v>
-      </c>
-      <c r="BB31">
-        <v>5.2</v>
-      </c>
-      <c r="BC31">
-        <v>4.9</v>
-      </c>
-      <c r="BD31">
-        <v>5.5</v>
-      </c>
-      <c r="BE31">
-        <v>6.2</v>
-      </c>
-      <c r="BF31">
-        <v>3.85</v>
-      </c>
-      <c r="BG31">
-        <v>5.8</v>
       </c>
       <c r="BH31">
         <v>4.8</v>
@@ -8536,7 +8536,7 @@
         <v>1.72</v>
       </c>
       <c r="H32">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I32">
         <v>7.2</v>
@@ -9017,7 +9017,7 @@
         <v>1.76</v>
       </c>
       <c r="G34">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H34">
         <v>5.8</v>
@@ -9029,7 +9029,7 @@
         <v>3.25</v>
       </c>
       <c r="K34">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L34">
         <v>1.46</v>
@@ -9038,7 +9038,7 @@
         <v>1.12</v>
       </c>
       <c r="N34">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O34">
         <v>1.51</v>
@@ -9053,28 +9053,28 @@
         <v>1.19</v>
       </c>
       <c r="S34">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T34">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="U34">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="V34">
         <v>1.17</v>
       </c>
       <c r="W34">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X34">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="Y34">
         <v>15</v>
       </c>
       <c r="Z34">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AA34">
         <v>260</v>
@@ -9092,13 +9092,13 @@
         <v>160</v>
       </c>
       <c r="AF34">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG34">
         <v>11</v>
       </c>
       <c r="AH34">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI34">
         <v>170</v>
@@ -9116,7 +9116,7 @@
         <v>300</v>
       </c>
       <c r="AN34">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO34">
         <v>290</v>
@@ -9128,10 +9128,10 @@
         <v>10.5</v>
       </c>
       <c r="AR34">
-        <v>34</v>
+        <v>9.6</v>
       </c>
       <c r="AS34">
-        <v>150</v>
+        <v>11</v>
       </c>
       <c r="AT34">
         <v>5.4</v>
@@ -9143,7 +9143,7 @@
         <v>18.5</v>
       </c>
       <c r="AW34">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="AX34">
         <v>7</v>
@@ -9155,7 +9155,7 @@
         <v>20</v>
       </c>
       <c r="BA34">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="BB34">
         <v>14.5</v>
@@ -9164,70 +9164,70 @@
         <v>18</v>
       </c>
       <c r="BD34">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE34">
-        <v>170</v>
+        <v>11</v>
       </c>
       <c r="BF34">
         <v>14.5</v>
       </c>
       <c r="BG34">
-        <v>160</v>
+        <v>11</v>
       </c>
       <c r="BH34">
         <v>2.8</v>
       </c>
       <c r="BI34">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="BJ34">
         <v>12.5</v>
       </c>
       <c r="BK34">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="BN34">
         <v>4.2</v>
       </c>
       <c r="BO34">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BP34">
         <v>14.5</v>
       </c>
       <c r="BQ34">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="BR34">
         <v>40</v>
       </c>
       <c r="BS34">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="BT34">
         <v>9.4</v>
       </c>
       <c r="BU34">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="BX34">
         <v>1000</v>
       </c>
       <c r="BY34">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="BZ34">
         <v>0</v>
@@ -9274,7 +9274,7 @@
         <v>3.6</v>
       </c>
       <c r="L35">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M35">
         <v>1.1</v>
@@ -9537,7 +9537,7 @@
         <v>1.53</v>
       </c>
       <c r="S36">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="T36">
         <v>2</v>
@@ -9854,10 +9854,10 @@
         <v>10.5</v>
       </c>
       <c r="AR37">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AS37">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT37">
         <v>6.8</v>
@@ -9869,7 +9869,7 @@
         <v>15.5</v>
       </c>
       <c r="AW37">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AX37">
         <v>10</v>
@@ -9881,7 +9881,7 @@
         <v>17</v>
       </c>
       <c r="BA37">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BB37">
         <v>20</v>
@@ -9890,16 +9890,16 @@
         <v>19.5</v>
       </c>
       <c r="BD37">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BE37">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF37">
         <v>12.5</v>
       </c>
       <c r="BG37">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BH37">
         <v>3.25</v>
@@ -9985,7 +9985,7 @@
         <v>2</v>
       </c>
       <c r="G38">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H38">
         <v>4.1</v>
@@ -9994,37 +9994,37 @@
         <v>4.8</v>
       </c>
       <c r="J38">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K38">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L38">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M38">
         <v>1.09</v>
       </c>
       <c r="N38">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O38">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P38">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="Q38">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R38">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S38">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T38">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U38">
         <v>1.91</v>
@@ -10033,13 +10033,13 @@
         <v>1.27</v>
       </c>
       <c r="W38">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="X38">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y38">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z38">
         <v>36</v>
@@ -10048,7 +10048,7 @@
         <v>150</v>
       </c>
       <c r="AB38">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC38">
         <v>8</v>
@@ -10096,10 +10096,10 @@
         <v>10</v>
       </c>
       <c r="AR38">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS38">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT38">
         <v>6.8</v>
@@ -10111,7 +10111,7 @@
         <v>13.5</v>
       </c>
       <c r="AW38">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX38">
         <v>10</v>
@@ -10123,52 +10123,52 @@
         <v>17</v>
       </c>
       <c r="BA38">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB38">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC38">
         <v>21</v>
       </c>
       <c r="BD38">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE38">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF38">
         <v>15.5</v>
       </c>
       <c r="BG38">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH38">
         <v>3.15</v>
       </c>
       <c r="BI38">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="BJ38">
         <v>11</v>
       </c>
       <c r="BK38">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN38">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO38">
         <v>3.75</v>
       </c>
       <c r="BP38">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ38">
         <v>6.4</v>
@@ -10177,7 +10177,7 @@
         <v>1000</v>
       </c>
       <c r="BS38">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT38">
         <v>7.8</v>
@@ -10201,7 +10201,7 @@
         <v>1000</v>
       </c>
       <c r="CA38">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CB38" t="s">
         <v>220</v>
@@ -10263,7 +10263,7 @@
         <v>1.19</v>
       </c>
       <c r="S39">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T39">
         <v>2.22</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M40">
         <v>1.07</v>
@@ -10708,226 +10708,226 @@
         <v>216</v>
       </c>
       <c r="F41">
-        <v>1.14</v>
+        <v>1.85</v>
       </c>
       <c r="G41">
-        <v>1000</v>
+        <v>2.02</v>
       </c>
       <c r="H41">
-        <v>1.14</v>
+        <v>4</v>
       </c>
       <c r="I41">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="J41">
+        <v>3.2</v>
+      </c>
+      <c r="K41">
+        <v>4</v>
+      </c>
+      <c r="L41">
+        <v>1.36</v>
+      </c>
+      <c r="M41">
+        <v>1.07</v>
+      </c>
+      <c r="N41">
         <v>3.25</v>
       </c>
-      <c r="K41">
-        <v>1000</v>
-      </c>
-      <c r="L41">
-        <v>1.01</v>
-      </c>
-      <c r="M41">
-        <v>1.01</v>
-      </c>
-      <c r="N41">
-        <v>1.1</v>
-      </c>
       <c r="O41">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P41">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="Q41">
-        <v>1.31</v>
+        <v>1.91</v>
       </c>
       <c r="R41">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="S41">
-        <v>1.33</v>
+        <v>3.2</v>
       </c>
       <c r="T41">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="U41">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="V41">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="W41">
-        <v>1.02</v>
+        <v>1.98</v>
       </c>
       <c r="X41">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y41">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z41">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA41">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB41">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC41">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD41">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE41">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF41">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG41">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH41">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI41">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ41">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK41">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL41">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM41">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN41">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO41">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP41">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AQ41">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AR41">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AS41">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT41">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU41">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AV41">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AW41">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AX41">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AY41">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AZ41">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA41">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BB41">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC41">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BD41">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE41">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF41">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG41">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH41">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI41">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BJ41">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK41">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BL41">
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BN41">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO41">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP41">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ41">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR41">
         <v>1000</v>
       </c>
       <c r="BS41">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="BT41">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU41">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV41">
         <v>1000</v>
       </c>
       <c r="BW41">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BX41">
         <v>1000</v>
       </c>
       <c r="BY41">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BZ41">
         <v>1000</v>
       </c>
       <c r="CA41">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="CB41" t="s">
         <v>220</v>
@@ -11192,226 +11192,226 @@
         <v>218</v>
       </c>
       <c r="F43">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="G43">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="H43">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="I43">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J43">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K43">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L43">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M43">
         <v>1.06</v>
       </c>
       <c r="N43">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O43">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="P43">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q43">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R43">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S43">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="T43">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="U43">
         <v>2.08</v>
       </c>
       <c r="V43">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="W43">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="X43">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y43">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z43">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AA43">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AB43">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC43">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD43">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AE43">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF43">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG43">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH43">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI43">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ43">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AK43">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AL43">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM43">
         <v>110</v>
       </c>
       <c r="AN43">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO43">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AP43">
-        <v>3.8</v>
+        <v>12.5</v>
       </c>
       <c r="AQ43">
-        <v>3.75</v>
+        <v>11.5</v>
       </c>
       <c r="AR43">
-        <v>4.2</v>
+        <v>21</v>
       </c>
       <c r="AS43">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AT43">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU43">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV43">
         <v>12.5</v>
       </c>
       <c r="AW43">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX43">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY43">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AZ43">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA43">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BB43">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BC43">
-        <v>4</v>
+        <v>18.5</v>
       </c>
       <c r="BD43">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BE43">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF43">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG43">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH43">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BI43">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BJ43">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK43">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BL43">
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BN43">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BO43">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BP43">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BQ43">
+        <v>5.3</v>
+      </c>
+      <c r="BR43">
+        <v>32</v>
+      </c>
+      <c r="BS43">
+        <v>6.2</v>
+      </c>
+      <c r="BT43">
+        <v>7.6</v>
+      </c>
+      <c r="BU43">
+        <v>5.2</v>
+      </c>
+      <c r="BV43">
+        <v>32</v>
+      </c>
+      <c r="BW43">
+        <v>6.2</v>
+      </c>
+      <c r="BX43">
+        <v>42</v>
+      </c>
+      <c r="BY43">
+        <v>6.4</v>
+      </c>
+      <c r="BZ43">
+        <v>26</v>
+      </c>
+      <c r="CA43">
         <v>5.9</v>
-      </c>
-      <c r="BR43">
-        <v>29</v>
-      </c>
-      <c r="BS43">
-        <v>7.4</v>
-      </c>
-      <c r="BT43">
-        <v>8</v>
-      </c>
-      <c r="BU43">
-        <v>5.8</v>
-      </c>
-      <c r="BV43">
-        <v>36</v>
-      </c>
-      <c r="BW43">
-        <v>7.8</v>
-      </c>
-      <c r="BX43">
-        <v>46</v>
-      </c>
-      <c r="BY43">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BZ43">
-        <v>25</v>
-      </c>
-      <c r="CA43">
-        <v>7</v>
       </c>
       <c r="CB43" t="s">
         <v>220</v>
@@ -11452,7 +11452,7 @@
         <v>3.45</v>
       </c>
       <c r="L44">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M44">
         <v>1.09</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -676,7 +676,7 @@
     <t>Everton De Vina</t>
   </si>
   <si>
-    <t>2026-07-26 12:56:39</t>
+    <t>2026-07-26 15:07:13</t>
   </si>
 </sst>
 </file>
@@ -1270,22 +1270,22 @@
         <v>177</v>
       </c>
       <c r="F2">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G2">
         <v>1.79</v>
       </c>
       <c r="H2">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J2">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
         <v>1.41</v>
@@ -1294,28 +1294,28 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O2">
         <v>1.32</v>
       </c>
       <c r="P2">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q2">
         <v>2</v>
       </c>
       <c r="R2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T2">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V2">
         <v>1.21</v>
@@ -1327,58 +1327,58 @@
         <v>16</v>
       </c>
       <c r="Y2">
+        <v>18.5</v>
+      </c>
+      <c r="Z2">
+        <v>44</v>
+      </c>
+      <c r="AA2">
+        <v>170</v>
+      </c>
+      <c r="AB2">
+        <v>8.4</v>
+      </c>
+      <c r="AC2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD2">
         <v>22</v>
-      </c>
-      <c r="Z2">
-        <v>55</v>
-      </c>
-      <c r="AA2">
-        <v>160</v>
-      </c>
-      <c r="AB2">
-        <v>8.6</v>
-      </c>
-      <c r="AC2">
-        <v>9.4</v>
-      </c>
-      <c r="AD2">
-        <v>25</v>
       </c>
       <c r="AE2">
         <v>75</v>
       </c>
       <c r="AF2">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI2">
         <v>100</v>
       </c>
       <c r="AJ2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AL2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM2">
+        <v>200</v>
+      </c>
+      <c r="AN2">
+        <v>11.5</v>
+      </c>
+      <c r="AO2">
         <v>150</v>
       </c>
-      <c r="AN2">
-        <v>14.5</v>
-      </c>
-      <c r="AO2">
-        <v>110</v>
-      </c>
       <c r="AP2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ2">
         <v>15.5</v>
@@ -1387,46 +1387,46 @@
         <v>32</v>
       </c>
       <c r="AS2">
-        <v>7.8</v>
+        <v>44</v>
       </c>
       <c r="AT2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU2">
         <v>8</v>
       </c>
       <c r="AV2">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AW2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AX2">
         <v>9.199999999999999</v>
       </c>
       <c r="AY2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA2">
         <v>46</v>
       </c>
       <c r="BB2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE2">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG2">
         <v>55</v>
@@ -1435,22 +1435,22 @@
         <v>3.45</v>
       </c>
       <c r="BI2">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2">
         <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO2">
         <v>3.35</v>
@@ -1459,37 +1459,37 @@
         <v>12</v>
       </c>
       <c r="BQ2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2">
         <v>9</v>
       </c>
       <c r="BU2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB2" t="s">
         <v>220</v>
@@ -1518,7 +1518,7 @@
         <v>2.4</v>
       </c>
       <c r="H3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I3">
         <v>3.6</v>
@@ -1527,7 +1527,7 @@
         <v>3.35</v>
       </c>
       <c r="K3">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L3">
         <v>1.46</v>
@@ -1536,7 +1536,7 @@
         <v>1.08</v>
       </c>
       <c r="N3">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O3">
         <v>1.38</v>
@@ -1545,25 +1545,25 @@
         <v>1.84</v>
       </c>
       <c r="Q3">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R3">
         <v>1.32</v>
       </c>
       <c r="S3">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T3">
         <v>1.86</v>
       </c>
       <c r="U3">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X3">
         <v>14.5</v>
@@ -1572,13 +1572,13 @@
         <v>12.5</v>
       </c>
       <c r="Z3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3">
         <v>7.6</v>
@@ -1593,7 +1593,7 @@
         <v>14.5</v>
       </c>
       <c r="AG3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH3">
         <v>18</v>
@@ -1605,19 +1605,19 @@
         <v>32</v>
       </c>
       <c r="AK3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL3">
+        <v>44</v>
+      </c>
+      <c r="AM3">
+        <v>110</v>
+      </c>
+      <c r="AN3">
+        <v>22</v>
+      </c>
+      <c r="AO3">
         <v>46</v>
-      </c>
-      <c r="AM3">
-        <v>120</v>
-      </c>
-      <c r="AN3">
-        <v>23</v>
-      </c>
-      <c r="AO3">
-        <v>50</v>
       </c>
       <c r="AP3">
         <v>11</v>
@@ -1638,31 +1638,31 @@
         <v>7</v>
       </c>
       <c r="AV3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW3">
         <v>38</v>
       </c>
       <c r="AX3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
         <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BB3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BC3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BE3">
         <v>85</v>
@@ -1674,7 +1674,7 @@
         <v>38</v>
       </c>
       <c r="BH3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI3">
         <v>3</v>
@@ -1683,55 +1683,55 @@
         <v>9.6</v>
       </c>
       <c r="BK3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BN3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP3">
         <v>17.5</v>
       </c>
       <c r="BQ3">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR3">
         <v>32</v>
       </c>
       <c r="BS3">
+        <v>12</v>
+      </c>
+      <c r="BT3">
+        <v>6.6</v>
+      </c>
+      <c r="BU3">
+        <v>4.9</v>
+      </c>
+      <c r="BV3">
+        <v>28</v>
+      </c>
+      <c r="BW3">
         <v>11.5</v>
-      </c>
-      <c r="BT3">
-        <v>6.8</v>
-      </c>
-      <c r="BU3">
-        <v>6</v>
-      </c>
-      <c r="BV3">
-        <v>29</v>
-      </c>
-      <c r="BW3">
-        <v>11</v>
       </c>
       <c r="BX3">
         <v>42</v>
       </c>
       <c r="BY3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB3" t="s">
         <v>220</v>
@@ -1754,25 +1754,25 @@
         <v>179</v>
       </c>
       <c r="F4">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G4">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K4">
         <v>3.55</v>
       </c>
       <c r="L4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M4">
         <v>1.08</v>
@@ -1784,13 +1784,13 @@
         <v>1.35</v>
       </c>
       <c r="P4">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q4">
         <v>2.06</v>
       </c>
       <c r="R4">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S4">
         <v>3.75</v>
@@ -1799,7 +1799,7 @@
         <v>1.81</v>
       </c>
       <c r="U4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V4">
         <v>1.44</v>
@@ -1820,7 +1820,7 @@
         <v>60</v>
       </c>
       <c r="AB4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC4">
         <v>7.8</v>
@@ -1841,7 +1841,7 @@
         <v>18</v>
       </c>
       <c r="AI4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ4">
         <v>36</v>
@@ -1856,10 +1856,10 @@
         <v>100</v>
       </c>
       <c r="AN4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP4">
         <v>12</v>
@@ -1877,7 +1877,7 @@
         <v>9.4</v>
       </c>
       <c r="AU4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV4">
         <v>12.5</v>
@@ -1898,7 +1898,7 @@
         <v>42</v>
       </c>
       <c r="BB4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BC4">
         <v>24</v>
@@ -1907,7 +1907,7 @@
         <v>36</v>
       </c>
       <c r="BE4">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="BF4">
         <v>20</v>
@@ -1970,7 +1970,7 @@
         <v>11.5</v>
       </c>
       <c r="BZ4">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
         <v>10.5</v>
@@ -1996,13 +1996,13 @@
         <v>180</v>
       </c>
       <c r="F5">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G5">
         <v>1.62</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
         <v>6.8</v>
@@ -2020,22 +2020,22 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O5">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P5">
         <v>2.2</v>
       </c>
       <c r="Q5">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R5">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S5">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T5">
         <v>1.87</v>
@@ -2071,10 +2071,10 @@
         <v>25</v>
       </c>
       <c r="AE5">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG5">
         <v>10</v>
@@ -2083,7 +2083,7 @@
         <v>21</v>
       </c>
       <c r="AI5">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AJ5">
         <v>15.5</v>
@@ -2095,7 +2095,7 @@
         <v>32</v>
       </c>
       <c r="AM5">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="AN5">
         <v>8.199999999999999</v>
@@ -2113,10 +2113,10 @@
         <v>44</v>
       </c>
       <c r="AS5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU5">
         <v>9</v>
@@ -2125,7 +2125,7 @@
         <v>21</v>
       </c>
       <c r="AW5">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AX5">
         <v>9</v>
@@ -2152,7 +2152,7 @@
         <v>60</v>
       </c>
       <c r="BF5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG5">
         <v>55</v>
@@ -2167,25 +2167,25 @@
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN5">
         <v>4.4</v>
       </c>
       <c r="BO5">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="BP5">
         <v>10.5</v>
       </c>
       <c r="BQ5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR5">
         <v>25</v>
@@ -2203,16 +2203,16 @@
         <v>55</v>
       </c>
       <c r="BW5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX5">
         <v>55</v>
       </c>
       <c r="BY5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CA5">
         <v>7</v>
@@ -2238,7 +2238,7 @@
         <v>181</v>
       </c>
       <c r="F6">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G6">
         <v>1.52</v>
@@ -2247,52 +2247,52 @@
         <v>7.8</v>
       </c>
       <c r="I6">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K6">
         <v>4.9</v>
       </c>
       <c r="L6">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M6">
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O6">
         <v>1.28</v>
       </c>
       <c r="P6">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q6">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="R6">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S6">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T6">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="U6">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="V6">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W6">
         <v>2.92</v>
       </c>
       <c r="X6">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y6">
         <v>27</v>
@@ -2301,10 +2301,10 @@
         <v>75</v>
       </c>
       <c r="AA6">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AB6">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6">
         <v>11</v>
@@ -2313,7 +2313,7 @@
         <v>32</v>
       </c>
       <c r="AE6">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF6">
         <v>8.800000000000001</v>
@@ -2325,25 +2325,25 @@
         <v>26</v>
       </c>
       <c r="AI6">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ6">
         <v>13</v>
       </c>
       <c r="AK6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM6">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN6">
         <v>7.6</v>
       </c>
       <c r="AO6">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AP6">
         <v>15</v>
@@ -2358,7 +2358,7 @@
         <v>11</v>
       </c>
       <c r="AT6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU6">
         <v>9.199999999999999</v>
@@ -2367,7 +2367,7 @@
         <v>24</v>
       </c>
       <c r="AW6">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="AX6">
         <v>7.6</v>
@@ -2379,7 +2379,7 @@
         <v>21</v>
       </c>
       <c r="BA6">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="BB6">
         <v>10.5</v>
@@ -2388,34 +2388,34 @@
         <v>13.5</v>
       </c>
       <c r="BD6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF6">
         <v>6.4</v>
       </c>
       <c r="BG6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH6">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI6">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BJ6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK6">
         <v>5.5</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN6">
         <v>4.1</v>
@@ -2424,7 +2424,7 @@
         <v>3.1</v>
       </c>
       <c r="BP6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BQ6">
         <v>5</v>
@@ -2433,28 +2433,28 @@
         <v>26</v>
       </c>
       <c r="BS6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT6">
         <v>12</v>
       </c>
       <c r="BU6">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV6">
         <v>75</v>
       </c>
       <c r="BW6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX6">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BY6">
         <v>9.199999999999999</v>
       </c>
       <c r="BZ6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA6">
         <v>6.4</v>
@@ -2498,7 +2498,7 @@
         <v>3.7</v>
       </c>
       <c r="L7">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M7">
         <v>1.1</v>
@@ -2525,7 +2525,7 @@
         <v>2.02</v>
       </c>
       <c r="U7">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V7">
         <v>1.2</v>
@@ -2722,61 +2722,61 @@
         <v>183</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="H8">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="I8">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="J8">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="K8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L8">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M8">
         <v>1.02</v>
       </c>
       <c r="N8">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O8">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P8">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q8">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="R8">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="S8">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="T8">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U8">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V8">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Y8">
         <v>14.5</v>
@@ -2788,34 +2788,34 @@
         <v>11.5</v>
       </c>
       <c r="AB8">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AC8">
         <v>19.5</v>
       </c>
       <c r="AD8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF8">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AG8">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AH8">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI8">
         <v>32</v>
       </c>
       <c r="AJ8">
-        <v>460</v>
+        <v>560</v>
       </c>
       <c r="AK8">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="AL8">
         <v>130</v>
@@ -2824,16 +2824,16 @@
         <v>130</v>
       </c>
       <c r="AN8">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AO8">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="AP8">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="AQ8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR8">
         <v>9</v>
@@ -2842,100 +2842,100 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AT8">
-        <v>7.6</v>
+        <v>50</v>
       </c>
       <c r="AU8">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AV8">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW8">
         <v>11</v>
       </c>
       <c r="AX8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY8">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="AZ8">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BA8">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BB8">
+        <v>9</v>
+      </c>
+      <c r="BC8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD8">
         <v>8.6</v>
       </c>
-      <c r="BC8">
-        <v>8.4</v>
-      </c>
-      <c r="BD8">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE8">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF8">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG8">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="BH8">
+        <v>5.6</v>
+      </c>
+      <c r="BI8">
+        <v>4.6</v>
+      </c>
+      <c r="BJ8">
+        <v>12.5</v>
+      </c>
+      <c r="BK8">
         <v>5.5</v>
       </c>
-      <c r="BI8">
-        <v>4.2</v>
-      </c>
-      <c r="BJ8">
-        <v>12</v>
-      </c>
-      <c r="BK8">
-        <v>5.6</v>
-      </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN8">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BO8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BP8">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT8">
         <v>4.3</v>
       </c>
       <c r="BU8">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="BV8">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BW8">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BY8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -3129,7 +3129,7 @@
         <v>3.85</v>
       </c>
       <c r="BI9">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="BJ9">
         <v>9.6</v>
@@ -3206,10 +3206,10 @@
         <v>185</v>
       </c>
       <c r="F10">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G10">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="H10">
         <v>4.7</v>
@@ -3218,13 +3218,13 @@
         <v>5.2</v>
       </c>
       <c r="J10">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K10">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L10">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="M10">
         <v>1.07</v>
@@ -3236,7 +3236,7 @@
         <v>1.34</v>
       </c>
       <c r="P10">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q10">
         <v>1.99</v>
@@ -3257,7 +3257,7 @@
         <v>1.24</v>
       </c>
       <c r="W10">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="X10">
         <v>16.5</v>
@@ -3269,22 +3269,22 @@
         <v>40</v>
       </c>
       <c r="AA10">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB10">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC10">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AE10">
         <v>70</v>
       </c>
       <c r="AF10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG10">
         <v>12</v>
@@ -3293,10 +3293,10 @@
         <v>21</v>
       </c>
       <c r="AI10">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ10">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK10">
         <v>22</v>
@@ -3305,10 +3305,10 @@
         <v>40</v>
       </c>
       <c r="AM10">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO10">
         <v>80</v>
@@ -3317,13 +3317,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ10">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AR10">
         <v>30</v>
       </c>
       <c r="AS10">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AT10">
         <v>7.8</v>
@@ -3332,7 +3332,7 @@
         <v>7.4</v>
       </c>
       <c r="AV10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW10">
         <v>50</v>
@@ -3350,7 +3350,7 @@
         <v>55</v>
       </c>
       <c r="BB10">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BC10">
         <v>18</v>
@@ -3359,7 +3359,7 @@
         <v>32</v>
       </c>
       <c r="BE10">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BF10">
         <v>12</v>
@@ -3457,13 +3457,13 @@
         <v>1.8</v>
       </c>
       <c r="I11">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="J11">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K11">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L11">
         <v>1.34</v>
@@ -3490,16 +3490,16 @@
         <v>3.15</v>
       </c>
       <c r="T11">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U11">
+        <v>2.06</v>
+      </c>
+      <c r="V11">
         <v>2.04</v>
       </c>
-      <c r="V11">
-        <v>2.02</v>
-      </c>
       <c r="W11">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X11">
         <v>16.5</v>
@@ -3514,13 +3514,13 @@
         <v>23</v>
       </c>
       <c r="AB11">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AC11">
         <v>9</v>
       </c>
       <c r="AD11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE11">
         <v>21</v>
@@ -3556,19 +3556,19 @@
         <v>13.5</v>
       </c>
       <c r="AP11">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AQ11">
         <v>7.2</v>
       </c>
       <c r="AR11">
-        <v>4.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS11">
         <v>16</v>
       </c>
       <c r="AT11">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AU11">
         <v>6.8</v>
@@ -3577,34 +3577,34 @@
         <v>8</v>
       </c>
       <c r="AW11">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="AX11">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AY11">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AZ11">
         <v>14</v>
       </c>
       <c r="BA11">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB11">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC11">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BD11">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE11">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF11">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG11">
         <v>9.6</v>
@@ -3690,82 +3690,82 @@
         <v>187</v>
       </c>
       <c r="F12">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="G12">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="H12">
+        <v>4.7</v>
+      </c>
+      <c r="I12">
+        <v>5.5</v>
+      </c>
+      <c r="J12">
+        <v>3.85</v>
+      </c>
+      <c r="K12">
         <v>4.4</v>
       </c>
-      <c r="I12">
-        <v>7</v>
-      </c>
-      <c r="J12">
-        <v>3.5</v>
-      </c>
-      <c r="K12">
-        <v>4.6</v>
-      </c>
       <c r="L12">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N12">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O12">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P12">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q12">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="R12">
         <v>1.41</v>
       </c>
       <c r="S12">
-        <v>2.58</v>
+        <v>3.05</v>
       </c>
       <c r="T12">
         <v>1.79</v>
       </c>
       <c r="U12">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V12">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W12">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="X12">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y12">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Z12">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AA12">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AB12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD12">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE12">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF12">
         <v>13</v>
@@ -3774,10 +3774,10 @@
         <v>12.5</v>
       </c>
       <c r="AH12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI12">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ12">
         <v>21</v>
@@ -3789,127 +3789,127 @@
         <v>42</v>
       </c>
       <c r="AM12">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN12">
         <v>11.5</v>
       </c>
       <c r="AO12">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AP12">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AQ12">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AR12">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AS12">
+        <v>4.9</v>
+      </c>
+      <c r="AT12">
+        <v>7</v>
+      </c>
+      <c r="AU12">
+        <v>3.45</v>
+      </c>
+      <c r="AV12">
+        <v>17.5</v>
+      </c>
+      <c r="AW12">
+        <v>4.8</v>
+      </c>
+      <c r="AX12">
+        <v>8.4</v>
+      </c>
+      <c r="AY12">
+        <v>7.6</v>
+      </c>
+      <c r="AZ12">
         <v>4.1</v>
       </c>
-      <c r="AT12">
-        <v>3.1</v>
-      </c>
-      <c r="AU12">
-        <v>3.1</v>
-      </c>
-      <c r="AV12">
-        <v>3.65</v>
-      </c>
-      <c r="AW12">
-        <v>4</v>
-      </c>
-      <c r="AX12">
-        <v>3.2</v>
-      </c>
-      <c r="AY12">
-        <v>3.15</v>
-      </c>
-      <c r="AZ12">
-        <v>3.6</v>
-      </c>
       <c r="BA12">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BB12">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BC12">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BD12">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BE12">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF12">
-        <v>3.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG12">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BH12">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BI12">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="BJ12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK12">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="BN12">
         <v>4.5</v>
       </c>
       <c r="BO12">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BP12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ12">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BR12">
         <v>26</v>
       </c>
       <c r="BS12">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BT12">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BU12">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>8.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="BX12">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>8.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="BZ12">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="CA12">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="CB12" t="s">
         <v>220</v>
@@ -3932,31 +3932,31 @@
         <v>188</v>
       </c>
       <c r="F13">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="G13">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="H13">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J13">
-        <v>2.52</v>
+        <v>3.35</v>
       </c>
       <c r="K13">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L13">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M13">
         <v>1.06</v>
       </c>
       <c r="N13">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O13">
         <v>1.3</v>
@@ -3965,13 +3965,13 @@
         <v>1.92</v>
       </c>
       <c r="Q13">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="R13">
         <v>1.36</v>
       </c>
       <c r="S13">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T13">
         <v>1.7</v>
@@ -3980,10 +3980,10 @@
         <v>2.14</v>
       </c>
       <c r="V13">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="X13">
         <v>18</v>
@@ -4174,22 +4174,22 @@
         <v>189</v>
       </c>
       <c r="F14">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="G14">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="H14">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="I14">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="J14">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K14">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="L14">
         <v>1.27</v>
@@ -4198,34 +4198,34 @@
         <v>1.05</v>
       </c>
       <c r="N14">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O14">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P14">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q14">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R14">
         <v>1.45</v>
       </c>
       <c r="S14">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="T14">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U14">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="V14">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
         <v>22</v>
@@ -4234,13 +4234,13 @@
         <v>8.6</v>
       </c>
       <c r="Z14">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AA14">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AB14">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AC14">
         <v>13</v>
@@ -4255,7 +4255,7 @@
         <v>110</v>
       </c>
       <c r="AG14">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AH14">
         <v>32</v>
@@ -4264,31 +4264,31 @@
         <v>44</v>
       </c>
       <c r="AJ14">
-        <v>440</v>
+        <v>560</v>
       </c>
       <c r="AK14">
         <v>200</v>
       </c>
       <c r="AL14">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="AM14">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="AN14">
-        <v>270</v>
+        <v>350</v>
       </c>
       <c r="AO14">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AP14">
         <v>14</v>
       </c>
       <c r="AQ14">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AR14">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="AS14">
         <v>8.6</v>
@@ -4306,22 +4306,22 @@
         <v>11.5</v>
       </c>
       <c r="AX14">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY14">
+        <v>6</v>
+      </c>
+      <c r="AZ14">
+        <v>5.6</v>
+      </c>
+      <c r="BA14">
         <v>5.9</v>
-      </c>
-      <c r="AZ14">
-        <v>5.7</v>
-      </c>
-      <c r="BA14">
-        <v>6</v>
       </c>
       <c r="BB14">
         <v>6.8</v>
       </c>
       <c r="BC14">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BD14">
         <v>6.6</v>
@@ -4330,22 +4330,22 @@
         <v>6.6</v>
       </c>
       <c r="BF14">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG14">
         <v>4.9</v>
       </c>
       <c r="BH14">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI14">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ14">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK14">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL14">
         <v>1000</v>
@@ -4354,10 +4354,10 @@
         <v>9.6</v>
       </c>
       <c r="BN14">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BO14">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BP14">
         <v>1000</v>
@@ -4372,28 +4372,28 @@
         <v>9</v>
       </c>
       <c r="BT14">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BU14">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BV14">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BW14">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BX14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY14">
         <v>7.2</v>
       </c>
       <c r="BZ14">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA14">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="CB14" t="s">
         <v>220</v>
@@ -4422,16 +4422,16 @@
         <v>4.5</v>
       </c>
       <c r="H15">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="I15">
         <v>2.08</v>
       </c>
       <c r="J15">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L15">
         <v>1.37</v>
@@ -4446,7 +4446,7 @@
         <v>1.28</v>
       </c>
       <c r="P15">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q15">
         <v>1.83</v>
@@ -4467,7 +4467,7 @@
         <v>1.92</v>
       </c>
       <c r="W15">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X15">
         <v>19</v>
@@ -4476,7 +4476,7 @@
         <v>10.5</v>
       </c>
       <c r="Z15">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA15">
         <v>28</v>
@@ -4485,7 +4485,7 @@
         <v>17</v>
       </c>
       <c r="AC15">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD15">
         <v>12.5</v>
@@ -4494,10 +4494,10 @@
         <v>21</v>
       </c>
       <c r="AF15">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AG15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH15">
         <v>21</v>
@@ -4512,16 +4512,16 @@
         <v>60</v>
       </c>
       <c r="AL15">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM15">
         <v>110</v>
       </c>
       <c r="AN15">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AO15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP15">
         <v>13</v>
@@ -4548,7 +4548,7 @@
         <v>17</v>
       </c>
       <c r="AX15">
-        <v>23</v>
+        <v>5.1</v>
       </c>
       <c r="AY15">
         <v>12.5</v>
@@ -4557,22 +4557,22 @@
         <v>15</v>
       </c>
       <c r="BA15">
-        <v>24</v>
+        <v>5.3</v>
       </c>
       <c r="BB15">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BC15">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BD15">
-        <v>40</v>
+        <v>5.5</v>
       </c>
       <c r="BE15">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF15">
-        <v>38</v>
+        <v>5.4</v>
       </c>
       <c r="BG15">
         <v>9.6</v>
@@ -4581,7 +4581,7 @@
         <v>3.7</v>
       </c>
       <c r="BI15">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ15">
         <v>10</v>
@@ -4623,7 +4623,7 @@
         <v>14.5</v>
       </c>
       <c r="BW15">
-        <v>9.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="BX15">
         <v>28</v>
@@ -4658,16 +4658,16 @@
         <v>191</v>
       </c>
       <c r="F16">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G16">
         <v>1.94</v>
       </c>
       <c r="H16">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I16">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J16">
         <v>4.3</v>
@@ -4676,7 +4676,7 @@
         <v>4.4</v>
       </c>
       <c r="L16">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M16">
         <v>1.04</v>
@@ -4685,40 +4685,40 @@
         <v>5.9</v>
       </c>
       <c r="O16">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P16">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="Q16">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R16">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S16">
         <v>2.38</v>
       </c>
       <c r="T16">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U16">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="V16">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W16">
         <v>2.06</v>
       </c>
       <c r="X16">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y16">
         <v>23</v>
       </c>
       <c r="Z16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA16">
         <v>75</v>
@@ -4733,10 +4733,10 @@
         <v>16.5</v>
       </c>
       <c r="AE16">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF16">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG16">
         <v>11</v>
@@ -4745,7 +4745,7 @@
         <v>15.5</v>
       </c>
       <c r="AI16">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ16">
         <v>23</v>
@@ -4760,7 +4760,7 @@
         <v>60</v>
       </c>
       <c r="AN16">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AO16">
         <v>27</v>
@@ -4772,7 +4772,7 @@
         <v>20</v>
       </c>
       <c r="AR16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS16">
         <v>34</v>
@@ -4823,22 +4823,22 @@
         <v>4.7</v>
       </c>
       <c r="BI16">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="BJ16">
         <v>9</v>
       </c>
       <c r="BK16">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL16">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
         <v>9</v>
       </c>
       <c r="BN16">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO16">
         <v>3.95</v>
@@ -4847,22 +4847,22 @@
         <v>13</v>
       </c>
       <c r="BQ16">
-        <v>9.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BR16">
         <v>22</v>
       </c>
       <c r="BS16">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT16">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU16">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV16">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW16">
         <v>7.4</v>
@@ -4871,7 +4871,7 @@
         <v>32</v>
       </c>
       <c r="BY16">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ16">
         <v>15</v>
@@ -4915,10 +4915,10 @@
         <v>4</v>
       </c>
       <c r="K17">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L17">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M17">
         <v>1.05</v>
@@ -4945,7 +4945,7 @@
         <v>1.7</v>
       </c>
       <c r="U17">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V17">
         <v>1.27</v>
@@ -4957,10 +4957,10 @@
         <v>21</v>
       </c>
       <c r="Y17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z17">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA17">
         <v>110</v>
@@ -4969,10 +4969,10 @@
         <v>11</v>
       </c>
       <c r="AC17">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD17">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE17">
         <v>55</v>
@@ -4984,7 +4984,7 @@
         <v>10</v>
       </c>
       <c r="AH17">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AI17">
         <v>55</v>
@@ -4996,31 +4996,31 @@
         <v>17.5</v>
       </c>
       <c r="AL17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM17">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN17">
         <v>9.199999999999999</v>
       </c>
       <c r="AO17">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP17">
         <v>16.5</v>
       </c>
       <c r="AQ17">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR17">
-        <v>9.6</v>
+        <v>32</v>
       </c>
       <c r="AS17">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AT17">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU17">
         <v>8.800000000000001</v>
@@ -5029,10 +5029,10 @@
         <v>16.5</v>
       </c>
       <c r="AW17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX17">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AY17">
         <v>9.199999999999999</v>
@@ -5041,25 +5041,25 @@
         <v>15.5</v>
       </c>
       <c r="BA17">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="BB17">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC17">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD17">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="BE17">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF17">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG17">
-        <v>9.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BH17">
         <v>4</v>
@@ -5071,7 +5071,7 @@
         <v>9.4</v>
       </c>
       <c r="BK17">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BL17">
         <v>95</v>
@@ -5151,7 +5151,7 @@
         <v>6.4</v>
       </c>
       <c r="I18">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="J18">
         <v>5.5</v>
@@ -5169,7 +5169,7 @@
         <v>7.8</v>
       </c>
       <c r="O18">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P18">
         <v>3.35</v>
@@ -5181,7 +5181,7 @@
         <v>1.97</v>
       </c>
       <c r="S18">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="T18">
         <v>1.59</v>
@@ -5190,7 +5190,7 @@
         <v>2.5</v>
       </c>
       <c r="V18">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W18">
         <v>3</v>
@@ -5208,10 +5208,10 @@
         <v>190</v>
       </c>
       <c r="AB18">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AC18">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AD18">
         <v>32</v>
@@ -5220,10 +5220,10 @@
         <v>85</v>
       </c>
       <c r="AF18">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AG18">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH18">
         <v>23</v>
@@ -5232,13 +5232,13 @@
         <v>65</v>
       </c>
       <c r="AJ18">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK18">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AL18">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AM18">
         <v>75</v>
@@ -5250,16 +5250,16 @@
         <v>60</v>
       </c>
       <c r="AP18">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AQ18">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AR18">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS18">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AT18">
         <v>12.5</v>
@@ -5271,7 +5271,7 @@
         <v>21</v>
       </c>
       <c r="AW18">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX18">
         <v>10</v>
@@ -5283,7 +5283,7 @@
         <v>15</v>
       </c>
       <c r="BA18">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BB18">
         <v>11.5</v>
@@ -5295,19 +5295,19 @@
         <v>18</v>
       </c>
       <c r="BE18">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BF18">
         <v>3.35</v>
       </c>
       <c r="BG18">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BH18">
         <v>5.6</v>
       </c>
       <c r="BI18">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BJ18">
         <v>9.6</v>
@@ -5319,7 +5319,7 @@
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN18">
         <v>4.8</v>
@@ -5337,13 +5337,13 @@
         <v>970</v>
       </c>
       <c r="BS18">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT18">
         <v>11.5</v>
       </c>
       <c r="BU18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV18">
         <v>1000</v>
@@ -5384,16 +5384,16 @@
         <v>194</v>
       </c>
       <c r="F19">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G19">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="H19">
         <v>5.1</v>
       </c>
       <c r="I19">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -5405,7 +5405,7 @@
         <v>1.31</v>
       </c>
       <c r="M19">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N19">
         <v>4.2</v>
@@ -5414,7 +5414,7 @@
         <v>1.27</v>
       </c>
       <c r="P19">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q19">
         <v>1.79</v>
@@ -5450,7 +5450,7 @@
         <v>140</v>
       </c>
       <c r="AB19">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC19">
         <v>11</v>
@@ -5477,7 +5477,7 @@
         <v>21</v>
       </c>
       <c r="AK19">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AL19">
         <v>38</v>
@@ -5486,7 +5486,7 @@
         <v>110</v>
       </c>
       <c r="AN19">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AO19">
         <v>80</v>
@@ -5498,10 +5498,10 @@
         <v>15</v>
       </c>
       <c r="AR19">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS19">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AT19">
         <v>8.6</v>
@@ -5513,7 +5513,7 @@
         <v>15.5</v>
       </c>
       <c r="AW19">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX19">
         <v>9.800000000000001</v>
@@ -5525,31 +5525,31 @@
         <v>16.5</v>
       </c>
       <c r="BA19">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB19">
         <v>15.5</v>
       </c>
       <c r="BC19">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD19">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE19">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF19">
         <v>8.6</v>
       </c>
       <c r="BG19">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH19">
         <v>3.75</v>
       </c>
       <c r="BI19">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ19">
         <v>9.800000000000001</v>
@@ -5632,7 +5632,7 @@
         <v>3.05</v>
       </c>
       <c r="H20">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I20">
         <v>2.9</v>
@@ -5644,34 +5644,34 @@
         <v>3.3</v>
       </c>
       <c r="L20">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M20">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N20">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O20">
         <v>1.43</v>
       </c>
       <c r="P20">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q20">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R20">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T20">
         <v>1.9</v>
       </c>
       <c r="U20">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V20">
         <v>1.52</v>
@@ -5686,7 +5686,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z20">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AA20">
         <v>55</v>
@@ -5695,10 +5695,10 @@
         <v>11.5</v>
       </c>
       <c r="AC20">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD20">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE20">
         <v>36</v>
@@ -5710,7 +5710,7 @@
         <v>15</v>
       </c>
       <c r="AH20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI20">
         <v>65</v>
@@ -5734,31 +5734,31 @@
         <v>36</v>
       </c>
       <c r="AP20">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ20">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR20">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS20">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT20">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU20">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV20">
         <v>11</v>
       </c>
       <c r="AW20">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AX20">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY20">
         <v>11.5</v>
@@ -5767,25 +5767,25 @@
         <v>17</v>
       </c>
       <c r="BA20">
+        <v>6.2</v>
+      </c>
+      <c r="BB20">
+        <v>6.2</v>
+      </c>
+      <c r="BC20">
+        <v>6</v>
+      </c>
+      <c r="BD20">
+        <v>6.2</v>
+      </c>
+      <c r="BE20">
+        <v>6.6</v>
+      </c>
+      <c r="BF20">
+        <v>6</v>
+      </c>
+      <c r="BG20">
         <v>5.9</v>
-      </c>
-      <c r="BB20">
-        <v>6</v>
-      </c>
-      <c r="BC20">
-        <v>5.7</v>
-      </c>
-      <c r="BD20">
-        <v>6</v>
-      </c>
-      <c r="BE20">
-        <v>6.2</v>
-      </c>
-      <c r="BF20">
-        <v>32</v>
-      </c>
-      <c r="BG20">
-        <v>5.6</v>
       </c>
       <c r="BH20">
         <v>3</v>
@@ -5877,13 +5877,13 @@
         <v>3.45</v>
       </c>
       <c r="I21">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J21">
         <v>3.75</v>
       </c>
       <c r="K21">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L21">
         <v>1.28</v>
@@ -5892,22 +5892,22 @@
         <v>1.05</v>
       </c>
       <c r="N21">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O21">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P21">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q21">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R21">
         <v>1.45</v>
       </c>
       <c r="S21">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="T21">
         <v>1.65</v>
@@ -5916,7 +5916,7 @@
         <v>2.3</v>
       </c>
       <c r="V21">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W21">
         <v>1.84</v>
@@ -5943,19 +5943,19 @@
         <v>19</v>
       </c>
       <c r="AE21">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AF21">
         <v>17.5</v>
       </c>
       <c r="AG21">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH21">
         <v>20</v>
       </c>
       <c r="AI21">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ21">
         <v>32</v>
@@ -5997,7 +5997,7 @@
         <v>11.5</v>
       </c>
       <c r="AW21">
-        <v>32</v>
+        <v>3.9</v>
       </c>
       <c r="AX21">
         <v>10.5</v>
@@ -6015,10 +6015,10 @@
         <v>18</v>
       </c>
       <c r="BC21">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BD21">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BE21">
         <v>4</v>
@@ -6027,25 +6027,25 @@
         <v>9</v>
       </c>
       <c r="BG21">
-        <v>24</v>
+        <v>3.85</v>
       </c>
       <c r="BH21">
         <v>4</v>
       </c>
       <c r="BI21">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BJ21">
         <v>9.4</v>
       </c>
       <c r="BK21">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN21">
         <v>5.3</v>
@@ -6054,7 +6054,7 @@
         <v>3.9</v>
       </c>
       <c r="BP21">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ21">
         <v>6</v>
@@ -6075,13 +6075,13 @@
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ21">
         <v>20</v>
@@ -6110,31 +6110,31 @@
         <v>197</v>
       </c>
       <c r="F22">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="G22">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H22">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="I22">
         <v>2.68</v>
       </c>
       <c r="J22">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K22">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L22">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M22">
         <v>1.05</v>
       </c>
       <c r="N22">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O22">
         <v>1.25</v>
@@ -6143,13 +6143,13 @@
         <v>2.16</v>
       </c>
       <c r="Q22">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R22">
         <v>1.45</v>
       </c>
       <c r="S22">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T22">
         <v>1.62</v>
@@ -6158,10 +6158,10 @@
         <v>2.42</v>
       </c>
       <c r="V22">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W22">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X22">
         <v>19</v>
@@ -6182,7 +6182,7 @@
         <v>9</v>
       </c>
       <c r="AD22">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE22">
         <v>28</v>
@@ -6197,7 +6197,7 @@
         <v>16.5</v>
       </c>
       <c r="AI22">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ22">
         <v>50</v>
@@ -6206,7 +6206,7 @@
         <v>32</v>
       </c>
       <c r="AL22">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM22">
         <v>75</v>
@@ -6215,7 +6215,7 @@
         <v>25</v>
       </c>
       <c r="AO22">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AP22">
         <v>15.5</v>
@@ -6227,7 +6227,7 @@
         <v>15.5</v>
       </c>
       <c r="AS22">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT22">
         <v>11.5</v>
@@ -6251,19 +6251,19 @@
         <v>13</v>
       </c>
       <c r="BA22">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB22">
+        <v>6.4</v>
+      </c>
+      <c r="BC22">
         <v>6</v>
       </c>
-      <c r="BC22">
-        <v>5.6</v>
-      </c>
       <c r="BD22">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE22">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF22">
         <v>16.5</v>
@@ -6352,7 +6352,7 @@
         <v>198</v>
       </c>
       <c r="F23">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G23">
         <v>3.05</v>
@@ -6382,10 +6382,10 @@
         <v>1.19</v>
       </c>
       <c r="P23">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q23">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R23">
         <v>1.62</v>
@@ -6394,7 +6394,7 @@
         <v>2.42</v>
       </c>
       <c r="T23">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U23">
         <v>2.64</v>
@@ -6406,13 +6406,13 @@
         <v>1.48</v>
       </c>
       <c r="X23">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y23">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z23">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AA23">
         <v>40</v>
@@ -6424,22 +6424,22 @@
         <v>12.5</v>
       </c>
       <c r="AD23">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AE23">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF23">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AG23">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH23">
         <v>18</v>
       </c>
       <c r="AI23">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ23">
         <v>55</v>
@@ -6460,52 +6460,52 @@
         <v>16</v>
       </c>
       <c r="AP23">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AQ23">
         <v>13.5</v>
       </c>
       <c r="AR23">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AS23">
         <v>24</v>
       </c>
       <c r="AT23">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AU23">
         <v>8.800000000000001</v>
       </c>
       <c r="AV23">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AW23">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX23">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AY23">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ23">
         <v>13</v>
       </c>
       <c r="BA23">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB23">
-        <v>4.6</v>
+        <v>32</v>
       </c>
       <c r="BC23">
         <v>20</v>
       </c>
       <c r="BD23">
-        <v>22</v>
+        <v>3.6</v>
       </c>
       <c r="BE23">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="BF23">
         <v>12.5</v>
@@ -6514,22 +6514,22 @@
         <v>11</v>
       </c>
       <c r="BH23">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI23">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ23">
         <v>8.6</v>
       </c>
       <c r="BK23">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN23">
         <v>6.6</v>
@@ -6541,13 +6541,13 @@
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BT23">
         <v>5.9</v>
@@ -6559,19 +6559,19 @@
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ23">
         <v>16</v>
       </c>
       <c r="CA23">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB23" t="s">
         <v>220</v>
@@ -6597,13 +6597,13 @@
         <v>2.3</v>
       </c>
       <c r="G24">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H24">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I24">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J24">
         <v>3.6</v>
@@ -6618,7 +6618,7 @@
         <v>1.05</v>
       </c>
       <c r="N24">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O24">
         <v>1.26</v>
@@ -6636,7 +6636,7 @@
         <v>2.94</v>
       </c>
       <c r="T24">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U24">
         <v>2.3</v>
@@ -6645,7 +6645,7 @@
         <v>1.43</v>
       </c>
       <c r="W24">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X24">
         <v>21</v>
@@ -6657,7 +6657,7 @@
         <v>27</v>
       </c>
       <c r="AA24">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB24">
         <v>14</v>
@@ -6666,10 +6666,10 @@
         <v>10</v>
       </c>
       <c r="AD24">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE24">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF24">
         <v>19.5</v>
@@ -6696,7 +6696,7 @@
         <v>85</v>
       </c>
       <c r="AN24">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO24">
         <v>32</v>
@@ -6705,7 +6705,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ24">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR24">
         <v>17.5</v>
@@ -6723,7 +6723,7 @@
         <v>10.5</v>
       </c>
       <c r="AW24">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX24">
         <v>12.5</v>
@@ -6735,7 +6735,7 @@
         <v>12</v>
       </c>
       <c r="BA24">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB24">
         <v>4.5</v>
@@ -6744,34 +6744,34 @@
         <v>18</v>
       </c>
       <c r="BD24">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE24">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF24">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BG24">
         <v>20</v>
       </c>
       <c r="BH24">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI24">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BJ24">
         <v>9</v>
       </c>
       <c r="BK24">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN24">
         <v>5.5</v>
@@ -6783,13 +6783,13 @@
         <v>17</v>
       </c>
       <c r="BQ24">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR24">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT24">
         <v>6.6</v>
@@ -6798,10 +6798,10 @@
         <v>5.1</v>
       </c>
       <c r="BV24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW24">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX24">
         <v>1000</v>
@@ -6836,16 +6836,16 @@
         <v>200</v>
       </c>
       <c r="F25">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="G25">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="H25">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="I25">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="J25">
         <v>2.64</v>
@@ -6857,25 +6857,25 @@
         <v>1.53</v>
       </c>
       <c r="M25">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N25">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O25">
         <v>1.55</v>
       </c>
       <c r="P25">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q25">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R25">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S25">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="T25">
         <v>2.12</v>
@@ -6884,16 +6884,16 @@
         <v>1.69</v>
       </c>
       <c r="V25">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="W25">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X25">
         <v>9.199999999999999</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z25">
         <v>15.5</v>
@@ -6905,7 +6905,7 @@
         <v>12</v>
       </c>
       <c r="AC25">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD25">
         <v>14.5</v>
@@ -6923,7 +6923,7 @@
         <v>29</v>
       </c>
       <c r="AI25">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ25">
         <v>110</v>
@@ -6944,58 +6944,58 @@
         <v>46</v>
       </c>
       <c r="AP25">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AQ25">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AR25">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AS25">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AT25">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AU25">
         <v>3.2</v>
       </c>
       <c r="AV25">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AW25">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AX25">
+        <v>4.5</v>
+      </c>
+      <c r="AY25">
+        <v>4.2</v>
+      </c>
+      <c r="AZ25">
+        <v>4.5</v>
+      </c>
+      <c r="BA25">
+        <v>5</v>
+      </c>
+      <c r="BB25">
+        <v>5.1</v>
+      </c>
+      <c r="BC25">
+        <v>5</v>
+      </c>
+      <c r="BD25">
+        <v>5.1</v>
+      </c>
+      <c r="BE25">
+        <v>5.2</v>
+      </c>
+      <c r="BF25">
+        <v>5.1</v>
+      </c>
+      <c r="BG25">
         <v>4.7</v>
-      </c>
-      <c r="AY25">
-        <v>4.4</v>
-      </c>
-      <c r="AZ25">
-        <v>4.6</v>
-      </c>
-      <c r="BA25">
-        <v>5.1</v>
-      </c>
-      <c r="BB25">
-        <v>5.3</v>
-      </c>
-      <c r="BC25">
-        <v>5.2</v>
-      </c>
-      <c r="BD25">
-        <v>5.3</v>
-      </c>
-      <c r="BE25">
-        <v>5.4</v>
-      </c>
-      <c r="BF25">
-        <v>5.3</v>
-      </c>
-      <c r="BG25">
-        <v>4.9</v>
       </c>
       <c r="BH25">
         <v>2.72</v>
@@ -7078,10 +7078,10 @@
         <v>201</v>
       </c>
       <c r="F26">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="G26">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="H26">
         <v>2.62</v>
@@ -7099,13 +7099,13 @@
         <v>1.6</v>
       </c>
       <c r="M26">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N26">
         <v>2.06</v>
       </c>
       <c r="O26">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="P26">
         <v>1.38</v>
@@ -7117,7 +7117,7 @@
         <v>1.13</v>
       </c>
       <c r="S26">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="T26">
         <v>2.28</v>
@@ -7129,7 +7129,7 @@
         <v>1.43</v>
       </c>
       <c r="W26">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X26">
         <v>7.8</v>
@@ -7144,13 +7144,13 @@
         <v>70</v>
       </c>
       <c r="AB26">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC26">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AD26">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE26">
         <v>65</v>
@@ -7159,10 +7159,10 @@
         <v>21</v>
       </c>
       <c r="AG26">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AH26">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AI26">
         <v>110</v>
@@ -7186,58 +7186,58 @@
         <v>90</v>
       </c>
       <c r="AP26">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="AQ26">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="AR26">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AS26">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="AT26">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="AU26">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="AV26">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AW26">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX26">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="AY26">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AZ26">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BA26">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BB26">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC26">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BD26">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BE26">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BF26">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BG26">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH26">
         <v>2.5</v>
@@ -7320,28 +7320,28 @@
         <v>202</v>
       </c>
       <c r="F27">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="G27">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="H27">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I27">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J27">
-        <v>2.82</v>
+        <v>2.52</v>
       </c>
       <c r="K27">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="L27">
         <v>1.49</v>
       </c>
       <c r="M27">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N27">
         <v>2.4</v>
@@ -7362,22 +7362,22 @@
         <v>1.05</v>
       </c>
       <c r="T27">
-        <v>2.32</v>
+        <v>1.94</v>
       </c>
       <c r="U27">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="V27">
         <v>1.13</v>
       </c>
       <c r="W27">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="X27">
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z27">
         <v>65</v>
@@ -7389,31 +7389,31 @@
         <v>6.8</v>
       </c>
       <c r="AC27">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD27">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="AE27">
         <v>180</v>
       </c>
       <c r="AF27">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AG27">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH27">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="AI27">
         <v>210</v>
       </c>
       <c r="AJ27">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK27">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AL27">
         <v>85</v>
@@ -7422,64 +7422,64 @@
         <v>370</v>
       </c>
       <c r="AN27">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AO27">
         <v>370</v>
       </c>
       <c r="AP27">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="AQ27">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AR27">
+        <v>5.9</v>
+      </c>
+      <c r="AS27">
+        <v>6.2</v>
+      </c>
+      <c r="AT27">
+        <v>3.3</v>
+      </c>
+      <c r="AU27">
+        <v>3.65</v>
+      </c>
+      <c r="AV27">
+        <v>5.3</v>
+      </c>
+      <c r="AW27">
+        <v>6.2</v>
+      </c>
+      <c r="AX27">
+        <v>3.85</v>
+      </c>
+      <c r="AY27">
         <v>4.2</v>
       </c>
-      <c r="AS27">
-        <v>4.4</v>
-      </c>
-      <c r="AT27">
-        <v>2.72</v>
-      </c>
-      <c r="AU27">
-        <v>3.1</v>
-      </c>
-      <c r="AV27">
-        <v>3.95</v>
-      </c>
-      <c r="AW27">
-        <v>4.4</v>
-      </c>
-      <c r="AX27">
-        <v>3.2</v>
-      </c>
-      <c r="AY27">
-        <v>3.4</v>
-      </c>
       <c r="AZ27">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="BA27">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB27">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="BC27">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BD27">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BE27">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF27">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="BG27">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH27">
         <v>2.76</v>
@@ -7807,10 +7807,10 @@
         <v>1.59</v>
       </c>
       <c r="G29">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H29">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I29">
         <v>6.8</v>
@@ -7828,7 +7828,7 @@
         <v>1.06</v>
       </c>
       <c r="N29">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O29">
         <v>1.28</v>
@@ -7837,16 +7837,16 @@
         <v>2</v>
       </c>
       <c r="Q29">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R29">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S29">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T29">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U29">
         <v>1.94</v>
@@ -7855,7 +7855,7 @@
         <v>1.17</v>
       </c>
       <c r="W29">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X29">
         <v>20</v>
@@ -7864,7 +7864,7 @@
         <v>22</v>
       </c>
       <c r="Z29">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA29">
         <v>220</v>
@@ -7891,7 +7891,7 @@
         <v>950</v>
       </c>
       <c r="AI29">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ29">
         <v>16</v>
@@ -7924,7 +7924,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AT29">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU29">
         <v>8.199999999999999</v>
@@ -7942,7 +7942,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ29">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA29">
         <v>7.8</v>
@@ -7954,7 +7954,7 @@
         <v>14.5</v>
       </c>
       <c r="BD29">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="BE29">
         <v>8</v>
@@ -8046,37 +8046,37 @@
         <v>205</v>
       </c>
       <c r="F30">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G30">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H30">
         <v>2.4</v>
       </c>
       <c r="I30">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J30">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K30">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L30">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M30">
         <v>1.08</v>
       </c>
       <c r="N30">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O30">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P30">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q30">
         <v>2.1</v>
@@ -8085,19 +8085,19 @@
         <v>1.3</v>
       </c>
       <c r="S30">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T30">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U30">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V30">
         <v>1.63</v>
       </c>
       <c r="W30">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X30">
         <v>13</v>
@@ -8121,7 +8121,7 @@
         <v>12</v>
       </c>
       <c r="AE30">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF30">
         <v>23</v>
@@ -8133,7 +8133,7 @@
         <v>18.5</v>
       </c>
       <c r="AI30">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ30">
         <v>60</v>
@@ -8145,13 +8145,13 @@
         <v>55</v>
       </c>
       <c r="AM30">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN30">
         <v>44</v>
       </c>
       <c r="AO30">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP30">
         <v>9.6</v>
@@ -8163,7 +8163,7 @@
         <v>12</v>
       </c>
       <c r="AS30">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AT30">
         <v>9</v>
@@ -8190,19 +8190,19 @@
         <v>32</v>
       </c>
       <c r="BB30">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BC30">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BD30">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BE30">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF30">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BG30">
         <v>21</v>
@@ -8294,13 +8294,13 @@
         <v>1.93</v>
       </c>
       <c r="H31">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="I31">
         <v>5</v>
       </c>
       <c r="J31">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K31">
         <v>4.8</v>
@@ -8312,7 +8312,7 @@
         <v>1.01</v>
       </c>
       <c r="N31">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="O31">
         <v>1.17</v>
@@ -8327,13 +8327,13 @@
         <v>1.59</v>
       </c>
       <c r="S31">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="T31">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="U31">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="V31">
         <v>1.25</v>
@@ -8345,13 +8345,13 @@
         <v>28</v>
       </c>
       <c r="Y31">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="Z31">
         <v>50</v>
       </c>
       <c r="AA31">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB31">
         <v>14</v>
@@ -8363,7 +8363,7 @@
         <v>19.5</v>
       </c>
       <c r="AE31">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AF31">
         <v>15</v>
@@ -8375,10 +8375,10 @@
         <v>17.5</v>
       </c>
       <c r="AI31">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AJ31">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AK31">
         <v>18</v>
@@ -8387,7 +8387,7 @@
         <v>28</v>
       </c>
       <c r="AM31">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AN31">
         <v>8.199999999999999</v>
@@ -8396,64 +8396,64 @@
         <v>48</v>
       </c>
       <c r="AP31">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AQ31">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR31">
+        <v>6.4</v>
+      </c>
+      <c r="AS31">
+        <v>7.2</v>
+      </c>
+      <c r="AT31">
+        <v>5</v>
+      </c>
+      <c r="AU31">
+        <v>4.6</v>
+      </c>
+      <c r="AV31">
+        <v>5.5</v>
+      </c>
+      <c r="AW31">
+        <v>6.6</v>
+      </c>
+      <c r="AX31">
         <v>5.1</v>
       </c>
-      <c r="AS31">
-        <v>5.6</v>
-      </c>
-      <c r="AT31">
+      <c r="AY31">
+        <v>4.6</v>
+      </c>
+      <c r="AZ31">
+        <v>5.4</v>
+      </c>
+      <c r="BA31">
+        <v>6.6</v>
+      </c>
+      <c r="BB31">
+        <v>5.7</v>
+      </c>
+      <c r="BC31">
+        <v>5.4</v>
+      </c>
+      <c r="BD31">
+        <v>6</v>
+      </c>
+      <c r="BE31">
+        <v>7</v>
+      </c>
+      <c r="BF31">
         <v>4</v>
       </c>
-      <c r="AU31">
-        <v>3.8</v>
-      </c>
-      <c r="AV31">
-        <v>4.4</v>
-      </c>
-      <c r="AW31">
-        <v>5.2</v>
-      </c>
-      <c r="AX31">
-        <v>4.1</v>
-      </c>
-      <c r="AY31">
-        <v>3.8</v>
-      </c>
-      <c r="AZ31">
-        <v>4.2</v>
-      </c>
-      <c r="BA31">
-        <v>5</v>
-      </c>
-      <c r="BB31">
-        <v>4.7</v>
-      </c>
-      <c r="BC31">
-        <v>4.3</v>
-      </c>
-      <c r="BD31">
-        <v>4.7</v>
-      </c>
-      <c r="BE31">
-        <v>5.3</v>
-      </c>
-      <c r="BF31">
-        <v>3.35</v>
-      </c>
       <c r="BG31">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BH31">
         <v>4.8</v>
       </c>
       <c r="BI31">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="BJ31">
         <v>9.4</v>
@@ -8471,7 +8471,7 @@
         <v>5.2</v>
       </c>
       <c r="BO31">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BP31">
         <v>12</v>
@@ -8498,7 +8498,7 @@
         <v>6.8</v>
       </c>
       <c r="BX31">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY31">
         <v>7</v>
@@ -8539,10 +8539,10 @@
         <v>6</v>
       </c>
       <c r="I32">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J32">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K32">
         <v>4.4</v>
@@ -8560,13 +8560,13 @@
         <v>1.32</v>
       </c>
       <c r="P32">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q32">
         <v>1.95</v>
       </c>
       <c r="R32">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S32">
         <v>3.45</v>
@@ -8575,79 +8575,79 @@
         <v>1.96</v>
       </c>
       <c r="U32">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V32">
         <v>1.16</v>
       </c>
       <c r="W32">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X32">
         <v>17.5</v>
       </c>
       <c r="Y32">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="Z32">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA32">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AB32">
+        <v>8</v>
+      </c>
+      <c r="AC32">
         <v>9.4</v>
       </c>
-      <c r="AC32">
-        <v>11.5</v>
-      </c>
       <c r="AD32">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AE32">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF32">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG32">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH32">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AI32">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ32">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AK32">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AL32">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM32">
+        <v>170</v>
+      </c>
+      <c r="AN32">
+        <v>11</v>
+      </c>
+      <c r="AO32">
         <v>160</v>
       </c>
-      <c r="AN32">
-        <v>12</v>
-      </c>
-      <c r="AO32">
-        <v>150</v>
-      </c>
       <c r="AP32">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ32">
-        <v>3.95</v>
+        <v>17</v>
       </c>
       <c r="AR32">
-        <v>34</v>
+        <v>8.4</v>
       </c>
       <c r="AS32">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT32">
         <v>7</v>
@@ -8656,40 +8656,40 @@
         <v>8</v>
       </c>
       <c r="AV32">
-        <v>21</v>
+        <v>7.2</v>
       </c>
       <c r="AW32">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX32">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY32">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ32">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="BA32">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB32">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC32">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="BD32">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="BE32">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF32">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BG32">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH32">
         <v>3.45</v>
@@ -9017,7 +9017,7 @@
         <v>1.76</v>
       </c>
       <c r="G34">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H34">
         <v>5.8</v>
@@ -9032,19 +9032,19 @@
         <v>3.65</v>
       </c>
       <c r="L34">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="M34">
         <v>1.12</v>
       </c>
       <c r="N34">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O34">
         <v>1.51</v>
       </c>
       <c r="P34">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="Q34">
         <v>2.52</v>
@@ -9059,13 +9059,13 @@
         <v>2.26</v>
       </c>
       <c r="U34">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V34">
         <v>1.17</v>
       </c>
       <c r="W34">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X34">
         <v>9.4</v>
@@ -9119,7 +9119,7 @@
         <v>21</v>
       </c>
       <c r="AO34">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AP34">
         <v>6.8</v>
@@ -9134,7 +9134,7 @@
         <v>11</v>
       </c>
       <c r="AT34">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU34">
         <v>6</v>
@@ -9164,7 +9164,7 @@
         <v>18</v>
       </c>
       <c r="BD34">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="BE34">
         <v>11</v>
@@ -9259,19 +9259,19 @@
         <v>4.2</v>
       </c>
       <c r="G35">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H35">
         <v>1.96</v>
       </c>
       <c r="I35">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="J35">
         <v>3.15</v>
       </c>
       <c r="K35">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L35">
         <v>1.46</v>
@@ -9283,13 +9283,13 @@
         <v>2.96</v>
       </c>
       <c r="O35">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P35">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q35">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R35">
         <v>1.24</v>
@@ -9304,7 +9304,7 @@
         <v>1.84</v>
       </c>
       <c r="V35">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="W35">
         <v>1.26</v>
@@ -9498,19 +9498,19 @@
         <v>211</v>
       </c>
       <c r="F36">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="G36">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="H36">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I36">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J36">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="K36">
         <v>6.2</v>
@@ -9522,16 +9522,16 @@
         <v>1.01</v>
       </c>
       <c r="N36">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="O36">
         <v>1.21</v>
       </c>
       <c r="P36">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q36">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R36">
         <v>1.53</v>
@@ -9540,7 +9540,7 @@
         <v>2.58</v>
       </c>
       <c r="T36">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U36">
         <v>1.83</v>
@@ -9549,7 +9549,7 @@
         <v>1.07</v>
       </c>
       <c r="W36">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="X36">
         <v>28</v>
@@ -9558,25 +9558,25 @@
         <v>44</v>
       </c>
       <c r="Z36">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA36">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="AB36">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC36">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD36">
         <v>48</v>
       </c>
       <c r="AE36">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AF36">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG36">
         <v>13</v>
@@ -9588,10 +9588,10 @@
         <v>160</v>
       </c>
       <c r="AJ36">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AK36">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL36">
         <v>44</v>
@@ -9600,64 +9600,64 @@
         <v>180</v>
       </c>
       <c r="AN36">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AO36">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AP36">
+        <v>3.85</v>
+      </c>
+      <c r="AQ36">
+        <v>4</v>
+      </c>
+      <c r="AR36">
+        <v>4.3</v>
+      </c>
+      <c r="AS36">
+        <v>4.4</v>
+      </c>
+      <c r="AT36">
+        <v>3.2</v>
+      </c>
+      <c r="AU36">
+        <v>3.5</v>
+      </c>
+      <c r="AV36">
         <v>4.1</v>
       </c>
-      <c r="AQ36">
+      <c r="AW36">
         <v>4.4</v>
       </c>
-      <c r="AR36">
-        <v>4.7</v>
-      </c>
-      <c r="AS36">
-        <v>4.8</v>
-      </c>
-      <c r="AT36">
-        <v>3.4</v>
-      </c>
-      <c r="AU36">
-        <v>3.7</v>
-      </c>
-      <c r="AV36">
+      <c r="AX36">
+        <v>3.15</v>
+      </c>
+      <c r="AY36">
+        <v>3.35</v>
+      </c>
+      <c r="AZ36">
+        <v>3.95</v>
+      </c>
+      <c r="BA36">
+        <v>4.3</v>
+      </c>
+      <c r="BB36">
+        <v>3.35</v>
+      </c>
+      <c r="BC36">
+        <v>3.55</v>
+      </c>
+      <c r="BD36">
+        <v>4</v>
+      </c>
+      <c r="BE36">
         <v>4.4</v>
       </c>
-      <c r="AW36">
-        <v>4.8</v>
-      </c>
-      <c r="AX36">
-        <v>3.3</v>
-      </c>
-      <c r="AY36">
-        <v>3.55</v>
-      </c>
-      <c r="AZ36">
-        <v>4.3</v>
-      </c>
-      <c r="BA36">
-        <v>4.7</v>
-      </c>
-      <c r="BB36">
-        <v>3.5</v>
-      </c>
-      <c r="BC36">
-        <v>3.85</v>
-      </c>
-      <c r="BD36">
+      <c r="BF36">
+        <v>2.6</v>
+      </c>
+      <c r="BG36">
         <v>4.4</v>
-      </c>
-      <c r="BE36">
-        <v>4.7</v>
-      </c>
-      <c r="BF36">
-        <v>2.7</v>
-      </c>
-      <c r="BG36">
-        <v>4.8</v>
       </c>
       <c r="BH36">
         <v>4.3</v>
@@ -9666,10 +9666,10 @@
         <v>3.2</v>
       </c>
       <c r="BJ36">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK36">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL36">
         <v>1000</v>
@@ -9678,13 +9678,13 @@
         <v>1.75</v>
       </c>
       <c r="BN36">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BO36">
         <v>3</v>
       </c>
       <c r="BP36">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BQ36">
         <v>4.8</v>
@@ -9693,13 +9693,13 @@
         <v>24</v>
       </c>
       <c r="BS36">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT36">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BU36">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV36">
         <v>1000</v>
@@ -9714,7 +9714,7 @@
         <v>2.9</v>
       </c>
       <c r="BZ36">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CA36">
         <v>6.2</v>
@@ -9740,7 +9740,7 @@
         <v>212</v>
       </c>
       <c r="F37">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="G37">
         <v>2.06</v>
@@ -9758,7 +9758,7 @@
         <v>3.85</v>
       </c>
       <c r="L37">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="M37">
         <v>1.08</v>
@@ -9770,7 +9770,7 @@
         <v>1.37</v>
       </c>
       <c r="P37">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="Q37">
         <v>2.12</v>
@@ -9782,7 +9782,7 @@
         <v>3.85</v>
       </c>
       <c r="T37">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U37">
         <v>1.94</v>
@@ -9845,7 +9845,7 @@
         <v>18.5</v>
       </c>
       <c r="AO37">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AP37">
         <v>10</v>
@@ -9857,19 +9857,19 @@
         <v>5.9</v>
       </c>
       <c r="AS37">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT37">
         <v>6.8</v>
       </c>
       <c r="AU37">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV37">
         <v>15.5</v>
       </c>
       <c r="AW37">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX37">
         <v>10</v>
@@ -9893,7 +9893,7 @@
         <v>6</v>
       </c>
       <c r="BE37">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF37">
         <v>12.5</v>
@@ -9905,7 +9905,7 @@
         <v>3.25</v>
       </c>
       <c r="BI37">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="BJ37">
         <v>11</v>
@@ -10000,7 +10000,7 @@
         <v>3.55</v>
       </c>
       <c r="L38">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="M38">
         <v>1.09</v>
@@ -10024,13 +10024,13 @@
         <v>4.3</v>
       </c>
       <c r="T38">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U38">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="V38">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W38">
         <v>1.85</v>
@@ -10051,7 +10051,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC38">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD38">
         <v>18.5</v>
@@ -10069,16 +10069,16 @@
         <v>21</v>
       </c>
       <c r="AI38">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ38">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK38">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL38">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM38">
         <v>150</v>
@@ -10096,10 +10096,10 @@
         <v>10</v>
       </c>
       <c r="AR38">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS38">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT38">
         <v>6.8</v>
@@ -10111,7 +10111,7 @@
         <v>13.5</v>
       </c>
       <c r="AW38">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX38">
         <v>10</v>
@@ -10123,25 +10123,25 @@
         <v>17</v>
       </c>
       <c r="BA38">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB38">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC38">
         <v>21</v>
       </c>
       <c r="BD38">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE38">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF38">
         <v>15.5</v>
       </c>
       <c r="BG38">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH38">
         <v>3.15</v>
@@ -10192,7 +10192,7 @@
         <v>8.4</v>
       </c>
       <c r="BX38">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY38">
         <v>9</v>
@@ -10224,7 +10224,7 @@
         <v>214</v>
       </c>
       <c r="F39">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G39">
         <v>2.02</v>
@@ -10278,10 +10278,10 @@
         <v>1.98</v>
       </c>
       <c r="X39">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y39">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z39">
         <v>48</v>
@@ -10293,10 +10293,10 @@
         <v>6.6</v>
       </c>
       <c r="AC39">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD39">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE39">
         <v>120</v>
@@ -10305,7 +10305,7 @@
         <v>13</v>
       </c>
       <c r="AG39">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH39">
         <v>32</v>
@@ -10338,10 +10338,10 @@
         <v>9.6</v>
       </c>
       <c r="AR39">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS39">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="AT39">
         <v>5.7</v>
@@ -10353,7 +10353,7 @@
         <v>19</v>
       </c>
       <c r="AW39">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="AX39">
         <v>9.199999999999999</v>
@@ -10362,10 +10362,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ39">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BA39">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="BB39">
         <v>21</v>
@@ -10374,16 +10374,16 @@
         <v>20</v>
       </c>
       <c r="BD39">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE39">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BF39">
         <v>17.5</v>
       </c>
       <c r="BG39">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BH39">
         <v>2.74</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M40">
         <v>1.07</v>
@@ -10708,64 +10708,64 @@
         <v>216</v>
       </c>
       <c r="F41">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G41">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I41">
         <v>5.4</v>
       </c>
       <c r="J41">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K41">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L41">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M41">
         <v>1.07</v>
       </c>
       <c r="N41">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O41">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P41">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q41">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="R41">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S41">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="T41">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="U41">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V41">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W41">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="X41">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y41">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="Z41">
         <v>48</v>
@@ -10777,10 +10777,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC41">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD41">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AE41">
         <v>75</v>
@@ -10792,7 +10792,7 @@
         <v>10.5</v>
       </c>
       <c r="AH41">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI41">
         <v>80</v>
@@ -10804,130 +10804,130 @@
         <v>22</v>
       </c>
       <c r="AL41">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AM41">
         <v>130</v>
       </c>
       <c r="AN41">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO41">
         <v>85</v>
       </c>
       <c r="AP41">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AQ41">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AR41">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="AS41">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT41">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU41">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AV41">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AW41">
+        <v>8.6</v>
+      </c>
+      <c r="AX41">
+        <v>9</v>
+      </c>
+      <c r="AY41">
+        <v>8</v>
+      </c>
+      <c r="AZ41">
+        <v>14.5</v>
+      </c>
+      <c r="BA41">
+        <v>8.6</v>
+      </c>
+      <c r="BB41">
+        <v>16.5</v>
+      </c>
+      <c r="BC41">
+        <v>18</v>
+      </c>
+      <c r="BD41">
         <v>7.8</v>
       </c>
-      <c r="AX41">
-        <v>5.1</v>
-      </c>
-      <c r="AY41">
-        <v>4.8</v>
-      </c>
-      <c r="AZ41">
-        <v>6</v>
-      </c>
-      <c r="BA41">
-        <v>8</v>
-      </c>
-      <c r="BB41">
-        <v>6.4</v>
-      </c>
-      <c r="BC41">
-        <v>6.2</v>
-      </c>
-      <c r="BD41">
-        <v>7.2</v>
-      </c>
       <c r="BE41">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF41">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BG41">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH41">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BI41">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="BJ41">
         <v>10.5</v>
       </c>
       <c r="BK41">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BL41">
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>2.62</v>
+        <v>11.5</v>
       </c>
       <c r="BN41">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO41">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BP41">
         <v>14</v>
       </c>
       <c r="BQ41">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR41">
         <v>1000</v>
       </c>
       <c r="BS41">
-        <v>2.44</v>
+        <v>9</v>
       </c>
       <c r="BT41">
         <v>8.199999999999999</v>
       </c>
       <c r="BU41">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BV41">
         <v>1000</v>
       </c>
       <c r="BW41">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="BX41">
         <v>1000</v>
       </c>
       <c r="BY41">
-        <v>2.54</v>
+        <v>10</v>
       </c>
       <c r="BZ41">
         <v>1000</v>
       </c>
       <c r="CA41">
-        <v>2.42</v>
+        <v>8.6</v>
       </c>
       <c r="CB41" t="s">
         <v>220</v>
@@ -10962,7 +10962,7 @@
         <v>2.66</v>
       </c>
       <c r="J42">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K42">
         <v>3.6</v>
@@ -10974,13 +10974,13 @@
         <v>1.09</v>
       </c>
       <c r="N42">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O42">
         <v>1.38</v>
       </c>
       <c r="P42">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q42">
         <v>2.12</v>
@@ -11058,10 +11058,10 @@
         <v>29</v>
       </c>
       <c r="AP42">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ42">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AR42">
         <v>11.5</v>
@@ -11070,7 +11070,7 @@
         <v>4.7</v>
       </c>
       <c r="AT42">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU42">
         <v>5.9</v>
@@ -11115,7 +11115,7 @@
         <v>3.2</v>
       </c>
       <c r="BI42">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="BJ42">
         <v>10.5</v>
@@ -11216,7 +11216,7 @@
         <v>1.06</v>
       </c>
       <c r="N43">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O43">
         <v>1.27</v>
@@ -11225,7 +11225,7 @@
         <v>1.91</v>
       </c>
       <c r="Q43">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R43">
         <v>1.35</v>
@@ -11246,10 +11246,10 @@
         <v>1.72</v>
       </c>
       <c r="X43">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Y43">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Z43">
         <v>29</v>
@@ -11264,7 +11264,7 @@
         <v>9</v>
       </c>
       <c r="AD43">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AE43">
         <v>55</v>
@@ -11300,31 +11300,31 @@
         <v>50</v>
       </c>
       <c r="AP43">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AQ43">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR43">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AS43">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AT43">
         <v>7.6</v>
       </c>
       <c r="AU43">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV43">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AW43">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AX43">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY43">
         <v>8</v>
@@ -11333,25 +11333,25 @@
         <v>12.5</v>
       </c>
       <c r="BA43">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BB43">
         <v>19.5</v>
       </c>
       <c r="BC43">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD43">
+        <v>4.5</v>
+      </c>
+      <c r="BE43">
         <v>4.8</v>
-      </c>
-      <c r="BE43">
-        <v>5.2</v>
       </c>
       <c r="BF43">
         <v>11.5</v>
       </c>
       <c r="BG43">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BH43">
         <v>3.75</v>
@@ -11375,7 +11375,7 @@
         <v>5.4</v>
       </c>
       <c r="BO43">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BP43">
         <v>17</v>
@@ -11434,25 +11434,25 @@
         <v>219</v>
       </c>
       <c r="F44">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G44">
         <v>2.5</v>
       </c>
       <c r="H44">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I44">
         <v>3.55</v>
       </c>
       <c r="J44">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K44">
         <v>3.45</v>
       </c>
       <c r="L44">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="M44">
         <v>1.09</v>
@@ -11479,7 +11479,7 @@
         <v>1.86</v>
       </c>
       <c r="U44">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="V44">
         <v>1.4</v>
@@ -11497,7 +11497,7 @@
         <v>24</v>
       </c>
       <c r="AA44">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB44">
         <v>11</v>
@@ -11563,7 +11563,7 @@
         <v>12.5</v>
       </c>
       <c r="AW44">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AX44">
         <v>13</v>
@@ -11584,16 +11584,16 @@
         <v>4.8</v>
       </c>
       <c r="BD44">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BE44">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF44">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG44">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH44">
         <v>3.15</v>
@@ -11611,7 +11611,7 @@
         <v>1000</v>
       </c>
       <c r="BM44">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BN44">
         <v>5.3</v>
@@ -11623,7 +11623,7 @@
         <v>1000</v>
       </c>
       <c r="BQ44">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BR44">
         <v>1000</v>
@@ -11647,13 +11647,13 @@
         <v>1000</v>
       </c>
       <c r="BY44">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ44">
         <v>1000</v>
       </c>
       <c r="CA44">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CB44" t="s">
         <v>220</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -667,7 +667,7 @@
     <t>Everton De Vina</t>
   </si>
   <si>
-    <t>2026-07-26 17:16:30</t>
+    <t>2026-07-26 19:25:08</t>
   </si>
 </sst>
 </file>
@@ -1261,22 +1261,22 @@
         <v>175</v>
       </c>
       <c r="F2">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="G2">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="H2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I2">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>1.42</v>
@@ -1294,28 +1294,28 @@
         <v>1.93</v>
       </c>
       <c r="Q2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R2">
         <v>1.35</v>
       </c>
       <c r="S2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T2">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U2">
         <v>1.98</v>
       </c>
       <c r="V2">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W2">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y2">
         <v>18</v>
@@ -1324,13 +1324,13 @@
         <v>44</v>
       </c>
       <c r="AA2">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AB2">
         <v>8.199999999999999</v>
       </c>
       <c r="AC2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2">
         <v>22</v>
@@ -1348,7 +1348,7 @@
         <v>25</v>
       </c>
       <c r="AI2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ2">
         <v>18</v>
@@ -1357,67 +1357,67 @@
         <v>19</v>
       </c>
       <c r="AL2">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AM2">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="AN2">
         <v>12</v>
       </c>
       <c r="AO2">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="AP2">
         <v>13</v>
       </c>
       <c r="AQ2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AS2">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AT2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU2">
         <v>8</v>
       </c>
       <c r="AV2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW2">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AX2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA2">
         <v>50</v>
       </c>
       <c r="BB2">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE2">
         <v>85</v>
       </c>
       <c r="BF2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG2">
         <v>55</v>
@@ -1426,28 +1426,28 @@
         <v>3.4</v>
       </c>
       <c r="BI2">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2">
         <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BN2">
         <v>4.3</v>
       </c>
       <c r="BO2">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="BP2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ2">
         <v>8.800000000000001</v>
@@ -1456,31 +1456,31 @@
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT2">
         <v>8.800000000000001</v>
       </c>
       <c r="BU2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BV2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BW2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX2">
         <v>60</v>
       </c>
       <c r="BY2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CA2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="s">
         <v>217</v>
@@ -1509,55 +1509,55 @@
         <v>2.5</v>
       </c>
       <c r="H3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I3">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M3">
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O3">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P3">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q3">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T3">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U3">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
         <v>1.67</v>
       </c>
       <c r="X3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y3">
         <v>12</v>
@@ -1566,16 +1566,16 @@
         <v>23</v>
       </c>
       <c r="AA3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3">
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE3">
         <v>44</v>
@@ -1584,7 +1584,7 @@
         <v>15</v>
       </c>
       <c r="AG3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH3">
         <v>18</v>
@@ -1593,7 +1593,7 @@
         <v>60</v>
       </c>
       <c r="AJ3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK3">
         <v>29</v>
@@ -1605,10 +1605,10 @@
         <v>130</v>
       </c>
       <c r="AN3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP3">
         <v>10.5</v>
@@ -1644,10 +1644,10 @@
         <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BB3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC3">
         <v>24</v>
@@ -1662,7 +1662,7 @@
         <v>21</v>
       </c>
       <c r="BG3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH3">
         <v>3.2</v>
@@ -1671,7 +1671,7 @@
         <v>2.96</v>
       </c>
       <c r="BJ3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK3">
         <v>6.2</v>
@@ -1680,49 +1680,49 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BN3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP3">
         <v>19</v>
       </c>
       <c r="BQ3">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR3">
         <v>34</v>
       </c>
       <c r="BS3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BT3">
         <v>6.4</v>
       </c>
       <c r="BU3">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV3">
         <v>27</v>
       </c>
       <c r="BW3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BX3">
         <v>42</v>
       </c>
       <c r="BY3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BZ3">
         <v>32</v>
       </c>
       <c r="CA3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CB3" t="s">
         <v>217</v>
@@ -1745,226 +1745,226 @@
         <v>177</v>
       </c>
       <c r="F4">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="G4">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="H4">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="I4">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L4">
         <v>1.43</v>
       </c>
       <c r="M4">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O4">
+        <v>1.34</v>
+      </c>
+      <c r="P4">
+        <v>1.93</v>
+      </c>
+      <c r="Q4">
+        <v>2.02</v>
+      </c>
+      <c r="R4">
         <v>1.35</v>
       </c>
-      <c r="P4">
-        <v>1.91</v>
-      </c>
-      <c r="Q4">
-        <v>2.04</v>
-      </c>
-      <c r="R4">
-        <v>1.34</v>
-      </c>
       <c r="S4">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T4">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U4">
         <v>2.12</v>
       </c>
       <c r="V4">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="W4">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="X4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z4">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AA4">
+        <v>80</v>
+      </c>
+      <c r="AB4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD4">
+        <v>16</v>
+      </c>
+      <c r="AE4">
+        <v>50</v>
+      </c>
+      <c r="AF4">
+        <v>12.5</v>
+      </c>
+      <c r="AG4">
+        <v>10.5</v>
+      </c>
+      <c r="AH4">
+        <v>19</v>
+      </c>
+      <c r="AI4">
+        <v>60</v>
+      </c>
+      <c r="AJ4">
+        <v>26</v>
+      </c>
+      <c r="AK4">
+        <v>22</v>
+      </c>
+      <c r="AL4">
+        <v>38</v>
+      </c>
+      <c r="AM4">
+        <v>110</v>
+      </c>
+      <c r="AN4">
+        <v>17</v>
+      </c>
+      <c r="AO4">
         <v>55</v>
       </c>
-      <c r="AB4">
-        <v>10</v>
-      </c>
-      <c r="AC4">
-        <v>7.8</v>
-      </c>
-      <c r="AD4">
-        <v>13.5</v>
-      </c>
-      <c r="AE4">
-        <v>38</v>
-      </c>
-      <c r="AF4">
-        <v>16</v>
-      </c>
-      <c r="AG4">
-        <v>12</v>
-      </c>
-      <c r="AH4">
-        <v>18</v>
-      </c>
-      <c r="AI4">
-        <v>48</v>
-      </c>
-      <c r="AJ4">
-        <v>36</v>
-      </c>
-      <c r="AK4">
-        <v>28</v>
-      </c>
-      <c r="AL4">
+      <c r="AP4">
+        <v>12.5</v>
+      </c>
+      <c r="AQ4">
+        <v>13</v>
+      </c>
+      <c r="AR4">
+        <v>24</v>
+      </c>
+      <c r="AS4">
+        <v>70</v>
+      </c>
+      <c r="AT4">
+        <v>8.4</v>
+      </c>
+      <c r="AU4">
+        <v>7.4</v>
+      </c>
+      <c r="AV4">
+        <v>14.5</v>
+      </c>
+      <c r="AW4">
         <v>42</v>
       </c>
-      <c r="AM4">
-        <v>100</v>
-      </c>
-      <c r="AN4">
-        <v>23</v>
-      </c>
-      <c r="AO4">
-        <v>36</v>
-      </c>
-      <c r="AP4">
-        <v>12</v>
-      </c>
-      <c r="AQ4">
-        <v>11</v>
-      </c>
-      <c r="AR4">
-        <v>19</v>
-      </c>
-      <c r="AS4">
-        <v>46</v>
-      </c>
-      <c r="AT4">
-        <v>9.4</v>
-      </c>
-      <c r="AU4">
-        <v>7</v>
-      </c>
-      <c r="AV4">
-        <v>12.5</v>
-      </c>
-      <c r="AW4">
-        <v>32</v>
-      </c>
       <c r="AX4">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AY4">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4">
         <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BB4">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BC4">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="BD4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE4">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BF4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BG4">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BH4">
         <v>3.3</v>
       </c>
       <c r="BI4">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="BJ4">
         <v>9.6</v>
       </c>
       <c r="BK4">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM4">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN4">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BO4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP4">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="BQ4">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BR4">
+        <v>30</v>
+      </c>
+      <c r="BS4">
+        <v>21</v>
+      </c>
+      <c r="BT4">
+        <v>7</v>
+      </c>
+      <c r="BU4">
+        <v>6.2</v>
+      </c>
+      <c r="BV4">
         <v>32</v>
       </c>
-      <c r="BS4">
-        <v>10.5</v>
-      </c>
-      <c r="BT4">
-        <v>6.4</v>
-      </c>
-      <c r="BU4">
-        <v>5</v>
-      </c>
-      <c r="BV4">
+      <c r="BW4">
         <v>26</v>
       </c>
-      <c r="BW4">
-        <v>10</v>
-      </c>
       <c r="BX4">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BY4">
+        <v>13.5</v>
+      </c>
+      <c r="BZ4">
+        <v>27</v>
+      </c>
+      <c r="CA4">
         <v>11.5</v>
-      </c>
-      <c r="BZ4">
-        <v>29</v>
-      </c>
-      <c r="CA4">
-        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
         <v>217</v>
@@ -1999,70 +1999,70 @@
         <v>6.8</v>
       </c>
       <c r="J5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K5">
         <v>4.5</v>
       </c>
       <c r="L5">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M5">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O5">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P5">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="Q5">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="R5">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T5">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U5">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V5">
         <v>1.17</v>
       </c>
       <c r="W5">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="X5">
         <v>18.5</v>
       </c>
       <c r="Y5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA5">
         <v>180</v>
       </c>
       <c r="AB5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC5">
         <v>9.6</v>
       </c>
-      <c r="AC5">
-        <v>10</v>
-      </c>
       <c r="AD5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF5">
         <v>9.800000000000001</v>
@@ -2074,7 +2074,7 @@
         <v>21</v>
       </c>
       <c r="AI5">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AJ5">
         <v>15.5</v>
@@ -2086,16 +2086,16 @@
         <v>32</v>
       </c>
       <c r="AM5">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AN5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO5">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ5">
         <v>21</v>
@@ -2104,10 +2104,10 @@
         <v>48</v>
       </c>
       <c r="AS5">
-        <v>16.5</v>
+        <v>65</v>
       </c>
       <c r="AT5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU5">
         <v>9</v>
@@ -2116,10 +2116,10 @@
         <v>21</v>
       </c>
       <c r="AW5">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AX5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY5">
         <v>9</v>
@@ -2140,67 +2140,67 @@
         <v>28</v>
       </c>
       <c r="BE5">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BF5">
         <v>7.4</v>
       </c>
       <c r="BG5">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="BH5">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BI5">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BJ5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BL5">
         <v>130</v>
       </c>
       <c r="BM5">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BN5">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BO5">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="BP5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ5">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR5">
         <v>25</v>
       </c>
       <c r="BS5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BT5">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU5">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV5">
         <v>55</v>
       </c>
       <c r="BW5">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BX5">
         <v>60</v>
       </c>
       <c r="BY5">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="BZ5">
         <v>17</v>
@@ -2229,22 +2229,22 @@
         <v>179</v>
       </c>
       <c r="F6">
+        <v>1.48</v>
+      </c>
+      <c r="G6">
         <v>1.5</v>
-      </c>
-      <c r="G6">
-        <v>1.52</v>
       </c>
       <c r="H6">
         <v>7.8</v>
       </c>
       <c r="I6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6">
         <v>4.6</v>
       </c>
       <c r="K6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>1.36</v>
@@ -2256,31 +2256,31 @@
         <v>4.4</v>
       </c>
       <c r="O6">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P6">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q6">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R6">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S6">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T6">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U6">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V6">
         <v>1.13</v>
       </c>
       <c r="W6">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="X6">
         <v>18</v>
@@ -2304,7 +2304,7 @@
         <v>32</v>
       </c>
       <c r="AE6">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF6">
         <v>8.800000000000001</v>
@@ -2334,7 +2334,7 @@
         <v>7.6</v>
       </c>
       <c r="AO6">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AP6">
         <v>15</v>
@@ -2379,7 +2379,7 @@
         <v>13.5</v>
       </c>
       <c r="BD6">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BE6">
         <v>85</v>
@@ -2391,64 +2391,64 @@
         <v>11</v>
       </c>
       <c r="BH6">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BI6">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="BJ6">
         <v>11.5</v>
       </c>
       <c r="BK6">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BL6">
         <v>150</v>
       </c>
       <c r="BM6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BN6">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BO6">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BP6">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ6">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BR6">
         <v>26</v>
       </c>
       <c r="BS6">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BT6">
         <v>12</v>
       </c>
       <c r="BU6">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BV6">
         <v>75</v>
       </c>
       <c r="BW6">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BX6">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BY6">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BZ6">
         <v>16.5</v>
       </c>
       <c r="CA6">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB6" t="s">
         <v>217</v>
@@ -2471,25 +2471,25 @@
         <v>180</v>
       </c>
       <c r="F7">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="G7">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="H7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M7">
         <v>1.08</v>
@@ -2498,40 +2498,40 @@
         <v>2.84</v>
       </c>
       <c r="O7">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P7">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="Q7">
         <v>2.2</v>
       </c>
       <c r="R7">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S7">
         <v>3.6</v>
       </c>
       <c r="T7">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U7">
         <v>1.64</v>
       </c>
       <c r="V7">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W7">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="X7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y7">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z7">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AA7">
         <v>370</v>
@@ -2540,7 +2540,7 @@
         <v>6.8</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD7">
         <v>40</v>
@@ -2555,100 +2555,100 @@
         <v>11</v>
       </c>
       <c r="AH7">
-        <v>950</v>
+        <v>65</v>
       </c>
       <c r="AI7">
         <v>180</v>
       </c>
       <c r="AJ7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK7">
         <v>21</v>
       </c>
       <c r="AL7">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM7">
         <v>250</v>
       </c>
       <c r="AN7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO7">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AP7">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AQ7">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AR7">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS7">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT7">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AU7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV7">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AW7">
+        <v>7.2</v>
+      </c>
+      <c r="AX7">
+        <v>4</v>
+      </c>
+      <c r="AY7">
+        <v>4.5</v>
+      </c>
+      <c r="AZ7">
+        <v>6</v>
+      </c>
+      <c r="BA7">
+        <v>7.2</v>
+      </c>
+      <c r="BB7">
+        <v>5.1</v>
+      </c>
+      <c r="BC7">
+        <v>5.6</v>
+      </c>
+      <c r="BD7">
         <v>6.6</v>
       </c>
-      <c r="AX7">
-        <v>3.8</v>
-      </c>
-      <c r="AY7">
-        <v>4.3</v>
-      </c>
-      <c r="AZ7">
-        <v>5.7</v>
-      </c>
-      <c r="BA7">
-        <v>6.6</v>
-      </c>
-      <c r="BB7">
-        <v>4.8</v>
-      </c>
-      <c r="BC7">
-        <v>5.2</v>
-      </c>
-      <c r="BD7">
-        <v>6.2</v>
-      </c>
       <c r="BE7">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG7">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH7">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI7">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="BJ7">
         <v>13.5</v>
       </c>
       <c r="BK7">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BN7">
         <v>4</v>
@@ -2657,10 +2657,10 @@
         <v>3</v>
       </c>
       <c r="BP7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ7">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BR7">
         <v>1000</v>
@@ -2669,7 +2669,7 @@
         <v>2.24</v>
       </c>
       <c r="BT7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BU7">
         <v>5.3</v>
@@ -2678,7 +2678,7 @@
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BX7">
         <v>1000</v>
@@ -2687,10 +2687,10 @@
         <v>2.34</v>
       </c>
       <c r="BZ7">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>7</v>
+        <v>2.2</v>
       </c>
       <c r="CB7" t="s">
         <v>217</v>
@@ -2722,16 +2722,16 @@
         <v>1.23</v>
       </c>
       <c r="I8">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="J8">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="K8">
         <v>8.199999999999999</v>
       </c>
       <c r="L8">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="M8">
         <v>1.02</v>
@@ -2746,28 +2746,28 @@
         <v>3.2</v>
       </c>
       <c r="Q8">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R8">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="S8">
         <v>1.89</v>
       </c>
       <c r="T8">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U8">
         <v>2.02</v>
       </c>
       <c r="V8">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="W8">
         <v>1.06</v>
       </c>
       <c r="X8">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Y8">
         <v>14.5</v>
@@ -2782,10 +2782,10 @@
         <v>70</v>
       </c>
       <c r="AC8">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AD8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE8">
         <v>13</v>
@@ -2797,31 +2797,31 @@
         <v>55</v>
       </c>
       <c r="AH8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI8">
         <v>32</v>
       </c>
       <c r="AJ8">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="AK8">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AL8">
         <v>130</v>
       </c>
       <c r="AM8">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN8">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AO8">
         <v>3.45</v>
       </c>
       <c r="AP8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AQ8">
         <v>12</v>
@@ -2836,7 +2836,7 @@
         <v>50</v>
       </c>
       <c r="AU8">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AV8">
         <v>9.6</v>
@@ -2845,40 +2845,40 @@
         <v>11</v>
       </c>
       <c r="AX8">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY8">
         <v>40</v>
       </c>
       <c r="AZ8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA8">
         <v>24</v>
       </c>
       <c r="BB8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BC8">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BD8">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BE8">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BF8">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG8">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BH8">
         <v>5.6</v>
       </c>
       <c r="BI8">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BJ8">
         <v>12.5</v>
@@ -2914,7 +2914,7 @@
         <v>4.3</v>
       </c>
       <c r="BU8">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BV8">
         <v>7</v>
@@ -2964,7 +2964,7 @@
         <v>3.2</v>
       </c>
       <c r="I9">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J9">
         <v>3.45</v>
@@ -3003,7 +3003,7 @@
         <v>2.2</v>
       </c>
       <c r="V9">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
         <v>1.73</v>
@@ -3015,7 +3015,7 @@
         <v>18.5</v>
       </c>
       <c r="Z9">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA9">
         <v>75</v>
@@ -3024,13 +3024,13 @@
         <v>13.5</v>
       </c>
       <c r="AC9">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE9">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF9">
         <v>18.5</v>
@@ -3042,25 +3042,25 @@
         <v>20</v>
       </c>
       <c r="AI9">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ9">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK9">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL9">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM9">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="AN9">
         <v>18</v>
       </c>
       <c r="AO9">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AP9">
         <v>12.5</v>
@@ -3072,19 +3072,19 @@
         <v>19</v>
       </c>
       <c r="AS9">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AT9">
         <v>8.199999999999999</v>
       </c>
       <c r="AU9">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV9">
         <v>10.5</v>
       </c>
       <c r="AW9">
-        <v>3.95</v>
+        <v>18</v>
       </c>
       <c r="AX9">
         <v>11</v>
@@ -3096,7 +3096,7 @@
         <v>12</v>
       </c>
       <c r="BA9">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BB9">
         <v>20</v>
@@ -3105,22 +3105,22 @@
         <v>16</v>
       </c>
       <c r="BD9">
-        <v>3.9</v>
+        <v>20</v>
       </c>
       <c r="BE9">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BF9">
         <v>10.5</v>
       </c>
       <c r="BG9">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="BH9">
         <v>3.85</v>
       </c>
       <c r="BI9">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="BJ9">
         <v>9.6</v>
@@ -3197,16 +3197,16 @@
         <v>183</v>
       </c>
       <c r="F10">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="G10">
         <v>1.87</v>
       </c>
       <c r="H10">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I10">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J10">
         <v>3.75</v>
@@ -3221,58 +3221,58 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O10">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P10">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q10">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="R10">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S10">
         <v>3.55</v>
       </c>
       <c r="T10">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U10">
         <v>2.04</v>
       </c>
       <c r="V10">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W10">
         <v>2.14</v>
       </c>
       <c r="X10">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z10">
         <v>40</v>
       </c>
       <c r="AA10">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB10">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD10">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE10">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="AF10">
         <v>12</v>
@@ -3281,22 +3281,22 @@
         <v>11.5</v>
       </c>
       <c r="AH10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI10">
         <v>80</v>
       </c>
       <c r="AJ10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL10">
         <v>40</v>
       </c>
       <c r="AM10">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AN10">
         <v>15</v>
@@ -3308,13 +3308,13 @@
         <v>12</v>
       </c>
       <c r="AQ10">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR10">
         <v>30</v>
       </c>
       <c r="AS10">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="AT10">
         <v>7.8</v>
@@ -3329,7 +3329,7 @@
         <v>50</v>
       </c>
       <c r="AX10">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY10">
         <v>9.4</v>
@@ -3341,19 +3341,19 @@
         <v>55</v>
       </c>
       <c r="BB10">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="BC10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD10">
         <v>32</v>
       </c>
       <c r="BE10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG10">
         <v>55</v>
@@ -3362,13 +3362,13 @@
         <v>3.4</v>
       </c>
       <c r="BI10">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3383,22 +3383,22 @@
         <v>3.45</v>
       </c>
       <c r="BP10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT10">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BU10">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BV10">
         <v>1000</v>
@@ -3410,13 +3410,13 @@
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB10" t="s">
         <v>217</v>
@@ -3439,22 +3439,22 @@
         <v>184</v>
       </c>
       <c r="F11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G11">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H11">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="I11">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="J11">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K11">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L11">
         <v>1.38</v>
@@ -3469,7 +3469,7 @@
         <v>1.29</v>
       </c>
       <c r="P11">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q11">
         <v>1.86</v>
@@ -3481,7 +3481,7 @@
         <v>3.15</v>
       </c>
       <c r="T11">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U11">
         <v>2.06</v>
@@ -3496,7 +3496,7 @@
         <v>16.5</v>
       </c>
       <c r="Y11">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z11">
         <v>13</v>
@@ -3505,7 +3505,7 @@
         <v>23</v>
       </c>
       <c r="AB11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC11">
         <v>9</v>
@@ -3517,37 +3517,37 @@
         <v>21</v>
       </c>
       <c r="AF11">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AG11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH11">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI11">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AJ11">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK11">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="AL11">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AM11">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN11">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="AO11">
         <v>13.5</v>
       </c>
       <c r="AP11">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ11">
         <v>7.2</v>
@@ -3559,7 +3559,7 @@
         <v>16</v>
       </c>
       <c r="AT11">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU11">
         <v>6.8</v>
@@ -3571,31 +3571,31 @@
         <v>16</v>
       </c>
       <c r="AX11">
+        <v>7</v>
+      </c>
+      <c r="AY11">
         <v>6.2</v>
-      </c>
-      <c r="AY11">
-        <v>5.5</v>
       </c>
       <c r="AZ11">
         <v>14</v>
       </c>
       <c r="BA11">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BB11">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC11">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD11">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE11">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG11">
         <v>9.6</v>
@@ -3684,19 +3684,19 @@
         <v>10.5</v>
       </c>
       <c r="G12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="H12">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="I12">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="J12">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K12">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L12">
         <v>1.27</v>
@@ -3705,10 +3705,10 @@
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O12">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P12">
         <v>2.16</v>
@@ -3720,19 +3720,19 @@
         <v>1.45</v>
       </c>
       <c r="S12">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="T12">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U12">
         <v>1.75</v>
       </c>
       <c r="V12">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
         <v>22</v>
@@ -3741,13 +3741,13 @@
         <v>8.6</v>
       </c>
       <c r="Z12">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA12">
         <v>13.5</v>
       </c>
       <c r="AB12">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AC12">
         <v>13</v>
@@ -3756,7 +3756,7 @@
         <v>11</v>
       </c>
       <c r="AE12">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF12">
         <v>110</v>
@@ -3774,13 +3774,13 @@
         <v>560</v>
       </c>
       <c r="AK12">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AL12">
-        <v>190</v>
+        <v>470</v>
       </c>
       <c r="AM12">
-        <v>220</v>
+        <v>390</v>
       </c>
       <c r="AN12">
         <v>350</v>
@@ -3807,76 +3807,76 @@
         <v>9.4</v>
       </c>
       <c r="AV12">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW12">
         <v>11.5</v>
       </c>
       <c r="AX12">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY12">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AZ12">
-        <v>5.7</v>
+        <v>14.5</v>
       </c>
       <c r="BA12">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="BB12">
+        <v>7</v>
+      </c>
+      <c r="BC12">
+        <v>7</v>
+      </c>
+      <c r="BD12">
         <v>6.8</v>
       </c>
-      <c r="BC12">
-        <v>6.6</v>
-      </c>
-      <c r="BD12">
-        <v>6.6</v>
-      </c>
       <c r="BE12">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF12">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="BG12">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH12">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI12">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ12">
         <v>13</v>
       </c>
       <c r="BK12">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN12">
         <v>14.5</v>
       </c>
       <c r="BO12">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BT12">
         <v>3.9</v>
@@ -3888,19 +3888,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BW12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BX12">
         <v>26</v>
       </c>
       <c r="BY12">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ12">
         <v>13.5</v>
       </c>
       <c r="CA12">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB12" t="s">
         <v>217</v>
@@ -3923,25 +3923,25 @@
         <v>186</v>
       </c>
       <c r="F13">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G13">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="H13">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="I13">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J13">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K13">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L13">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M13">
         <v>1.06</v>
@@ -3953,28 +3953,28 @@
         <v>1.28</v>
       </c>
       <c r="P13">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q13">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="R13">
         <v>1.38</v>
       </c>
       <c r="S13">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T13">
         <v>1.74</v>
       </c>
       <c r="U13">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="V13">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="W13">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="X13">
         <v>19</v>
@@ -3989,7 +3989,7 @@
         <v>23</v>
       </c>
       <c r="AB13">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AC13">
         <v>10.5</v>
@@ -4004,7 +4004,7 @@
         <v>48</v>
       </c>
       <c r="AG13">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AH13">
         <v>21</v>
@@ -4013,88 +4013,88 @@
         <v>42</v>
       </c>
       <c r="AJ13">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AK13">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AL13">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM13">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="AN13">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AO13">
         <v>13</v>
       </c>
       <c r="AP13">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="AQ13">
-        <v>3.85</v>
+        <v>8.4</v>
       </c>
       <c r="AR13">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AS13">
-        <v>4.8</v>
+        <v>19.5</v>
       </c>
       <c r="AT13">
-        <v>4.6</v>
+        <v>13.5</v>
       </c>
       <c r="AU13">
-        <v>3.85</v>
+        <v>7.4</v>
       </c>
       <c r="AV13">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="AW13">
-        <v>4.7</v>
+        <v>17</v>
       </c>
       <c r="AX13">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="AY13">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="AZ13">
-        <v>4.7</v>
+        <v>15</v>
       </c>
       <c r="BA13">
-        <v>5.3</v>
+        <v>24</v>
       </c>
       <c r="BB13">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC13">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD13">
-        <v>5.6</v>
+        <v>23</v>
       </c>
       <c r="BE13">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF13">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG13">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BH13">
         <v>3.7</v>
       </c>
       <c r="BI13">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="BJ13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK13">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BL13">
         <v>1000</v>
@@ -4103,10 +4103,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN13">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BO13">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BP13">
         <v>1000</v>
@@ -4118,19 +4118,19 @@
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT13">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BU13">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BV13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BW13">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BX13">
         <v>28</v>
@@ -4139,10 +4139,10 @@
         <v>7.2</v>
       </c>
       <c r="BZ13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CA13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB13" t="s">
         <v>217</v>
@@ -4165,97 +4165,97 @@
         <v>187</v>
       </c>
       <c r="F14">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="G14">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="I14">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J14">
         <v>3.35</v>
       </c>
       <c r="K14">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L14">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M14">
         <v>1.06</v>
       </c>
       <c r="N14">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O14">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P14">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q14">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="R14">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S14">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="T14">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U14">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W14">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X14">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y14">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Z14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA14">
-        <v>70</v>
+        <v>280</v>
       </c>
       <c r="AB14">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC14">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE14">
         <v>46</v>
       </c>
       <c r="AF14">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AG14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH14">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AI14">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AJ14">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AK14">
         <v>32</v>
@@ -4264,76 +4264,76 @@
         <v>46</v>
       </c>
       <c r="AM14">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AN14">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AO14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AP14">
-        <v>3.45</v>
+        <v>5.3</v>
       </c>
       <c r="AQ14">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="AR14">
-        <v>3.75</v>
+        <v>5.9</v>
       </c>
       <c r="AS14">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="AT14">
-        <v>3.25</v>
+        <v>5.8</v>
       </c>
       <c r="AU14">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="AV14">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="AW14">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="AX14">
-        <v>3.55</v>
+        <v>5.3</v>
       </c>
       <c r="AY14">
-        <v>3.3</v>
+        <v>6.4</v>
       </c>
       <c r="AZ14">
-        <v>3.55</v>
+        <v>5.4</v>
       </c>
       <c r="BA14">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BB14">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="BC14">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD14">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="BE14">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="BF14">
+        <v>5.6</v>
+      </c>
+      <c r="BG14">
+        <v>6.4</v>
+      </c>
+      <c r="BH14">
         <v>3.65</v>
       </c>
-      <c r="BG14">
-        <v>3.9</v>
-      </c>
-      <c r="BH14">
-        <v>3.6</v>
-      </c>
       <c r="BI14">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BJ14">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK14">
         <v>5</v>
@@ -4345,13 +4345,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN14">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO14">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP14">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ14">
         <v>6.6</v>
@@ -4363,10 +4363,10 @@
         <v>7.8</v>
       </c>
       <c r="BT14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU14">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV14">
         <v>1000</v>
@@ -4407,28 +4407,28 @@
         <v>188</v>
       </c>
       <c r="F15">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G15">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H15">
         <v>4.8</v>
       </c>
       <c r="I15">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J15">
         <v>3.6</v>
       </c>
       <c r="K15">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L15">
         <v>1.35</v>
       </c>
       <c r="M15">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N15">
         <v>3.45</v>
@@ -4437,10 +4437,10 @@
         <v>1.34</v>
       </c>
       <c r="P15">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q15">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R15">
         <v>1.32</v>
@@ -4449,7 +4449,7 @@
         <v>3.55</v>
       </c>
       <c r="T15">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U15">
         <v>1.96</v>
@@ -4458,7 +4458,7 @@
         <v>1.22</v>
       </c>
       <c r="W15">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X15">
         <v>14</v>
@@ -4467,22 +4467,22 @@
         <v>16.5</v>
       </c>
       <c r="Z15">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA15">
+        <v>900</v>
+      </c>
+      <c r="AB15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC15">
+        <v>8.4</v>
+      </c>
+      <c r="AD15">
+        <v>24</v>
+      </c>
+      <c r="AE15">
         <v>160</v>
-      </c>
-      <c r="AB15">
-        <v>8.4</v>
-      </c>
-      <c r="AC15">
-        <v>8.6</v>
-      </c>
-      <c r="AD15">
-        <v>25</v>
-      </c>
-      <c r="AE15">
-        <v>95</v>
       </c>
       <c r="AF15">
         <v>13</v>
@@ -4494,7 +4494,7 @@
         <v>25</v>
       </c>
       <c r="AI15">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="AJ15">
         <v>25</v>
@@ -4506,10 +4506,10 @@
         <v>48</v>
       </c>
       <c r="AM15">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO15">
         <v>110</v>
@@ -4518,13 +4518,13 @@
         <v>12</v>
       </c>
       <c r="AQ15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR15">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AS15">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT15">
         <v>6.2</v>
@@ -4536,7 +4536,7 @@
         <v>14.5</v>
       </c>
       <c r="AW15">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX15">
         <v>8</v>
@@ -4548,7 +4548,7 @@
         <v>17.5</v>
       </c>
       <c r="BA15">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB15">
         <v>17.5</v>
@@ -4557,16 +4557,16 @@
         <v>17.5</v>
       </c>
       <c r="BD15">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE15">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF15">
         <v>9.800000000000001</v>
       </c>
       <c r="BG15">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH15">
         <v>3.35</v>
@@ -4590,7 +4590,7 @@
         <v>4.4</v>
       </c>
       <c r="BO15">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="BP15">
         <v>13</v>
@@ -4649,10 +4649,10 @@
         <v>189</v>
       </c>
       <c r="F16">
+        <v>1.9</v>
+      </c>
+      <c r="G16">
         <v>1.92</v>
-      </c>
-      <c r="G16">
-        <v>1.94</v>
       </c>
       <c r="H16">
         <v>4</v>
@@ -4679,28 +4679,28 @@
         <v>1.18</v>
       </c>
       <c r="P16">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q16">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R16">
         <v>1.7</v>
       </c>
       <c r="S16">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T16">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U16">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="V16">
         <v>1.32</v>
       </c>
       <c r="W16">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X16">
         <v>27</v>
@@ -4742,22 +4742,22 @@
         <v>23</v>
       </c>
       <c r="AK16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM16">
         <v>60</v>
       </c>
       <c r="AN16">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AO16">
         <v>27</v>
       </c>
       <c r="AP16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ16">
         <v>21</v>
@@ -4796,19 +4796,19 @@
         <v>19.5</v>
       </c>
       <c r="BC16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD16">
         <v>22</v>
       </c>
       <c r="BE16">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF16">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG16">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BH16">
         <v>4.7</v>
@@ -4894,22 +4894,22 @@
         <v>2</v>
       </c>
       <c r="G17">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H17">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I17">
         <v>3.95</v>
       </c>
       <c r="J17">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K17">
         <v>4.2</v>
       </c>
       <c r="L17">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M17">
         <v>1.05</v>
@@ -4942,19 +4942,19 @@
         <v>1.33</v>
       </c>
       <c r="W17">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X17">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y17">
         <v>21</v>
       </c>
       <c r="Z17">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AA17">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB17">
         <v>14.5</v>
@@ -4966,19 +4966,19 @@
         <v>19</v>
       </c>
       <c r="AE17">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AF17">
         <v>17.5</v>
       </c>
       <c r="AG17">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH17">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AI17">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AJ17">
         <v>32</v>
@@ -4987,70 +4987,70 @@
         <v>25</v>
       </c>
       <c r="AL17">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AM17">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AN17">
         <v>15</v>
       </c>
       <c r="AO17">
-        <v>42</v>
+        <v>220</v>
       </c>
       <c r="AP17">
+        <v>16</v>
+      </c>
+      <c r="AQ17">
         <v>14</v>
       </c>
-      <c r="AQ17">
+      <c r="AR17">
+        <v>13</v>
+      </c>
+      <c r="AS17">
+        <v>5</v>
+      </c>
+      <c r="AT17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU17">
+        <v>7.8</v>
+      </c>
+      <c r="AV17">
+        <v>13</v>
+      </c>
+      <c r="AW17">
+        <v>4.7</v>
+      </c>
+      <c r="AX17">
         <v>12</v>
       </c>
-      <c r="AR17">
+      <c r="AY17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ17">
+        <v>14</v>
+      </c>
+      <c r="BA17">
+        <v>4.8</v>
+      </c>
+      <c r="BB17">
         <v>20</v>
       </c>
-      <c r="AS17">
-        <v>4</v>
-      </c>
-      <c r="AT17">
-        <v>8.6</v>
-      </c>
-      <c r="AU17">
-        <v>6.8</v>
-      </c>
-      <c r="AV17">
-        <v>11.5</v>
-      </c>
-      <c r="AW17">
-        <v>3.9</v>
-      </c>
-      <c r="AX17">
-        <v>10.5</v>
-      </c>
-      <c r="AY17">
-        <v>8</v>
-      </c>
-      <c r="AZ17">
-        <v>12</v>
-      </c>
-      <c r="BA17">
-        <v>3.9</v>
-      </c>
-      <c r="BB17">
+      <c r="BC17">
+        <v>17</v>
+      </c>
+      <c r="BD17">
         <v>18</v>
       </c>
-      <c r="BC17">
-        <v>14.5</v>
-      </c>
-      <c r="BD17">
-        <v>3.8</v>
-      </c>
       <c r="BE17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BF17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BG17">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="BH17">
         <v>4.1</v>
@@ -5133,31 +5133,31 @@
         <v>191</v>
       </c>
       <c r="F18">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H18">
         <v>2.74</v>
       </c>
       <c r="I18">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J18">
         <v>3.2</v>
       </c>
       <c r="K18">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L18">
         <v>1.43</v>
       </c>
       <c r="M18">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N18">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O18">
         <v>1.43</v>
@@ -5166,7 +5166,7 @@
         <v>1.7</v>
       </c>
       <c r="Q18">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R18">
         <v>1.26</v>
@@ -5175,7 +5175,7 @@
         <v>4.4</v>
       </c>
       <c r="T18">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U18">
         <v>1.96</v>
@@ -5184,10 +5184,10 @@
         <v>1.53</v>
       </c>
       <c r="W18">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X18">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y18">
         <v>9.800000000000001</v>
@@ -5199,16 +5199,16 @@
         <v>55</v>
       </c>
       <c r="AB18">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC18">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD18">
         <v>15</v>
       </c>
       <c r="AE18">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AF18">
         <v>22</v>
@@ -5223,16 +5223,16 @@
         <v>65</v>
       </c>
       <c r="AJ18">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK18">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AL18">
         <v>65</v>
       </c>
       <c r="AM18">
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="AN18">
         <v>48</v>
@@ -5250,10 +5250,10 @@
         <v>15.5</v>
       </c>
       <c r="AS18">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT18">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU18">
         <v>6.6</v>
@@ -5262,37 +5262,37 @@
         <v>11</v>
       </c>
       <c r="AW18">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="AX18">
         <v>16.5</v>
       </c>
       <c r="AY18">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ18">
         <v>17</v>
       </c>
       <c r="BA18">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB18">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BC18">
-        <v>5.7</v>
+        <v>16</v>
       </c>
       <c r="BD18">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE18">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BF18">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BG18">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BH18">
         <v>3</v>
@@ -5381,7 +5381,7 @@
         <v>3.05</v>
       </c>
       <c r="H19">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I19">
         <v>2.66</v>
@@ -5390,10 +5390,10 @@
         <v>3.55</v>
       </c>
       <c r="K19">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L19">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M19">
         <v>1.05</v>
@@ -5414,13 +5414,13 @@
         <v>1.46</v>
       </c>
       <c r="S19">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="T19">
         <v>1.62</v>
       </c>
       <c r="U19">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="V19">
         <v>1.6</v>
@@ -5432,13 +5432,13 @@
         <v>19</v>
       </c>
       <c r="Y19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z19">
         <v>21</v>
       </c>
       <c r="AA19">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB19">
         <v>15</v>
@@ -5450,31 +5450,31 @@
         <v>12.5</v>
       </c>
       <c r="AE19">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH19">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI19">
         <v>36</v>
       </c>
       <c r="AJ19">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AK19">
         <v>32</v>
       </c>
       <c r="AL19">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM19">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AN19">
         <v>25</v>
@@ -5492,7 +5492,7 @@
         <v>15.5</v>
       </c>
       <c r="AS19">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT19">
         <v>11.5</v>
@@ -5516,19 +5516,19 @@
         <v>13</v>
       </c>
       <c r="BA19">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BB19">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC19">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BD19">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE19">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF19">
         <v>16.5</v>
@@ -5617,19 +5617,19 @@
         <v>193</v>
       </c>
       <c r="F20">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G20">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="H20">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I20">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="K20">
         <v>6.6</v>
@@ -5638,7 +5638,7 @@
         <v>1.18</v>
       </c>
       <c r="M20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N20">
         <v>7.2</v>
@@ -5665,10 +5665,10 @@
         <v>2.5</v>
       </c>
       <c r="V20">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W20">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="X20">
         <v>48</v>
@@ -5677,7 +5677,7 @@
         <v>48</v>
       </c>
       <c r="Z20">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="AA20">
         <v>190</v>
@@ -5686,25 +5686,25 @@
         <v>17</v>
       </c>
       <c r="AC20">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD20">
         <v>32</v>
       </c>
       <c r="AE20">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="AF20">
         <v>14</v>
       </c>
       <c r="AG20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH20">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI20">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AJ20">
         <v>15.5</v>
@@ -5713,28 +5713,28 @@
         <v>14.5</v>
       </c>
       <c r="AL20">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AM20">
-        <v>75</v>
+        <v>260</v>
       </c>
       <c r="AN20">
         <v>4.6</v>
       </c>
       <c r="AO20">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AP20">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ20">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="AR20">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS20">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT20">
         <v>12.5</v>
@@ -5746,7 +5746,7 @@
         <v>21</v>
       </c>
       <c r="AW20">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX20">
         <v>10</v>
@@ -5758,7 +5758,7 @@
         <v>15</v>
       </c>
       <c r="BA20">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB20">
         <v>11.5</v>
@@ -5770,19 +5770,19 @@
         <v>18</v>
       </c>
       <c r="BE20">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF20">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="BG20">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH20">
         <v>5.6</v>
       </c>
       <c r="BI20">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BJ20">
         <v>9.4</v>
@@ -5859,7 +5859,7 @@
         <v>194</v>
       </c>
       <c r="F21">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G21">
         <v>1.83</v>
@@ -5871,10 +5871,10 @@
         <v>4.9</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K21">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L21">
         <v>1.33</v>
@@ -5889,7 +5889,7 @@
         <v>1.24</v>
       </c>
       <c r="P21">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q21">
         <v>1.71</v>
@@ -5901,7 +5901,7 @@
         <v>2.78</v>
       </c>
       <c r="T21">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U21">
         <v>2.36</v>
@@ -5913,10 +5913,10 @@
         <v>2.2</v>
       </c>
       <c r="X21">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y21">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z21">
         <v>40</v>
@@ -5931,7 +5931,7 @@
         <v>9.6</v>
       </c>
       <c r="AD21">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE21">
         <v>55</v>
@@ -5943,7 +5943,7 @@
         <v>10</v>
       </c>
       <c r="AH21">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI21">
         <v>55</v>
@@ -5961,13 +5961,13 @@
         <v>80</v>
       </c>
       <c r="AN21">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO21">
         <v>46</v>
       </c>
       <c r="AP21">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ21">
         <v>18</v>
@@ -5976,7 +5976,7 @@
         <v>34</v>
       </c>
       <c r="AS21">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AT21">
         <v>10</v>
@@ -5988,7 +5988,7 @@
         <v>16.5</v>
       </c>
       <c r="AW21">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="AX21">
         <v>11</v>
@@ -6012,7 +6012,7 @@
         <v>26</v>
       </c>
       <c r="BE21">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BF21">
         <v>8.4</v>
@@ -6048,7 +6048,7 @@
         <v>12</v>
       </c>
       <c r="BQ21">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR21">
         <v>23</v>
@@ -6110,10 +6110,10 @@
         <v>5.2</v>
       </c>
       <c r="I22">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K22">
         <v>4.3</v>
@@ -6131,19 +6131,19 @@
         <v>1.27</v>
       </c>
       <c r="P22">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q22">
         <v>1.79</v>
       </c>
       <c r="R22">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S22">
         <v>3</v>
       </c>
       <c r="T22">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U22">
         <v>2.14</v>
@@ -6155,31 +6155,31 @@
         <v>2.28</v>
       </c>
       <c r="X22">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y22">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z22">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="AA22">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
         <v>9.800000000000001</v>
       </c>
       <c r="AC22">
+        <v>10</v>
+      </c>
+      <c r="AD22">
+        <v>23</v>
+      </c>
+      <c r="AE22">
+        <v>150</v>
+      </c>
+      <c r="AF22">
         <v>11</v>
-      </c>
-      <c r="AD22">
-        <v>24</v>
-      </c>
-      <c r="AE22">
-        <v>70</v>
-      </c>
-      <c r="AF22">
-        <v>11.5</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -6188,10 +6188,10 @@
         <v>22</v>
       </c>
       <c r="AI22">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AJ22">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK22">
         <v>18</v>
@@ -6200,25 +6200,25 @@
         <v>38</v>
       </c>
       <c r="AM22">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN22">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO22">
-        <v>80</v>
+        <v>310</v>
       </c>
       <c r="AP22">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ22">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AR22">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="AS22">
-        <v>6.4</v>
+        <v>40</v>
       </c>
       <c r="AT22">
         <v>8.6</v>
@@ -6227,40 +6227,40 @@
         <v>8.4</v>
       </c>
       <c r="AV22">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW22">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="AX22">
         <v>9.800000000000001</v>
       </c>
       <c r="AY22">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ22">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA22">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="BB22">
         <v>15.5</v>
       </c>
       <c r="BC22">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="BD22">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="BE22">
-        <v>6.4</v>
+        <v>38</v>
       </c>
       <c r="BF22">
         <v>8.6</v>
       </c>
       <c r="BG22">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="BH22">
         <v>3.75</v>
@@ -6343,7 +6343,7 @@
         <v>196</v>
       </c>
       <c r="F23">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="G23">
         <v>3.05</v>
@@ -6352,13 +6352,13 @@
         <v>2.34</v>
       </c>
       <c r="I23">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J23">
         <v>3.9</v>
       </c>
       <c r="K23">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L23">
         <v>1.29</v>
@@ -6376,7 +6376,7 @@
         <v>2.56</v>
       </c>
       <c r="Q23">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R23">
         <v>1.63</v>
@@ -6391,13 +6391,13 @@
         <v>2.66</v>
       </c>
       <c r="V23">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W23">
         <v>1.48</v>
       </c>
       <c r="X23">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y23">
         <v>19.5</v>
@@ -6451,10 +6451,10 @@
         <v>16</v>
       </c>
       <c r="AP23">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ23">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="AR23">
         <v>15</v>
@@ -6493,10 +6493,10 @@
         <v>20</v>
       </c>
       <c r="BD23">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="BE23">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF23">
         <v>12.5</v>
@@ -6591,7 +6591,7 @@
         <v>2.48</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I24">
         <v>3.35</v>
@@ -6600,37 +6600,37 @@
         <v>3.6</v>
       </c>
       <c r="K24">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L24">
         <v>1.31</v>
       </c>
       <c r="M24">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N24">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O24">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P24">
         <v>2.12</v>
       </c>
       <c r="Q24">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R24">
         <v>1.44</v>
       </c>
       <c r="S24">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T24">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V24">
         <v>1.43</v>
@@ -6672,7 +6672,7 @@
         <v>18</v>
       </c>
       <c r="AI24">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ24">
         <v>38</v>
@@ -6708,13 +6708,13 @@
         <v>9.4</v>
       </c>
       <c r="AU24">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV24">
         <v>10.5</v>
       </c>
       <c r="AW24">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="AX24">
         <v>12.5</v>
@@ -6726,19 +6726,19 @@
         <v>12</v>
       </c>
       <c r="BA24">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB24">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="BC24">
         <v>18</v>
       </c>
       <c r="BD24">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="BE24">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF24">
         <v>14</v>
@@ -6750,7 +6750,7 @@
         <v>3.75</v>
       </c>
       <c r="BI24">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BJ24">
         <v>9</v>
@@ -6830,19 +6830,19 @@
         <v>3.4</v>
       </c>
       <c r="G25">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="H25">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I25">
         <v>2.58</v>
       </c>
       <c r="J25">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="K25">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="L25">
         <v>1.53</v>
@@ -6878,31 +6878,31 @@
         <v>1.63</v>
       </c>
       <c r="W25">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X25">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Y25">
         <v>7.4</v>
       </c>
       <c r="Z25">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA25">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AB25">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC25">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD25">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE25">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AF25">
         <v>32</v>
@@ -6911,22 +6911,22 @@
         <v>21</v>
       </c>
       <c r="AH25">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI25">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AJ25">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AK25">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AL25">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AM25">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AN25">
         <v>130</v>
@@ -6935,58 +6935,58 @@
         <v>46</v>
       </c>
       <c r="AP25">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="AQ25">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="AR25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS25">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT25">
+        <v>4.5</v>
+      </c>
+      <c r="AU25">
         <v>3.8</v>
       </c>
-      <c r="AU25">
-        <v>3.3</v>
-      </c>
       <c r="AV25">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AW25">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX25">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AY25">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="AZ25">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BA25">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BB25">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BC25">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BD25">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BE25">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF25">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BG25">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH25">
         <v>2.72</v>
@@ -7069,19 +7069,19 @@
         <v>199</v>
       </c>
       <c r="F26">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="G26">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="H26">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="I26">
         <v>3.3</v>
       </c>
       <c r="J26">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="K26">
         <v>3.1</v>
@@ -7102,13 +7102,13 @@
         <v>1.38</v>
       </c>
       <c r="Q26">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="R26">
         <v>1.13</v>
       </c>
       <c r="S26">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T26">
         <v>2.28</v>
@@ -7120,10 +7120,10 @@
         <v>1.43</v>
       </c>
       <c r="W26">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="X26">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -7132,103 +7132,103 @@
         <v>19</v>
       </c>
       <c r="AA26">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AB26">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AD26">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE26">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AF26">
         <v>21</v>
       </c>
       <c r="AG26">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AH26">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AI26">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ26">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AK26">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AL26">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="AM26">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AN26">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AO26">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AP26">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AQ26">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AR26">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AS26">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="AT26">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AU26">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="AV26">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="AW26">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="AX26">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AY26">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="AZ26">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BA26">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BB26">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC26">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BD26">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BE26">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BF26">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BG26">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH26">
         <v>2.5</v>
@@ -7311,19 +7311,19 @@
         <v>200</v>
       </c>
       <c r="F27">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="G27">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="H27">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I27">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J27">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="K27">
         <v>3.7</v>
@@ -7332,10 +7332,10 @@
         <v>1.49</v>
       </c>
       <c r="M27">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N27">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="O27">
         <v>1.55</v>
@@ -7359,118 +7359,118 @@
         <v>1.57</v>
       </c>
       <c r="V27">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W27">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y27">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z27">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="AA27">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="AB27">
         <v>6.8</v>
       </c>
       <c r="AC27">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD27">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AE27">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AF27">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AG27">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH27">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AI27">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AJ27">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK27">
         <v>34</v>
       </c>
       <c r="AL27">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AM27">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AN27">
         <v>27</v>
       </c>
       <c r="AO27">
-        <v>370</v>
+        <v>700</v>
       </c>
       <c r="AP27">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="AQ27">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="AR27">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AS27">
+        <v>6.6</v>
+      </c>
+      <c r="AT27">
+        <v>3.5</v>
+      </c>
+      <c r="AU27">
+        <v>4.9</v>
+      </c>
+      <c r="AV27">
+        <v>5.5</v>
+      </c>
+      <c r="AW27">
+        <v>6.6</v>
+      </c>
+      <c r="AX27">
         <v>4.4</v>
       </c>
-      <c r="AT27">
-        <v>2.7</v>
-      </c>
-      <c r="AU27">
-        <v>3.05</v>
-      </c>
-      <c r="AV27">
-        <v>3.95</v>
-      </c>
-      <c r="AW27">
+      <c r="AY27">
         <v>4.3</v>
       </c>
-      <c r="AX27">
-        <v>3.15</v>
-      </c>
-      <c r="AY27">
-        <v>3.35</v>
-      </c>
       <c r="AZ27">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="BA27">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BB27">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="BC27">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="BD27">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BE27">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF27">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="BG27">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH27">
         <v>2.76</v>
@@ -7553,22 +7553,22 @@
         <v>201</v>
       </c>
       <c r="F28">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G28">
         <v>1.82</v>
       </c>
       <c r="H28">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I28">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J28">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K28">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L28">
         <v>1.2</v>
@@ -7601,19 +7601,19 @@
         <v>2.74</v>
       </c>
       <c r="V28">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W28">
         <v>2.22</v>
       </c>
       <c r="X28">
+        <v>40</v>
+      </c>
+      <c r="Y28">
+        <v>32</v>
+      </c>
+      <c r="Z28">
         <v>44</v>
-      </c>
-      <c r="Y28">
-        <v>34</v>
-      </c>
-      <c r="Z28">
-        <v>50</v>
       </c>
       <c r="AA28">
         <v>100</v>
@@ -7628,7 +7628,7 @@
         <v>22</v>
       </c>
       <c r="AE28">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AF28">
         <v>18.5</v>
@@ -7640,37 +7640,37 @@
         <v>18.5</v>
       </c>
       <c r="AI28">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ28">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK28">
         <v>18.5</v>
       </c>
       <c r="AL28">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AM28">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN28">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AO28">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AP28">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ28">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR28">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS28">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AT28">
         <v>13</v>
@@ -7682,7 +7682,7 @@
         <v>14.5</v>
       </c>
       <c r="AW28">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX28">
         <v>12</v>
@@ -7694,7 +7694,7 @@
         <v>12</v>
       </c>
       <c r="BA28">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB28">
         <v>15.5</v>
@@ -7706,7 +7706,7 @@
         <v>17</v>
       </c>
       <c r="BE28">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BF28">
         <v>4.7</v>
@@ -7724,46 +7724,46 @@
         <v>9</v>
       </c>
       <c r="BK28">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN28">
         <v>5.4</v>
       </c>
       <c r="BO28">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP28">
         <v>11.5</v>
       </c>
       <c r="BQ28">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR28">
         <v>18.5</v>
       </c>
       <c r="BS28">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT28">
         <v>9</v>
       </c>
       <c r="BU28">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV28">
         <v>30</v>
       </c>
       <c r="BW28">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX28">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY28">
         <v>7.4</v>
@@ -7772,7 +7772,7 @@
         <v>11.5</v>
       </c>
       <c r="CA28">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="CB28" t="s">
         <v>217</v>
@@ -7795,13 +7795,13 @@
         <v>202</v>
       </c>
       <c r="F29">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="G29">
         <v>1.68</v>
       </c>
       <c r="H29">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I29">
         <v>6.4</v>
@@ -7810,10 +7810,10 @@
         <v>4</v>
       </c>
       <c r="K29">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L29">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M29">
         <v>1.06</v>
@@ -7822,13 +7822,13 @@
         <v>3.85</v>
       </c>
       <c r="O29">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P29">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q29">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R29">
         <v>1.39</v>
@@ -7840,7 +7840,7 @@
         <v>1.92</v>
       </c>
       <c r="U29">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V29">
         <v>1.18</v>
@@ -7849,28 +7849,28 @@
         <v>2.46</v>
       </c>
       <c r="X29">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y29">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z29">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="AA29">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AB29">
         <v>8.800000000000001</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD29">
         <v>25</v>
       </c>
       <c r="AE29">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AF29">
         <v>9.6</v>
@@ -7879,13 +7879,13 @@
         <v>10</v>
       </c>
       <c r="AH29">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AI29">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="AJ29">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AK29">
         <v>20</v>
@@ -7894,16 +7894,16 @@
         <v>42</v>
       </c>
       <c r="AM29">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AN29">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AO29">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AP29">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ29">
         <v>16</v>
@@ -7912,7 +7912,7 @@
         <v>38</v>
       </c>
       <c r="AS29">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT29">
         <v>7.4</v>
@@ -7924,7 +7924,7 @@
         <v>20</v>
       </c>
       <c r="AW29">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX29">
         <v>8.199999999999999</v>
@@ -7936,7 +7936,7 @@
         <v>19</v>
       </c>
       <c r="BA29">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB29">
         <v>13</v>
@@ -7948,13 +7948,13 @@
         <v>29</v>
       </c>
       <c r="BE29">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BF29">
         <v>7.6</v>
       </c>
       <c r="BG29">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BH29">
         <v>3.7</v>
@@ -7966,13 +7966,13 @@
         <v>11</v>
       </c>
       <c r="BK29">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN29">
         <v>4.4</v>
@@ -7981,40 +7981,40 @@
         <v>3.3</v>
       </c>
       <c r="BP29">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ29">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR29">
         <v>27</v>
       </c>
       <c r="BS29">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT29">
         <v>9.6</v>
       </c>
       <c r="BU29">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV29">
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BZ29">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA29">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB29" t="s">
         <v>217</v>
@@ -8037,22 +8037,22 @@
         <v>203</v>
       </c>
       <c r="F30">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G30">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H30">
         <v>2.4</v>
       </c>
       <c r="I30">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J30">
         <v>3.25</v>
       </c>
       <c r="K30">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L30">
         <v>1.38</v>
@@ -8067,7 +8067,7 @@
         <v>1.38</v>
       </c>
       <c r="P30">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q30">
         <v>2.12</v>
@@ -8082,22 +8082,22 @@
         <v>1.85</v>
       </c>
       <c r="U30">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V30">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W30">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X30">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y30">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z30">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA30">
         <v>36</v>
@@ -8112,7 +8112,7 @@
         <v>12</v>
       </c>
       <c r="AE30">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AF30">
         <v>23</v>
@@ -8127,19 +8127,19 @@
         <v>44</v>
       </c>
       <c r="AJ30">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AK30">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AL30">
         <v>55</v>
       </c>
       <c r="AM30">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN30">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="AO30">
         <v>25</v>
@@ -8157,7 +8157,7 @@
         <v>25</v>
       </c>
       <c r="AT30">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU30">
         <v>6.8</v>
@@ -8181,19 +8181,19 @@
         <v>32</v>
       </c>
       <c r="BB30">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="BC30">
         <v>30</v>
       </c>
       <c r="BD30">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE30">
+        <v>10</v>
+      </c>
+      <c r="BF30">
         <v>9.4</v>
-      </c>
-      <c r="BF30">
-        <v>8.199999999999999</v>
       </c>
       <c r="BG30">
         <v>21</v>
@@ -8202,7 +8202,7 @@
         <v>3.25</v>
       </c>
       <c r="BI30">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="BJ30">
         <v>9.800000000000001</v>
@@ -8220,7 +8220,7 @@
         <v>6.4</v>
       </c>
       <c r="BO30">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BP30">
         <v>27</v>
@@ -8238,7 +8238,7 @@
         <v>5.3</v>
       </c>
       <c r="BU30">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BV30">
         <v>19</v>
@@ -8279,19 +8279,19 @@
         <v>204</v>
       </c>
       <c r="F31">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="G31">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="H31">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I31">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J31">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K31">
         <v>4.3</v>
@@ -8303,100 +8303,100 @@
         <v>1.07</v>
       </c>
       <c r="N31">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O31">
         <v>1.33</v>
       </c>
       <c r="P31">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q31">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R31">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S31">
         <v>3.5</v>
       </c>
       <c r="T31">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U31">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V31">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W31">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="X31">
         <v>17.5</v>
       </c>
       <c r="Y31">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="Z31">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA31">
-        <v>230</v>
+        <v>900</v>
       </c>
       <c r="AB31">
         <v>8</v>
       </c>
       <c r="AC31">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD31">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="AE31">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="AF31">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG31">
         <v>10</v>
       </c>
       <c r="AH31">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI31">
-        <v>120</v>
+        <v>320</v>
       </c>
       <c r="AJ31">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AK31">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AL31">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AM31">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AN31">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO31">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AP31">
         <v>12.5</v>
       </c>
       <c r="AQ31">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AR31">
         <v>9</v>
       </c>
       <c r="AS31">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT31">
         <v>7</v>
@@ -8405,46 +8405,46 @@
         <v>8</v>
       </c>
       <c r="AV31">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AW31">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX31">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY31">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ31">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BA31">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB31">
         <v>14</v>
       </c>
       <c r="BC31">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BD31">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE31">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF31">
         <v>9.4</v>
       </c>
       <c r="BG31">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH31">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI31">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BJ31">
         <v>11</v>
@@ -8459,13 +8459,13 @@
         <v>14.5</v>
       </c>
       <c r="BN31">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO31">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP31">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ31">
         <v>6.6</v>
@@ -8477,10 +8477,10 @@
         <v>10</v>
       </c>
       <c r="BT31">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU31">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV31">
         <v>1000</v>
@@ -8492,13 +8492,13 @@
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ31">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA31">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB31" t="s">
         <v>217</v>
@@ -8527,13 +8527,13 @@
         <v>1.93</v>
       </c>
       <c r="H32">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I32">
         <v>5</v>
       </c>
       <c r="J32">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K32">
         <v>5</v>
@@ -8542,16 +8542,16 @@
         <v>1.24</v>
       </c>
       <c r="M32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N32">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="O32">
         <v>1.17</v>
       </c>
       <c r="P32">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="Q32">
         <v>1.51</v>
@@ -8584,19 +8584,19 @@
         <v>50</v>
       </c>
       <c r="AA32">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AB32">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC32">
         <v>11.5</v>
       </c>
       <c r="AD32">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE32">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AF32">
         <v>15</v>
@@ -8608,7 +8608,7 @@
         <v>17.5</v>
       </c>
       <c r="AI32">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="AJ32">
         <v>22</v>
@@ -8620,7 +8620,7 @@
         <v>28</v>
       </c>
       <c r="AM32">
-        <v>70</v>
+        <v>580</v>
       </c>
       <c r="AN32">
         <v>8.199999999999999</v>
@@ -8629,22 +8629,22 @@
         <v>48</v>
       </c>
       <c r="AP32">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AQ32">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AR32">
         <v>6.4</v>
       </c>
       <c r="AS32">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT32">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AU32">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AV32">
         <v>5.5</v>
@@ -8653,34 +8653,34 @@
         <v>6.6</v>
       </c>
       <c r="AX32">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AY32">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AZ32">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BA32">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB32">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BC32">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BD32">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BE32">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF32">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BG32">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH32">
         <v>4.8</v>
@@ -8766,19 +8766,19 @@
         <v>1.74</v>
       </c>
       <c r="G33">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H33">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I33">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J33">
         <v>4.4</v>
       </c>
       <c r="K33">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L33">
         <v>1.23</v>
@@ -8793,7 +8793,7 @@
         <v>1.14</v>
       </c>
       <c r="P33">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q33">
         <v>1.41</v>
@@ -8802,19 +8802,19 @@
         <v>1.79</v>
       </c>
       <c r="S33">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T33">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="U33">
         <v>2.68</v>
       </c>
       <c r="V33">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W33">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X33">
         <v>42</v>
@@ -8823,13 +8823,13 @@
         <v>34</v>
       </c>
       <c r="Z33">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA33">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AB33">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC33">
         <v>14.5</v>
@@ -8838,10 +8838,10 @@
         <v>23</v>
       </c>
       <c r="AE33">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF33">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG33">
         <v>13.5</v>
@@ -8853,16 +8853,16 @@
         <v>50</v>
       </c>
       <c r="AJ33">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK33">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL33">
         <v>30</v>
       </c>
       <c r="AM33">
-        <v>65</v>
+        <v>580</v>
       </c>
       <c r="AN33">
         <v>7.6</v>
@@ -8883,7 +8883,7 @@
         <v>4.5</v>
       </c>
       <c r="AT33">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU33">
         <v>8.800000000000001</v>
@@ -8898,7 +8898,7 @@
         <v>11.5</v>
       </c>
       <c r="AY33">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ33">
         <v>11.5</v>
@@ -8910,19 +8910,19 @@
         <v>15</v>
       </c>
       <c r="BC33">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD33">
         <v>17</v>
       </c>
       <c r="BE33">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF33">
         <v>4.8</v>
       </c>
       <c r="BG33">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BH33">
         <v>5.2</v>
@@ -8940,7 +8940,7 @@
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN33">
         <v>5.3</v>
@@ -8958,10 +8958,10 @@
         <v>19</v>
       </c>
       <c r="BS33">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT33">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU33">
         <v>5.6</v>
@@ -8970,16 +8970,16 @@
         <v>40</v>
       </c>
       <c r="BW33">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX33">
         <v>42</v>
       </c>
       <c r="BY33">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ33">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA33">
         <v>7.4</v>
@@ -9005,7 +9005,7 @@
         <v>207</v>
       </c>
       <c r="F34">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G34">
         <v>1.73</v>
@@ -9014,7 +9014,7 @@
         <v>7</v>
       </c>
       <c r="I34">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J34">
         <v>3.5</v>
@@ -9023,22 +9023,22 @@
         <v>3.95</v>
       </c>
       <c r="L34">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M34">
         <v>1.11</v>
       </c>
       <c r="N34">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O34">
         <v>1.49</v>
       </c>
       <c r="P34">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q34">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R34">
         <v>1.21</v>
@@ -9050,10 +9050,10 @@
         <v>2.34</v>
       </c>
       <c r="U34">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V34">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W34">
         <v>2.36</v>
@@ -9068,7 +9068,7 @@
         <v>90</v>
       </c>
       <c r="AA34">
-        <v>370</v>
+        <v>700</v>
       </c>
       <c r="AB34">
         <v>6</v>
@@ -9077,10 +9077,10 @@
         <v>10</v>
       </c>
       <c r="AD34">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AE34">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AF34">
         <v>8.6</v>
@@ -9092,25 +9092,25 @@
         <v>32</v>
       </c>
       <c r="AI34">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AJ34">
         <v>17</v>
       </c>
       <c r="AK34">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL34">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AM34">
-        <v>330</v>
+        <v>700</v>
       </c>
       <c r="AN34">
         <v>16.5</v>
       </c>
       <c r="AO34">
-        <v>390</v>
+        <v>700</v>
       </c>
       <c r="AP34">
         <v>7.2</v>
@@ -9119,22 +9119,22 @@
         <v>12.5</v>
       </c>
       <c r="AR34">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS34">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT34">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AU34">
         <v>6.4</v>
       </c>
       <c r="AV34">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AW34">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX34">
         <v>6.2</v>
@@ -9143,10 +9143,10 @@
         <v>8</v>
       </c>
       <c r="AZ34">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="BA34">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB34">
         <v>12</v>
@@ -9158,13 +9158,13 @@
         <v>42</v>
       </c>
       <c r="BE34">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF34">
         <v>11.5</v>
       </c>
       <c r="BG34">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH34">
         <v>2.88</v>
@@ -9253,19 +9253,19 @@
         <v>5</v>
       </c>
       <c r="H35">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="I35">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J35">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K35">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L35">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M35">
         <v>1.1</v>
@@ -9274,7 +9274,7 @@
         <v>2.96</v>
       </c>
       <c r="O35">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P35">
         <v>1.67</v>
@@ -9286,7 +9286,7 @@
         <v>1.24</v>
       </c>
       <c r="S35">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T35">
         <v>2</v>
@@ -9295,10 +9295,10 @@
         <v>1.85</v>
       </c>
       <c r="V35">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W35">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X35">
         <v>13</v>
@@ -9313,7 +9313,7 @@
         <v>30</v>
       </c>
       <c r="AB35">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AC35">
         <v>9</v>
@@ -9325,7 +9325,7 @@
         <v>28</v>
       </c>
       <c r="AF35">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AG35">
         <v>23</v>
@@ -9337,19 +9337,19 @@
         <v>50</v>
       </c>
       <c r="AJ35">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK35">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AL35">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AM35">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN35">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AO35">
         <v>24</v>
@@ -9364,7 +9364,7 @@
         <v>9</v>
       </c>
       <c r="AS35">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="AT35">
         <v>10.5</v>
@@ -9379,7 +9379,7 @@
         <v>19</v>
       </c>
       <c r="AX35">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="AY35">
         <v>12.5</v>
@@ -9388,28 +9388,28 @@
         <v>16</v>
       </c>
       <c r="BA35">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BB35">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BC35">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BD35">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE35">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF35">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BG35">
         <v>17</v>
       </c>
       <c r="BH35">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI35">
         <v>2.48</v>
@@ -9418,13 +9418,13 @@
         <v>11</v>
       </c>
       <c r="BK35">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN35">
         <v>7.8</v>
@@ -9436,13 +9436,13 @@
         <v>1000</v>
       </c>
       <c r="BQ35">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR35">
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT35">
         <v>4.7</v>
@@ -9454,19 +9454,19 @@
         <v>16</v>
       </c>
       <c r="BW35">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ35">
         <v>1000</v>
       </c>
       <c r="CA35">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB35" t="s">
         <v>217</v>
@@ -9495,10 +9495,10 @@
         <v>1.38</v>
       </c>
       <c r="H36">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I36">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="J36">
         <v>5.4</v>
@@ -9513,13 +9513,13 @@
         <v>1.01</v>
       </c>
       <c r="N36">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="O36">
         <v>1.21</v>
       </c>
       <c r="P36">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q36">
         <v>1.62</v>
@@ -9537,10 +9537,10 @@
         <v>1.83</v>
       </c>
       <c r="V36">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W36">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X36">
         <v>28</v>
@@ -9555,10 +9555,10 @@
         <v>480</v>
       </c>
       <c r="AB36">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC36">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AD36">
         <v>48</v>
@@ -9567,13 +9567,13 @@
         <v>210</v>
       </c>
       <c r="AF36">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG36">
         <v>13</v>
       </c>
       <c r="AH36">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AI36">
         <v>160</v>
@@ -9582,73 +9582,73 @@
         <v>13</v>
       </c>
       <c r="AK36">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AL36">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM36">
         <v>180</v>
       </c>
       <c r="AN36">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AO36">
         <v>270</v>
       </c>
       <c r="AP36">
-        <v>3.85</v>
+        <v>5.9</v>
       </c>
       <c r="AQ36">
+        <v>6.4</v>
+      </c>
+      <c r="AR36">
+        <v>7</v>
+      </c>
+      <c r="AS36">
+        <v>7.4</v>
+      </c>
+      <c r="AT36">
+        <v>4.2</v>
+      </c>
+      <c r="AU36">
+        <v>4.9</v>
+      </c>
+      <c r="AV36">
+        <v>6.4</v>
+      </c>
+      <c r="AW36">
+        <v>7.2</v>
+      </c>
+      <c r="AX36">
         <v>4</v>
       </c>
-      <c r="AR36">
-        <v>4.3</v>
-      </c>
-      <c r="AS36">
-        <v>4.4</v>
-      </c>
-      <c r="AT36">
-        <v>3.2</v>
-      </c>
-      <c r="AU36">
-        <v>3.5</v>
-      </c>
-      <c r="AV36">
-        <v>4.1</v>
-      </c>
-      <c r="AW36">
-        <v>4.4</v>
-      </c>
-      <c r="AX36">
-        <v>3.15</v>
-      </c>
       <c r="AY36">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="AZ36">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="BA36">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="BB36">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="BC36">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="BD36">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="BE36">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF36">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="BG36">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH36">
         <v>4.3</v>
@@ -9731,10 +9731,10 @@
         <v>210</v>
       </c>
       <c r="F37">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G37">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H37">
         <v>4.3</v>
@@ -9743,7 +9743,7 @@
         <v>4.9</v>
       </c>
       <c r="J37">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K37">
         <v>3.75</v>
@@ -9758,7 +9758,7 @@
         <v>3.2</v>
       </c>
       <c r="O37">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P37">
         <v>1.79</v>
@@ -9779,22 +9779,22 @@
         <v>1.94</v>
       </c>
       <c r="V37">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W37">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X37">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y37">
         <v>15.5</v>
       </c>
       <c r="Z37">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA37">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB37">
         <v>9.800000000000001</v>
@@ -9806,7 +9806,7 @@
         <v>23</v>
       </c>
       <c r="AE37">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF37">
         <v>12.5</v>
@@ -9818,7 +9818,7 @@
         <v>22</v>
       </c>
       <c r="AI37">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="AJ37">
         <v>26</v>
@@ -9830,28 +9830,28 @@
         <v>55</v>
       </c>
       <c r="AM37">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN37">
         <v>18.5</v>
       </c>
       <c r="AO37">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AP37">
         <v>10</v>
       </c>
       <c r="AQ37">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AR37">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="AS37">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT37">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU37">
         <v>7</v>
@@ -9860,7 +9860,7 @@
         <v>15.5</v>
       </c>
       <c r="AW37">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX37">
         <v>10</v>
@@ -9872,7 +9872,7 @@
         <v>17</v>
       </c>
       <c r="BA37">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB37">
         <v>20</v>
@@ -9881,16 +9881,16 @@
         <v>19.5</v>
       </c>
       <c r="BD37">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE37">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF37">
         <v>12.5</v>
       </c>
       <c r="BG37">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BH37">
         <v>3.25</v>
@@ -9973,25 +9973,25 @@
         <v>211</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G38">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H38">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I38">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J38">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K38">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="L38">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M38">
         <v>1.09</v>
@@ -10015,7 +10015,7 @@
         <v>4.3</v>
       </c>
       <c r="T38">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U38">
         <v>1.89</v>
@@ -10024,10 +10024,10 @@
         <v>1.26</v>
       </c>
       <c r="W38">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X38">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y38">
         <v>13.5</v>
@@ -10036,7 +10036,7 @@
         <v>36</v>
       </c>
       <c r="AA38">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB38">
         <v>8.199999999999999</v>
@@ -10048,7 +10048,7 @@
         <v>18.5</v>
       </c>
       <c r="AE38">
-        <v>65</v>
+        <v>370</v>
       </c>
       <c r="AF38">
         <v>13</v>
@@ -10060,25 +10060,25 @@
         <v>21</v>
       </c>
       <c r="AI38">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AJ38">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="AK38">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="AL38">
         <v>55</v>
       </c>
       <c r="AM38">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN38">
         <v>22</v>
       </c>
       <c r="AO38">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP38">
         <v>9.6</v>
@@ -10087,10 +10087,10 @@
         <v>10</v>
       </c>
       <c r="AR38">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="AS38">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT38">
         <v>6.8</v>
@@ -10102,7 +10102,7 @@
         <v>13.5</v>
       </c>
       <c r="AW38">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AX38">
         <v>10</v>
@@ -10114,25 +10114,25 @@
         <v>17</v>
       </c>
       <c r="BA38">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB38">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BC38">
         <v>21</v>
       </c>
       <c r="BD38">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE38">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF38">
         <v>15.5</v>
       </c>
       <c r="BG38">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH38">
         <v>3.15</v>
@@ -10183,7 +10183,7 @@
         <v>8.4</v>
       </c>
       <c r="BX38">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY38">
         <v>9</v>
@@ -10215,34 +10215,34 @@
         <v>212</v>
       </c>
       <c r="F39">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="G39">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="H39">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="I39">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J39">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K39">
         <v>3.45</v>
       </c>
       <c r="L39">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="M39">
         <v>1.12</v>
       </c>
       <c r="N39">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O39">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P39">
         <v>1.56</v>
@@ -10251,7 +10251,7 @@
         <v>2.58</v>
       </c>
       <c r="R39">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S39">
         <v>5.4</v>
@@ -10263,46 +10263,46 @@
         <v>1.72</v>
       </c>
       <c r="V39">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W39">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="X39">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y39">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="Z39">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AA39">
-        <v>180</v>
+        <v>900</v>
       </c>
       <c r="AB39">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AC39">
         <v>7.8</v>
       </c>
       <c r="AD39">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="AE39">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="AF39">
+        <v>12.5</v>
+      </c>
+      <c r="AG39">
         <v>13</v>
-      </c>
-      <c r="AG39">
-        <v>13.5</v>
       </c>
       <c r="AH39">
         <v>32</v>
       </c>
       <c r="AI39">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="AJ39">
         <v>30</v>
@@ -10314,37 +10314,37 @@
         <v>75</v>
       </c>
       <c r="AM39">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AN39">
         <v>30</v>
       </c>
       <c r="AO39">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AP39">
         <v>8</v>
       </c>
       <c r="AQ39">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR39">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="AS39">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="AT39">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AU39">
         <v>6.8</v>
       </c>
       <c r="AV39">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AW39">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="AX39">
         <v>9.199999999999999</v>
@@ -10353,10 +10353,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ39">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BA39">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BB39">
         <v>21</v>
@@ -10365,16 +10365,16 @@
         <v>20</v>
       </c>
       <c r="BD39">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BE39">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF39">
         <v>17.5</v>
       </c>
       <c r="BG39">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BH39">
         <v>2.74</v>
@@ -10466,10 +10466,10 @@
         <v>4.5</v>
       </c>
       <c r="I40">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J40">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K40">
         <v>3.95</v>
@@ -10705,7 +10705,7 @@
         <v>3.7</v>
       </c>
       <c r="H41">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I41">
         <v>2.66</v>
@@ -10989,10 +10989,10 @@
         <v>2.08</v>
       </c>
       <c r="V42">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W42">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X42">
         <v>19</v>
@@ -11288,7 +11288,7 @@
         <v>30</v>
       </c>
       <c r="AO43">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP43">
         <v>10.5</v>
@@ -11300,7 +11300,7 @@
         <v>4.5</v>
       </c>
       <c r="AS43">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT43">
         <v>8</v>
@@ -11312,7 +11312,7 @@
         <v>12.5</v>
       </c>
       <c r="AW43">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX43">
         <v>13</v>
@@ -11339,7 +11339,7 @@
         <v>5.3</v>
       </c>
       <c r="BF43">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG43">
         <v>5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -667,7 +667,7 @@
     <t>Everton De Vina</t>
   </si>
   <si>
-    <t>2026-07-26 19:25:08</t>
+    <t>2026-07-26 21:32:28</t>
   </si>
 </sst>
 </file>
@@ -1261,226 +1261,226 @@
         <v>175</v>
       </c>
       <c r="F2">
-        <v>1.76</v>
+        <v>1.1</v>
       </c>
       <c r="G2">
-        <v>1.8</v>
+        <v>1.12</v>
       </c>
       <c r="H2">
-        <v>5.3</v>
+        <v>40</v>
       </c>
       <c r="I2">
-        <v>5.6</v>
+        <v>60</v>
       </c>
       <c r="J2">
-        <v>3.8</v>
+        <v>12.5</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L2">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1.93</v>
+        <v>7.6</v>
       </c>
       <c r="Q2">
-        <v>2.02</v>
+        <v>1.14</v>
       </c>
       <c r="R2">
-        <v>1.35</v>
+        <v>2.46</v>
       </c>
       <c r="S2">
-        <v>3.65</v>
+        <v>1.65</v>
       </c>
       <c r="T2">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="U2">
-        <v>1.98</v>
+        <v>2.34</v>
       </c>
       <c r="V2">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>2.24</v>
+        <v>10</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AG2">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH2">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AI2">
         <v>90</v>
       </c>
       <c r="AJ2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AK2">
+        <v>7.8</v>
+      </c>
+      <c r="AL2">
+        <v>16.5</v>
+      </c>
+      <c r="AM2">
+        <v>75</v>
+      </c>
+      <c r="AN2">
+        <v>3.25</v>
+      </c>
+      <c r="AO2">
+        <v>170</v>
+      </c>
+      <c r="AP2">
         <v>19</v>
       </c>
-      <c r="AL2">
-        <v>38</v>
-      </c>
-      <c r="AM2">
-        <v>130</v>
-      </c>
-      <c r="AN2">
-        <v>12</v>
-      </c>
-      <c r="AO2">
-        <v>95</v>
-      </c>
-      <c r="AP2">
-        <v>13</v>
-      </c>
       <c r="AQ2">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AR2">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="AS2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="AT2">
-        <v>7.6</v>
+        <v>19</v>
       </c>
       <c r="AU2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AV2">
         <v>19</v>
       </c>
       <c r="AW2">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="AX2">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AY2">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA2">
+        <v>60</v>
+      </c>
+      <c r="BB2">
+        <v>6.4</v>
+      </c>
+      <c r="BC2">
+        <v>7.2</v>
+      </c>
+      <c r="BD2">
+        <v>15.5</v>
+      </c>
+      <c r="BE2">
         <v>50</v>
       </c>
-      <c r="BB2">
-        <v>16.5</v>
-      </c>
-      <c r="BC2">
-        <v>17</v>
-      </c>
-      <c r="BD2">
-        <v>34</v>
-      </c>
-      <c r="BE2">
-        <v>85</v>
-      </c>
       <c r="BF2">
-        <v>10.5</v>
+        <v>3.1</v>
       </c>
       <c r="BG2">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="BH2">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.8</v>
+        <v>3.95</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>7.6</v>
+        <v>3.95</v>
       </c>
       <c r="BL2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="BM2">
-        <v>14</v>
+        <v>3.8</v>
       </c>
       <c r="BN2">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BP2">
-        <v>12.5</v>
+        <v>1.6</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>1.56</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="BT2">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="BV2">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>11.5</v>
+        <v>3.95</v>
       </c>
       <c r="BX2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>12.5</v>
+        <v>3.95</v>
       </c>
       <c r="BZ2">
-        <v>24</v>
+        <v>5.6</v>
       </c>
       <c r="CA2">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="CB2" t="s">
         <v>217</v>
@@ -1503,226 +1503,226 @@
         <v>176</v>
       </c>
       <c r="F3">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="G3">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="H3">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I3">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="J3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L3">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="M3">
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P3">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q3">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R3">
         <v>1.3</v>
       </c>
       <c r="S3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T3">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U3">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V3">
         <v>1.42</v>
       </c>
       <c r="W3">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X3">
         <v>12.5</v>
       </c>
       <c r="Y3">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Z3">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD3">
-        <v>14</v>
+        <v>990</v>
       </c>
       <c r="AE3">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="AG3">
-        <v>11.5</v>
+        <v>990</v>
       </c>
       <c r="AH3">
-        <v>18</v>
+        <v>990</v>
       </c>
       <c r="AI3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO3">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
         <v>10.5</v>
       </c>
       <c r="AQ3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR3">
+        <v>2.24</v>
+      </c>
+      <c r="AS3">
+        <v>2.48</v>
+      </c>
+      <c r="AT3">
+        <v>8</v>
+      </c>
+      <c r="AU3">
+        <v>7</v>
+      </c>
+      <c r="AV3">
+        <v>2.46</v>
+      </c>
+      <c r="AW3">
+        <v>2.46</v>
+      </c>
+      <c r="AX3">
+        <v>3</v>
+      </c>
+      <c r="AY3">
+        <v>2.06</v>
+      </c>
+      <c r="AZ3">
+        <v>12</v>
+      </c>
+      <c r="BA3">
+        <v>44</v>
+      </c>
+      <c r="BB3">
+        <v>2.24</v>
+      </c>
+      <c r="BC3">
+        <v>2.24</v>
+      </c>
+      <c r="BD3">
+        <v>2.46</v>
+      </c>
+      <c r="BE3">
+        <v>2.46</v>
+      </c>
+      <c r="BF3">
+        <v>3.45</v>
+      </c>
+      <c r="BG3">
+        <v>2.46</v>
+      </c>
+      <c r="BH3">
+        <v>2.58</v>
+      </c>
+      <c r="BI3">
+        <v>2.42</v>
+      </c>
+      <c r="BJ3">
+        <v>12.5</v>
+      </c>
+      <c r="BK3">
+        <v>10</v>
+      </c>
+      <c r="BL3">
+        <v>330</v>
+      </c>
+      <c r="BM3">
+        <v>7.6</v>
+      </c>
+      <c r="BN3">
+        <v>5.2</v>
+      </c>
+      <c r="BO3">
+        <v>4.4</v>
+      </c>
+      <c r="BP3">
         <v>20</v>
       </c>
-      <c r="AS3">
-        <v>50</v>
-      </c>
-      <c r="AT3">
-        <v>8.6</v>
-      </c>
-      <c r="AU3">
-        <v>6.8</v>
-      </c>
-      <c r="AV3">
-        <v>13</v>
-      </c>
-      <c r="AW3">
-        <v>36</v>
-      </c>
-      <c r="AX3">
-        <v>13</v>
-      </c>
-      <c r="AY3">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3">
-        <v>16.5</v>
-      </c>
-      <c r="BA3">
-        <v>42</v>
-      </c>
-      <c r="BB3">
+      <c r="BQ3">
+        <v>16</v>
+      </c>
+      <c r="BR3">
+        <v>60</v>
+      </c>
+      <c r="BS3">
         <v>30</v>
       </c>
-      <c r="BC3">
-        <v>24</v>
-      </c>
-      <c r="BD3">
+      <c r="BT3">
+        <v>6.6</v>
+      </c>
+      <c r="BU3">
+        <v>5.5</v>
+      </c>
+      <c r="BV3">
+        <v>38</v>
+      </c>
+      <c r="BW3">
+        <v>18</v>
+      </c>
+      <c r="BX3">
+        <v>70</v>
+      </c>
+      <c r="BY3">
         <v>40</v>
       </c>
-      <c r="BE3">
-        <v>80</v>
-      </c>
-      <c r="BF3">
-        <v>21</v>
-      </c>
-      <c r="BG3">
-        <v>36</v>
-      </c>
-      <c r="BH3">
-        <v>3.2</v>
-      </c>
-      <c r="BI3">
-        <v>2.96</v>
-      </c>
-      <c r="BJ3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK3">
-        <v>6.2</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>15</v>
-      </c>
-      <c r="BN3">
-        <v>5.3</v>
-      </c>
-      <c r="BO3">
-        <v>4.7</v>
-      </c>
-      <c r="BP3">
-        <v>19</v>
-      </c>
-      <c r="BQ3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR3">
-        <v>34</v>
-      </c>
-      <c r="BS3">
-        <v>11</v>
-      </c>
-      <c r="BT3">
-        <v>6.4</v>
-      </c>
-      <c r="BU3">
-        <v>5.6</v>
-      </c>
-      <c r="BV3">
-        <v>27</v>
-      </c>
-      <c r="BW3">
-        <v>10</v>
-      </c>
-      <c r="BX3">
-        <v>42</v>
-      </c>
-      <c r="BY3">
-        <v>12</v>
-      </c>
       <c r="BZ3">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="CA3">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="CB3" t="s">
         <v>217</v>
@@ -1745,226 +1745,226 @@
         <v>177</v>
       </c>
       <c r="F4">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="G4">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="H4">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="I4">
+        <v>4.9</v>
+      </c>
+      <c r="J4">
+        <v>3.65</v>
+      </c>
+      <c r="K4">
         <v>3.9</v>
       </c>
-      <c r="J4">
-        <v>3.6</v>
-      </c>
-      <c r="K4">
-        <v>3.65</v>
-      </c>
       <c r="L4">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P4">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="Q4">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S4">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T4">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="U4">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V4">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="W4">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="X4">
+        <v>14</v>
+      </c>
+      <c r="Y4">
+        <v>16.5</v>
+      </c>
+      <c r="Z4">
+        <v>38</v>
+      </c>
+      <c r="AA4">
+        <v>130</v>
+      </c>
+      <c r="AB4">
+        <v>8.4</v>
+      </c>
+      <c r="AC4">
+        <v>8.4</v>
+      </c>
+      <c r="AD4">
+        <v>19</v>
+      </c>
+      <c r="AE4">
+        <v>70</v>
+      </c>
+      <c r="AF4">
+        <v>10.5</v>
+      </c>
+      <c r="AG4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH4">
+        <v>19.5</v>
+      </c>
+      <c r="AI4">
+        <v>65</v>
+      </c>
+      <c r="AJ4">
+        <v>19</v>
+      </c>
+      <c r="AK4">
+        <v>18.5</v>
+      </c>
+      <c r="AL4">
+        <v>34</v>
+      </c>
+      <c r="AM4">
+        <v>120</v>
+      </c>
+      <c r="AN4">
+        <v>12.5</v>
+      </c>
+      <c r="AO4">
+        <v>85</v>
+      </c>
+      <c r="AP4">
+        <v>13.5</v>
+      </c>
+      <c r="AQ4">
         <v>14.5</v>
       </c>
-      <c r="Y4">
-        <v>14</v>
-      </c>
-      <c r="Z4">
-        <v>28</v>
-      </c>
-      <c r="AA4">
-        <v>80</v>
-      </c>
-      <c r="AB4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC4">
+      <c r="AR4">
+        <v>32</v>
+      </c>
+      <c r="AS4">
+        <v>100</v>
+      </c>
+      <c r="AT4">
+        <v>8</v>
+      </c>
+      <c r="AU4">
+        <v>8</v>
+      </c>
+      <c r="AV4">
+        <v>17.5</v>
+      </c>
+      <c r="AW4">
+        <v>60</v>
+      </c>
+      <c r="AX4">
+        <v>10</v>
+      </c>
+      <c r="AY4">
+        <v>9.4</v>
+      </c>
+      <c r="AZ4">
+        <v>17.5</v>
+      </c>
+      <c r="BA4">
+        <v>55</v>
+      </c>
+      <c r="BB4">
+        <v>18</v>
+      </c>
+      <c r="BC4">
+        <v>18</v>
+      </c>
+      <c r="BD4">
+        <v>32</v>
+      </c>
+      <c r="BE4">
+        <v>100</v>
+      </c>
+      <c r="BF4">
+        <v>11.5</v>
+      </c>
+      <c r="BG4">
+        <v>65</v>
+      </c>
+      <c r="BH4">
+        <v>3.35</v>
+      </c>
+      <c r="BI4">
+        <v>2.9</v>
+      </c>
+      <c r="BJ4">
+        <v>970</v>
+      </c>
+      <c r="BK4">
+        <v>7.6</v>
+      </c>
+      <c r="BL4">
+        <v>940</v>
+      </c>
+      <c r="BM4">
+        <v>3.35</v>
+      </c>
+      <c r="BN4">
+        <v>4.6</v>
+      </c>
+      <c r="BO4">
+        <v>3.95</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>9.6</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>3.45</v>
+      </c>
+      <c r="BT4">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD4">
-        <v>16</v>
-      </c>
-      <c r="AE4">
-        <v>50</v>
-      </c>
-      <c r="AF4">
-        <v>12.5</v>
-      </c>
-      <c r="AG4">
-        <v>10.5</v>
-      </c>
-      <c r="AH4">
-        <v>19</v>
-      </c>
-      <c r="AI4">
-        <v>60</v>
-      </c>
-      <c r="AJ4">
-        <v>26</v>
-      </c>
-      <c r="AK4">
-        <v>22</v>
-      </c>
-      <c r="AL4">
-        <v>38</v>
-      </c>
-      <c r="AM4">
-        <v>110</v>
-      </c>
-      <c r="AN4">
-        <v>17</v>
-      </c>
-      <c r="AO4">
-        <v>55</v>
-      </c>
-      <c r="AP4">
-        <v>12.5</v>
-      </c>
-      <c r="AQ4">
-        <v>13</v>
-      </c>
-      <c r="AR4">
-        <v>24</v>
-      </c>
-      <c r="AS4">
-        <v>70</v>
-      </c>
-      <c r="AT4">
-        <v>8.4</v>
-      </c>
-      <c r="AU4">
-        <v>7.4</v>
-      </c>
-      <c r="AV4">
-        <v>14.5</v>
-      </c>
-      <c r="AW4">
-        <v>42</v>
-      </c>
-      <c r="AX4">
-        <v>11.5</v>
-      </c>
-      <c r="AY4">
-        <v>9.6</v>
-      </c>
-      <c r="AZ4">
-        <v>16.5</v>
-      </c>
-      <c r="BA4">
-        <v>50</v>
-      </c>
-      <c r="BB4">
-        <v>23</v>
-      </c>
-      <c r="BC4">
-        <v>19.5</v>
-      </c>
-      <c r="BD4">
-        <v>34</v>
-      </c>
-      <c r="BE4">
-        <v>38</v>
-      </c>
-      <c r="BF4">
-        <v>15</v>
-      </c>
-      <c r="BG4">
-        <v>46</v>
-      </c>
-      <c r="BH4">
-        <v>3.3</v>
-      </c>
-      <c r="BI4">
-        <v>3</v>
-      </c>
-      <c r="BJ4">
-        <v>9.6</v>
-      </c>
-      <c r="BK4">
-        <v>8.4</v>
-      </c>
-      <c r="BL4">
-        <v>130</v>
-      </c>
-      <c r="BM4">
-        <v>17.5</v>
-      </c>
-      <c r="BN4">
-        <v>4.9</v>
-      </c>
-      <c r="BO4">
-        <v>4.4</v>
-      </c>
-      <c r="BP4">
-        <v>15.5</v>
-      </c>
-      <c r="BQ4">
-        <v>13.5</v>
-      </c>
-      <c r="BR4">
-        <v>30</v>
-      </c>
-      <c r="BS4">
-        <v>21</v>
-      </c>
-      <c r="BT4">
+      <c r="BU4">
         <v>7</v>
       </c>
-      <c r="BU4">
-        <v>6.2</v>
-      </c>
       <c r="BV4">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>26</v>
+        <v>3.45</v>
       </c>
       <c r="BX4">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>13.5</v>
+        <v>3.45</v>
       </c>
       <c r="BZ4">
-        <v>27</v>
+        <v>960</v>
       </c>
       <c r="CA4">
-        <v>11.5</v>
+        <v>3.45</v>
       </c>
       <c r="CB4" t="s">
         <v>217</v>
@@ -1987,25 +1987,25 @@
         <v>178</v>
       </c>
       <c r="F5">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="G5">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="I5">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="J5">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M5">
         <v>1.06</v>
@@ -2014,199 +2014,199 @@
         <v>4.4</v>
       </c>
       <c r="O5">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P5">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="Q5">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R5">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S5">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T5">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="U5">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V5">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W5">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="X5">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA5">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB5">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD5">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE5">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AG5">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AH5">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI5">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ5">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK5">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL5">
         <v>32</v>
       </c>
       <c r="AM5">
+        <v>95</v>
+      </c>
+      <c r="AN5">
+        <v>9.4</v>
+      </c>
+      <c r="AO5">
+        <v>90</v>
+      </c>
+      <c r="AP5">
+        <v>15.5</v>
+      </c>
+      <c r="AQ5">
+        <v>18.5</v>
+      </c>
+      <c r="AR5">
+        <v>44</v>
+      </c>
+      <c r="AS5">
         <v>120</v>
       </c>
-      <c r="AN5">
+      <c r="AT5">
         <v>8.199999999999999</v>
       </c>
-      <c r="AO5">
-        <v>110</v>
-      </c>
-      <c r="AP5">
-        <v>16.5</v>
-      </c>
-      <c r="AQ5">
-        <v>21</v>
-      </c>
-      <c r="AR5">
-        <v>48</v>
-      </c>
-      <c r="AS5">
+      <c r="AU5">
+        <v>8.4</v>
+      </c>
+      <c r="AV5">
+        <v>20</v>
+      </c>
+      <c r="AW5">
         <v>65</v>
       </c>
-      <c r="AT5">
-        <v>8.6</v>
-      </c>
-      <c r="AU5">
-        <v>9</v>
-      </c>
-      <c r="AV5">
-        <v>21</v>
-      </c>
-      <c r="AW5">
-        <v>75</v>
-      </c>
       <c r="AX5">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY5">
         <v>9</v>
       </c>
       <c r="AZ5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA5">
+        <v>60</v>
+      </c>
+      <c r="BB5">
+        <v>15</v>
+      </c>
+      <c r="BC5">
+        <v>15.5</v>
+      </c>
+      <c r="BD5">
+        <v>29</v>
+      </c>
+      <c r="BE5">
+        <v>85</v>
+      </c>
+      <c r="BF5">
+        <v>8.4</v>
+      </c>
+      <c r="BG5">
         <v>70</v>
       </c>
-      <c r="BB5">
-        <v>13.5</v>
-      </c>
-      <c r="BC5">
-        <v>14.5</v>
-      </c>
-      <c r="BD5">
-        <v>28</v>
-      </c>
-      <c r="BE5">
-        <v>100</v>
-      </c>
-      <c r="BF5">
-        <v>7.4</v>
-      </c>
-      <c r="BG5">
-        <v>80</v>
-      </c>
       <c r="BH5">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI5">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL5">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM5">
-        <v>14.5</v>
+        <v>110</v>
       </c>
       <c r="BN5">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BO5">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BP5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BQ5">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BR5">
         <v>25</v>
       </c>
       <c r="BS5">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT5">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU5">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BV5">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BW5">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX5">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BZ5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CA5">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="CB5" t="s">
         <v>217</v>
@@ -2229,19 +2229,19 @@
         <v>179</v>
       </c>
       <c r="F6">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="G6">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H6">
         <v>7.8</v>
       </c>
       <c r="I6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K6">
         <v>5</v>
@@ -2265,16 +2265,16 @@
         <v>1.82</v>
       </c>
       <c r="R6">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S6">
         <v>3.05</v>
       </c>
       <c r="T6">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U6">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V6">
         <v>1.13</v>
@@ -2283,10 +2283,10 @@
         <v>3</v>
       </c>
       <c r="X6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z6">
         <v>75</v>
@@ -2295,7 +2295,7 @@
         <v>320</v>
       </c>
       <c r="AB6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC6">
         <v>11</v>
@@ -2307,7 +2307,7 @@
         <v>160</v>
       </c>
       <c r="AF6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG6">
         <v>10.5</v>
@@ -2316,13 +2316,13 @@
         <v>26</v>
       </c>
       <c r="AI6">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AJ6">
         <v>13</v>
       </c>
       <c r="AK6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL6">
         <v>38</v>
@@ -2331,37 +2331,37 @@
         <v>200</v>
       </c>
       <c r="AN6">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO6">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AP6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ6">
         <v>22</v>
       </c>
       <c r="AR6">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="AS6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT6">
         <v>7.6</v>
       </c>
       <c r="AU6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AW6">
-        <v>70</v>
+        <v>11.5</v>
       </c>
       <c r="AX6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY6">
         <v>9.199999999999999</v>
@@ -2370,7 +2370,7 @@
         <v>21</v>
       </c>
       <c r="BA6">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BB6">
         <v>11.5</v>
@@ -2382,13 +2382,13 @@
         <v>30</v>
       </c>
       <c r="BE6">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="BF6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH6">
         <v>3.85</v>
@@ -2406,10 +2406,10 @@
         <v>150</v>
       </c>
       <c r="BM6">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="BN6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BO6">
         <v>3.55</v>
@@ -2424,7 +2424,7 @@
         <v>26</v>
       </c>
       <c r="BS6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT6">
         <v>12</v>
@@ -2436,19 +2436,19 @@
         <v>75</v>
       </c>
       <c r="BW6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX6">
         <v>75</v>
       </c>
       <c r="BY6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
         <v>16.5</v>
       </c>
       <c r="CA6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB6" t="s">
         <v>217</v>
@@ -2471,7 +2471,7 @@
         <v>180</v>
       </c>
       <c r="F7">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G7">
         <v>1.64</v>
@@ -2486,13 +2486,13 @@
         <v>3.6</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L7">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M7">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N7">
         <v>2.84</v>
@@ -2501,16 +2501,16 @@
         <v>1.41</v>
       </c>
       <c r="P7">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q7">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R7">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S7">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="T7">
         <v>2.2</v>
@@ -2519,13 +2519,13 @@
         <v>1.64</v>
       </c>
       <c r="V7">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W7">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="X7">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y7">
         <v>23</v>
@@ -2537,7 +2537,7 @@
         <v>370</v>
       </c>
       <c r="AB7">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AC7">
         <v>9.6</v>
@@ -2570,7 +2570,7 @@
         <v>120</v>
       </c>
       <c r="AM7">
-        <v>250</v>
+        <v>580</v>
       </c>
       <c r="AN7">
         <v>14</v>
@@ -2579,58 +2579,58 @@
         <v>390</v>
       </c>
       <c r="AP7">
+        <v>5.1</v>
+      </c>
+      <c r="AQ7">
+        <v>6.2</v>
+      </c>
+      <c r="AR7">
+        <v>7.8</v>
+      </c>
+      <c r="AS7">
+        <v>8.6</v>
+      </c>
+      <c r="AT7">
+        <v>3.85</v>
+      </c>
+      <c r="AU7">
         <v>4.9</v>
       </c>
-      <c r="AQ7">
-        <v>5.7</v>
-      </c>
-      <c r="AR7">
+      <c r="AV7">
+        <v>7</v>
+      </c>
+      <c r="AW7">
+        <v>8.4</v>
+      </c>
+      <c r="AX7">
+        <v>4.5</v>
+      </c>
+      <c r="AY7">
+        <v>4.9</v>
+      </c>
+      <c r="AZ7">
         <v>6.8</v>
       </c>
-      <c r="AS7">
-        <v>7.4</v>
-      </c>
-      <c r="AT7">
-        <v>3.55</v>
-      </c>
-      <c r="AU7">
-        <v>4.2</v>
-      </c>
-      <c r="AV7">
+      <c r="BA7">
+        <v>8.4</v>
+      </c>
+      <c r="BB7">
         <v>6.2</v>
       </c>
-      <c r="AW7">
-        <v>7.2</v>
-      </c>
-      <c r="AX7">
-        <v>4</v>
-      </c>
-      <c r="AY7">
-        <v>4.5</v>
-      </c>
-      <c r="AZ7">
-        <v>6</v>
-      </c>
-      <c r="BA7">
-        <v>7.2</v>
-      </c>
-      <c r="BB7">
-        <v>5.1</v>
-      </c>
       <c r="BC7">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD7">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE7">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF7">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BG7">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH7">
         <v>3.15</v>
@@ -2716,7 +2716,7 @@
         <v>13</v>
       </c>
       <c r="G8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="H8">
         <v>1.23</v>
@@ -2725,7 +2725,7 @@
         <v>1.28</v>
       </c>
       <c r="J8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K8">
         <v>8.199999999999999</v>
@@ -2743,25 +2743,25 @@
         <v>1.12</v>
       </c>
       <c r="P8">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q8">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="R8">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="S8">
         <v>1.89</v>
       </c>
       <c r="T8">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V8">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="W8">
         <v>1.06</v>
@@ -2770,13 +2770,13 @@
         <v>46</v>
       </c>
       <c r="Y8">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z8">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AA8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AB8">
         <v>70</v>
@@ -2800,7 +2800,7 @@
         <v>30</v>
       </c>
       <c r="AI8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ8">
         <v>550</v>
@@ -2815,16 +2815,16 @@
         <v>130</v>
       </c>
       <c r="AN8">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AO8">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AP8">
         <v>30</v>
       </c>
       <c r="AQ8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR8">
         <v>9</v>
@@ -2845,7 +2845,7 @@
         <v>11</v>
       </c>
       <c r="AX8">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY8">
         <v>40</v>
@@ -2857,31 +2857,31 @@
         <v>24</v>
       </c>
       <c r="BB8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC8">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD8">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BE8">
-        <v>28</v>
+        <v>9.6</v>
       </c>
       <c r="BF8">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG8">
-        <v>2.98</v>
+        <v>2.56</v>
       </c>
       <c r="BH8">
         <v>5.6</v>
       </c>
       <c r="BI8">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BJ8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK8">
         <v>5.5</v>
@@ -2890,19 +2890,19 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN8">
         <v>16</v>
       </c>
       <c r="BO8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR8">
         <v>1000</v>
@@ -2914,7 +2914,7 @@
         <v>4.3</v>
       </c>
       <c r="BU8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV8">
         <v>7</v>
@@ -2923,7 +2923,7 @@
         <v>5.3</v>
       </c>
       <c r="BX8">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BY8">
         <v>6.6</v>
@@ -3018,7 +3018,7 @@
         <v>28</v>
       </c>
       <c r="AA9">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AB9">
         <v>13.5</v>
@@ -3045,16 +3045,16 @@
         <v>48</v>
       </c>
       <c r="AJ9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL9">
         <v>36</v>
       </c>
       <c r="AM9">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AN9">
         <v>18</v>
@@ -3063,64 +3063,64 @@
         <v>36</v>
       </c>
       <c r="AP9">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="AQ9">
-        <v>11</v>
+        <v>4.6</v>
       </c>
       <c r="AR9">
-        <v>19</v>
+        <v>4.7</v>
       </c>
       <c r="AS9">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT9">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AU9">
         <v>7.2</v>
       </c>
       <c r="AV9">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW9">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="AX9">
-        <v>11</v>
+        <v>4.6</v>
       </c>
       <c r="AY9">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AZ9">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="BA9">
+        <v>5.1</v>
+      </c>
+      <c r="BB9">
+        <v>4.8</v>
+      </c>
+      <c r="BC9">
+        <v>4.6</v>
+      </c>
+      <c r="BD9">
         <v>4.9</v>
       </c>
-      <c r="BB9">
-        <v>20</v>
-      </c>
-      <c r="BC9">
-        <v>16</v>
-      </c>
-      <c r="BD9">
-        <v>20</v>
-      </c>
       <c r="BE9">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF9">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG9">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BH9">
         <v>3.85</v>
       </c>
       <c r="BI9">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="BJ9">
         <v>9.6</v>
@@ -3200,10 +3200,10 @@
         <v>1.8</v>
       </c>
       <c r="G10">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="H10">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I10">
         <v>5.5</v>
@@ -3215,7 +3215,7 @@
         <v>3.9</v>
       </c>
       <c r="L10">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="M10">
         <v>1.07</v>
@@ -3248,10 +3248,10 @@
         <v>1.22</v>
       </c>
       <c r="W10">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="X10">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Y10">
         <v>21</v>
@@ -3263,10 +3263,10 @@
         <v>900</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD10">
         <v>20</v>
@@ -3275,10 +3275,10 @@
         <v>320</v>
       </c>
       <c r="AF10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG10">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH10">
         <v>21</v>
@@ -3290,7 +3290,7 @@
         <v>20</v>
       </c>
       <c r="AK10">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AL10">
         <v>40</v>
@@ -3299,13 +3299,13 @@
         <v>500</v>
       </c>
       <c r="AN10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO10">
         <v>85</v>
       </c>
       <c r="AP10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ10">
         <v>16</v>
@@ -3320,28 +3320,28 @@
         <v>7.8</v>
       </c>
       <c r="AU10">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW10">
         <v>50</v>
       </c>
       <c r="AX10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY10">
         <v>9.4</v>
       </c>
       <c r="AZ10">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA10">
         <v>55</v>
       </c>
       <c r="BB10">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BC10">
         <v>17</v>
@@ -3350,7 +3350,7 @@
         <v>32</v>
       </c>
       <c r="BE10">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="BF10">
         <v>11</v>
@@ -3439,22 +3439,22 @@
         <v>184</v>
       </c>
       <c r="F11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G11">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H11">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="I11">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="J11">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K11">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L11">
         <v>1.38</v>
@@ -3469,7 +3469,7 @@
         <v>1.29</v>
       </c>
       <c r="P11">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q11">
         <v>1.86</v>
@@ -3487,10 +3487,10 @@
         <v>2.06</v>
       </c>
       <c r="V11">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W11">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X11">
         <v>16.5</v>
@@ -3499,10 +3499,10 @@
         <v>9.4</v>
       </c>
       <c r="Z11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB11">
         <v>17</v>
@@ -3520,13 +3520,13 @@
         <v>80</v>
       </c>
       <c r="AG11">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH11">
         <v>19.5</v>
       </c>
       <c r="AI11">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ11">
         <v>900</v>
@@ -3544,10 +3544,10 @@
         <v>140</v>
       </c>
       <c r="AO11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP11">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AQ11">
         <v>7.2</v>
@@ -3559,7 +3559,7 @@
         <v>16</v>
       </c>
       <c r="AT11">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AU11">
         <v>6.8</v>
@@ -3571,40 +3571,40 @@
         <v>16</v>
       </c>
       <c r="AX11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY11">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AZ11">
         <v>14</v>
       </c>
       <c r="BA11">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BB11">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC11">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BD11">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE11">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF11">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG11">
         <v>9.6</v>
       </c>
       <c r="BH11">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BI11">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
@@ -3616,10 +3616,10 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BO11">
         <v>4.5</v>
@@ -3628,31 +3628,31 @@
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT11">
         <v>4.8</v>
       </c>
       <c r="BU11">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BV11">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BW11">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3696,7 +3696,7 @@
         <v>5.1</v>
       </c>
       <c r="K12">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L12">
         <v>1.27</v>
@@ -3711,7 +3711,7 @@
         <v>1.26</v>
       </c>
       <c r="P12">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q12">
         <v>1.76</v>
@@ -3738,7 +3738,7 @@
         <v>22</v>
       </c>
       <c r="Y12">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z12">
         <v>9.199999999999999</v>
@@ -3747,7 +3747,7 @@
         <v>13.5</v>
       </c>
       <c r="AB12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AC12">
         <v>13</v>
@@ -3813,40 +3813,40 @@
         <v>11.5</v>
       </c>
       <c r="AX12">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY12">
         <v>18</v>
       </c>
       <c r="AZ12">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA12">
         <v>20</v>
       </c>
       <c r="BB12">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD12">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF12">
         <v>15</v>
       </c>
       <c r="BG12">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH12">
         <v>4.1</v>
       </c>
       <c r="BI12">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ12">
         <v>13</v>
@@ -3888,7 +3888,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BW12">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BX12">
         <v>26</v>
@@ -3923,16 +3923,16 @@
         <v>186</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G13">
         <v>4.7</v>
       </c>
       <c r="H13">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="I13">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J13">
         <v>3.6</v>
@@ -3971,7 +3971,7 @@
         <v>2.14</v>
       </c>
       <c r="V13">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="W13">
         <v>1.27</v>
@@ -3986,7 +3986,7 @@
         <v>13.5</v>
       </c>
       <c r="AA13">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AB13">
         <v>17</v>
@@ -4025,10 +4025,10 @@
         <v>320</v>
       </c>
       <c r="AN13">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AO13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP13">
         <v>13</v>
@@ -4067,7 +4067,7 @@
         <v>24</v>
       </c>
       <c r="BB13">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BC13">
         <v>9.199999999999999</v>
@@ -4106,7 +4106,7 @@
         <v>8</v>
       </c>
       <c r="BO13">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP13">
         <v>1000</v>
@@ -4124,7 +4124,7 @@
         <v>5</v>
       </c>
       <c r="BU13">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BV13">
         <v>14.5</v>
@@ -4204,7 +4204,7 @@
         <v>1.37</v>
       </c>
       <c r="S14">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="T14">
         <v>1.69</v>
@@ -4240,7 +4240,7 @@
         <v>15</v>
       </c>
       <c r="AE14">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AF14">
         <v>17</v>
@@ -4258,10 +4258,10 @@
         <v>80</v>
       </c>
       <c r="AK14">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AL14">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AM14">
         <v>500</v>
@@ -4273,16 +4273,16 @@
         <v>50</v>
       </c>
       <c r="AP14">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AQ14">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AR14">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AS14">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AT14">
         <v>5.8</v>
@@ -4291,40 +4291,40 @@
         <v>4.9</v>
       </c>
       <c r="AV14">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AW14">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX14">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AY14">
         <v>6.4</v>
       </c>
       <c r="AZ14">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BA14">
+        <v>7.6</v>
+      </c>
+      <c r="BB14">
+        <v>7</v>
+      </c>
+      <c r="BC14">
         <v>6.6</v>
       </c>
-      <c r="BB14">
-        <v>6.4</v>
-      </c>
-      <c r="BC14">
-        <v>6.2</v>
-      </c>
       <c r="BD14">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE14">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF14">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BG14">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BH14">
         <v>3.65</v>
@@ -4357,7 +4357,7 @@
         <v>6.6</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS14">
         <v>7.8</v>
@@ -4410,31 +4410,31 @@
         <v>1.83</v>
       </c>
       <c r="G15">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="H15">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I15">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J15">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K15">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L15">
+        <v>1.42</v>
+      </c>
+      <c r="M15">
+        <v>1.07</v>
+      </c>
+      <c r="N15">
+        <v>3.35</v>
+      </c>
+      <c r="O15">
         <v>1.35</v>
-      </c>
-      <c r="M15">
-        <v>1.08</v>
-      </c>
-      <c r="N15">
-        <v>3.45</v>
-      </c>
-      <c r="O15">
-        <v>1.34</v>
       </c>
       <c r="P15">
         <v>1.83</v>
@@ -4446,13 +4446,13 @@
         <v>1.32</v>
       </c>
       <c r="S15">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T15">
         <v>1.9</v>
       </c>
       <c r="U15">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V15">
         <v>1.22</v>
@@ -4464,7 +4464,7 @@
         <v>14</v>
       </c>
       <c r="Y15">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z15">
         <v>46</v>
@@ -4494,7 +4494,7 @@
         <v>25</v>
       </c>
       <c r="AI15">
-        <v>170</v>
+        <v>320</v>
       </c>
       <c r="AJ15">
         <v>25</v>
@@ -4509,7 +4509,7 @@
         <v>580</v>
       </c>
       <c r="AN15">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AO15">
         <v>110</v>
@@ -4521,10 +4521,10 @@
         <v>12</v>
       </c>
       <c r="AR15">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AS15">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AT15">
         <v>6.2</v>
@@ -4536,7 +4536,7 @@
         <v>14.5</v>
       </c>
       <c r="AW15">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX15">
         <v>8</v>
@@ -4548,7 +4548,7 @@
         <v>17.5</v>
       </c>
       <c r="BA15">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB15">
         <v>17.5</v>
@@ -4557,16 +4557,16 @@
         <v>17.5</v>
       </c>
       <c r="BD15">
+        <v>5.6</v>
+      </c>
+      <c r="BE15">
         <v>6</v>
-      </c>
-      <c r="BE15">
-        <v>6.4</v>
       </c>
       <c r="BF15">
         <v>9.800000000000001</v>
       </c>
       <c r="BG15">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BH15">
         <v>3.35</v>
@@ -4578,13 +4578,13 @@
         <v>10.5</v>
       </c>
       <c r="BK15">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BN15">
         <v>4.4</v>
@@ -4593,40 +4593,40 @@
         <v>3.9</v>
       </c>
       <c r="BP15">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BQ15">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BR15">
         <v>29</v>
       </c>
       <c r="BS15">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BT15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU15">
+        <v>4.6</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
         <v>8.6</v>
       </c>
-      <c r="BU15">
-        <v>5.5</v>
-      </c>
-      <c r="BV15">
-        <v>1000</v>
-      </c>
-      <c r="BW15">
-        <v>11.5</v>
-      </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BZ15">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="CA15">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="CB15" t="s">
         <v>217</v>
@@ -4667,28 +4667,28 @@
         <v>4.4</v>
       </c>
       <c r="L16">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M16">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N16">
         <v>6.2</v>
       </c>
       <c r="O16">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P16">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="Q16">
         <v>1.53</v>
       </c>
       <c r="R16">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S16">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T16">
         <v>1.55</v>
@@ -4814,19 +4814,19 @@
         <v>4.7</v>
       </c>
       <c r="BI16">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ16">
         <v>9</v>
       </c>
       <c r="BK16">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN16">
         <v>5.4</v>
@@ -4838,10 +4838,10 @@
         <v>13</v>
       </c>
       <c r="BQ16">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BR16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS16">
         <v>7</v>
@@ -4856,19 +4856,19 @@
         <v>28</v>
       </c>
       <c r="BW16">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX16">
         <v>32</v>
       </c>
       <c r="BY16">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA16">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB16" t="s">
         <v>217</v>
@@ -5008,7 +5008,7 @@
         <v>13</v>
       </c>
       <c r="AS17">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT17">
         <v>9.800000000000001</v>
@@ -5020,7 +5020,7 @@
         <v>13</v>
       </c>
       <c r="AW17">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AX17">
         <v>12</v>
@@ -5032,7 +5032,7 @@
         <v>14</v>
       </c>
       <c r="BA17">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BB17">
         <v>20</v>
@@ -5041,7 +5041,7 @@
         <v>17</v>
       </c>
       <c r="BD17">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BE17">
         <v>5</v>
@@ -5151,7 +5151,7 @@
         <v>3.25</v>
       </c>
       <c r="L18">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M18">
         <v>1.09</v>
@@ -5375,7 +5375,7 @@
         <v>192</v>
       </c>
       <c r="F19">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G19">
         <v>3.05</v>
@@ -5384,16 +5384,16 @@
         <v>2.46</v>
       </c>
       <c r="I19">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J19">
         <v>3.55</v>
       </c>
       <c r="K19">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L19">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M19">
         <v>1.05</v>
@@ -5402,13 +5402,13 @@
         <v>4.4</v>
       </c>
       <c r="O19">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P19">
         <v>2.16</v>
       </c>
       <c r="Q19">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R19">
         <v>1.46</v>
@@ -5423,10 +5423,10 @@
         <v>2.36</v>
       </c>
       <c r="V19">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W19">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X19">
         <v>19</v>
@@ -5438,7 +5438,7 @@
         <v>21</v>
       </c>
       <c r="AA19">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB19">
         <v>15</v>
@@ -5450,7 +5450,7 @@
         <v>12.5</v>
       </c>
       <c r="AE19">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF19">
         <v>23</v>
@@ -5480,7 +5480,7 @@
         <v>25</v>
       </c>
       <c r="AO19">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP19">
         <v>15.5</v>
@@ -5492,13 +5492,13 @@
         <v>15.5</v>
       </c>
       <c r="AS19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT19">
         <v>11.5</v>
       </c>
       <c r="AU19">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV19">
         <v>10</v>
@@ -5519,16 +5519,16 @@
         <v>16</v>
       </c>
       <c r="BB19">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC19">
         <v>14.5</v>
       </c>
       <c r="BD19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE19">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF19">
         <v>16.5</v>
@@ -5626,7 +5626,7 @@
         <v>6.8</v>
       </c>
       <c r="I20">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J20">
         <v>5.7</v>
@@ -5668,7 +5668,7 @@
         <v>1.14</v>
       </c>
       <c r="W20">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X20">
         <v>48</v>
@@ -5683,10 +5683,10 @@
         <v>190</v>
       </c>
       <c r="AB20">
+        <v>19</v>
+      </c>
+      <c r="AC20">
         <v>17</v>
-      </c>
-      <c r="AC20">
-        <v>16</v>
       </c>
       <c r="AD20">
         <v>32</v>
@@ -5695,22 +5695,22 @@
         <v>400</v>
       </c>
       <c r="AF20">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AG20">
         <v>11.5</v>
       </c>
       <c r="AH20">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AI20">
         <v>200</v>
       </c>
       <c r="AJ20">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK20">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AL20">
         <v>40</v>
@@ -5725,16 +5725,16 @@
         <v>150</v>
       </c>
       <c r="AP20">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="AQ20">
-        <v>32</v>
+        <v>5.7</v>
       </c>
       <c r="AR20">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AS20">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="AT20">
         <v>12.5</v>
@@ -5746,7 +5746,7 @@
         <v>21</v>
       </c>
       <c r="AW20">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AX20">
         <v>10</v>
@@ -5758,7 +5758,7 @@
         <v>15</v>
       </c>
       <c r="BA20">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="BB20">
         <v>11.5</v>
@@ -5770,7 +5770,7 @@
         <v>18</v>
       </c>
       <c r="BE20">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF20">
         <v>3.7</v>
@@ -5862,7 +5862,7 @@
         <v>1.81</v>
       </c>
       <c r="G21">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H21">
         <v>4.6</v>
@@ -5889,13 +5889,13 @@
         <v>1.24</v>
       </c>
       <c r="P21">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q21">
         <v>1.71</v>
       </c>
       <c r="R21">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S21">
         <v>2.78</v>
@@ -5931,7 +5931,7 @@
         <v>9.6</v>
       </c>
       <c r="AD21">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE21">
         <v>55</v>
@@ -5955,19 +5955,19 @@
         <v>17.5</v>
       </c>
       <c r="AL21">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM21">
         <v>80</v>
       </c>
       <c r="AN21">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO21">
         <v>46</v>
       </c>
       <c r="AP21">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ21">
         <v>18</v>
@@ -6012,7 +6012,7 @@
         <v>26</v>
       </c>
       <c r="BE21">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BF21">
         <v>8.4</v>
@@ -6036,7 +6036,7 @@
         <v>95</v>
       </c>
       <c r="BM21">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BN21">
         <v>4.7</v>
@@ -6048,7 +6048,7 @@
         <v>12</v>
       </c>
       <c r="BQ21">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR21">
         <v>23</v>
@@ -6063,7 +6063,7 @@
         <v>5.7</v>
       </c>
       <c r="BV21">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW21">
         <v>12.5</v>
@@ -6072,7 +6072,7 @@
         <v>40</v>
       </c>
       <c r="BY21">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ21">
         <v>17</v>
@@ -6104,7 +6104,7 @@
         <v>1.72</v>
       </c>
       <c r="G22">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H22">
         <v>5.2</v>
@@ -6113,7 +6113,7 @@
         <v>5.6</v>
       </c>
       <c r="J22">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K22">
         <v>4.3</v>
@@ -6131,10 +6131,10 @@
         <v>1.27</v>
       </c>
       <c r="P22">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q22">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R22">
         <v>1.47</v>
@@ -6152,7 +6152,7 @@
         <v>1.22</v>
       </c>
       <c r="W22">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X22">
         <v>19.5</v>
@@ -6161,16 +6161,16 @@
         <v>22</v>
       </c>
       <c r="Z22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AB22">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD22">
         <v>23</v>
@@ -6197,40 +6197,40 @@
         <v>18</v>
       </c>
       <c r="AL22">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AM22">
-        <v>580</v>
+        <v>310</v>
       </c>
       <c r="AN22">
         <v>10.5</v>
       </c>
       <c r="AO22">
-        <v>310</v>
+        <v>140</v>
       </c>
       <c r="AP22">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ22">
         <v>17.5</v>
       </c>
       <c r="AR22">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AS22">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT22">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU22">
         <v>8.4</v>
       </c>
       <c r="AV22">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW22">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX22">
         <v>9.800000000000001</v>
@@ -6248,10 +6248,10 @@
         <v>15.5</v>
       </c>
       <c r="BC22">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD22">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BE22">
         <v>38</v>
@@ -6260,7 +6260,7 @@
         <v>8.6</v>
       </c>
       <c r="BG22">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH22">
         <v>3.75</v>
@@ -6355,13 +6355,13 @@
         <v>2.52</v>
       </c>
       <c r="J23">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K23">
         <v>4.1</v>
       </c>
       <c r="L23">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="M23">
         <v>1.03</v>
@@ -6409,7 +6409,7 @@
         <v>40</v>
       </c>
       <c r="AB23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC23">
         <v>11</v>
@@ -6448,7 +6448,7 @@
         <v>22</v>
       </c>
       <c r="AO23">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AP23">
         <v>11.5</v>
@@ -6463,10 +6463,10 @@
         <v>24</v>
       </c>
       <c r="AT23">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AU23">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AV23">
         <v>10.5</v>
@@ -6496,7 +6496,7 @@
         <v>16</v>
       </c>
       <c r="BE23">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF23">
         <v>12.5</v>
@@ -6511,7 +6511,7 @@
         <v>4</v>
       </c>
       <c r="BJ23">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK23">
         <v>5.4</v>
@@ -6520,7 +6520,7 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN23">
         <v>6.6</v>
@@ -6532,13 +6532,13 @@
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT23">
         <v>5.9</v>
@@ -6550,19 +6550,19 @@
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB23" t="s">
         <v>217</v>
@@ -6585,19 +6585,19 @@
         <v>197</v>
       </c>
       <c r="F24">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="G24">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="H24">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="I24">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="J24">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K24">
         <v>3.7</v>
@@ -6606,19 +6606,19 @@
         <v>1.31</v>
       </c>
       <c r="M24">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N24">
         <v>4.3</v>
       </c>
       <c r="O24">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P24">
         <v>2.12</v>
       </c>
       <c r="Q24">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R24">
         <v>1.44</v>
@@ -6627,19 +6627,19 @@
         <v>2.96</v>
       </c>
       <c r="T24">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U24">
         <v>2.32</v>
       </c>
       <c r="V24">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W24">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="X24">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y24">
         <v>16.5</v>
@@ -6648,7 +6648,7 @@
         <v>26</v>
       </c>
       <c r="AA24">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB24">
         <v>13.5</v>
@@ -6672,10 +6672,10 @@
         <v>18</v>
       </c>
       <c r="AI24">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AJ24">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK24">
         <v>28</v>
@@ -6684,7 +6684,7 @@
         <v>40</v>
       </c>
       <c r="AM24">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AN24">
         <v>18</v>
@@ -6708,7 +6708,7 @@
         <v>9.4</v>
       </c>
       <c r="AU24">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV24">
         <v>10.5</v>
@@ -6726,7 +6726,7 @@
         <v>12</v>
       </c>
       <c r="BA24">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BB24">
         <v>14.5</v>
@@ -6738,7 +6738,7 @@
         <v>16</v>
       </c>
       <c r="BE24">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF24">
         <v>14</v>
@@ -6750,55 +6750,55 @@
         <v>3.75</v>
       </c>
       <c r="BI24">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="BJ24">
         <v>9</v>
       </c>
       <c r="BK24">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN24">
         <v>5.5</v>
       </c>
       <c r="BO24">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP24">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ24">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS24">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT24">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU24">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW24">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ24">
         <v>0</v>
@@ -6935,13 +6935,13 @@
         <v>46</v>
       </c>
       <c r="AP25">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ25">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AR25">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS25">
         <v>6.2</v>
@@ -6950,7 +6950,7 @@
         <v>4.5</v>
       </c>
       <c r="AU25">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AV25">
         <v>4.8</v>
@@ -7183,7 +7183,7 @@
         <v>6</v>
       </c>
       <c r="AR26">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AS26">
         <v>7.2</v>
@@ -7195,13 +7195,13 @@
         <v>4.2</v>
       </c>
       <c r="AV26">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AW26">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX26">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY26">
         <v>9</v>
@@ -7317,7 +7317,7 @@
         <v>1.93</v>
       </c>
       <c r="H27">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I27">
         <v>7.4</v>
@@ -7332,10 +7332,10 @@
         <v>1.49</v>
       </c>
       <c r="M27">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N27">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="O27">
         <v>1.55</v>
@@ -7383,7 +7383,7 @@
         <v>8.6</v>
       </c>
       <c r="AD27">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AE27">
         <v>700</v>
@@ -7422,7 +7422,7 @@
         <v>4.2</v>
       </c>
       <c r="AQ27">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="AR27">
         <v>6</v>
@@ -7446,7 +7446,7 @@
         <v>4.4</v>
       </c>
       <c r="AY27">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="AZ27">
         <v>5.7</v>
@@ -7562,10 +7562,10 @@
         <v>4.2</v>
       </c>
       <c r="I28">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J28">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K28">
         <v>5.1</v>
@@ -7577,7 +7577,7 @@
         <v>1.02</v>
       </c>
       <c r="N28">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O28">
         <v>1.13</v>
@@ -7589,7 +7589,7 @@
         <v>1.39</v>
       </c>
       <c r="R28">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="S28">
         <v>1.99</v>
@@ -7616,13 +7616,13 @@
         <v>44</v>
       </c>
       <c r="AA28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB28">
         <v>18</v>
       </c>
       <c r="AC28">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AD28">
         <v>22</v>
@@ -7637,7 +7637,7 @@
         <v>13</v>
       </c>
       <c r="AH28">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI28">
         <v>40</v>
@@ -7646,7 +7646,7 @@
         <v>22</v>
       </c>
       <c r="AK28">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AL28">
         <v>24</v>
@@ -7661,16 +7661,16 @@
         <v>26</v>
       </c>
       <c r="AP28">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ28">
         <v>24</v>
       </c>
       <c r="AR28">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AS28">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT28">
         <v>13</v>
@@ -7682,7 +7682,7 @@
         <v>14.5</v>
       </c>
       <c r="AW28">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AX28">
         <v>12</v>
@@ -7694,7 +7694,7 @@
         <v>12</v>
       </c>
       <c r="BA28">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB28">
         <v>15.5</v>
@@ -7706,7 +7706,7 @@
         <v>17</v>
       </c>
       <c r="BE28">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF28">
         <v>4.7</v>
@@ -7795,13 +7795,13 @@
         <v>202</v>
       </c>
       <c r="F29">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G29">
         <v>1.68</v>
       </c>
       <c r="H29">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>6.4</v>
@@ -7810,7 +7810,7 @@
         <v>4</v>
       </c>
       <c r="K29">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L29">
         <v>1.32</v>
@@ -7819,28 +7819,28 @@
         <v>1.06</v>
       </c>
       <c r="N29">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O29">
         <v>1.3</v>
       </c>
       <c r="P29">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q29">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R29">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S29">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T29">
         <v>1.92</v>
       </c>
       <c r="U29">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V29">
         <v>1.18</v>
@@ -7849,7 +7849,7 @@
         <v>2.46</v>
       </c>
       <c r="X29">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Y29">
         <v>20</v>
@@ -7864,7 +7864,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC29">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD29">
         <v>25</v>
@@ -7912,7 +7912,7 @@
         <v>38</v>
       </c>
       <c r="AS29">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT29">
         <v>7.4</v>
@@ -7924,22 +7924,22 @@
         <v>20</v>
       </c>
       <c r="AW29">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AX29">
         <v>8.199999999999999</v>
       </c>
       <c r="AY29">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ29">
         <v>19</v>
       </c>
       <c r="BA29">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB29">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC29">
         <v>14.5</v>
@@ -7948,13 +7948,13 @@
         <v>29</v>
       </c>
       <c r="BE29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF29">
         <v>7.6</v>
       </c>
       <c r="BG29">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH29">
         <v>3.7</v>
@@ -8037,16 +8037,16 @@
         <v>203</v>
       </c>
       <c r="F30">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G30">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H30">
         <v>2.4</v>
       </c>
       <c r="I30">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J30">
         <v>3.25</v>
@@ -8061,7 +8061,7 @@
         <v>1.09</v>
       </c>
       <c r="N30">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O30">
         <v>1.38</v>
@@ -8073,7 +8073,7 @@
         <v>2.12</v>
       </c>
       <c r="R30">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S30">
         <v>3.9</v>
@@ -8085,10 +8085,10 @@
         <v>2.04</v>
       </c>
       <c r="V30">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W30">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X30">
         <v>12.5</v>
@@ -8127,7 +8127,7 @@
         <v>44</v>
       </c>
       <c r="AJ30">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AK30">
         <v>95</v>
@@ -8315,7 +8315,7 @@
         <v>1.97</v>
       </c>
       <c r="R31">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S31">
         <v>3.5</v>
@@ -8348,7 +8348,7 @@
         <v>8</v>
       </c>
       <c r="AC31">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD31">
         <v>40</v>
@@ -8357,7 +8357,7 @@
         <v>400</v>
       </c>
       <c r="AF31">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG31">
         <v>10</v>
@@ -8369,7 +8369,7 @@
         <v>320</v>
       </c>
       <c r="AJ31">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AK31">
         <v>34</v>
@@ -8393,10 +8393,10 @@
         <v>10.5</v>
       </c>
       <c r="AR31">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS31">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT31">
         <v>7</v>
@@ -8408,7 +8408,7 @@
         <v>11.5</v>
       </c>
       <c r="AW31">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX31">
         <v>8.6</v>
@@ -8420,7 +8420,7 @@
         <v>11.5</v>
       </c>
       <c r="BA31">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB31">
         <v>14</v>
@@ -8429,7 +8429,7 @@
         <v>9</v>
       </c>
       <c r="BD31">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE31">
         <v>10.5</v>
@@ -8495,7 +8495,7 @@
         <v>12.5</v>
       </c>
       <c r="BZ31">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA31">
         <v>9.6</v>
@@ -8766,7 +8766,7 @@
         <v>1.74</v>
       </c>
       <c r="G33">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="H33">
         <v>3.95</v>
@@ -8793,7 +8793,7 @@
         <v>1.14</v>
       </c>
       <c r="P33">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="Q33">
         <v>1.41</v>
@@ -8814,7 +8814,7 @@
         <v>1.27</v>
       </c>
       <c r="W33">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X33">
         <v>42</v>
@@ -8823,7 +8823,7 @@
         <v>34</v>
       </c>
       <c r="Z33">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA33">
         <v>500</v>
@@ -8844,7 +8844,7 @@
         <v>19.5</v>
       </c>
       <c r="AG33">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH33">
         <v>17</v>
@@ -8877,7 +8877,7 @@
         <v>19.5</v>
       </c>
       <c r="AR33">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AS33">
         <v>4.5</v>
@@ -8928,7 +8928,7 @@
         <v>5.2</v>
       </c>
       <c r="BI33">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ33">
         <v>8.800000000000001</v>
@@ -8964,7 +8964,7 @@
         <v>8.6</v>
       </c>
       <c r="BU33">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV33">
         <v>40</v>
@@ -9029,7 +9029,7 @@
         <v>1.11</v>
       </c>
       <c r="N34">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O34">
         <v>1.49</v>
@@ -9107,7 +9107,7 @@
         <v>700</v>
       </c>
       <c r="AN34">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO34">
         <v>700</v>
@@ -9119,7 +9119,7 @@
         <v>12.5</v>
       </c>
       <c r="AR34">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS34">
         <v>7.6</v>
@@ -9134,19 +9134,19 @@
         <v>14.5</v>
       </c>
       <c r="AW34">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX34">
         <v>6.2</v>
       </c>
       <c r="AY34">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AZ34">
         <v>18</v>
       </c>
       <c r="BA34">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB34">
         <v>12</v>
@@ -9277,7 +9277,7 @@
         <v>1.44</v>
       </c>
       <c r="P35">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q35">
         <v>2.32</v>
@@ -9358,7 +9358,7 @@
         <v>9.4</v>
       </c>
       <c r="AQ35">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR35">
         <v>9</v>
@@ -9734,7 +9734,7 @@
         <v>1.94</v>
       </c>
       <c r="G37">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H37">
         <v>4.3</v>
@@ -9749,7 +9749,7 @@
         <v>3.75</v>
       </c>
       <c r="L37">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M37">
         <v>1.08</v>
@@ -9779,10 +9779,10 @@
         <v>1.94</v>
       </c>
       <c r="V37">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W37">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X37">
         <v>13</v>
@@ -9797,7 +9797,7 @@
         <v>900</v>
       </c>
       <c r="AB37">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC37">
         <v>8</v>
@@ -9815,13 +9815,13 @@
         <v>13</v>
       </c>
       <c r="AH37">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI37">
         <v>170</v>
       </c>
       <c r="AJ37">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK37">
         <v>25</v>
@@ -9833,10 +9833,10 @@
         <v>580</v>
       </c>
       <c r="AN37">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO37">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="AP37">
         <v>10</v>
@@ -9848,7 +9848,7 @@
         <v>14.5</v>
       </c>
       <c r="AS37">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT37">
         <v>7.2</v>
@@ -9860,7 +9860,7 @@
         <v>15.5</v>
       </c>
       <c r="AW37">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX37">
         <v>10</v>
@@ -9872,7 +9872,7 @@
         <v>17</v>
       </c>
       <c r="BA37">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB37">
         <v>20</v>
@@ -9881,34 +9881,34 @@
         <v>19.5</v>
       </c>
       <c r="BD37">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE37">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF37">
         <v>12.5</v>
       </c>
       <c r="BG37">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH37">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI37">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ37">
         <v>11</v>
       </c>
       <c r="BK37">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL37">
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN37">
         <v>4.8</v>
@@ -9920,13 +9920,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ37">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR37">
         <v>34</v>
       </c>
       <c r="BS37">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BT37">
         <v>8</v>
@@ -9938,19 +9938,19 @@
         <v>42</v>
       </c>
       <c r="BW37">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BX37">
         <v>55</v>
       </c>
       <c r="BY37">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ37">
         <v>32</v>
       </c>
       <c r="CA37">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB37" t="s">
         <v>217</v>
@@ -9973,7 +9973,7 @@
         <v>211</v>
       </c>
       <c r="F38">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G38">
         <v>2.16</v>
@@ -9982,7 +9982,7 @@
         <v>4.2</v>
       </c>
       <c r="I38">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J38">
         <v>3.25</v>
@@ -9994,7 +9994,7 @@
         <v>1.47</v>
       </c>
       <c r="M38">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N38">
         <v>3</v>
@@ -10012,7 +10012,7 @@
         <v>1.25</v>
       </c>
       <c r="S38">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T38">
         <v>1.96</v>
@@ -10021,7 +10021,7 @@
         <v>1.89</v>
       </c>
       <c r="V38">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W38">
         <v>1.86</v>
@@ -10033,7 +10033,7 @@
         <v>13.5</v>
       </c>
       <c r="Z38">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AA38">
         <v>900</v>
@@ -10090,7 +10090,7 @@
         <v>13</v>
       </c>
       <c r="AS38">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT38">
         <v>6.8</v>
@@ -10102,7 +10102,7 @@
         <v>13.5</v>
       </c>
       <c r="AW38">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX38">
         <v>10</v>
@@ -10114,7 +10114,7 @@
         <v>17</v>
       </c>
       <c r="BA38">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB38">
         <v>11.5</v>
@@ -10123,19 +10123,19 @@
         <v>21</v>
       </c>
       <c r="BD38">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE38">
+        <v>9.6</v>
+      </c>
+      <c r="BF38">
+        <v>17.5</v>
+      </c>
+      <c r="BG38">
         <v>9.199999999999999</v>
       </c>
-      <c r="BF38">
-        <v>15.5</v>
-      </c>
-      <c r="BG38">
-        <v>9</v>
-      </c>
       <c r="BH38">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI38">
         <v>2.52</v>
@@ -10144,13 +10144,13 @@
         <v>11</v>
       </c>
       <c r="BK38">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN38">
         <v>4.8</v>
@@ -10162,13 +10162,13 @@
         <v>17</v>
       </c>
       <c r="BQ38">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR38">
         <v>1000</v>
       </c>
       <c r="BS38">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT38">
         <v>7.8</v>
@@ -10180,19 +10180,19 @@
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX38">
         <v>60</v>
       </c>
       <c r="BY38">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ38">
         <v>1000</v>
       </c>
       <c r="CA38">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB38" t="s">
         <v>217</v>
@@ -10230,37 +10230,37 @@
         <v>3.3</v>
       </c>
       <c r="K39">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L39">
         <v>1.57</v>
       </c>
       <c r="M39">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N39">
         <v>2.68</v>
       </c>
       <c r="O39">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="P39">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q39">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="R39">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S39">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T39">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="U39">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="V39">
         <v>1.26</v>
@@ -10269,10 +10269,10 @@
         <v>1.88</v>
       </c>
       <c r="X39">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="Y39">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z39">
         <v>34</v>
@@ -10281,7 +10281,7 @@
         <v>900</v>
       </c>
       <c r="AB39">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC39">
         <v>7.8</v>
@@ -10290,7 +10290,7 @@
         <v>19.5</v>
       </c>
       <c r="AE39">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="AF39">
         <v>12.5</v>
@@ -10302,7 +10302,7 @@
         <v>32</v>
       </c>
       <c r="AI39">
-        <v>240</v>
+        <v>540</v>
       </c>
       <c r="AJ39">
         <v>30</v>
@@ -10326,7 +10326,7 @@
         <v>8</v>
       </c>
       <c r="AQ39">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR39">
         <v>6.8</v>
@@ -10335,16 +10335,16 @@
         <v>8</v>
       </c>
       <c r="AT39">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU39">
         <v>6.8</v>
       </c>
       <c r="AV39">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW39">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX39">
         <v>9.199999999999999</v>
@@ -10353,7 +10353,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ39">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="BA39">
         <v>7.8</v>
@@ -10362,22 +10362,22 @@
         <v>21</v>
       </c>
       <c r="BC39">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BD39">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="BE39">
         <v>8.199999999999999</v>
       </c>
       <c r="BF39">
-        <v>17.5</v>
+        <v>6.8</v>
       </c>
       <c r="BG39">
         <v>8</v>
       </c>
       <c r="BH39">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BI39">
         <v>2.36</v>
@@ -10398,22 +10398,22 @@
         <v>4.4</v>
       </c>
       <c r="BO39">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP39">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ39">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR39">
         <v>1000</v>
       </c>
       <c r="BS39">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT39">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU39">
         <v>6</v>
@@ -10422,19 +10422,19 @@
         <v>1000</v>
       </c>
       <c r="BW39">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BX39">
         <v>1000</v>
       </c>
       <c r="BY39">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BZ39">
         <v>1000</v>
       </c>
       <c r="CA39">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CB39" t="s">
         <v>217</v>
@@ -10457,16 +10457,16 @@
         <v>213</v>
       </c>
       <c r="F40">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="G40">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="H40">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I40">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="J40">
         <v>3.45</v>
@@ -10475,43 +10475,43 @@
         <v>3.95</v>
       </c>
       <c r="L40">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M40">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N40">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O40">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P40">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q40">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R40">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S40">
         <v>3.75</v>
       </c>
       <c r="T40">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="U40">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="V40">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W40">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X40">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y40">
         <v>950</v>
@@ -10520,7 +10520,7 @@
         <v>48</v>
       </c>
       <c r="AA40">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AB40">
         <v>8.800000000000001</v>
@@ -10529,10 +10529,10 @@
         <v>8.4</v>
       </c>
       <c r="AD40">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE40">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AF40">
         <v>12</v>
@@ -10541,10 +10541,10 @@
         <v>10.5</v>
       </c>
       <c r="AH40">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI40">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ40">
         <v>23</v>
@@ -10556,40 +10556,40 @@
         <v>48</v>
       </c>
       <c r="AM40">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AN40">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO40">
         <v>110</v>
       </c>
       <c r="AP40">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AQ40">
         <v>13</v>
       </c>
       <c r="AR40">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS40">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT40">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AU40">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AV40">
         <v>14</v>
       </c>
       <c r="AW40">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AX40">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AY40">
         <v>8</v>
@@ -10598,7 +10598,7 @@
         <v>14.5</v>
       </c>
       <c r="BA40">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BB40">
         <v>16.5</v>
@@ -10607,40 +10607,40 @@
         <v>16</v>
       </c>
       <c r="BD40">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BE40">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF40">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG40">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH40">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI40">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BJ40">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK40">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN40">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO40">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP40">
         <v>14</v>
@@ -10652,7 +10652,7 @@
         <v>1000</v>
       </c>
       <c r="BS40">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT40">
         <v>8.4</v>
@@ -10664,19 +10664,19 @@
         <v>1000</v>
       </c>
       <c r="BW40">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX40">
         <v>1000</v>
       </c>
       <c r="BY40">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ40">
         <v>1000</v>
       </c>
       <c r="CA40">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB40" t="s">
         <v>217</v>
@@ -10699,49 +10699,49 @@
         <v>214</v>
       </c>
       <c r="F41">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G41">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H41">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I41">
         <v>2.66</v>
       </c>
       <c r="J41">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K41">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L41">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M41">
         <v>1.09</v>
       </c>
       <c r="N41">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O41">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P41">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q41">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R41">
         <v>1.26</v>
       </c>
       <c r="S41">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T41">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U41">
         <v>1.95</v>
@@ -10753,7 +10753,7 @@
         <v>1.37</v>
       </c>
       <c r="X41">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y41">
         <v>10.5</v>
@@ -10777,7 +10777,7 @@
         <v>34</v>
       </c>
       <c r="AF41">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG41">
         <v>17</v>
@@ -10816,7 +10816,7 @@
         <v>11.5</v>
       </c>
       <c r="AS41">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT41">
         <v>9.6</v>
@@ -10828,7 +10828,7 @@
         <v>9</v>
       </c>
       <c r="AW41">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX41">
         <v>17</v>
@@ -10840,46 +10840,46 @@
         <v>14.5</v>
       </c>
       <c r="BA41">
+        <v>5</v>
+      </c>
+      <c r="BB41">
+        <v>5.1</v>
+      </c>
+      <c r="BC41">
         <v>4.9</v>
       </c>
-      <c r="BB41">
+      <c r="BD41">
+        <v>5.1</v>
+      </c>
+      <c r="BE41">
+        <v>5.3</v>
+      </c>
+      <c r="BF41">
         <v>5</v>
-      </c>
-      <c r="BC41">
-        <v>4.8</v>
-      </c>
-      <c r="BD41">
-        <v>5</v>
-      </c>
-      <c r="BE41">
-        <v>5.2</v>
-      </c>
-      <c r="BF41">
-        <v>4.9</v>
       </c>
       <c r="BG41">
         <v>20</v>
       </c>
       <c r="BH41">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI41">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ41">
         <v>10.5</v>
       </c>
       <c r="BK41">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL41">
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN41">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO41">
         <v>5</v>
@@ -10888,13 +10888,13 @@
         <v>30</v>
       </c>
       <c r="BQ41">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR41">
         <v>46</v>
       </c>
       <c r="BS41">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT41">
         <v>5.5</v>
@@ -10906,19 +10906,19 @@
         <v>21</v>
       </c>
       <c r="BW41">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BX41">
         <v>38</v>
       </c>
       <c r="BY41">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ41">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA41">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="CB41" t="s">
         <v>217</v>
@@ -10941,25 +10941,25 @@
         <v>215</v>
       </c>
       <c r="F42">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G42">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H42">
         <v>3.3</v>
       </c>
       <c r="I42">
+        <v>4</v>
+      </c>
+      <c r="J42">
+        <v>3.35</v>
+      </c>
+      <c r="K42">
         <v>4.1</v>
       </c>
-      <c r="J42">
-        <v>3.3</v>
-      </c>
-      <c r="K42">
-        <v>4.2</v>
-      </c>
       <c r="L42">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M42">
         <v>1.06</v>
@@ -10968,70 +10968,70 @@
         <v>3.65</v>
       </c>
       <c r="O42">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P42">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q42">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R42">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S42">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T42">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U42">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V42">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W42">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X42">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y42">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Z42">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA42">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB42">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC42">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD42">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE42">
         <v>55</v>
       </c>
       <c r="AF42">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG42">
         <v>13.5</v>
       </c>
       <c r="AH42">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI42">
         <v>60</v>
       </c>
       <c r="AJ42">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AK42">
         <v>28</v>
@@ -11043,7 +11043,7 @@
         <v>110</v>
       </c>
       <c r="AN42">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AO42">
         <v>50</v>
@@ -11055,10 +11055,10 @@
         <v>10.5</v>
       </c>
       <c r="AR42">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS42">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT42">
         <v>7.6</v>
@@ -11070,97 +11070,97 @@
         <v>11</v>
       </c>
       <c r="AW42">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX42">
         <v>10.5</v>
       </c>
       <c r="AY42">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ42">
         <v>12.5</v>
       </c>
       <c r="BA42">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB42">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC42">
         <v>16.5</v>
       </c>
       <c r="BD42">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE42">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF42">
         <v>11.5</v>
       </c>
       <c r="BG42">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH42">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI42">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BJ42">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK42">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL42">
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BN42">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO42">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BP42">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ42">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BR42">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS42">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BT42">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU42">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BV42">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW42">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BX42">
         <v>42</v>
       </c>
       <c r="BY42">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BZ42">
         <v>26</v>
       </c>
       <c r="CA42">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="CB42" t="s">
         <v>217</v>
@@ -11183,19 +11183,19 @@
         <v>216</v>
       </c>
       <c r="F43">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G43">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H43">
         <v>3.25</v>
       </c>
       <c r="I43">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J43">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K43">
         <v>3.45</v>
@@ -11234,7 +11234,7 @@
         <v>1.4</v>
       </c>
       <c r="W43">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X43">
         <v>14.5</v>
@@ -11345,22 +11345,22 @@
         <v>5</v>
       </c>
       <c r="BH43">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI43">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ43">
         <v>9.800000000000001</v>
       </c>
       <c r="BK43">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL43">
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>2.06</v>
+        <v>4.9</v>
       </c>
       <c r="BN43">
         <v>5.3</v>
@@ -11372,13 +11372,13 @@
         <v>1000</v>
       </c>
       <c r="BQ43">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR43">
         <v>1000</v>
       </c>
       <c r="BS43">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT43">
         <v>6.4</v>
@@ -11390,19 +11390,19 @@
         <v>1000</v>
       </c>
       <c r="BW43">
+        <v>10</v>
+      </c>
+      <c r="BX43">
+        <v>1000</v>
+      </c>
+      <c r="BY43">
+        <v>11.5</v>
+      </c>
+      <c r="BZ43">
+        <v>1000</v>
+      </c>
+      <c r="CA43">
         <v>10.5</v>
-      </c>
-      <c r="BX43">
-        <v>1000</v>
-      </c>
-      <c r="BY43">
-        <v>12</v>
-      </c>
-      <c r="BZ43">
-        <v>1000</v>
-      </c>
-      <c r="CA43">
-        <v>11</v>
       </c>
       <c r="CB43" t="s">
         <v>217</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -613,7 +613,7 @@
     <t>Everton De Vina</t>
   </si>
   <si>
-    <t>2026-07-27 01:47:59</t>
+    <t>2026-07-27 03:55:36</t>
   </si>
 </sst>
 </file>
@@ -1207,46 +1207,46 @@
         <v>162</v>
       </c>
       <c r="F2">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="G2">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J2">
         <v>3.45</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M2">
         <v>1.1</v>
       </c>
       <c r="N2">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O2">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P2">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q2">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R2">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S2">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T2">
         <v>2.14</v>
@@ -1255,19 +1255,19 @@
         <v>1.69</v>
       </c>
       <c r="V2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W2">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="X2">
         <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z2">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AA2">
         <v>900</v>
@@ -1276,28 +1276,28 @@
         <v>6.6</v>
       </c>
       <c r="AC2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD2">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AE2">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AF2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG2">
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI2">
         <v>170</v>
       </c>
       <c r="AJ2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK2">
         <v>24</v>
@@ -1309,124 +1309,124 @@
         <v>580</v>
       </c>
       <c r="AN2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO2">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AP2">
-        <v>5.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ2">
-        <v>5.7</v>
+        <v>15.5</v>
       </c>
       <c r="AR2">
-        <v>9.199999999999999</v>
+        <v>46</v>
       </c>
       <c r="AS2">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT2">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="AU2">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AV2">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="AW2">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="AY2">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BA2">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="BC2">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>9.199999999999999</v>
+        <v>44</v>
       </c>
       <c r="BE2">
-        <v>7.8</v>
+        <v>140</v>
       </c>
       <c r="BF2">
-        <v>5.6</v>
+        <v>13.5</v>
       </c>
       <c r="BG2">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI2">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2">
         <v>13</v>
       </c>
       <c r="BK2">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>2.28</v>
+        <v>170</v>
       </c>
       <c r="BN2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO2">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="BP2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ2">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>2.16</v>
+        <v>8.4</v>
       </c>
       <c r="BT2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU2">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>2.22</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>2.24</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>2.16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB2" t="s">
         <v>199</v>
@@ -1449,7 +1449,7 @@
         <v>163</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="G3">
         <v>16</v>
@@ -1458,13 +1458,13 @@
         <v>1.25</v>
       </c>
       <c r="I3">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="J3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="L3">
         <v>1.21</v>
@@ -1491,25 +1491,25 @@
         <v>1.96</v>
       </c>
       <c r="T3">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U3">
         <v>2.1</v>
       </c>
       <c r="V3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="W3">
         <v>1.07</v>
       </c>
       <c r="X3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA3">
         <v>11.5</v>
@@ -1518,7 +1518,7 @@
         <v>70</v>
       </c>
       <c r="AC3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AD3">
         <v>12</v>
@@ -1551,7 +1551,7 @@
         <v>120</v>
       </c>
       <c r="AN3">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AO3">
         <v>3.25</v>
@@ -1581,10 +1581,10 @@
         <v>11</v>
       </c>
       <c r="AX3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AZ3">
         <v>24</v>
@@ -1593,16 +1593,16 @@
         <v>24</v>
       </c>
       <c r="BB3">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="BC3">
         <v>13</v>
       </c>
       <c r="BD3">
-        <v>42</v>
+        <v>13.5</v>
       </c>
       <c r="BE3">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="BF3">
         <v>15</v>
@@ -1620,31 +1620,31 @@
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN3">
         <v>16</v>
       </c>
       <c r="BO3">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BP3">
         <v>90</v>
       </c>
       <c r="BQ3">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR3">
         <v>70</v>
       </c>
       <c r="BS3">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT3">
         <v>4.3</v>
@@ -1659,10 +1659,10 @@
         <v>5.8</v>
       </c>
       <c r="BX3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BY3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1700,25 +1700,25 @@
         <v>3.3</v>
       </c>
       <c r="I4">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K4">
         <v>3.95</v>
       </c>
       <c r="L4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M4">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4">
         <v>4.3</v>
       </c>
       <c r="O4">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P4">
         <v>2.14</v>
@@ -1733,130 +1733,130 @@
         <v>3</v>
       </c>
       <c r="T4">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="U4">
-        <v>1.85</v>
+        <v>2.22</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W4">
         <v>1.76</v>
       </c>
       <c r="X4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y4">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Z4">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="AA4">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB4">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD4">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AE4">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="AF4">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AG4">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH4">
-        <v>60</v>
+        <v>17.5</v>
       </c>
       <c r="AI4">
-        <v>250</v>
+        <v>48</v>
       </c>
       <c r="AJ4">
-        <v>900</v>
+        <v>28</v>
       </c>
       <c r="AK4">
         <v>23</v>
       </c>
       <c r="AL4">
-        <v>150</v>
+        <v>34</v>
       </c>
       <c r="AM4">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO4">
-        <v>600</v>
+        <v>36</v>
       </c>
       <c r="AP4">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="AQ4">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="AR4">
-        <v>2.6</v>
+        <v>21</v>
       </c>
       <c r="AS4">
-        <v>2.12</v>
+        <v>11</v>
       </c>
       <c r="AT4">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="AU4">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="AW4">
-        <v>2.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX4">
-        <v>3.25</v>
+        <v>6.6</v>
       </c>
       <c r="AY4">
         <v>7</v>
       </c>
       <c r="AZ4">
-        <v>3.25</v>
+        <v>14</v>
       </c>
       <c r="BA4">
-        <v>2.12</v>
+        <v>12.5</v>
       </c>
       <c r="BB4">
-        <v>2.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC4">
-        <v>2.42</v>
+        <v>9.6</v>
       </c>
       <c r="BD4">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="BE4">
-        <v>2.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BG4">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BH4">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI4">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4">
         <v>9.6</v>
@@ -1877,10 +1877,10 @@
         <v>4</v>
       </c>
       <c r="BP4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR4">
         <v>28</v>
@@ -1892,7 +1892,7 @@
         <v>7.2</v>
       </c>
       <c r="BU4">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV4">
         <v>28</v>
@@ -1904,7 +1904,7 @@
         <v>38</v>
       </c>
       <c r="BY4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1933,22 +1933,22 @@
         <v>165</v>
       </c>
       <c r="F5">
+        <v>1.79</v>
+      </c>
+      <c r="G5">
         <v>1.8</v>
       </c>
-      <c r="G5">
-        <v>1.84</v>
-      </c>
       <c r="H5">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="I5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J5">
         <v>3.85</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L5">
         <v>1.42</v>
@@ -1963,10 +1963,10 @@
         <v>1.33</v>
       </c>
       <c r="P5">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R5">
         <v>1.36</v>
@@ -1978,13 +1978,13 @@
         <v>1.87</v>
       </c>
       <c r="U5">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
         <v>1.22</v>
       </c>
       <c r="W5">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="X5">
         <v>16.5</v>
@@ -1993,49 +1993,49 @@
         <v>21</v>
       </c>
       <c r="Z5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA5">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AB5">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC5">
         <v>9.6</v>
       </c>
       <c r="AD5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AE5">
         <v>75</v>
       </c>
       <c r="AF5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI5">
         <v>80</v>
       </c>
       <c r="AJ5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK5">
         <v>23</v>
       </c>
       <c r="AL5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM5">
-        <v>390</v>
+        <v>120</v>
       </c>
       <c r="AN5">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AO5">
         <v>85</v>
@@ -2044,13 +2044,13 @@
         <v>13</v>
       </c>
       <c r="AQ5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR5">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AS5">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AT5">
         <v>7.8</v>
@@ -2065,10 +2065,10 @@
         <v>60</v>
       </c>
       <c r="AX5">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
         <v>18.5</v>
@@ -2077,10 +2077,10 @@
         <v>60</v>
       </c>
       <c r="BB5">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD5">
         <v>32</v>
@@ -2089,28 +2089,28 @@
         <v>80</v>
       </c>
       <c r="BF5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BH5">
         <v>3.35</v>
       </c>
       <c r="BI5">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BJ5">
         <v>10</v>
       </c>
       <c r="BK5">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.7</v>
+        <v>16.5</v>
       </c>
       <c r="BN5">
         <v>4.4</v>
@@ -2122,16 +2122,16 @@
         <v>12.5</v>
       </c>
       <c r="BQ5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU5">
         <v>5.9</v>
@@ -2146,7 +2146,7 @@
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>4.5</v>
+        <v>9.4</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
@@ -2175,73 +2175,73 @@
         <v>166</v>
       </c>
       <c r="F6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G6">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H6">
         <v>1.86</v>
       </c>
       <c r="I6">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="J6">
         <v>3.75</v>
       </c>
       <c r="K6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L6">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M6">
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="O6">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="P6">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="Q6">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="R6">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S6">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T6">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="U6">
+        <v>2.14</v>
+      </c>
+      <c r="V6">
         <v>2.06</v>
       </c>
-      <c r="V6">
-        <v>2.04</v>
-      </c>
       <c r="W6">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X6">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y6">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Z6">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA6">
         <v>23</v>
       </c>
       <c r="AB6">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC6">
         <v>9</v>
@@ -2259,106 +2259,106 @@
         <v>18</v>
       </c>
       <c r="AH6">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ6">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="AK6">
+        <v>55</v>
+      </c>
+      <c r="AL6">
         <v>80</v>
-      </c>
-      <c r="AL6">
-        <v>150</v>
       </c>
       <c r="AM6">
         <v>390</v>
       </c>
       <c r="AN6">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="AO6">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP6">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AQ6">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AR6">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS6">
         <v>18</v>
       </c>
       <c r="AT6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV6">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW6">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AX6">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="AY6">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA6">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="BB6">
         <v>55</v>
       </c>
       <c r="BC6">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BD6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE6">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="BF6">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BG6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH6">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BI6">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BJ6">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BK6">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN6">
         <v>8</v>
       </c>
       <c r="BO6">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BP6">
         <v>1000</v>
@@ -2370,7 +2370,7 @@
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT6">
         <v>4.8</v>
@@ -2388,7 +2388,7 @@
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2417,19 +2417,19 @@
         <v>167</v>
       </c>
       <c r="F7">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="H7">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="I7">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="J7">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K7">
         <v>5.7</v>
@@ -2444,31 +2444,31 @@
         <v>4.6</v>
       </c>
       <c r="O7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P7">
         <v>2.24</v>
       </c>
       <c r="Q7">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R7">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S7">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T7">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U7">
         <v>1.76</v>
       </c>
       <c r="V7">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="W7">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
         <v>19.5</v>
@@ -2480,19 +2480,19 @@
         <v>8</v>
       </c>
       <c r="AA7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AB7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD7">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AE7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AF7">
         <v>110</v>
@@ -2507,76 +2507,76 @@
         <v>44</v>
       </c>
       <c r="AJ7">
-        <v>450</v>
+        <v>530</v>
       </c>
       <c r="AK7">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AL7">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AM7">
-        <v>390</v>
+        <v>200</v>
       </c>
       <c r="AN7">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="AO7">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AP7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR7">
         <v>7</v>
       </c>
       <c r="AS7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT7">
         <v>30</v>
       </c>
       <c r="AU7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV7">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX7">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="AY7">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="AZ7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA7">
         <v>34</v>
       </c>
       <c r="BB7">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BC7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BD7">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="BE7">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF7">
         <v>15</v>
       </c>
       <c r="BG7">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH7">
         <v>4.1</v>
@@ -2588,16 +2588,16 @@
         <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BO7">
         <v>10</v>
@@ -2606,22 +2606,22 @@
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT7">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BU7">
         <v>3</v>
       </c>
       <c r="BV7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BW7">
         <v>4.9</v>
@@ -2630,10 +2630,10 @@
         <v>25</v>
       </c>
       <c r="BY7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA7">
         <v>6.4</v>
@@ -2659,22 +2659,22 @@
         <v>168</v>
       </c>
       <c r="F8">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="G8">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H8">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="I8">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="J8">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K8">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L8">
         <v>1.38</v>
@@ -2686,13 +2686,13 @@
         <v>4.2</v>
       </c>
       <c r="O8">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P8">
         <v>2.06</v>
       </c>
       <c r="Q8">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R8">
         <v>1.41</v>
@@ -2704,34 +2704,34 @@
         <v>1.73</v>
       </c>
       <c r="U8">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V8">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="W8">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA8">
         <v>32</v>
       </c>
       <c r="AB8">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AC8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD8">
         <v>10.5</v>
-      </c>
-      <c r="AD8">
-        <v>12.5</v>
       </c>
       <c r="AE8">
         <v>21</v>
@@ -2740,13 +2740,13 @@
         <v>48</v>
       </c>
       <c r="AG8">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AH8">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI8">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ8">
         <v>500</v>
@@ -2764,10 +2764,10 @@
         <v>120</v>
       </c>
       <c r="AO8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ8">
         <v>8.4</v>
@@ -2782,10 +2782,10 @@
         <v>13.5</v>
       </c>
       <c r="AU8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV8">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW8">
         <v>17</v>
@@ -2797,31 +2797,31 @@
         <v>14.5</v>
       </c>
       <c r="AZ8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA8">
         <v>24</v>
       </c>
       <c r="BB8">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC8">
         <v>9.199999999999999</v>
       </c>
       <c r="BD8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE8">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF8">
         <v>9.4</v>
       </c>
       <c r="BG8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH8">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI8">
         <v>3.15</v>
@@ -2836,10 +2836,10 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN8">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO8">
         <v>5.8</v>
@@ -2848,13 +2848,13 @@
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT8">
         <v>5</v>
@@ -2866,19 +2866,19 @@
         <v>14.5</v>
       </c>
       <c r="BW8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX8">
         <v>28</v>
       </c>
       <c r="BY8">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ8">
         <v>24</v>
       </c>
       <c r="CA8">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB8" t="s">
         <v>199</v>
@@ -2901,97 +2901,97 @@
         <v>169</v>
       </c>
       <c r="F9">
-        <v>2.36</v>
+        <v>2.66</v>
       </c>
       <c r="G9">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="H9">
-        <v>2.96</v>
+        <v>2.64</v>
       </c>
       <c r="I9">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="J9">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K9">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L9">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M9">
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O9">
         <v>1.3</v>
       </c>
       <c r="P9">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q9">
         <v>1.92</v>
       </c>
       <c r="R9">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S9">
         <v>3.35</v>
       </c>
       <c r="T9">
-        <v>1.43</v>
+        <v>1.72</v>
       </c>
       <c r="U9">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="V9">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="W9">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="X9">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Y9">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z9">
-        <v>50</v>
+        <v>19.5</v>
       </c>
       <c r="AA9">
-        <v>900</v>
+        <v>280</v>
       </c>
       <c r="AB9">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AC9">
-        <v>42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF9">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AG9">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH9">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AI9">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AJ9">
-        <v>900</v>
+        <v>44</v>
       </c>
       <c r="AK9">
         <v>75</v>
@@ -3006,115 +3006,115 @@
         <v>600</v>
       </c>
       <c r="AO9">
-        <v>600</v>
+        <v>25</v>
       </c>
       <c r="AP9">
-        <v>2.08</v>
+        <v>13</v>
       </c>
       <c r="AQ9">
-        <v>2.06</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR9">
-        <v>2.18</v>
+        <v>15.5</v>
       </c>
       <c r="AS9">
-        <v>2.26</v>
+        <v>30</v>
       </c>
       <c r="AT9">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="AU9">
+        <v>7</v>
+      </c>
+      <c r="AV9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW9">
+        <v>16</v>
+      </c>
+      <c r="AX9">
+        <v>16.5</v>
+      </c>
+      <c r="AY9">
+        <v>10.5</v>
+      </c>
+      <c r="AZ9">
+        <v>14.5</v>
+      </c>
+      <c r="BA9">
+        <v>30</v>
+      </c>
+      <c r="BB9">
+        <v>7.8</v>
+      </c>
+      <c r="BC9">
+        <v>23</v>
+      </c>
+      <c r="BD9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE9">
+        <v>7.8</v>
+      </c>
+      <c r="BF9">
+        <v>21</v>
+      </c>
+      <c r="BG9">
+        <v>17.5</v>
+      </c>
+      <c r="BH9">
+        <v>3.6</v>
+      </c>
+      <c r="BI9">
+        <v>2.8</v>
+      </c>
+      <c r="BJ9">
+        <v>9.6</v>
+      </c>
+      <c r="BK9">
+        <v>5.4</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>11</v>
+      </c>
+      <c r="BN9">
+        <v>6</v>
+      </c>
+      <c r="BO9">
+        <v>5.1</v>
+      </c>
+      <c r="BP9">
+        <v>21</v>
+      </c>
+      <c r="BQ9">
+        <v>7.8</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>9</v>
+      </c>
+      <c r="BT9">
+        <v>5.9</v>
+      </c>
+      <c r="BU9">
         <v>4.9</v>
       </c>
-      <c r="AV9">
-        <v>2.06</v>
-      </c>
-      <c r="AW9">
-        <v>2.24</v>
-      </c>
-      <c r="AX9">
-        <v>2.12</v>
-      </c>
-      <c r="AY9">
-        <v>6.4</v>
-      </c>
-      <c r="AZ9">
-        <v>2.1</v>
-      </c>
-      <c r="BA9">
-        <v>2.24</v>
-      </c>
-      <c r="BB9">
-        <v>2.22</v>
-      </c>
-      <c r="BC9">
-        <v>2.2</v>
-      </c>
-      <c r="BD9">
-        <v>2.24</v>
-      </c>
-      <c r="BE9">
-        <v>2.26</v>
-      </c>
-      <c r="BF9">
-        <v>4.4</v>
-      </c>
-      <c r="BG9">
-        <v>6</v>
-      </c>
-      <c r="BH9">
-        <v>1000</v>
-      </c>
-      <c r="BI9">
-        <v>1.04</v>
-      </c>
-      <c r="BJ9">
-        <v>1000</v>
-      </c>
-      <c r="BK9">
-        <v>4.3</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>8</v>
-      </c>
-      <c r="BN9">
-        <v>1000</v>
-      </c>
-      <c r="BO9">
-        <v>3.15</v>
-      </c>
-      <c r="BP9">
-        <v>1000</v>
-      </c>
-      <c r="BQ9">
-        <v>4.9</v>
-      </c>
-      <c r="BR9">
-        <v>1000</v>
-      </c>
-      <c r="BS9">
-        <v>6.6</v>
-      </c>
-      <c r="BT9">
-        <v>1000</v>
-      </c>
-      <c r="BU9">
-        <v>3.55</v>
-      </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BZ9">
         <v>0</v>
@@ -3143,22 +3143,22 @@
         <v>170</v>
       </c>
       <c r="F10">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="G10">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H10">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I10">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J10">
         <v>3.7</v>
       </c>
       <c r="K10">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L10">
         <v>1.43</v>
@@ -3170,19 +3170,19 @@
         <v>3.6</v>
       </c>
       <c r="O10">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P10">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q10">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R10">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S10">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T10">
         <v>1.92</v>
@@ -3194,13 +3194,13 @@
         <v>1.24</v>
       </c>
       <c r="W10">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X10">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y10">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z10">
         <v>46</v>
@@ -3209,7 +3209,7 @@
         <v>900</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC10">
         <v>8.4</v>
@@ -3230,10 +3230,10 @@
         <v>25</v>
       </c>
       <c r="AI10">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="AJ10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK10">
         <v>25</v>
@@ -3242,10 +3242,10 @@
         <v>48</v>
       </c>
       <c r="AM10">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN10">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO10">
         <v>110</v>
@@ -3257,10 +3257,10 @@
         <v>13.5</v>
       </c>
       <c r="AR10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS10">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="AT10">
         <v>7.2</v>
@@ -3269,7 +3269,7 @@
         <v>7.4</v>
       </c>
       <c r="AV10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW10">
         <v>44</v>
@@ -3281,22 +3281,22 @@
         <v>9</v>
       </c>
       <c r="AZ10">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA10">
         <v>46</v>
       </c>
       <c r="BB10">
+        <v>17.5</v>
+      </c>
+      <c r="BC10">
         <v>18.5</v>
-      </c>
-      <c r="BC10">
-        <v>19</v>
       </c>
       <c r="BD10">
         <v>29</v>
       </c>
       <c r="BE10">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="BF10">
         <v>12</v>
@@ -3305,7 +3305,7 @@
         <v>50</v>
       </c>
       <c r="BH10">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI10">
         <v>3</v>
@@ -3320,16 +3320,16 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN10">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO10">
         <v>3.9</v>
       </c>
       <c r="BP10">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ10">
         <v>9.6</v>
@@ -3344,25 +3344,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU10">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV10">
         <v>60</v>
       </c>
       <c r="BW10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ10">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="CA10">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="CB10" t="s">
         <v>199</v>
@@ -3400,37 +3400,37 @@
         <v>3.6</v>
       </c>
       <c r="K11">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L11">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M11">
         <v>1.05</v>
       </c>
       <c r="N11">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O11">
         <v>1.24</v>
       </c>
       <c r="P11">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q11">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R11">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S11">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="T11">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U11">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="V11">
         <v>1.61</v>
@@ -3445,7 +3445,7 @@
         <v>14</v>
       </c>
       <c r="Z11">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AA11">
         <v>36</v>
@@ -3469,7 +3469,7 @@
         <v>13.5</v>
       </c>
       <c r="AH11">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI11">
         <v>36</v>
@@ -3484,28 +3484,28 @@
         <v>38</v>
       </c>
       <c r="AM11">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AN11">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO11">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP11">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS11">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="AT11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU11">
         <v>7.6</v>
@@ -3517,43 +3517,43 @@
         <v>21</v>
       </c>
       <c r="AX11">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA11">
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="BB11">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BC11">
+        <v>25</v>
+      </c>
+      <c r="BD11">
+        <v>30</v>
+      </c>
+      <c r="BE11">
+        <v>50</v>
+      </c>
+      <c r="BF11">
+        <v>18.5</v>
+      </c>
+      <c r="BG11">
         <v>15</v>
       </c>
-      <c r="BD11">
-        <v>18.5</v>
-      </c>
-      <c r="BE11">
-        <v>29</v>
-      </c>
-      <c r="BF11">
-        <v>16.5</v>
-      </c>
-      <c r="BG11">
-        <v>14</v>
-      </c>
       <c r="BH11">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BI11">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BJ11">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK11">
         <v>5.2</v>
@@ -3562,49 +3562,49 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN11">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO11">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BP11">
         <v>21</v>
       </c>
       <c r="BQ11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR11">
         <v>30</v>
       </c>
       <c r="BS11">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT11">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU11">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV11">
         <v>18</v>
       </c>
       <c r="BW11">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX11">
         <v>28</v>
       </c>
       <c r="BY11">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ11">
         <v>21</v>
       </c>
       <c r="CA11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB11" t="s">
         <v>199</v>
@@ -3627,52 +3627,52 @@
         <v>172</v>
       </c>
       <c r="F12">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G12">
         <v>1.94</v>
       </c>
       <c r="H12">
+        <v>3.85</v>
+      </c>
+      <c r="I12">
         <v>3.95</v>
       </c>
-      <c r="I12">
-        <v>4.1</v>
-      </c>
       <c r="J12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K12">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L12">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M12">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N12">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="O12">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P12">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="Q12">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="R12">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="S12">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="T12">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="U12">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="V12">
         <v>1.33</v>
@@ -3681,10 +3681,10 @@
         <v>2.06</v>
       </c>
       <c r="X12">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Y12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z12">
         <v>36</v>
@@ -3693,7 +3693,7 @@
         <v>75</v>
       </c>
       <c r="AB12">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AC12">
         <v>10.5</v>
@@ -3702,64 +3702,64 @@
         <v>17</v>
       </c>
       <c r="AE12">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF12">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG12">
         <v>11</v>
       </c>
       <c r="AH12">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI12">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK12">
         <v>17</v>
       </c>
       <c r="AL12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM12">
+        <v>50</v>
+      </c>
+      <c r="AN12">
+        <v>7.4</v>
+      </c>
+      <c r="AO12">
+        <v>24</v>
+      </c>
+      <c r="AP12">
+        <v>27</v>
+      </c>
+      <c r="AQ12">
+        <v>23</v>
+      </c>
+      <c r="AR12">
+        <v>30</v>
+      </c>
+      <c r="AS12">
         <v>60</v>
       </c>
-      <c r="AN12">
-        <v>8</v>
-      </c>
-      <c r="AO12">
-        <v>27</v>
-      </c>
-      <c r="AP12">
-        <v>23</v>
-      </c>
-      <c r="AQ12">
-        <v>21</v>
-      </c>
-      <c r="AR12">
-        <v>32</v>
-      </c>
-      <c r="AS12">
-        <v>50</v>
-      </c>
       <c r="AT12">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU12">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV12">
         <v>15</v>
       </c>
       <c r="AW12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX12">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY12">
         <v>9.800000000000001</v>
@@ -3768,49 +3768,49 @@
         <v>14</v>
       </c>
       <c r="BA12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB12">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BC12">
         <v>15.5</v>
       </c>
       <c r="BD12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE12">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF12">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BG12">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BH12">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BI12">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BJ12">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK12">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL12">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BM12">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN12">
         <v>5.4</v>
       </c>
       <c r="BO12">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BP12">
         <v>12.5</v>
@@ -3819,7 +3819,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BR12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BS12">
         <v>15</v>
@@ -3828,22 +3828,22 @@
         <v>8</v>
       </c>
       <c r="BU12">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV12">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BW12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX12">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BY12">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ12">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="CA12">
         <v>10</v>
@@ -3869,22 +3869,22 @@
         <v>173</v>
       </c>
       <c r="F13">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G13">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H13">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I13">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J13">
         <v>3.85</v>
       </c>
       <c r="K13">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L13">
         <v>1.34</v>
@@ -3893,34 +3893,34 @@
         <v>1.05</v>
       </c>
       <c r="N13">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O13">
         <v>1.24</v>
       </c>
       <c r="P13">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q13">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R13">
         <v>1.49</v>
       </c>
       <c r="S13">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="T13">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U13">
         <v>2.3</v>
       </c>
       <c r="V13">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W13">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X13">
         <v>20</v>
@@ -3929,22 +3929,22 @@
         <v>21</v>
       </c>
       <c r="Z13">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AA13">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB13">
         <v>12</v>
       </c>
       <c r="AC13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD13">
         <v>16.5</v>
       </c>
       <c r="AE13">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AF13">
         <v>15</v>
@@ -3956,25 +3956,25 @@
         <v>17</v>
       </c>
       <c r="AI13">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AJ13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK13">
         <v>21</v>
       </c>
       <c r="AL13">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AM13">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="AN13">
         <v>12.5</v>
       </c>
       <c r="AO13">
-        <v>220</v>
+        <v>38</v>
       </c>
       <c r="AP13">
         <v>16</v>
@@ -3983,10 +3983,10 @@
         <v>14</v>
       </c>
       <c r="AR13">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AS13">
-        <v>8.4</v>
+        <v>46</v>
       </c>
       <c r="AT13">
         <v>9.800000000000001</v>
@@ -3998,7 +3998,7 @@
         <v>13</v>
       </c>
       <c r="AW13">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="AX13">
         <v>12</v>
@@ -4019,16 +4019,16 @@
         <v>17</v>
       </c>
       <c r="BD13">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BE13">
-        <v>7.2</v>
+        <v>55</v>
       </c>
       <c r="BF13">
         <v>10</v>
       </c>
       <c r="BG13">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="BH13">
         <v>4.1</v>
@@ -4040,16 +4040,16 @@
         <v>9.4</v>
       </c>
       <c r="BK13">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN13">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO13">
         <v>3.9</v>
@@ -4058,7 +4058,7 @@
         <v>14.5</v>
       </c>
       <c r="BQ13">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR13">
         <v>26</v>
@@ -4070,19 +4070,19 @@
         <v>7.6</v>
       </c>
       <c r="BU13">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ13">
         <v>20</v>
@@ -4111,10 +4111,10 @@
         <v>174</v>
       </c>
       <c r="F14">
+        <v>1.81</v>
+      </c>
+      <c r="G14">
         <v>1.83</v>
-      </c>
-      <c r="G14">
-        <v>1.84</v>
       </c>
       <c r="H14">
         <v>4.6</v>
@@ -4141,13 +4141,13 @@
         <v>1.24</v>
       </c>
       <c r="P14">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q14">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S14">
         <v>2.82</v>
@@ -4162,7 +4162,7 @@
         <v>1.26</v>
       </c>
       <c r="W14">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X14">
         <v>19</v>
@@ -4171,10 +4171,10 @@
         <v>21</v>
       </c>
       <c r="Z14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA14">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB14">
         <v>11</v>
@@ -4183,7 +4183,7 @@
         <v>9.6</v>
       </c>
       <c r="AD14">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE14">
         <v>55</v>
@@ -4201,25 +4201,25 @@
         <v>55</v>
       </c>
       <c r="AJ14">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK14">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL14">
         <v>29</v>
       </c>
       <c r="AM14">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN14">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO14">
         <v>46</v>
       </c>
       <c r="AP14">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ14">
         <v>19</v>
@@ -4228,7 +4228,7 @@
         <v>34</v>
       </c>
       <c r="AS14">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="AT14">
         <v>10</v>
@@ -4240,22 +4240,22 @@
         <v>16.5</v>
       </c>
       <c r="AW14">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AX14">
         <v>11.5</v>
       </c>
       <c r="AY14">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ14">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA14">
         <v>46</v>
       </c>
       <c r="BB14">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BC14">
         <v>15.5</v>
@@ -4264,7 +4264,7 @@
         <v>26</v>
       </c>
       <c r="BE14">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BF14">
         <v>8.4</v>
@@ -4273,25 +4273,25 @@
         <v>38</v>
       </c>
       <c r="BH14">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI14">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="BJ14">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK14">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL14">
         <v>95</v>
       </c>
       <c r="BM14">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN14">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO14">
         <v>4.1</v>
@@ -4300,37 +4300,37 @@
         <v>12</v>
       </c>
       <c r="BQ14">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BR14">
         <v>23</v>
       </c>
       <c r="BS14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT14">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU14">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV14">
         <v>34</v>
       </c>
       <c r="BW14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX14">
         <v>40</v>
       </c>
       <c r="BY14">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ14">
         <v>17</v>
       </c>
       <c r="CA14">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB14" t="s">
         <v>199</v>
@@ -4353,22 +4353,22 @@
         <v>175</v>
       </c>
       <c r="F15">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="G15">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="H15">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="I15">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K15">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L15">
         <v>1.36</v>
@@ -4377,34 +4377,34 @@
         <v>1.05</v>
       </c>
       <c r="N15">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O15">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P15">
+        <v>2.22</v>
+      </c>
+      <c r="Q15">
+        <v>1.78</v>
+      </c>
+      <c r="R15">
+        <v>1.48</v>
+      </c>
+      <c r="S15">
+        <v>2.96</v>
+      </c>
+      <c r="T15">
+        <v>1.82</v>
+      </c>
+      <c r="U15">
         <v>2.18</v>
       </c>
-      <c r="Q15">
-        <v>1.8</v>
-      </c>
-      <c r="R15">
-        <v>1.47</v>
-      </c>
-      <c r="S15">
-        <v>3.05</v>
-      </c>
-      <c r="T15">
-        <v>1.8</v>
-      </c>
-      <c r="U15">
-        <v>2.14</v>
-      </c>
       <c r="V15">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W15">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="X15">
         <v>18</v>
@@ -4413,10 +4413,10 @@
         <v>22</v>
       </c>
       <c r="Z15">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="AA15">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB15">
         <v>9.800000000000001</v>
@@ -4428,10 +4428,10 @@
         <v>22</v>
       </c>
       <c r="AE15">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AF15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -4440,67 +4440,67 @@
         <v>20</v>
       </c>
       <c r="AI15">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ15">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AK15">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AL15">
         <v>32</v>
       </c>
       <c r="AM15">
-        <v>310</v>
+        <v>100</v>
       </c>
       <c r="AN15">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO15">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP15">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AQ15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR15">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AS15">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT15">
         <v>9</v>
       </c>
       <c r="AU15">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV15">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW15">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AX15">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY15">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA15">
         <v>55</v>
       </c>
       <c r="BB15">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BC15">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD15">
         <v>28</v>
@@ -4509,70 +4509,70 @@
         <v>38</v>
       </c>
       <c r="BF15">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG15">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BH15">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BI15">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ15">
         <v>9.800000000000001</v>
       </c>
       <c r="BK15">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BN15">
         <v>4.4</v>
       </c>
       <c r="BO15">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ15">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT15">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BU15">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY15">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ15">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA15">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="CB15" t="s">
         <v>199</v>
@@ -4595,16 +4595,16 @@
         <v>176</v>
       </c>
       <c r="F16">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G16">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H16">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I16">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J16">
         <v>5.7</v>
@@ -4658,10 +4658,10 @@
         <v>450</v>
       </c>
       <c r="AA16">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AB16">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC16">
         <v>17</v>
@@ -4673,25 +4673,25 @@
         <v>400</v>
       </c>
       <c r="AF16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG16">
         <v>11</v>
       </c>
       <c r="AH16">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AI16">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="AJ16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK16">
         <v>16</v>
       </c>
       <c r="AL16">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AM16">
         <v>260</v>
@@ -4703,16 +4703,16 @@
         <v>150</v>
       </c>
       <c r="AP16">
-        <v>18.5</v>
+        <v>29</v>
       </c>
       <c r="AQ16">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="AR16">
-        <v>6.2</v>
+        <v>60</v>
       </c>
       <c r="AS16">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT16">
         <v>12.5</v>
@@ -4721,40 +4721,40 @@
         <v>11</v>
       </c>
       <c r="AV16">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW16">
-        <v>6.2</v>
+        <v>55</v>
       </c>
       <c r="AX16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY16">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16">
         <v>17</v>
       </c>
       <c r="BA16">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BB16">
+        <v>13</v>
+      </c>
+      <c r="BC16">
         <v>12</v>
       </c>
-      <c r="BC16">
-        <v>10.5</v>
-      </c>
       <c r="BD16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BE16">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="BF16">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BG16">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BH16">
         <v>5.6</v>
@@ -4766,13 +4766,13 @@
         <v>9.4</v>
       </c>
       <c r="BK16">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN16">
         <v>4.7</v>
@@ -4790,19 +4790,19 @@
         <v>970</v>
       </c>
       <c r="BS16">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT16">
         <v>11</v>
       </c>
       <c r="BU16">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX16">
         <v>1000</v>
@@ -4814,7 +4814,7 @@
         <v>8.6</v>
       </c>
       <c r="CA16">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="CB16" t="s">
         <v>199</v>
@@ -4837,16 +4837,16 @@
         <v>177</v>
       </c>
       <c r="F17">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G17">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="H17">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="I17">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="J17">
         <v>3.25</v>
@@ -4861,16 +4861,16 @@
         <v>1.1</v>
       </c>
       <c r="N17">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O17">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P17">
         <v>1.7</v>
       </c>
       <c r="Q17">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R17">
         <v>1.26</v>
@@ -4879,19 +4879,19 @@
         <v>4.5</v>
       </c>
       <c r="T17">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U17">
         <v>1.97</v>
       </c>
       <c r="V17">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W17">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="X17">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y17">
         <v>9.6</v>
@@ -4927,10 +4927,10 @@
         <v>65</v>
       </c>
       <c r="AJ17">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AK17">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AL17">
         <v>55</v>
@@ -4939,16 +4939,16 @@
         <v>580</v>
       </c>
       <c r="AN17">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="AO17">
-        <v>38</v>
+        <v>600</v>
       </c>
       <c r="AP17">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ17">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR17">
         <v>15.5</v>
@@ -4957,7 +4957,7 @@
         <v>18</v>
       </c>
       <c r="AT17">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU17">
         <v>6.6</v>
@@ -4972,10 +4972,10 @@
         <v>16.5</v>
       </c>
       <c r="AY17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ17">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA17">
         <v>23</v>
@@ -4990,13 +4990,13 @@
         <v>23</v>
       </c>
       <c r="BE17">
+        <v>8.4</v>
+      </c>
+      <c r="BF17">
         <v>7.4</v>
       </c>
-      <c r="BF17">
-        <v>6.8</v>
-      </c>
       <c r="BG17">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="BH17">
         <v>2.96</v>
@@ -5008,7 +5008,7 @@
         <v>10.5</v>
       </c>
       <c r="BK17">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL17">
         <v>1000</v>
@@ -5079,16 +5079,16 @@
         <v>178</v>
       </c>
       <c r="F18">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="G18">
         <v>3.05</v>
       </c>
       <c r="H18">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I18">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J18">
         <v>3.8</v>
@@ -5100,7 +5100,7 @@
         <v>1.29</v>
       </c>
       <c r="M18">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N18">
         <v>5.7</v>
@@ -5121,73 +5121,73 @@
         <v>2.46</v>
       </c>
       <c r="T18">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U18">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="V18">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W18">
         <v>1.48</v>
       </c>
       <c r="X18">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y18">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z18">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA18">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB18">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC18">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD18">
+        <v>12.5</v>
+      </c>
+      <c r="AE18">
+        <v>26</v>
+      </c>
+      <c r="AF18">
+        <v>27</v>
+      </c>
+      <c r="AG18">
+        <v>14</v>
+      </c>
+      <c r="AH18">
         <v>15</v>
       </c>
-      <c r="AE18">
-        <v>28</v>
-      </c>
-      <c r="AF18">
-        <v>29</v>
-      </c>
-      <c r="AG18">
-        <v>16.5</v>
-      </c>
-      <c r="AH18">
-        <v>17</v>
-      </c>
       <c r="AI18">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ18">
         <v>55</v>
       </c>
       <c r="AK18">
+        <v>32</v>
+      </c>
+      <c r="AL18">
         <v>36</v>
       </c>
-      <c r="AL18">
-        <v>40</v>
-      </c>
       <c r="AM18">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AN18">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO18">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AP18">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="AQ18">
         <v>14</v>
@@ -5196,7 +5196,7 @@
         <v>17</v>
       </c>
       <c r="AS18">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AT18">
         <v>15.5</v>
@@ -5208,10 +5208,10 @@
         <v>10.5</v>
       </c>
       <c r="AW18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX18">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY18">
         <v>12</v>
@@ -5220,25 +5220,25 @@
         <v>12.5</v>
       </c>
       <c r="BA18">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BB18">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BC18">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="BD18">
-        <v>16.5</v>
+        <v>26</v>
       </c>
       <c r="BE18">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BF18">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG18">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH18">
         <v>4.4</v>
@@ -5250,31 +5250,31 @@
         <v>8.4</v>
       </c>
       <c r="BK18">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>13.5</v>
+        <v>2.98</v>
       </c>
       <c r="BN18">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO18">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT18">
         <v>5.9</v>
@@ -5286,19 +5286,19 @@
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB18" t="s">
         <v>199</v>
@@ -5321,10 +5321,10 @@
         <v>179</v>
       </c>
       <c r="F19">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G19">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H19">
         <v>3.05</v>
@@ -5354,13 +5354,13 @@
         <v>2.14</v>
       </c>
       <c r="Q19">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R19">
         <v>1.45</v>
       </c>
       <c r="S19">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T19">
         <v>1.65</v>
@@ -5372,7 +5372,7 @@
         <v>1.45</v>
       </c>
       <c r="W19">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X19">
         <v>19.5</v>
@@ -5384,19 +5384,19 @@
         <v>26</v>
       </c>
       <c r="AA19">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB19">
         <v>13.5</v>
       </c>
       <c r="AC19">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD19">
         <v>16</v>
       </c>
       <c r="AE19">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="AF19">
         <v>19</v>
@@ -5408,19 +5408,19 @@
         <v>18</v>
       </c>
       <c r="AI19">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AJ19">
         <v>34</v>
       </c>
       <c r="AK19">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL19">
         <v>36</v>
       </c>
       <c r="AM19">
-        <v>580</v>
+        <v>75</v>
       </c>
       <c r="AN19">
         <v>18</v>
@@ -5429,58 +5429,58 @@
         <v>32</v>
       </c>
       <c r="AP19">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AQ19">
         <v>12.5</v>
       </c>
       <c r="AR19">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AS19">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AT19">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AU19">
         <v>7.4</v>
       </c>
       <c r="AV19">
+        <v>12</v>
+      </c>
+      <c r="AW19">
+        <v>26</v>
+      </c>
+      <c r="AX19">
+        <v>15.5</v>
+      </c>
+      <c r="AY19">
         <v>10.5</v>
       </c>
-      <c r="AW19">
-        <v>16</v>
-      </c>
-      <c r="AX19">
-        <v>12.5</v>
-      </c>
-      <c r="AY19">
-        <v>9</v>
-      </c>
       <c r="AZ19">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA19">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="BB19">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BC19">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BD19">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="BE19">
-        <v>5.9</v>
+        <v>55</v>
       </c>
       <c r="BF19">
         <v>14</v>
       </c>
       <c r="BG19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH19">
         <v>3.75</v>
@@ -5563,22 +5563,22 @@
         <v>180</v>
       </c>
       <c r="F20">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G20">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="H20">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I20">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J20">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K20">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L20">
         <v>1.23</v>
@@ -5587,34 +5587,34 @@
         <v>1.02</v>
       </c>
       <c r="N20">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O20">
         <v>1.13</v>
       </c>
       <c r="P20">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q20">
         <v>1.41</v>
       </c>
       <c r="R20">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S20">
         <v>2.04</v>
       </c>
       <c r="T20">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="U20">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="V20">
         <v>1.27</v>
       </c>
       <c r="W20">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X20">
         <v>40</v>
@@ -5626,7 +5626,7 @@
         <v>44</v>
       </c>
       <c r="AA20">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AB20">
         <v>18</v>
@@ -5635,16 +5635,16 @@
         <v>13</v>
       </c>
       <c r="AD20">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE20">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF20">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG20">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH20">
         <v>16.5</v>
@@ -5653,7 +5653,7 @@
         <v>40</v>
       </c>
       <c r="AJ20">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK20">
         <v>16.5</v>
@@ -5662,67 +5662,67 @@
         <v>24</v>
       </c>
       <c r="AM20">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN20">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AO20">
         <v>26</v>
       </c>
       <c r="AP20">
-        <v>6.6</v>
+        <v>29</v>
       </c>
       <c r="AQ20">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR20">
-        <v>6.8</v>
+        <v>36</v>
       </c>
       <c r="AS20">
-        <v>7.4</v>
+        <v>55</v>
       </c>
       <c r="AT20">
+        <v>14.5</v>
+      </c>
+      <c r="AU20">
+        <v>10.5</v>
+      </c>
+      <c r="AV20">
+        <v>17</v>
+      </c>
+      <c r="AW20">
+        <v>30</v>
+      </c>
+      <c r="AX20">
+        <v>14</v>
+      </c>
+      <c r="AY20">
+        <v>9.6</v>
+      </c>
+      <c r="AZ20">
+        <v>13.5</v>
+      </c>
+      <c r="BA20">
+        <v>29</v>
+      </c>
+      <c r="BB20">
+        <v>18</v>
+      </c>
+      <c r="BC20">
         <v>13</v>
       </c>
-      <c r="AU20">
-        <v>9.6</v>
-      </c>
-      <c r="AV20">
-        <v>14.5</v>
-      </c>
-      <c r="AW20">
-        <v>6.8</v>
-      </c>
-      <c r="AX20">
-        <v>12</v>
-      </c>
-      <c r="AY20">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ20">
-        <v>12</v>
-      </c>
-      <c r="BA20">
-        <v>6.6</v>
-      </c>
-      <c r="BB20">
-        <v>15.5</v>
-      </c>
-      <c r="BC20">
-        <v>12</v>
-      </c>
       <c r="BD20">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BE20">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="BF20">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BG20">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH20">
         <v>5.5</v>
@@ -5734,22 +5734,22 @@
         <v>9</v>
       </c>
       <c r="BK20">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN20">
         <v>5.4</v>
       </c>
       <c r="BO20">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BP20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ20">
         <v>5.4</v>
@@ -5758,31 +5758,31 @@
         <v>18.5</v>
       </c>
       <c r="BS20">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT20">
         <v>9</v>
       </c>
       <c r="BU20">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV20">
         <v>29</v>
       </c>
       <c r="BW20">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX20">
         <v>30</v>
       </c>
       <c r="BY20">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ20">
         <v>11</v>
       </c>
       <c r="CA20">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="CB20" t="s">
         <v>199</v>
@@ -5805,100 +5805,100 @@
         <v>181</v>
       </c>
       <c r="F21">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="G21">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="H21">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="I21">
-        <v>870</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>2.9</v>
       </c>
       <c r="K21">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M21">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N21">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="O21">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="P21">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="Q21">
+        <v>2.84</v>
+      </c>
+      <c r="R21">
+        <v>1.15</v>
+      </c>
+      <c r="S21">
+        <v>5.5</v>
+      </c>
+      <c r="T21">
+        <v>2.42</v>
+      </c>
+      <c r="U21">
         <v>1.57</v>
       </c>
-      <c r="R21">
-        <v>1.12</v>
-      </c>
-      <c r="S21">
-        <v>2.22</v>
-      </c>
-      <c r="T21">
-        <v>1.8</v>
-      </c>
-      <c r="U21">
-        <v>1.32</v>
-      </c>
       <c r="V21">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="W21">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="X21">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="Y21">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Z21">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AA21">
         <v>900</v>
       </c>
       <c r="AB21">
-        <v>970</v>
+        <v>6.6</v>
       </c>
       <c r="AC21">
-        <v>42</v>
+        <v>8.4</v>
       </c>
       <c r="AD21">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="AE21">
         <v>700</v>
       </c>
       <c r="AF21">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AG21">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH21">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AI21">
         <v>700</v>
       </c>
       <c r="AJ21">
-        <v>900</v>
+        <v>24</v>
       </c>
       <c r="AK21">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AL21">
         <v>500</v>
@@ -5907,124 +5907,124 @@
         <v>500</v>
       </c>
       <c r="AN21">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AO21">
         <v>700</v>
       </c>
       <c r="AP21">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ21">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR21">
-        <v>1.57</v>
+        <v>7.4</v>
       </c>
       <c r="AS21">
-        <v>1.59</v>
+        <v>7.6</v>
       </c>
       <c r="AT21">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AU21">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AV21">
-        <v>1.56</v>
+        <v>13</v>
       </c>
       <c r="AW21">
-        <v>1.59</v>
+        <v>7.4</v>
       </c>
       <c r="AX21">
         <v>4.4</v>
       </c>
       <c r="AY21">
-        <v>1.48</v>
+        <v>7</v>
       </c>
       <c r="AZ21">
-        <v>1.57</v>
+        <v>19</v>
       </c>
       <c r="BA21">
-        <v>1.59</v>
+        <v>7.6</v>
       </c>
       <c r="BB21">
-        <v>1.54</v>
+        <v>5.9</v>
       </c>
       <c r="BC21">
-        <v>1.56</v>
+        <v>20</v>
       </c>
       <c r="BD21">
-        <v>1.58</v>
+        <v>7.2</v>
       </c>
       <c r="BE21">
-        <v>1.59</v>
+        <v>7.6</v>
       </c>
       <c r="BF21">
-        <v>1.58</v>
+        <v>6</v>
       </c>
       <c r="BG21">
-        <v>1.59</v>
+        <v>7.6</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="BI21">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK21">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO21">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ21">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU21">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
       </c>
       <c r="CA21">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="CB21" t="s">
         <v>199</v>
@@ -6047,97 +6047,97 @@
         <v>182</v>
       </c>
       <c r="F22">
-        <v>2.54</v>
+        <v>2.82</v>
       </c>
       <c r="G22">
-        <v>9.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="H22">
-        <v>2.14</v>
+        <v>2.9</v>
       </c>
       <c r="I22">
-        <v>6.6</v>
+        <v>3.2</v>
       </c>
       <c r="J22">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="K22">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L22">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="M22">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N22">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O22">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="P22">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Q22">
-        <v>2.1</v>
+        <v>2.78</v>
       </c>
       <c r="R22">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S22">
-        <v>1.05</v>
+        <v>5.9</v>
       </c>
       <c r="T22">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="U22">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="V22">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W22">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="X22">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z22">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AA22">
         <v>900</v>
       </c>
       <c r="AB22">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC22">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="AD22">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AE22">
         <v>500</v>
       </c>
       <c r="AF22">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AG22">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH22">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="AI22">
         <v>500</v>
       </c>
       <c r="AJ22">
-        <v>900</v>
+        <v>250</v>
       </c>
       <c r="AK22">
         <v>500</v>
@@ -6149,124 +6149,124 @@
         <v>500</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP22">
-        <v>1.35</v>
+        <v>6.4</v>
       </c>
       <c r="AQ22">
-        <v>1.43</v>
+        <v>7</v>
       </c>
       <c r="AR22">
-        <v>1.4</v>
+        <v>16</v>
       </c>
       <c r="AS22">
-        <v>1.46</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT22">
-        <v>1.45</v>
+        <v>6.8</v>
       </c>
       <c r="AU22">
-        <v>1.34</v>
+        <v>5.9</v>
       </c>
       <c r="AV22">
-        <v>1.4</v>
+        <v>12</v>
       </c>
       <c r="AW22">
-        <v>1.46</v>
+        <v>14</v>
       </c>
       <c r="AX22">
-        <v>1.45</v>
+        <v>14.5</v>
       </c>
       <c r="AY22">
-        <v>1.46</v>
+        <v>12</v>
       </c>
       <c r="AZ22">
-        <v>1.47</v>
+        <v>20</v>
       </c>
       <c r="BA22">
-        <v>1.47</v>
+        <v>7.8</v>
       </c>
       <c r="BB22">
-        <v>1.47</v>
+        <v>7.4</v>
       </c>
       <c r="BC22">
-        <v>1.47</v>
+        <v>8</v>
       </c>
       <c r="BD22">
-        <v>1.47</v>
+        <v>8</v>
       </c>
       <c r="BE22">
-        <v>1.48</v>
+        <v>9</v>
       </c>
       <c r="BF22">
-        <v>1.55</v>
+        <v>7.4</v>
       </c>
       <c r="BG22">
-        <v>1.55</v>
+        <v>7.6</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="BI22">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK22">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO22">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU22">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW22">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="CB22" t="s">
         <v>199</v>
@@ -6289,226 +6289,226 @@
         <v>183</v>
       </c>
       <c r="F23">
-        <v>2.08</v>
+        <v>2.66</v>
       </c>
       <c r="G23">
-        <v>7.8</v>
+        <v>3.1</v>
       </c>
       <c r="H23">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="I23">
-        <v>9</v>
+        <v>3.75</v>
       </c>
       <c r="J23">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="K23">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="L23">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="M23">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="N23">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="O23">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="P23">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Q23">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="R23">
         <v>1.12</v>
       </c>
       <c r="S23">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="T23">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="U23">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="V23">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="W23">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="X23">
-        <v>970</v>
+        <v>6.6</v>
       </c>
       <c r="Y23">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z23">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AA23">
         <v>500</v>
       </c>
       <c r="AB23">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AC23">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AD23">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AE23">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AF23">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AG23">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH23">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AI23">
         <v>500</v>
       </c>
       <c r="AJ23">
+        <v>160</v>
+      </c>
+      <c r="AK23">
+        <v>150</v>
+      </c>
+      <c r="AL23">
         <v>500</v>
-      </c>
-      <c r="AK23">
-        <v>500</v>
-      </c>
-      <c r="AL23">
-        <v>540</v>
       </c>
       <c r="AM23">
         <v>500</v>
       </c>
       <c r="AN23">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO23">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP23">
-        <v>1.34</v>
+        <v>4.9</v>
       </c>
       <c r="AQ23">
-        <v>1.44</v>
+        <v>4.3</v>
       </c>
       <c r="AR23">
-        <v>2.5</v>
+        <v>7.6</v>
       </c>
       <c r="AS23">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="AT23">
-        <v>1.44</v>
+        <v>6</v>
       </c>
       <c r="AU23">
-        <v>1.46</v>
+        <v>5.9</v>
       </c>
       <c r="AV23">
-        <v>1.38</v>
+        <v>6</v>
       </c>
       <c r="AW23">
-        <v>1.49</v>
+        <v>8</v>
       </c>
       <c r="AX23">
-        <v>1.34</v>
+        <v>14</v>
       </c>
       <c r="AY23">
-        <v>1.38</v>
+        <v>5.7</v>
       </c>
       <c r="AZ23">
-        <v>1.48</v>
+        <v>7</v>
       </c>
       <c r="BA23">
-        <v>1.5</v>
+        <v>8.4</v>
       </c>
       <c r="BB23">
-        <v>1.5</v>
+        <v>7.8</v>
       </c>
       <c r="BC23">
-        <v>1.5</v>
+        <v>7.8</v>
       </c>
       <c r="BD23">
-        <v>1.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE23">
-        <v>1.51</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF23">
-        <v>1.55</v>
+        <v>8</v>
       </c>
       <c r="BG23">
-        <v>1.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH23">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="BI23">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK23">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO23">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU23">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="CB23" t="s">
         <v>199</v>
@@ -6531,16 +6531,16 @@
         <v>184</v>
       </c>
       <c r="F24">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G24">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="H24">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="I24">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J24">
         <v>4.1</v>
@@ -6549,88 +6549,88 @@
         <v>4.3</v>
       </c>
       <c r="L24">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M24">
         <v>1.06</v>
       </c>
       <c r="N24">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="O24">
         <v>1.3</v>
       </c>
       <c r="P24">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q24">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R24">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S24">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T24">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U24">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V24">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W24">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="X24">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y24">
         <v>21</v>
       </c>
       <c r="Z24">
-        <v>220</v>
+        <v>48</v>
       </c>
       <c r="AA24">
-        <v>700</v>
+        <v>180</v>
       </c>
       <c r="AB24">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC24">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD24">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="AE24">
-        <v>700</v>
+        <v>85</v>
       </c>
       <c r="AF24">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AG24">
         <v>10</v>
       </c>
       <c r="AH24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI24">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="AJ24">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK24">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL24">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM24">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AN24">
         <v>10</v>
@@ -6639,58 +6639,58 @@
         <v>700</v>
       </c>
       <c r="AP24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ24">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR24">
-        <v>9.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="AS24">
-        <v>10.5</v>
+        <v>40</v>
       </c>
       <c r="AT24">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU24">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV24">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AW24">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AX24">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY24">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA24">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="BB24">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC24">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD24">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="BE24">
-        <v>10.5</v>
+        <v>80</v>
       </c>
       <c r="BF24">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG24">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="BH24">
         <v>3.7</v>
@@ -6702,55 +6702,55 @@
         <v>11</v>
       </c>
       <c r="BK24">
+        <v>5.2</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN24">
+        <v>4.5</v>
+      </c>
+      <c r="BO24">
+        <v>3.35</v>
+      </c>
+      <c r="BP24">
+        <v>12</v>
+      </c>
+      <c r="BQ24">
         <v>5.4</v>
       </c>
-      <c r="BL24">
-        <v>1000</v>
-      </c>
-      <c r="BM24">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN24">
-        <v>4.4</v>
-      </c>
-      <c r="BO24">
-        <v>3.3</v>
-      </c>
-      <c r="BP24">
-        <v>11.5</v>
-      </c>
-      <c r="BQ24">
-        <v>5.5</v>
-      </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT24">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BU24">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BZ24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA24">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB24" t="s">
         <v>199</v>
@@ -6785,7 +6785,7 @@
         <v>2.48</v>
       </c>
       <c r="J25">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K25">
         <v>3.4</v>
@@ -6800,7 +6800,7 @@
         <v>3.45</v>
       </c>
       <c r="O25">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P25">
         <v>1.82</v>
@@ -6809,7 +6809,7 @@
         <v>2.16</v>
       </c>
       <c r="R25">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S25">
         <v>3.95</v>
@@ -6830,16 +6830,16 @@
         <v>12.5</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="Z25">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA25">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AB25">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC25">
         <v>7.6</v>
@@ -6848,10 +6848,10 @@
         <v>12</v>
       </c>
       <c r="AE25">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AF25">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG25">
         <v>16.5</v>
@@ -6863,16 +6863,16 @@
         <v>44</v>
       </c>
       <c r="AJ25">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AK25">
         <v>44</v>
       </c>
       <c r="AL25">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AM25">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="AN25">
         <v>150</v>
@@ -6905,7 +6905,7 @@
         <v>21</v>
       </c>
       <c r="AX25">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AY25">
         <v>11</v>
@@ -6917,19 +6917,19 @@
         <v>32</v>
       </c>
       <c r="BB25">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="BC25">
         <v>30</v>
       </c>
       <c r="BD25">
-        <v>9.6</v>
+        <v>38</v>
       </c>
       <c r="BE25">
-        <v>10.5</v>
+        <v>29</v>
       </c>
       <c r="BF25">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BG25">
         <v>21</v>
@@ -7015,16 +7015,16 @@
         <v>186</v>
       </c>
       <c r="F26">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G26">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="H26">
         <v>4.4</v>
       </c>
       <c r="I26">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>4.3</v>
@@ -7033,46 +7033,46 @@
         <v>4.7</v>
       </c>
       <c r="L26">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M26">
         <v>1.03</v>
       </c>
       <c r="N26">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="O26">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P26">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="Q26">
         <v>1.54</v>
       </c>
       <c r="R26">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="S26">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="T26">
         <v>1.58</v>
       </c>
       <c r="U26">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V26">
         <v>1.25</v>
       </c>
       <c r="W26">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="X26">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="Y26">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z26">
         <v>500</v>
@@ -7081,7 +7081,7 @@
         <v>900</v>
       </c>
       <c r="AB26">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC26">
         <v>11</v>
@@ -7105,10 +7105,10 @@
         <v>150</v>
       </c>
       <c r="AJ26">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK26">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL26">
         <v>48</v>
@@ -7117,76 +7117,76 @@
         <v>200</v>
       </c>
       <c r="AN26">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO26">
         <v>48</v>
       </c>
       <c r="AP26">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="AQ26">
         <v>7.2</v>
       </c>
       <c r="AR26">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS26">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT26">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU26">
         <v>5.3</v>
       </c>
       <c r="AV26">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AW26">
-        <v>8.6</v>
+        <v>38</v>
       </c>
       <c r="AX26">
+        <v>11.5</v>
+      </c>
+      <c r="AY26">
+        <v>5.4</v>
+      </c>
+      <c r="AZ26">
+        <v>6.2</v>
+      </c>
+      <c r="BA26">
+        <v>32</v>
+      </c>
+      <c r="BB26">
+        <v>6.6</v>
+      </c>
+      <c r="BC26">
+        <v>6.2</v>
+      </c>
+      <c r="BD26">
+        <v>7.4</v>
+      </c>
+      <c r="BE26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF26">
         <v>6</v>
       </c>
-      <c r="AY26">
-        <v>5.5</v>
-      </c>
-      <c r="AZ26">
-        <v>6.4</v>
-      </c>
-      <c r="BA26">
-        <v>8.6</v>
-      </c>
-      <c r="BB26">
-        <v>7</v>
-      </c>
-      <c r="BC26">
-        <v>6.6</v>
-      </c>
-      <c r="BD26">
-        <v>7.6</v>
-      </c>
-      <c r="BE26">
-        <v>9</v>
-      </c>
-      <c r="BF26">
-        <v>4.4</v>
-      </c>
       <c r="BG26">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH26">
         <v>4.6</v>
       </c>
       <c r="BI26">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="BJ26">
         <v>9.199999999999999</v>
       </c>
       <c r="BK26">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL26">
         <v>1000</v>
@@ -7198,37 +7198,37 @@
         <v>5.1</v>
       </c>
       <c r="BO26">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BP26">
         <v>11.5</v>
       </c>
       <c r="BQ26">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BR26">
         <v>21</v>
       </c>
       <c r="BS26">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT26">
         <v>8.6</v>
       </c>
       <c r="BU26">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX26">
         <v>36</v>
       </c>
       <c r="BY26">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ26">
         <v>0</v>
@@ -7257,58 +7257,58 @@
         <v>187</v>
       </c>
       <c r="F27">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G27">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="H27">
+        <v>5.9</v>
+      </c>
+      <c r="I27">
         <v>6.4</v>
       </c>
-      <c r="I27">
-        <v>7.2</v>
-      </c>
       <c r="J27">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K27">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L27">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="M27">
         <v>1.06</v>
       </c>
       <c r="N27">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O27">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="P27">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="Q27">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="R27">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S27">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="T27">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="U27">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="V27">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W27">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="X27">
         <v>21</v>
@@ -7323,7 +7323,7 @@
         <v>900</v>
       </c>
       <c r="AB27">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AC27">
         <v>9.4</v>
@@ -7335,7 +7335,7 @@
         <v>700</v>
       </c>
       <c r="AF27">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG27">
         <v>10.5</v>
@@ -7347,10 +7347,10 @@
         <v>700</v>
       </c>
       <c r="AJ27">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="AK27">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="AL27">
         <v>500</v>
@@ -7359,19 +7359,19 @@
         <v>700</v>
       </c>
       <c r="AN27">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO27">
         <v>700</v>
       </c>
       <c r="AP27">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ27">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR27">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AS27">
         <v>14.5</v>
@@ -7380,19 +7380,19 @@
         <v>7.2</v>
       </c>
       <c r="AU27">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV27">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AW27">
-        <v>13.5</v>
+        <v>38</v>
       </c>
       <c r="AX27">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AY27">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ27">
         <v>11.5</v>
@@ -7407,43 +7407,43 @@
         <v>14.5</v>
       </c>
       <c r="BD27">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE27">
         <v>14</v>
       </c>
       <c r="BF27">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG27">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH27">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="BI27">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="BJ27">
+        <v>10.5</v>
+      </c>
+      <c r="BK27">
+        <v>6.4</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>14.5</v>
+      </c>
+      <c r="BN27">
+        <v>4.3</v>
+      </c>
+      <c r="BO27">
+        <v>3.4</v>
+      </c>
+      <c r="BP27">
         <v>11</v>
-      </c>
-      <c r="BK27">
-        <v>6.8</v>
-      </c>
-      <c r="BL27">
-        <v>1000</v>
-      </c>
-      <c r="BM27">
-        <v>16</v>
-      </c>
-      <c r="BN27">
-        <v>4.1</v>
-      </c>
-      <c r="BO27">
-        <v>3.3</v>
-      </c>
-      <c r="BP27">
-        <v>10.5</v>
       </c>
       <c r="BQ27">
         <v>6.6</v>
@@ -7452,31 +7452,31 @@
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT27">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU27">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BV27">
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB27" t="s">
         <v>199</v>
@@ -7499,13 +7499,13 @@
         <v>188</v>
       </c>
       <c r="F28">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G28">
         <v>1.83</v>
       </c>
       <c r="H28">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I28">
         <v>4.5</v>
@@ -7514,10 +7514,10 @@
         <v>4.5</v>
       </c>
       <c r="K28">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M28">
         <v>1.02</v>
@@ -7529,28 +7529,28 @@
         <v>1.14</v>
       </c>
       <c r="P28">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q28">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R28">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="S28">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="T28">
         <v>1.49</v>
       </c>
       <c r="U28">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="V28">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W28">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X28">
         <v>42</v>
@@ -7583,7 +7583,7 @@
         <v>13.5</v>
       </c>
       <c r="AH28">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI28">
         <v>50</v>
@@ -7595,28 +7595,28 @@
         <v>20</v>
       </c>
       <c r="AL28">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AM28">
         <v>580</v>
       </c>
       <c r="AN28">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AO28">
         <v>32</v>
       </c>
       <c r="AP28">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="AQ28">
         <v>19.5</v>
       </c>
       <c r="AR28">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="AS28">
-        <v>5.4</v>
+        <v>55</v>
       </c>
       <c r="AT28">
         <v>12</v>
@@ -7628,7 +7628,7 @@
         <v>13.5</v>
       </c>
       <c r="AW28">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="AX28">
         <v>11.5</v>
@@ -7640,7 +7640,7 @@
         <v>11.5</v>
       </c>
       <c r="BA28">
-        <v>4.9</v>
+        <v>27</v>
       </c>
       <c r="BB28">
         <v>15</v>
@@ -7652,40 +7652,40 @@
         <v>17</v>
       </c>
       <c r="BE28">
-        <v>5.1</v>
+        <v>38</v>
       </c>
       <c r="BF28">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG28">
         <v>17.5</v>
       </c>
       <c r="BH28">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BI28">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ28">
         <v>8.6</v>
       </c>
       <c r="BK28">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN28">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BO28">
         <v>4.5</v>
       </c>
       <c r="BP28">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ28">
         <v>7.2</v>
@@ -7694,31 +7694,31 @@
         <v>25</v>
       </c>
       <c r="BS28">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT28">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU28">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV28">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW28">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX28">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY28">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BZ28">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA28">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB28" t="s">
         <v>199</v>
@@ -7759,7 +7759,7 @@
         <v>3.85</v>
       </c>
       <c r="L29">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M29">
         <v>1.11</v>
@@ -7768,19 +7768,19 @@
         <v>2.78</v>
       </c>
       <c r="O29">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P29">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q29">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R29">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S29">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T29">
         <v>2.34</v>
@@ -7789,7 +7789,7 @@
         <v>1.65</v>
       </c>
       <c r="V29">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W29">
         <v>2.34</v>
@@ -7810,7 +7810,7 @@
         <v>6</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD29">
         <v>30</v>
@@ -7843,88 +7843,88 @@
         <v>700</v>
       </c>
       <c r="AN29">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO29">
         <v>700</v>
       </c>
       <c r="AP29">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AQ29">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AR29">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="AS29">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT29">
         <v>5.3</v>
       </c>
       <c r="AU29">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV29">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AW29">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX29">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY29">
         <v>9.4</v>
       </c>
       <c r="AZ29">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA29">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB29">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BC29">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD29">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BE29">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF29">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG29">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH29">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BI29">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ29">
         <v>13</v>
       </c>
       <c r="BK29">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN29">
         <v>3.95</v>
       </c>
       <c r="BO29">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP29">
         <v>12.5</v>
@@ -7936,7 +7936,7 @@
         <v>38</v>
       </c>
       <c r="BS29">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT29">
         <v>10.5</v>
@@ -7948,13 +7948,13 @@
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ29">
         <v>0</v>
@@ -7983,7 +7983,7 @@
         <v>190</v>
       </c>
       <c r="F30">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G30">
         <v>4.4</v>
@@ -7995,40 +7995,40 @@
         <v>2.12</v>
       </c>
       <c r="J30">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K30">
         <v>3.45</v>
       </c>
       <c r="L30">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="M30">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N30">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O30">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="P30">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="Q30">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="R30">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S30">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="T30">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="U30">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="V30">
         <v>1.89</v>
@@ -8037,25 +8037,25 @@
         <v>1.3</v>
       </c>
       <c r="X30">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y30">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z30">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AA30">
         <v>65</v>
       </c>
       <c r="AB30">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AC30">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD30">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE30">
         <v>55</v>
@@ -8070,7 +8070,7 @@
         <v>36</v>
       </c>
       <c r="AI30">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AJ30">
         <v>900</v>
@@ -8088,13 +8088,13 @@
         <v>500</v>
       </c>
       <c r="AO30">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AP30">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AQ30">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR30">
         <v>10</v>
@@ -8103,67 +8103,67 @@
         <v>11.5</v>
       </c>
       <c r="AT30">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AU30">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV30">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW30">
         <v>11.5</v>
       </c>
       <c r="AX30">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AY30">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ30">
         <v>10.5</v>
       </c>
       <c r="BA30">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BB30">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BC30">
+        <v>12</v>
+      </c>
+      <c r="BD30">
+        <v>11.5</v>
+      </c>
+      <c r="BE30">
+        <v>12.5</v>
+      </c>
+      <c r="BF30">
+        <v>11.5</v>
+      </c>
+      <c r="BG30">
+        <v>14</v>
+      </c>
+      <c r="BH30">
+        <v>3.3</v>
+      </c>
+      <c r="BI30">
+        <v>2.82</v>
+      </c>
+      <c r="BJ30">
         <v>9.800000000000001</v>
       </c>
-      <c r="BD30">
-        <v>10</v>
-      </c>
-      <c r="BE30">
-        <v>10.5</v>
-      </c>
-      <c r="BF30">
-        <v>10</v>
-      </c>
-      <c r="BG30">
-        <v>17</v>
-      </c>
-      <c r="BH30">
-        <v>3.1</v>
-      </c>
-      <c r="BI30">
-        <v>2.56</v>
-      </c>
-      <c r="BJ30">
-        <v>10.5</v>
-      </c>
       <c r="BK30">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="BN30">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO30">
         <v>5.7</v>
@@ -8172,37 +8172,37 @@
         <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT30">
         <v>4.7</v>
       </c>
       <c r="BU30">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BV30">
         <v>1000</v>
       </c>
       <c r="BW30">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
       </c>
       <c r="CA30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB30" t="s">
         <v>199</v>
@@ -8225,22 +8225,22 @@
         <v>191</v>
       </c>
       <c r="F31">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G31">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="H31">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="I31">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="J31">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="K31">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="L31">
         <v>1.27</v>
@@ -8249,139 +8249,139 @@
         <v>1.02</v>
       </c>
       <c r="N31">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="O31">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="P31">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q31">
         <v>1.56</v>
       </c>
       <c r="R31">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="S31">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="T31">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U31">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="V31">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W31">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="X31">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="Y31">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="Z31">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AA31">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AB31">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AC31">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD31">
-        <v>950</v>
+        <v>44</v>
       </c>
       <c r="AE31">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF31">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AG31">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH31">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AI31">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ31">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AK31">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AL31">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AM31">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN31">
-        <v>29</v>
+        <v>5.1</v>
       </c>
       <c r="AO31">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AP31">
-        <v>1.43</v>
+        <v>7.6</v>
       </c>
       <c r="AQ31">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR31">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS31">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AT31">
-        <v>1.88</v>
+        <v>5</v>
       </c>
       <c r="AU31">
-        <v>1.46</v>
+        <v>6</v>
       </c>
       <c r="AV31">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AW31">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AX31">
-        <v>1.63</v>
+        <v>4.7</v>
       </c>
       <c r="AY31">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="AZ31">
-        <v>1.48</v>
+        <v>7.8</v>
       </c>
       <c r="BA31">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="BB31">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="BC31">
-        <v>1.83</v>
+        <v>6.2</v>
       </c>
       <c r="BD31">
-        <v>1.45</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE31">
-        <v>1.51</v>
+        <v>10</v>
       </c>
       <c r="BF31">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="BG31">
         <v>10.5</v>
@@ -8467,13 +8467,13 @@
         <v>192</v>
       </c>
       <c r="F32">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G32">
         <v>2.04</v>
       </c>
       <c r="H32">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I32">
         <v>4.7</v>
@@ -8482,7 +8482,7 @@
         <v>3.45</v>
       </c>
       <c r="K32">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L32">
         <v>1.46</v>
@@ -8497,7 +8497,7 @@
         <v>1.38</v>
       </c>
       <c r="P32">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q32">
         <v>2.16</v>
@@ -8509,10 +8509,10 @@
         <v>4</v>
       </c>
       <c r="T32">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U32">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V32">
         <v>1.27</v>
@@ -8569,7 +8569,7 @@
         <v>580</v>
       </c>
       <c r="AN32">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO32">
         <v>180</v>
@@ -8584,7 +8584,7 @@
         <v>14.5</v>
       </c>
       <c r="AS32">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT32">
         <v>7.2</v>
@@ -8608,7 +8608,7 @@
         <v>17</v>
       </c>
       <c r="BA32">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB32">
         <v>20</v>
@@ -8620,7 +8620,7 @@
         <v>8.6</v>
       </c>
       <c r="BE32">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF32">
         <v>15.5</v>
@@ -8638,7 +8638,7 @@
         <v>11</v>
       </c>
       <c r="BK32">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BL32">
         <v>1000</v>
@@ -8650,7 +8650,7 @@
         <v>4.7</v>
       </c>
       <c r="BO32">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BP32">
         <v>15</v>
@@ -8668,7 +8668,7 @@
         <v>8</v>
       </c>
       <c r="BU32">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV32">
         <v>42</v>
@@ -8709,22 +8709,22 @@
         <v>193</v>
       </c>
       <c r="F33">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="G33">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="H33">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I33">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J33">
+        <v>3.25</v>
+      </c>
+      <c r="K33">
         <v>3.35</v>
-      </c>
-      <c r="K33">
-        <v>3.5</v>
       </c>
       <c r="L33">
         <v>1.5</v>
@@ -8736,16 +8736,16 @@
         <v>3.1</v>
       </c>
       <c r="O33">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P33">
         <v>1.69</v>
       </c>
       <c r="Q33">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R33">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S33">
         <v>4.5</v>
@@ -8754,25 +8754,25 @@
         <v>1.99</v>
       </c>
       <c r="U33">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V33">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="X33">
         <v>11</v>
       </c>
       <c r="Y33">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z33">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA33">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB33">
         <v>8.4</v>
@@ -8799,13 +8799,13 @@
         <v>170</v>
       </c>
       <c r="AJ33">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="AK33">
         <v>65</v>
       </c>
       <c r="AL33">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AM33">
         <v>450</v>
@@ -8817,7 +8817,7 @@
         <v>500</v>
       </c>
       <c r="AP33">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ33">
         <v>10</v>
@@ -8838,7 +8838,7 @@
         <v>12.5</v>
       </c>
       <c r="AW33">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="AX33">
         <v>11</v>
@@ -8859,10 +8859,10 @@
         <v>23</v>
       </c>
       <c r="BD33">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE33">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF33">
         <v>22</v>
@@ -8871,7 +8871,7 @@
         <v>50</v>
       </c>
       <c r="BH33">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI33">
         <v>2.5</v>
@@ -8886,7 +8886,7 @@
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN33">
         <v>5.1</v>
@@ -8898,16 +8898,16 @@
         <v>18.5</v>
       </c>
       <c r="BQ33">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR33">
         <v>38</v>
       </c>
       <c r="BS33">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT33">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU33">
         <v>5.8</v>
@@ -8916,19 +8916,19 @@
         <v>36</v>
       </c>
       <c r="BW33">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX33">
         <v>55</v>
       </c>
       <c r="BY33">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ33">
         <v>1000</v>
       </c>
       <c r="CA33">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB33" t="s">
         <v>199</v>
@@ -8951,22 +8951,22 @@
         <v>194</v>
       </c>
       <c r="F34">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="G34">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="H34">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I34">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J34">
+        <v>3.3</v>
+      </c>
+      <c r="K34">
         <v>3.35</v>
-      </c>
-      <c r="K34">
-        <v>3.45</v>
       </c>
       <c r="L34">
         <v>1.58</v>
@@ -8975,46 +8975,46 @@
         <v>1.12</v>
       </c>
       <c r="N34">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O34">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P34">
         <v>1.55</v>
       </c>
       <c r="Q34">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R34">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S34">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T34">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U34">
         <v>1.75</v>
       </c>
       <c r="V34">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W34">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="X34">
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z34">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA34">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AB34">
         <v>6.4</v>
@@ -9026,7 +9026,7 @@
         <v>23</v>
       </c>
       <c r="AE34">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AF34">
         <v>10.5</v>
@@ -9038,7 +9038,7 @@
         <v>32</v>
       </c>
       <c r="AI34">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="AJ34">
         <v>26</v>
@@ -9056,7 +9056,7 @@
         <v>27</v>
       </c>
       <c r="AO34">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AP34">
         <v>7.8</v>
@@ -9065,10 +9065,10 @@
         <v>11.5</v>
       </c>
       <c r="AR34">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AS34">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AT34">
         <v>5.9</v>
@@ -9077,10 +9077,10 @@
         <v>6.6</v>
       </c>
       <c r="AV34">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW34">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX34">
         <v>9.199999999999999</v>
@@ -9092,7 +9092,7 @@
         <v>23</v>
       </c>
       <c r="BA34">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB34">
         <v>21</v>
@@ -9104,73 +9104,73 @@
         <v>50</v>
       </c>
       <c r="BE34">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BF34">
         <v>21</v>
       </c>
       <c r="BG34">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BH34">
         <v>2.72</v>
       </c>
       <c r="BI34">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="BJ34">
         <v>12</v>
       </c>
       <c r="BK34">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BN34">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BO34">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BP34">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BQ34">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BT34">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU34">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BX34">
         <v>1000</v>
       </c>
       <c r="BY34">
-        <v>2.34</v>
+        <v>14</v>
       </c>
       <c r="BZ34">
         <v>1000</v>
       </c>
       <c r="CA34">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="CB34" t="s">
         <v>199</v>
@@ -9202,13 +9202,13 @@
         <v>3.35</v>
       </c>
       <c r="I35">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J35">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K35">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L35">
         <v>1.4</v>
@@ -9238,7 +9238,7 @@
         <v>1.71</v>
       </c>
       <c r="U35">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V35">
         <v>1.37</v>
@@ -9247,112 +9247,112 @@
         <v>1.76</v>
       </c>
       <c r="X35">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y35">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z35">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA35">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB35">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC35">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD35">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE35">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF35">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AG35">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH35">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI35">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ35">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK35">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL35">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM35">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN35">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO35">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP35">
-        <v>1.15</v>
+        <v>4</v>
       </c>
       <c r="AQ35">
-        <v>1.07</v>
+        <v>10</v>
       </c>
       <c r="AR35">
-        <v>1.16</v>
+        <v>4.4</v>
       </c>
       <c r="AS35">
-        <v>1.16</v>
+        <v>4.8</v>
       </c>
       <c r="AT35">
-        <v>1.15</v>
+        <v>7.6</v>
       </c>
       <c r="AU35">
-        <v>1.15</v>
+        <v>6.8</v>
       </c>
       <c r="AV35">
-        <v>1.15</v>
+        <v>4</v>
       </c>
       <c r="AW35">
-        <v>1.16</v>
+        <v>4.7</v>
       </c>
       <c r="AX35">
-        <v>1.08</v>
+        <v>4</v>
       </c>
       <c r="AY35">
-        <v>1.15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ35">
-        <v>1.15</v>
+        <v>12.5</v>
       </c>
       <c r="BA35">
-        <v>1.16</v>
+        <v>4.7</v>
       </c>
       <c r="BB35">
-        <v>1.16</v>
+        <v>21</v>
       </c>
       <c r="BC35">
-        <v>1.16</v>
+        <v>4.3</v>
       </c>
       <c r="BD35">
-        <v>1.16</v>
+        <v>4.6</v>
       </c>
       <c r="BE35">
-        <v>1.16</v>
+        <v>4.9</v>
       </c>
       <c r="BF35">
-        <v>1.15</v>
+        <v>4.1</v>
       </c>
       <c r="BG35">
-        <v>1.16</v>
+        <v>4.6</v>
       </c>
       <c r="BH35">
         <v>3.6</v>
@@ -9370,25 +9370,25 @@
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN35">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO35">
         <v>4.4</v>
       </c>
       <c r="BP35">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ35">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR35">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS35">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT35">
         <v>7</v>
@@ -9400,19 +9400,19 @@
         <v>29</v>
       </c>
       <c r="BW35">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX35">
         <v>40</v>
       </c>
       <c r="BY35">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ35">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CA35">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB35" t="s">
         <v>199</v>
@@ -9438,46 +9438,46 @@
         <v>1.84</v>
       </c>
       <c r="G36">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="H36">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I36">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J36">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K36">
         <v>3.85</v>
       </c>
       <c r="L36">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M36">
         <v>1.08</v>
       </c>
       <c r="N36">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O36">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P36">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q36">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R36">
         <v>1.29</v>
       </c>
       <c r="S36">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T36">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="U36">
         <v>1.9</v>
@@ -9486,49 +9486,49 @@
         <v>1.23</v>
       </c>
       <c r="W36">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X36">
         <v>14</v>
       </c>
       <c r="Y36">
-        <v>950</v>
+        <v>16</v>
       </c>
       <c r="Z36">
         <v>48</v>
       </c>
       <c r="AA36">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB36">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC36">
         <v>8.4</v>
       </c>
       <c r="AD36">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE36">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF36">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG36">
         <v>10.5</v>
       </c>
       <c r="AH36">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI36">
         <v>85</v>
       </c>
       <c r="AJ36">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK36">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL36">
         <v>46</v>
@@ -9537,64 +9537,64 @@
         <v>140</v>
       </c>
       <c r="AN36">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AO36">
         <v>110</v>
       </c>
       <c r="AP36">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="AQ36">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR36">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="AS36">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AT36">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU36">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV36">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="AW36">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="AX36">
-        <v>3.55</v>
+        <v>9.4</v>
       </c>
       <c r="AY36">
         <v>8</v>
       </c>
       <c r="AZ36">
-        <v>5</v>
+        <v>18.5</v>
       </c>
       <c r="BA36">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="BB36">
-        <v>4.1</v>
+        <v>15.5</v>
       </c>
       <c r="BC36">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD36">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="BE36">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="BF36">
-        <v>3.9</v>
+        <v>13.5</v>
       </c>
       <c r="BG36">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH36">
         <v>3.2</v>
@@ -9603,7 +9603,7 @@
         <v>2.9</v>
       </c>
       <c r="BJ36">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK36">
         <v>6.2</v>
@@ -9615,16 +9615,16 @@
         <v>13.5</v>
       </c>
       <c r="BN36">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO36">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BP36">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ36">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR36">
         <v>1000</v>
@@ -9633,16 +9633,16 @@
         <v>10</v>
       </c>
       <c r="BT36">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU36">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV36">
         <v>1000</v>
       </c>
       <c r="BW36">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX36">
         <v>1000</v>
@@ -9654,7 +9654,7 @@
         <v>1000</v>
       </c>
       <c r="CA36">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB36" t="s">
         <v>199</v>
@@ -9677,22 +9677,22 @@
         <v>197</v>
       </c>
       <c r="F37">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G37">
         <v>3.5</v>
       </c>
       <c r="H37">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="I37">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J37">
         <v>3.15</v>
       </c>
       <c r="K37">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L37">
         <v>1.48</v>
@@ -9701,37 +9701,37 @@
         <v>1.09</v>
       </c>
       <c r="N37">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O37">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P37">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q37">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R37">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S37">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T37">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="U37">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V37">
         <v>1.61</v>
       </c>
       <c r="W37">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X37">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y37">
         <v>10.5</v>
@@ -9746,7 +9746,7 @@
         <v>13</v>
       </c>
       <c r="AC37">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD37">
         <v>13.5</v>
@@ -9755,10 +9755,10 @@
         <v>34</v>
       </c>
       <c r="AF37">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG37">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH37">
         <v>22</v>
@@ -9767,7 +9767,7 @@
         <v>55</v>
       </c>
       <c r="AJ37">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK37">
         <v>50</v>
@@ -9785,64 +9785,64 @@
         <v>29</v>
       </c>
       <c r="AP37">
-        <v>3.95</v>
+        <v>9.6</v>
       </c>
       <c r="AQ37">
-        <v>3.65</v>
+        <v>7.8</v>
       </c>
       <c r="AR37">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AS37">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AT37">
-        <v>3.95</v>
+        <v>9.4</v>
       </c>
       <c r="AU37">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV37">
-        <v>4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW37">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AX37">
-        <v>4.6</v>
+        <v>17</v>
       </c>
       <c r="AY37">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AZ37">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA37">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BB37">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BC37">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BD37">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BE37">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF37">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BG37">
-        <v>4.7</v>
+        <v>21</v>
       </c>
       <c r="BH37">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI37">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="BJ37">
         <v>10.5</v>
@@ -9854,7 +9854,7 @@
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN37">
         <v>6.6</v>
@@ -9863,10 +9863,10 @@
         <v>5</v>
       </c>
       <c r="BP37">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BQ37">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR37">
         <v>1000</v>
@@ -9887,16 +9887,16 @@
         <v>7</v>
       </c>
       <c r="BX37">
+        <v>40</v>
+      </c>
+      <c r="BY37">
+        <v>8.4</v>
+      </c>
+      <c r="BZ37">
         <v>38</v>
       </c>
-      <c r="BY37">
+      <c r="CA37">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BZ37">
-        <v>36</v>
-      </c>
-      <c r="CA37">
-        <v>8</v>
       </c>
       <c r="CB37" t="s">
         <v>199</v>
@@ -9919,7 +9919,7 @@
         <v>198</v>
       </c>
       <c r="F38">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="G38">
         <v>2.52</v>
@@ -9928,13 +9928,13 @@
         <v>3.25</v>
       </c>
       <c r="I38">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J38">
         <v>3.25</v>
       </c>
       <c r="K38">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L38">
         <v>1.47</v>
@@ -9955,7 +9955,7 @@
         <v>2.14</v>
       </c>
       <c r="R38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S38">
         <v>4</v>
@@ -9967,10 +9967,10 @@
         <v>2.04</v>
       </c>
       <c r="V38">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W38">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X38">
         <v>14.5</v>
@@ -10096,7 +10096,7 @@
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>2.58</v>
+        <v>16.5</v>
       </c>
       <c r="BN38">
         <v>5.2</v>
@@ -10120,7 +10120,7 @@
         <v>6.4</v>
       </c>
       <c r="BU38">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV38">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -613,7 +613,7 @@
     <t>Everton De Vina</t>
   </si>
   <si>
-    <t>2026-07-27 03:55:36</t>
+    <t>2026-07-27 06:02:53</t>
   </si>
 </sst>
 </file>
@@ -1207,16 +1207,16 @@
         <v>162</v>
       </c>
       <c r="F2">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="G2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J2">
         <v>3.45</v>
@@ -1225,46 +1225,46 @@
         <v>3.95</v>
       </c>
       <c r="L2">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="O2">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="P2">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q2">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R2">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S2">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T2">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U2">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V2">
         <v>1.14</v>
       </c>
       <c r="W2">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="X2">
         <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z2">
         <v>160</v>
@@ -1276,13 +1276,13 @@
         <v>6.6</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AE2">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AF2">
         <v>9.199999999999999</v>
@@ -1291,52 +1291,52 @@
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AI2">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AJ2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL2">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM2">
         <v>580</v>
       </c>
       <c r="AN2">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AO2">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="AP2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR2">
-        <v>46</v>
+        <v>9.4</v>
       </c>
       <c r="AS2">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT2">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AU2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV2">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="AW2">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX2">
         <v>7.4</v>
@@ -1345,40 +1345,40 @@
         <v>8.6</v>
       </c>
       <c r="AZ2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA2">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2">
         <v>14.5</v>
       </c>
       <c r="BC2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD2">
-        <v>44</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE2">
         <v>140</v>
       </c>
       <c r="BF2">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG2">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH2">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BI2">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="BJ2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1390,43 +1390,43 @@
         <v>4.2</v>
       </c>
       <c r="BO2">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BP2">
         <v>13.5</v>
       </c>
       <c r="BQ2">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BU2">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB2" t="s">
         <v>199</v>
@@ -1449,22 +1449,22 @@
         <v>163</v>
       </c>
       <c r="F3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="H3">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="I3">
         <v>1.27</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="K3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L3">
         <v>1.21</v>
@@ -1473,25 +1473,25 @@
         <v>1.02</v>
       </c>
       <c r="N3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O3">
         <v>1.12</v>
       </c>
       <c r="P3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R3">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S3">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="T3">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U3">
         <v>2.1</v>
@@ -1500,10 +1500,10 @@
         <v>4.7</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Y3">
         <v>15</v>
@@ -1518,7 +1518,7 @@
         <v>70</v>
       </c>
       <c r="AC3">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AD3">
         <v>12</v>
@@ -1539,16 +1539,16 @@
         <v>30</v>
       </c>
       <c r="AJ3">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AK3">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AL3">
+        <v>140</v>
+      </c>
+      <c r="AM3">
         <v>130</v>
-      </c>
-      <c r="AM3">
-        <v>120</v>
       </c>
       <c r="AN3">
         <v>150</v>
@@ -1557,16 +1557,16 @@
         <v>3.25</v>
       </c>
       <c r="AP3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AQ3">
         <v>13</v>
       </c>
       <c r="AR3">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AS3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT3">
         <v>55</v>
@@ -1593,10 +1593,10 @@
         <v>24</v>
       </c>
       <c r="BB3">
-        <v>12</v>
+        <v>4.2</v>
       </c>
       <c r="BC3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD3">
         <v>13.5</v>
@@ -1611,40 +1611,40 @@
         <v>3.05</v>
       </c>
       <c r="BH3">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BI3">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BJ3">
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN3">
         <v>16</v>
       </c>
       <c r="BO3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BP3">
         <v>90</v>
       </c>
       <c r="BQ3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BR3">
         <v>70</v>
       </c>
       <c r="BS3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT3">
         <v>4.3</v>
@@ -1662,7 +1662,7 @@
         <v>18.5</v>
       </c>
       <c r="BY3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1691,46 +1691,46 @@
         <v>164</v>
       </c>
       <c r="F4">
+        <v>2.04</v>
+      </c>
+      <c r="G4">
         <v>2.12</v>
       </c>
-      <c r="G4">
-        <v>2.32</v>
-      </c>
       <c r="H4">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="I4">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
         <v>1.36</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O4">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P4">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q4">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="R4">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T4">
         <v>1.67</v>
@@ -1739,40 +1739,40 @@
         <v>2.22</v>
       </c>
       <c r="V4">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="X4">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y4">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z4">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AA4">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AB4">
         <v>11.5</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AD4">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF4">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH4">
         <v>17.5</v>
@@ -1781,31 +1781,31 @@
         <v>48</v>
       </c>
       <c r="AJ4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AK4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM4">
         <v>200</v>
       </c>
       <c r="AN4">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AO4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AP4">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="AQ4">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AR4">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AS4">
         <v>11</v>
@@ -1817,16 +1817,16 @@
         <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="AW4">
         <v>9.800000000000001</v>
       </c>
       <c r="AX4">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AY4">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
         <v>14</v>
@@ -1835,76 +1835,76 @@
         <v>12.5</v>
       </c>
       <c r="BB4">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="BC4">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="BD4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BG4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH4">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BI4">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BJ4">
         <v>9.6</v>
       </c>
       <c r="BK4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN4">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BO4">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BP4">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BS4">
         <v>7.4</v>
       </c>
       <c r="BT4">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BU4">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BV4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BW4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX4">
         <v>38</v>
       </c>
       <c r="BY4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1933,25 +1933,25 @@
         <v>165</v>
       </c>
       <c r="F5">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G5">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="H5">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I5">
         <v>5.6</v>
       </c>
       <c r="J5">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L5">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M5">
         <v>1.07</v>
@@ -1963,28 +1963,28 @@
         <v>1.33</v>
       </c>
       <c r="P5">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q5">
         <v>1.98</v>
       </c>
       <c r="R5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S5">
         <v>3.55</v>
       </c>
       <c r="T5">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U5">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V5">
         <v>1.22</v>
       </c>
       <c r="W5">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="X5">
         <v>16.5</v>
@@ -1993,16 +1993,16 @@
         <v>21</v>
       </c>
       <c r="Z5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA5">
         <v>140</v>
       </c>
       <c r="AB5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC5">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5">
         <v>20</v>
@@ -2014,7 +2014,7 @@
         <v>12</v>
       </c>
       <c r="AG5">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH5">
         <v>20</v>
@@ -2035,43 +2035,43 @@
         <v>120</v>
       </c>
       <c r="AN5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO5">
         <v>85</v>
       </c>
       <c r="AP5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ5">
         <v>16.5</v>
       </c>
       <c r="AR5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS5">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AT5">
         <v>7.8</v>
       </c>
       <c r="AU5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV5">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AW5">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AX5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA5">
         <v>60</v>
@@ -2080,37 +2080,37 @@
         <v>16.5</v>
       </c>
       <c r="BC5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD5">
         <v>32</v>
       </c>
       <c r="BE5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BF5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG5">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BH5">
         <v>3.35</v>
       </c>
       <c r="BI5">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BJ5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BN5">
         <v>4.4</v>
@@ -2119,10 +2119,10 @@
         <v>4</v>
       </c>
       <c r="BP5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR5">
         <v>1000</v>
@@ -2134,25 +2134,25 @@
         <v>8.6</v>
       </c>
       <c r="BU5">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
+        <v>13</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
         <v>13.5</v>
       </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>9.4</v>
-      </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB5" t="s">
         <v>199</v>
@@ -2175,31 +2175,31 @@
         <v>166</v>
       </c>
       <c r="F6">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="G6">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="I6">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="J6">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="K6">
         <v>4.2</v>
       </c>
       <c r="L6">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M6">
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O6">
         <v>1.27</v>
@@ -2214,73 +2214,73 @@
         <v>1.42</v>
       </c>
       <c r="S6">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T6">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U6">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V6">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W6">
         <v>1.27</v>
       </c>
       <c r="X6">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y6">
+        <v>10</v>
+      </c>
+      <c r="Z6">
+        <v>12.5</v>
+      </c>
+      <c r="AA6">
+        <v>21</v>
+      </c>
+      <c r="AB6">
+        <v>18.5</v>
+      </c>
+      <c r="AC6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD6">
         <v>10.5</v>
       </c>
-      <c r="Z6">
-        <v>13.5</v>
-      </c>
-      <c r="AA6">
-        <v>23</v>
-      </c>
-      <c r="AB6">
-        <v>17.5</v>
-      </c>
-      <c r="AC6">
-        <v>9</v>
-      </c>
-      <c r="AD6">
-        <v>11</v>
-      </c>
       <c r="AE6">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AF6">
         <v>42</v>
       </c>
       <c r="AG6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH6">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI6">
         <v>46</v>
       </c>
       <c r="AJ6">
-        <v>310</v>
+        <v>500</v>
       </c>
       <c r="AK6">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AL6">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AM6">
-        <v>390</v>
+        <v>200</v>
       </c>
       <c r="AN6">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="AO6">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP6">
         <v>14.5</v>
@@ -2292,19 +2292,19 @@
         <v>10.5</v>
       </c>
       <c r="AS6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT6">
         <v>14</v>
       </c>
       <c r="AU6">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV6">
         <v>8.800000000000001</v>
       </c>
       <c r="AW6">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX6">
         <v>27</v>
@@ -2316,7 +2316,7 @@
         <v>15.5</v>
       </c>
       <c r="BA6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB6">
         <v>55</v>
@@ -2334,7 +2334,7 @@
         <v>32</v>
       </c>
       <c r="BG6">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BH6">
         <v>3.8</v>
@@ -2346,13 +2346,13 @@
         <v>9.6</v>
       </c>
       <c r="BK6">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN6">
         <v>8</v>
@@ -2364,13 +2364,13 @@
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT6">
         <v>4.8</v>
@@ -2382,13 +2382,13 @@
         <v>13.5</v>
       </c>
       <c r="BW6">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2417,22 +2417,22 @@
         <v>167</v>
       </c>
       <c r="F7">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="H7">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="I7">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="J7">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="K7">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L7">
         <v>1.34</v>
@@ -2441,88 +2441,88 @@
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O7">
         <v>1.25</v>
       </c>
       <c r="P7">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q7">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R7">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S7">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T7">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="U7">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="V7">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
         <v>19.5</v>
       </c>
       <c r="Y7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB7">
         <v>36</v>
       </c>
       <c r="AC7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD7">
         <v>10.5</v>
       </c>
       <c r="AE7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AF7">
         <v>110</v>
       </c>
       <c r="AG7">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AH7">
         <v>32</v>
       </c>
       <c r="AI7">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ7">
-        <v>530</v>
+        <v>450</v>
       </c>
       <c r="AK7">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AL7">
-        <v>170</v>
+        <v>470</v>
       </c>
       <c r="AM7">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN7">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="AO7">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AP7">
         <v>17</v>
@@ -2531,43 +2531,43 @@
         <v>7.8</v>
       </c>
       <c r="AR7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT7">
         <v>30</v>
       </c>
       <c r="AU7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV7">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AX7">
         <v>48</v>
       </c>
       <c r="AY7">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AZ7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA7">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BB7">
+        <v>12.5</v>
+      </c>
+      <c r="BC7">
+        <v>13</v>
+      </c>
+      <c r="BD7">
         <v>14</v>
-      </c>
-      <c r="BC7">
-        <v>15</v>
-      </c>
-      <c r="BD7">
-        <v>15.5</v>
       </c>
       <c r="BE7">
         <v>28</v>
@@ -2588,16 +2588,16 @@
         <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BO7">
         <v>10</v>
@@ -2606,13 +2606,13 @@
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT7">
         <v>3.8</v>
@@ -2630,13 +2630,13 @@
         <v>25</v>
       </c>
       <c r="BY7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CA7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB7" t="s">
         <v>199</v>
@@ -2659,19 +2659,19 @@
         <v>168</v>
       </c>
       <c r="F8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G8">
         <v>4.6</v>
       </c>
       <c r="H8">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="I8">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="J8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K8">
         <v>3.85</v>
@@ -2683,16 +2683,16 @@
         <v>1.06</v>
       </c>
       <c r="N8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P8">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q8">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R8">
         <v>1.41</v>
@@ -2701,28 +2701,28 @@
         <v>3.25</v>
       </c>
       <c r="T8">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U8">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V8">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W8">
         <v>1.28</v>
       </c>
       <c r="X8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z8">
         <v>13</v>
       </c>
       <c r="AA8">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AB8">
         <v>19</v>
@@ -2734,7 +2734,7 @@
         <v>10.5</v>
       </c>
       <c r="AE8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF8">
         <v>48</v>
@@ -2743,10 +2743,10 @@
         <v>20</v>
       </c>
       <c r="AH8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI8">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AJ8">
         <v>500</v>
@@ -2764,7 +2764,7 @@
         <v>120</v>
       </c>
       <c r="AO8">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP8">
         <v>12.5</v>
@@ -2776,10 +2776,10 @@
         <v>10.5</v>
       </c>
       <c r="AS8">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT8">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AU8">
         <v>7.2</v>
@@ -2794,7 +2794,7 @@
         <v>14.5</v>
       </c>
       <c r="AY8">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ8">
         <v>14.5</v>
@@ -2803,16 +2803,16 @@
         <v>24</v>
       </c>
       <c r="BB8">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BD8">
         <v>25</v>
       </c>
       <c r="BE8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF8">
         <v>9.4</v>
@@ -2824,7 +2824,7 @@
         <v>3.7</v>
       </c>
       <c r="BI8">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ8">
         <v>9.800000000000001</v>
@@ -2836,7 +2836,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN8">
         <v>7.6</v>
@@ -2848,37 +2848,37 @@
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT8">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU8">
         <v>4.2</v>
       </c>
       <c r="BV8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BW8">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BX8">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ8">
+        <v>22</v>
+      </c>
+      <c r="CA8">
         <v>8</v>
-      </c>
-      <c r="BZ8">
-        <v>24</v>
-      </c>
-      <c r="CA8">
-        <v>7.6</v>
       </c>
       <c r="CB8" t="s">
         <v>199</v>
@@ -2901,7 +2901,7 @@
         <v>169</v>
       </c>
       <c r="F9">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G9">
         <v>2.8</v>
@@ -2919,13 +2919,13 @@
         <v>3.9</v>
       </c>
       <c r="L9">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M9">
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O9">
         <v>1.3</v>
@@ -2934,19 +2934,19 @@
         <v>2</v>
       </c>
       <c r="Q9">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="R9">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S9">
         <v>3.35</v>
       </c>
       <c r="T9">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U9">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V9">
         <v>1.54</v>
@@ -2994,7 +2994,7 @@
         <v>44</v>
       </c>
       <c r="AK9">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AL9">
         <v>100</v>
@@ -3051,7 +3051,7 @@
         <v>23</v>
       </c>
       <c r="BD9">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BE9">
         <v>7.8</v>
@@ -3143,55 +3143,55 @@
         <v>170</v>
       </c>
       <c r="F10">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G10">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H10">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I10">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L10">
         <v>1.43</v>
       </c>
       <c r="M10">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O10">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P10">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q10">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R10">
         <v>1.33</v>
       </c>
       <c r="S10">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T10">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U10">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W10">
         <v>2.14</v>
@@ -3200,7 +3200,7 @@
         <v>14.5</v>
       </c>
       <c r="Y10">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z10">
         <v>46</v>
@@ -3209,19 +3209,19 @@
         <v>900</v>
       </c>
       <c r="AB10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC10">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AE10">
         <v>95</v>
       </c>
       <c r="AF10">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG10">
         <v>12</v>
@@ -3248,7 +3248,7 @@
         <v>13.5</v>
       </c>
       <c r="AO10">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="AP10">
         <v>12</v>
@@ -3269,13 +3269,13 @@
         <v>7.4</v>
       </c>
       <c r="AV10">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AW10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY10">
         <v>9</v>
@@ -3302,7 +3302,7 @@
         <v>12</v>
       </c>
       <c r="BG10">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BH10">
         <v>3.35</v>
@@ -3314,13 +3314,13 @@
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BN10">
         <v>4.4</v>
@@ -3338,28 +3338,28 @@
         <v>36</v>
       </c>
       <c r="BS10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT10">
         <v>8.199999999999999</v>
       </c>
       <c r="BU10">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BV10">
         <v>60</v>
       </c>
       <c r="BW10">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BZ10">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="CA10">
         <v>10.5</v>
@@ -3385,19 +3385,19 @@
         <v>171</v>
       </c>
       <c r="F11">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G11">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H11">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I11">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J11">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K11">
         <v>3.8</v>
@@ -3412,40 +3412,40 @@
         <v>4.9</v>
       </c>
       <c r="O11">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P11">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q11">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R11">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S11">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T11">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U11">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V11">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W11">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y11">
         <v>14</v>
       </c>
       <c r="Z11">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA11">
         <v>36</v>
@@ -3457,7 +3457,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE11">
         <v>26</v>
@@ -3472,25 +3472,25 @@
         <v>15.5</v>
       </c>
       <c r="AI11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ11">
         <v>46</v>
       </c>
       <c r="AK11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL11">
         <v>38</v>
       </c>
       <c r="AM11">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AN11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP11">
         <v>16.5</v>
@@ -3502,13 +3502,13 @@
         <v>16.5</v>
       </c>
       <c r="AS11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT11">
         <v>13</v>
       </c>
       <c r="AU11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV11">
         <v>10.5</v>
@@ -3523,7 +3523,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA11">
         <v>27</v>
@@ -3541,28 +3541,28 @@
         <v>50</v>
       </c>
       <c r="BF11">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG11">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BH11">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI11">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ11">
         <v>8.800000000000001</v>
       </c>
       <c r="BK11">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN11">
         <v>6.2</v>
@@ -3574,13 +3574,13 @@
         <v>21</v>
       </c>
       <c r="BQ11">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR11">
         <v>30</v>
       </c>
       <c r="BS11">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT11">
         <v>5.8</v>
@@ -3592,19 +3592,19 @@
         <v>18</v>
       </c>
       <c r="BW11">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX11">
         <v>28</v>
       </c>
       <c r="BY11">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA11">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB11" t="s">
         <v>199</v>
@@ -3627,16 +3627,16 @@
         <v>172</v>
       </c>
       <c r="F12">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G12">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="H12">
+        <v>3.75</v>
+      </c>
+      <c r="I12">
         <v>3.85</v>
-      </c>
-      <c r="I12">
-        <v>3.95</v>
       </c>
       <c r="J12">
         <v>4.4</v>
@@ -3645,7 +3645,7 @@
         <v>4.5</v>
       </c>
       <c r="L12">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M12">
         <v>1.03</v>
@@ -3657,13 +3657,13 @@
         <v>1.16</v>
       </c>
       <c r="P12">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q12">
         <v>1.5</v>
       </c>
       <c r="R12">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S12">
         <v>2.22</v>
@@ -3672,13 +3672,13 @@
         <v>1.51</v>
       </c>
       <c r="U12">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X12">
         <v>30</v>
@@ -3687,10 +3687,10 @@
         <v>25</v>
       </c>
       <c r="Z12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA12">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB12">
         <v>16</v>
@@ -3699,7 +3699,7 @@
         <v>10.5</v>
       </c>
       <c r="AD12">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE12">
         <v>36</v>
@@ -3711,7 +3711,7 @@
         <v>11</v>
       </c>
       <c r="AH12">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI12">
         <v>36</v>
@@ -3720,52 +3720,52 @@
         <v>24</v>
       </c>
       <c r="AK12">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM12">
         <v>50</v>
       </c>
       <c r="AN12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO12">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ12">
         <v>23</v>
       </c>
       <c r="AR12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS12">
         <v>60</v>
       </c>
       <c r="AT12">
+        <v>15</v>
+      </c>
+      <c r="AU12">
+        <v>10</v>
+      </c>
+      <c r="AV12">
         <v>14.5</v>
       </c>
-      <c r="AU12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV12">
-        <v>15</v>
-      </c>
       <c r="AW12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX12">
         <v>14.5</v>
       </c>
       <c r="AY12">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA12">
         <v>32</v>
@@ -3780,13 +3780,13 @@
         <v>21</v>
       </c>
       <c r="BE12">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BF12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH12">
         <v>5</v>
@@ -3804,7 +3804,7 @@
         <v>70</v>
       </c>
       <c r="BM12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN12">
         <v>5.4</v>
@@ -3831,7 +3831,7 @@
         <v>4.8</v>
       </c>
       <c r="BV12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW12">
         <v>8.199999999999999</v>
@@ -3840,7 +3840,7 @@
         <v>29</v>
       </c>
       <c r="BY12">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ12">
         <v>13</v>
@@ -3869,22 +3869,22 @@
         <v>173</v>
       </c>
       <c r="F13">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G13">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H13">
         <v>3.65</v>
       </c>
       <c r="I13">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J13">
         <v>3.85</v>
       </c>
       <c r="K13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L13">
         <v>1.34</v>
@@ -3911,10 +3911,10 @@
         <v>2.92</v>
       </c>
       <c r="T13">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U13">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V13">
         <v>1.35</v>
@@ -3959,7 +3959,7 @@
         <v>55</v>
       </c>
       <c r="AJ13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK13">
         <v>21</v>
@@ -3974,7 +3974,7 @@
         <v>12.5</v>
       </c>
       <c r="AO13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP13">
         <v>16</v>
@@ -3986,7 +3986,7 @@
         <v>23</v>
       </c>
       <c r="AS13">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AT13">
         <v>9.800000000000001</v>
@@ -4013,7 +4013,7 @@
         <v>36</v>
       </c>
       <c r="BB13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC13">
         <v>17</v>
@@ -4028,13 +4028,13 @@
         <v>10</v>
       </c>
       <c r="BG13">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH13">
         <v>4.1</v>
       </c>
       <c r="BI13">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ13">
         <v>9.4</v>
@@ -4111,22 +4111,22 @@
         <v>174</v>
       </c>
       <c r="F14">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G14">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H14">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I14">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J14">
         <v>4.1</v>
       </c>
       <c r="K14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L14">
         <v>1.34</v>
@@ -4135,28 +4135,28 @@
         <v>1.05</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O14">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P14">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q14">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R14">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S14">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="T14">
         <v>1.7</v>
       </c>
       <c r="U14">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V14">
         <v>1.26</v>
@@ -4165,7 +4165,7 @@
         <v>2.2</v>
       </c>
       <c r="X14">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y14">
         <v>21</v>
@@ -4177,7 +4177,7 @@
         <v>100</v>
       </c>
       <c r="AB14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC14">
         <v>9.6</v>
@@ -4192,10 +4192,10 @@
         <v>12.5</v>
       </c>
       <c r="AG14">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH14">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI14">
         <v>55</v>
@@ -4222,7 +4222,7 @@
         <v>18</v>
       </c>
       <c r="AQ14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR14">
         <v>34</v>
@@ -4231,7 +4231,7 @@
         <v>85</v>
       </c>
       <c r="AT14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU14">
         <v>8.800000000000001</v>
@@ -4249,13 +4249,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA14">
         <v>46</v>
       </c>
       <c r="BB14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC14">
         <v>15.5</v>
@@ -4264,13 +4264,13 @@
         <v>26</v>
       </c>
       <c r="BE14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF14">
         <v>8.4</v>
       </c>
       <c r="BG14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH14">
         <v>3.95</v>
@@ -4359,19 +4359,19 @@
         <v>1.68</v>
       </c>
       <c r="H15">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J15">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K15">
         <v>4.5</v>
       </c>
       <c r="L15">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M15">
         <v>1.05</v>
@@ -4383,31 +4383,31 @@
         <v>1.25</v>
       </c>
       <c r="P15">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q15">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R15">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S15">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T15">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U15">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V15">
         <v>1.2</v>
       </c>
       <c r="W15">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X15">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y15">
         <v>22</v>
@@ -4416,10 +4416,10 @@
         <v>48</v>
       </c>
       <c r="AA15">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB15">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC15">
         <v>9.6</v>
@@ -4431,19 +4431,19 @@
         <v>75</v>
       </c>
       <c r="AF15">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG15">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AH15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI15">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AJ15">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK15">
         <v>16</v>
@@ -4455,7 +4455,7 @@
         <v>100</v>
       </c>
       <c r="AN15">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO15">
         <v>75</v>
@@ -4464,13 +4464,13 @@
         <v>17</v>
       </c>
       <c r="AQ15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AS15">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AT15">
         <v>9</v>
@@ -4479,13 +4479,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV15">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW15">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX15">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY15">
         <v>9.199999999999999</v>
@@ -4494,7 +4494,7 @@
         <v>18</v>
       </c>
       <c r="BA15">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB15">
         <v>14.5</v>
@@ -4506,25 +4506,25 @@
         <v>28</v>
       </c>
       <c r="BE15">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BF15">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG15">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BH15">
         <v>3.85</v>
       </c>
       <c r="BI15">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ15">
         <v>9.800000000000001</v>
       </c>
       <c r="BK15">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL15">
         <v>1000</v>
@@ -4548,19 +4548,19 @@
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT15">
         <v>9.4</v>
       </c>
       <c r="BU15">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX15">
         <v>50</v>
@@ -4569,7 +4569,7 @@
         <v>12.5</v>
       </c>
       <c r="BZ15">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CA15">
         <v>8.4</v>
@@ -4595,13 +4595,13 @@
         <v>176</v>
       </c>
       <c r="F16">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G16">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H16">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I16">
         <v>8</v>
@@ -4625,28 +4625,28 @@
         <v>1.12</v>
       </c>
       <c r="P16">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q16">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R16">
         <v>1.98</v>
       </c>
       <c r="S16">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="T16">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U16">
         <v>2.52</v>
       </c>
       <c r="V16">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W16">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X16">
         <v>48</v>
@@ -4655,13 +4655,13 @@
         <v>48</v>
       </c>
       <c r="Z16">
-        <v>450</v>
+        <v>170</v>
       </c>
       <c r="AA16">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB16">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC16">
         <v>17</v>
@@ -4679,7 +4679,7 @@
         <v>11</v>
       </c>
       <c r="AH16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI16">
         <v>130</v>
@@ -4688,7 +4688,7 @@
         <v>17</v>
       </c>
       <c r="AK16">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL16">
         <v>34</v>
@@ -4697,7 +4697,7 @@
         <v>260</v>
       </c>
       <c r="AN16">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AO16">
         <v>150</v>
@@ -4712,16 +4712,16 @@
         <v>60</v>
       </c>
       <c r="AS16">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT16">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU16">
         <v>11</v>
       </c>
       <c r="AV16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW16">
         <v>55</v>
@@ -4736,10 +4736,10 @@
         <v>17</v>
       </c>
       <c r="BA16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC16">
         <v>12</v>
@@ -4751,10 +4751,10 @@
         <v>46</v>
       </c>
       <c r="BF16">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BG16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH16">
         <v>5.6</v>
@@ -4766,13 +4766,13 @@
         <v>9.4</v>
       </c>
       <c r="BK16">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN16">
         <v>4.7</v>
@@ -4781,37 +4781,37 @@
         <v>3.8</v>
       </c>
       <c r="BP16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BQ16">
+        <v>5.6</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT16">
+        <v>11.5</v>
+      </c>
+      <c r="BU16">
+        <v>7</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>13</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>12.5</v>
+      </c>
+      <c r="BZ16">
         <v>8.4</v>
-      </c>
-      <c r="BQ16">
-        <v>5.7</v>
-      </c>
-      <c r="BR16">
-        <v>970</v>
-      </c>
-      <c r="BS16">
-        <v>8.6</v>
-      </c>
-      <c r="BT16">
-        <v>11</v>
-      </c>
-      <c r="BU16">
-        <v>6.6</v>
-      </c>
-      <c r="BV16">
-        <v>1000</v>
-      </c>
-      <c r="BW16">
-        <v>12.5</v>
-      </c>
-      <c r="BX16">
-        <v>1000</v>
-      </c>
-      <c r="BY16">
-        <v>12</v>
-      </c>
-      <c r="BZ16">
-        <v>8.6</v>
       </c>
       <c r="CA16">
         <v>5.7</v>
@@ -4846,7 +4846,7 @@
         <v>2.74</v>
       </c>
       <c r="I17">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J17">
         <v>3.25</v>
@@ -4867,16 +4867,16 @@
         <v>1.45</v>
       </c>
       <c r="P17">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q17">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R17">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S17">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T17">
         <v>1.94</v>
@@ -4891,40 +4891,40 @@
         <v>1.49</v>
       </c>
       <c r="X17">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y17">
         <v>9.6</v>
       </c>
       <c r="Z17">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AA17">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AB17">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC17">
         <v>7.4</v>
       </c>
       <c r="AD17">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE17">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="AF17">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG17">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH17">
         <v>23</v>
       </c>
       <c r="AI17">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ17">
         <v>55</v>
@@ -4939,70 +4939,70 @@
         <v>580</v>
       </c>
       <c r="AN17">
-        <v>600</v>
+        <v>42</v>
       </c>
       <c r="AO17">
-        <v>600</v>
+        <v>36</v>
       </c>
       <c r="AP17">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ17">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR17">
         <v>15.5</v>
       </c>
       <c r="AS17">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="AT17">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU17">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV17">
         <v>11</v>
       </c>
       <c r="AW17">
+        <v>32</v>
+      </c>
+      <c r="AX17">
+        <v>17</v>
+      </c>
+      <c r="AY17">
+        <v>12</v>
+      </c>
+      <c r="AZ17">
+        <v>18.5</v>
+      </c>
+      <c r="BA17">
+        <v>46</v>
+      </c>
+      <c r="BB17">
+        <v>44</v>
+      </c>
+      <c r="BC17">
+        <v>34</v>
+      </c>
+      <c r="BD17">
+        <v>48</v>
+      </c>
+      <c r="BE17">
         <v>16.5</v>
       </c>
-      <c r="AX17">
-        <v>16.5</v>
-      </c>
-      <c r="AY17">
-        <v>11.5</v>
-      </c>
-      <c r="AZ17">
-        <v>17.5</v>
-      </c>
-      <c r="BA17">
-        <v>23</v>
-      </c>
-      <c r="BB17">
-        <v>20</v>
-      </c>
-      <c r="BC17">
-        <v>16.5</v>
-      </c>
-      <c r="BD17">
-        <v>23</v>
-      </c>
-      <c r="BE17">
-        <v>8.4</v>
-      </c>
       <c r="BF17">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="BG17">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BH17">
         <v>2.96</v>
       </c>
       <c r="BI17">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ17">
         <v>10.5</v>
@@ -5014,7 +5014,7 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN17">
         <v>5.9</v>
@@ -5026,16 +5026,16 @@
         <v>25</v>
       </c>
       <c r="BQ17">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT17">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU17">
         <v>4.5</v>
@@ -5044,13 +5044,13 @@
         <v>23</v>
       </c>
       <c r="BW17">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX17">
         <v>40</v>
       </c>
       <c r="BY17">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -5079,22 +5079,22 @@
         <v>178</v>
       </c>
       <c r="F18">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G18">
         <v>3.05</v>
       </c>
       <c r="H18">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I18">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J18">
         <v>3.8</v>
       </c>
       <c r="K18">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L18">
         <v>1.29</v>
@@ -5103,13 +5103,13 @@
         <v>1.04</v>
       </c>
       <c r="N18">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O18">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P18">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q18">
         <v>1.58</v>
@@ -5118,25 +5118,25 @@
         <v>1.65</v>
       </c>
       <c r="S18">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T18">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="U18">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="V18">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W18">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X18">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y18">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z18">
         <v>21</v>
@@ -5148,7 +5148,7 @@
         <v>20</v>
       </c>
       <c r="AC18">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD18">
         <v>12.5</v>
@@ -5157,10 +5157,10 @@
         <v>26</v>
       </c>
       <c r="AF18">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG18">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH18">
         <v>15</v>
@@ -5169,19 +5169,19 @@
         <v>32</v>
       </c>
       <c r="AJ18">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK18">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL18">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM18">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN18">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO18">
         <v>14</v>
@@ -5193,52 +5193,52 @@
         <v>14</v>
       </c>
       <c r="AR18">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS18">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT18">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AU18">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV18">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW18">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX18">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY18">
+        <v>11.5</v>
+      </c>
+      <c r="AZ18">
         <v>12</v>
       </c>
-      <c r="AZ18">
-        <v>12.5</v>
-      </c>
       <c r="BA18">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB18">
         <v>36</v>
       </c>
       <c r="BC18">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BD18">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE18">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BF18">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG18">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH18">
         <v>4.4</v>
@@ -5321,64 +5321,64 @@
         <v>179</v>
       </c>
       <c r="F19">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G19">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H19">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="I19">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J19">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K19">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L19">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M19">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N19">
         <v>4.5</v>
       </c>
       <c r="O19">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P19">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="Q19">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="R19">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S19">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T19">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="U19">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="V19">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W19">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="X19">
         <v>19.5</v>
       </c>
       <c r="Y19">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z19">
         <v>26</v>
@@ -5390,16 +5390,16 @@
         <v>13.5</v>
       </c>
       <c r="AC19">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD19">
         <v>16</v>
       </c>
       <c r="AE19">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF19">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG19">
         <v>13</v>
@@ -5411,16 +5411,16 @@
         <v>55</v>
       </c>
       <c r="AJ19">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK19">
         <v>27</v>
       </c>
       <c r="AL19">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AM19">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AN19">
         <v>18</v>
@@ -5444,10 +5444,10 @@
         <v>11</v>
       </c>
       <c r="AU19">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV19">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW19">
         <v>26</v>
@@ -5456,10 +5456,10 @@
         <v>15.5</v>
       </c>
       <c r="AY19">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA19">
         <v>30</v>
@@ -5471,7 +5471,7 @@
         <v>21</v>
       </c>
       <c r="BD19">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BE19">
         <v>55</v>
@@ -5480,40 +5480,40 @@
         <v>14</v>
       </c>
       <c r="BG19">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH19">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI19">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ19">
         <v>9</v>
       </c>
       <c r="BK19">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN19">
         <v>5.5</v>
       </c>
       <c r="BO19">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP19">
         <v>17</v>
       </c>
       <c r="BQ19">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="BR19">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS19">
         <v>10.5</v>
@@ -5525,10 +5525,10 @@
         <v>5</v>
       </c>
       <c r="BV19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW19">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX19">
         <v>1000</v>
@@ -5563,16 +5563,16 @@
         <v>180</v>
       </c>
       <c r="F20">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="G20">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H20">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I20">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>4.7</v>
@@ -5587,49 +5587,49 @@
         <v>1.02</v>
       </c>
       <c r="N20">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O20">
         <v>1.13</v>
       </c>
       <c r="P20">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q20">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R20">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S20">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T20">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="U20">
         <v>2.84</v>
       </c>
       <c r="V20">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W20">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X20">
         <v>40</v>
       </c>
       <c r="Y20">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Z20">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AA20">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AB20">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC20">
         <v>13</v>
@@ -5638,10 +5638,10 @@
         <v>20</v>
       </c>
       <c r="AE20">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AF20">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG20">
         <v>12</v>
@@ -5656,10 +5656,10 @@
         <v>21</v>
       </c>
       <c r="AK20">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL20">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM20">
         <v>50</v>
@@ -5668,7 +5668,7 @@
         <v>5.7</v>
       </c>
       <c r="AO20">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP20">
         <v>29</v>
@@ -5677,10 +5677,10 @@
         <v>26</v>
       </c>
       <c r="AR20">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AS20">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT20">
         <v>14.5</v>
@@ -5689,13 +5689,13 @@
         <v>10.5</v>
       </c>
       <c r="AV20">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW20">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX20">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY20">
         <v>9.6</v>
@@ -5707,7 +5707,7 @@
         <v>29</v>
       </c>
       <c r="BB20">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC20">
         <v>13</v>
@@ -5719,16 +5719,16 @@
         <v>40</v>
       </c>
       <c r="BF20">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BG20">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH20">
         <v>5.5</v>
       </c>
       <c r="BI20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ20">
         <v>9</v>
@@ -5737,10 +5737,10 @@
         <v>4.9</v>
       </c>
       <c r="BL20">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM20">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN20">
         <v>5.4</v>
@@ -5752,10 +5752,10 @@
         <v>11</v>
       </c>
       <c r="BQ20">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR20">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BS20">
         <v>6.8</v>
@@ -5770,19 +5770,19 @@
         <v>29</v>
       </c>
       <c r="BW20">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX20">
         <v>30</v>
       </c>
       <c r="BY20">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ20">
         <v>11</v>
       </c>
       <c r="CA20">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="CB20" t="s">
         <v>199</v>
@@ -5805,7 +5805,7 @@
         <v>181</v>
       </c>
       <c r="F21">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G21">
         <v>1.99</v>
@@ -5970,61 +5970,61 @@
         <v>2.64</v>
       </c>
       <c r="BI21">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="BJ21">
         <v>14</v>
       </c>
       <c r="BK21">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BN21">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO21">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="BP21">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BQ21">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BT21">
         <v>9.800000000000001</v>
       </c>
       <c r="BU21">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
+        <v>11.5</v>
+      </c>
+      <c r="BZ21">
+        <v>1000</v>
+      </c>
+      <c r="CA21">
         <v>10</v>
-      </c>
-      <c r="BZ21">
-        <v>1000</v>
-      </c>
-      <c r="CA21">
-        <v>9</v>
       </c>
       <c r="CB21" t="s">
         <v>199</v>
@@ -6047,7 +6047,7 @@
         <v>182</v>
       </c>
       <c r="F22">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G22">
         <v>3.2</v>
@@ -6068,10 +6068,10 @@
         <v>1.64</v>
       </c>
       <c r="M22">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N22">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="O22">
         <v>1.62</v>
@@ -6083,13 +6083,13 @@
         <v>2.78</v>
       </c>
       <c r="R22">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S22">
         <v>5.9</v>
       </c>
       <c r="T22">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U22">
         <v>1.69</v>
@@ -6131,7 +6131,7 @@
         <v>15</v>
       </c>
       <c r="AH22">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI22">
         <v>500</v>
@@ -6149,7 +6149,7 @@
         <v>500</v>
       </c>
       <c r="AN22">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="AO22">
         <v>600</v>
@@ -6167,46 +6167,46 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AT22">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU22">
         <v>5.9</v>
       </c>
       <c r="AV22">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW22">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="AX22">
         <v>14.5</v>
       </c>
       <c r="AY22">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ22">
         <v>20</v>
       </c>
       <c r="BA22">
+        <v>8.4</v>
+      </c>
+      <c r="BB22">
+        <v>17.5</v>
+      </c>
+      <c r="BC22">
         <v>7.8</v>
       </c>
-      <c r="BB22">
+      <c r="BD22">
+        <v>8.4</v>
+      </c>
+      <c r="BE22">
+        <v>8</v>
+      </c>
+      <c r="BF22">
+        <v>7.2</v>
+      </c>
+      <c r="BG22">
         <v>7.4</v>
-      </c>
-      <c r="BC22">
-        <v>8</v>
-      </c>
-      <c r="BD22">
-        <v>8</v>
-      </c>
-      <c r="BE22">
-        <v>9</v>
-      </c>
-      <c r="BF22">
-        <v>7.4</v>
-      </c>
-      <c r="BG22">
-        <v>7.6</v>
       </c>
       <c r="BH22">
         <v>2.66</v>
@@ -6218,7 +6218,7 @@
         <v>12.5</v>
       </c>
       <c r="BK22">
-        <v>9.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BL22">
         <v>1000</v>
@@ -6289,16 +6289,16 @@
         <v>183</v>
       </c>
       <c r="F23">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="G23">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H23">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I23">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="J23">
         <v>2.58</v>
@@ -6307,19 +6307,19 @@
         <v>2.92</v>
       </c>
       <c r="L23">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="M23">
         <v>1.18</v>
       </c>
       <c r="N23">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="O23">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="P23">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="Q23">
         <v>3.25</v>
@@ -6337,19 +6337,19 @@
         <v>1.56</v>
       </c>
       <c r="V23">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="X23">
         <v>6.6</v>
       </c>
       <c r="Y23">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z23">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA23">
         <v>500</v>
@@ -6361,25 +6361,25 @@
         <v>7.4</v>
       </c>
       <c r="AD23">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE23">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AF23">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AG23">
         <v>16</v>
       </c>
       <c r="AH23">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AI23">
         <v>500</v>
       </c>
       <c r="AJ23">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AK23">
         <v>150</v>
@@ -6394,19 +6394,19 @@
         <v>600</v>
       </c>
       <c r="AO23">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="AP23">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AQ23">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="AR23">
         <v>7.6</v>
       </c>
       <c r="AS23">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT23">
         <v>6</v>
@@ -6415,43 +6415,43 @@
         <v>5.9</v>
       </c>
       <c r="AV23">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW23">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX23">
         <v>14</v>
       </c>
       <c r="AY23">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AZ23">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA23">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB23">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC23">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD23">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF23">
+        <v>8.6</v>
+      </c>
+      <c r="BG23">
         <v>8.800000000000001</v>
       </c>
-      <c r="BF23">
-        <v>8</v>
-      </c>
-      <c r="BG23">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BH23">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BI23">
         <v>2</v>
@@ -6466,34 +6466,34 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN23">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BO23">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT23">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU23">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW23">
         <v>8.4</v>
@@ -6508,7 +6508,7 @@
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB23" t="s">
         <v>199</v>
@@ -6531,22 +6531,22 @@
         <v>184</v>
       </c>
       <c r="F24">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="G24">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="H24">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I24">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="J24">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K24">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L24">
         <v>1.4</v>
@@ -6555,7 +6555,7 @@
         <v>1.06</v>
       </c>
       <c r="N24">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O24">
         <v>1.3</v>
@@ -6564,52 +6564,52 @@
         <v>2</v>
       </c>
       <c r="Q24">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R24">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S24">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T24">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U24">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V24">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W24">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X24">
         <v>15.5</v>
       </c>
       <c r="Y24">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z24">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA24">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AB24">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC24">
         <v>9</v>
       </c>
-      <c r="AC24">
-        <v>9.4</v>
-      </c>
       <c r="AD24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE24">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AF24">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG24">
         <v>10</v>
@@ -6621,34 +6621,34 @@
         <v>90</v>
       </c>
       <c r="AJ24">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK24">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AL24">
         <v>38</v>
       </c>
       <c r="AM24">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN24">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO24">
-        <v>700</v>
+        <v>90</v>
       </c>
       <c r="AP24">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ24">
         <v>17.5</v>
       </c>
       <c r="AR24">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AS24">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AT24">
         <v>7.8</v>
@@ -6672,22 +6672,22 @@
         <v>19</v>
       </c>
       <c r="BA24">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB24">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC24">
         <v>15.5</v>
       </c>
       <c r="BD24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE24">
         <v>80</v>
       </c>
       <c r="BF24">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG24">
         <v>55</v>
@@ -6714,7 +6714,7 @@
         <v>4.5</v>
       </c>
       <c r="BO24">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP24">
         <v>12</v>
@@ -6732,7 +6732,7 @@
         <v>9.4</v>
       </c>
       <c r="BU24">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV24">
         <v>1000</v>
@@ -6776,7 +6776,7 @@
         <v>3.3</v>
       </c>
       <c r="G25">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H25">
         <v>2.4</v>
@@ -6785,10 +6785,10 @@
         <v>2.48</v>
       </c>
       <c r="J25">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K25">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L25">
         <v>1.46</v>
@@ -6803,22 +6803,22 @@
         <v>1.38</v>
       </c>
       <c r="P25">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q25">
         <v>2.16</v>
       </c>
       <c r="R25">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S25">
         <v>3.95</v>
       </c>
       <c r="T25">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U25">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V25">
         <v>1.67</v>
@@ -6827,10 +6827,10 @@
         <v>1.4</v>
       </c>
       <c r="X25">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y25">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z25">
         <v>15</v>
@@ -6839,7 +6839,7 @@
         <v>34</v>
       </c>
       <c r="AB25">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC25">
         <v>7.6</v>
@@ -6848,88 +6848,88 @@
         <v>12</v>
       </c>
       <c r="AE25">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AF25">
         <v>23</v>
       </c>
       <c r="AG25">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH25">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI25">
         <v>44</v>
       </c>
       <c r="AJ25">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="AK25">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL25">
         <v>55</v>
       </c>
       <c r="AM25">
-        <v>450</v>
+        <v>130</v>
       </c>
       <c r="AN25">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="AO25">
         <v>24</v>
       </c>
       <c r="AP25">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AQ25">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AR25">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS25">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AT25">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU25">
         <v>6.8</v>
       </c>
       <c r="AV25">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW25">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AX25">
         <v>20</v>
       </c>
       <c r="AY25">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ25">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA25">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BB25">
         <v>42</v>
       </c>
       <c r="BC25">
+        <v>36</v>
+      </c>
+      <c r="BD25">
+        <v>46</v>
+      </c>
+      <c r="BE25">
+        <v>80</v>
+      </c>
+      <c r="BF25">
         <v>30</v>
-      </c>
-      <c r="BD25">
-        <v>38</v>
-      </c>
-      <c r="BE25">
-        <v>29</v>
-      </c>
-      <c r="BF25">
-        <v>29</v>
       </c>
       <c r="BG25">
         <v>21</v>
@@ -7015,220 +7015,220 @@
         <v>186</v>
       </c>
       <c r="F26">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="G26">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="H26">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="J26">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="K26">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L26">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="M26">
         <v>1.03</v>
       </c>
       <c r="N26">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="O26">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P26">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="Q26">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="R26">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="S26">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="T26">
         <v>1.58</v>
       </c>
       <c r="U26">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V26">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="W26">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="X26">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="Y26">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Z26">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AA26">
-        <v>900</v>
+        <v>330</v>
       </c>
       <c r="AB26">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC26">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD26">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE26">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AF26">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG26">
         <v>11.5</v>
       </c>
       <c r="AH26">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI26">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AJ26">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AK26">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AL26">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AM26">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN26">
+        <v>10.5</v>
+      </c>
+      <c r="AO26">
+        <v>250</v>
+      </c>
+      <c r="AP26">
+        <v>18.5</v>
+      </c>
+      <c r="AQ26">
+        <v>16</v>
+      </c>
+      <c r="AR26">
+        <v>7.8</v>
+      </c>
+      <c r="AS26">
+        <v>7.6</v>
+      </c>
+      <c r="AT26">
+        <v>10.5</v>
+      </c>
+      <c r="AU26">
+        <v>8.4</v>
+      </c>
+      <c r="AV26">
+        <v>13.5</v>
+      </c>
+      <c r="AW26">
+        <v>7.2</v>
+      </c>
+      <c r="AX26">
+        <v>12</v>
+      </c>
+      <c r="AY26">
+        <v>9</v>
+      </c>
+      <c r="AZ26">
+        <v>13</v>
+      </c>
+      <c r="BA26">
+        <v>30</v>
+      </c>
+      <c r="BB26">
+        <v>19</v>
+      </c>
+      <c r="BC26">
+        <v>15.5</v>
+      </c>
+      <c r="BD26">
+        <v>17.5</v>
+      </c>
+      <c r="BE26">
+        <v>28</v>
+      </c>
+      <c r="BF26">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG26">
+        <v>7.8</v>
+      </c>
+      <c r="BH26">
+        <v>4.4</v>
+      </c>
+      <c r="BI26">
+        <v>3.6</v>
+      </c>
+      <c r="BJ26">
+        <v>9.4</v>
+      </c>
+      <c r="BK26">
         <v>7.4</v>
       </c>
-      <c r="AO26">
-        <v>48</v>
-      </c>
-      <c r="AP26">
-        <v>22</v>
-      </c>
-      <c r="AQ26">
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>8.4</v>
+      </c>
+      <c r="BN26">
+        <v>5.4</v>
+      </c>
+      <c r="BO26">
+        <v>4.3</v>
+      </c>
+      <c r="BP26">
+        <v>13.5</v>
+      </c>
+      <c r="BQ26">
+        <v>6</v>
+      </c>
+      <c r="BR26">
+        <v>24</v>
+      </c>
+      <c r="BS26">
+        <v>7.4</v>
+      </c>
+      <c r="BT26">
+        <v>8</v>
+      </c>
+      <c r="BU26">
+        <v>6.2</v>
+      </c>
+      <c r="BV26">
+        <v>1000</v>
+      </c>
+      <c r="BW26">
+        <v>7</v>
+      </c>
+      <c r="BX26">
+        <v>1000</v>
+      </c>
+      <c r="BY26">
         <v>7.2</v>
-      </c>
-      <c r="AR26">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS26">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT26">
-        <v>6</v>
-      </c>
-      <c r="AU26">
-        <v>5.3</v>
-      </c>
-      <c r="AV26">
-        <v>6.6</v>
-      </c>
-      <c r="AW26">
-        <v>38</v>
-      </c>
-      <c r="AX26">
-        <v>11.5</v>
-      </c>
-      <c r="AY26">
-        <v>5.4</v>
-      </c>
-      <c r="AZ26">
-        <v>6.2</v>
-      </c>
-      <c r="BA26">
-        <v>32</v>
-      </c>
-      <c r="BB26">
-        <v>6.6</v>
-      </c>
-      <c r="BC26">
-        <v>6.2</v>
-      </c>
-      <c r="BD26">
-        <v>7.4</v>
-      </c>
-      <c r="BE26">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF26">
-        <v>6</v>
-      </c>
-      <c r="BG26">
-        <v>8</v>
-      </c>
-      <c r="BH26">
-        <v>4.6</v>
-      </c>
-      <c r="BI26">
-        <v>3.75</v>
-      </c>
-      <c r="BJ26">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK26">
-        <v>5.2</v>
-      </c>
-      <c r="BL26">
-        <v>1000</v>
-      </c>
-      <c r="BM26">
-        <v>6.6</v>
-      </c>
-      <c r="BN26">
-        <v>5.1</v>
-      </c>
-      <c r="BO26">
-        <v>3.6</v>
-      </c>
-      <c r="BP26">
-        <v>11.5</v>
-      </c>
-      <c r="BQ26">
-        <v>5.9</v>
-      </c>
-      <c r="BR26">
-        <v>21</v>
-      </c>
-      <c r="BS26">
-        <v>7.6</v>
-      </c>
-      <c r="BT26">
-        <v>8.6</v>
-      </c>
-      <c r="BU26">
-        <v>5</v>
-      </c>
-      <c r="BV26">
-        <v>1000</v>
-      </c>
-      <c r="BW26">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX26">
-        <v>36</v>
-      </c>
-      <c r="BY26">
-        <v>9</v>
       </c>
       <c r="BZ26">
         <v>0</v>
@@ -7257,22 +7257,22 @@
         <v>187</v>
       </c>
       <c r="F27">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G27">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="H27">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="I27">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J27">
         <v>4</v>
       </c>
       <c r="K27">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L27">
         <v>1.39</v>
@@ -7284,19 +7284,19 @@
         <v>4.1</v>
       </c>
       <c r="O27">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P27">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q27">
         <v>1.9</v>
       </c>
       <c r="R27">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S27">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T27">
         <v>1.89</v>
@@ -7305,19 +7305,19 @@
         <v>2</v>
       </c>
       <c r="V27">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W27">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="X27">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="Y27">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Z27">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AA27">
         <v>900</v>
@@ -7329,7 +7329,7 @@
         <v>9.4</v>
       </c>
       <c r="AD27">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AE27">
         <v>700</v>
@@ -7341,67 +7341,67 @@
         <v>10.5</v>
       </c>
       <c r="AH27">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AI27">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AJ27">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AK27">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AL27">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AM27">
         <v>700</v>
       </c>
       <c r="AN27">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO27">
         <v>700</v>
       </c>
       <c r="AP27">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AQ27">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR27">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AS27">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT27">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU27">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV27">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="AW27">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AX27">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY27">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ27">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA27">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="BB27">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC27">
         <v>14.5</v>
@@ -7410,73 +7410,73 @@
         <v>30</v>
       </c>
       <c r="BE27">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="BF27">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BG27">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH27">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI27">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BJ27">
         <v>10.5</v>
       </c>
       <c r="BK27">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN27">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO27">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP27">
         <v>11</v>
       </c>
       <c r="BQ27">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
+        <v>11</v>
+      </c>
+      <c r="BT27">
+        <v>9</v>
+      </c>
+      <c r="BU27">
+        <v>6.2</v>
+      </c>
+      <c r="BV27">
+        <v>1000</v>
+      </c>
+      <c r="BW27">
+        <v>14</v>
+      </c>
+      <c r="BX27">
+        <v>1000</v>
+      </c>
+      <c r="BY27">
+        <v>14.5</v>
+      </c>
+      <c r="BZ27">
+        <v>19.5</v>
+      </c>
+      <c r="CA27">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BT27">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU27">
-        <v>5.9</v>
-      </c>
-      <c r="BV27">
-        <v>1000</v>
-      </c>
-      <c r="BW27">
-        <v>12</v>
-      </c>
-      <c r="BX27">
-        <v>1000</v>
-      </c>
-      <c r="BY27">
-        <v>12.5</v>
-      </c>
-      <c r="BZ27">
-        <v>1000</v>
-      </c>
-      <c r="CA27">
-        <v>8.800000000000001</v>
       </c>
       <c r="CB27" t="s">
         <v>199</v>
@@ -7502,7 +7502,7 @@
         <v>1.78</v>
       </c>
       <c r="G28">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H28">
         <v>4.2</v>
@@ -7523,31 +7523,31 @@
         <v>1.02</v>
       </c>
       <c r="N28">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O28">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P28">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Q28">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R28">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="S28">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="T28">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U28">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="V28">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W28">
         <v>2.2</v>
@@ -7559,112 +7559,112 @@
         <v>34</v>
       </c>
       <c r="Z28">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AA28">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AB28">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC28">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD28">
         <v>23</v>
       </c>
       <c r="AE28">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AF28">
         <v>19</v>
       </c>
       <c r="AG28">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH28">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI28">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ28">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK28">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL28">
         <v>24</v>
       </c>
       <c r="AM28">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN28">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AO28">
         <v>32</v>
       </c>
       <c r="AP28">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ28">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AR28">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AS28">
         <v>55</v>
       </c>
       <c r="AT28">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AU28">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AV28">
+        <v>16</v>
+      </c>
+      <c r="AW28">
+        <v>34</v>
+      </c>
+      <c r="AX28">
+        <v>14.5</v>
+      </c>
+      <c r="AY28">
+        <v>10</v>
+      </c>
+      <c r="AZ28">
         <v>13.5</v>
       </c>
-      <c r="AW28">
-        <v>29</v>
-      </c>
-      <c r="AX28">
-        <v>11.5</v>
-      </c>
-      <c r="AY28">
-        <v>8.4</v>
-      </c>
-      <c r="AZ28">
-        <v>11.5</v>
-      </c>
       <c r="BA28">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BB28">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC28">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD28">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BE28">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF28">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG28">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BH28">
         <v>5.3</v>
       </c>
       <c r="BI28">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BJ28">
         <v>8.6</v>
@@ -7676,7 +7676,7 @@
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>13.5</v>
+        <v>5.2</v>
       </c>
       <c r="BN28">
         <v>5.2</v>
@@ -7688,10 +7688,10 @@
         <v>11</v>
       </c>
       <c r="BQ28">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR28">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
         <v>8.800000000000001</v>
@@ -7703,13 +7703,13 @@
         <v>5.6</v>
       </c>
       <c r="BV28">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
         <v>10.5</v>
       </c>
       <c r="BX28">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
         <v>10.5</v>
@@ -7718,7 +7718,7 @@
         <v>11</v>
       </c>
       <c r="CA28">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="CB28" t="s">
         <v>199</v>
@@ -7741,10 +7741,10 @@
         <v>189</v>
       </c>
       <c r="F29">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G29">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="H29">
         <v>6.8</v>
@@ -7753,7 +7753,7 @@
         <v>7.8</v>
       </c>
       <c r="J29">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K29">
         <v>3.85</v>
@@ -7765,22 +7765,22 @@
         <v>1.11</v>
       </c>
       <c r="N29">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="O29">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P29">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q29">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R29">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S29">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="T29">
         <v>2.34</v>
@@ -7789,19 +7789,19 @@
         <v>1.65</v>
       </c>
       <c r="V29">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W29">
         <v>2.34</v>
       </c>
       <c r="X29">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y29">
         <v>20</v>
       </c>
       <c r="Z29">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AA29">
         <v>900</v>
@@ -7825,7 +7825,7 @@
         <v>12.5</v>
       </c>
       <c r="AH29">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AI29">
         <v>700</v>
@@ -7837,7 +7837,7 @@
         <v>23</v>
       </c>
       <c r="AL29">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AM29">
         <v>700</v>
@@ -7852,13 +7852,13 @@
         <v>8.4</v>
       </c>
       <c r="AQ29">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR29">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="AS29">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT29">
         <v>5.3</v>
@@ -7870,7 +7870,7 @@
         <v>23</v>
       </c>
       <c r="AW29">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="AX29">
         <v>7.4</v>
@@ -7879,10 +7879,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ29">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BA29">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="BB29">
         <v>14.5</v>
@@ -7894,13 +7894,13 @@
         <v>36</v>
       </c>
       <c r="BE29">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF29">
         <v>13.5</v>
       </c>
       <c r="BG29">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH29">
         <v>2.86</v>
@@ -7983,85 +7983,85 @@
         <v>190</v>
       </c>
       <c r="F30">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="G30">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="H30">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="I30">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="J30">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K30">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="L30">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M30">
         <v>1.08</v>
       </c>
       <c r="N30">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O30">
         <v>1.38</v>
       </c>
       <c r="P30">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q30">
         <v>2.12</v>
       </c>
       <c r="R30">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S30">
         <v>3.9</v>
       </c>
       <c r="T30">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U30">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V30">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="W30">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X30">
         <v>13.5</v>
       </c>
       <c r="Y30">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z30">
-        <v>12.5</v>
+        <v>500</v>
       </c>
       <c r="AA30">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AB30">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD30">
         <v>11</v>
       </c>
       <c r="AE30">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF30">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AG30">
         <v>26</v>
@@ -8085,70 +8085,70 @@
         <v>580</v>
       </c>
       <c r="AN30">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AO30">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="AP30">
+        <v>11.5</v>
+      </c>
+      <c r="AQ30">
+        <v>7.8</v>
+      </c>
+      <c r="AR30">
         <v>11</v>
       </c>
-      <c r="AQ30">
-        <v>7.2</v>
-      </c>
-      <c r="AR30">
-        <v>10</v>
-      </c>
       <c r="AS30">
+        <v>12</v>
+      </c>
+      <c r="AT30">
         <v>11.5</v>
-      </c>
-      <c r="AT30">
-        <v>12.5</v>
       </c>
       <c r="AU30">
         <v>6.8</v>
       </c>
       <c r="AV30">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW30">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX30">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY30">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ30">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BA30">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="BB30">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="BC30">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BD30">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="BE30">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="BF30">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG30">
-        <v>14</v>
+        <v>5.9</v>
       </c>
       <c r="BH30">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI30">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="BJ30">
         <v>9.800000000000001</v>
@@ -8160,10 +8160,10 @@
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="BN30">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BO30">
         <v>5.7</v>
@@ -8172,25 +8172,25 @@
         <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BT30">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BU30">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BV30">
         <v>1000</v>
       </c>
       <c r="BW30">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX30">
         <v>1000</v>
@@ -8228,7 +8228,7 @@
         <v>1.3</v>
       </c>
       <c r="G31">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="H31">
         <v>11.5</v>
@@ -8252,22 +8252,22 @@
         <v>4.5</v>
       </c>
       <c r="O31">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P31">
         <v>2.36</v>
       </c>
       <c r="Q31">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="R31">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S31">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="T31">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U31">
         <v>1.81</v>
@@ -8276,7 +8276,7 @@
         <v>1.08</v>
       </c>
       <c r="W31">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="X31">
         <v>29</v>
@@ -8467,22 +8467,22 @@
         <v>192</v>
       </c>
       <c r="F32">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="G32">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H32">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I32">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J32">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K32">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L32">
         <v>1.46</v>
@@ -8506,7 +8506,7 @@
         <v>1.3</v>
       </c>
       <c r="S32">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T32">
         <v>1.92</v>
@@ -8515,10 +8515,10 @@
         <v>1.96</v>
       </c>
       <c r="V32">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W32">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X32">
         <v>13</v>
@@ -8533,7 +8533,7 @@
         <v>900</v>
       </c>
       <c r="AB32">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC32">
         <v>8</v>
@@ -8718,10 +8718,10 @@
         <v>3.6</v>
       </c>
       <c r="I33">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J33">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K33">
         <v>3.35</v>
@@ -8736,13 +8736,13 @@
         <v>3.1</v>
       </c>
       <c r="O33">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P33">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q33">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R33">
         <v>1.26</v>
@@ -8757,10 +8757,10 @@
         <v>1.92</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W33">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X33">
         <v>11</v>
@@ -8781,7 +8781,7 @@
         <v>7.6</v>
       </c>
       <c r="AD33">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE33">
         <v>55</v>
@@ -8817,7 +8817,7 @@
         <v>500</v>
       </c>
       <c r="AP33">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ33">
         <v>10</v>
@@ -8862,7 +8862,7 @@
         <v>42</v>
       </c>
       <c r="BE33">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF33">
         <v>22</v>
@@ -8904,7 +8904,7 @@
         <v>38</v>
       </c>
       <c r="BS33">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT33">
         <v>7</v>
@@ -8928,7 +8928,7 @@
         <v>1000</v>
       </c>
       <c r="CA33">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB33" t="s">
         <v>199</v>
@@ -8951,13 +8951,13 @@
         <v>194</v>
       </c>
       <c r="F34">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G34">
         <v>2.06</v>
       </c>
       <c r="H34">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I34">
         <v>4.8</v>
@@ -8975,22 +8975,22 @@
         <v>1.12</v>
       </c>
       <c r="N34">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O34">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P34">
         <v>1.55</v>
       </c>
       <c r="Q34">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R34">
         <v>1.2</v>
       </c>
       <c r="S34">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T34">
         <v>2.2</v>
@@ -8999,7 +8999,7 @@
         <v>1.75</v>
       </c>
       <c r="V34">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W34">
         <v>1.94</v>
@@ -9017,7 +9017,7 @@
         <v>130</v>
       </c>
       <c r="AB34">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC34">
         <v>7.6</v>
@@ -9062,25 +9062,25 @@
         <v>7.8</v>
       </c>
       <c r="AQ34">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR34">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS34">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT34">
         <v>5.9</v>
       </c>
       <c r="AU34">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV34">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW34">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX34">
         <v>9.199999999999999</v>
@@ -9092,10 +9092,10 @@
         <v>23</v>
       </c>
       <c r="BA34">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB34">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC34">
         <v>23</v>
@@ -9104,31 +9104,31 @@
         <v>50</v>
       </c>
       <c r="BE34">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BF34">
         <v>21</v>
       </c>
       <c r="BG34">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH34">
         <v>2.72</v>
       </c>
       <c r="BI34">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BJ34">
         <v>12</v>
       </c>
       <c r="BK34">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BN34">
         <v>4.5</v>
@@ -9137,7 +9137,7 @@
         <v>4</v>
       </c>
       <c r="BP34">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ34">
         <v>8.6</v>
@@ -9146,7 +9146,7 @@
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT34">
         <v>8</v>
@@ -9193,58 +9193,58 @@
         <v>195</v>
       </c>
       <c r="F35">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G35">
         <v>2.32</v>
       </c>
       <c r="H35">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I35">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="J35">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K35">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L35">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M35">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N35">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O35">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P35">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="Q35">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="R35">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S35">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T35">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="U35">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="V35">
         <v>1.37</v>
       </c>
       <c r="W35">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X35">
         <v>18</v>
@@ -9256,19 +9256,19 @@
         <v>30</v>
       </c>
       <c r="AA35">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AB35">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC35">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD35">
         <v>18</v>
       </c>
       <c r="AE35">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF35">
         <v>17.5</v>
@@ -9277,142 +9277,142 @@
         <v>13.5</v>
       </c>
       <c r="AH35">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI35">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ35">
         <v>34</v>
       </c>
       <c r="AK35">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL35">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM35">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN35">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO35">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AP35">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ35">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR35">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AS35">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AT35">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU35">
         <v>6.8</v>
       </c>
       <c r="AV35">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AW35">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AX35">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AY35">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ35">
+        <v>4.4</v>
+      </c>
+      <c r="BA35">
+        <v>5.1</v>
+      </c>
+      <c r="BB35">
+        <v>4.8</v>
+      </c>
+      <c r="BC35">
+        <v>4.6</v>
+      </c>
+      <c r="BD35">
+        <v>4.9</v>
+      </c>
+      <c r="BE35">
+        <v>5.3</v>
+      </c>
+      <c r="BF35">
         <v>12.5</v>
       </c>
-      <c r="BA35">
-        <v>4.7</v>
-      </c>
-      <c r="BB35">
-        <v>21</v>
-      </c>
-      <c r="BC35">
-        <v>4.3</v>
-      </c>
-      <c r="BD35">
-        <v>4.6</v>
-      </c>
-      <c r="BE35">
+      <c r="BG35">
         <v>4.9</v>
       </c>
-      <c r="BF35">
-        <v>4.1</v>
-      </c>
-      <c r="BG35">
-        <v>4.6</v>
-      </c>
       <c r="BH35">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BI35">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="BJ35">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK35">
+        <v>7</v>
+      </c>
+      <c r="BL35">
+        <v>1000</v>
+      </c>
+      <c r="BM35">
+        <v>9.6</v>
+      </c>
+      <c r="BN35">
+        <v>5.4</v>
+      </c>
+      <c r="BO35">
+        <v>4.5</v>
+      </c>
+      <c r="BP35">
+        <v>16.5</v>
+      </c>
+      <c r="BQ35">
+        <v>6.4</v>
+      </c>
+      <c r="BR35">
+        <v>28</v>
+      </c>
+      <c r="BS35">
+        <v>7.6</v>
+      </c>
+      <c r="BT35">
         <v>7.2</v>
-      </c>
-      <c r="BL35">
-        <v>1000</v>
-      </c>
-      <c r="BM35">
-        <v>10</v>
-      </c>
-      <c r="BN35">
-        <v>5.3</v>
-      </c>
-      <c r="BO35">
-        <v>4.4</v>
-      </c>
-      <c r="BP35">
-        <v>17</v>
-      </c>
-      <c r="BQ35">
-        <v>6.6</v>
-      </c>
-      <c r="BR35">
-        <v>30</v>
-      </c>
-      <c r="BS35">
-        <v>8</v>
-      </c>
-      <c r="BT35">
-        <v>7</v>
       </c>
       <c r="BU35">
         <v>5.8</v>
       </c>
       <c r="BV35">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BW35">
+        <v>7.4</v>
+      </c>
+      <c r="BX35">
+        <v>36</v>
+      </c>
+      <c r="BY35">
         <v>8</v>
       </c>
-      <c r="BX35">
-        <v>40</v>
-      </c>
-      <c r="BY35">
-        <v>8.6</v>
-      </c>
       <c r="BZ35">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="CA35">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB35" t="s">
         <v>199</v>
@@ -9435,16 +9435,16 @@
         <v>196</v>
       </c>
       <c r="F36">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="G36">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="H36">
         <v>4.9</v>
       </c>
       <c r="I36">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J36">
         <v>3.5</v>
@@ -9453,7 +9453,7 @@
         <v>3.85</v>
       </c>
       <c r="L36">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M36">
         <v>1.08</v>
@@ -9462,10 +9462,10 @@
         <v>3.3</v>
       </c>
       <c r="O36">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P36">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q36">
         <v>2.16</v>
@@ -9474,19 +9474,19 @@
         <v>1.29</v>
       </c>
       <c r="S36">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T36">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U36">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V36">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W36">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X36">
         <v>14</v>
@@ -9537,7 +9537,7 @@
         <v>140</v>
       </c>
       <c r="AN36">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO36">
         <v>110</v>
@@ -9549,10 +9549,10 @@
         <v>12</v>
       </c>
       <c r="AR36">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS36">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT36">
         <v>6.8</v>
@@ -9564,7 +9564,7 @@
         <v>16</v>
       </c>
       <c r="AW36">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX36">
         <v>9.4</v>
@@ -9576,7 +9576,7 @@
         <v>18.5</v>
       </c>
       <c r="BA36">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB36">
         <v>15.5</v>
@@ -9585,16 +9585,16 @@
         <v>16</v>
       </c>
       <c r="BD36">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE36">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF36">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG36">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH36">
         <v>3.2</v>
@@ -9683,7 +9683,7 @@
         <v>3.5</v>
       </c>
       <c r="H37">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="I37">
         <v>2.62</v>
@@ -9707,7 +9707,7 @@
         <v>1.41</v>
       </c>
       <c r="P37">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q37">
         <v>2.28</v>
@@ -9725,10 +9725,10 @@
         <v>1.94</v>
       </c>
       <c r="V37">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W37">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X37">
         <v>12.5</v>
@@ -9869,7 +9869,7 @@
         <v>7.8</v>
       </c>
       <c r="BR37">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS37">
         <v>8.6</v>
@@ -9919,19 +9919,19 @@
         <v>198</v>
       </c>
       <c r="F38">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G38">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="H38">
         <v>3.25</v>
       </c>
       <c r="I38">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J38">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K38">
         <v>3.5</v>
@@ -9949,7 +9949,7 @@
         <v>1.4</v>
       </c>
       <c r="P38">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="Q38">
         <v>2.14</v>
@@ -9967,16 +9967,16 @@
         <v>2.04</v>
       </c>
       <c r="V38">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W38">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="X38">
         <v>14.5</v>
       </c>
       <c r="Y38">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z38">
         <v>24</v>
@@ -9985,7 +9985,7 @@
         <v>75</v>
       </c>
       <c r="AB38">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AC38">
         <v>7.6</v>
@@ -10030,13 +10030,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ38">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR38">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AS38">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AT38">
         <v>8</v>
@@ -10048,7 +10048,7 @@
         <v>12.5</v>
       </c>
       <c r="AW38">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AX38">
         <v>13</v>
@@ -10060,25 +10060,25 @@
         <v>16</v>
       </c>
       <c r="BA38">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BB38">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BC38">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BD38">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BE38">
+        <v>6.2</v>
+      </c>
+      <c r="BF38">
         <v>5.3</v>
       </c>
-      <c r="BF38">
-        <v>4.7</v>
-      </c>
       <c r="BG38">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BH38">
         <v>3.15</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -613,7 +613,7 @@
     <t>Everton De Vina</t>
   </si>
   <si>
-    <t>2026-07-27 06:02:53</t>
+    <t>2026-07-27 08:10:19</t>
   </si>
 </sst>
 </file>
@@ -1207,226 +1207,226 @@
         <v>162</v>
       </c>
       <c r="F2">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="G2">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>100</v>
       </c>
       <c r="I2">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="J2">
-        <v>3.45</v>
+        <v>60</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>170</v>
       </c>
       <c r="L2">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>1.23</v>
+        <v>6</v>
       </c>
       <c r="S2">
-        <v>4.5</v>
+        <v>1.18</v>
       </c>
       <c r="T2">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U2">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V2">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>2.34</v>
+        <v>60</v>
       </c>
       <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>6.6</v>
+      </c>
+      <c r="AK2">
         <v>11.5</v>
       </c>
-      <c r="Y2">
-        <v>21</v>
-      </c>
-      <c r="Z2">
-        <v>160</v>
-      </c>
-      <c r="AA2">
-        <v>900</v>
-      </c>
-      <c r="AB2">
-        <v>6.6</v>
-      </c>
-      <c r="AC2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD2">
-        <v>34</v>
-      </c>
-      <c r="AE2">
-        <v>700</v>
-      </c>
-      <c r="AF2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG2">
-        <v>11</v>
-      </c>
-      <c r="AH2">
-        <v>36</v>
-      </c>
-      <c r="AI2">
-        <v>700</v>
-      </c>
-      <c r="AJ2">
-        <v>18</v>
-      </c>
-      <c r="AK2">
-        <v>22</v>
-      </c>
       <c r="AL2">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="AM2">
-        <v>580</v>
+        <v>150</v>
       </c>
       <c r="AN2">
-        <v>16</v>
+        <v>1.49</v>
       </c>
       <c r="AO2">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>9</v>
+        <v>250</v>
       </c>
       <c r="AQ2">
-        <v>16</v>
+        <v>250</v>
       </c>
       <c r="AR2">
+        <v>250</v>
+      </c>
+      <c r="AS2">
+        <v>250</v>
+      </c>
+      <c r="AT2">
+        <v>250</v>
+      </c>
+      <c r="AU2">
+        <v>250</v>
+      </c>
+      <c r="AV2">
+        <v>250</v>
+      </c>
+      <c r="AW2">
+        <v>250</v>
+      </c>
+      <c r="AX2">
+        <v>17.5</v>
+      </c>
+      <c r="AY2">
+        <v>17.5</v>
+      </c>
+      <c r="AZ2">
+        <v>17.5</v>
+      </c>
+      <c r="BA2">
+        <v>17.5</v>
+      </c>
+      <c r="BB2">
+        <v>5.6</v>
+      </c>
+      <c r="BC2">
         <v>9.4</v>
       </c>
-      <c r="AS2">
-        <v>9</v>
-      </c>
-      <c r="AT2">
-        <v>5.6</v>
-      </c>
-      <c r="AU2">
-        <v>7.4</v>
-      </c>
-      <c r="AV2">
-        <v>24</v>
-      </c>
-      <c r="AW2">
-        <v>9</v>
-      </c>
-      <c r="AX2">
-        <v>7.4</v>
-      </c>
-      <c r="AY2">
-        <v>8.6</v>
-      </c>
-      <c r="AZ2">
-        <v>22</v>
-      </c>
-      <c r="BA2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB2">
-        <v>14.5</v>
-      </c>
-      <c r="BC2">
-        <v>18</v>
-      </c>
       <c r="BD2">
-        <v>9.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BE2">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="BF2">
-        <v>12.5</v>
+        <v>1.41</v>
       </c>
       <c r="BG2">
-        <v>9</v>
+        <v>150</v>
       </c>
       <c r="BH2">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>199</v>
@@ -1449,22 +1449,22 @@
         <v>163</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="G3">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="H3">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="I3">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="J3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="L3">
         <v>1.21</v>
@@ -1473,7 +1473,7 @@
         <v>1.02</v>
       </c>
       <c r="N3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O3">
         <v>1.12</v>
@@ -1485,22 +1485,22 @@
         <v>1.39</v>
       </c>
       <c r="R3">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="S3">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="T3">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V3">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>44</v>
@@ -1512,49 +1512,49 @@
         <v>11.5</v>
       </c>
       <c r="AA3">
+        <v>12</v>
+      </c>
+      <c r="AB3">
+        <v>65</v>
+      </c>
+      <c r="AC3">
+        <v>17.5</v>
+      </c>
+      <c r="AD3">
         <v>11.5</v>
-      </c>
-      <c r="AB3">
-        <v>70</v>
-      </c>
-      <c r="AC3">
-        <v>18.5</v>
-      </c>
-      <c r="AD3">
-        <v>12</v>
       </c>
       <c r="AE3">
         <v>13</v>
       </c>
       <c r="AF3">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AG3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AH3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AJ3">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="AK3">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AL3">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AM3">
+        <v>110</v>
+      </c>
+      <c r="AN3">
         <v>130</v>
       </c>
-      <c r="AN3">
-        <v>150</v>
-      </c>
       <c r="AO3">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AP3">
         <v>38</v>
@@ -1563,16 +1563,16 @@
         <v>13</v>
       </c>
       <c r="AR3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AU3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AV3">
         <v>10</v>
@@ -1581,34 +1581,34 @@
         <v>11</v>
       </c>
       <c r="AX3">
+        <v>14.5</v>
+      </c>
+      <c r="AY3">
+        <v>38</v>
+      </c>
+      <c r="AZ3">
+        <v>22</v>
+      </c>
+      <c r="BA3">
+        <v>23</v>
+      </c>
+      <c r="BB3">
+        <v>14</v>
+      </c>
+      <c r="BC3">
+        <v>15</v>
+      </c>
+      <c r="BD3">
+        <v>14.5</v>
+      </c>
+      <c r="BE3">
+        <v>14.5</v>
+      </c>
+      <c r="BF3">
         <v>13.5</v>
       </c>
-      <c r="AY3">
-        <v>42</v>
-      </c>
-      <c r="AZ3">
-        <v>24</v>
-      </c>
-      <c r="BA3">
-        <v>24</v>
-      </c>
-      <c r="BB3">
-        <v>4.2</v>
-      </c>
-      <c r="BC3">
-        <v>14</v>
-      </c>
-      <c r="BD3">
-        <v>13.5</v>
-      </c>
-      <c r="BE3">
-        <v>48</v>
-      </c>
-      <c r="BF3">
-        <v>15</v>
-      </c>
       <c r="BG3">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BH3">
         <v>5.6</v>
@@ -1617,52 +1617,52 @@
         <v>4.9</v>
       </c>
       <c r="BJ3">
+        <v>11.5</v>
+      </c>
+      <c r="BK3">
+        <v>6.2</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
         <v>12</v>
       </c>
-      <c r="BK3">
-        <v>6</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>11</v>
-      </c>
       <c r="BN3">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BO3">
         <v>7</v>
       </c>
       <c r="BP3">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="BQ3">
+        <v>11.5</v>
+      </c>
+      <c r="BR3">
+        <v>60</v>
+      </c>
+      <c r="BS3">
         <v>11</v>
-      </c>
-      <c r="BR3">
-        <v>70</v>
-      </c>
-      <c r="BS3">
-        <v>10.5</v>
       </c>
       <c r="BT3">
         <v>4.3</v>
       </c>
       <c r="BU3">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BV3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BW3">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BX3">
         <v>18.5</v>
       </c>
       <c r="BY3">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1691,172 +1691,172 @@
         <v>164</v>
       </c>
       <c r="F4">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="G4">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="H4">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M4">
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O4">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S4">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T4">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U4">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W4">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="X4">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y4">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="Z4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA4">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AB4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AE4">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AF4">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG4">
         <v>11</v>
       </c>
       <c r="AH4">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI4">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ4">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL4">
         <v>32</v>
       </c>
       <c r="AM4">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN4">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AO4">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AP4">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ4">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR4">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS4">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT4">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AU4">
+        <v>8</v>
+      </c>
+      <c r="AV4">
+        <v>15</v>
+      </c>
+      <c r="AW4">
+        <v>8.4</v>
+      </c>
+      <c r="AX4">
+        <v>10.5</v>
+      </c>
+      <c r="AY4">
+        <v>8.6</v>
+      </c>
+      <c r="AZ4">
+        <v>15</v>
+      </c>
+      <c r="BA4">
+        <v>8.4</v>
+      </c>
+      <c r="BB4">
+        <v>17.5</v>
+      </c>
+      <c r="BC4">
+        <v>15.5</v>
+      </c>
+      <c r="BD4">
+        <v>23</v>
+      </c>
+      <c r="BE4">
+        <v>8</v>
+      </c>
+      <c r="BF4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG4">
         <v>7.4</v>
       </c>
-      <c r="AV4">
-        <v>12.5</v>
-      </c>
-      <c r="AW4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX4">
-        <v>12</v>
-      </c>
-      <c r="AY4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ4">
-        <v>14</v>
-      </c>
-      <c r="BA4">
-        <v>12.5</v>
-      </c>
-      <c r="BB4">
-        <v>21</v>
-      </c>
-      <c r="BC4">
-        <v>17.5</v>
-      </c>
-      <c r="BD4">
-        <v>7.8</v>
-      </c>
-      <c r="BE4">
-        <v>9</v>
-      </c>
-      <c r="BF4">
-        <v>10</v>
-      </c>
-      <c r="BG4">
-        <v>8</v>
-      </c>
       <c r="BH4">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI4">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4">
         <v>9.6</v>
@@ -1865,43 +1865,43 @@
         <v>5</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM4">
         <v>9.6</v>
       </c>
       <c r="BN4">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BO4">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BP4">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS4">
         <v>7.4</v>
       </c>
       <c r="BT4">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU4">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV4">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BW4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY4">
         <v>8.199999999999999</v>
@@ -1933,67 +1933,67 @@
         <v>165</v>
       </c>
       <c r="F5">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G5">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="H5">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I5">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K5">
         <v>3.8</v>
       </c>
       <c r="L5">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M5">
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O5">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P5">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q5">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R5">
         <v>1.37</v>
       </c>
       <c r="S5">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="T5">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U5">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V5">
         <v>1.22</v>
       </c>
       <c r="W5">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="X5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y5">
         <v>21</v>
       </c>
       <c r="Z5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA5">
         <v>140</v>
@@ -2014,7 +2014,7 @@
         <v>12</v>
       </c>
       <c r="AG5">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AH5">
         <v>20</v>
@@ -2041,7 +2041,7 @@
         <v>85</v>
       </c>
       <c r="AP5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ5">
         <v>16.5</v>
@@ -2050,22 +2050,22 @@
         <v>34</v>
       </c>
       <c r="AS5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AT5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV5">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AW5">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AX5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY5">
         <v>9</v>
@@ -2080,7 +2080,7 @@
         <v>16.5</v>
       </c>
       <c r="BC5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD5">
         <v>32</v>
@@ -2089,52 +2089,52 @@
         <v>75</v>
       </c>
       <c r="BF5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH5">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="BI5">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="BJ5">
+        <v>10</v>
+      </c>
+      <c r="BK5">
+        <v>7.4</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>15.5</v>
+      </c>
+      <c r="BN5">
+        <v>4.2</v>
+      </c>
+      <c r="BO5">
+        <v>3.8</v>
+      </c>
+      <c r="BP5">
+        <v>11.5</v>
+      </c>
+      <c r="BQ5">
+        <v>6.8</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
         <v>10.5</v>
-      </c>
-      <c r="BK5">
-        <v>6.6</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>16</v>
-      </c>
-      <c r="BN5">
-        <v>4.4</v>
-      </c>
-      <c r="BO5">
-        <v>4</v>
-      </c>
-      <c r="BP5">
-        <v>12</v>
-      </c>
-      <c r="BQ5">
-        <v>7.2</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
-        <v>11</v>
       </c>
       <c r="BT5">
         <v>8.6</v>
       </c>
       <c r="BU5">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BV5">
         <v>1000</v>
@@ -2146,13 +2146,13 @@
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB5" t="s">
         <v>199</v>
@@ -2181,13 +2181,13 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="I6">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="J6">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K6">
         <v>4.2</v>
@@ -2199,43 +2199,43 @@
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O6">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P6">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q6">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R6">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S6">
         <v>3.15</v>
       </c>
       <c r="T6">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U6">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V6">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="W6">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X6">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA6">
         <v>21</v>
@@ -2244,16 +2244,16 @@
         <v>18.5</v>
       </c>
       <c r="AC6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD6">
         <v>10.5</v>
       </c>
       <c r="AE6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AF6">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AG6">
         <v>19</v>
@@ -2262,22 +2262,22 @@
         <v>19.5</v>
       </c>
       <c r="AI6">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ6">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AK6">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AL6">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AM6">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="AN6">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="AO6">
         <v>11.5</v>
@@ -2286,19 +2286,19 @@
         <v>14.5</v>
       </c>
       <c r="AQ6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR6">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS6">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AT6">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AU6">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV6">
         <v>8.800000000000001</v>
@@ -2316,13 +2316,13 @@
         <v>15.5</v>
       </c>
       <c r="BA6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BC6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BD6">
         <v>38</v>
@@ -2331,64 +2331,64 @@
         <v>65</v>
       </c>
       <c r="BF6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG6">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH6">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK6">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN6">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BO6">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BU6">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BV6">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BW6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2417,22 +2417,22 @@
         <v>167</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="G7">
         <v>11</v>
       </c>
       <c r="H7">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="I7">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="J7">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="K7">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L7">
         <v>1.34</v>
@@ -2441,31 +2441,31 @@
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O7">
         <v>1.25</v>
       </c>
       <c r="P7">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q7">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R7">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S7">
         <v>2.96</v>
       </c>
       <c r="T7">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="U7">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="V7">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="W7">
         <v>1.1</v>
@@ -2477,52 +2477,52 @@
         <v>8.6</v>
       </c>
       <c r="Z7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AA7">
+        <v>12.5</v>
+      </c>
+      <c r="AB7">
+        <v>34</v>
+      </c>
+      <c r="AC7">
+        <v>11.5</v>
+      </c>
+      <c r="AD7">
         <v>12</v>
-      </c>
-      <c r="AB7">
-        <v>36</v>
-      </c>
-      <c r="AC7">
-        <v>12.5</v>
-      </c>
-      <c r="AD7">
-        <v>10.5</v>
       </c>
       <c r="AE7">
         <v>15</v>
       </c>
       <c r="AF7">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AG7">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AH7">
         <v>32</v>
       </c>
       <c r="AI7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ7">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="AK7">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AL7">
-        <v>470</v>
+        <v>140</v>
       </c>
       <c r="AM7">
-        <v>180</v>
+        <v>390</v>
       </c>
       <c r="AN7">
         <v>230</v>
       </c>
       <c r="AO7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AP7">
         <v>17</v>
@@ -2531,112 +2531,112 @@
         <v>7.8</v>
       </c>
       <c r="AR7">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AU7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV7">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW7">
         <v>13</v>
       </c>
       <c r="AX7">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AY7">
+        <v>30</v>
+      </c>
+      <c r="AZ7">
+        <v>23</v>
+      </c>
+      <c r="BA7">
         <v>32</v>
       </c>
-      <c r="AZ7">
-        <v>26</v>
-      </c>
-      <c r="BA7">
-        <v>26</v>
-      </c>
       <c r="BB7">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="BC7">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="BD7">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="BE7">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="BF7">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BG7">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BH7">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI7">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7">
         <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BO7">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BQ7">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BS7">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT7">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BU7">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="BV7">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BW7">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BX7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY7">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BZ7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CA7">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="CB7" t="s">
         <v>199</v>
@@ -2662,43 +2662,43 @@
         <v>4.4</v>
       </c>
       <c r="G8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H8">
         <v>1.93</v>
       </c>
       <c r="I8">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="J8">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K8">
         <v>3.85</v>
       </c>
       <c r="L8">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M8">
         <v>1.06</v>
       </c>
       <c r="N8">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O8">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P8">
         <v>2.08</v>
       </c>
       <c r="Q8">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R8">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S8">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T8">
         <v>1.74</v>
@@ -2707,7 +2707,7 @@
         <v>2.18</v>
       </c>
       <c r="V8">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W8">
         <v>1.28</v>
@@ -2725,10 +2725,10 @@
         <v>23</v>
       </c>
       <c r="AB8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC8">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD8">
         <v>10.5</v>
@@ -2737,16 +2737,16 @@
         <v>20</v>
       </c>
       <c r="AF8">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AG8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH8">
         <v>17.5</v>
       </c>
       <c r="AI8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ8">
         <v>500</v>
@@ -2755,22 +2755,22 @@
         <v>120</v>
       </c>
       <c r="AL8">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="AM8">
         <v>320</v>
       </c>
       <c r="AN8">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AO8">
         <v>12.5</v>
       </c>
       <c r="AP8">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ8">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR8">
         <v>10.5</v>
@@ -2782,7 +2782,7 @@
         <v>16</v>
       </c>
       <c r="AU8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV8">
         <v>8.800000000000001</v>
@@ -2791,7 +2791,7 @@
         <v>17</v>
       </c>
       <c r="AX8">
-        <v>14.5</v>
+        <v>27</v>
       </c>
       <c r="AY8">
         <v>16.5</v>
@@ -2800,85 +2800,85 @@
         <v>14.5</v>
       </c>
       <c r="BA8">
+        <v>25</v>
+      </c>
+      <c r="BB8">
+        <v>10.5</v>
+      </c>
+      <c r="BC8">
         <v>24</v>
       </c>
-      <c r="BB8">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC8">
-        <v>9.6</v>
-      </c>
       <c r="BD8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BE8">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF8">
-        <v>9.4</v>
+        <v>18.5</v>
       </c>
       <c r="BG8">
         <v>10.5</v>
       </c>
       <c r="BH8">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI8">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="BJ8">
         <v>9.800000000000001</v>
       </c>
       <c r="BK8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN8">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BO8">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT8">
         <v>4.9</v>
       </c>
       <c r="BU8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BW8">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BZ8">
         <v>22</v>
       </c>
       <c r="CA8">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="CB8" t="s">
         <v>199</v>
@@ -2904,19 +2904,19 @@
         <v>2.64</v>
       </c>
       <c r="G9">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H9">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="I9">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="J9">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K9">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L9">
         <v>1.39</v>
@@ -2928,13 +2928,13 @@
         <v>4</v>
       </c>
       <c r="O9">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P9">
         <v>2</v>
       </c>
       <c r="Q9">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R9">
         <v>1.4</v>
@@ -2943,10 +2943,10 @@
         <v>3.35</v>
       </c>
       <c r="T9">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U9">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V9">
         <v>1.54</v>
@@ -2955,7 +2955,7 @@
         <v>1.56</v>
       </c>
       <c r="X9">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Y9">
         <v>12.5</v>
@@ -2976,13 +2976,13 @@
         <v>13</v>
       </c>
       <c r="AE9">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="AF9">
         <v>20</v>
       </c>
       <c r="AG9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH9">
         <v>18</v>
@@ -3009,10 +3009,10 @@
         <v>25</v>
       </c>
       <c r="AP9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ9">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR9">
         <v>15.5</v>
@@ -3027,7 +3027,7 @@
         <v>7</v>
       </c>
       <c r="AV9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW9">
         <v>16</v>
@@ -3042,19 +3042,19 @@
         <v>14.5</v>
       </c>
       <c r="BA9">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="BB9">
         <v>7.8</v>
       </c>
       <c r="BC9">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="BD9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE9">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF9">
         <v>21</v>
@@ -3063,7 +3063,7 @@
         <v>17.5</v>
       </c>
       <c r="BH9">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI9">
         <v>2.8</v>
@@ -3072,49 +3072,49 @@
         <v>9.6</v>
       </c>
       <c r="BK9">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN9">
+        <v>6.2</v>
+      </c>
+      <c r="BO9">
+        <v>5</v>
+      </c>
+      <c r="BP9">
+        <v>22</v>
+      </c>
+      <c r="BQ9">
+        <v>6.8</v>
+      </c>
+      <c r="BR9">
+        <v>34</v>
+      </c>
+      <c r="BS9">
+        <v>7.8</v>
+      </c>
+      <c r="BT9">
         <v>6</v>
       </c>
-      <c r="BO9">
-        <v>5.1</v>
-      </c>
-      <c r="BP9">
-        <v>21</v>
-      </c>
-      <c r="BQ9">
-        <v>7.8</v>
-      </c>
-      <c r="BR9">
-        <v>1000</v>
-      </c>
-      <c r="BS9">
-        <v>9</v>
-      </c>
-      <c r="BT9">
-        <v>5.9</v>
-      </c>
       <c r="BU9">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW9">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BX9">
         <v>34</v>
       </c>
       <c r="BY9">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BZ9">
         <v>0</v>
@@ -3143,22 +3143,22 @@
         <v>170</v>
       </c>
       <c r="F10">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="G10">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="H10">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="I10">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="J10">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K10">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L10">
         <v>1.43</v>
@@ -3179,55 +3179,55 @@
         <v>2.02</v>
       </c>
       <c r="R10">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S10">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T10">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="U10">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V10">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W10">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="X10">
         <v>14.5</v>
       </c>
       <c r="Y10">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z10">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AA10">
         <v>900</v>
       </c>
       <c r="AB10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC10">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD10">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE10">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="AF10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG10">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI10">
         <v>170</v>
@@ -3236,73 +3236,73 @@
         <v>24</v>
       </c>
       <c r="AK10">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL10">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM10">
         <v>580</v>
       </c>
       <c r="AN10">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AO10">
         <v>300</v>
       </c>
       <c r="AP10">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ10">
         <v>13.5</v>
       </c>
       <c r="AR10">
-        <v>28</v>
+        <v>17.5</v>
       </c>
       <c r="AS10">
-        <v>80</v>
+        <v>11.5</v>
       </c>
       <c r="AT10">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU10">
         <v>7.4</v>
       </c>
       <c r="AV10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW10">
-        <v>42</v>
+        <v>10.5</v>
       </c>
       <c r="AX10">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY10">
         <v>9</v>
       </c>
       <c r="AZ10">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA10">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB10">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC10">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE10">
-        <v>28</v>
+        <v>11.5</v>
       </c>
       <c r="BF10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG10">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="BH10">
         <v>3.35</v>
@@ -3314,55 +3314,55 @@
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="BN10">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BO10">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BP10">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BQ10">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BR10">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BS10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT10">
+        <v>8</v>
+      </c>
+      <c r="BU10">
+        <v>6</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>10.5</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
         <v>11</v>
       </c>
-      <c r="BT10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU10">
-        <v>5.7</v>
-      </c>
-      <c r="BV10">
-        <v>60</v>
-      </c>
-      <c r="BW10">
-        <v>13</v>
-      </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
-        <v>13.5</v>
-      </c>
       <c r="BZ10">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB10" t="s">
         <v>199</v>
@@ -3385,19 +3385,19 @@
         <v>171</v>
       </c>
       <c r="F11">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="G11">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="H11">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="I11">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J11">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K11">
         <v>3.8</v>
@@ -3412,34 +3412,34 @@
         <v>4.9</v>
       </c>
       <c r="O11">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P11">
         <v>2.3</v>
       </c>
       <c r="Q11">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R11">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S11">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T11">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U11">
         <v>2.46</v>
       </c>
       <c r="V11">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W11">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="X11">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y11">
         <v>14</v>
@@ -3460,7 +3460,7 @@
         <v>12</v>
       </c>
       <c r="AE11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF11">
         <v>22</v>
@@ -3469,7 +3469,7 @@
         <v>13.5</v>
       </c>
       <c r="AH11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI11">
         <v>34</v>
@@ -3484,22 +3484,22 @@
         <v>38</v>
       </c>
       <c r="AM11">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="AN11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO11">
+        <v>16.5</v>
+      </c>
+      <c r="AP11">
         <v>17</v>
-      </c>
-      <c r="AP11">
-        <v>16.5</v>
       </c>
       <c r="AQ11">
         <v>12</v>
       </c>
       <c r="AR11">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS11">
         <v>27</v>
@@ -3517,7 +3517,7 @@
         <v>21</v>
       </c>
       <c r="AX11">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY11">
         <v>11.5</v>
@@ -3541,46 +3541,46 @@
         <v>50</v>
       </c>
       <c r="BF11">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BG11">
         <v>14.5</v>
       </c>
       <c r="BH11">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BI11">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ11">
         <v>8.800000000000001</v>
       </c>
       <c r="BK11">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO11">
         <v>5.5</v>
       </c>
       <c r="BP11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ11">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS11">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BT11">
         <v>5.8</v>
@@ -3592,19 +3592,19 @@
         <v>18</v>
       </c>
       <c r="BW11">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BX11">
         <v>28</v>
       </c>
       <c r="BY11">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BZ11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA11">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CB11" t="s">
         <v>199</v>
@@ -3627,10 +3627,10 @@
         <v>172</v>
       </c>
       <c r="F12">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G12">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="H12">
         <v>3.75</v>
@@ -3639,49 +3639,49 @@
         <v>3.85</v>
       </c>
       <c r="J12">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K12">
         <v>4.5</v>
       </c>
       <c r="L12">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M12">
         <v>1.03</v>
       </c>
       <c r="N12">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P12">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q12">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R12">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S12">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T12">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="U12">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V12">
         <v>1.35</v>
       </c>
       <c r="W12">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y12">
         <v>25</v>
@@ -3693,40 +3693,40 @@
         <v>70</v>
       </c>
       <c r="AB12">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC12">
         <v>10.5</v>
       </c>
       <c r="AD12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE12">
         <v>36</v>
       </c>
       <c r="AF12">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG12">
         <v>11</v>
       </c>
       <c r="AH12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AI12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ12">
         <v>24</v>
       </c>
       <c r="AK12">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL12">
         <v>23</v>
       </c>
       <c r="AM12">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AN12">
         <v>7.6</v>
@@ -3738,13 +3738,13 @@
         <v>28</v>
       </c>
       <c r="AQ12">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR12">
         <v>32</v>
       </c>
       <c r="AS12">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT12">
         <v>15</v>
@@ -3756,10 +3756,10 @@
         <v>14.5</v>
       </c>
       <c r="AW12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX12">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY12">
         <v>10</v>
@@ -3768,10 +3768,10 @@
         <v>13.5</v>
       </c>
       <c r="BA12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC12">
         <v>15.5</v>
@@ -3789,64 +3789,64 @@
         <v>20</v>
       </c>
       <c r="BH12">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI12">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BJ12">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BK12">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BL12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BM12">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN12">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO12">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BP12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ12">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BR12">
         <v>20</v>
       </c>
       <c r="BS12">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT12">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BU12">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BV12">
         <v>25</v>
       </c>
       <c r="BW12">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX12">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY12">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BZ12">
         <v>13</v>
       </c>
       <c r="CA12">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="CB12" t="s">
         <v>199</v>
@@ -3869,19 +3869,19 @@
         <v>173</v>
       </c>
       <c r="F13">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G13">
         <v>2.12</v>
       </c>
       <c r="H13">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I13">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J13">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K13">
         <v>4.2</v>
@@ -3893,7 +3893,7 @@
         <v>1.05</v>
       </c>
       <c r="N13">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O13">
         <v>1.24</v>
@@ -3905,10 +3905,10 @@
         <v>1.74</v>
       </c>
       <c r="R13">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S13">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="T13">
         <v>1.66</v>
@@ -3920,31 +3920,31 @@
         <v>1.35</v>
       </c>
       <c r="W13">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X13">
         <v>20</v>
       </c>
       <c r="Y13">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA13">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AB13">
         <v>12</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD13">
         <v>16.5</v>
       </c>
       <c r="AE13">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF13">
         <v>15</v>
@@ -3956,16 +3956,16 @@
         <v>17</v>
       </c>
       <c r="AI13">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK13">
         <v>21</v>
       </c>
       <c r="AL13">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM13">
         <v>95</v>
@@ -3974,7 +3974,7 @@
         <v>12.5</v>
       </c>
       <c r="AO13">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP13">
         <v>16</v>
@@ -3983,19 +3983,19 @@
         <v>14</v>
       </c>
       <c r="AR13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS13">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AT13">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU13">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW13">
         <v>29</v>
@@ -4004,7 +4004,7 @@
         <v>12</v>
       </c>
       <c r="AY13">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13">
         <v>14</v>
@@ -4013,13 +4013,13 @@
         <v>36</v>
       </c>
       <c r="BB13">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BC13">
         <v>17</v>
       </c>
       <c r="BD13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE13">
         <v>55</v>
@@ -4028,7 +4028,7 @@
         <v>10</v>
       </c>
       <c r="BG13">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BH13">
         <v>4.1</v>
@@ -4040,55 +4040,55 @@
         <v>9.4</v>
       </c>
       <c r="BK13">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN13">
         <v>5.3</v>
       </c>
       <c r="BO13">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BP13">
         <v>14.5</v>
       </c>
       <c r="BQ13">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR13">
         <v>26</v>
       </c>
       <c r="BS13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT13">
+        <v>7.4</v>
+      </c>
+      <c r="BU13">
+        <v>6</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
         <v>7.6</v>
       </c>
-      <c r="BU13">
-        <v>5.4</v>
-      </c>
-      <c r="BV13">
-        <v>1000</v>
-      </c>
-      <c r="BW13">
-        <v>7.4</v>
-      </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ13">
         <v>20</v>
       </c>
       <c r="CA13">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB13" t="s">
         <v>199</v>
@@ -4111,22 +4111,22 @@
         <v>174</v>
       </c>
       <c r="F14">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="G14">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="H14">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K14">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L14">
         <v>1.34</v>
@@ -4141,49 +4141,49 @@
         <v>1.23</v>
       </c>
       <c r="P14">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q14">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R14">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S14">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T14">
         <v>1.7</v>
       </c>
       <c r="U14">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V14">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W14">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="X14">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AA14">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC14">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD14">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE14">
         <v>55</v>
@@ -4192,121 +4192,121 @@
         <v>12.5</v>
       </c>
       <c r="AG14">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH14">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI14">
         <v>55</v>
       </c>
       <c r="AJ14">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK14">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM14">
         <v>75</v>
       </c>
       <c r="AN14">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AO14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ14">
         <v>20</v>
       </c>
       <c r="AR14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS14">
         <v>85</v>
       </c>
       <c r="AT14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU14">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV14">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AX14">
         <v>11.5</v>
       </c>
       <c r="AY14">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14">
+        <v>16.5</v>
+      </c>
+      <c r="BA14">
+        <v>50</v>
+      </c>
+      <c r="BB14">
+        <v>17</v>
+      </c>
+      <c r="BC14">
         <v>15</v>
       </c>
-      <c r="BA14">
-        <v>46</v>
-      </c>
-      <c r="BB14">
-        <v>17.5</v>
-      </c>
-      <c r="BC14">
-        <v>15.5</v>
-      </c>
       <c r="BD14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE14">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF14">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG14">
         <v>40</v>
       </c>
       <c r="BH14">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BI14">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BJ14">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK14">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL14">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BM14">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BN14">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO14">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ14">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BR14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT14">
         <v>8.199999999999999</v>
@@ -4315,22 +4315,22 @@
         <v>5.7</v>
       </c>
       <c r="BV14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW14">
+        <v>12</v>
+      </c>
+      <c r="BX14">
+        <v>38</v>
+      </c>
+      <c r="BY14">
         <v>12.5</v>
       </c>
-      <c r="BX14">
-        <v>40</v>
-      </c>
-      <c r="BY14">
-        <v>13</v>
-      </c>
       <c r="BZ14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CA14">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="CB14" t="s">
         <v>199</v>
@@ -4353,85 +4353,85 @@
         <v>175</v>
       </c>
       <c r="F15">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="G15">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="H15">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="I15">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="J15">
         <v>4.4</v>
       </c>
       <c r="K15">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L15">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M15">
         <v>1.05</v>
       </c>
       <c r="N15">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O15">
         <v>1.25</v>
       </c>
       <c r="P15">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q15">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R15">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S15">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T15">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U15">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V15">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W15">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="X15">
         <v>19.5</v>
       </c>
       <c r="Y15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z15">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA15">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB15">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC15">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE15">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF15">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG15">
         <v>9.4</v>
@@ -4440,10 +4440,10 @@
         <v>21</v>
       </c>
       <c r="AI15">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AJ15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK15">
         <v>16</v>
@@ -4455,28 +4455,28 @@
         <v>100</v>
       </c>
       <c r="AN15">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AO15">
         <v>75</v>
       </c>
       <c r="AP15">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ15">
         <v>21</v>
       </c>
       <c r="AR15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS15">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AT15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU15">
         <v>9</v>
-      </c>
-      <c r="AU15">
-        <v>8.800000000000001</v>
       </c>
       <c r="AV15">
         <v>20</v>
@@ -4485,19 +4485,19 @@
         <v>65</v>
       </c>
       <c r="AX15">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY15">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ15">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA15">
         <v>60</v>
       </c>
       <c r="BB15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC15">
         <v>14.5</v>
@@ -4506,46 +4506,46 @@
         <v>28</v>
       </c>
       <c r="BE15">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="BF15">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG15">
         <v>55</v>
       </c>
       <c r="BH15">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI15">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BJ15">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK15">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL15">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM15">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN15">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO15">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="BP15">
         <v>10.5</v>
       </c>
       <c r="BQ15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS15">
         <v>10</v>
@@ -4554,25 +4554,25 @@
         <v>9.4</v>
       </c>
       <c r="BU15">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX15">
         <v>50</v>
       </c>
       <c r="BY15">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CA15">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB15" t="s">
         <v>199</v>
@@ -4595,7 +4595,7 @@
         <v>176</v>
       </c>
       <c r="F16">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="G16">
         <v>1.45</v>
@@ -4613,7 +4613,7 @@
         <v>6.2</v>
       </c>
       <c r="L16">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M16">
         <v>1.02</v>
@@ -4631,7 +4631,7 @@
         <v>1.37</v>
       </c>
       <c r="R16">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S16">
         <v>1.95</v>
@@ -4640,16 +4640,16 @@
         <v>1.6</v>
       </c>
       <c r="U16">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V16">
         <v>1.14</v>
       </c>
       <c r="W16">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="X16">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="Y16">
         <v>48</v>
@@ -4658,10 +4658,10 @@
         <v>170</v>
       </c>
       <c r="AA16">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AB16">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC16">
         <v>17</v>
@@ -4670,10 +4670,10 @@
         <v>32</v>
       </c>
       <c r="AE16">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="AF16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG16">
         <v>11</v>
@@ -4709,16 +4709,16 @@
         <v>38</v>
       </c>
       <c r="AR16">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="AS16">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT16">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU16">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AV16">
         <v>24</v>
@@ -4727,13 +4727,13 @@
         <v>55</v>
       </c>
       <c r="AX16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY16">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ16">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA16">
         <v>36</v>
@@ -4748,73 +4748,73 @@
         <v>19</v>
       </c>
       <c r="BE16">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BF16">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BG16">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH16">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BI16">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BJ16">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK16">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN16">
         <v>4.7</v>
       </c>
       <c r="BO16">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BP16">
         <v>8.199999999999999</v>
       </c>
       <c r="BQ16">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT16">
         <v>11.5</v>
       </c>
       <c r="BU16">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ16">
         <v>8.4</v>
       </c>
       <c r="CA16">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="CB16" t="s">
         <v>199</v>
@@ -4840,19 +4840,19 @@
         <v>2.96</v>
       </c>
       <c r="G17">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H17">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I17">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J17">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K17">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L17">
         <v>1.51</v>
@@ -4861,40 +4861,40 @@
         <v>1.1</v>
       </c>
       <c r="N17">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O17">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P17">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Q17">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R17">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S17">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T17">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="U17">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V17">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W17">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X17">
         <v>10.5</v>
       </c>
       <c r="Y17">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z17">
         <v>17</v>
@@ -4903,7 +4903,7 @@
         <v>46</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC17">
         <v>7.4</v>
@@ -4915,16 +4915,16 @@
         <v>36</v>
       </c>
       <c r="AF17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG17">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH17">
         <v>23</v>
       </c>
       <c r="AI17">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ17">
         <v>55</v>
@@ -4963,10 +4963,10 @@
         <v>6.8</v>
       </c>
       <c r="AV17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW17">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AX17">
         <v>17</v>
@@ -4975,7 +4975,7 @@
         <v>12</v>
       </c>
       <c r="AZ17">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BA17">
         <v>46</v>
@@ -4987,22 +4987,22 @@
         <v>34</v>
       </c>
       <c r="BD17">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BE17">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="BF17">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BG17">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH17">
         <v>2.96</v>
       </c>
       <c r="BI17">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="BJ17">
         <v>10.5</v>
@@ -5014,7 +5014,7 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BN17">
         <v>5.9</v>
@@ -5023,34 +5023,34 @@
         <v>4.7</v>
       </c>
       <c r="BP17">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ17">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS17">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BT17">
         <v>5.5</v>
       </c>
       <c r="BU17">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV17">
         <v>23</v>
       </c>
       <c r="BW17">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX17">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY17">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -5079,16 +5079,16 @@
         <v>178</v>
       </c>
       <c r="F18">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G18">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="H18">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="I18">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="J18">
         <v>3.8</v>
@@ -5097,208 +5097,208 @@
         <v>3.9</v>
       </c>
       <c r="L18">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M18">
         <v>1.04</v>
       </c>
       <c r="N18">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O18">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P18">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q18">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R18">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S18">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="T18">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="U18">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="V18">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W18">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="X18">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Y18">
+        <v>15.5</v>
+      </c>
+      <c r="Z18">
         <v>18.5</v>
       </c>
-      <c r="Z18">
-        <v>21</v>
-      </c>
       <c r="AA18">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AB18">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE18">
+        <v>22</v>
+      </c>
+      <c r="AF18">
         <v>26</v>
       </c>
-      <c r="AF18">
-        <v>28</v>
-      </c>
       <c r="AG18">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH18">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI18">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AJ18">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AK18">
         <v>30</v>
       </c>
       <c r="AL18">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM18">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN18">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AO18">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AP18">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AQ18">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR18">
         <v>16.5</v>
       </c>
       <c r="AS18">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AT18">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AU18">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV18">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW18">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX18">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY18">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AZ18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA18">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BB18">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BC18">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BD18">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BE18">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BF18">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG18">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH18">
         <v>4.4</v>
       </c>
       <c r="BI18">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BJ18">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BK18">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BL18">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM18">
-        <v>2.98</v>
+        <v>13</v>
       </c>
       <c r="BN18">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO18">
         <v>5.8</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ18">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS18">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT18">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU18">
         <v>5.2</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW18">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY18">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA18">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB18" t="s">
         <v>199</v>
@@ -5324,19 +5324,19 @@
         <v>2.4</v>
       </c>
       <c r="G19">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H19">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I19">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J19">
         <v>3.55</v>
       </c>
       <c r="K19">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L19">
         <v>1.35</v>
@@ -5345,100 +5345,100 @@
         <v>1.05</v>
       </c>
       <c r="N19">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O19">
         <v>1.25</v>
       </c>
       <c r="P19">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q19">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R19">
         <v>1.48</v>
       </c>
       <c r="S19">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T19">
         <v>1.61</v>
       </c>
       <c r="U19">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V19">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W19">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X19">
         <v>19.5</v>
       </c>
       <c r="Y19">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA19">
         <v>60</v>
       </c>
       <c r="AB19">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC19">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD19">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE19">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF19">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AG19">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH19">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI19">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ19">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK19">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL19">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AM19">
         <v>200</v>
       </c>
       <c r="AN19">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO19">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AP19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ19">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AR19">
         <v>20</v>
       </c>
       <c r="AS19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT19">
         <v>11</v>
@@ -5465,16 +5465,16 @@
         <v>30</v>
       </c>
       <c r="BB19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC19">
         <v>21</v>
       </c>
       <c r="BD19">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BE19">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF19">
         <v>14</v>
@@ -5483,7 +5483,7 @@
         <v>20</v>
       </c>
       <c r="BH19">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI19">
         <v>3.15</v>
@@ -5492,31 +5492,31 @@
         <v>9</v>
       </c>
       <c r="BK19">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BN19">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO19">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BP19">
         <v>17</v>
       </c>
       <c r="BQ19">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR19">
         <v>27</v>
       </c>
       <c r="BS19">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT19">
         <v>6.4</v>
@@ -5528,13 +5528,13 @@
         <v>22</v>
       </c>
       <c r="BW19">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY19">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ19">
         <v>0</v>
@@ -5563,22 +5563,22 @@
         <v>180</v>
       </c>
       <c r="F20">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G20">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="H20">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J20">
         <v>4.7</v>
       </c>
       <c r="K20">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L20">
         <v>1.23</v>
@@ -5593,10 +5593,10 @@
         <v>1.13</v>
       </c>
       <c r="P20">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q20">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R20">
         <v>1.92</v>
@@ -5608,22 +5608,22 @@
         <v>1.48</v>
       </c>
       <c r="U20">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="V20">
         <v>1.25</v>
       </c>
       <c r="W20">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="X20">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="Y20">
         <v>38</v>
       </c>
       <c r="Z20">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AA20">
         <v>500</v>
@@ -5632,10 +5632,10 @@
         <v>17.5</v>
       </c>
       <c r="AC20">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD20">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE20">
         <v>46</v>
@@ -5644,13 +5644,13 @@
         <v>16.5</v>
       </c>
       <c r="AG20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH20">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI20">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AJ20">
         <v>21</v>
@@ -5668,7 +5668,7 @@
         <v>5.7</v>
       </c>
       <c r="AO20">
-        <v>28</v>
+        <v>600</v>
       </c>
       <c r="AP20">
         <v>29</v>
@@ -5683,7 +5683,7 @@
         <v>60</v>
       </c>
       <c r="AT20">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU20">
         <v>10.5</v>
@@ -5695,7 +5695,7 @@
         <v>32</v>
       </c>
       <c r="AX20">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY20">
         <v>9.6</v>
@@ -5713,16 +5713,16 @@
         <v>13</v>
       </c>
       <c r="BD20">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BE20">
         <v>40</v>
       </c>
       <c r="BF20">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG20">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BH20">
         <v>5.5</v>
@@ -5734,55 +5734,55 @@
         <v>9</v>
       </c>
       <c r="BK20">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BL20">
         <v>65</v>
       </c>
       <c r="BM20">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN20">
         <v>5.4</v>
       </c>
       <c r="BO20">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BP20">
         <v>11</v>
       </c>
       <c r="BQ20">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BR20">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BS20">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BT20">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU20">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV20">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BW20">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BX20">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY20">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ20">
         <v>11</v>
       </c>
       <c r="CA20">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="CB20" t="s">
         <v>199</v>
@@ -5817,22 +5817,22 @@
         <v>7</v>
       </c>
       <c r="J21">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K21">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L21">
         <v>1.6</v>
       </c>
       <c r="M21">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N21">
         <v>2.3</v>
       </c>
       <c r="O21">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P21">
         <v>1.43</v>
@@ -5850,7 +5850,7 @@
         <v>2.42</v>
       </c>
       <c r="U21">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V21">
         <v>1.16</v>
@@ -5886,7 +5886,7 @@
         <v>9.6</v>
       </c>
       <c r="AG21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH21">
         <v>85</v>
@@ -5907,7 +5907,7 @@
         <v>500</v>
       </c>
       <c r="AN21">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AO21">
         <v>700</v>
@@ -5919,13 +5919,13 @@
         <v>11.5</v>
       </c>
       <c r="AR21">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AS21">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AT21">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="AU21">
         <v>6.8</v>
@@ -5934,97 +5934,97 @@
         <v>13</v>
       </c>
       <c r="AW21">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AX21">
         <v>4.4</v>
       </c>
       <c r="AY21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ21">
+        <v>19.5</v>
+      </c>
+      <c r="BA21">
         <v>7</v>
       </c>
-      <c r="AZ21">
-        <v>19</v>
-      </c>
-      <c r="BA21">
-        <v>7.6</v>
-      </c>
       <c r="BB21">
+        <v>18.5</v>
+      </c>
+      <c r="BC21">
         <v>5.9</v>
-      </c>
-      <c r="BC21">
-        <v>20</v>
       </c>
       <c r="BD21">
         <v>7.2</v>
       </c>
       <c r="BE21">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF21">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BG21">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH21">
         <v>2.64</v>
       </c>
       <c r="BI21">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="BJ21">
         <v>14</v>
       </c>
       <c r="BK21">
+        <v>6.2</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>10.5</v>
+      </c>
+      <c r="BN21">
+        <v>4.3</v>
+      </c>
+      <c r="BO21">
+        <v>3.55</v>
+      </c>
+      <c r="BP21">
+        <v>16.5</v>
+      </c>
+      <c r="BQ21">
         <v>6.6</v>
       </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
-        <v>12</v>
-      </c>
-      <c r="BN21">
-        <v>4.2</v>
-      </c>
-      <c r="BO21">
-        <v>3.6</v>
-      </c>
-      <c r="BP21">
-        <v>15.5</v>
-      </c>
-      <c r="BQ21">
-        <v>7</v>
-      </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BT21">
         <v>9.800000000000001</v>
       </c>
       <c r="BU21">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
       </c>
       <c r="CA21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CB21" t="s">
         <v>199</v>
@@ -6047,25 +6047,25 @@
         <v>182</v>
       </c>
       <c r="F22">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="G22">
         <v>3.2</v>
       </c>
       <c r="H22">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="I22">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="J22">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="K22">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L22">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M22">
         <v>1.15</v>
@@ -6074,10 +6074,10 @@
         <v>2.34</v>
       </c>
       <c r="O22">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="P22">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="Q22">
         <v>2.78</v>
@@ -6086,7 +6086,7 @@
         <v>1.16</v>
       </c>
       <c r="S22">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>2.14</v>
@@ -6095,10 +6095,10 @@
         <v>1.69</v>
       </c>
       <c r="V22">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X22">
         <v>8</v>
@@ -6107,10 +6107,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z22">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA22">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB22">
         <v>8.800000000000001</v>
@@ -6122,22 +6122,22 @@
         <v>15.5</v>
       </c>
       <c r="AE22">
+        <v>95</v>
+      </c>
+      <c r="AF22">
+        <v>19</v>
+      </c>
+      <c r="AG22">
+        <v>15.5</v>
+      </c>
+      <c r="AH22">
         <v>500</v>
-      </c>
-      <c r="AF22">
-        <v>18.5</v>
-      </c>
-      <c r="AG22">
-        <v>15</v>
-      </c>
-      <c r="AH22">
-        <v>30</v>
       </c>
       <c r="AI22">
         <v>500</v>
       </c>
       <c r="AJ22">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="AK22">
         <v>500</v>
@@ -6155,70 +6155,70 @@
         <v>600</v>
       </c>
       <c r="AP22">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ22">
         <v>7</v>
       </c>
       <c r="AR22">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS22">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AT22">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU22">
         <v>5.9</v>
       </c>
       <c r="AV22">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW22">
-        <v>36</v>
+        <v>19.5</v>
       </c>
       <c r="AX22">
         <v>14.5</v>
       </c>
       <c r="AY22">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ22">
         <v>20</v>
       </c>
       <c r="BA22">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BB22">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="BC22">
         <v>7.8</v>
       </c>
       <c r="BD22">
+        <v>7.8</v>
+      </c>
+      <c r="BE22">
         <v>8.4</v>
       </c>
-      <c r="BE22">
-        <v>8</v>
-      </c>
       <c r="BF22">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG22">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH22">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BI22">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BJ22">
         <v>12.5</v>
       </c>
       <c r="BK22">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL22">
         <v>1000</v>
@@ -6227,10 +6227,10 @@
         <v>10</v>
       </c>
       <c r="BN22">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO22">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BP22">
         <v>1000</v>
@@ -6248,10 +6248,10 @@
         <v>6.2</v>
       </c>
       <c r="BU22">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BV22">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
         <v>7.8</v>
@@ -6266,7 +6266,7 @@
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB22" t="s">
         <v>199</v>
@@ -6289,40 +6289,40 @@
         <v>183</v>
       </c>
       <c r="F23">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="G23">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="I23">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J23">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="K23">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="L23">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="M23">
         <v>1.18</v>
       </c>
       <c r="N23">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="O23">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="P23">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="Q23">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R23">
         <v>1.12</v>
@@ -6331,49 +6331,49 @@
         <v>7.6</v>
       </c>
       <c r="T23">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U23">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V23">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W23">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="X23">
         <v>6.6</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z23">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA23">
         <v>500</v>
       </c>
       <c r="AB23">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC23">
         <v>7.4</v>
       </c>
       <c r="AD23">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE23">
         <v>500</v>
       </c>
       <c r="AF23">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG23">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH23">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AI23">
         <v>500</v>
@@ -6382,7 +6382,7 @@
         <v>500</v>
       </c>
       <c r="AK23">
-        <v>150</v>
+        <v>440</v>
       </c>
       <c r="AL23">
         <v>500</v>
@@ -6391,70 +6391,70 @@
         <v>500</v>
       </c>
       <c r="AN23">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="AO23">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP23">
         <v>5.3</v>
       </c>
       <c r="AQ23">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AR23">
-        <v>7.6</v>
+        <v>15.5</v>
       </c>
       <c r="AS23">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AT23">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU23">
         <v>5.9</v>
       </c>
       <c r="AV23">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AW23">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AX23">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AY23">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="AZ23">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="BA23">
+        <v>8.4</v>
+      </c>
+      <c r="BB23">
+        <v>8</v>
+      </c>
+      <c r="BC23">
+        <v>7.8</v>
+      </c>
+      <c r="BD23">
+        <v>8.4</v>
+      </c>
+      <c r="BE23">
         <v>8.800000000000001</v>
       </c>
-      <c r="BB23">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC23">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD23">
-        <v>8.6</v>
-      </c>
-      <c r="BE23">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BF23">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG23">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BH23">
         <v>2.4</v>
       </c>
       <c r="BI23">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BJ23">
         <v>14</v>
@@ -6466,13 +6466,13 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN23">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO23">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BP23">
         <v>1000</v>
@@ -6484,19 +6484,19 @@
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT23">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU23">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV23">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX23">
         <v>1000</v>
@@ -6508,7 +6508,7 @@
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB23" t="s">
         <v>199</v>
@@ -6531,16 +6531,16 @@
         <v>184</v>
       </c>
       <c r="F24">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="G24">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="H24">
         <v>5.5</v>
       </c>
       <c r="I24">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>4</v>
@@ -6564,7 +6564,7 @@
         <v>2</v>
       </c>
       <c r="Q24">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R24">
         <v>1.4</v>
@@ -6582,31 +6582,31 @@
         <v>1.2</v>
       </c>
       <c r="W24">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="X24">
         <v>15.5</v>
       </c>
       <c r="Y24">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z24">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AA24">
-        <v>700</v>
+        <v>160</v>
       </c>
       <c r="AB24">
         <v>8.800000000000001</v>
       </c>
       <c r="AC24">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD24">
         <v>22</v>
       </c>
       <c r="AE24">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AF24">
         <v>10.5</v>
@@ -6615,16 +6615,16 @@
         <v>10</v>
       </c>
       <c r="AH24">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI24">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ24">
         <v>17.5</v>
       </c>
       <c r="AK24">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL24">
         <v>38</v>
@@ -6636,7 +6636,7 @@
         <v>10.5</v>
       </c>
       <c r="AO24">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="AP24">
         <v>13.5</v>
@@ -6648,7 +6648,7 @@
         <v>38</v>
       </c>
       <c r="AS24">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="AT24">
         <v>7.8</v>
@@ -6660,7 +6660,7 @@
         <v>21</v>
       </c>
       <c r="AW24">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AX24">
         <v>8.800000000000001</v>
@@ -6672,7 +6672,7 @@
         <v>19</v>
       </c>
       <c r="BA24">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BB24">
         <v>15.5</v>
@@ -6681,7 +6681,7 @@
         <v>15.5</v>
       </c>
       <c r="BD24">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BE24">
         <v>80</v>
@@ -6690,10 +6690,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG24">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BH24">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI24">
         <v>2.84</v>
@@ -6702,55 +6702,55 @@
         <v>11</v>
       </c>
       <c r="BK24">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN24">
         <v>4.5</v>
       </c>
       <c r="BO24">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BP24">
         <v>12</v>
       </c>
       <c r="BQ24">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT24">
         <v>9.4</v>
       </c>
       <c r="BU24">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ24">
         <v>22</v>
       </c>
       <c r="CA24">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB24" t="s">
         <v>199</v>
@@ -6773,16 +6773,16 @@
         <v>185</v>
       </c>
       <c r="F25">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G25">
         <v>3.45</v>
       </c>
       <c r="H25">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I25">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J25">
         <v>3.35</v>
@@ -6791,7 +6791,7 @@
         <v>3.45</v>
       </c>
       <c r="L25">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M25">
         <v>1.09</v>
@@ -6803,7 +6803,7 @@
         <v>1.38</v>
       </c>
       <c r="P25">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q25">
         <v>2.16</v>
@@ -6812,22 +6812,22 @@
         <v>1.31</v>
       </c>
       <c r="S25">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T25">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U25">
         <v>2.06</v>
       </c>
       <c r="V25">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W25">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X25">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y25">
         <v>9.6</v>
@@ -6836,10 +6836,10 @@
         <v>15</v>
       </c>
       <c r="AA25">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB25">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC25">
         <v>7.6</v>
@@ -6848,7 +6848,7 @@
         <v>12</v>
       </c>
       <c r="AE25">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF25">
         <v>23</v>
@@ -6863,7 +6863,7 @@
         <v>44</v>
       </c>
       <c r="AJ25">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AK25">
         <v>42</v>
@@ -6875,7 +6875,7 @@
         <v>130</v>
       </c>
       <c r="AN25">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO25">
         <v>24</v>
@@ -6896,7 +6896,7 @@
         <v>11</v>
       </c>
       <c r="AU25">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV25">
         <v>10.5</v>
@@ -6929,7 +6929,7 @@
         <v>80</v>
       </c>
       <c r="BF25">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BG25">
         <v>21</v>
@@ -6938,19 +6938,19 @@
         <v>3.2</v>
       </c>
       <c r="BI25">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="BJ25">
         <v>9.800000000000001</v>
       </c>
       <c r="BK25">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BN25">
         <v>6.4</v>
@@ -6962,37 +6962,37 @@
         <v>27</v>
       </c>
       <c r="BQ25">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BT25">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU25">
         <v>4.7</v>
       </c>
       <c r="BV25">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BW25">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY25">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ25">
         <v>32</v>
       </c>
       <c r="CA25">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CB25" t="s">
         <v>199</v>
@@ -7015,22 +7015,22 @@
         <v>186</v>
       </c>
       <c r="F26">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="G26">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="H26">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="I26">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K26">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L26">
         <v>1.3</v>
@@ -7039,73 +7039,73 @@
         <v>1.03</v>
       </c>
       <c r="N26">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O26">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P26">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q26">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R26">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S26">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="T26">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="U26">
         <v>2.38</v>
       </c>
       <c r="V26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W26">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="X26">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Y26">
         <v>21</v>
       </c>
       <c r="Z26">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AA26">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="AB26">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC26">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD26">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE26">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AF26">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG26">
         <v>11.5</v>
       </c>
       <c r="AH26">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI26">
         <v>110</v>
       </c>
       <c r="AJ26">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK26">
         <v>19.5</v>
@@ -7114,73 +7114,73 @@
         <v>29</v>
       </c>
       <c r="AM26">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN26">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO26">
-        <v>250</v>
+        <v>34</v>
       </c>
       <c r="AP26">
-        <v>18.5</v>
+        <v>6</v>
       </c>
       <c r="AQ26">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR26">
-        <v>7.8</v>
+        <v>22</v>
       </c>
       <c r="AS26">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AT26">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU26">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV26">
         <v>13.5</v>
       </c>
       <c r="AW26">
-        <v>7.2</v>
+        <v>27</v>
       </c>
       <c r="AX26">
         <v>12</v>
       </c>
       <c r="AY26">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AZ26">
         <v>13</v>
       </c>
       <c r="BA26">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="BB26">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC26">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD26">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="BE26">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="BF26">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BG26">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BH26">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI26">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ26">
         <v>9.4</v>
@@ -7192,7 +7192,7 @@
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BN26">
         <v>5.4</v>
@@ -7204,31 +7204,31 @@
         <v>13.5</v>
       </c>
       <c r="BQ26">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BR26">
         <v>24</v>
       </c>
       <c r="BS26">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT26">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU26">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV26">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW26">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BX26">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY26">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BZ26">
         <v>0</v>
@@ -7260,61 +7260,61 @@
         <v>1.66</v>
       </c>
       <c r="G27">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="H27">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I27">
         <v>6.2</v>
       </c>
       <c r="J27">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K27">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L27">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M27">
         <v>1.06</v>
       </c>
       <c r="N27">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O27">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P27">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="Q27">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="R27">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S27">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T27">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="U27">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V27">
         <v>1.19</v>
       </c>
       <c r="W27">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="X27">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y27">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z27">
         <v>110</v>
@@ -7323,43 +7323,43 @@
         <v>900</v>
       </c>
       <c r="AB27">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC27">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD27">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE27">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="AF27">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG27">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH27">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI27">
         <v>320</v>
       </c>
       <c r="AJ27">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AK27">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AL27">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AM27">
         <v>700</v>
       </c>
       <c r="AN27">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO27">
         <v>700</v>
@@ -7368,34 +7368,34 @@
         <v>14</v>
       </c>
       <c r="AQ27">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR27">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS27">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="AT27">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU27">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV27">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AW27">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX27">
+        <v>9</v>
+      </c>
+      <c r="AY27">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY27">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ27">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA27">
         <v>46</v>
@@ -7407,76 +7407,76 @@
         <v>14.5</v>
       </c>
       <c r="BD27">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE27">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF27">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG27">
-        <v>18.5</v>
+        <v>55</v>
       </c>
       <c r="BH27">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BI27">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ27">
         <v>10.5</v>
       </c>
       <c r="BK27">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="BN27">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO27">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="BP27">
         <v>11</v>
       </c>
       <c r="BQ27">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BR27">
         <v>1000</v>
       </c>
       <c r="BS27">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BT27">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU27">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BV27">
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BZ27">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="CA27">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB27" t="s">
         <v>199</v>
@@ -7499,10 +7499,10 @@
         <v>188</v>
       </c>
       <c r="F28">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G28">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="H28">
         <v>4.2</v>
@@ -7514,7 +7514,7 @@
         <v>4.5</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L28">
         <v>1.23</v>
@@ -7526,7 +7526,7 @@
         <v>7.6</v>
       </c>
       <c r="O28">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P28">
         <v>3.25</v>
@@ -7538,19 +7538,19 @@
         <v>1.9</v>
       </c>
       <c r="S28">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T28">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="U28">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="V28">
         <v>1.29</v>
       </c>
       <c r="W28">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X28">
         <v>42</v>
@@ -7559,16 +7559,16 @@
         <v>34</v>
       </c>
       <c r="Z28">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA28">
         <v>95</v>
       </c>
       <c r="AB28">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC28">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD28">
         <v>23</v>
@@ -7577,22 +7577,22 @@
         <v>55</v>
       </c>
       <c r="AF28">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG28">
         <v>12</v>
       </c>
       <c r="AH28">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI28">
         <v>46</v>
       </c>
       <c r="AJ28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK28">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AL28">
         <v>24</v>
@@ -7604,7 +7604,7 @@
         <v>7</v>
       </c>
       <c r="AO28">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AP28">
         <v>23</v>
@@ -7619,7 +7619,7 @@
         <v>55</v>
       </c>
       <c r="AT28">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU28">
         <v>10.5</v>
@@ -7640,31 +7640,31 @@
         <v>13.5</v>
       </c>
       <c r="BA28">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB28">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC28">
         <v>14</v>
       </c>
       <c r="BD28">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BE28">
         <v>40</v>
       </c>
       <c r="BF28">
+        <v>5.4</v>
+      </c>
+      <c r="BG28">
+        <v>21</v>
+      </c>
+      <c r="BH28">
         <v>5.5</v>
       </c>
-      <c r="BG28">
-        <v>20</v>
-      </c>
-      <c r="BH28">
-        <v>5.3</v>
-      </c>
       <c r="BI28">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BJ28">
         <v>8.6</v>
@@ -7673,16 +7673,16 @@
         <v>5.7</v>
       </c>
       <c r="BL28">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BM28">
-        <v>5.2</v>
+        <v>13</v>
       </c>
       <c r="BN28">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO28">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BP28">
         <v>11</v>
@@ -7691,10 +7691,10 @@
         <v>6.6</v>
       </c>
       <c r="BR28">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BS28">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT28">
         <v>8.4</v>
@@ -7706,19 +7706,19 @@
         <v>1000</v>
       </c>
       <c r="BW28">
+        <v>10</v>
+      </c>
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
+        <v>10</v>
+      </c>
+      <c r="BZ28">
         <v>10.5</v>
       </c>
-      <c r="BX28">
-        <v>1000</v>
-      </c>
-      <c r="BY28">
-        <v>10.5</v>
-      </c>
-      <c r="BZ28">
-        <v>11</v>
-      </c>
       <c r="CA28">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB28" t="s">
         <v>199</v>
@@ -7744,7 +7744,7 @@
         <v>1.65</v>
       </c>
       <c r="G29">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H29">
         <v>6.8</v>
@@ -7753,10 +7753,10 @@
         <v>7.8</v>
       </c>
       <c r="J29">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K29">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L29">
         <v>1.53</v>
@@ -7765,22 +7765,22 @@
         <v>1.11</v>
       </c>
       <c r="N29">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="O29">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="P29">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q29">
         <v>2.48</v>
       </c>
       <c r="R29">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S29">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T29">
         <v>2.34</v>
@@ -7789,7 +7789,7 @@
         <v>1.65</v>
       </c>
       <c r="V29">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W29">
         <v>2.34</v>
@@ -7798,10 +7798,10 @@
         <v>11.5</v>
       </c>
       <c r="Y29">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Z29">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="AA29">
         <v>900</v>
@@ -7837,19 +7837,19 @@
         <v>23</v>
       </c>
       <c r="AL29">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="AM29">
         <v>700</v>
       </c>
       <c r="AN29">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO29">
         <v>700</v>
       </c>
       <c r="AP29">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ29">
         <v>14.5</v>
@@ -7858,7 +7858,7 @@
         <v>40</v>
       </c>
       <c r="AS29">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT29">
         <v>5.3</v>
@@ -7882,7 +7882,7 @@
         <v>24</v>
       </c>
       <c r="BA29">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BB29">
         <v>14.5</v>
@@ -7891,22 +7891,22 @@
         <v>19.5</v>
       </c>
       <c r="BD29">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE29">
         <v>10</v>
       </c>
       <c r="BF29">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG29">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH29">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BI29">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="BJ29">
         <v>13</v>
@@ -7921,10 +7921,10 @@
         <v>14.5</v>
       </c>
       <c r="BN29">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BO29">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BP29">
         <v>12.5</v>
@@ -7933,7 +7933,7 @@
         <v>6.8</v>
       </c>
       <c r="BR29">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
         <v>11</v>
@@ -7983,16 +7983,16 @@
         <v>190</v>
       </c>
       <c r="F30">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="G30">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H30">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I30">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="J30">
         <v>3.45</v>
@@ -8007,16 +8007,16 @@
         <v>1.08</v>
       </c>
       <c r="N30">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O30">
         <v>1.38</v>
       </c>
       <c r="P30">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q30">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R30">
         <v>1.32</v>
@@ -8025,28 +8025,28 @@
         <v>3.9</v>
       </c>
       <c r="T30">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U30">
         <v>2.06</v>
       </c>
       <c r="V30">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="W30">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X30">
         <v>13.5</v>
       </c>
       <c r="Y30">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Z30">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AA30">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="AB30">
         <v>13.5</v>
@@ -8058,49 +8058,49 @@
         <v>11</v>
       </c>
       <c r="AE30">
+        <v>32</v>
+      </c>
+      <c r="AF30">
+        <v>34</v>
+      </c>
+      <c r="AG30">
+        <v>18</v>
+      </c>
+      <c r="AH30">
+        <v>23</v>
+      </c>
+      <c r="AI30">
+        <v>120</v>
+      </c>
+      <c r="AJ30">
+        <v>330</v>
+      </c>
+      <c r="AK30">
         <v>65</v>
       </c>
-      <c r="AF30">
-        <v>500</v>
-      </c>
-      <c r="AG30">
-        <v>26</v>
-      </c>
-      <c r="AH30">
-        <v>36</v>
-      </c>
-      <c r="AI30">
-        <v>500</v>
-      </c>
-      <c r="AJ30">
-        <v>900</v>
-      </c>
-      <c r="AK30">
-        <v>500</v>
-      </c>
       <c r="AL30">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AM30">
-        <v>580</v>
+        <v>310</v>
       </c>
       <c r="AN30">
         <v>70</v>
       </c>
       <c r="AO30">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="AP30">
         <v>11.5</v>
       </c>
       <c r="AQ30">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR30">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS30">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AT30">
         <v>11.5</v>
@@ -8109,100 +8109,100 @@
         <v>6.8</v>
       </c>
       <c r="AV30">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW30">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="AX30">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AY30">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ30">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BA30">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BB30">
-        <v>7.6</v>
+        <v>50</v>
       </c>
       <c r="BC30">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BD30">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="BE30">
-        <v>7.8</v>
+        <v>29</v>
       </c>
       <c r="BF30">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="BG30">
-        <v>5.9</v>
+        <v>16</v>
       </c>
       <c r="BH30">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI30">
-        <v>2.76</v>
+        <v>2.98</v>
       </c>
       <c r="BJ30">
         <v>9.800000000000001</v>
       </c>
       <c r="BK30">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>16.5</v>
+        <v>1.83</v>
       </c>
       <c r="BN30">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO30">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BP30">
         <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BT30">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU30">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV30">
         <v>1000</v>
       </c>
       <c r="BW30">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
       </c>
       <c r="CA30">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB30" t="s">
         <v>199</v>
@@ -8225,37 +8225,37 @@
         <v>191</v>
       </c>
       <c r="F31">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="G31">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H31">
         <v>11.5</v>
       </c>
       <c r="I31">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J31">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K31">
         <v>6.6</v>
       </c>
       <c r="L31">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M31">
         <v>1.02</v>
       </c>
       <c r="N31">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O31">
         <v>1.2</v>
       </c>
       <c r="P31">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q31">
         <v>1.6</v>
@@ -8273,34 +8273,34 @@
         <v>1.81</v>
       </c>
       <c r="V31">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W31">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="X31">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Y31">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="Z31">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AA31">
-        <v>530</v>
+        <v>1000</v>
       </c>
       <c r="AB31">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC31">
         <v>14</v>
       </c>
       <c r="AD31">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AE31">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="AF31">
         <v>8.6</v>
@@ -8312,49 +8312,49 @@
         <v>30</v>
       </c>
       <c r="AI31">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="AJ31">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK31">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL31">
         <v>38</v>
       </c>
       <c r="AM31">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN31">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AO31">
-        <v>300</v>
+        <v>380</v>
       </c>
       <c r="AP31">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ31">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR31">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AS31">
         <v>10</v>
       </c>
       <c r="AT31">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AU31">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV31">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW31">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX31">
         <v>4.7</v>
@@ -8363,25 +8363,25 @@
         <v>5.3</v>
       </c>
       <c r="AZ31">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BA31">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB31">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BC31">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BD31">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BE31">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF31">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BG31">
         <v>10.5</v>
@@ -8390,19 +8390,19 @@
         <v>4.4</v>
       </c>
       <c r="BI31">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ31">
         <v>12.5</v>
       </c>
       <c r="BK31">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BN31">
         <v>3.9</v>
@@ -8411,40 +8411,40 @@
         <v>3</v>
       </c>
       <c r="BP31">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BQ31">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR31">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS31">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT31">
         <v>14.5</v>
       </c>
       <c r="BU31">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV31">
         <v>1000</v>
       </c>
       <c r="BW31">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BZ31">
         <v>12</v>
       </c>
       <c r="CA31">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB31" t="s">
         <v>199</v>
@@ -8470,7 +8470,7 @@
         <v>2.02</v>
       </c>
       <c r="G32">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H32">
         <v>4.3</v>
@@ -8482,16 +8482,16 @@
         <v>3.5</v>
       </c>
       <c r="K32">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L32">
         <v>1.46</v>
       </c>
       <c r="M32">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N32">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O32">
         <v>1.38</v>
@@ -8506,25 +8506,25 @@
         <v>1.3</v>
       </c>
       <c r="S32">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T32">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U32">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V32">
         <v>1.28</v>
       </c>
       <c r="W32">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X32">
         <v>13</v>
       </c>
       <c r="Y32">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z32">
         <v>34</v>
@@ -8533,19 +8533,19 @@
         <v>900</v>
       </c>
       <c r="AB32">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC32">
         <v>8</v>
       </c>
       <c r="AD32">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE32">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AF32">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG32">
         <v>11</v>
@@ -8554,10 +8554,10 @@
         <v>21</v>
       </c>
       <c r="AI32">
-        <v>170</v>
+        <v>370</v>
       </c>
       <c r="AJ32">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK32">
         <v>24</v>
@@ -8572,19 +8572,19 @@
         <v>18.5</v>
       </c>
       <c r="AO32">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AP32">
         <v>10</v>
       </c>
       <c r="AQ32">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR32">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AS32">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT32">
         <v>7.2</v>
@@ -8596,7 +8596,7 @@
         <v>15.5</v>
       </c>
       <c r="AW32">
-        <v>9.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="AX32">
         <v>10</v>
@@ -8608,7 +8608,7 @@
         <v>17</v>
       </c>
       <c r="BA32">
-        <v>9.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BB32">
         <v>20</v>
@@ -8617,76 +8617,76 @@
         <v>19.5</v>
       </c>
       <c r="BD32">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="BE32">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF32">
         <v>15.5</v>
       </c>
       <c r="BG32">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BH32">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI32">
-        <v>2.56</v>
+        <v>2.92</v>
       </c>
       <c r="BJ32">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK32">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN32">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO32">
         <v>4</v>
       </c>
       <c r="BP32">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ32">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR32">
         <v>34</v>
       </c>
       <c r="BS32">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT32">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU32">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV32">
         <v>42</v>
       </c>
       <c r="BW32">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX32">
         <v>55</v>
       </c>
       <c r="BY32">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BZ32">
         <v>32</v>
       </c>
       <c r="CA32">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB32" t="s">
         <v>199</v>
@@ -8709,22 +8709,22 @@
         <v>193</v>
       </c>
       <c r="F33">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G33">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H33">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I33">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J33">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K33">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L33">
         <v>1.5</v>
@@ -8733,37 +8733,37 @@
         <v>1.1</v>
       </c>
       <c r="N33">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O33">
         <v>1.46</v>
       </c>
       <c r="P33">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q33">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R33">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S33">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T33">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U33">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V33">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="X33">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y33">
         <v>12</v>
@@ -8784,19 +8784,19 @@
         <v>15.5</v>
       </c>
       <c r="AE33">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF33">
         <v>13.5</v>
       </c>
       <c r="AG33">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH33">
         <v>22</v>
       </c>
       <c r="AI33">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AJ33">
         <v>32</v>
@@ -8805,16 +8805,16 @@
         <v>65</v>
       </c>
       <c r="AL33">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AM33">
-        <v>450</v>
+        <v>160</v>
       </c>
       <c r="AN33">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO33">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP33">
         <v>9.4</v>
@@ -8835,100 +8835,100 @@
         <v>6.8</v>
       </c>
       <c r="AV33">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW33">
         <v>42</v>
       </c>
       <c r="AX33">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY33">
         <v>10</v>
       </c>
       <c r="AZ33">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA33">
         <v>50</v>
       </c>
       <c r="BB33">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BC33">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD33">
         <v>42</v>
       </c>
       <c r="BE33">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BF33">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BG33">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BH33">
         <v>3.05</v>
       </c>
       <c r="BI33">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ33">
         <v>11</v>
       </c>
       <c r="BK33">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BN33">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO33">
         <v>4.3</v>
       </c>
       <c r="BP33">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BQ33">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR33">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS33">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT33">
         <v>7</v>
       </c>
       <c r="BU33">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV33">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW33">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX33">
         <v>55</v>
       </c>
       <c r="BY33">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ33">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA33">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB33" t="s">
         <v>199</v>
@@ -8951,16 +8951,16 @@
         <v>194</v>
       </c>
       <c r="F34">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G34">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="H34">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I34">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J34">
         <v>3.3</v>
@@ -8975,22 +8975,22 @@
         <v>1.12</v>
       </c>
       <c r="N34">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="O34">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P34">
         <v>1.55</v>
       </c>
       <c r="Q34">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R34">
         <v>1.2</v>
       </c>
       <c r="S34">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T34">
         <v>2.2</v>
@@ -8999,37 +8999,37 @@
         <v>1.75</v>
       </c>
       <c r="V34">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W34">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="X34">
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z34">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA34">
         <v>130</v>
       </c>
       <c r="AB34">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC34">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD34">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE34">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="AF34">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG34">
         <v>12</v>
@@ -9038,64 +9038,64 @@
         <v>32</v>
       </c>
       <c r="AI34">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="AJ34">
         <v>26</v>
       </c>
       <c r="AK34">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL34">
         <v>65</v>
       </c>
       <c r="AM34">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="AN34">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AO34">
         <v>140</v>
       </c>
       <c r="AP34">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ34">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR34">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AS34">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AT34">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AU34">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV34">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW34">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="AX34">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY34">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ34">
         <v>23</v>
       </c>
       <c r="BA34">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BB34">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC34">
         <v>23</v>
@@ -9104,73 +9104,73 @@
         <v>50</v>
       </c>
       <c r="BE34">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BF34">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BG34">
-        <v>12.5</v>
+        <v>46</v>
       </c>
       <c r="BH34">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="BI34">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="BJ34">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK34">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN34">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO34">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP34">
         <v>16.5</v>
       </c>
       <c r="BQ34">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT34">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU34">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BX34">
         <v>1000</v>
       </c>
       <c r="BY34">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BZ34">
         <v>1000</v>
       </c>
       <c r="CA34">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CB34" t="s">
         <v>199</v>
@@ -9193,10 +9193,10 @@
         <v>195</v>
       </c>
       <c r="F35">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G35">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H35">
         <v>3.3</v>
@@ -9205,13 +9205,13 @@
         <v>3.7</v>
       </c>
       <c r="J35">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K35">
         <v>4</v>
       </c>
       <c r="L35">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M35">
         <v>1.05</v>
@@ -9226,31 +9226,31 @@
         <v>2.08</v>
       </c>
       <c r="Q35">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R35">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S35">
         <v>3.1</v>
       </c>
       <c r="T35">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U35">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V35">
         <v>1.37</v>
       </c>
       <c r="W35">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X35">
         <v>18</v>
       </c>
       <c r="Y35">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z35">
         <v>30</v>
@@ -9268,7 +9268,7 @@
         <v>18</v>
       </c>
       <c r="AE35">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF35">
         <v>17.5</v>
@@ -9277,7 +9277,7 @@
         <v>13.5</v>
       </c>
       <c r="AH35">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI35">
         <v>55</v>
@@ -9289,130 +9289,130 @@
         <v>27</v>
       </c>
       <c r="AL35">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM35">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN35">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AO35">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP35">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="AQ35">
         <v>11</v>
       </c>
       <c r="AR35">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AS35">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AT35">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AU35">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV35">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="AW35">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AX35">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="AY35">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ35">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="BA35">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BB35">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BC35">
-        <v>4.6</v>
+        <v>18.5</v>
       </c>
       <c r="BD35">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE35">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BF35">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG35">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BH35">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI35">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ35">
         <v>9.6</v>
       </c>
       <c r="BK35">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN35">
         <v>5.4</v>
       </c>
       <c r="BO35">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BP35">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ35">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BR35">
         <v>28</v>
       </c>
       <c r="BS35">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT35">
         <v>7.2</v>
       </c>
       <c r="BU35">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BV35">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BW35">
         <v>7.4</v>
       </c>
       <c r="BX35">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY35">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ35">
         <v>23</v>
       </c>
       <c r="CA35">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB35" t="s">
         <v>199</v>
@@ -9441,13 +9441,13 @@
         <v>1.89</v>
       </c>
       <c r="H36">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I36">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J36">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K36">
         <v>3.85</v>
@@ -9459,7 +9459,7 @@
         <v>1.08</v>
       </c>
       <c r="N36">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O36">
         <v>1.38</v>
@@ -9468,49 +9468,49 @@
         <v>1.79</v>
       </c>
       <c r="Q36">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R36">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S36">
         <v>3.95</v>
       </c>
       <c r="T36">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U36">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V36">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W36">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X36">
         <v>14</v>
       </c>
       <c r="Y36">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Z36">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA36">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AB36">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC36">
         <v>8.4</v>
       </c>
       <c r="AD36">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE36">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AF36">
         <v>11</v>
@@ -9522,37 +9522,37 @@
         <v>26</v>
       </c>
       <c r="AI36">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AJ36">
+        <v>21</v>
+      </c>
+      <c r="AK36">
         <v>22</v>
       </c>
-      <c r="AK36">
-        <v>24</v>
-      </c>
       <c r="AL36">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM36">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AN36">
         <v>15</v>
       </c>
       <c r="AO36">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP36">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ36">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR36">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="AS36">
-        <v>9.4</v>
+        <v>30</v>
       </c>
       <c r="AT36">
         <v>6.8</v>
@@ -9561,58 +9561,58 @@
         <v>7.2</v>
       </c>
       <c r="AV36">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW36">
-        <v>8.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="AX36">
         <v>9.4</v>
       </c>
       <c r="AY36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ36">
         <v>18.5</v>
       </c>
       <c r="BA36">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="BB36">
         <v>15.5</v>
       </c>
       <c r="BC36">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD36">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="BE36">
-        <v>9.4</v>
+        <v>30</v>
       </c>
       <c r="BF36">
         <v>13</v>
       </c>
       <c r="BG36">
-        <v>9.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="BH36">
         <v>3.2</v>
       </c>
       <c r="BI36">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="BJ36">
         <v>11</v>
       </c>
       <c r="BK36">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>13.5</v>
+        <v>2.48</v>
       </c>
       <c r="BN36">
         <v>4.4</v>
@@ -9621,7 +9621,7 @@
         <v>3.5</v>
       </c>
       <c r="BP36">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ36">
         <v>7</v>
@@ -9633,10 +9633,10 @@
         <v>10</v>
       </c>
       <c r="BT36">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU36">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV36">
         <v>1000</v>
@@ -9677,70 +9677,70 @@
         <v>197</v>
       </c>
       <c r="F37">
+        <v>3.55</v>
+      </c>
+      <c r="G37">
+        <v>4</v>
+      </c>
+      <c r="H37">
+        <v>2.22</v>
+      </c>
+      <c r="I37">
+        <v>2.34</v>
+      </c>
+      <c r="J37">
         <v>3.2</v>
-      </c>
-      <c r="G37">
-        <v>3.5</v>
-      </c>
-      <c r="H37">
-        <v>2.42</v>
-      </c>
-      <c r="I37">
-        <v>2.62</v>
-      </c>
-      <c r="J37">
-        <v>3.15</v>
       </c>
       <c r="K37">
         <v>3.45</v>
       </c>
       <c r="L37">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M37">
         <v>1.09</v>
       </c>
       <c r="N37">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O37">
         <v>1.41</v>
       </c>
       <c r="P37">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q37">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R37">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S37">
         <v>4.3</v>
       </c>
       <c r="T37">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U37">
         <v>1.94</v>
       </c>
       <c r="V37">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="W37">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="X37">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y37">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z37">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA37">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AB37">
         <v>13</v>
@@ -9749,154 +9749,154 @@
         <v>7.8</v>
       </c>
       <c r="AD37">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE37">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AF37">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AG37">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AH37">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI37">
         <v>55</v>
       </c>
       <c r="AJ37">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AK37">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL37">
         <v>65</v>
       </c>
       <c r="AM37">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AN37">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AO37">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AP37">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ37">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR37">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="AS37">
-        <v>5.7</v>
+        <v>24</v>
       </c>
       <c r="AT37">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU37">
         <v>6.4</v>
       </c>
       <c r="AV37">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW37">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="AX37">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AY37">
+        <v>13.5</v>
+      </c>
+      <c r="AZ37">
+        <v>16.5</v>
+      </c>
+      <c r="BA37">
+        <v>32</v>
+      </c>
+      <c r="BB37">
+        <v>46</v>
+      </c>
+      <c r="BC37">
+        <v>32</v>
+      </c>
+      <c r="BD37">
+        <v>42</v>
+      </c>
+      <c r="BE37">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF37">
+        <v>38</v>
+      </c>
+      <c r="BG37">
+        <v>20</v>
+      </c>
+      <c r="BH37">
+        <v>3.2</v>
+      </c>
+      <c r="BI37">
+        <v>2.58</v>
+      </c>
+      <c r="BJ37">
         <v>11</v>
       </c>
-      <c r="AZ37">
-        <v>14.5</v>
-      </c>
-      <c r="BA37">
-        <v>5.9</v>
-      </c>
-      <c r="BB37">
-        <v>6</v>
-      </c>
-      <c r="BC37">
-        <v>5.8</v>
-      </c>
-      <c r="BD37">
-        <v>6</v>
-      </c>
-      <c r="BE37">
-        <v>6.2</v>
-      </c>
-      <c r="BF37">
-        <v>5.9</v>
-      </c>
-      <c r="BG37">
-        <v>21</v>
-      </c>
-      <c r="BH37">
-        <v>3.15</v>
-      </c>
-      <c r="BI37">
-        <v>2.52</v>
-      </c>
-      <c r="BJ37">
-        <v>10.5</v>
-      </c>
       <c r="BK37">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL37">
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN37">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO37">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BP37">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BQ37">
         <v>7.8</v>
       </c>
       <c r="BR37">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BS37">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT37">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BU37">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BV37">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BW37">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BX37">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BY37">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BZ37">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA37">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CB37" t="s">
         <v>199</v>
@@ -9919,25 +9919,25 @@
         <v>198</v>
       </c>
       <c r="F38">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="G38">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="H38">
+        <v>3.1</v>
+      </c>
+      <c r="I38">
         <v>3.25</v>
-      </c>
-      <c r="I38">
-        <v>3.4</v>
       </c>
       <c r="J38">
         <v>3.3</v>
       </c>
       <c r="K38">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L38">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M38">
         <v>1.09</v>
@@ -9949,97 +9949,97 @@
         <v>1.4</v>
       </c>
       <c r="P38">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q38">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R38">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S38">
         <v>4</v>
       </c>
       <c r="T38">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U38">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V38">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="X38">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y38">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z38">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA38">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB38">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC38">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD38">
+        <v>13.5</v>
+      </c>
+      <c r="AE38">
+        <v>44</v>
+      </c>
+      <c r="AF38">
         <v>16</v>
       </c>
-      <c r="AE38">
-        <v>46</v>
-      </c>
-      <c r="AF38">
-        <v>18</v>
-      </c>
       <c r="AG38">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH38">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AI38">
         <v>65</v>
       </c>
       <c r="AJ38">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK38">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL38">
         <v>55</v>
       </c>
       <c r="AM38">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN38">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO38">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP38">
         <v>10.5</v>
       </c>
       <c r="AQ38">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR38">
-        <v>5.1</v>
+        <v>16.5</v>
       </c>
       <c r="AS38">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="AT38">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU38">
         <v>6.6</v>
@@ -10048,58 +10048,58 @@
         <v>12.5</v>
       </c>
       <c r="AW38">
-        <v>5.7</v>
+        <v>27</v>
       </c>
       <c r="AX38">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY38">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ38">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA38">
-        <v>5.8</v>
+        <v>38</v>
       </c>
       <c r="BB38">
-        <v>5.6</v>
+        <v>26</v>
       </c>
       <c r="BC38">
-        <v>5.5</v>
+        <v>23</v>
       </c>
       <c r="BD38">
-        <v>5.8</v>
+        <v>32</v>
       </c>
       <c r="BE38">
-        <v>6.2</v>
+        <v>40</v>
       </c>
       <c r="BF38">
-        <v>5.3</v>
+        <v>19</v>
       </c>
       <c r="BG38">
-        <v>5.8</v>
+        <v>25</v>
       </c>
       <c r="BH38">
         <v>3.15</v>
       </c>
       <c r="BI38">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="BJ38">
         <v>9.800000000000001</v>
       </c>
       <c r="BK38">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>16.5</v>
+        <v>4.9</v>
       </c>
       <c r="BN38">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO38">
         <v>4</v>
@@ -10108,37 +10108,37 @@
         <v>1000</v>
       </c>
       <c r="BQ38">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BR38">
         <v>1000</v>
       </c>
       <c r="BS38">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT38">
         <v>6.4</v>
       </c>
       <c r="BU38">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
+        <v>10</v>
+      </c>
+      <c r="BX38">
+        <v>1000</v>
+      </c>
+      <c r="BY38">
+        <v>12</v>
+      </c>
+      <c r="BZ38">
+        <v>1000</v>
+      </c>
+      <c r="CA38">
         <v>11</v>
-      </c>
-      <c r="BX38">
-        <v>1000</v>
-      </c>
-      <c r="BY38">
-        <v>13</v>
-      </c>
-      <c r="BZ38">
-        <v>1000</v>
-      </c>
-      <c r="CA38">
-        <v>12</v>
       </c>
       <c r="CB38" t="s">
         <v>199</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-27.xlsx
@@ -601,7 +601,7 @@
     <t>Everton De Vina</t>
   </si>
   <si>
-    <t>2026-07-27 11:06:49</t>
+    <t>2026-07-27 13:13:42</t>
   </si>
 </sst>
 </file>
@@ -1195,220 +1195,220 @@
         <v>159</v>
       </c>
       <c r="F2">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="G2">
-        <v>14.5</v>
+        <v>330</v>
       </c>
       <c r="H2">
+        <v>1.12</v>
+      </c>
+      <c r="I2">
+        <v>1.14</v>
+      </c>
+      <c r="J2">
+        <v>9.4</v>
+      </c>
+      <c r="K2">
+        <v>11</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>5.4</v>
+      </c>
+      <c r="O2">
+        <v>1.21</v>
+      </c>
+      <c r="P2">
+        <v>1.86</v>
+      </c>
+      <c r="Q2">
+        <v>2.1</v>
+      </c>
+      <c r="R2">
         <v>1.26</v>
       </c>
-      <c r="I2">
-        <v>1.27</v>
-      </c>
-      <c r="J2">
-        <v>7.4</v>
-      </c>
-      <c r="K2">
-        <v>7.8</v>
-      </c>
-      <c r="L2">
-        <v>1.21</v>
-      </c>
-      <c r="M2">
-        <v>1.02</v>
-      </c>
-      <c r="N2">
-        <v>8.4</v>
-      </c>
-      <c r="O2">
-        <v>1.11</v>
-      </c>
-      <c r="P2">
-        <v>3.5</v>
-      </c>
-      <c r="Q2">
-        <v>1.37</v>
-      </c>
-      <c r="R2">
-        <v>2.02</v>
-      </c>
       <c r="S2">
-        <v>1.93</v>
+        <v>4.5</v>
       </c>
       <c r="T2">
-        <v>1.79</v>
+        <v>3</v>
       </c>
       <c r="U2">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="V2">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>15</v>
+        <v>5.1</v>
       </c>
       <c r="Z2">
+        <v>4.2</v>
+      </c>
+      <c r="AA2">
+        <v>6.6</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>20</v>
+      </c>
+      <c r="AD2">
         <v>11</v>
       </c>
-      <c r="AA2">
-        <v>13</v>
-      </c>
-      <c r="AB2">
-        <v>70</v>
-      </c>
-      <c r="AC2">
-        <v>18</v>
-      </c>
-      <c r="AD2">
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>990</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>10.5</v>
+      </c>
+      <c r="AP2">
+        <v>5.6</v>
+      </c>
+      <c r="AQ2">
+        <v>4.7</v>
+      </c>
+      <c r="AR2">
+        <v>3.7</v>
+      </c>
+      <c r="AS2">
+        <v>6</v>
+      </c>
+      <c r="AT2">
+        <v>5.6</v>
+      </c>
+      <c r="AU2">
         <v>12</v>
-      </c>
-      <c r="AE2">
-        <v>13</v>
-      </c>
-      <c r="AF2">
-        <v>200</v>
-      </c>
-      <c r="AG2">
-        <v>48</v>
-      </c>
-      <c r="AH2">
-        <v>29</v>
-      </c>
-      <c r="AI2">
-        <v>30</v>
-      </c>
-      <c r="AJ2">
-        <v>410</v>
-      </c>
-      <c r="AK2">
-        <v>190</v>
-      </c>
-      <c r="AL2">
-        <v>130</v>
-      </c>
-      <c r="AM2">
-        <v>120</v>
-      </c>
-      <c r="AN2">
-        <v>200</v>
-      </c>
-      <c r="AO2">
-        <v>3.1</v>
-      </c>
-      <c r="AP2">
-        <v>38</v>
-      </c>
-      <c r="AQ2">
-        <v>12.5</v>
-      </c>
-      <c r="AR2">
-        <v>9.4</v>
-      </c>
-      <c r="AS2">
-        <v>10</v>
-      </c>
-      <c r="AT2">
-        <v>55</v>
-      </c>
-      <c r="AU2">
-        <v>15.5</v>
       </c>
       <c r="AV2">
         <v>10</v>
       </c>
       <c r="AW2">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AX2">
-        <v>11</v>
+        <v>5.6</v>
       </c>
       <c r="AY2">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AZ2">
-        <v>24</v>
+        <v>9.4</v>
       </c>
       <c r="BA2">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="BB2">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC2">
-        <v>11</v>
+        <v>310</v>
       </c>
       <c r="BD2">
-        <v>10.5</v>
+        <v>280</v>
       </c>
       <c r="BE2">
-        <v>15.5</v>
+        <v>250</v>
       </c>
       <c r="BF2">
-        <v>11</v>
+        <v>520</v>
       </c>
       <c r="BG2">
-        <v>2.96</v>
+        <v>8.6</v>
       </c>
       <c r="BH2">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1437,220 +1437,220 @@
         <v>160</v>
       </c>
       <c r="F3">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="G3">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="H3">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="I3">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="K3">
+        <v>2.7</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>1.36</v>
+      </c>
+      <c r="N3">
+        <v>1.56</v>
+      </c>
+      <c r="O3">
+        <v>2.74</v>
+      </c>
+      <c r="P3">
+        <v>1.15</v>
+      </c>
+      <c r="Q3">
+        <v>7.2</v>
+      </c>
+      <c r="R3">
+        <v>1.03</v>
+      </c>
+      <c r="S3">
+        <v>30</v>
+      </c>
+      <c r="T3">
+        <v>4.4</v>
+      </c>
+      <c r="U3">
+        <v>1.24</v>
+      </c>
+      <c r="V3">
+        <v>1.16</v>
+      </c>
+      <c r="W3">
+        <v>1.85</v>
+      </c>
+      <c r="X3">
+        <v>4</v>
+      </c>
+      <c r="Y3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z3">
+        <v>65</v>
+      </c>
+      <c r="AA3">
+        <v>590</v>
+      </c>
+      <c r="AB3">
         <v>4.2</v>
       </c>
-      <c r="L3">
-        <v>1.34</v>
-      </c>
-      <c r="M3">
-        <v>1.05</v>
-      </c>
-      <c r="N3">
-        <v>4.5</v>
-      </c>
-      <c r="O3">
-        <v>1.26</v>
-      </c>
-      <c r="P3">
-        <v>2.22</v>
-      </c>
-      <c r="Q3">
-        <v>1.76</v>
-      </c>
-      <c r="R3">
-        <v>1.48</v>
-      </c>
-      <c r="S3">
-        <v>2.92</v>
-      </c>
-      <c r="T3">
-        <v>1.67</v>
-      </c>
-      <c r="U3">
-        <v>2.22</v>
-      </c>
-      <c r="V3">
-        <v>1.28</v>
-      </c>
-      <c r="W3">
-        <v>2.04</v>
-      </c>
-      <c r="X3">
-        <v>21</v>
-      </c>
-      <c r="Y3">
+      <c r="AC3">
+        <v>9.6</v>
+      </c>
+      <c r="AD3">
+        <v>60</v>
+      </c>
+      <c r="AE3">
+        <v>540</v>
+      </c>
+      <c r="AF3">
+        <v>10</v>
+      </c>
+      <c r="AG3">
         <v>23</v>
       </c>
-      <c r="Z3">
+      <c r="AH3">
+        <v>130</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
         <v>36</v>
       </c>
-      <c r="AA3">
+      <c r="AK3">
         <v>110</v>
       </c>
-      <c r="AB3">
-        <v>11.5</v>
-      </c>
-      <c r="AC3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD3">
-        <v>18.5</v>
-      </c>
-      <c r="AE3">
-        <v>50</v>
-      </c>
-      <c r="AF3">
-        <v>13.5</v>
-      </c>
-      <c r="AG3">
-        <v>11</v>
-      </c>
-      <c r="AH3">
-        <v>22</v>
-      </c>
-      <c r="AI3">
-        <v>55</v>
-      </c>
-      <c r="AJ3">
-        <v>22</v>
-      </c>
-      <c r="AK3">
+      <c r="AL3">
+        <v>530</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>120</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>3.65</v>
+      </c>
+      <c r="AQ3">
+        <v>9</v>
+      </c>
+      <c r="AR3">
+        <v>44</v>
+      </c>
+      <c r="AS3">
+        <v>170</v>
+      </c>
+      <c r="AT3">
+        <v>3.75</v>
+      </c>
+      <c r="AU3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV3">
+        <v>42</v>
+      </c>
+      <c r="AW3">
+        <v>140</v>
+      </c>
+      <c r="AX3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY3">
         <v>19.5</v>
       </c>
-      <c r="AL3">
-        <v>38</v>
-      </c>
-      <c r="AM3">
-        <v>95</v>
-      </c>
-      <c r="AN3">
-        <v>11</v>
-      </c>
-      <c r="AO3">
-        <v>46</v>
-      </c>
-      <c r="AP3">
-        <v>16.5</v>
-      </c>
-      <c r="AQ3">
-        <v>15.5</v>
-      </c>
-      <c r="AR3">
-        <v>25</v>
-      </c>
-      <c r="AS3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU3">
-        <v>8</v>
-      </c>
-      <c r="AV3">
-        <v>15</v>
-      </c>
-      <c r="AW3">
-        <v>7.6</v>
-      </c>
-      <c r="AX3">
-        <v>10.5</v>
-      </c>
-      <c r="AY3">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AZ3">
-        <v>14.5</v>
+        <v>85</v>
       </c>
       <c r="BA3">
-        <v>7.6</v>
+        <v>320</v>
       </c>
       <c r="BB3">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="BC3">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="BD3">
-        <v>22</v>
+        <v>220</v>
       </c>
       <c r="BE3">
-        <v>8</v>
+        <v>340</v>
       </c>
       <c r="BF3">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="BG3">
-        <v>27</v>
+        <v>430</v>
       </c>
       <c r="BH3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1679,226 +1679,226 @@
         <v>161</v>
       </c>
       <c r="F4">
-        <v>1.79</v>
+        <v>1.02</v>
       </c>
       <c r="G4">
-        <v>1.8</v>
+        <v>1.03</v>
       </c>
       <c r="H4">
-        <v>5.5</v>
+        <v>180</v>
       </c>
       <c r="I4">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="J4">
-        <v>3.8</v>
+        <v>48</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>55</v>
       </c>
       <c r="L4">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>1.95</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>1.99</v>
+        <v>1.16</v>
       </c>
       <c r="R4">
-        <v>1.37</v>
+        <v>2.26</v>
       </c>
       <c r="S4">
-        <v>3.6</v>
+        <v>1.76</v>
       </c>
       <c r="T4">
-        <v>1.9</v>
+        <v>1.06</v>
       </c>
       <c r="U4">
-        <v>2.02</v>
+        <v>1.02</v>
       </c>
       <c r="V4">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>2.24</v>
+        <v>38</v>
       </c>
       <c r="X4">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
+        <v>7.8</v>
+      </c>
+      <c r="AG4">
+        <v>16</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>5.3</v>
+      </c>
+      <c r="AK4">
         <v>10.5</v>
       </c>
-      <c r="AG4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH4">
-        <v>21</v>
-      </c>
-      <c r="AI4">
-        <v>110</v>
-      </c>
-      <c r="AJ4">
-        <v>18</v>
-      </c>
-      <c r="AK4">
-        <v>19</v>
-      </c>
       <c r="AL4">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>11.5</v>
+        <v>2.52</v>
       </c>
       <c r="AO4">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
         <v>13</v>
       </c>
       <c r="AQ4">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AR4">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="AS4">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AT4">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AU4">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AV4">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AW4">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AX4">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AY4">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>65</v>
+        <v>8.6</v>
       </c>
       <c r="BB4">
-        <v>16</v>
+        <v>4.4</v>
       </c>
       <c r="BC4">
-        <v>16.5</v>
+        <v>8.4</v>
       </c>
       <c r="BD4">
-        <v>34</v>
+        <v>8.6</v>
       </c>
       <c r="BE4">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="BF4">
-        <v>10.5</v>
+        <v>2.36</v>
       </c>
       <c r="BG4">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="BH4">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>930</v>
       </c>
       <c r="BM4">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="BN4">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.85</v>
+        <v>9.6</v>
       </c>
       <c r="BP4">
-        <v>11.5</v>
+        <v>1.32</v>
       </c>
       <c r="BQ4">
-        <v>7.2</v>
+        <v>1.27</v>
       </c>
       <c r="BR4">
-        <v>28</v>
+        <v>800</v>
       </c>
       <c r="BS4">
-        <v>11.5</v>
+        <v>4</v>
       </c>
       <c r="BT4">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="BX4">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="BZ4">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="CA4">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="CB4" t="s">
         <v>195</v>
@@ -1921,220 +1921,220 @@
         <v>162</v>
       </c>
       <c r="F5">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="G5">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="H5">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="I5">
+        <v>2.02</v>
+      </c>
+      <c r="J5">
+        <v>3.4</v>
+      </c>
+      <c r="K5">
+        <v>3.5</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>8.6</v>
+      </c>
+      <c r="Q5">
+        <v>1.12</v>
+      </c>
+      <c r="R5">
+        <v>2.84</v>
+      </c>
+      <c r="S5">
+        <v>1.52</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>2</v>
+      </c>
+      <c r="W5">
+        <v>1.24</v>
+      </c>
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD5">
+        <v>6.6</v>
+      </c>
+      <c r="AE5">
+        <v>9.6</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>12</v>
+      </c>
+      <c r="AH5">
+        <v>7.4</v>
+      </c>
+      <c r="AI5">
+        <v>12</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>34</v>
+      </c>
+      <c r="AL5">
+        <v>25</v>
+      </c>
+      <c r="AM5">
+        <v>34</v>
+      </c>
+      <c r="AN5">
+        <v>38</v>
+      </c>
+      <c r="AO5">
+        <v>7.6</v>
+      </c>
+      <c r="AP5">
+        <v>13</v>
+      </c>
+      <c r="AQ5">
+        <v>13</v>
+      </c>
+      <c r="AR5">
+        <v>13</v>
+      </c>
+      <c r="AS5">
+        <v>13</v>
+      </c>
+      <c r="AT5">
+        <v>13</v>
+      </c>
+      <c r="AU5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV5">
+        <v>6</v>
+      </c>
+      <c r="AW5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX5">
+        <v>13</v>
+      </c>
+      <c r="AY5">
+        <v>10.5</v>
+      </c>
+      <c r="AZ5">
+        <v>6.8</v>
+      </c>
+      <c r="BA5">
+        <v>10</v>
+      </c>
+      <c r="BB5">
+        <v>13</v>
+      </c>
+      <c r="BC5">
+        <v>27</v>
+      </c>
+      <c r="BD5">
+        <v>18</v>
+      </c>
+      <c r="BE5">
+        <v>25</v>
+      </c>
+      <c r="BF5">
+        <v>26</v>
+      </c>
+      <c r="BG5">
+        <v>7</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>11</v>
+      </c>
+      <c r="BJ5">
         <v>1.9</v>
       </c>
-      <c r="J5">
-        <v>3.9</v>
-      </c>
-      <c r="K5">
+      <c r="BK5">
+        <v>1.73</v>
+      </c>
+      <c r="BL5">
+        <v>26</v>
+      </c>
+      <c r="BM5">
+        <v>20</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>11</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>11</v>
+      </c>
+      <c r="BR5">
+        <v>10</v>
+      </c>
+      <c r="BS5">
+        <v>7.6</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>11</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>11</v>
+      </c>
+      <c r="BX5">
+        <v>5.1</v>
+      </c>
+      <c r="BY5">
         <v>4.1</v>
-      </c>
-      <c r="L5">
-        <v>1.37</v>
-      </c>
-      <c r="M5">
-        <v>1.06</v>
-      </c>
-      <c r="N5">
-        <v>4.2</v>
-      </c>
-      <c r="O5">
-        <v>1.27</v>
-      </c>
-      <c r="P5">
-        <v>2.12</v>
-      </c>
-      <c r="Q5">
-        <v>1.82</v>
-      </c>
-      <c r="R5">
-        <v>1.44</v>
-      </c>
-      <c r="S5">
-        <v>3.1</v>
-      </c>
-      <c r="T5">
-        <v>1.76</v>
-      </c>
-      <c r="U5">
-        <v>2.1</v>
-      </c>
-      <c r="V5">
-        <v>2.1</v>
-      </c>
-      <c r="W5">
-        <v>1.27</v>
-      </c>
-      <c r="X5">
-        <v>17.5</v>
-      </c>
-      <c r="Y5">
-        <v>10</v>
-      </c>
-      <c r="Z5">
-        <v>12</v>
-      </c>
-      <c r="AA5">
-        <v>21</v>
-      </c>
-      <c r="AB5">
-        <v>18.5</v>
-      </c>
-      <c r="AC5">
-        <v>9.4</v>
-      </c>
-      <c r="AD5">
-        <v>10.5</v>
-      </c>
-      <c r="AE5">
-        <v>19.5</v>
-      </c>
-      <c r="AF5">
-        <v>42</v>
-      </c>
-      <c r="AG5">
-        <v>18.5</v>
-      </c>
-      <c r="AH5">
-        <v>19.5</v>
-      </c>
-      <c r="AI5">
-        <v>34</v>
-      </c>
-      <c r="AJ5">
-        <v>110</v>
-      </c>
-      <c r="AK5">
-        <v>60</v>
-      </c>
-      <c r="AL5">
-        <v>80</v>
-      </c>
-      <c r="AM5">
-        <v>110</v>
-      </c>
-      <c r="AN5">
-        <v>60</v>
-      </c>
-      <c r="AO5">
-        <v>11.5</v>
-      </c>
-      <c r="AP5">
-        <v>15</v>
-      </c>
-      <c r="AQ5">
-        <v>8.6</v>
-      </c>
-      <c r="AR5">
-        <v>10.5</v>
-      </c>
-      <c r="AS5">
-        <v>17.5</v>
-      </c>
-      <c r="AT5">
-        <v>16.5</v>
-      </c>
-      <c r="AU5">
-        <v>8</v>
-      </c>
-      <c r="AV5">
-        <v>9</v>
-      </c>
-      <c r="AW5">
-        <v>16.5</v>
-      </c>
-      <c r="AX5">
-        <v>30</v>
-      </c>
-      <c r="AY5">
-        <v>16</v>
-      </c>
-      <c r="AZ5">
-        <v>16.5</v>
-      </c>
-      <c r="BA5">
-        <v>23</v>
-      </c>
-      <c r="BB5">
-        <v>55</v>
-      </c>
-      <c r="BC5">
-        <v>46</v>
-      </c>
-      <c r="BD5">
-        <v>38</v>
-      </c>
-      <c r="BE5">
-        <v>60</v>
-      </c>
-      <c r="BF5">
-        <v>40</v>
-      </c>
-      <c r="BG5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BH5">
-        <v>3.75</v>
-      </c>
-      <c r="BI5">
-        <v>3.3</v>
-      </c>
-      <c r="BJ5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK5">
-        <v>5.8</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>12</v>
-      </c>
-      <c r="BN5">
-        <v>8.4</v>
-      </c>
-      <c r="BO5">
-        <v>5.5</v>
-      </c>
-      <c r="BP5">
-        <v>1000</v>
-      </c>
-      <c r="BQ5">
-        <v>10</v>
-      </c>
-      <c r="BR5">
-        <v>44</v>
-      </c>
-      <c r="BS5">
-        <v>10</v>
-      </c>
-      <c r="BT5">
-        <v>4.7</v>
-      </c>
-      <c r="BU5">
-        <v>4</v>
-      </c>
-      <c r="BV5">
-        <v>12.5</v>
-      </c>
-      <c r="BW5">
-        <v>6.4</v>
-      </c>
-      <c r="BX5">
-        <v>26</v>
-      </c>
-      <c r="BY5">
-        <v>8.800000000000001</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -2163,226 +2163,226 @@
         <v>163</v>
       </c>
       <c r="F6">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>1.52</v>
+      </c>
+      <c r="I6">
+        <v>1.54</v>
+      </c>
+      <c r="J6">
+        <v>4.2</v>
+      </c>
+      <c r="K6">
+        <v>4.4</v>
+      </c>
+      <c r="L6">
+        <v>1.55</v>
+      </c>
+      <c r="M6">
+        <v>1.09</v>
+      </c>
+      <c r="N6">
+        <v>3.6</v>
+      </c>
+      <c r="O6">
+        <v>1.36</v>
+      </c>
+      <c r="P6">
+        <v>1.8</v>
+      </c>
+      <c r="Q6">
+        <v>2.18</v>
+      </c>
+      <c r="R6">
+        <v>1.3</v>
+      </c>
+      <c r="S6">
+        <v>4.1</v>
+      </c>
+      <c r="T6">
+        <v>2.28</v>
+      </c>
+      <c r="U6">
+        <v>1.69</v>
+      </c>
+      <c r="V6">
+        <v>2.8</v>
+      </c>
+      <c r="W6">
+        <v>1.13</v>
+      </c>
+      <c r="X6">
+        <v>13.5</v>
+      </c>
+      <c r="Y6">
+        <v>6.6</v>
+      </c>
+      <c r="Z6">
+        <v>7.4</v>
+      </c>
+      <c r="AA6">
+        <v>12.5</v>
+      </c>
+      <c r="AB6">
+        <v>25</v>
+      </c>
+      <c r="AC6">
         <v>10.5</v>
       </c>
-      <c r="H6">
-        <v>1.41</v>
-      </c>
-      <c r="I6">
-        <v>1.44</v>
-      </c>
-      <c r="J6">
-        <v>4.9</v>
-      </c>
-      <c r="K6">
-        <v>5.1</v>
-      </c>
-      <c r="L6">
-        <v>1.34</v>
-      </c>
-      <c r="M6">
-        <v>1.05</v>
-      </c>
-      <c r="N6">
-        <v>4.4</v>
-      </c>
-      <c r="O6">
-        <v>1.26</v>
-      </c>
-      <c r="P6">
-        <v>2.18</v>
-      </c>
-      <c r="Q6">
-        <v>1.78</v>
-      </c>
-      <c r="R6">
-        <v>1.46</v>
-      </c>
-      <c r="S6">
-        <v>3</v>
-      </c>
-      <c r="T6">
-        <v>2.02</v>
-      </c>
-      <c r="U6">
-        <v>1.87</v>
-      </c>
-      <c r="V6">
-        <v>3.2</v>
-      </c>
-      <c r="W6">
-        <v>1.1</v>
-      </c>
-      <c r="X6">
+      <c r="AD6">
+        <v>10.5</v>
+      </c>
+      <c r="AE6">
         <v>18.5</v>
       </c>
-      <c r="Y6">
-        <v>8.4</v>
-      </c>
-      <c r="Z6">
-        <v>8.6</v>
-      </c>
-      <c r="AA6">
-        <v>12</v>
-      </c>
-      <c r="AB6">
-        <v>34</v>
-      </c>
-      <c r="AC6">
-        <v>11.5</v>
-      </c>
-      <c r="AD6">
-        <v>10</v>
-      </c>
-      <c r="AE6">
-        <v>15</v>
-      </c>
       <c r="AF6">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AG6">
         <v>36</v>
       </c>
       <c r="AH6">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AI6">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AJ6">
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="AK6">
         <v>210</v>
       </c>
       <c r="AL6">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AM6">
-        <v>390</v>
+        <v>310</v>
       </c>
       <c r="AN6">
-        <v>200</v>
+        <v>420</v>
       </c>
       <c r="AO6">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="AP6">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AQ6">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AR6">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS6">
         <v>10.5</v>
       </c>
       <c r="AT6">
+        <v>23</v>
+      </c>
+      <c r="AU6">
+        <v>9.4</v>
+      </c>
+      <c r="AV6">
+        <v>9.6</v>
+      </c>
+      <c r="AW6">
+        <v>16.5</v>
+      </c>
+      <c r="AX6">
+        <v>70</v>
+      </c>
+      <c r="AY6">
+        <v>32</v>
+      </c>
+      <c r="AZ6">
+        <v>28</v>
+      </c>
+      <c r="BA6">
+        <v>46</v>
+      </c>
+      <c r="BB6">
+        <v>260</v>
+      </c>
+      <c r="BC6">
+        <v>150</v>
+      </c>
+      <c r="BD6">
+        <v>130</v>
+      </c>
+      <c r="BE6">
+        <v>170</v>
+      </c>
+      <c r="BF6">
+        <v>230</v>
+      </c>
+      <c r="BG6">
+        <v>8.4</v>
+      </c>
+      <c r="BH6">
+        <v>3</v>
+      </c>
+      <c r="BI6">
+        <v>2.9</v>
+      </c>
+      <c r="BJ6">
+        <v>28</v>
+      </c>
+      <c r="BK6">
+        <v>12.5</v>
+      </c>
+      <c r="BL6">
+        <v>320</v>
+      </c>
+      <c r="BM6">
+        <v>170</v>
+      </c>
+      <c r="BN6">
+        <v>12.5</v>
+      </c>
+      <c r="BO6">
+        <v>10.5</v>
+      </c>
+      <c r="BP6">
+        <v>120</v>
+      </c>
+      <c r="BQ6">
+        <v>90</v>
+      </c>
+      <c r="BR6">
+        <v>140</v>
+      </c>
+      <c r="BS6">
+        <v>100</v>
+      </c>
+      <c r="BT6">
+        <v>3.55</v>
+      </c>
+      <c r="BU6">
+        <v>3.25</v>
+      </c>
+      <c r="BV6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BW6">
+        <v>8.6</v>
+      </c>
+      <c r="BX6">
+        <v>38</v>
+      </c>
+      <c r="BY6">
+        <v>34</v>
+      </c>
+      <c r="BZ6">
         <v>27</v>
       </c>
-      <c r="AU6">
-        <v>10</v>
-      </c>
-      <c r="AV6">
-        <v>9.4</v>
-      </c>
-      <c r="AW6">
-        <v>13</v>
-      </c>
-      <c r="AX6">
-        <v>60</v>
-      </c>
-      <c r="AY6">
-        <v>30</v>
-      </c>
-      <c r="AZ6">
-        <v>24</v>
-      </c>
-      <c r="BA6">
-        <v>32</v>
-      </c>
-      <c r="BB6">
-        <v>46</v>
-      </c>
-      <c r="BC6">
-        <v>90</v>
-      </c>
-      <c r="BD6">
-        <v>75</v>
-      </c>
-      <c r="BE6">
-        <v>85</v>
-      </c>
-      <c r="BF6">
-        <v>110</v>
-      </c>
-      <c r="BG6">
-        <v>5.9</v>
-      </c>
-      <c r="BH6">
-        <v>4</v>
-      </c>
-      <c r="BI6">
-        <v>3.5</v>
-      </c>
-      <c r="BJ6">
-        <v>12</v>
-      </c>
-      <c r="BK6">
-        <v>6</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>11.5</v>
-      </c>
-      <c r="BN6">
-        <v>13</v>
-      </c>
-      <c r="BO6">
-        <v>6.4</v>
-      </c>
-      <c r="BP6">
-        <v>1000</v>
-      </c>
-      <c r="BQ6">
-        <v>10.5</v>
-      </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>10.5</v>
-      </c>
-      <c r="BT6">
-        <v>3.95</v>
-      </c>
-      <c r="BU6">
-        <v>3.55</v>
-      </c>
-      <c r="BV6">
-        <v>8.6</v>
-      </c>
-      <c r="BW6">
-        <v>7.4</v>
-      </c>
-      <c r="BX6">
-        <v>25</v>
-      </c>
-      <c r="BY6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BZ6">
-        <v>14.5</v>
-      </c>
       <c r="CA6">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="CB6" t="s">
         <v>195</v>
@@ -2405,226 +2405,226 @@
         <v>164</v>
       </c>
       <c r="F7">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="G7">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="H7">
-        <v>1.86</v>
+        <v>1.51</v>
       </c>
       <c r="I7">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="J7">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>15.5</v>
+      </c>
+      <c r="O7">
         <v>1.06</v>
       </c>
-      <c r="N7">
-        <v>4.2</v>
-      </c>
-      <c r="O7">
-        <v>1.28</v>
-      </c>
       <c r="P7">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="Q7">
-        <v>1.87</v>
+        <v>1.3</v>
       </c>
       <c r="R7">
-        <v>1.42</v>
+        <v>2.02</v>
       </c>
       <c r="S7">
-        <v>3.25</v>
+        <v>1.92</v>
       </c>
       <c r="T7">
-        <v>1.76</v>
+        <v>1.35</v>
       </c>
       <c r="U7">
-        <v>2.16</v>
+        <v>3.6</v>
       </c>
       <c r="V7">
-        <v>2.1</v>
+        <v>2.84</v>
       </c>
       <c r="W7">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="X7">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="Z7">
         <v>12</v>
       </c>
       <c r="AA7">
+        <v>16</v>
+      </c>
+      <c r="AB7">
+        <v>1000</v>
+      </c>
+      <c r="AC7">
+        <v>13</v>
+      </c>
+      <c r="AD7">
+        <v>8.4</v>
+      </c>
+      <c r="AE7">
+        <v>12</v>
+      </c>
+      <c r="AF7">
+        <v>1000</v>
+      </c>
+      <c r="AG7">
         <v>21</v>
       </c>
-      <c r="AB7">
+      <c r="AH7">
+        <v>12.5</v>
+      </c>
+      <c r="AI7">
         <v>18.5</v>
       </c>
-      <c r="AC7">
-        <v>9</v>
-      </c>
-      <c r="AD7">
-        <v>10</v>
-      </c>
-      <c r="AE7">
-        <v>19.5</v>
-      </c>
-      <c r="AF7">
-        <v>38</v>
-      </c>
-      <c r="AG7">
-        <v>19.5</v>
-      </c>
-      <c r="AH7">
-        <v>17.5</v>
-      </c>
-      <c r="AI7">
-        <v>34</v>
-      </c>
       <c r="AJ7">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL7">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AM7">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AN7">
-        <v>600</v>
+        <v>48</v>
       </c>
       <c r="AO7">
+        <v>6.6</v>
+      </c>
+      <c r="AP7">
         <v>12</v>
       </c>
-      <c r="AP7">
-        <v>14</v>
-      </c>
       <c r="AQ7">
-        <v>8.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="AR7">
         <v>10.5</v>
       </c>
       <c r="AS7">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AT7">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="AU7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AV7">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AW7">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AX7">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="AY7">
         <v>16.5</v>
       </c>
       <c r="AZ7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA7">
-        <v>28</v>
+        <v>15.5</v>
       </c>
       <c r="BB7">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="BC7">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="BD7">
         <v>26</v>
       </c>
       <c r="BE7">
-        <v>13.5</v>
+        <v>34</v>
       </c>
       <c r="BF7">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="BG7">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="BH7">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.96</v>
+        <v>11.5</v>
       </c>
       <c r="BJ7">
-        <v>9.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="BK7">
+        <v>5.2</v>
+      </c>
+      <c r="BL7">
+        <v>48</v>
+      </c>
+      <c r="BM7">
+        <v>36</v>
+      </c>
+      <c r="BN7">
+        <v>1000</v>
+      </c>
+      <c r="BO7">
+        <v>11.5</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>11.5</v>
+      </c>
+      <c r="BR7">
+        <v>29</v>
+      </c>
+      <c r="BS7">
+        <v>21</v>
+      </c>
+      <c r="BT7">
+        <v>3.05</v>
+      </c>
+      <c r="BU7">
+        <v>2.88</v>
+      </c>
+      <c r="BV7">
         <v>5.3</v>
       </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
+      <c r="BW7">
+        <v>4.8</v>
+      </c>
+      <c r="BX7">
         <v>10.5</v>
       </c>
-      <c r="BN7">
-        <v>8</v>
-      </c>
-      <c r="BO7">
-        <v>4.8</v>
-      </c>
-      <c r="BP7">
-        <v>1000</v>
-      </c>
-      <c r="BQ7">
-        <v>9</v>
-      </c>
-      <c r="BR7">
-        <v>44</v>
-      </c>
-      <c r="BS7">
+      <c r="BY7">
         <v>9.4</v>
       </c>
-      <c r="BT7">
-        <v>4.8</v>
-      </c>
-      <c r="BU7">
-        <v>4.1</v>
-      </c>
-      <c r="BV7">
-        <v>13</v>
-      </c>
-      <c r="BW7">
-        <v>6.2</v>
-      </c>
-      <c r="BX7">
-        <v>27</v>
-      </c>
-      <c r="BY7">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BZ7">
-        <v>22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="s">
         <v>195</v>
@@ -2647,220 +2647,220 @@
         <v>165</v>
       </c>
       <c r="F8">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="G8">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="H8">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="I8">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="J8">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K8">
+        <v>3.6</v>
+      </c>
+      <c r="L8">
+        <v>1.56</v>
+      </c>
+      <c r="M8">
+        <v>1.08</v>
+      </c>
+      <c r="N8">
+        <v>3.5</v>
+      </c>
+      <c r="O8">
+        <v>1.37</v>
+      </c>
+      <c r="P8">
+        <v>1.81</v>
+      </c>
+      <c r="Q8">
+        <v>2.14</v>
+      </c>
+      <c r="R8">
+        <v>1.32</v>
+      </c>
+      <c r="S8">
         <v>3.9</v>
       </c>
-      <c r="L8">
-        <v>1.39</v>
-      </c>
-      <c r="M8">
-        <v>1.06</v>
-      </c>
-      <c r="N8">
-        <v>4</v>
-      </c>
-      <c r="O8">
-        <v>1.3</v>
-      </c>
-      <c r="P8">
-        <v>2.04</v>
-      </c>
-      <c r="Q8">
-        <v>1.9</v>
-      </c>
-      <c r="R8">
-        <v>1.39</v>
-      </c>
-      <c r="S8">
-        <v>3.3</v>
-      </c>
       <c r="T8">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="U8">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="V8">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="W8">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="X8">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Y8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z8">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA8">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB8">
         <v>12.5</v>
       </c>
       <c r="AC8">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE8">
         <v>28</v>
       </c>
       <c r="AF8">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AG8">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AH8">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI8">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AJ8">
-        <v>900</v>
+        <v>70</v>
       </c>
       <c r="AK8">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AL8">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AM8">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="AN8">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AO8">
         <v>22</v>
       </c>
       <c r="AP8">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ8">
+        <v>9</v>
+      </c>
+      <c r="AR8">
+        <v>13</v>
+      </c>
+      <c r="AS8">
+        <v>28</v>
+      </c>
+      <c r="AT8">
         <v>10.5</v>
       </c>
-      <c r="AR8">
-        <v>15</v>
-      </c>
-      <c r="AS8">
-        <v>32</v>
-      </c>
-      <c r="AT8">
-        <v>11.5</v>
-      </c>
       <c r="AU8">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW8">
         <v>23</v>
       </c>
       <c r="AX8">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AY8">
+        <v>12.5</v>
+      </c>
+      <c r="AZ8">
+        <v>7.4</v>
+      </c>
+      <c r="BA8">
+        <v>34</v>
+      </c>
+      <c r="BB8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC8">
+        <v>32</v>
+      </c>
+      <c r="BD8">
+        <v>42</v>
+      </c>
+      <c r="BE8">
+        <v>85</v>
+      </c>
+      <c r="BF8">
+        <v>34</v>
+      </c>
+      <c r="BG8">
+        <v>19</v>
+      </c>
+      <c r="BH8">
+        <v>2.94</v>
+      </c>
+      <c r="BI8">
+        <v>2.62</v>
+      </c>
+      <c r="BJ8">
         <v>11</v>
       </c>
-      <c r="AZ8">
-        <v>15</v>
-      </c>
-      <c r="BA8">
-        <v>32</v>
-      </c>
-      <c r="BB8">
-        <v>38</v>
-      </c>
-      <c r="BC8">
-        <v>28</v>
-      </c>
-      <c r="BD8">
-        <v>36</v>
-      </c>
-      <c r="BE8">
-        <v>11.5</v>
-      </c>
-      <c r="BF8">
-        <v>23</v>
-      </c>
-      <c r="BG8">
-        <v>18.5</v>
-      </c>
-      <c r="BH8">
-        <v>3.6</v>
-      </c>
-      <c r="BI8">
-        <v>3.1</v>
-      </c>
-      <c r="BJ8">
-        <v>9.6</v>
-      </c>
       <c r="BK8">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="BM8">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="BN8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO8">
         <v>5.3</v>
       </c>
       <c r="BP8">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="BQ8">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="BR8">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BS8">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT8">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BU8">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BV8">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>7.2</v>
+        <v>17</v>
       </c>
       <c r="BX8">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BY8">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2889,82 +2889,82 @@
         <v>166</v>
       </c>
       <c r="F9">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="G9">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="H9">
+        <v>4.1</v>
+      </c>
+      <c r="I9">
         <v>4.4</v>
       </c>
-      <c r="I9">
-        <v>4.6</v>
-      </c>
       <c r="J9">
+        <v>3.35</v>
+      </c>
+      <c r="K9">
+        <v>3.6</v>
+      </c>
+      <c r="L9">
+        <v>1.58</v>
+      </c>
+      <c r="M9">
+        <v>1.09</v>
+      </c>
+      <c r="N9">
         <v>3.85</v>
       </c>
-      <c r="K9">
-        <v>4.1</v>
-      </c>
-      <c r="L9">
-        <v>1.41</v>
-      </c>
-      <c r="M9">
-        <v>1.06</v>
-      </c>
-      <c r="N9">
-        <v>4.1</v>
-      </c>
       <c r="O9">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="P9">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="Q9">
-        <v>1.92</v>
+        <v>1.35</v>
       </c>
       <c r="R9">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="S9">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="T9">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W9">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="X9">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="Y9">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Z9">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AA9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB9">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC9">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD9">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE9">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AF9">
         <v>12</v>
@@ -2973,142 +2973,142 @@
         <v>11</v>
       </c>
       <c r="AH9">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AI9">
+        <v>85</v>
+      </c>
+      <c r="AJ9">
+        <v>34</v>
+      </c>
+      <c r="AK9">
+        <v>23</v>
+      </c>
+      <c r="AL9">
+        <v>55</v>
+      </c>
+      <c r="AM9">
+        <v>150</v>
+      </c>
+      <c r="AN9">
+        <v>21</v>
+      </c>
+      <c r="AO9">
+        <v>80</v>
+      </c>
+      <c r="AP9">
+        <v>10.5</v>
+      </c>
+      <c r="AQ9">
+        <v>12.5</v>
+      </c>
+      <c r="AR9">
+        <v>26</v>
+      </c>
+      <c r="AS9">
+        <v>70</v>
+      </c>
+      <c r="AT9">
+        <v>7.6</v>
+      </c>
+      <c r="AU9">
+        <v>6.8</v>
+      </c>
+      <c r="AV9">
+        <v>16</v>
+      </c>
+      <c r="AW9">
+        <v>48</v>
+      </c>
+      <c r="AX9">
+        <v>10.5</v>
+      </c>
+      <c r="AY9">
+        <v>10</v>
+      </c>
+      <c r="AZ9">
+        <v>18.5</v>
+      </c>
+      <c r="BA9">
         <v>65</v>
       </c>
-      <c r="AJ9">
-        <v>23</v>
-      </c>
-      <c r="AK9">
-        <v>19</v>
-      </c>
-      <c r="AL9">
-        <v>40</v>
-      </c>
-      <c r="AM9">
+      <c r="BB9">
+        <v>21</v>
+      </c>
+      <c r="BC9">
+        <v>19.5</v>
+      </c>
+      <c r="BD9">
+        <v>42</v>
+      </c>
+      <c r="BE9">
         <v>110</v>
       </c>
-      <c r="AN9">
-        <v>12.5</v>
-      </c>
-      <c r="AO9">
-        <v>60</v>
-      </c>
-      <c r="AP9">
-        <v>14</v>
-      </c>
-      <c r="AQ9">
-        <v>14.5</v>
-      </c>
-      <c r="AR9">
-        <v>30</v>
-      </c>
-      <c r="AS9">
-        <v>34</v>
-      </c>
-      <c r="AT9">
-        <v>9</v>
-      </c>
-      <c r="AU9">
-        <v>7.6</v>
-      </c>
-      <c r="AV9">
-        <v>15.5</v>
-      </c>
-      <c r="AW9">
-        <v>46</v>
-      </c>
-      <c r="AX9">
-        <v>10</v>
-      </c>
-      <c r="AY9">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ9">
-        <v>18</v>
-      </c>
-      <c r="BA9">
-        <v>50</v>
-      </c>
-      <c r="BB9">
-        <v>19</v>
-      </c>
-      <c r="BC9">
-        <v>17</v>
-      </c>
-      <c r="BD9">
-        <v>20</v>
-      </c>
-      <c r="BE9">
-        <v>15</v>
-      </c>
       <c r="BF9">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BG9">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BH9">
-        <v>3.5</v>
+        <v>2.76</v>
       </c>
       <c r="BI9">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="BJ9">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BK9">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BM9">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN9">
         <v>4.6</v>
       </c>
       <c r="BO9">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP9">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="BQ9">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="BR9">
+        <v>46</v>
+      </c>
+      <c r="BS9">
+        <v>36</v>
+      </c>
+      <c r="BT9">
+        <v>7.2</v>
+      </c>
+      <c r="BU9">
+        <v>6.4</v>
+      </c>
+      <c r="BV9">
+        <v>44</v>
+      </c>
+      <c r="BW9">
+        <v>32</v>
+      </c>
+      <c r="BX9">
+        <v>950</v>
+      </c>
+      <c r="BY9">
+        <v>50</v>
+      </c>
+      <c r="BZ9">
+        <v>55</v>
+      </c>
+      <c r="CA9">
         <v>27</v>
-      </c>
-      <c r="BS9">
-        <v>10.5</v>
-      </c>
-      <c r="BT9">
-        <v>7.8</v>
-      </c>
-      <c r="BU9">
-        <v>6</v>
-      </c>
-      <c r="BV9">
-        <v>1000</v>
-      </c>
-      <c r="BW9">
-        <v>12</v>
-      </c>
-      <c r="BX9">
-        <v>1000</v>
-      </c>
-      <c r="BY9">
-        <v>12.5</v>
-      </c>
-      <c r="BZ9">
-        <v>23</v>
-      </c>
-      <c r="CA9">
-        <v>10</v>
       </c>
       <c r="CB9" t="s">
         <v>195</v>
@@ -3131,19 +3131,19 @@
         <v>167</v>
       </c>
       <c r="F10">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G10">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H10">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="I10">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J10">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K10">
         <v>3.8</v>
@@ -3155,13 +3155,13 @@
         <v>1.05</v>
       </c>
       <c r="N10">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O10">
         <v>1.24</v>
       </c>
       <c r="P10">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q10">
         <v>1.74</v>
@@ -3170,28 +3170,28 @@
         <v>1.53</v>
       </c>
       <c r="S10">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T10">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U10">
         <v>2.5</v>
       </c>
       <c r="V10">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W10">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X10">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y10">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z10">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA10">
         <v>36</v>
@@ -3200,19 +3200,19 @@
         <v>15</v>
       </c>
       <c r="AC10">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE10">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AF10">
         <v>22</v>
       </c>
       <c r="AG10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH10">
         <v>15</v>
@@ -3233,37 +3233,37 @@
         <v>70</v>
       </c>
       <c r="AN10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO10">
+        <v>16.5</v>
+      </c>
+      <c r="AP10">
         <v>17</v>
       </c>
-      <c r="AP10">
-        <v>16.5</v>
-      </c>
       <c r="AQ10">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR10">
         <v>16.5</v>
       </c>
       <c r="AS10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV10">
         <v>10.5</v>
       </c>
       <c r="AW10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX10">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY10">
         <v>11.5</v>
@@ -3272,31 +3272,31 @@
         <v>13.5</v>
       </c>
       <c r="BA10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE10">
         <v>50</v>
       </c>
       <c r="BF10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BG10">
         <v>15</v>
       </c>
       <c r="BH10">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI10">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="BJ10">
         <v>8.800000000000001</v>
@@ -3311,22 +3311,22 @@
         <v>12</v>
       </c>
       <c r="BN10">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO10">
         <v>5.5</v>
       </c>
       <c r="BP10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR10">
         <v>30</v>
       </c>
       <c r="BS10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT10">
         <v>5.8</v>
@@ -3335,22 +3335,22 @@
         <v>5.1</v>
       </c>
       <c r="BV10">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BW10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX10">
         <v>28</v>
       </c>
       <c r="BY10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB10" t="s">
         <v>195</v>
@@ -3373,16 +3373,16 @@
         <v>168</v>
       </c>
       <c r="F11">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G11">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="H11">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J11">
         <v>4.3</v>
@@ -3400,19 +3400,19 @@
         <v>7</v>
       </c>
       <c r="O11">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P11">
         <v>3</v>
       </c>
       <c r="Q11">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R11">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="S11">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T11">
         <v>1.5</v>
@@ -3421,16 +3421,16 @@
         <v>2.96</v>
       </c>
       <c r="V11">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W11">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="X11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y11">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z11">
         <v>36</v>
@@ -3442,16 +3442,16 @@
         <v>16</v>
       </c>
       <c r="AC11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE11">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG11">
         <v>10.5</v>
@@ -3466,13 +3466,13 @@
         <v>23</v>
       </c>
       <c r="AK11">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL11">
         <v>23</v>
       </c>
       <c r="AM11">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AN11">
         <v>7.4</v>
@@ -3484,28 +3484,28 @@
         <v>28</v>
       </c>
       <c r="AQ11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR11">
         <v>32</v>
       </c>
       <c r="AS11">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AT11">
         <v>15</v>
       </c>
       <c r="AU11">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AV11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW11">
         <v>36</v>
       </c>
       <c r="AX11">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY11">
         <v>10</v>
@@ -3514,52 +3514,52 @@
         <v>13.5</v>
       </c>
       <c r="BA11">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BB11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC11">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE11">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BF11">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI11">
         <v>4.5</v>
       </c>
       <c r="BJ11">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK11">
         <v>7.6</v>
       </c>
       <c r="BL11">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BM11">
         <v>48</v>
       </c>
       <c r="BN11">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ11">
         <v>10.5</v>
@@ -3568,7 +3568,7 @@
         <v>19</v>
       </c>
       <c r="BS11">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BT11">
         <v>7.8</v>
@@ -3577,19 +3577,19 @@
         <v>7</v>
       </c>
       <c r="BV11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BW11">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BX11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY11">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BZ11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA11">
         <v>11</v>
@@ -3615,22 +3615,22 @@
         <v>169</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G12">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="H12">
+        <v>3.65</v>
+      </c>
+      <c r="I12">
         <v>3.8</v>
       </c>
-      <c r="I12">
-        <v>4</v>
-      </c>
       <c r="J12">
+        <v>3.9</v>
+      </c>
+      <c r="K12">
         <v>3.95</v>
-      </c>
-      <c r="K12">
-        <v>4.2</v>
       </c>
       <c r="L12">
         <v>1.34</v>
@@ -3648,37 +3648,37 @@
         <v>2.3</v>
       </c>
       <c r="Q12">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R12">
         <v>1.5</v>
       </c>
       <c r="S12">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T12">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U12">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="X12">
         <v>21</v>
       </c>
       <c r="Y12">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z12">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA12">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB12">
         <v>12</v>
@@ -3687,22 +3687,22 @@
         <v>9.4</v>
       </c>
       <c r="AD12">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE12">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AF12">
         <v>14.5</v>
       </c>
       <c r="AG12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH12">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI12">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ12">
         <v>25</v>
@@ -3714,13 +3714,13 @@
         <v>32</v>
       </c>
       <c r="AM12">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AN12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO12">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AP12">
         <v>17</v>
@@ -3729,22 +3729,22 @@
         <v>15.5</v>
       </c>
       <c r="AR12">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="AS12">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="AT12">
         <v>10</v>
       </c>
       <c r="AU12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW12">
-        <v>29</v>
+        <v>18.5</v>
       </c>
       <c r="AX12">
         <v>12</v>
@@ -3756,85 +3756,85 @@
         <v>14</v>
       </c>
       <c r="BA12">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BB12">
         <v>20</v>
       </c>
       <c r="BC12">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BD12">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="BE12">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="BF12">
         <v>10</v>
       </c>
       <c r="BG12">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI12">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK12">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB12" t="s">
         <v>195</v>
@@ -3857,19 +3857,19 @@
         <v>170</v>
       </c>
       <c r="F13">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G13">
         <v>1.43</v>
       </c>
       <c r="H13">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I13">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J13">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K13">
         <v>6.2</v>
@@ -3881,169 +3881,169 @@
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O13">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P13">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q13">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S13">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="T13">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="U13">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="V13">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W13">
         <v>3.3</v>
       </c>
       <c r="X13">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Y13">
-        <v>65</v>
+        <v>950</v>
       </c>
       <c r="Z13">
         <v>170</v>
       </c>
       <c r="AA13">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AB13">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AC13">
         <v>16</v>
       </c>
       <c r="AD13">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AE13">
         <v>170</v>
       </c>
       <c r="AF13">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG13">
         <v>11.5</v>
       </c>
       <c r="AH13">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI13">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="AJ13">
         <v>15</v>
       </c>
       <c r="AK13">
+        <v>14</v>
+      </c>
+      <c r="AL13">
+        <v>30</v>
+      </c>
+      <c r="AM13">
+        <v>790</v>
+      </c>
+      <c r="AN13">
+        <v>3.9</v>
+      </c>
+      <c r="AO13">
+        <v>55</v>
+      </c>
+      <c r="AP13">
+        <v>11</v>
+      </c>
+      <c r="AQ13">
+        <v>20</v>
+      </c>
+      <c r="AR13">
+        <v>28</v>
+      </c>
+      <c r="AS13">
         <v>13.5</v>
       </c>
-      <c r="AL13">
-        <v>32</v>
-      </c>
-      <c r="AM13">
-        <v>80</v>
-      </c>
-      <c r="AN13">
-        <v>3.95</v>
-      </c>
-      <c r="AO13">
-        <v>75</v>
-      </c>
-      <c r="AP13">
-        <v>29</v>
-      </c>
-      <c r="AQ13">
-        <v>40</v>
-      </c>
-      <c r="AR13">
-        <v>40</v>
-      </c>
-      <c r="AS13">
+      <c r="AT13">
+        <v>17</v>
+      </c>
+      <c r="AU13">
+        <v>14</v>
+      </c>
+      <c r="AV13">
+        <v>23</v>
+      </c>
+      <c r="AW13">
         <v>12.5</v>
       </c>
-      <c r="AT13">
-        <v>14</v>
-      </c>
-      <c r="AU13">
-        <v>13.5</v>
-      </c>
-      <c r="AV13">
-        <v>25</v>
-      </c>
-      <c r="AW13">
-        <v>55</v>
-      </c>
       <c r="AX13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY13">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ13">
         <v>17.5</v>
       </c>
       <c r="BA13">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="BB13">
+        <v>13.5</v>
+      </c>
+      <c r="BC13">
+        <v>11.5</v>
+      </c>
+      <c r="BD13">
+        <v>19.5</v>
+      </c>
+      <c r="BE13">
         <v>12.5</v>
       </c>
-      <c r="BC13">
+      <c r="BF13">
+        <v>3.6</v>
+      </c>
+      <c r="BG13">
         <v>12</v>
       </c>
-      <c r="BD13">
-        <v>20</v>
-      </c>
-      <c r="BE13">
-        <v>46</v>
-      </c>
-      <c r="BF13">
-        <v>3.55</v>
-      </c>
-      <c r="BG13">
-        <v>40</v>
-      </c>
       <c r="BH13">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BI13">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BJ13">
         <v>9.6</v>
       </c>
       <c r="BK13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN13">
         <v>4.7</v>
       </c>
       <c r="BO13">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP13">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BQ13">
         <v>5.5</v>
@@ -4052,31 +4052,31 @@
         <v>16.5</v>
       </c>
       <c r="BS13">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT13">
         <v>11.5</v>
       </c>
       <c r="BU13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
+        <v>13</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
         <v>12.5</v>
       </c>
-      <c r="BX13">
-        <v>1000</v>
-      </c>
-      <c r="BY13">
-        <v>12</v>
-      </c>
       <c r="BZ13">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="CA13">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB13" t="s">
         <v>195</v>
@@ -4099,10 +4099,10 @@
         <v>171</v>
       </c>
       <c r="F14">
+        <v>1.56</v>
+      </c>
+      <c r="G14">
         <v>1.58</v>
-      </c>
-      <c r="G14">
-        <v>1.59</v>
       </c>
       <c r="H14">
         <v>6.4</v>
@@ -4111,118 +4111,118 @@
         <v>6.6</v>
       </c>
       <c r="J14">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K14">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L14">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M14">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O14">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P14">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q14">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R14">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S14">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="T14">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="U14">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V14">
         <v>1.17</v>
       </c>
       <c r="W14">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="X14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA14">
-        <v>180</v>
+        <v>690</v>
       </c>
       <c r="AB14">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC14">
         <v>10.5</v>
       </c>
       <c r="AD14">
+        <v>23</v>
+      </c>
+      <c r="AE14">
+        <v>80</v>
+      </c>
+      <c r="AF14">
+        <v>10</v>
+      </c>
+      <c r="AG14">
+        <v>9.6</v>
+      </c>
+      <c r="AH14">
+        <v>20</v>
+      </c>
+      <c r="AI14">
+        <v>80</v>
+      </c>
+      <c r="AJ14">
+        <v>14</v>
+      </c>
+      <c r="AK14">
+        <v>15</v>
+      </c>
+      <c r="AL14">
+        <v>30</v>
+      </c>
+      <c r="AM14">
+        <v>95</v>
+      </c>
+      <c r="AN14">
+        <v>6.8</v>
+      </c>
+      <c r="AO14">
+        <v>80</v>
+      </c>
+      <c r="AP14">
+        <v>20</v>
+      </c>
+      <c r="AQ14">
         <v>24</v>
       </c>
-      <c r="AE14">
-        <v>85</v>
-      </c>
-      <c r="AF14">
+      <c r="AR14">
+        <v>50</v>
+      </c>
+      <c r="AS14">
+        <v>110</v>
+      </c>
+      <c r="AT14">
+        <v>9.4</v>
+      </c>
+      <c r="AU14">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AG14">
-        <v>9.4</v>
-      </c>
-      <c r="AH14">
-        <v>21</v>
-      </c>
-      <c r="AI14">
-        <v>75</v>
-      </c>
-      <c r="AJ14">
-        <v>14.5</v>
-      </c>
-      <c r="AK14">
-        <v>15.5</v>
-      </c>
-      <c r="AL14">
-        <v>32</v>
-      </c>
-      <c r="AM14">
-        <v>100</v>
-      </c>
-      <c r="AN14">
-        <v>7.2</v>
-      </c>
-      <c r="AO14">
-        <v>90</v>
-      </c>
-      <c r="AP14">
-        <v>19</v>
-      </c>
-      <c r="AQ14">
-        <v>22</v>
-      </c>
-      <c r="AR14">
-        <v>48</v>
-      </c>
-      <c r="AS14">
-        <v>46</v>
-      </c>
-      <c r="AT14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU14">
-        <v>9.6</v>
       </c>
       <c r="AV14">
         <v>21</v>
@@ -4234,91 +4234,91 @@
         <v>9.6</v>
       </c>
       <c r="AY14">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA14">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB14">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC14">
         <v>14</v>
       </c>
       <c r="BD14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE14">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BF14">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG14">
         <v>70</v>
       </c>
       <c r="BH14">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BI14">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="BJ14">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BL14">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BM14">
         <v>90</v>
       </c>
       <c r="BN14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO14">
         <v>3.95</v>
       </c>
       <c r="BP14">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BQ14">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BS14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT14">
         <v>9.800000000000001</v>
       </c>
       <c r="BU14">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV14">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BW14">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BX14">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY14">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BZ14">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="CA14">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB14" t="s">
         <v>195</v>
@@ -4353,10 +4353,10 @@
         <v>5.1</v>
       </c>
       <c r="J15">
+        <v>4.3</v>
+      </c>
+      <c r="K15">
         <v>4.4</v>
-      </c>
-      <c r="K15">
-        <v>4.5</v>
       </c>
       <c r="L15">
         <v>1.31</v>
@@ -4365,28 +4365,28 @@
         <v>1.04</v>
       </c>
       <c r="N15">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O15">
         <v>1.22</v>
       </c>
       <c r="P15">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="Q15">
+        <v>1.63</v>
+      </c>
+      <c r="R15">
+        <v>1.6</v>
+      </c>
+      <c r="S15">
+        <v>2.6</v>
+      </c>
+      <c r="T15">
         <v>1.66</v>
       </c>
-      <c r="R15">
-        <v>1.59</v>
-      </c>
-      <c r="S15">
-        <v>2.64</v>
-      </c>
-      <c r="T15">
-        <v>1.69</v>
-      </c>
       <c r="U15">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V15">
         <v>1.24</v>
@@ -4395,13 +4395,13 @@
         <v>2.3</v>
       </c>
       <c r="X15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA15">
         <v>110</v>
@@ -4413,7 +4413,7 @@
         <v>10.5</v>
       </c>
       <c r="AD15">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE15">
         <v>55</v>
@@ -4422,13 +4422,13 @@
         <v>12.5</v>
       </c>
       <c r="AG15">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH15">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI15">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ15">
         <v>18</v>
@@ -4443,19 +4443,19 @@
         <v>70</v>
       </c>
       <c r="AN15">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AO15">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP15">
         <v>20</v>
       </c>
       <c r="AQ15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR15">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AS15">
         <v>85</v>
@@ -4479,43 +4479,43 @@
         <v>9.6</v>
       </c>
       <c r="AZ15">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA15">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB15">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC15">
         <v>15</v>
       </c>
       <c r="BD15">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE15">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF15">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG15">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BH15">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI15">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BJ15">
         <v>9.199999999999999</v>
       </c>
       <c r="BK15">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL15">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BM15">
         <v>70</v>
@@ -4524,43 +4524,43 @@
         <v>4.7</v>
       </c>
       <c r="BO15">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP15">
         <v>11</v>
       </c>
       <c r="BQ15">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS15">
-        <v>9.4</v>
+        <v>16.5</v>
       </c>
       <c r="BT15">
         <v>8.6</v>
       </c>
       <c r="BU15">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BV15">
         <v>36</v>
       </c>
       <c r="BW15">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX15">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY15">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="BZ15">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CB15" t="s">
         <v>195</v>
@@ -4583,16 +4583,16 @@
         <v>173</v>
       </c>
       <c r="F16">
+        <v>2.8</v>
+      </c>
+      <c r="G16">
+        <v>2.82</v>
+      </c>
+      <c r="H16">
+        <v>2.92</v>
+      </c>
+      <c r="I16">
         <v>2.96</v>
-      </c>
-      <c r="G16">
-        <v>3.05</v>
-      </c>
-      <c r="H16">
-        <v>2.72</v>
-      </c>
-      <c r="I16">
-        <v>2.78</v>
       </c>
       <c r="J16">
         <v>3.25</v>
@@ -4607,7 +4607,7 @@
         <v>1.1</v>
       </c>
       <c r="N16">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O16">
         <v>1.44</v>
@@ -4616,10 +4616,10 @@
         <v>1.72</v>
       </c>
       <c r="Q16">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R16">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S16">
         <v>4.5</v>
@@ -4628,130 +4628,130 @@
         <v>1.94</v>
       </c>
       <c r="U16">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V16">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="W16">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="X16">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y16">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z16">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AA16">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AB16">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC16">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD16">
+        <v>13</v>
+      </c>
+      <c r="AE16">
+        <v>38</v>
+      </c>
+      <c r="AF16">
+        <v>17.5</v>
+      </c>
+      <c r="AG16">
         <v>12.5</v>
-      </c>
-      <c r="AE16">
-        <v>34</v>
-      </c>
-      <c r="AF16">
-        <v>19</v>
-      </c>
-      <c r="AG16">
-        <v>13.5</v>
       </c>
       <c r="AH16">
         <v>19.5</v>
       </c>
       <c r="AI16">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ16">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AK16">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL16">
         <v>55</v>
       </c>
       <c r="AM16">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="AN16">
+        <v>36</v>
+      </c>
+      <c r="AO16">
         <v>40</v>
       </c>
-      <c r="AO16">
-        <v>34</v>
-      </c>
       <c r="AP16">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ16">
+        <v>9.4</v>
+      </c>
+      <c r="AR16">
+        <v>15.5</v>
+      </c>
+      <c r="AS16">
+        <v>42</v>
+      </c>
+      <c r="AT16">
         <v>8.6</v>
-      </c>
-      <c r="AR16">
-        <v>15</v>
-      </c>
-      <c r="AS16">
-        <v>38</v>
-      </c>
-      <c r="AT16">
-        <v>9.4</v>
       </c>
       <c r="AU16">
         <v>6.8</v>
       </c>
       <c r="AV16">
+        <v>12</v>
+      </c>
+      <c r="AW16">
+        <v>34</v>
+      </c>
+      <c r="AX16">
+        <v>15</v>
+      </c>
+      <c r="AY16">
         <v>11.5</v>
       </c>
-      <c r="AW16">
+      <c r="AZ16">
+        <v>17.5</v>
+      </c>
+      <c r="BA16">
+        <v>48</v>
+      </c>
+      <c r="BB16">
+        <v>38</v>
+      </c>
+      <c r="BC16">
         <v>30</v>
       </c>
-      <c r="AX16">
-        <v>17</v>
-      </c>
-      <c r="AY16">
-        <v>12</v>
-      </c>
-      <c r="AZ16">
-        <v>18</v>
-      </c>
-      <c r="BA16">
-        <v>44</v>
-      </c>
-      <c r="BB16">
-        <v>36</v>
-      </c>
-      <c r="BC16">
+      <c r="BD16">
         <v>34</v>
-      </c>
-      <c r="BD16">
-        <v>32</v>
       </c>
       <c r="BE16">
         <v>29</v>
       </c>
       <c r="BF16">
+        <v>30</v>
+      </c>
+      <c r="BG16">
         <v>34</v>
       </c>
-      <c r="BG16">
-        <v>30</v>
-      </c>
       <c r="BH16">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BI16">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK16">
         <v>6.6</v>
@@ -4760,43 +4760,43 @@
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>32</v>
+        <v>16.5</v>
       </c>
       <c r="BN16">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BO16">
+        <v>5.1</v>
+      </c>
+      <c r="BP16">
+        <v>23</v>
+      </c>
+      <c r="BQ16">
+        <v>10</v>
+      </c>
+      <c r="BR16">
+        <v>42</v>
+      </c>
+      <c r="BS16">
+        <v>12.5</v>
+      </c>
+      <c r="BT16">
+        <v>5.8</v>
+      </c>
+      <c r="BU16">
         <v>5.2</v>
       </c>
-      <c r="BP16">
+      <c r="BV16">
         <v>25</v>
-      </c>
-      <c r="BQ16">
-        <v>11</v>
-      </c>
-      <c r="BR16">
-        <v>1000</v>
-      </c>
-      <c r="BS16">
-        <v>13.5</v>
-      </c>
-      <c r="BT16">
-        <v>5.5</v>
-      </c>
-      <c r="BU16">
-        <v>5</v>
-      </c>
-      <c r="BV16">
-        <v>22</v>
       </c>
       <c r="BW16">
         <v>10.5</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY16">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4825,61 +4825,61 @@
         <v>174</v>
       </c>
       <c r="F17">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G17">
         <v>2.98</v>
       </c>
       <c r="H17">
+        <v>2.44</v>
+      </c>
+      <c r="I17">
         <v>2.46</v>
-      </c>
-      <c r="I17">
-        <v>2.5</v>
       </c>
       <c r="J17">
         <v>3.85</v>
       </c>
       <c r="K17">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L17">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M17">
         <v>1.03</v>
       </c>
       <c r="N17">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O17">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P17">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="Q17">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="R17">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S17">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="T17">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="U17">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="V17">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W17">
         <v>1.5</v>
       </c>
       <c r="X17">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y17">
         <v>17.5</v>
@@ -4891,7 +4891,7 @@
         <v>34</v>
       </c>
       <c r="AB17">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AC17">
         <v>9.6</v>
@@ -4903,10 +4903,10 @@
         <v>22</v>
       </c>
       <c r="AF17">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG17">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH17">
         <v>13.5</v>
@@ -4915,40 +4915,40 @@
         <v>27</v>
       </c>
       <c r="AJ17">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL17">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM17">
         <v>48</v>
       </c>
       <c r="AN17">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO17">
         <v>11.5</v>
       </c>
       <c r="AP17">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ17">
         <v>16</v>
       </c>
       <c r="AR17">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS17">
         <v>29</v>
       </c>
       <c r="AT17">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AU17">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV17">
         <v>11</v>
@@ -4957,7 +4957,7 @@
         <v>19.5</v>
       </c>
       <c r="AX17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY17">
         <v>12</v>
@@ -4966,7 +4966,7 @@
         <v>12.5</v>
       </c>
       <c r="BA17">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB17">
         <v>38</v>
@@ -4975,13 +4975,13 @@
         <v>24</v>
       </c>
       <c r="BD17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE17">
         <v>40</v>
       </c>
       <c r="BF17">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG17">
         <v>10.5</v>
@@ -4996,31 +4996,31 @@
         <v>8.4</v>
       </c>
       <c r="BK17">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL17">
         <v>65</v>
       </c>
       <c r="BM17">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN17">
         <v>6.6</v>
       </c>
       <c r="BO17">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BP17">
         <v>18.5</v>
       </c>
       <c r="BQ17">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BR17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS17">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT17">
         <v>6</v>
@@ -5032,19 +5032,19 @@
         <v>16</v>
       </c>
       <c r="BW17">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY17">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ17">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA17">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB17" t="s">
         <v>195</v>
@@ -5067,16 +5067,16 @@
         <v>175</v>
       </c>
       <c r="F18">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="G18">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H18">
         <v>3.35</v>
       </c>
       <c r="I18">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J18">
         <v>3.65</v>
@@ -5091,19 +5091,19 @@
         <v>1.05</v>
       </c>
       <c r="N18">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O18">
         <v>1.23</v>
       </c>
       <c r="P18">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q18">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R18">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S18">
         <v>2.84</v>
@@ -5112,13 +5112,13 @@
         <v>1.61</v>
       </c>
       <c r="U18">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V18">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="X18">
         <v>19</v>
@@ -5127,7 +5127,7 @@
         <v>17</v>
       </c>
       <c r="Z18">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA18">
         <v>60</v>
@@ -5154,10 +5154,10 @@
         <v>15</v>
       </c>
       <c r="AI18">
+        <v>42</v>
+      </c>
+      <c r="AJ18">
         <v>48</v>
-      </c>
-      <c r="AJ18">
-        <v>32</v>
       </c>
       <c r="AK18">
         <v>22</v>
@@ -5166,13 +5166,13 @@
         <v>42</v>
       </c>
       <c r="AM18">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AN18">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO18">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP18">
         <v>16.5</v>
@@ -5181,10 +5181,10 @@
         <v>14.5</v>
       </c>
       <c r="AR18">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AS18">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="AT18">
         <v>11.5</v>
@@ -5202,7 +5202,7 @@
         <v>14.5</v>
       </c>
       <c r="AY18">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ18">
         <v>13</v>
@@ -5214,37 +5214,37 @@
         <v>22</v>
       </c>
       <c r="BC18">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD18">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="BE18">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BF18">
         <v>11.5</v>
       </c>
       <c r="BG18">
-        <v>19.5</v>
+        <v>10</v>
       </c>
       <c r="BH18">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI18">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ18">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK18">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BN18">
         <v>5.1</v>
@@ -5256,31 +5256,31 @@
         <v>14.5</v>
       </c>
       <c r="BQ18">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="BR18">
         <v>24</v>
       </c>
       <c r="BS18">
+        <v>9.6</v>
+      </c>
+      <c r="BT18">
+        <v>7</v>
+      </c>
+      <c r="BU18">
+        <v>4.8</v>
+      </c>
+      <c r="BV18">
+        <v>26</v>
+      </c>
+      <c r="BW18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX18">
+        <v>34</v>
+      </c>
+      <c r="BY18">
         <v>10.5</v>
-      </c>
-      <c r="BT18">
-        <v>6.8</v>
-      </c>
-      <c r="BU18">
-        <v>5.7</v>
-      </c>
-      <c r="BV18">
-        <v>25</v>
-      </c>
-      <c r="BW18">
-        <v>10.5</v>
-      </c>
-      <c r="BX18">
-        <v>32</v>
-      </c>
-      <c r="BY18">
-        <v>12</v>
       </c>
       <c r="BZ18">
         <v>0</v>
@@ -5309,25 +5309,25 @@
         <v>176</v>
       </c>
       <c r="F19">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="G19">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="H19">
+        <v>4.2</v>
+      </c>
+      <c r="I19">
         <v>4.4</v>
       </c>
-      <c r="I19">
-        <v>4.8</v>
-      </c>
       <c r="J19">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K19">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L19">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M19">
         <v>1.03</v>
@@ -5339,13 +5339,13 @@
         <v>1.14</v>
       </c>
       <c r="P19">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q19">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R19">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="S19">
         <v>2.16</v>
@@ -5354,25 +5354,25 @@
         <v>1.51</v>
       </c>
       <c r="U19">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V19">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W19">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="X19">
         <v>34</v>
       </c>
       <c r="Y19">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z19">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA19">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB19">
         <v>15.5</v>
@@ -5381,13 +5381,13 @@
         <v>11.5</v>
       </c>
       <c r="AD19">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE19">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF19">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG19">
         <v>10.5</v>
@@ -5396,7 +5396,7 @@
         <v>15.5</v>
       </c>
       <c r="AI19">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ19">
         <v>21</v>
@@ -5408,13 +5408,13 @@
         <v>21</v>
       </c>
       <c r="AM19">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN19">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO19">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AP19">
         <v>30</v>
@@ -5423,109 +5423,109 @@
         <v>26</v>
       </c>
       <c r="AR19">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AS19">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AT19">
         <v>14</v>
       </c>
       <c r="AU19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV19">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW19">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AX19">
         <v>14</v>
       </c>
       <c r="AY19">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ19">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA19">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BB19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC19">
         <v>14.5</v>
       </c>
       <c r="BD19">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE19">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BF19">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG19">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BH19">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BI19">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ19">
         <v>9</v>
       </c>
       <c r="BK19">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL19">
         <v>65</v>
       </c>
       <c r="BM19">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN19">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BO19">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP19">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ19">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="BR19">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BS19">
         <v>7</v>
       </c>
       <c r="BT19">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BU19">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BV19">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BW19">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BX19">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY19">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BZ19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CA19">
         <v>5.7</v>
@@ -5551,10 +5551,10 @@
         <v>177</v>
       </c>
       <c r="F20">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G20">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H20">
         <v>5</v>
@@ -5563,10 +5563,10 @@
         <v>6.2</v>
       </c>
       <c r="J20">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K20">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L20">
         <v>1.55</v>
@@ -5575,34 +5575,34 @@
         <v>1.15</v>
       </c>
       <c r="N20">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O20">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="P20">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q20">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="R20">
         <v>1.14</v>
       </c>
       <c r="S20">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="T20">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="U20">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="V20">
         <v>1.2</v>
       </c>
       <c r="W20">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X20">
         <v>7.8</v>
@@ -5617,13 +5617,13 @@
         <v>900</v>
       </c>
       <c r="AB20">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AC20">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD20">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AE20">
         <v>700</v>
@@ -5632,16 +5632,16 @@
         <v>11</v>
       </c>
       <c r="AG20">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH20">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AI20">
         <v>700</v>
       </c>
       <c r="AJ20">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AK20">
         <v>48</v>
@@ -5653,64 +5653,64 @@
         <v>500</v>
       </c>
       <c r="AN20">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO20">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AP20">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR20">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AS20">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AT20">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU20">
         <v>6.6</v>
       </c>
       <c r="AV20">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW20">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX20">
         <v>8.6</v>
       </c>
       <c r="AY20">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ20">
         <v>15</v>
       </c>
       <c r="BA20">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BB20">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BC20">
         <v>13.5</v>
       </c>
       <c r="BD20">
+        <v>7.8</v>
+      </c>
+      <c r="BE20">
+        <v>8.6</v>
+      </c>
+      <c r="BF20">
+        <v>10</v>
+      </c>
+      <c r="BG20">
         <v>8.4</v>
-      </c>
-      <c r="BE20">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF20">
-        <v>7.6</v>
-      </c>
-      <c r="BG20">
-        <v>9</v>
       </c>
       <c r="BH20">
         <v>2.58</v>
@@ -5719,7 +5719,7 @@
         <v>2.22</v>
       </c>
       <c r="BJ20">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK20">
         <v>5.9</v>
@@ -5737,22 +5737,22 @@
         <v>3.75</v>
       </c>
       <c r="BP20">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ20">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT20">
         <v>9</v>
       </c>
       <c r="BU20">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BV20">
         <v>1000</v>
@@ -5764,13 +5764,13 @@
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB20" t="s">
         <v>195</v>
@@ -5793,73 +5793,73 @@
         <v>178</v>
       </c>
       <c r="F21">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="G21">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="H21">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="I21">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="J21">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="K21">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="L21">
         <v>1.64</v>
       </c>
       <c r="M21">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N21">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O21">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="P21">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q21">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="R21">
         <v>1.15</v>
       </c>
       <c r="S21">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T21">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U21">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V21">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W21">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="Y21">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z21">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AA21">
         <v>100</v>
       </c>
       <c r="AB21">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC21">
         <v>7.4</v>
@@ -5871,52 +5871,52 @@
         <v>95</v>
       </c>
       <c r="AF21">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AG21">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH21">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="AI21">
         <v>460</v>
       </c>
       <c r="AJ21">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="AK21">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AL21">
-        <v>290</v>
+        <v>460</v>
       </c>
       <c r="AM21">
         <v>500</v>
       </c>
       <c r="AN21">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AO21">
         <v>600</v>
       </c>
       <c r="AP21">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ21">
         <v>7</v>
       </c>
       <c r="AR21">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS21">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AT21">
         <v>7</v>
       </c>
       <c r="AU21">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV21">
         <v>12</v>
@@ -5934,7 +5934,7 @@
         <v>20</v>
       </c>
       <c r="BA21">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="BB21">
         <v>18</v>
@@ -5943,76 +5943,76 @@
         <v>20</v>
       </c>
       <c r="BD21">
-        <v>28</v>
+        <v>8.6</v>
       </c>
       <c r="BE21">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF21">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG21">
         <v>10.5</v>
       </c>
       <c r="BH21">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="BI21">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="BJ21">
         <v>12.5</v>
       </c>
       <c r="BK21">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BN21">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BO21">
         <v>4.5</v>
       </c>
       <c r="BP21">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT21">
         <v>6.2</v>
       </c>
       <c r="BU21">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV21">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
       </c>
       <c r="CA21">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB21" t="s">
         <v>195</v>
@@ -6035,22 +6035,22 @@
         <v>179</v>
       </c>
       <c r="F22">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G22">
         <v>3.55</v>
       </c>
       <c r="H22">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I22">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J22">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="K22">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="L22">
         <v>1.78</v>
@@ -6062,13 +6062,13 @@
         <v>2.06</v>
       </c>
       <c r="O22">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="P22">
         <v>1.34</v>
       </c>
       <c r="Q22">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R22">
         <v>1.12</v>
@@ -6077,16 +6077,16 @@
         <v>7.6</v>
       </c>
       <c r="T22">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U22">
         <v>1.57</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W22">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X22">
         <v>6.6</v>
@@ -6107,7 +6107,7 @@
         <v>7.4</v>
       </c>
       <c r="AD22">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE22">
         <v>500</v>
@@ -6116,10 +6116,10 @@
         <v>21</v>
       </c>
       <c r="AG22">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH22">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AI22">
         <v>500</v>
@@ -6128,7 +6128,7 @@
         <v>420</v>
       </c>
       <c r="AK22">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="AL22">
         <v>540</v>
@@ -6140,19 +6140,19 @@
         <v>120</v>
       </c>
       <c r="AO22">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP22">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AQ22">
         <v>6</v>
       </c>
       <c r="AR22">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS22">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT22">
         <v>6.4</v>
@@ -6164,7 +6164,7 @@
         <v>13</v>
       </c>
       <c r="AW22">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX22">
         <v>16.5</v>
@@ -6173,13 +6173,13 @@
         <v>14</v>
       </c>
       <c r="AZ22">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BA22">
         <v>8.199999999999999</v>
       </c>
       <c r="BB22">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC22">
         <v>7.8</v>
@@ -6197,64 +6197,64 @@
         <v>8</v>
       </c>
       <c r="BH22">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BI22">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BJ22">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK22">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BN22">
         <v>6.4</v>
       </c>
       <c r="BO22">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BT22">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU22">
         <v>4.8</v>
       </c>
       <c r="BV22">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CB22" t="s">
         <v>195</v>
@@ -6277,79 +6277,79 @@
         <v>180</v>
       </c>
       <c r="F23">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="G23">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="H23">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="I23">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K23">
         <v>4.2</v>
       </c>
       <c r="L23">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M23">
         <v>1.07</v>
       </c>
       <c r="N23">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O23">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P23">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q23">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="R23">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S23">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T23">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="U23">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V23">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W23">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="X23">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y23">
+        <v>20</v>
+      </c>
+      <c r="Z23">
+        <v>44</v>
+      </c>
+      <c r="AA23">
+        <v>140</v>
+      </c>
+      <c r="AB23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC23">
+        <v>9.6</v>
+      </c>
+      <c r="AD23">
         <v>21</v>
-      </c>
-      <c r="Z23">
-        <v>46</v>
-      </c>
-      <c r="AA23">
-        <v>160</v>
-      </c>
-      <c r="AB23">
-        <v>9</v>
-      </c>
-      <c r="AC23">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD23">
-        <v>23</v>
       </c>
       <c r="AE23">
         <v>90</v>
@@ -6358,91 +6358,91 @@
         <v>10.5</v>
       </c>
       <c r="AG23">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH23">
         <v>21</v>
       </c>
       <c r="AI23">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ23">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK23">
         <v>18</v>
       </c>
       <c r="AL23">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM23">
-        <v>390</v>
+        <v>110</v>
       </c>
       <c r="AN23">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO23">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AP23">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ23">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR23">
         <v>38</v>
       </c>
       <c r="AS23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AT23">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU23">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV23">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW23">
         <v>55</v>
       </c>
       <c r="AX23">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY23">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA23">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB23">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC23">
         <v>16</v>
       </c>
       <c r="BD23">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE23">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BF23">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG23">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BH23">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI23">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="BJ23">
         <v>10.5</v>
@@ -6457,46 +6457,46 @@
         <v>10.5</v>
       </c>
       <c r="BN23">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO23">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BP23">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ23">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR23">
         <v>27</v>
       </c>
       <c r="BS23">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT23">
+        <v>9</v>
+      </c>
+      <c r="BU23">
+        <v>5.1</v>
+      </c>
+      <c r="BV23">
+        <v>46</v>
+      </c>
+      <c r="BW23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
         <v>9.4</v>
       </c>
-      <c r="BU23">
-        <v>5.2</v>
-      </c>
-      <c r="BV23">
-        <v>50</v>
-      </c>
-      <c r="BW23">
-        <v>9.6</v>
-      </c>
-      <c r="BX23">
-        <v>1000</v>
-      </c>
-      <c r="BY23">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BZ23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA23">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB23" t="s">
         <v>195</v>
@@ -6519,73 +6519,73 @@
         <v>181</v>
       </c>
       <c r="F24">
+        <v>3.4</v>
+      </c>
+      <c r="G24">
+        <v>3.5</v>
+      </c>
+      <c r="H24">
+        <v>2.44</v>
+      </c>
+      <c r="I24">
+        <v>2.48</v>
+      </c>
+      <c r="J24">
         <v>3.25</v>
       </c>
-      <c r="G24">
-        <v>3.4</v>
-      </c>
-      <c r="H24">
-        <v>2.48</v>
-      </c>
-      <c r="I24">
-        <v>2.54</v>
-      </c>
-      <c r="J24">
-        <v>3.35</v>
-      </c>
       <c r="K24">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L24">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M24">
         <v>1.1</v>
       </c>
       <c r="N24">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O24">
         <v>1.4</v>
       </c>
       <c r="P24">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q24">
         <v>2.22</v>
       </c>
       <c r="R24">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S24">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T24">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="U24">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V24">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W24">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X24">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y24">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z24">
         <v>15</v>
       </c>
       <c r="AA24">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB24">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC24">
         <v>7.4</v>
@@ -6594,7 +6594,7 @@
         <v>11.5</v>
       </c>
       <c r="AE24">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF24">
         <v>22</v>
@@ -6603,10 +6603,10 @@
         <v>14.5</v>
       </c>
       <c r="AH24">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI24">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ24">
         <v>65</v>
@@ -6618,40 +6618,40 @@
         <v>60</v>
       </c>
       <c r="AM24">
-        <v>450</v>
+        <v>130</v>
       </c>
       <c r="AN24">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AO24">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP24">
         <v>10</v>
       </c>
       <c r="AQ24">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR24">
         <v>13</v>
       </c>
       <c r="AS24">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU24">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV24">
         <v>10.5</v>
       </c>
       <c r="AW24">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AX24">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY24">
         <v>12.5</v>
@@ -6663,40 +6663,40 @@
         <v>40</v>
       </c>
       <c r="BB24">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BC24">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD24">
         <v>46</v>
       </c>
       <c r="BE24">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF24">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BG24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH24">
         <v>3.05</v>
       </c>
       <c r="BI24">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="BJ24">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK24">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BN24">
         <v>6.2</v>
@@ -6705,40 +6705,40 @@
         <v>5.6</v>
       </c>
       <c r="BP24">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BQ24">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS24">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BT24">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU24">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV24">
         <v>20</v>
       </c>
       <c r="BW24">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY24">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BZ24">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA24">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CB24" t="s">
         <v>195</v>
@@ -6761,25 +6761,25 @@
         <v>182</v>
       </c>
       <c r="F25">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="G25">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="H25">
+        <v>4.5</v>
+      </c>
+      <c r="I25">
+        <v>4.9</v>
+      </c>
+      <c r="J25">
         <v>4.3</v>
-      </c>
-      <c r="I25">
-        <v>4.4</v>
-      </c>
-      <c r="J25">
-        <v>4</v>
       </c>
       <c r="K25">
         <v>4.5</v>
       </c>
       <c r="L25">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M25">
         <v>1.04</v>
@@ -6794,142 +6794,142 @@
         <v>2.5</v>
       </c>
       <c r="Q25">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="R25">
+        <v>1.6</v>
+      </c>
+      <c r="S25">
+        <v>2.54</v>
+      </c>
+      <c r="T25">
         <v>1.59</v>
-      </c>
-      <c r="S25">
-        <v>2.56</v>
-      </c>
-      <c r="T25">
-        <v>1.58</v>
       </c>
       <c r="U25">
         <v>2.42</v>
       </c>
       <c r="V25">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W25">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="X25">
         <v>25</v>
       </c>
       <c r="Y25">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z25">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AA25">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AB25">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC25">
         <v>10.5</v>
       </c>
       <c r="AD25">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AE25">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AF25">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG25">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH25">
         <v>17</v>
       </c>
       <c r="AI25">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AJ25">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AK25">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AL25">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AM25">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AN25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO25">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AP25">
         <v>20</v>
       </c>
       <c r="AQ25">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR25">
-        <v>16.5</v>
+        <v>34</v>
       </c>
       <c r="AS25">
-        <v>8.800000000000001</v>
+        <v>60</v>
       </c>
       <c r="AT25">
         <v>11</v>
       </c>
       <c r="AU25">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV25">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW25">
-        <v>17.5</v>
+        <v>42</v>
       </c>
       <c r="AX25">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY25">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ25">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA25">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="BB25">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC25">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD25">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="BE25">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="BF25">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BG25">
-        <v>7.6</v>
+        <v>27</v>
       </c>
       <c r="BH25">
         <v>4.5</v>
       </c>
       <c r="BI25">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BJ25">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK25">
         <v>5.2</v>
@@ -6938,43 +6938,43 @@
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN25">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BO25">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BP25">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BQ25">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BR25">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS25">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT25">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BU25">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BV25">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BW25">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX25">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BY25">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ25">
         <v>0</v>
@@ -7003,22 +7003,22 @@
         <v>183</v>
       </c>
       <c r="F26">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="G26">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="H26">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="I26">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K26">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L26">
         <v>1.36</v>
@@ -7027,64 +7027,64 @@
         <v>1.06</v>
       </c>
       <c r="N26">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O26">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P26">
         <v>2.14</v>
       </c>
       <c r="Q26">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R26">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S26">
         <v>3.1</v>
       </c>
       <c r="T26">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="U26">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="V26">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W26">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="X26">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y26">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z26">
         <v>60</v>
       </c>
       <c r="AA26">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AB26">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC26">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD26">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE26">
-        <v>260</v>
+        <v>400</v>
       </c>
       <c r="AF26">
+        <v>9.4</v>
+      </c>
+      <c r="AG26">
         <v>10.5</v>
-      </c>
-      <c r="AG26">
-        <v>10</v>
       </c>
       <c r="AH26">
         <v>22</v>
@@ -7093,76 +7093,76 @@
         <v>260</v>
       </c>
       <c r="AJ26">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AK26">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL26">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM26">
-        <v>580</v>
+        <v>390</v>
       </c>
       <c r="AN26">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AO26">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="AP26">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ26">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR26">
         <v>40</v>
       </c>
       <c r="AS26">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="AT26">
+        <v>8</v>
+      </c>
+      <c r="AU26">
+        <v>9</v>
+      </c>
+      <c r="AV26">
+        <v>22</v>
+      </c>
+      <c r="AW26">
+        <v>55</v>
+      </c>
+      <c r="AX26">
         <v>8.4</v>
       </c>
-      <c r="AU26">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV26">
+      <c r="AY26">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ26">
         <v>20</v>
       </c>
-      <c r="AW26">
+      <c r="BA26">
         <v>50</v>
       </c>
-      <c r="AX26">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY26">
-        <v>9</v>
-      </c>
-      <c r="AZ26">
-        <v>19</v>
-      </c>
-      <c r="BA26">
-        <v>46</v>
-      </c>
       <c r="BB26">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC26">
         <v>14.5</v>
       </c>
       <c r="BD26">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE26">
         <v>80</v>
       </c>
       <c r="BF26">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG26">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH26">
         <v>3.8</v>
@@ -7171,10 +7171,10 @@
         <v>3.15</v>
       </c>
       <c r="BJ26">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BK26">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL26">
         <v>1000</v>
@@ -7183,16 +7183,16 @@
         <v>100</v>
       </c>
       <c r="BN26">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BO26">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BP26">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BQ26">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR26">
         <v>24</v>
@@ -7201,28 +7201,28 @@
         <v>10</v>
       </c>
       <c r="BT26">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BU26">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ26">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA26">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="CB26" t="s">
         <v>195</v>
@@ -7245,22 +7245,22 @@
         <v>184</v>
       </c>
       <c r="F27">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="G27">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="H27">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="I27">
+        <v>3.95</v>
+      </c>
+      <c r="J27">
         <v>4.4</v>
       </c>
-      <c r="J27">
-        <v>4.5</v>
-      </c>
       <c r="K27">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L27">
         <v>1.23</v>
@@ -7269,10 +7269,10 @@
         <v>1.02</v>
       </c>
       <c r="N27">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O27">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P27">
         <v>3.25</v>
@@ -7281,25 +7281,25 @@
         <v>1.42</v>
       </c>
       <c r="R27">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="S27">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T27">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="U27">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V27">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="X27">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Y27">
         <v>29</v>
@@ -7308,10 +7308,10 @@
         <v>42</v>
       </c>
       <c r="AA27">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AB27">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AC27">
         <v>12.5</v>
@@ -7320,91 +7320,91 @@
         <v>18.5</v>
       </c>
       <c r="AE27">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF27">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG27">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH27">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI27">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ27">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK27">
         <v>16.5</v>
       </c>
       <c r="AL27">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM27">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN27">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO27">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP27">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AQ27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR27">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS27">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AT27">
+        <v>17</v>
+      </c>
+      <c r="AU27">
+        <v>10.5</v>
+      </c>
+      <c r="AV27">
         <v>15.5</v>
       </c>
-      <c r="AU27">
-        <v>11</v>
-      </c>
-      <c r="AV27">
+      <c r="AW27">
+        <v>32</v>
+      </c>
+      <c r="AX27">
         <v>16</v>
-      </c>
-      <c r="AW27">
-        <v>34</v>
-      </c>
-      <c r="AX27">
-        <v>15</v>
       </c>
       <c r="AY27">
         <v>10</v>
       </c>
       <c r="AZ27">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA27">
         <v>30</v>
       </c>
       <c r="BB27">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BC27">
         <v>14</v>
       </c>
       <c r="BD27">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BE27">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF27">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BG27">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BH27">
         <v>5.4</v>
@@ -7413,49 +7413,49 @@
         <v>4.8</v>
       </c>
       <c r="BJ27">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK27">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BL27">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BM27">
         <v>46</v>
       </c>
       <c r="BN27">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BO27">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP27">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BQ27">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR27">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BS27">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT27">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU27">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV27">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BW27">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX27">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BY27">
         <v>10.5</v>
@@ -7487,127 +7487,127 @@
         <v>185</v>
       </c>
       <c r="F28">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="G28">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="H28">
+        <v>5.9</v>
+      </c>
+      <c r="I28">
         <v>6.8</v>
-      </c>
-      <c r="I28">
-        <v>8</v>
       </c>
       <c r="J28">
         <v>3.5</v>
       </c>
       <c r="K28">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L28">
         <v>1.53</v>
       </c>
       <c r="M28">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N28">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="O28">
         <v>1.48</v>
       </c>
       <c r="P28">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Q28">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R28">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S28">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T28">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="U28">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="V28">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W28">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y28">
         <v>17.5</v>
       </c>
       <c r="Z28">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AA28">
         <v>900</v>
       </c>
       <c r="AB28">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC28">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD28">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AE28">
-        <v>700</v>
+        <v>260</v>
       </c>
       <c r="AF28">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG28">
         <v>11</v>
       </c>
       <c r="AH28">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI28">
-        <v>700</v>
+        <v>190</v>
       </c>
       <c r="AJ28">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK28">
         <v>23</v>
       </c>
       <c r="AL28">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AM28">
         <v>700</v>
       </c>
       <c r="AN28">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AO28">
-        <v>460</v>
+        <v>600</v>
       </c>
       <c r="AP28">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ28">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR28">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AS28">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT28">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AU28">
         <v>7.6</v>
@@ -7616,49 +7616,49 @@
         <v>21</v>
       </c>
       <c r="AW28">
-        <v>12.5</v>
+        <v>55</v>
       </c>
       <c r="AX28">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY28">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ28">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA28">
-        <v>12.5</v>
+        <v>65</v>
       </c>
       <c r="BB28">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BC28">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD28">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BE28">
         <v>150</v>
       </c>
       <c r="BF28">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BG28">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BH28">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="BI28">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BJ28">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BK28">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL28">
         <v>1000</v>
@@ -7667,40 +7667,40 @@
         <v>200</v>
       </c>
       <c r="BN28">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BO28">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="BP28">
+        <v>13.5</v>
+      </c>
+      <c r="BQ28">
+        <v>7</v>
+      </c>
+      <c r="BR28">
+        <v>36</v>
+      </c>
+      <c r="BS28">
+        <v>10.5</v>
+      </c>
+      <c r="BT28">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU28">
+        <v>5.7</v>
+      </c>
+      <c r="BV28">
+        <v>1000</v>
+      </c>
+      <c r="BW28">
+        <v>12</v>
+      </c>
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
         <v>12.5</v>
-      </c>
-      <c r="BQ28">
-        <v>6.8</v>
-      </c>
-      <c r="BR28">
-        <v>38</v>
-      </c>
-      <c r="BS28">
-        <v>11</v>
-      </c>
-      <c r="BT28">
-        <v>10.5</v>
-      </c>
-      <c r="BU28">
-        <v>6.2</v>
-      </c>
-      <c r="BV28">
-        <v>1000</v>
-      </c>
-      <c r="BW28">
-        <v>13</v>
-      </c>
-      <c r="BX28">
-        <v>1000</v>
-      </c>
-      <c r="BY28">
-        <v>13.5</v>
       </c>
       <c r="BZ28">
         <v>0</v>
@@ -7729,16 +7729,16 @@
         <v>186</v>
       </c>
       <c r="F29">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G29">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H29">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I29">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="J29">
         <v>3.4</v>
@@ -7747,7 +7747,7 @@
         <v>3.6</v>
       </c>
       <c r="L29">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M29">
         <v>1.08</v>
@@ -7762,7 +7762,7 @@
         <v>1.81</v>
       </c>
       <c r="Q29">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R29">
         <v>1.31</v>
@@ -7771,13 +7771,13 @@
         <v>4</v>
       </c>
       <c r="T29">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U29">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V29">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W29">
         <v>1.33</v>
@@ -7798,7 +7798,7 @@
         <v>13</v>
       </c>
       <c r="AC29">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD29">
         <v>11.5</v>
@@ -7807,31 +7807,31 @@
         <v>25</v>
       </c>
       <c r="AF29">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AG29">
         <v>17</v>
       </c>
       <c r="AH29">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AI29">
         <v>55</v>
       </c>
       <c r="AJ29">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK29">
         <v>55</v>
       </c>
       <c r="AL29">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AM29">
         <v>390</v>
       </c>
       <c r="AN29">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO29">
         <v>21</v>
@@ -7846,22 +7846,22 @@
         <v>11</v>
       </c>
       <c r="AS29">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT29">
         <v>12</v>
       </c>
       <c r="AU29">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV29">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW29">
         <v>22</v>
       </c>
       <c r="AX29">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY29">
         <v>14.5</v>
@@ -7870,22 +7870,22 @@
         <v>17.5</v>
       </c>
       <c r="BA29">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB29">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC29">
         <v>44</v>
       </c>
       <c r="BD29">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE29">
         <v>80</v>
       </c>
       <c r="BF29">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BG29">
         <v>17.5</v>
@@ -7912,22 +7912,22 @@
         <v>7</v>
       </c>
       <c r="BO29">
+        <v>5</v>
+      </c>
+      <c r="BP29">
+        <v>1000</v>
+      </c>
+      <c r="BQ29">
+        <v>10.5</v>
+      </c>
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
+        <v>12</v>
+      </c>
+      <c r="BT29">
         <v>4.9</v>
-      </c>
-      <c r="BP29">
-        <v>1000</v>
-      </c>
-      <c r="BQ29">
-        <v>10</v>
-      </c>
-      <c r="BR29">
-        <v>1000</v>
-      </c>
-      <c r="BS29">
-        <v>11</v>
-      </c>
-      <c r="BT29">
-        <v>5</v>
       </c>
       <c r="BU29">
         <v>4.4</v>
@@ -7936,19 +7936,19 @@
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ29">
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB29" t="s">
         <v>195</v>
@@ -7980,10 +7980,10 @@
         <v>11.5</v>
       </c>
       <c r="I30">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="J30">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="K30">
         <v>6.6</v>
@@ -8007,10 +8007,10 @@
         <v>1.59</v>
       </c>
       <c r="R30">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S30">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T30">
         <v>2.04</v>
@@ -8022,7 +8022,7 @@
         <v>1.06</v>
       </c>
       <c r="W30">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="X30">
         <v>30</v>
@@ -8040,7 +8040,7 @@
         <v>9.4</v>
       </c>
       <c r="AC30">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD30">
         <v>950</v>
@@ -8052,7 +8052,7 @@
         <v>8.4</v>
       </c>
       <c r="AG30">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH30">
         <v>32</v>
@@ -8076,58 +8076,58 @@
         <v>5</v>
       </c>
       <c r="AO30">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AP30">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AQ30">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AR30">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AS30">
         <v>10</v>
       </c>
       <c r="AT30">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AU30">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AV30">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AW30">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AX30">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AY30">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AZ30">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA30">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BB30">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BC30">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BD30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BE30">
         <v>100</v>
       </c>
       <c r="BF30">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BG30">
         <v>10.5</v>
@@ -8213,10 +8213,10 @@
         <v>188</v>
       </c>
       <c r="F31">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G31">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H31">
         <v>4</v>
@@ -8228,10 +8228,10 @@
         <v>3.5</v>
       </c>
       <c r="K31">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L31">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M31">
         <v>1.09</v>
@@ -8255,7 +8255,7 @@
         <v>4</v>
       </c>
       <c r="T31">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U31">
         <v>2.02</v>
@@ -8264,7 +8264,7 @@
         <v>1.31</v>
       </c>
       <c r="W31">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X31">
         <v>12.5</v>
@@ -8276,10 +8276,10 @@
         <v>30</v>
       </c>
       <c r="AA31">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AB31">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC31">
         <v>8</v>
@@ -8288,22 +8288,22 @@
         <v>17</v>
       </c>
       <c r="AE31">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AF31">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG31">
         <v>11</v>
       </c>
       <c r="AH31">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI31">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="AJ31">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK31">
         <v>25</v>
@@ -8330,19 +8330,19 @@
         <v>25</v>
       </c>
       <c r="AS31">
-        <v>10.5</v>
+        <v>46</v>
       </c>
       <c r="AT31">
         <v>7.4</v>
       </c>
       <c r="AU31">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV31">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW31">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AX31">
         <v>10.5</v>
@@ -8351,7 +8351,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ31">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA31">
         <v>46</v>
@@ -8369,10 +8369,10 @@
         <v>95</v>
       </c>
       <c r="BF31">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BG31">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="BH31">
         <v>3.15</v>
@@ -8384,7 +8384,7 @@
         <v>10.5</v>
       </c>
       <c r="BK31">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL31">
         <v>1000</v>
@@ -8393,46 +8393,46 @@
         <v>120</v>
       </c>
       <c r="BN31">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO31">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP31">
         <v>15.5</v>
       </c>
       <c r="BQ31">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR31">
         <v>34</v>
       </c>
       <c r="BS31">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT31">
         <v>7.6</v>
       </c>
       <c r="BU31">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV31">
         <v>38</v>
       </c>
       <c r="BW31">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX31">
         <v>55</v>
       </c>
       <c r="BY31">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ31">
         <v>32</v>
       </c>
       <c r="CA31">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB31" t="s">
         <v>195</v>
@@ -8467,7 +8467,7 @@
         <v>4.2</v>
       </c>
       <c r="J32">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K32">
         <v>3.4</v>
@@ -8479,19 +8479,19 @@
         <v>1.1</v>
       </c>
       <c r="N32">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O32">
         <v>1.45</v>
       </c>
       <c r="P32">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q32">
         <v>2.36</v>
       </c>
       <c r="R32">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S32">
         <v>4.6</v>
@@ -8509,7 +8509,7 @@
         <v>1.84</v>
       </c>
       <c r="X32">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y32">
         <v>12.5</v>
@@ -8521,19 +8521,19 @@
         <v>110</v>
       </c>
       <c r="AB32">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC32">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD32">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE32">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AF32">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG32">
         <v>11.5</v>
@@ -8542,10 +8542,10 @@
         <v>21</v>
       </c>
       <c r="AI32">
-        <v>370</v>
+        <v>170</v>
       </c>
       <c r="AJ32">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK32">
         <v>27</v>
@@ -8560,10 +8560,10 @@
         <v>23</v>
       </c>
       <c r="AO32">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="AP32">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ32">
         <v>11</v>
@@ -8599,7 +8599,7 @@
         <v>65</v>
       </c>
       <c r="BB32">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC32">
         <v>23</v>
@@ -8614,19 +8614,19 @@
         <v>20</v>
       </c>
       <c r="BG32">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BH32">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI32">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ32">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK32">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BL32">
         <v>1000</v>
@@ -8635,46 +8635,46 @@
         <v>130</v>
       </c>
       <c r="BN32">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO32">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP32">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ32">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR32">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS32">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT32">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU32">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV32">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW32">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX32">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY32">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ32">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA32">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="CB32" t="s">
         <v>195</v>
@@ -8697,70 +8697,70 @@
         <v>190</v>
       </c>
       <c r="F33">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G33">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H33">
+        <v>4.5</v>
+      </c>
+      <c r="I33">
         <v>4.6</v>
-      </c>
-      <c r="I33">
-        <v>4.7</v>
       </c>
       <c r="J33">
         <v>3.3</v>
       </c>
       <c r="K33">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L33">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M33">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N33">
         <v>2.7</v>
       </c>
       <c r="O33">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P33">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q33">
         <v>2.72</v>
       </c>
       <c r="R33">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S33">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="T33">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U33">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V33">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W33">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X33">
         <v>8.800000000000001</v>
       </c>
       <c r="Y33">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z33">
         <v>32</v>
       </c>
       <c r="AA33">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB33">
         <v>6.8</v>
@@ -8778,7 +8778,7 @@
         <v>11.5</v>
       </c>
       <c r="AG33">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH33">
         <v>26</v>
@@ -8787,37 +8787,37 @@
         <v>110</v>
       </c>
       <c r="AJ33">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AK33">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL33">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM33">
         <v>500</v>
       </c>
       <c r="AN33">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO33">
         <v>140</v>
       </c>
       <c r="AP33">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ33">
         <v>10.5</v>
       </c>
       <c r="AR33">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS33">
         <v>90</v>
       </c>
       <c r="AT33">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU33">
         <v>7</v>
@@ -8829,19 +8829,19 @@
         <v>55</v>
       </c>
       <c r="AX33">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY33">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ33">
         <v>23</v>
       </c>
       <c r="BA33">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB33">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC33">
         <v>26</v>
@@ -8856,19 +8856,19 @@
         <v>24</v>
       </c>
       <c r="BG33">
-        <v>46</v>
+        <v>18.5</v>
       </c>
       <c r="BH33">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BI33">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ33">
         <v>11.5</v>
       </c>
       <c r="BK33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BL33">
         <v>1000</v>
@@ -8886,16 +8886,16 @@
         <v>17</v>
       </c>
       <c r="BQ33">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR33">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS33">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT33">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU33">
         <v>6.8</v>
@@ -8904,19 +8904,19 @@
         <v>48</v>
       </c>
       <c r="BW33">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BX33">
         <v>70</v>
       </c>
       <c r="BY33">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BZ33">
         <v>44</v>
       </c>
       <c r="CA33">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CB33" t="s">
         <v>195</v>
@@ -8939,22 +8939,22 @@
         <v>191</v>
       </c>
       <c r="F34">
+        <v>2.08</v>
+      </c>
+      <c r="G34">
         <v>2.18</v>
       </c>
-      <c r="G34">
-        <v>2.3</v>
-      </c>
       <c r="H34">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="I34">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="J34">
         <v>3.55</v>
       </c>
       <c r="K34">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L34">
         <v>1.37</v>
@@ -8963,64 +8963,64 @@
         <v>1.06</v>
       </c>
       <c r="N34">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O34">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P34">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q34">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R34">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S34">
         <v>3.1</v>
       </c>
       <c r="T34">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U34">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V34">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W34">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="X34">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y34">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z34">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA34">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AB34">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC34">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD34">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE34">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AF34">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AG34">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AH34">
         <v>17.5</v>
@@ -9029,88 +9029,88 @@
         <v>65</v>
       </c>
       <c r="AJ34">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK34">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL34">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM34">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN34">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO34">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AP34">
         <v>14.5</v>
       </c>
       <c r="AQ34">
+        <v>14</v>
+      </c>
+      <c r="AR34">
+        <v>21</v>
+      </c>
+      <c r="AS34">
+        <v>42</v>
+      </c>
+      <c r="AT34">
+        <v>9</v>
+      </c>
+      <c r="AU34">
+        <v>7.6</v>
+      </c>
+      <c r="AV34">
         <v>13</v>
       </c>
-      <c r="AR34">
-        <v>19.5</v>
-      </c>
-      <c r="AS34">
-        <v>44</v>
-      </c>
-      <c r="AT34">
-        <v>9.4</v>
-      </c>
-      <c r="AU34">
-        <v>7.4</v>
-      </c>
-      <c r="AV34">
-        <v>12.5</v>
-      </c>
       <c r="AW34">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AX34">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AY34">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ34">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA34">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BB34">
         <v>21</v>
       </c>
       <c r="BC34">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD34">
         <v>26</v>
       </c>
       <c r="BE34">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="BF34">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BG34">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BH34">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI34">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ34">
         <v>9.6</v>
       </c>
       <c r="BK34">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BL34">
         <v>1000</v>
@@ -9119,16 +9119,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN34">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO34">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BP34">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BQ34">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BR34">
         <v>28</v>
@@ -9137,13 +9137,13 @@
         <v>7.4</v>
       </c>
       <c r="BT34">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU34">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV34">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BW34">
         <v>7.4</v>
@@ -9181,22 +9181,22 @@
         <v>192</v>
       </c>
       <c r="F35">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G35">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H35">
         <v>5.1</v>
       </c>
       <c r="I35">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J35">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K35">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L35">
         <v>1.45</v>
@@ -9205,7 +9205,7 @@
         <v>1.08</v>
       </c>
       <c r="N35">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O35">
         <v>1.38</v>
@@ -9223,13 +9223,13 @@
         <v>3.9</v>
       </c>
       <c r="T35">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U35">
         <v>1.9</v>
       </c>
       <c r="V35">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W35">
         <v>2.12</v>
@@ -9238,13 +9238,13 @@
         <v>12.5</v>
       </c>
       <c r="Y35">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="Z35">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA35">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB35">
         <v>7.6</v>
@@ -9253,10 +9253,10 @@
         <v>8.4</v>
       </c>
       <c r="AD35">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AE35">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF35">
         <v>10.5</v>
@@ -9265,10 +9265,10 @@
         <v>10.5</v>
       </c>
       <c r="AH35">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI35">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ35">
         <v>23</v>
@@ -9283,10 +9283,10 @@
         <v>160</v>
       </c>
       <c r="AN35">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO35">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AP35">
         <v>11</v>
@@ -9298,7 +9298,7 @@
         <v>30</v>
       </c>
       <c r="AS35">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT35">
         <v>6.8</v>
@@ -9325,16 +9325,16 @@
         <v>50</v>
       </c>
       <c r="BB35">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC35">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD35">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BE35">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF35">
         <v>12.5</v>
@@ -9346,22 +9346,22 @@
         <v>3.2</v>
       </c>
       <c r="BI35">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ35">
         <v>11</v>
       </c>
       <c r="BK35">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>2.3</v>
+        <v>14</v>
       </c>
       <c r="BN35">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO35">
         <v>3.5</v>
@@ -9370,37 +9370,37 @@
         <v>13</v>
       </c>
       <c r="BQ35">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR35">
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT35">
         <v>8.6</v>
       </c>
       <c r="BU35">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV35">
         <v>1000</v>
       </c>
       <c r="BW35">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BZ35">
         <v>1000</v>
       </c>
       <c r="CA35">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB35" t="s">
         <v>195</v>
@@ -9423,22 +9423,22 @@
         <v>193</v>
       </c>
       <c r="F36">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="G36">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="H36">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="I36">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="J36">
         <v>3.15</v>
       </c>
       <c r="K36">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L36">
         <v>1.54</v>
@@ -9447,16 +9447,16 @@
         <v>1.11</v>
       </c>
       <c r="N36">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="O36">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P36">
         <v>1.63</v>
       </c>
       <c r="Q36">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R36">
         <v>1.23</v>
@@ -9465,184 +9465,184 @@
         <v>4.8</v>
       </c>
       <c r="T36">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U36">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V36">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="W36">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="X36">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="Y36">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="Z36">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AA36">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AB36">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC36">
         <v>7.4</v>
       </c>
       <c r="AD36">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE36">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF36">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AG36">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AH36">
         <v>22</v>
       </c>
       <c r="AI36">
+        <v>75</v>
+      </c>
+      <c r="AJ36">
+        <v>140</v>
+      </c>
+      <c r="AK36">
         <v>65</v>
       </c>
-      <c r="AJ36">
-        <v>80</v>
-      </c>
-      <c r="AK36">
-        <v>60</v>
-      </c>
       <c r="AL36">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AM36">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN36">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AO36">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AP36">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ36">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR36">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS36">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="AT36">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU36">
         <v>6.2</v>
       </c>
       <c r="AV36">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW36">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AX36">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY36">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ36">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA36">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="BB36">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="BC36">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BD36">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="BE36">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="BF36">
-        <v>8.4</v>
+        <v>55</v>
       </c>
       <c r="BG36">
-        <v>7.6</v>
+        <v>17.5</v>
       </c>
       <c r="BH36">
         <v>2.9</v>
       </c>
       <c r="BI36">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BJ36">
         <v>11.5</v>
       </c>
       <c r="BK36">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
+        <v>12</v>
+      </c>
+      <c r="BN36">
+        <v>7</v>
+      </c>
+      <c r="BO36">
+        <v>5.5</v>
+      </c>
+      <c r="BP36">
+        <v>38</v>
+      </c>
+      <c r="BQ36">
+        <v>9.6</v>
+      </c>
+      <c r="BR36">
+        <v>60</v>
+      </c>
+      <c r="BS36">
         <v>10.5</v>
       </c>
-      <c r="BN36">
-        <v>6.6</v>
-      </c>
-      <c r="BO36">
+      <c r="BT36">
         <v>5</v>
-      </c>
-      <c r="BP36">
-        <v>34</v>
-      </c>
-      <c r="BQ36">
-        <v>8.4</v>
-      </c>
-      <c r="BR36">
-        <v>55</v>
-      </c>
-      <c r="BS36">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT36">
-        <v>5.4</v>
       </c>
       <c r="BU36">
         <v>4.1</v>
       </c>
       <c r="BV36">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="BW36">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX36">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BY36">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ36">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="CA36">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB36" t="s">
         <v>195</v>
@@ -9665,13 +9665,13 @@
         <v>194</v>
       </c>
       <c r="F37">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G37">
         <v>2.62</v>
       </c>
       <c r="H37">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I37">
         <v>3.2</v>
@@ -9680,7 +9680,7 @@
         <v>3.3</v>
       </c>
       <c r="K37">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L37">
         <v>1.46</v>
@@ -9692,7 +9692,7 @@
         <v>3.3</v>
       </c>
       <c r="O37">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P37">
         <v>1.8</v>
@@ -9707,7 +9707,7 @@
         <v>4</v>
       </c>
       <c r="T37">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U37">
         <v>2.06</v>
@@ -9719,7 +9719,7 @@
         <v>1.61</v>
       </c>
       <c r="X37">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y37">
         <v>11</v>
@@ -9728,13 +9728,13 @@
         <v>21</v>
       </c>
       <c r="AA37">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB37">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC37">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD37">
         <v>13.5</v>
@@ -9743,10 +9743,10 @@
         <v>40</v>
       </c>
       <c r="AF37">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG37">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH37">
         <v>22</v>
@@ -9758,7 +9758,7 @@
         <v>38</v>
       </c>
       <c r="AK37">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL37">
         <v>60</v>
@@ -9776,16 +9776,16 @@
         <v>10.5</v>
       </c>
       <c r="AQ37">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR37">
         <v>18.5</v>
       </c>
       <c r="AS37">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AT37">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU37">
         <v>6.8</v>
@@ -9800,16 +9800,16 @@
         <v>14.5</v>
       </c>
       <c r="AY37">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ37">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA37">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BB37">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC37">
         <v>27</v>
@@ -9821,7 +9821,7 @@
         <v>80</v>
       </c>
       <c r="BF37">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BG37">
         <v>26</v>
@@ -9830,61 +9830,61 @@
         <v>3.15</v>
       </c>
       <c r="BI37">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BJ37">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK37">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BL37">
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BN37">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO37">
         <v>4.1</v>
       </c>
       <c r="BP37">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ37">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR37">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS37">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT37">
         <v>6.4</v>
       </c>
       <c r="BU37">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV37">
         <v>1000</v>
       </c>
       <c r="BW37">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BX37">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY37">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BZ37">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA37">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="CB37" t="s">
         <v>195</v>
